--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="122">
   <si>
     <t>CUMA</t>
   </si>
@@ -333,9 +333,6 @@
     <t>Sultanahmet</t>
   </si>
   <si>
-    <t>15.06.2026 Pazartesi</t>
-  </si>
-  <si>
     <t>CUMHURBAŞKANLIĞI</t>
   </si>
   <si>
@@ -413,6 +410,12 @@
   </si>
   <si>
     <t>TEK.SAND. BASKETBOL</t>
+  </si>
+  <si>
+    <t>TRT World</t>
+  </si>
+  <si>
+    <t>15 Temmuz Anıtı</t>
   </si>
 </sst>
 </file>
@@ -1540,7 +1543,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1822,75 +1825,96 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="41" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="42" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="41" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="42" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="39" fillId="9" borderId="11" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1909,36 +1933,54 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2038,21 +2080,6 @@
     <xf numFmtId="49" fontId="40" fillId="9" borderId="33" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="6" borderId="32" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="6" borderId="33" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2089,15 +2116,6 @@
     <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="40" fillId="4" borderId="38" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2107,18 +2125,6 @@
     <xf numFmtId="49" fontId="40" fillId="4" borderId="40" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2135,12 +2141,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="9" borderId="35" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2155,16 +2155,10 @@
     <xf numFmtId="49" fontId="39" fillId="9" borderId="33" xfId="57" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="6" borderId="32" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="6" borderId="33" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2539,7 +2533,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="2" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="180" row="3" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2565,197 +2559,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.7109375" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" customWidth="1"/>
-    <col min="17" max="17" width="1.7109375" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" customWidth="1"/>
-    <col min="21" max="21" width="1.7109375" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" customWidth="1"/>
-    <col min="23" max="23" width="20.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="1.7109375" customWidth="1"/>
-    <col min="26" max="26" width="2.7109375" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" customWidth="1"/>
-    <col min="29" max="29" width="1.7109375" customWidth="1"/>
-    <col min="30" max="30" width="2.7109375" customWidth="1"/>
-    <col min="31" max="31" width="20.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.7109375" customWidth="1"/>
-    <col min="33" max="33" width="1.7109375" customWidth="1"/>
-    <col min="34" max="34" width="2.7109375" customWidth="1"/>
-    <col min="35" max="35" width="20.7109375" customWidth="1"/>
-    <col min="36" max="36" width="6.7109375" customWidth="1"/>
-    <col min="37" max="37" width="1.7109375" customWidth="1"/>
-    <col min="38" max="38" width="2.7109375" customWidth="1"/>
-    <col min="39" max="39" width="20.7109375" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" customWidth="1"/>
-    <col min="41" max="41" width="2.7109375" customWidth="1"/>
-    <col min="42" max="42" width="16.7109375" customWidth="1"/>
-    <col min="43" max="43" width="3.7109375" customWidth="1"/>
-    <col min="44" max="44" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.6640625" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" customWidth="1"/>
+    <col min="17" max="17" width="1.6640625" customWidth="1"/>
+    <col min="18" max="18" width="2.6640625" customWidth="1"/>
+    <col min="19" max="19" width="20.6640625" customWidth="1"/>
+    <col min="20" max="20" width="6.6640625" customWidth="1"/>
+    <col min="21" max="21" width="1.6640625" customWidth="1"/>
+    <col min="22" max="22" width="2.6640625" customWidth="1"/>
+    <col min="23" max="23" width="20.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="1.6640625" customWidth="1"/>
+    <col min="26" max="26" width="2.6640625" customWidth="1"/>
+    <col min="27" max="27" width="20.6640625" customWidth="1"/>
+    <col min="28" max="28" width="6.6640625" customWidth="1"/>
+    <col min="29" max="29" width="1.6640625" customWidth="1"/>
+    <col min="30" max="30" width="2.6640625" customWidth="1"/>
+    <col min="31" max="31" width="20.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.6640625" customWidth="1"/>
+    <col min="33" max="33" width="1.6640625" customWidth="1"/>
+    <col min="34" max="34" width="2.6640625" customWidth="1"/>
+    <col min="35" max="35" width="20.6640625" customWidth="1"/>
+    <col min="36" max="36" width="6.6640625" customWidth="1"/>
+    <col min="37" max="37" width="1.6640625" customWidth="1"/>
+    <col min="38" max="38" width="2.6640625" customWidth="1"/>
+    <col min="39" max="39" width="20.6640625" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" customWidth="1"/>
+    <col min="41" max="41" width="2.6640625" customWidth="1"/>
+    <col min="42" max="42" width="16.6640625" customWidth="1"/>
+    <col min="43" max="43" width="3.6640625" customWidth="1"/>
+    <col min="44" max="44" width="8.33203125" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="147" t="s">
+      <c r="F1" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="147" t="s">
+      <c r="J1" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="147"/>
-      <c r="L1" s="148"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="161"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="151" t="s">
+      <c r="N1" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="145" t="s">
+      <c r="R1" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
+      <c r="S1" s="158"/>
+      <c r="T1" s="158"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="145" t="s">
+      <c r="V1" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
+      <c r="W1" s="158"/>
+      <c r="X1" s="158"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="145" t="s">
+      <c r="Z1" s="158" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="145"/>
-      <c r="AB1" s="145"/>
+      <c r="AA1" s="158"/>
+      <c r="AB1" s="158"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="145" t="s">
+      <c r="AD1" s="158" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="145"/>
+      <c r="AE1" s="158"/>
+      <c r="AF1" s="158"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="145" t="s">
+      <c r="AH1" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="145"/>
-      <c r="AJ1" s="145"/>
+      <c r="AI1" s="158"/>
+      <c r="AJ1" s="158"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="145" t="s">
+      <c r="AL1" s="158" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="145"/>
-      <c r="AN1" s="163"/>
+      <c r="AM1" s="158"/>
+      <c r="AN1" s="176"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="149">
+      <c r="B2" s="162">
         <f>N2-3</f>
         <v>46185</v>
       </c>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="150">
+      <c r="F2" s="163">
         <f>N2-2</f>
         <v>46186</v>
       </c>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="150">
+      <c r="J2" s="163">
         <f>N2-1</f>
         <v>46187</v>
       </c>
-      <c r="K2" s="150"/>
-      <c r="L2" s="158"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="171"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="154">
+      <c r="N2" s="167">
         <v>46188</v>
       </c>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="141">
+      <c r="R2" s="152">
         <f>N2+1</f>
         <v>46189</v>
       </c>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="141">
+      <c r="V2" s="152">
         <f>N2+2</f>
         <v>46190</v>
       </c>
-      <c r="W2" s="141"/>
-      <c r="X2" s="141"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="152"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="141">
+      <c r="Z2" s="152">
         <f>N2+3</f>
         <v>46191</v>
       </c>
-      <c r="AA2" s="141"/>
-      <c r="AB2" s="141"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="141">
+      <c r="AD2" s="152">
         <f>N2+4</f>
         <v>46192</v>
       </c>
-      <c r="AE2" s="141"/>
-      <c r="AF2" s="141"/>
+      <c r="AE2" s="152"/>
+      <c r="AF2" s="152"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="141">
+      <c r="AH2" s="152">
         <f>N2+5</f>
         <v>46193</v>
       </c>
-      <c r="AI2" s="141"/>
-      <c r="AJ2" s="141"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="152"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="141">
+      <c r="AL2" s="152">
         <f>N2+6</f>
         <v>46194</v>
       </c>
-      <c r="AM2" s="141"/>
-      <c r="AN2" s="164"/>
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="177"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2801,101 +2795,101 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="159"/>
-      <c r="K4" s="159"/>
-      <c r="L4" s="159"/>
+      <c r="B4" s="172"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="172"/>
+      <c r="I4" s="172"/>
+      <c r="J4" s="172"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="172"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="137" t="s">
+      <c r="N4" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="137"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
-      <c r="V4" s="137"/>
-      <c r="W4" s="137"/>
-      <c r="X4" s="137"/>
-      <c r="Y4" s="137"/>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="148"/>
+      <c r="Q4" s="148"/>
+      <c r="R4" s="148"/>
+      <c r="S4" s="148"/>
+      <c r="T4" s="148"/>
+      <c r="U4" s="148"/>
+      <c r="V4" s="148"/>
+      <c r="W4" s="148"/>
+      <c r="X4" s="148"/>
+      <c r="Y4" s="148"/>
+      <c r="Z4" s="148"/>
+      <c r="AA4" s="148"/>
+      <c r="AB4" s="148"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="159"/>
-      <c r="AE4" s="159"/>
-      <c r="AF4" s="159"/>
-      <c r="AG4" s="159"/>
-      <c r="AH4" s="159"/>
-      <c r="AI4" s="159"/>
-      <c r="AJ4" s="159"/>
-      <c r="AK4" s="159"/>
-      <c r="AL4" s="159"/>
-      <c r="AM4" s="159"/>
-      <c r="AN4" s="159"/>
+      <c r="AD4" s="172"/>
+      <c r="AE4" s="172"/>
+      <c r="AF4" s="172"/>
+      <c r="AG4" s="172"/>
+      <c r="AH4" s="172"/>
+      <c r="AI4" s="172"/>
+      <c r="AJ4" s="172"/>
+      <c r="AK4" s="172"/>
+      <c r="AL4" s="172"/>
+      <c r="AM4" s="172"/>
+      <c r="AN4" s="172"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
-      <c r="B5" s="159"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="159"/>
-      <c r="E5" s="159"/>
-      <c r="F5" s="159"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159"/>
-      <c r="I5" s="159"/>
-      <c r="J5" s="159"/>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159"/>
+      <c r="B5" s="172"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="172"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="137"/>
-      <c r="O5" s="137"/>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="137"/>
-      <c r="R5" s="137"/>
-      <c r="S5" s="137"/>
-      <c r="T5" s="137"/>
-      <c r="U5" s="137"/>
-      <c r="V5" s="137"/>
-      <c r="W5" s="137"/>
-      <c r="X5" s="137"/>
-      <c r="Y5" s="137"/>
-      <c r="Z5" s="137"/>
-      <c r="AA5" s="137"/>
-      <c r="AB5" s="137"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="148"/>
+      <c r="Q5" s="148"/>
+      <c r="R5" s="148"/>
+      <c r="S5" s="148"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="148"/>
+      <c r="V5" s="148"/>
+      <c r="W5" s="148"/>
+      <c r="X5" s="148"/>
+      <c r="Y5" s="148"/>
+      <c r="Z5" s="148"/>
+      <c r="AA5" s="148"/>
+      <c r="AB5" s="148"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="159"/>
-      <c r="AE5" s="159"/>
-      <c r="AF5" s="159"/>
-      <c r="AG5" s="159"/>
-      <c r="AH5" s="159"/>
-      <c r="AI5" s="159"/>
-      <c r="AJ5" s="159"/>
-      <c r="AK5" s="159"/>
-      <c r="AL5" s="159"/>
-      <c r="AM5" s="159"/>
-      <c r="AN5" s="159"/>
+      <c r="AD5" s="172"/>
+      <c r="AE5" s="172"/>
+      <c r="AF5" s="172"/>
+      <c r="AG5" s="172"/>
+      <c r="AH5" s="172"/>
+      <c r="AI5" s="172"/>
+      <c r="AJ5" s="172"/>
+      <c r="AK5" s="172"/>
+      <c r="AL5" s="172"/>
+      <c r="AM5" s="172"/>
+      <c r="AN5" s="172"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="74"/>
       <c r="C6" s="75"/>
       <c r="D6" s="54"/>
@@ -2917,7 +2911,7 @@
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="110" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O6" s="111"/>
       <c r="P6" s="34" t="s">
@@ -2940,10 +2934,10 @@
       <c r="AE6" s="111"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="135" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI6" s="136"/>
+      <c r="AH6" s="116" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI6" s="117"/>
       <c r="AJ6" s="58" t="s">
         <v>49</v>
       </c>
@@ -2960,45 +2954,45 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="87"/>
       <c r="C7" s="88"/>
       <c r="D7" s="55"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="153"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="166"/>
       <c r="H7" s="73"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="153"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="166"/>
       <c r="L7" s="73"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="119"/>
-      <c r="O7" s="120"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="126"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="119"/>
-      <c r="S7" s="120"/>
+      <c r="R7" s="125"/>
+      <c r="S7" s="126"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="119"/>
-      <c r="W7" s="120"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="126"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="119"/>
-      <c r="AA7" s="120"/>
+      <c r="Z7" s="125"/>
+      <c r="AA7" s="126"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="119"/>
-      <c r="AE7" s="120"/>
+      <c r="AD7" s="125"/>
+      <c r="AE7" s="126"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="119"/>
-      <c r="AI7" s="120"/>
+      <c r="AH7" s="125"/>
+      <c r="AI7" s="126"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="119"/>
-      <c r="AM7" s="120"/>
+      <c r="AL7" s="125"/>
+      <c r="AM7" s="126"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -3009,22 +3003,22 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="82"/>
       <c r="C8" s="83"/>
       <c r="D8" s="84"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="155" t="s">
+      <c r="F8" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="156"/>
-      <c r="H8" s="157"/>
+      <c r="G8" s="169"/>
+      <c r="H8" s="170"/>
       <c r="I8" s="35"/>
-      <c r="J8" s="155" t="s">
+      <c r="J8" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="156"/>
-      <c r="L8" s="157"/>
+      <c r="K8" s="169"/>
+      <c r="L8" s="170"/>
       <c r="M8" s="3"/>
       <c r="N8" s="82" t="s">
         <v>9</v>
@@ -3066,22 +3060,22 @@
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="89"/>
       <c r="C9" s="90"/>
       <c r="D9" s="91"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="142" t="s">
+      <c r="F9" s="155" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="143"/>
-      <c r="H9" s="144"/>
+      <c r="G9" s="156"/>
+      <c r="H9" s="157"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="142" t="s">
+      <c r="J9" s="155" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="143"/>
-      <c r="L9" s="144"/>
+      <c r="K9" s="156"/>
+      <c r="L9" s="157"/>
       <c r="M9" s="3"/>
       <c r="N9" s="89"/>
       <c r="O9" s="90"/>
@@ -3119,46 +3113,46 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="160"/>
-      <c r="C10" s="161"/>
-      <c r="D10" s="162"/>
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="173"/>
+      <c r="C10" s="174"/>
+      <c r="D10" s="175"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="186"/>
-      <c r="G10" s="187"/>
-      <c r="H10" s="188"/>
+      <c r="F10" s="194"/>
+      <c r="G10" s="195"/>
+      <c r="H10" s="196"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="186"/>
-      <c r="K10" s="187"/>
-      <c r="L10" s="188"/>
+      <c r="J10" s="194"/>
+      <c r="K10" s="195"/>
+      <c r="L10" s="196"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="160"/>
-      <c r="O10" s="161"/>
-      <c r="P10" s="162"/>
+      <c r="N10" s="173"/>
+      <c r="O10" s="174"/>
+      <c r="P10" s="175"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="160"/>
-      <c r="S10" s="161"/>
-      <c r="T10" s="162"/>
+      <c r="R10" s="173"/>
+      <c r="S10" s="174"/>
+      <c r="T10" s="175"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="160"/>
-      <c r="W10" s="161"/>
-      <c r="X10" s="162"/>
+      <c r="V10" s="173"/>
+      <c r="W10" s="174"/>
+      <c r="X10" s="175"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="160"/>
-      <c r="AA10" s="161"/>
-      <c r="AB10" s="162"/>
+      <c r="Z10" s="173"/>
+      <c r="AA10" s="174"/>
+      <c r="AB10" s="175"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="160"/>
-      <c r="AE10" s="161"/>
-      <c r="AF10" s="162"/>
+      <c r="AD10" s="173"/>
+      <c r="AE10" s="174"/>
+      <c r="AF10" s="175"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="160"/>
-      <c r="AI10" s="161"/>
-      <c r="AJ10" s="162"/>
+      <c r="AH10" s="173"/>
+      <c r="AI10" s="174"/>
+      <c r="AJ10" s="175"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="160"/>
-      <c r="AM10" s="161"/>
-      <c r="AN10" s="162"/>
+      <c r="AL10" s="173"/>
+      <c r="AM10" s="174"/>
+      <c r="AN10" s="175"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -3168,7 +3162,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -3217,7 +3211,7 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="74"/>
       <c r="C12" s="75"/>
       <c r="D12" s="54"/>
@@ -3266,7 +3260,7 @@
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="87"/>
       <c r="C13" s="88"/>
       <c r="D13" s="55"/>
@@ -3291,12 +3285,12 @@
       <c r="W13" s="108"/>
       <c r="X13" s="109"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="119"/>
-      <c r="AA13" s="120"/>
+      <c r="Z13" s="125"/>
+      <c r="AA13" s="126"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="119"/>
-      <c r="AE13" s="120"/>
+      <c r="AD13" s="125"/>
+      <c r="AE13" s="126"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
       <c r="AH13" s="107"/>
@@ -3315,7 +3309,7 @@
       </c>
       <c r="AR13" s="30"/>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="82"/>
       <c r="C14" s="83"/>
       <c r="D14" s="84"/>
@@ -3360,11 +3354,11 @@
       </c>
       <c r="AQ14" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR14" s="30"/>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="89"/>
       <c r="C15" s="90"/>
       <c r="D15" s="91"/>
@@ -3413,46 +3407,46 @@
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="160"/>
-      <c r="C16" s="161"/>
-      <c r="D16" s="162"/>
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="173"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="175"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="160"/>
-      <c r="G16" s="161"/>
-      <c r="H16" s="162"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="174"/>
+      <c r="H16" s="175"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="160"/>
-      <c r="K16" s="161"/>
-      <c r="L16" s="162"/>
+      <c r="J16" s="173"/>
+      <c r="K16" s="174"/>
+      <c r="L16" s="175"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="160"/>
-      <c r="O16" s="161"/>
-      <c r="P16" s="162"/>
+      <c r="N16" s="173"/>
+      <c r="O16" s="174"/>
+      <c r="P16" s="175"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="160"/>
-      <c r="S16" s="161"/>
-      <c r="T16" s="162"/>
+      <c r="R16" s="173"/>
+      <c r="S16" s="174"/>
+      <c r="T16" s="175"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="160"/>
-      <c r="W16" s="161"/>
-      <c r="X16" s="162"/>
+      <c r="V16" s="173"/>
+      <c r="W16" s="174"/>
+      <c r="X16" s="175"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="160"/>
-      <c r="AA16" s="161"/>
-      <c r="AB16" s="162"/>
+      <c r="Z16" s="173"/>
+      <c r="AA16" s="174"/>
+      <c r="AB16" s="175"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="160"/>
-      <c r="AE16" s="161"/>
-      <c r="AF16" s="162"/>
+      <c r="AD16" s="173"/>
+      <c r="AE16" s="174"/>
+      <c r="AF16" s="175"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="160"/>
-      <c r="AI16" s="161"/>
-      <c r="AJ16" s="162"/>
+      <c r="AH16" s="173"/>
+      <c r="AI16" s="174"/>
+      <c r="AJ16" s="175"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="160"/>
-      <c r="AM16" s="161"/>
-      <c r="AN16" s="162"/>
+      <c r="AL16" s="173"/>
+      <c r="AM16" s="174"/>
+      <c r="AN16" s="175"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3462,7 +3456,7 @@
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3511,7 +3505,7 @@
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3524,23 +3518,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="137" t="s">
+      <c r="N18" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="137"/>
-      <c r="P18" s="137"/>
-      <c r="Q18" s="137"/>
-      <c r="R18" s="137"/>
-      <c r="S18" s="137"/>
-      <c r="T18" s="137"/>
-      <c r="U18" s="137"/>
-      <c r="V18" s="137"/>
-      <c r="W18" s="137"/>
-      <c r="X18" s="137"/>
-      <c r="Y18" s="137"/>
-      <c r="Z18" s="137"/>
-      <c r="AA18" s="137"/>
-      <c r="AB18" s="137"/>
+      <c r="O18" s="148"/>
+      <c r="P18" s="148"/>
+      <c r="Q18" s="148"/>
+      <c r="R18" s="148"/>
+      <c r="S18" s="148"/>
+      <c r="T18" s="148"/>
+      <c r="U18" s="148"/>
+      <c r="V18" s="148"/>
+      <c r="W18" s="148"/>
+      <c r="X18" s="148"/>
+      <c r="Y18" s="148"/>
+      <c r="Z18" s="148"/>
+      <c r="AA18" s="148"/>
+      <c r="AB18" s="148"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3562,7 +3556,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3575,21 +3569,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="137"/>
-      <c r="O19" s="137"/>
-      <c r="P19" s="137"/>
-      <c r="Q19" s="137"/>
-      <c r="R19" s="137"/>
-      <c r="S19" s="137"/>
-      <c r="T19" s="137"/>
-      <c r="U19" s="137"/>
-      <c r="V19" s="137"/>
-      <c r="W19" s="137"/>
-      <c r="X19" s="137"/>
-      <c r="Y19" s="137"/>
-      <c r="Z19" s="137"/>
-      <c r="AA19" s="137"/>
-      <c r="AB19" s="137"/>
+      <c r="N19" s="148"/>
+      <c r="O19" s="148"/>
+      <c r="P19" s="148"/>
+      <c r="Q19" s="148"/>
+      <c r="R19" s="148"/>
+      <c r="S19" s="148"/>
+      <c r="T19" s="148"/>
+      <c r="U19" s="148"/>
+      <c r="V19" s="148"/>
+      <c r="W19" s="148"/>
+      <c r="X19" s="148"/>
+      <c r="Y19" s="148"/>
+      <c r="Z19" s="148"/>
+      <c r="AA19" s="148"/>
+      <c r="AB19" s="148"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3611,7 +3605,7 @@
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
         <v>52</v>
       </c>
@@ -3636,22 +3630,22 @@
         <v>78</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="184"/>
-      <c r="O20" s="185"/>
+      <c r="N20" s="192"/>
+      <c r="O20" s="193"/>
       <c r="P20" s="59"/>
       <c r="Q20" s="36"/>
-      <c r="R20" s="184" t="s">
+      <c r="R20" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="S20" s="185"/>
+      <c r="S20" s="193"/>
       <c r="T20" s="59" t="s">
         <v>41</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="184" t="s">
+      <c r="V20" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="W20" s="185"/>
+      <c r="W20" s="193"/>
       <c r="X20" s="59" t="s">
         <v>41</v>
       </c>
@@ -3676,10 +3670,10 @@
       <c r="AI20" s="111"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="135" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM20" s="136"/>
+      <c r="AL20" s="116" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM20" s="117"/>
       <c r="AN20" s="58" t="s">
         <v>78</v>
       </c>
@@ -3692,47 +3686,47 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="87"/>
       <c r="C21" s="88"/>
       <c r="D21" s="55"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="152" t="s">
+      <c r="F21" s="165" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="153"/>
+      <c r="G21" s="166"/>
       <c r="H21" s="73"/>
       <c r="I21" s="36"/>
       <c r="J21" s="87"/>
       <c r="K21" s="88"/>
       <c r="L21" s="55"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="120"/>
+      <c r="N21" s="125"/>
+      <c r="O21" s="126"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="119"/>
-      <c r="S21" s="120"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="126"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="180"/>
-      <c r="W21" s="181"/>
+      <c r="V21" s="188"/>
+      <c r="W21" s="189"/>
       <c r="X21" s="60"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="119"/>
-      <c r="AA21" s="120"/>
+      <c r="Z21" s="125"/>
+      <c r="AA21" s="126"/>
       <c r="AB21" s="18"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="119"/>
-      <c r="AE21" s="120"/>
+      <c r="AD21" s="125"/>
+      <c r="AE21" s="126"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="119"/>
-      <c r="AI21" s="120"/>
+      <c r="AH21" s="125"/>
+      <c r="AI21" s="126"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="119"/>
-      <c r="AM21" s="120"/>
+      <c r="AL21" s="125"/>
+      <c r="AM21" s="126"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3743,7 +3737,7 @@
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="85" t="s">
         <v>7</v>
       </c>
@@ -3824,7 +3818,7 @@
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="80" t="s">
         <v>19</v>
       </c>
@@ -3833,18 +3827,18 @@
         <v>33</v>
       </c>
       <c r="E23" s="43"/>
-      <c r="F23" s="182" t="s">
+      <c r="F23" s="190" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="183"/>
+      <c r="G23" s="191"/>
       <c r="H23" s="64" t="s">
         <v>33</v>
       </c>
       <c r="I23" s="43"/>
-      <c r="J23" s="182" t="s">
+      <c r="J23" s="190" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="183"/>
+      <c r="K23" s="191"/>
       <c r="L23" s="64" t="s">
         <v>33</v>
       </c>
@@ -3905,7 +3899,7 @@
       </c>
       <c r="AR23" s="30"/>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="78" t="s">
         <v>11</v>
       </c>
@@ -3930,50 +3924,50 @@
         <v>34</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="122"/>
-      <c r="O24" s="123"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="124"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="200" t="s">
+      <c r="R24" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="201"/>
+      <c r="S24" s="154"/>
       <c r="T24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="U24" s="44"/>
-      <c r="V24" s="122" t="s">
+      <c r="V24" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="W24" s="123"/>
+      <c r="W24" s="124"/>
       <c r="X24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="122" t="s">
+      <c r="Z24" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="AA24" s="123"/>
+      <c r="AA24" s="124"/>
       <c r="AB24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="122" t="s">
+      <c r="AD24" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="AE24" s="123"/>
+      <c r="AE24" s="124"/>
       <c r="AF24" s="45" t="s">
         <v>34</v>
       </c>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="122"/>
-      <c r="AI24" s="123"/>
+      <c r="AH24" s="123"/>
+      <c r="AI24" s="124"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="122" t="s">
+      <c r="AL24" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="AM24" s="123"/>
+      <c r="AM24" s="124"/>
       <c r="AN24" s="45" t="s">
         <v>34</v>
       </c>
@@ -3986,7 +3980,7 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="78" t="s">
         <v>27</v>
       </c>
@@ -4011,50 +4005,50 @@
         <v>35</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="122"/>
-      <c r="O25" s="123"/>
+      <c r="N25" s="123"/>
+      <c r="O25" s="124"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="122" t="s">
+      <c r="R25" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="S25" s="123"/>
+      <c r="S25" s="124"/>
       <c r="T25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U25" s="44"/>
-      <c r="V25" s="122" t="s">
+      <c r="V25" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="W25" s="123"/>
+      <c r="W25" s="124"/>
       <c r="X25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="122" t="s">
+      <c r="Z25" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="AA25" s="123"/>
+      <c r="AA25" s="124"/>
       <c r="AB25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="122" t="s">
+      <c r="AD25" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="AE25" s="123"/>
+      <c r="AE25" s="124"/>
       <c r="AF25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="122"/>
-      <c r="AI25" s="123"/>
+      <c r="AH25" s="123"/>
+      <c r="AI25" s="124"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="122" t="s">
+      <c r="AL25" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="AM25" s="123"/>
+      <c r="AM25" s="124"/>
       <c r="AN25" s="45" t="s">
         <v>35</v>
       </c>
@@ -4067,7 +4061,7 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="78" t="s">
         <v>21</v>
       </c>
@@ -4092,50 +4086,50 @@
         <v>35</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="122"/>
-      <c r="O26" s="123"/>
+      <c r="N26" s="123"/>
+      <c r="O26" s="124"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="122" t="s">
+      <c r="R26" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="S26" s="123"/>
+      <c r="S26" s="124"/>
       <c r="T26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="U26" s="44"/>
-      <c r="V26" s="200" t="s">
+      <c r="V26" s="153" t="s">
         <v>20</v>
       </c>
-      <c r="W26" s="201"/>
+      <c r="W26" s="154"/>
       <c r="X26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="122" t="s">
+      <c r="Z26" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="AA26" s="123"/>
+      <c r="AA26" s="124"/>
       <c r="AB26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="122" t="s">
+      <c r="AD26" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="AE26" s="123"/>
+      <c r="AE26" s="124"/>
       <c r="AF26" s="45" t="s">
         <v>35</v>
       </c>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="122"/>
-      <c r="AI26" s="123"/>
+      <c r="AH26" s="123"/>
+      <c r="AI26" s="124"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="122" t="s">
+      <c r="AL26" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="AM26" s="123"/>
+      <c r="AM26" s="124"/>
       <c r="AN26" s="45" t="s">
         <v>35</v>
       </c>
@@ -4148,7 +4142,7 @@
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="95"/>
       <c r="C27" s="96"/>
       <c r="D27" s="65"/>
@@ -4163,36 +4157,36 @@
       <c r="K27" s="106"/>
       <c r="L27" s="65"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="103"/>
-      <c r="O27" s="104"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="122"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="198" t="s">
-        <v>106</v>
-      </c>
-      <c r="S27" s="199"/>
+      <c r="R27" s="103" t="s">
+        <v>105</v>
+      </c>
+      <c r="S27" s="104"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="198" t="s">
-        <v>107</v>
-      </c>
-      <c r="W27" s="199"/>
+      <c r="V27" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="W27" s="104"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="103"/>
-      <c r="AA27" s="104"/>
+      <c r="Z27" s="121"/>
+      <c r="AA27" s="122"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="103"/>
-      <c r="AE27" s="104"/>
+      <c r="AD27" s="121"/>
+      <c r="AE27" s="122"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="103"/>
-      <c r="AI27" s="104"/>
+      <c r="AH27" s="121"/>
+      <c r="AI27" s="122"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="103"/>
-      <c r="AM27" s="104"/>
+      <c r="AL27" s="121"/>
+      <c r="AM27" s="122"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="62" t="s">
         <v>13</v>
@@ -4205,7 +4199,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
@@ -4254,7 +4248,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
@@ -4267,23 +4261,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="137" t="s">
+      <c r="N29" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="137"/>
-      <c r="P29" s="137"/>
-      <c r="Q29" s="137"/>
-      <c r="R29" s="137"/>
-      <c r="S29" s="137"/>
-      <c r="T29" s="137"/>
-      <c r="U29" s="137"/>
-      <c r="V29" s="137"/>
-      <c r="W29" s="137"/>
-      <c r="X29" s="137"/>
-      <c r="Y29" s="137"/>
-      <c r="Z29" s="137"/>
-      <c r="AA29" s="137"/>
-      <c r="AB29" s="137"/>
+      <c r="O29" s="148"/>
+      <c r="P29" s="148"/>
+      <c r="Q29" s="148"/>
+      <c r="R29" s="148"/>
+      <c r="S29" s="148"/>
+      <c r="T29" s="148"/>
+      <c r="U29" s="148"/>
+      <c r="V29" s="148"/>
+      <c r="W29" s="148"/>
+      <c r="X29" s="148"/>
+      <c r="Y29" s="148"/>
+      <c r="Z29" s="148"/>
+      <c r="AA29" s="148"/>
+      <c r="AB29" s="148"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -4305,7 +4299,7 @@
       </c>
       <c r="AR29" s="30"/>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
@@ -4318,21 +4312,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="137"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="137"/>
-      <c r="Q30" s="137"/>
-      <c r="R30" s="137"/>
-      <c r="S30" s="137"/>
-      <c r="T30" s="137"/>
-      <c r="U30" s="137"/>
-      <c r="V30" s="137"/>
-      <c r="W30" s="137"/>
-      <c r="X30" s="137"/>
-      <c r="Y30" s="137"/>
-      <c r="Z30" s="137"/>
-      <c r="AA30" s="137"/>
-      <c r="AB30" s="137"/>
+      <c r="N30" s="148"/>
+      <c r="O30" s="148"/>
+      <c r="P30" s="148"/>
+      <c r="Q30" s="148"/>
+      <c r="R30" s="148"/>
+      <c r="S30" s="148"/>
+      <c r="T30" s="148"/>
+      <c r="U30" s="148"/>
+      <c r="V30" s="148"/>
+      <c r="W30" s="148"/>
+      <c r="X30" s="148"/>
+      <c r="Y30" s="148"/>
+      <c r="Z30" s="148"/>
+      <c r="AA30" s="148"/>
+      <c r="AB30" s="148"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -4354,7 +4348,7 @@
       </c>
       <c r="AR30" s="30"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="74" t="s">
         <v>81</v>
       </c>
@@ -4389,10 +4383,10 @@
         <v>53</v>
       </c>
       <c r="U31" s="36"/>
-      <c r="V31" s="124" t="s">
+      <c r="V31" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="W31" s="125"/>
+      <c r="W31" s="129"/>
       <c r="X31" s="57" t="s">
         <v>53</v>
       </c>
@@ -4428,7 +4422,7 @@
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="99" t="s">
         <v>82</v>
       </c>
@@ -4459,11 +4453,11 @@
       <c r="S32" s="108"/>
       <c r="T32" s="109"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="138" t="s">
+      <c r="V32" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="W32" s="139"/>
-      <c r="X32" s="140"/>
+      <c r="W32" s="146"/>
+      <c r="X32" s="147"/>
       <c r="Y32" s="37"/>
       <c r="Z32" s="107"/>
       <c r="AA32" s="108"/>
@@ -4490,7 +4484,7 @@
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="87"/>
       <c r="C33" s="88"/>
       <c r="D33" s="102"/>
@@ -4503,38 +4497,38 @@
       <c r="K33" s="88"/>
       <c r="L33" s="102"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="119"/>
-      <c r="O33" s="120"/>
-      <c r="P33" s="121"/>
+      <c r="N33" s="125"/>
+      <c r="O33" s="126"/>
+      <c r="P33" s="127"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="119"/>
-      <c r="S33" s="120"/>
-      <c r="T33" s="121"/>
+      <c r="R33" s="125"/>
+      <c r="S33" s="126"/>
+      <c r="T33" s="127"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="132" t="s">
-        <v>114</v>
-      </c>
-      <c r="W33" s="133"/>
-      <c r="X33" s="134"/>
+      <c r="V33" s="130" t="s">
+        <v>113</v>
+      </c>
+      <c r="W33" s="131"/>
+      <c r="X33" s="132"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="119"/>
-      <c r="AA33" s="120"/>
-      <c r="AB33" s="121"/>
+      <c r="Z33" s="125"/>
+      <c r="AA33" s="126"/>
+      <c r="AB33" s="127"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="119"/>
-      <c r="AE33" s="120"/>
-      <c r="AF33" s="121"/>
+      <c r="AD33" s="125"/>
+      <c r="AE33" s="126"/>
+      <c r="AF33" s="127"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="119"/>
-      <c r="AI33" s="120"/>
-      <c r="AJ33" s="121"/>
+      <c r="AH33" s="125"/>
+      <c r="AI33" s="126"/>
+      <c r="AJ33" s="127"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="119"/>
-      <c r="AM33" s="120"/>
-      <c r="AN33" s="121"/>
+      <c r="AL33" s="125"/>
+      <c r="AM33" s="126"/>
+      <c r="AN33" s="127"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
       <c r="B34" s="82" t="s">
         <v>25</v>
@@ -4566,11 +4560,11 @@
       <c r="S34" s="83"/>
       <c r="T34" s="84"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="129" t="s">
-        <v>115</v>
-      </c>
-      <c r="W34" s="130"/>
-      <c r="X34" s="131"/>
+      <c r="V34" s="136" t="s">
+        <v>114</v>
+      </c>
+      <c r="W34" s="137"/>
+      <c r="X34" s="138"/>
       <c r="Y34" s="32"/>
       <c r="Z34" s="82"/>
       <c r="AA34" s="83"/>
@@ -4598,7 +4592,7 @@
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="89" t="s">
         <v>26</v>
@@ -4630,11 +4624,11 @@
       <c r="S35" s="90"/>
       <c r="T35" s="91"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="126" t="s">
-        <v>116</v>
-      </c>
-      <c r="W35" s="127"/>
-      <c r="X35" s="128"/>
+      <c r="V35" s="133" t="s">
+        <v>115</v>
+      </c>
+      <c r="W35" s="134"/>
+      <c r="X35" s="135"/>
       <c r="Y35" s="32"/>
       <c r="Z35" s="89"/>
       <c r="AA35" s="90"/>
@@ -4661,7 +4655,7 @@
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
       <c r="B36" s="92" t="s">
         <v>83</v>
@@ -4681,57 +4675,57 @@
       <c r="K36" s="93"/>
       <c r="L36" s="94"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="116"/>
-      <c r="O36" s="117"/>
-      <c r="P36" s="118"/>
+      <c r="N36" s="118"/>
+      <c r="O36" s="119"/>
+      <c r="P36" s="120"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="116"/>
-      <c r="S36" s="117"/>
-      <c r="T36" s="118"/>
+      <c r="R36" s="118"/>
+      <c r="S36" s="119"/>
+      <c r="T36" s="120"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="175"/>
-      <c r="W36" s="176"/>
-      <c r="X36" s="177"/>
+      <c r="V36" s="139"/>
+      <c r="W36" s="140"/>
+      <c r="X36" s="141"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="117"/>
-      <c r="AB36" s="118"/>
+      <c r="Z36" s="118"/>
+      <c r="AA36" s="119"/>
+      <c r="AB36" s="120"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="116"/>
-      <c r="AE36" s="117"/>
-      <c r="AF36" s="118"/>
+      <c r="AD36" s="118"/>
+      <c r="AE36" s="119"/>
+      <c r="AF36" s="120"/>
       <c r="AG36" s="44"/>
-      <c r="AH36" s="116"/>
-      <c r="AI36" s="117"/>
-      <c r="AJ36" s="118"/>
+      <c r="AH36" s="118"/>
+      <c r="AI36" s="119"/>
+      <c r="AJ36" s="120"/>
       <c r="AK36" s="44"/>
-      <c r="AL36" s="116"/>
-      <c r="AM36" s="117"/>
-      <c r="AN36" s="118"/>
+      <c r="AL36" s="118"/>
+      <c r="AM36" s="119"/>
+      <c r="AN36" s="120"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
-      <c r="B37" s="202" t="s">
+      <c r="B37" s="203" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="203"/>
-      <c r="D37" s="204"/>
+      <c r="C37" s="204"/>
+      <c r="D37" s="205"/>
       <c r="E37" s="50"/>
-      <c r="F37" s="202" t="s">
+      <c r="F37" s="203" t="s">
         <v>84</v>
       </c>
-      <c r="G37" s="203"/>
-      <c r="H37" s="204"/>
+      <c r="G37" s="204"/>
+      <c r="H37" s="205"/>
       <c r="I37" s="50"/>
-      <c r="J37" s="202" t="s">
+      <c r="J37" s="203" t="s">
         <v>84</v>
       </c>
-      <c r="K37" s="203"/>
-      <c r="L37" s="204"/>
+      <c r="K37" s="204"/>
+      <c r="L37" s="205"/>
       <c r="M37" s="5"/>
       <c r="N37" s="35"/>
       <c r="O37" s="35"/>
@@ -4765,7 +4759,7 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="35"/>
       <c r="C38" s="35"/>
@@ -4811,10 +4805,10 @@
         <v>69</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="135" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM38" s="136"/>
+      <c r="AL38" s="116" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM38" s="117"/>
       <c r="AN38" s="58" t="s">
         <v>68</v>
       </c>
@@ -4823,7 +4817,7 @@
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="74" t="s">
         <v>85</v>
@@ -4872,7 +4866,7 @@
       <c r="AJ39" s="109"/>
       <c r="AK39" s="36"/>
       <c r="AL39" s="107" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AM39" s="108"/>
       <c r="AN39" s="109"/>
@@ -4881,7 +4875,7 @@
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="99" t="s">
         <v>55</v>
@@ -4897,39 +4891,39 @@
       <c r="K40" s="100"/>
       <c r="L40" s="101"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="119"/>
-      <c r="O40" s="120"/>
-      <c r="P40" s="121"/>
+      <c r="N40" s="125"/>
+      <c r="O40" s="126"/>
+      <c r="P40" s="127"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="119"/>
-      <c r="S40" s="120"/>
-      <c r="T40" s="121"/>
+      <c r="R40" s="125"/>
+      <c r="S40" s="126"/>
+      <c r="T40" s="127"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="119"/>
-      <c r="W40" s="120"/>
-      <c r="X40" s="121"/>
+      <c r="V40" s="125"/>
+      <c r="W40" s="126"/>
+      <c r="X40" s="127"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="119"/>
-      <c r="AA40" s="120"/>
-      <c r="AB40" s="121"/>
+      <c r="Z40" s="125"/>
+      <c r="AA40" s="126"/>
+      <c r="AB40" s="127"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="119"/>
-      <c r="AE40" s="120"/>
-      <c r="AF40" s="121"/>
+      <c r="AD40" s="125"/>
+      <c r="AE40" s="126"/>
+      <c r="AF40" s="127"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="119"/>
-      <c r="AI40" s="120"/>
-      <c r="AJ40" s="121"/>
+      <c r="AH40" s="125"/>
+      <c r="AI40" s="126"/>
+      <c r="AJ40" s="127"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="119"/>
-      <c r="AM40" s="120"/>
-      <c r="AN40" s="121"/>
+      <c r="AL40" s="125"/>
+      <c r="AM40" s="126"/>
+      <c r="AN40" s="127"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="87"/>
       <c r="C41" s="88"/>
@@ -4974,7 +4968,7 @@
       <c r="AJ41" s="91"/>
       <c r="AK41" s="37"/>
       <c r="AL41" s="82" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AM41" s="83"/>
       <c r="AN41" s="84"/>
@@ -4983,7 +4977,7 @@
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="82" t="s">
         <v>23</v>
@@ -5039,7 +5033,7 @@
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43" s="89" t="s">
         <v>8</v>
@@ -5057,53 +5051,51 @@
       <c r="K43" s="90"/>
       <c r="L43" s="91"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="116"/>
-      <c r="O43" s="117"/>
-      <c r="P43" s="118"/>
+      <c r="N43" s="118"/>
+      <c r="O43" s="119"/>
+      <c r="P43" s="120"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="116"/>
-      <c r="S43" s="117"/>
-      <c r="T43" s="118"/>
+      <c r="R43" s="118"/>
+      <c r="S43" s="119"/>
+      <c r="T43" s="120"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="116"/>
-      <c r="W43" s="117"/>
-      <c r="X43" s="118"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="119"/>
+      <c r="X43" s="120"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="116"/>
-      <c r="AA43" s="117"/>
-      <c r="AB43" s="118"/>
+      <c r="Z43" s="118"/>
+      <c r="AA43" s="119"/>
+      <c r="AB43" s="120"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="116"/>
-      <c r="AE43" s="117"/>
-      <c r="AF43" s="118"/>
+      <c r="AD43" s="118"/>
+      <c r="AE43" s="119"/>
+      <c r="AF43" s="120"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="116"/>
-      <c r="AI43" s="117"/>
-      <c r="AJ43" s="118"/>
+      <c r="AH43" s="118"/>
+      <c r="AI43" s="119"/>
+      <c r="AJ43" s="120"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="175" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM43" s="176"/>
-      <c r="AN43" s="177"/>
+      <c r="AL43" s="118"/>
+      <c r="AM43" s="119"/>
+      <c r="AN43" s="120"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
-      <c r="B44" s="116"/>
-      <c r="C44" s="117"/>
-      <c r="D44" s="118"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="119"/>
+      <c r="D44" s="120"/>
       <c r="E44" s="44"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="118"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="119"/>
+      <c r="H44" s="120"/>
       <c r="I44" s="50"/>
-      <c r="J44" s="116"/>
-      <c r="K44" s="117"/>
-      <c r="L44" s="118"/>
+      <c r="J44" s="118"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="120"/>
       <c r="M44" s="14"/>
       <c r="N44" s="35"/>
       <c r="O44" s="35"/>
@@ -5137,7 +5129,7 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="35"/>
       <c r="C45" s="35"/>
@@ -5167,10 +5159,10 @@
       <c r="AA45" s="111"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="135" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE45" s="136"/>
+      <c r="AD45" s="116" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE45" s="117"/>
       <c r="AF45" s="58"/>
       <c r="AG45" s="36"/>
       <c r="AH45" s="110" t="s">
@@ -5181,20 +5173,22 @@
         <v>46</v>
       </c>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="110"/>
-      <c r="AM45" s="111"/>
-      <c r="AN45" s="34"/>
+      <c r="AL45" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM45" s="117"/>
+      <c r="AN45" s="58"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
-      <c r="B46" s="135" t="s">
+      <c r="B46" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="136"/>
+      <c r="C46" s="117"/>
       <c r="D46" s="58"/>
       <c r="E46" s="32"/>
       <c r="F46" s="74"/>
@@ -5222,7 +5216,7 @@
       <c r="AB46" s="109"/>
       <c r="AC46" s="35"/>
       <c r="AD46" s="107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AE46" s="108"/>
       <c r="AF46" s="109"/>
@@ -5233,7 +5227,9 @@
       <c r="AI46" s="108"/>
       <c r="AJ46" s="109"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="107"/>
+      <c r="AL46" s="107" t="s">
+        <v>121</v>
+      </c>
       <c r="AM46" s="108"/>
       <c r="AN46" s="109"/>
       <c r="AO46" s="31"/>
@@ -5241,7 +5237,7 @@
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="99" t="s">
         <v>89</v>
@@ -5257,41 +5253,41 @@
       <c r="K47" s="100"/>
       <c r="L47" s="101"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="119"/>
-      <c r="O47" s="120"/>
-      <c r="P47" s="121"/>
+      <c r="N47" s="125"/>
+      <c r="O47" s="126"/>
+      <c r="P47" s="127"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="119"/>
-      <c r="S47" s="120"/>
-      <c r="T47" s="121"/>
+      <c r="R47" s="125"/>
+      <c r="S47" s="126"/>
+      <c r="T47" s="127"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="119"/>
-      <c r="W47" s="120"/>
-      <c r="X47" s="121"/>
+      <c r="V47" s="125"/>
+      <c r="W47" s="126"/>
+      <c r="X47" s="127"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="119"/>
-      <c r="AA47" s="120"/>
-      <c r="AB47" s="121"/>
+      <c r="Z47" s="125"/>
+      <c r="AA47" s="126"/>
+      <c r="AB47" s="127"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="119" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE47" s="120"/>
-      <c r="AF47" s="121"/>
+      <c r="AD47" s="125" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE47" s="126"/>
+      <c r="AF47" s="127"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="119"/>
-      <c r="AI47" s="120"/>
-      <c r="AJ47" s="121"/>
+      <c r="AH47" s="125"/>
+      <c r="AI47" s="126"/>
+      <c r="AJ47" s="127"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="119"/>
-      <c r="AM47" s="120"/>
-      <c r="AN47" s="121"/>
+      <c r="AL47" s="125"/>
+      <c r="AM47" s="126"/>
+      <c r="AN47" s="127"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="87"/>
       <c r="C48" s="88"/>
@@ -5333,15 +5329,17 @@
       <c r="AI48" s="90"/>
       <c r="AJ48" s="91"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="89"/>
-      <c r="AM48" s="90"/>
-      <c r="AN48" s="91"/>
+      <c r="AL48" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM48" s="83"/>
+      <c r="AN48" s="84"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="82" t="s">
         <v>18</v>
       </c>
@@ -5382,7 +5380,9 @@
       <c r="AI49" s="90"/>
       <c r="AJ49" s="91"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="89"/>
+      <c r="AL49" s="89" t="s">
+        <v>12</v>
+      </c>
       <c r="AM49" s="90"/>
       <c r="AN49" s="91"/>
       <c r="AO49" s="31"/>
@@ -5390,7 +5390,7 @@
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="89" t="s">
         <v>20</v>
       </c>
@@ -5405,50 +5405,50 @@
       <c r="K50" s="90"/>
       <c r="L50" s="91"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="116"/>
-      <c r="O50" s="117"/>
-      <c r="P50" s="118"/>
+      <c r="N50" s="118"/>
+      <c r="O50" s="119"/>
+      <c r="P50" s="120"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="116"/>
-      <c r="S50" s="117"/>
-      <c r="T50" s="118"/>
+      <c r="R50" s="118"/>
+      <c r="S50" s="119"/>
+      <c r="T50" s="120"/>
       <c r="U50" s="35"/>
-      <c r="V50" s="116"/>
-      <c r="W50" s="117"/>
-      <c r="X50" s="118"/>
+      <c r="V50" s="118"/>
+      <c r="W50" s="119"/>
+      <c r="X50" s="120"/>
       <c r="Y50" s="35"/>
-      <c r="Z50" s="116"/>
-      <c r="AA50" s="117"/>
-      <c r="AB50" s="118"/>
+      <c r="Z50" s="118"/>
+      <c r="AA50" s="119"/>
+      <c r="AB50" s="120"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="116"/>
-      <c r="AE50" s="117"/>
-      <c r="AF50" s="118"/>
+      <c r="AD50" s="118"/>
+      <c r="AE50" s="119"/>
+      <c r="AF50" s="120"/>
       <c r="AG50" s="44"/>
-      <c r="AH50" s="116"/>
-      <c r="AI50" s="117"/>
-      <c r="AJ50" s="118"/>
+      <c r="AH50" s="118"/>
+      <c r="AI50" s="119"/>
+      <c r="AJ50" s="120"/>
       <c r="AK50" s="44"/>
-      <c r="AL50" s="116"/>
-      <c r="AM50" s="117"/>
-      <c r="AN50" s="118"/>
+      <c r="AL50" s="118"/>
+      <c r="AM50" s="119"/>
+      <c r="AN50" s="120"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="116"/>
-      <c r="C51" s="117"/>
-      <c r="D51" s="118"/>
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="118"/>
+      <c r="C51" s="119"/>
+      <c r="D51" s="120"/>
       <c r="E51" s="44"/>
-      <c r="F51" s="116"/>
-      <c r="G51" s="117"/>
-      <c r="H51" s="118"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="119"/>
+      <c r="H51" s="120"/>
       <c r="I51" s="50"/>
-      <c r="J51" s="205"/>
-      <c r="K51" s="206"/>
-      <c r="L51" s="207"/>
+      <c r="J51" s="206"/>
+      <c r="K51" s="207"/>
+      <c r="L51" s="208"/>
       <c r="M51" s="14"/>
       <c r="N51" s="35"/>
       <c r="O51" s="35"/>
@@ -5482,7 +5482,7 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="35"/>
       <c r="C52" s="35"/>
       <c r="D52" s="35"/>
@@ -5524,11 +5524,11 @@
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="135" t="s">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="136"/>
+      <c r="C53" s="117"/>
       <c r="D53" s="58"/>
       <c r="E53" s="32"/>
       <c r="F53" s="74"/>
@@ -5568,7 +5568,7 @@
       <c r="AN53" s="109"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="99" t="s">
         <v>90</v>
       </c>
@@ -5583,36 +5583,36 @@
       <c r="K54" s="100"/>
       <c r="L54" s="101"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="119"/>
-      <c r="O54" s="120"/>
-      <c r="P54" s="121"/>
+      <c r="N54" s="125"/>
+      <c r="O54" s="126"/>
+      <c r="P54" s="127"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="119"/>
-      <c r="S54" s="120"/>
-      <c r="T54" s="121"/>
+      <c r="R54" s="125"/>
+      <c r="S54" s="126"/>
+      <c r="T54" s="127"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="119"/>
-      <c r="W54" s="120"/>
-      <c r="X54" s="121"/>
+      <c r="V54" s="125"/>
+      <c r="W54" s="126"/>
+      <c r="X54" s="127"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="119"/>
-      <c r="AA54" s="120"/>
-      <c r="AB54" s="121"/>
+      <c r="Z54" s="125"/>
+      <c r="AA54" s="126"/>
+      <c r="AB54" s="127"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="119"/>
-      <c r="AE54" s="120"/>
-      <c r="AF54" s="121"/>
+      <c r="AD54" s="125"/>
+      <c r="AE54" s="126"/>
+      <c r="AF54" s="127"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="119"/>
-      <c r="AI54" s="120"/>
-      <c r="AJ54" s="121"/>
+      <c r="AH54" s="125"/>
+      <c r="AI54" s="126"/>
+      <c r="AJ54" s="127"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="119"/>
-      <c r="AM54" s="120"/>
-      <c r="AN54" s="121"/>
+      <c r="AL54" s="125"/>
+      <c r="AM54" s="126"/>
+      <c r="AN54" s="127"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="87"/>
       <c r="C55" s="88"/>
       <c r="D55" s="102"/>
@@ -5654,7 +5654,7 @@
       <c r="AN55" s="84"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="89" t="s">
         <v>24</v>
       </c>
@@ -5698,7 +5698,7 @@
       <c r="AN56" s="91"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="92" t="s">
         <v>83</v>
       </c>
@@ -5713,47 +5713,47 @@
       <c r="K57" s="90"/>
       <c r="L57" s="91"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="116"/>
-      <c r="O57" s="117"/>
-      <c r="P57" s="118"/>
+      <c r="N57" s="118"/>
+      <c r="O57" s="119"/>
+      <c r="P57" s="120"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="116"/>
-      <c r="S57" s="117"/>
-      <c r="T57" s="118"/>
+      <c r="R57" s="118"/>
+      <c r="S57" s="119"/>
+      <c r="T57" s="120"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="116"/>
-      <c r="W57" s="117"/>
-      <c r="X57" s="118"/>
+      <c r="V57" s="118"/>
+      <c r="W57" s="119"/>
+      <c r="X57" s="120"/>
       <c r="Y57" s="50"/>
-      <c r="Z57" s="116"/>
-      <c r="AA57" s="117"/>
-      <c r="AB57" s="118"/>
+      <c r="Z57" s="118"/>
+      <c r="AA57" s="119"/>
+      <c r="AB57" s="120"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="116"/>
-      <c r="AE57" s="117"/>
-      <c r="AF57" s="118"/>
+      <c r="AD57" s="118"/>
+      <c r="AE57" s="119"/>
+      <c r="AF57" s="120"/>
       <c r="AG57" s="44"/>
-      <c r="AH57" s="116"/>
-      <c r="AI57" s="117"/>
-      <c r="AJ57" s="118"/>
+      <c r="AH57" s="118"/>
+      <c r="AI57" s="119"/>
+      <c r="AJ57" s="120"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="116"/>
-      <c r="AM57" s="117"/>
-      <c r="AN57" s="118"/>
+      <c r="AL57" s="118"/>
+      <c r="AM57" s="119"/>
+      <c r="AN57" s="120"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="116"/>
-      <c r="C58" s="117"/>
-      <c r="D58" s="118"/>
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="118"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="120"/>
       <c r="E58" s="44"/>
-      <c r="F58" s="116"/>
-      <c r="G58" s="117"/>
-      <c r="H58" s="118"/>
+      <c r="F58" s="118"/>
+      <c r="G58" s="119"/>
+      <c r="H58" s="120"/>
       <c r="I58" s="50"/>
-      <c r="J58" s="116"/>
-      <c r="K58" s="117"/>
-      <c r="L58" s="118"/>
+      <c r="J58" s="118"/>
+      <c r="K58" s="119"/>
+      <c r="L58" s="120"/>
       <c r="M58" s="5"/>
       <c r="N58" s="35"/>
       <c r="O58" s="35"/>
@@ -5784,7 +5784,7 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="35"/>
       <c r="C59" s="35"/>
       <c r="D59" s="35"/>
@@ -5809,22 +5809,22 @@
       <c r="S59" s="111"/>
       <c r="T59" s="34"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="124" t="s">
+      <c r="V59" s="128" t="s">
         <v>71</v>
       </c>
-      <c r="W59" s="125"/>
+      <c r="W59" s="129"/>
       <c r="X59" s="57"/>
       <c r="Y59" s="56"/>
-      <c r="Z59" s="124" t="s">
+      <c r="Z59" s="128" t="s">
         <v>71</v>
       </c>
-      <c r="AA59" s="125"/>
+      <c r="AA59" s="129"/>
       <c r="AB59" s="57"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="124" t="s">
+      <c r="AD59" s="128" t="s">
         <v>71</v>
       </c>
-      <c r="AE59" s="125"/>
+      <c r="AE59" s="129"/>
       <c r="AF59" s="57"/>
       <c r="AG59" s="36"/>
       <c r="AH59" s="110"/>
@@ -5836,11 +5836,11 @@
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="135" t="s">
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="136"/>
+      <c r="C60" s="117"/>
       <c r="D60" s="58"/>
       <c r="E60" s="32"/>
       <c r="F60" s="74"/>
@@ -5863,23 +5863,23 @@
       <c r="S60" s="108"/>
       <c r="T60" s="109"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="138" t="s">
+      <c r="V60" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="W60" s="139"/>
-      <c r="X60" s="140"/>
+      <c r="W60" s="146"/>
+      <c r="X60" s="147"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="138" t="s">
+      <c r="Z60" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="AA60" s="139"/>
-      <c r="AB60" s="140"/>
+      <c r="AA60" s="146"/>
+      <c r="AB60" s="147"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="138" t="s">
+      <c r="AD60" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="AE60" s="139"/>
-      <c r="AF60" s="140"/>
+      <c r="AE60" s="146"/>
+      <c r="AF60" s="147"/>
       <c r="AG60" s="36"/>
       <c r="AH60" s="107"/>
       <c r="AI60" s="108"/>
@@ -5890,7 +5890,7 @@
       <c r="AN60" s="109"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="99"/>
       <c r="C61" s="100"/>
       <c r="D61" s="101"/>
@@ -5903,36 +5903,36 @@
       <c r="K61" s="100"/>
       <c r="L61" s="101"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="119"/>
-      <c r="O61" s="120"/>
-      <c r="P61" s="121"/>
+      <c r="N61" s="125"/>
+      <c r="O61" s="126"/>
+      <c r="P61" s="127"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="119"/>
-      <c r="S61" s="120"/>
-      <c r="T61" s="121"/>
+      <c r="R61" s="125"/>
+      <c r="S61" s="126"/>
+      <c r="T61" s="127"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="208"/>
-      <c r="W61" s="209"/>
-      <c r="X61" s="214"/>
+      <c r="V61" s="142"/>
+      <c r="W61" s="143"/>
+      <c r="X61" s="144"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="208"/>
-      <c r="AA61" s="209"/>
-      <c r="AB61" s="214"/>
+      <c r="Z61" s="142"/>
+      <c r="AA61" s="143"/>
+      <c r="AB61" s="144"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="208"/>
-      <c r="AE61" s="209"/>
-      <c r="AF61" s="214"/>
+      <c r="AD61" s="142"/>
+      <c r="AE61" s="143"/>
+      <c r="AF61" s="144"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="119"/>
-      <c r="AI61" s="120"/>
-      <c r="AJ61" s="121"/>
+      <c r="AH61" s="125"/>
+      <c r="AI61" s="126"/>
+      <c r="AJ61" s="127"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="119"/>
-      <c r="AM61" s="120"/>
-      <c r="AN61" s="121"/>
+      <c r="AL61" s="125"/>
+      <c r="AM61" s="126"/>
+      <c r="AN61" s="127"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="87"/>
       <c r="C62" s="88"/>
       <c r="D62" s="102"/>
@@ -5957,23 +5957,23 @@
       <c r="S62" s="90"/>
       <c r="T62" s="91"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="129" t="s">
-        <v>118</v>
-      </c>
-      <c r="W62" s="130"/>
-      <c r="X62" s="131"/>
+      <c r="V62" s="136" t="s">
+        <v>117</v>
+      </c>
+      <c r="W62" s="137"/>
+      <c r="X62" s="138"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="129" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA62" s="130"/>
-      <c r="AB62" s="131"/>
+      <c r="Z62" s="136" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA62" s="137"/>
+      <c r="AB62" s="138"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="129" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE62" s="130"/>
-      <c r="AF62" s="131"/>
+      <c r="AD62" s="136" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE62" s="137"/>
+      <c r="AF62" s="138"/>
       <c r="AG62" s="37"/>
       <c r="AH62" s="82"/>
       <c r="AI62" s="83"/>
@@ -5984,7 +5984,7 @@
       <c r="AN62" s="84"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="82" t="s">
         <v>10</v>
       </c>
@@ -6009,17 +6009,17 @@
       <c r="S63" s="90"/>
       <c r="T63" s="91"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="215"/>
-      <c r="W63" s="216"/>
-      <c r="X63" s="217"/>
+      <c r="V63" s="149"/>
+      <c r="W63" s="150"/>
+      <c r="X63" s="151"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="215"/>
-      <c r="AA63" s="216"/>
-      <c r="AB63" s="217"/>
+      <c r="Z63" s="149"/>
+      <c r="AA63" s="150"/>
+      <c r="AB63" s="151"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="215"/>
-      <c r="AE63" s="216"/>
-      <c r="AF63" s="217"/>
+      <c r="AD63" s="149"/>
+      <c r="AE63" s="150"/>
+      <c r="AF63" s="151"/>
       <c r="AG63" s="44"/>
       <c r="AH63" s="89"/>
       <c r="AI63" s="90"/>
@@ -6030,55 +6030,55 @@
       <c r="AN63" s="91"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="189" t="s">
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="197" t="s">
         <v>92</v>
       </c>
-      <c r="C64" s="190"/>
-      <c r="D64" s="191"/>
+      <c r="C64" s="198"/>
+      <c r="D64" s="199"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="116"/>
-      <c r="G64" s="117"/>
-      <c r="H64" s="118"/>
+      <c r="F64" s="118"/>
+      <c r="G64" s="119"/>
+      <c r="H64" s="120"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="116"/>
-      <c r="K64" s="117"/>
-      <c r="L64" s="118"/>
+      <c r="J64" s="118"/>
+      <c r="K64" s="119"/>
+      <c r="L64" s="120"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="116"/>
-      <c r="O64" s="117"/>
-      <c r="P64" s="118"/>
+      <c r="N64" s="118"/>
+      <c r="O64" s="119"/>
+      <c r="P64" s="120"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="116"/>
-      <c r="S64" s="117"/>
-      <c r="T64" s="118"/>
+      <c r="R64" s="118"/>
+      <c r="S64" s="119"/>
+      <c r="T64" s="120"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="175"/>
-      <c r="W64" s="176"/>
-      <c r="X64" s="177"/>
+      <c r="V64" s="139"/>
+      <c r="W64" s="140"/>
+      <c r="X64" s="141"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="175"/>
-      <c r="AA64" s="176"/>
-      <c r="AB64" s="177"/>
+      <c r="Z64" s="139"/>
+      <c r="AA64" s="140"/>
+      <c r="AB64" s="141"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="175"/>
-      <c r="AE64" s="176"/>
-      <c r="AF64" s="177"/>
+      <c r="AD64" s="139"/>
+      <c r="AE64" s="140"/>
+      <c r="AF64" s="141"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="116"/>
-      <c r="AI64" s="117"/>
-      <c r="AJ64" s="118"/>
+      <c r="AH64" s="118"/>
+      <c r="AI64" s="119"/>
+      <c r="AJ64" s="120"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="116"/>
-      <c r="AM64" s="117"/>
-      <c r="AN64" s="118"/>
+      <c r="AL64" s="118"/>
+      <c r="AM64" s="119"/>
+      <c r="AN64" s="120"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A65" s="12"/>
-      <c r="B65" s="116"/>
-      <c r="C65" s="117"/>
-      <c r="D65" s="118"/>
+      <c r="B65" s="118"/>
+      <c r="C65" s="119"/>
+      <c r="D65" s="120"/>
       <c r="E65" s="33"/>
       <c r="F65" s="33"/>
       <c r="G65" s="33"/>
@@ -6120,7 +6120,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
       <c r="B66" s="40"/>
       <c r="C66" s="33"/>
@@ -6134,23 +6134,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="137" t="s">
+      <c r="N66" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="137"/>
-      <c r="P66" s="137"/>
-      <c r="Q66" s="137"/>
-      <c r="R66" s="137"/>
-      <c r="S66" s="137"/>
-      <c r="T66" s="137"/>
-      <c r="U66" s="137"/>
-      <c r="V66" s="137"/>
-      <c r="W66" s="137"/>
-      <c r="X66" s="137"/>
-      <c r="Y66" s="137"/>
-      <c r="Z66" s="137"/>
-      <c r="AA66" s="137"/>
-      <c r="AB66" s="137"/>
+      <c r="O66" s="148"/>
+      <c r="P66" s="148"/>
+      <c r="Q66" s="148"/>
+      <c r="R66" s="148"/>
+      <c r="S66" s="148"/>
+      <c r="T66" s="148"/>
+      <c r="U66" s="148"/>
+      <c r="V66" s="148"/>
+      <c r="W66" s="148"/>
+      <c r="X66" s="148"/>
+      <c r="Y66" s="148"/>
+      <c r="Z66" s="148"/>
+      <c r="AA66" s="148"/>
+      <c r="AB66" s="148"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -6167,7 +6167,7 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
       <c r="B67" s="33"/>
       <c r="C67" s="33"/>
@@ -6181,21 +6181,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="137"/>
-      <c r="O67" s="137"/>
-      <c r="P67" s="137"/>
-      <c r="Q67" s="137"/>
-      <c r="R67" s="137"/>
-      <c r="S67" s="137"/>
-      <c r="T67" s="137"/>
-      <c r="U67" s="137"/>
-      <c r="V67" s="137"/>
-      <c r="W67" s="137"/>
-      <c r="X67" s="137"/>
-      <c r="Y67" s="137"/>
-      <c r="Z67" s="137"/>
-      <c r="AA67" s="137"/>
-      <c r="AB67" s="137"/>
+      <c r="N67" s="148"/>
+      <c r="O67" s="148"/>
+      <c r="P67" s="148"/>
+      <c r="Q67" s="148"/>
+      <c r="R67" s="148"/>
+      <c r="S67" s="148"/>
+      <c r="T67" s="148"/>
+      <c r="U67" s="148"/>
+      <c r="V67" s="148"/>
+      <c r="W67" s="148"/>
+      <c r="X67" s="148"/>
+      <c r="Y67" s="148"/>
+      <c r="Z67" s="148"/>
+      <c r="AA67" s="148"/>
+      <c r="AB67" s="148"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -6213,7 +6213,7 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
       <c r="B68" s="76" t="s">
         <v>93</v>
@@ -6221,19 +6221,17 @@
       <c r="C68" s="77"/>
       <c r="D68" s="72"/>
       <c r="E68" s="36"/>
-      <c r="F68" s="135" t="s">
+      <c r="F68" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="G68" s="136"/>
+      <c r="G68" s="117"/>
       <c r="H68" s="58" t="s">
         <v>95</v>
       </c>
       <c r="I68" s="32"/>
-      <c r="J68" s="135" t="s">
-        <v>58</v>
-      </c>
-      <c r="K68" s="136"/>
-      <c r="L68" s="58"/>
+      <c r="J68" s="74"/>
+      <c r="K68" s="75"/>
+      <c r="L68" s="54"/>
       <c r="M68" s="4"/>
       <c r="N68" s="110" t="s">
         <v>58</v>
@@ -6279,25 +6277,23 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
-      <c r="B69" s="195" t="s">
+      <c r="B69" s="200" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="196"/>
-      <c r="D69" s="197"/>
+      <c r="C69" s="201"/>
+      <c r="D69" s="202"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="195" t="s">
+      <c r="F69" s="200" t="s">
         <v>97</v>
       </c>
-      <c r="G69" s="196"/>
-      <c r="H69" s="197"/>
+      <c r="G69" s="201"/>
+      <c r="H69" s="202"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="138" t="s">
-        <v>59</v>
-      </c>
-      <c r="K69" s="139"/>
-      <c r="L69" s="140"/>
+      <c r="J69" s="99"/>
+      <c r="K69" s="100"/>
+      <c r="L69" s="101"/>
       <c r="M69" s="4"/>
       <c r="N69" s="107" t="s">
         <v>59</v>
@@ -6341,63 +6337,61 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
-      <c r="B70" s="152" t="s">
+      <c r="B70" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="C70" s="153"/>
-      <c r="D70" s="170"/>
+      <c r="C70" s="166"/>
+      <c r="D70" s="183"/>
       <c r="E70" s="31"/>
-      <c r="F70" s="152" t="s">
+      <c r="F70" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="G70" s="153"/>
-      <c r="H70" s="170"/>
+      <c r="G70" s="166"/>
+      <c r="H70" s="183"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="192" t="s">
-        <v>98</v>
-      </c>
-      <c r="K70" s="193"/>
-      <c r="L70" s="194"/>
+      <c r="J70" s="87"/>
+      <c r="K70" s="88"/>
+      <c r="L70" s="102"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="119" t="s">
+      <c r="N70" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="120"/>
-      <c r="P70" s="121"/>
+      <c r="O70" s="126"/>
+      <c r="P70" s="127"/>
       <c r="Q70" s="32"/>
-      <c r="R70" s="119" t="s">
+      <c r="R70" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="S70" s="120"/>
-      <c r="T70" s="121"/>
+      <c r="S70" s="126"/>
+      <c r="T70" s="127"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="119" t="s">
+      <c r="V70" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="W70" s="120"/>
-      <c r="X70" s="121"/>
+      <c r="W70" s="126"/>
+      <c r="X70" s="127"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="119" t="s">
+      <c r="Z70" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="AA70" s="120"/>
-      <c r="AB70" s="121"/>
+      <c r="AA70" s="126"/>
+      <c r="AB70" s="127"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="119" t="s">
+      <c r="AD70" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="AE70" s="120"/>
-      <c r="AF70" s="121"/>
+      <c r="AE70" s="126"/>
+      <c r="AF70" s="127"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="119"/>
-      <c r="AI70" s="120"/>
-      <c r="AJ70" s="121"/>
+      <c r="AH70" s="125"/>
+      <c r="AI70" s="126"/>
+      <c r="AJ70" s="127"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="119"/>
-      <c r="AM70" s="120"/>
-      <c r="AN70" s="121"/>
+      <c r="AL70" s="125"/>
+      <c r="AM70" s="126"/>
+      <c r="AN70" s="127"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -6405,13 +6399,13 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="155" t="s">
+      <c r="B71" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="156"/>
-      <c r="D71" s="157"/>
+      <c r="C71" s="169"/>
+      <c r="D71" s="170"/>
       <c r="E71" s="32"/>
       <c r="F71" s="82" t="s">
         <v>19</v>
@@ -6419,9 +6413,7 @@
       <c r="G71" s="83"/>
       <c r="H71" s="84"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="82" t="s">
-        <v>14</v>
-      </c>
+      <c r="J71" s="82"/>
       <c r="K71" s="83"/>
       <c r="L71" s="84"/>
       <c r="M71" s="9"/>
@@ -6469,53 +6461,53 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12"/>
-      <c r="B72" s="165"/>
-      <c r="C72" s="166"/>
-      <c r="D72" s="167"/>
+      <c r="B72" s="178"/>
+      <c r="C72" s="179"/>
+      <c r="D72" s="180"/>
       <c r="E72" s="36"/>
-      <c r="F72" s="116"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="118"/>
+      <c r="F72" s="118"/>
+      <c r="G72" s="119"/>
+      <c r="H72" s="120"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="116"/>
-      <c r="K72" s="117"/>
-      <c r="L72" s="118"/>
+      <c r="J72" s="118"/>
+      <c r="K72" s="119"/>
+      <c r="L72" s="120"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="116"/>
-      <c r="O72" s="117"/>
-      <c r="P72" s="118"/>
+      <c r="N72" s="118"/>
+      <c r="O72" s="119"/>
+      <c r="P72" s="120"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="116"/>
-      <c r="S72" s="117"/>
-      <c r="T72" s="118"/>
+      <c r="R72" s="118"/>
+      <c r="S72" s="119"/>
+      <c r="T72" s="120"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="116"/>
-      <c r="W72" s="117"/>
-      <c r="X72" s="118"/>
+      <c r="V72" s="118"/>
+      <c r="W72" s="119"/>
+      <c r="X72" s="120"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="116"/>
-      <c r="AA72" s="117"/>
-      <c r="AB72" s="118"/>
+      <c r="Z72" s="118"/>
+      <c r="AA72" s="119"/>
+      <c r="AB72" s="120"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="116"/>
-      <c r="AE72" s="117"/>
-      <c r="AF72" s="118"/>
+      <c r="AD72" s="118"/>
+      <c r="AE72" s="119"/>
+      <c r="AF72" s="120"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="116"/>
-      <c r="AI72" s="117"/>
-      <c r="AJ72" s="118"/>
+      <c r="AH72" s="118"/>
+      <c r="AI72" s="119"/>
+      <c r="AJ72" s="120"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="116"/>
-      <c r="AM72" s="117"/>
-      <c r="AN72" s="118"/>
+      <c r="AL72" s="118"/>
+      <c r="AM72" s="119"/>
+      <c r="AN72" s="120"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -6561,7 +6553,7 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
       <c r="B74" s="74" t="s">
         <v>43</v>
@@ -6619,7 +6611,7 @@
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="99" t="s">
         <v>48</v>
@@ -6675,7 +6667,7 @@
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
       <c r="B76" s="87" t="s">
         <v>39</v>
@@ -6695,45 +6687,45 @@
       <c r="K76" s="88"/>
       <c r="L76" s="102"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="119" t="s">
+      <c r="N76" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="O76" s="120"/>
-      <c r="P76" s="121"/>
+      <c r="O76" s="126"/>
+      <c r="P76" s="127"/>
       <c r="Q76" s="32"/>
-      <c r="R76" s="119" t="s">
+      <c r="R76" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="S76" s="120"/>
-      <c r="T76" s="121"/>
+      <c r="S76" s="126"/>
+      <c r="T76" s="127"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="119"/>
-      <c r="W76" s="120"/>
-      <c r="X76" s="121"/>
+      <c r="V76" s="125"/>
+      <c r="W76" s="126"/>
+      <c r="X76" s="127"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="119"/>
-      <c r="AA76" s="120"/>
-      <c r="AB76" s="121"/>
+      <c r="Z76" s="125"/>
+      <c r="AA76" s="126"/>
+      <c r="AB76" s="127"/>
       <c r="AC76" s="36"/>
-      <c r="AD76" s="119" t="s">
+      <c r="AD76" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="AE76" s="120"/>
-      <c r="AF76" s="121"/>
+      <c r="AE76" s="126"/>
+      <c r="AF76" s="127"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="119"/>
-      <c r="AI76" s="120"/>
-      <c r="AJ76" s="121"/>
+      <c r="AH76" s="125"/>
+      <c r="AI76" s="126"/>
+      <c r="AJ76" s="127"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="119"/>
-      <c r="AM76" s="120"/>
-      <c r="AN76" s="121"/>
+      <c r="AL76" s="125"/>
+      <c r="AM76" s="126"/>
+      <c r="AN76" s="127"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
       <c r="B77" s="82" t="s">
         <v>28</v>
@@ -6791,53 +6783,53 @@
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
-      <c r="B78" s="116"/>
-      <c r="C78" s="117"/>
-      <c r="D78" s="118"/>
+      <c r="B78" s="118"/>
+      <c r="C78" s="119"/>
+      <c r="D78" s="120"/>
       <c r="E78" s="32"/>
-      <c r="F78" s="116"/>
-      <c r="G78" s="117"/>
-      <c r="H78" s="118"/>
+      <c r="F78" s="118"/>
+      <c r="G78" s="119"/>
+      <c r="H78" s="120"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="116"/>
-      <c r="K78" s="117"/>
-      <c r="L78" s="118"/>
+      <c r="J78" s="118"/>
+      <c r="K78" s="119"/>
+      <c r="L78" s="120"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="116"/>
-      <c r="O78" s="117"/>
-      <c r="P78" s="118"/>
+      <c r="N78" s="118"/>
+      <c r="O78" s="119"/>
+      <c r="P78" s="120"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="116"/>
-      <c r="S78" s="117"/>
-      <c r="T78" s="118"/>
+      <c r="R78" s="118"/>
+      <c r="S78" s="119"/>
+      <c r="T78" s="120"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="116"/>
-      <c r="W78" s="117"/>
-      <c r="X78" s="118"/>
+      <c r="V78" s="118"/>
+      <c r="W78" s="119"/>
+      <c r="X78" s="120"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="116"/>
-      <c r="AA78" s="117"/>
-      <c r="AB78" s="118"/>
+      <c r="Z78" s="118"/>
+      <c r="AA78" s="119"/>
+      <c r="AB78" s="120"/>
       <c r="AC78" s="32"/>
-      <c r="AD78" s="116"/>
-      <c r="AE78" s="117"/>
-      <c r="AF78" s="118"/>
+      <c r="AD78" s="118"/>
+      <c r="AE78" s="119"/>
+      <c r="AF78" s="120"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="116"/>
-      <c r="AI78" s="117"/>
-      <c r="AJ78" s="118"/>
+      <c r="AH78" s="118"/>
+      <c r="AI78" s="119"/>
+      <c r="AJ78" s="120"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="116"/>
-      <c r="AM78" s="117"/>
-      <c r="AN78" s="118"/>
+      <c r="AL78" s="118"/>
+      <c r="AM78" s="119"/>
+      <c r="AN78" s="120"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -6883,7 +6875,7 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
       <c r="B80" s="74" t="s">
         <v>42</v>
@@ -6891,10 +6883,10 @@
       <c r="C80" s="75"/>
       <c r="D80" s="54"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="135" t="s">
-        <v>99</v>
-      </c>
-      <c r="G80" s="136"/>
+      <c r="F80" s="116" t="s">
+        <v>98</v>
+      </c>
+      <c r="G80" s="117"/>
       <c r="H80" s="58" t="s">
         <v>69</v>
       </c>
@@ -6949,14 +6941,14 @@
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="99"/>
       <c r="C81" s="100"/>
       <c r="D81" s="101"/>
       <c r="E81" s="32"/>
       <c r="F81" s="99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G81" s="100"/>
       <c r="H81" s="101"/>
@@ -7009,7 +7001,7 @@
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
       <c r="B82" s="87" t="s">
         <v>39</v>
@@ -7017,51 +7009,51 @@
       <c r="C82" s="88"/>
       <c r="D82" s="102"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="152" t="s">
+      <c r="F82" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="153"/>
-      <c r="H82" s="170"/>
+      <c r="G82" s="166"/>
+      <c r="H82" s="183"/>
       <c r="I82" s="32"/>
       <c r="J82" s="87"/>
       <c r="K82" s="88"/>
       <c r="L82" s="102"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="119" t="s">
+      <c r="N82" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="O82" s="120"/>
-      <c r="P82" s="121"/>
+      <c r="O82" s="126"/>
+      <c r="P82" s="127"/>
       <c r="Q82" s="31"/>
-      <c r="R82" s="119"/>
-      <c r="S82" s="120"/>
-      <c r="T82" s="121"/>
+      <c r="R82" s="125"/>
+      <c r="S82" s="126"/>
+      <c r="T82" s="127"/>
       <c r="U82" s="36"/>
-      <c r="V82" s="119"/>
-      <c r="W82" s="120"/>
-      <c r="X82" s="121"/>
+      <c r="V82" s="125"/>
+      <c r="W82" s="126"/>
+      <c r="X82" s="127"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="119"/>
-      <c r="AA82" s="120"/>
-      <c r="AB82" s="121"/>
+      <c r="Z82" s="125"/>
+      <c r="AA82" s="126"/>
+      <c r="AB82" s="127"/>
       <c r="AC82" s="31"/>
-      <c r="AD82" s="119"/>
-      <c r="AE82" s="120"/>
-      <c r="AF82" s="121"/>
+      <c r="AD82" s="125"/>
+      <c r="AE82" s="126"/>
+      <c r="AF82" s="127"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="119"/>
-      <c r="AI82" s="120"/>
-      <c r="AJ82" s="121"/>
+      <c r="AH82" s="125"/>
+      <c r="AI82" s="126"/>
+      <c r="AJ82" s="127"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="119"/>
-      <c r="AM82" s="120"/>
-      <c r="AN82" s="121"/>
+      <c r="AL82" s="125"/>
+      <c r="AM82" s="126"/>
+      <c r="AN82" s="127"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
       <c r="B83" s="82" t="s">
         <v>15</v>
@@ -7125,55 +7117,55 @@
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12"/>
-      <c r="B84" s="116"/>
-      <c r="C84" s="117"/>
-      <c r="D84" s="118"/>
+      <c r="B84" s="118"/>
+      <c r="C84" s="119"/>
+      <c r="D84" s="120"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="116"/>
-      <c r="G84" s="117"/>
-      <c r="H84" s="118"/>
+      <c r="F84" s="118"/>
+      <c r="G84" s="119"/>
+      <c r="H84" s="120"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="116"/>
-      <c r="K84" s="117"/>
-      <c r="L84" s="118"/>
+      <c r="J84" s="118"/>
+      <c r="K84" s="119"/>
+      <c r="L84" s="120"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="116" t="s">
+      <c r="N84" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="O84" s="117"/>
-      <c r="P84" s="118"/>
+      <c r="O84" s="119"/>
+      <c r="P84" s="120"/>
       <c r="Q84" s="44"/>
-      <c r="R84" s="116"/>
-      <c r="S84" s="117"/>
-      <c r="T84" s="118"/>
+      <c r="R84" s="118"/>
+      <c r="S84" s="119"/>
+      <c r="T84" s="120"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="116"/>
-      <c r="W84" s="117"/>
-      <c r="X84" s="118"/>
+      <c r="V84" s="118"/>
+      <c r="W84" s="119"/>
+      <c r="X84" s="120"/>
       <c r="Y84" s="31"/>
-      <c r="Z84" s="116"/>
-      <c r="AA84" s="117"/>
-      <c r="AB84" s="118"/>
+      <c r="Z84" s="118"/>
+      <c r="AA84" s="119"/>
+      <c r="AB84" s="120"/>
       <c r="AC84" s="31"/>
-      <c r="AD84" s="116"/>
-      <c r="AE84" s="117"/>
-      <c r="AF84" s="118"/>
+      <c r="AD84" s="118"/>
+      <c r="AE84" s="119"/>
+      <c r="AF84" s="120"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="116"/>
-      <c r="AI84" s="117"/>
-      <c r="AJ84" s="118"/>
+      <c r="AH84" s="118"/>
+      <c r="AI84" s="119"/>
+      <c r="AJ84" s="120"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="116"/>
-      <c r="AM84" s="117"/>
-      <c r="AN84" s="118"/>
+      <c r="AL84" s="118"/>
+      <c r="AM84" s="119"/>
+      <c r="AN84" s="120"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -7219,12 +7211,12 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
-      <c r="B86" s="178" t="s">
-        <v>101</v>
-      </c>
-      <c r="C86" s="179"/>
+      <c r="B86" s="213" t="s">
+        <v>100</v>
+      </c>
+      <c r="C86" s="214"/>
       <c r="D86" s="63"/>
       <c r="E86" s="32"/>
       <c r="F86" s="74"/>
@@ -7275,11 +7267,11 @@
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
-      <c r="B87" s="195"/>
-      <c r="C87" s="196"/>
-      <c r="D87" s="197"/>
+      <c r="B87" s="200"/>
+      <c r="C87" s="201"/>
+      <c r="D87" s="202"/>
       <c r="E87" s="32"/>
       <c r="F87" s="99"/>
       <c r="G87" s="100"/>
@@ -7321,13 +7313,13 @@
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
-      <c r="B88" s="152" t="s">
+      <c r="B88" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="C88" s="153"/>
-      <c r="D88" s="170"/>
+      <c r="C88" s="166"/>
+      <c r="D88" s="183"/>
       <c r="E88" s="32"/>
       <c r="F88" s="87"/>
       <c r="G88" s="88"/>
@@ -7337,47 +7329,47 @@
       <c r="K88" s="88"/>
       <c r="L88" s="102"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="119" t="s">
+      <c r="N88" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="O88" s="120"/>
-      <c r="P88" s="121"/>
+      <c r="O88" s="126"/>
+      <c r="P88" s="127"/>
       <c r="Q88" s="31"/>
-      <c r="R88" s="119"/>
-      <c r="S88" s="120"/>
-      <c r="T88" s="121"/>
+      <c r="R88" s="125"/>
+      <c r="S88" s="126"/>
+      <c r="T88" s="127"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="119" t="s">
+      <c r="V88" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="W88" s="120"/>
-      <c r="X88" s="121"/>
+      <c r="W88" s="126"/>
+      <c r="X88" s="127"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="119" t="s">
+      <c r="Z88" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="AA88" s="120"/>
-      <c r="AB88" s="121"/>
+      <c r="AA88" s="126"/>
+      <c r="AB88" s="127"/>
       <c r="AC88" s="36"/>
-      <c r="AD88" s="119" t="s">
+      <c r="AD88" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="AE88" s="120"/>
-      <c r="AF88" s="121"/>
+      <c r="AE88" s="126"/>
+      <c r="AF88" s="127"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="119"/>
-      <c r="AI88" s="120"/>
-      <c r="AJ88" s="121"/>
+      <c r="AH88" s="125"/>
+      <c r="AI88" s="126"/>
+      <c r="AJ88" s="127"/>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="119"/>
-      <c r="AM88" s="120"/>
-      <c r="AN88" s="121"/>
+      <c r="AL88" s="125"/>
+      <c r="AM88" s="126"/>
+      <c r="AN88" s="127"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="82" t="s">
         <v>29</v>
@@ -7433,55 +7425,55 @@
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="12"/>
-      <c r="B90" s="202" t="s">
-        <v>102</v>
-      </c>
-      <c r="C90" s="203"/>
-      <c r="D90" s="204"/>
+      <c r="B90" s="203" t="s">
+        <v>101</v>
+      </c>
+      <c r="C90" s="204"/>
+      <c r="D90" s="205"/>
       <c r="E90" s="31"/>
-      <c r="F90" s="116"/>
-      <c r="G90" s="117"/>
-      <c r="H90" s="118"/>
+      <c r="F90" s="118"/>
+      <c r="G90" s="119"/>
+      <c r="H90" s="120"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="116"/>
-      <c r="K90" s="117"/>
-      <c r="L90" s="118"/>
+      <c r="J90" s="118"/>
+      <c r="K90" s="119"/>
+      <c r="L90" s="120"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="116"/>
-      <c r="O90" s="117"/>
-      <c r="P90" s="118"/>
+      <c r="N90" s="118"/>
+      <c r="O90" s="119"/>
+      <c r="P90" s="120"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="116"/>
-      <c r="S90" s="117"/>
-      <c r="T90" s="118"/>
+      <c r="R90" s="118"/>
+      <c r="S90" s="119"/>
+      <c r="T90" s="120"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="116"/>
-      <c r="W90" s="117"/>
-      <c r="X90" s="118"/>
+      <c r="V90" s="118"/>
+      <c r="W90" s="119"/>
+      <c r="X90" s="120"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="116"/>
-      <c r="AA90" s="117"/>
-      <c r="AB90" s="118"/>
+      <c r="Z90" s="118"/>
+      <c r="AA90" s="119"/>
+      <c r="AB90" s="120"/>
       <c r="AC90" s="32"/>
-      <c r="AD90" s="116"/>
-      <c r="AE90" s="117"/>
-      <c r="AF90" s="118"/>
+      <c r="AD90" s="118"/>
+      <c r="AE90" s="119"/>
+      <c r="AF90" s="120"/>
       <c r="AG90" s="31"/>
-      <c r="AH90" s="116"/>
-      <c r="AI90" s="117"/>
-      <c r="AJ90" s="118"/>
+      <c r="AH90" s="118"/>
+      <c r="AI90" s="119"/>
+      <c r="AJ90" s="120"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="116"/>
-      <c r="AM90" s="117"/>
-      <c r="AN90" s="118"/>
+      <c r="AL90" s="118"/>
+      <c r="AM90" s="119"/>
+      <c r="AN90" s="120"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35"/>
@@ -7527,18 +7519,18 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
-      <c r="B92" s="124" t="s">
+      <c r="B92" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="C92" s="125"/>
+      <c r="C92" s="129"/>
       <c r="D92" s="57"/>
       <c r="E92" s="32"/>
-      <c r="F92" s="173" t="s">
+      <c r="F92" s="186" t="s">
         <v>76</v>
       </c>
-      <c r="G92" s="174"/>
+      <c r="G92" s="187"/>
       <c r="H92" s="66"/>
       <c r="I92" s="32"/>
       <c r="J92" s="74"/>
@@ -7587,18 +7579,18 @@
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
-      <c r="B93" s="208" t="s">
-        <v>103</v>
-      </c>
-      <c r="C93" s="209"/>
+      <c r="B93" s="142" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" s="143"/>
       <c r="D93" s="67"/>
       <c r="E93" s="32"/>
-      <c r="F93" s="210" t="s">
-        <v>103</v>
-      </c>
-      <c r="G93" s="211"/>
+      <c r="F93" s="209" t="s">
+        <v>102</v>
+      </c>
+      <c r="G93" s="210"/>
       <c r="H93" s="68"/>
       <c r="I93" s="35"/>
       <c r="J93" s="99"/>
@@ -7647,20 +7639,20 @@
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
-      <c r="B94" s="212" t="s">
-        <v>102</v>
-      </c>
-      <c r="C94" s="213"/>
+      <c r="B94" s="211" t="s">
+        <v>101</v>
+      </c>
+      <c r="C94" s="212"/>
       <c r="D94" s="69" t="s">
         <v>32</v>
       </c>
       <c r="E94" s="32"/>
-      <c r="F94" s="212" t="s">
-        <v>102</v>
-      </c>
-      <c r="G94" s="213"/>
+      <c r="F94" s="211" t="s">
+        <v>101</v>
+      </c>
+      <c r="G94" s="212"/>
       <c r="H94" s="69" t="s">
         <v>32</v>
       </c>
@@ -7669,52 +7661,52 @@
       <c r="K94" s="88"/>
       <c r="L94" s="102"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="119"/>
-      <c r="O94" s="120"/>
-      <c r="P94" s="121"/>
+      <c r="N94" s="125"/>
+      <c r="O94" s="126"/>
+      <c r="P94" s="127"/>
       <c r="Q94" s="32"/>
-      <c r="R94" s="119"/>
-      <c r="S94" s="120"/>
-      <c r="T94" s="121"/>
+      <c r="R94" s="125"/>
+      <c r="S94" s="126"/>
+      <c r="T94" s="127"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="119"/>
-      <c r="W94" s="120"/>
-      <c r="X94" s="121"/>
+      <c r="V94" s="125"/>
+      <c r="W94" s="126"/>
+      <c r="X94" s="127"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="119"/>
-      <c r="AA94" s="120"/>
-      <c r="AB94" s="121"/>
+      <c r="Z94" s="125"/>
+      <c r="AA94" s="126"/>
+      <c r="AB94" s="127"/>
       <c r="AC94" s="31"/>
-      <c r="AD94" s="119"/>
-      <c r="AE94" s="120"/>
-      <c r="AF94" s="121"/>
+      <c r="AD94" s="125"/>
+      <c r="AE94" s="126"/>
+      <c r="AF94" s="127"/>
       <c r="AG94" s="32"/>
-      <c r="AH94" s="119"/>
-      <c r="AI94" s="120"/>
-      <c r="AJ94" s="121"/>
+      <c r="AH94" s="125"/>
+      <c r="AI94" s="126"/>
+      <c r="AJ94" s="127"/>
       <c r="AK94" s="32"/>
-      <c r="AL94" s="119"/>
-      <c r="AM94" s="120"/>
-      <c r="AN94" s="121"/>
+      <c r="AL94" s="125"/>
+      <c r="AM94" s="126"/>
+      <c r="AN94" s="127"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
-      <c r="B95" s="171" t="s">
-        <v>104</v>
-      </c>
-      <c r="C95" s="172"/>
+      <c r="B95" s="184" t="s">
+        <v>103</v>
+      </c>
+      <c r="C95" s="185"/>
       <c r="D95" s="70" t="s">
         <v>33</v>
       </c>
       <c r="E95" s="32"/>
-      <c r="F95" s="171" t="s">
-        <v>104</v>
-      </c>
-      <c r="G95" s="172"/>
+      <c r="F95" s="184" t="s">
+        <v>103</v>
+      </c>
+      <c r="G95" s="185"/>
       <c r="H95" s="70" t="s">
         <v>33</v>
       </c>
@@ -7765,27 +7757,27 @@
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="12"/>
-      <c r="B96" s="171" t="s">
-        <v>105</v>
-      </c>
-      <c r="C96" s="172"/>
+      <c r="B96" s="184" t="s">
+        <v>104</v>
+      </c>
+      <c r="C96" s="185"/>
       <c r="D96" s="70" t="s">
         <v>34</v>
       </c>
       <c r="E96" s="31"/>
-      <c r="F96" s="171" t="s">
-        <v>106</v>
-      </c>
-      <c r="G96" s="172"/>
+      <c r="F96" s="184" t="s">
+        <v>105</v>
+      </c>
+      <c r="G96" s="185"/>
       <c r="H96" s="70" t="s">
         <v>34</v>
       </c>
       <c r="I96" s="32"/>
-      <c r="J96" s="116"/>
-      <c r="K96" s="117"/>
-      <c r="L96" s="118"/>
+      <c r="J96" s="118"/>
+      <c r="K96" s="119"/>
+      <c r="L96" s="120"/>
       <c r="M96" s="26"/>
       <c r="N96" s="89"/>
       <c r="O96" s="90"/>
@@ -7807,32 +7799,32 @@
       <c r="AE96" s="90"/>
       <c r="AF96" s="91"/>
       <c r="AG96" s="31"/>
-      <c r="AH96" s="116"/>
-      <c r="AI96" s="117"/>
-      <c r="AJ96" s="118"/>
+      <c r="AH96" s="118"/>
+      <c r="AI96" s="119"/>
+      <c r="AJ96" s="120"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="116"/>
-      <c r="AM96" s="117"/>
-      <c r="AN96" s="118"/>
+      <c r="AL96" s="118"/>
+      <c r="AM96" s="119"/>
+      <c r="AN96" s="120"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
-      <c r="B97" s="171" t="s">
+      <c r="B97" s="184" t="s">
         <v>80</v>
       </c>
-      <c r="C97" s="172"/>
+      <c r="C97" s="185"/>
       <c r="D97" s="70" t="s">
         <v>35</v>
       </c>
       <c r="E97" s="31"/>
-      <c r="F97" s="171" t="s">
+      <c r="F97" s="184" t="s">
         <v>80</v>
       </c>
-      <c r="G97" s="172"/>
+      <c r="G97" s="185"/>
       <c r="H97" s="70" t="s">
         <v>35</v>
       </c>
@@ -7883,20 +7875,20 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="12"/>
-      <c r="B98" s="168" t="s">
-        <v>107</v>
-      </c>
-      <c r="C98" s="169"/>
+      <c r="B98" s="181" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" s="182"/>
       <c r="D98" s="71" t="s">
         <v>35</v>
       </c>
       <c r="E98" s="36"/>
-      <c r="F98" s="168" t="s">
-        <v>108</v>
-      </c>
-      <c r="G98" s="169"/>
+      <c r="F98" s="181" t="s">
+        <v>107</v>
+      </c>
+      <c r="G98" s="182"/>
       <c r="H98" s="71" t="s">
         <v>35</v>
       </c>
@@ -7947,7 +7939,7 @@
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35"/>
@@ -8003,7 +7995,7 @@
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
       <c r="B100" s="74" t="s">
         <v>66</v>
@@ -8049,19 +8041,19 @@
       <c r="AE100" s="90"/>
       <c r="AF100" s="91"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="119"/>
-      <c r="AI100" s="120"/>
-      <c r="AJ100" s="121"/>
+      <c r="AH100" s="125"/>
+      <c r="AI100" s="126"/>
+      <c r="AJ100" s="127"/>
       <c r="AK100" s="32"/>
-      <c r="AL100" s="119"/>
-      <c r="AM100" s="120"/>
-      <c r="AN100" s="121"/>
+      <c r="AL100" s="125"/>
+      <c r="AM100" s="126"/>
+      <c r="AN100" s="127"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
       <c r="B101" s="87" t="s">
         <v>48</v>
@@ -8119,55 +8111,55 @@
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
-      <c r="B102" s="116" t="s">
+      <c r="B102" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="C102" s="117"/>
-      <c r="D102" s="118"/>
+      <c r="C102" s="119"/>
+      <c r="D102" s="120"/>
       <c r="E102" s="32"/>
-      <c r="F102" s="116"/>
-      <c r="G102" s="117"/>
-      <c r="H102" s="118"/>
+      <c r="F102" s="118"/>
+      <c r="G102" s="119"/>
+      <c r="H102" s="120"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="116"/>
-      <c r="K102" s="117"/>
-      <c r="L102" s="118"/>
+      <c r="J102" s="118"/>
+      <c r="K102" s="119"/>
+      <c r="L102" s="120"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="116"/>
-      <c r="O102" s="117"/>
-      <c r="P102" s="118"/>
+      <c r="N102" s="118"/>
+      <c r="O102" s="119"/>
+      <c r="P102" s="120"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="116"/>
-      <c r="S102" s="117"/>
-      <c r="T102" s="118"/>
+      <c r="R102" s="118"/>
+      <c r="S102" s="119"/>
+      <c r="T102" s="120"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="116"/>
-      <c r="W102" s="117"/>
-      <c r="X102" s="118"/>
+      <c r="V102" s="118"/>
+      <c r="W102" s="119"/>
+      <c r="X102" s="120"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="116"/>
-      <c r="AA102" s="117"/>
-      <c r="AB102" s="118"/>
+      <c r="Z102" s="118"/>
+      <c r="AA102" s="119"/>
+      <c r="AB102" s="120"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="116"/>
-      <c r="AE102" s="117"/>
-      <c r="AF102" s="118"/>
+      <c r="AD102" s="118"/>
+      <c r="AE102" s="119"/>
+      <c r="AF102" s="120"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="116"/>
-      <c r="AI102" s="117"/>
-      <c r="AJ102" s="118"/>
+      <c r="AH102" s="118"/>
+      <c r="AI102" s="119"/>
+      <c r="AJ102" s="120"/>
       <c r="AK102" s="31"/>
-      <c r="AL102" s="116"/>
-      <c r="AM102" s="117"/>
-      <c r="AN102" s="118"/>
+      <c r="AL102" s="118"/>
+      <c r="AM102" s="119"/>
+      <c r="AN102" s="120"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -8213,7 +8205,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -8230,7 +8222,7 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="110"/>
       <c r="C105" s="111"/>
       <c r="D105" s="34"/>
@@ -8244,7 +8236,7 @@
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="107"/>
       <c r="C106" s="108"/>
       <c r="D106" s="109"/>
@@ -8257,20 +8249,20 @@
       <c r="K106" s="108"/>
       <c r="L106" s="109"/>
     </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="119"/>
-      <c r="C107" s="120"/>
-      <c r="D107" s="121"/>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="125"/>
+      <c r="C107" s="126"/>
+      <c r="D107" s="127"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="119"/>
-      <c r="G107" s="120"/>
-      <c r="H107" s="121"/>
+      <c r="F107" s="125"/>
+      <c r="G107" s="126"/>
+      <c r="H107" s="127"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="119"/>
-      <c r="K107" s="120"/>
-      <c r="L107" s="121"/>
-    </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J107" s="125"/>
+      <c r="K107" s="126"/>
+      <c r="L107" s="127"/>
+    </row>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="82"/>
       <c r="C108" s="83"/>
       <c r="D108" s="84"/>
@@ -8283,20 +8275,20 @@
       <c r="K108" s="83"/>
       <c r="L108" s="84"/>
     </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="116"/>
-      <c r="C109" s="117"/>
-      <c r="D109" s="118"/>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="118"/>
+      <c r="C109" s="119"/>
+      <c r="D109" s="120"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="116"/>
-      <c r="G109" s="117"/>
-      <c r="H109" s="118"/>
+      <c r="F109" s="118"/>
+      <c r="G109" s="119"/>
+      <c r="H109" s="120"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="116"/>
-      <c r="K109" s="117"/>
-      <c r="L109" s="118"/>
-    </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J109" s="118"/>
+      <c r="K109" s="119"/>
+      <c r="L109" s="120"/>
+    </row>
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -8309,7 +8301,7 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="110"/>
       <c r="C111" s="111"/>
       <c r="D111" s="34"/>
@@ -8322,7 +8314,7 @@
       <c r="K111" s="111"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="107"/>
       <c r="C112" s="108"/>
       <c r="D112" s="109"/>
@@ -8335,20 +8327,20 @@
       <c r="K112" s="108"/>
       <c r="L112" s="109"/>
     </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="119"/>
-      <c r="C113" s="120"/>
-      <c r="D113" s="121"/>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="125"/>
+      <c r="C113" s="126"/>
+      <c r="D113" s="127"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="119"/>
-      <c r="G113" s="120"/>
-      <c r="H113" s="121"/>
+      <c r="F113" s="125"/>
+      <c r="G113" s="126"/>
+      <c r="H113" s="127"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="119"/>
-      <c r="K113" s="120"/>
-      <c r="L113" s="121"/>
-    </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J113" s="125"/>
+      <c r="K113" s="126"/>
+      <c r="L113" s="127"/>
+    </row>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="82"/>
       <c r="C114" s="83"/>
       <c r="D114" s="84"/>
@@ -8361,20 +8353,20 @@
       <c r="K114" s="83"/>
       <c r="L114" s="84"/>
     </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="116"/>
-      <c r="C115" s="117"/>
-      <c r="D115" s="118"/>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="118"/>
+      <c r="C115" s="119"/>
+      <c r="D115" s="120"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="116"/>
-      <c r="G115" s="117"/>
-      <c r="H115" s="118"/>
+      <c r="F115" s="118"/>
+      <c r="G115" s="119"/>
+      <c r="H115" s="120"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="116"/>
-      <c r="K115" s="117"/>
-      <c r="L115" s="118"/>
-    </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J115" s="118"/>
+      <c r="K115" s="119"/>
+      <c r="L115" s="120"/>
+    </row>
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -8387,7 +8379,7 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="110"/>
       <c r="C117" s="111"/>
       <c r="D117" s="34"/>
@@ -8400,7 +8392,7 @@
       <c r="K117" s="111"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="107"/>
       <c r="C118" s="108"/>
       <c r="D118" s="109"/>
@@ -8413,20 +8405,20 @@
       <c r="K118" s="108"/>
       <c r="L118" s="109"/>
     </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="119"/>
-      <c r="C119" s="120"/>
-      <c r="D119" s="121"/>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="125"/>
+      <c r="C119" s="126"/>
+      <c r="D119" s="127"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="119"/>
-      <c r="G119" s="120"/>
-      <c r="H119" s="121"/>
+      <c r="F119" s="125"/>
+      <c r="G119" s="126"/>
+      <c r="H119" s="127"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="119"/>
-      <c r="K119" s="120"/>
-      <c r="L119" s="121"/>
-    </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J119" s="125"/>
+      <c r="K119" s="126"/>
+      <c r="L119" s="127"/>
+    </row>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="82"/>
       <c r="C120" s="83"/>
       <c r="D120" s="84"/>
@@ -8439,20 +8431,20 @@
       <c r="K120" s="83"/>
       <c r="L120" s="84"/>
     </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="116"/>
-      <c r="C121" s="117"/>
-      <c r="D121" s="118"/>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="118"/>
+      <c r="C121" s="119"/>
+      <c r="D121" s="120"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="116"/>
-      <c r="G121" s="117"/>
-      <c r="H121" s="118"/>
+      <c r="F121" s="118"/>
+      <c r="G121" s="119"/>
+      <c r="H121" s="120"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="116"/>
-      <c r="K121" s="117"/>
-      <c r="L121" s="118"/>
-    </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J121" s="118"/>
+      <c r="K121" s="119"/>
+      <c r="L121" s="120"/>
+    </row>
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -8465,7 +8457,7 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="110"/>
       <c r="C123" s="111"/>
       <c r="D123" s="34"/>
@@ -8478,7 +8470,7 @@
       <c r="K123" s="111"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="107"/>
       <c r="C124" s="108"/>
       <c r="D124" s="109"/>
@@ -8491,20 +8483,20 @@
       <c r="K124" s="108"/>
       <c r="L124" s="109"/>
     </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="119"/>
-      <c r="C125" s="120"/>
-      <c r="D125" s="121"/>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="125"/>
+      <c r="C125" s="126"/>
+      <c r="D125" s="127"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="119"/>
-      <c r="G125" s="120"/>
-      <c r="H125" s="121"/>
+      <c r="F125" s="125"/>
+      <c r="G125" s="126"/>
+      <c r="H125" s="127"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="119"/>
-      <c r="K125" s="120"/>
-      <c r="L125" s="121"/>
-    </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J125" s="125"/>
+      <c r="K125" s="126"/>
+      <c r="L125" s="127"/>
+    </row>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="82"/>
       <c r="C126" s="83"/>
       <c r="D126" s="84"/>
@@ -8517,20 +8509,20 @@
       <c r="K126" s="83"/>
       <c r="L126" s="84"/>
     </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="116"/>
-      <c r="C127" s="117"/>
-      <c r="D127" s="118"/>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="118"/>
+      <c r="C127" s="119"/>
+      <c r="D127" s="120"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="116"/>
-      <c r="G127" s="117"/>
-      <c r="H127" s="118"/>
+      <c r="F127" s="118"/>
+      <c r="G127" s="119"/>
+      <c r="H127" s="120"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="116"/>
-      <c r="K127" s="117"/>
-      <c r="L127" s="118"/>
-    </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J127" s="118"/>
+      <c r="K127" s="119"/>
+      <c r="L127" s="120"/>
+    </row>
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -8543,7 +8535,7 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="110"/>
       <c r="C129" s="111"/>
       <c r="D129" s="34"/>
@@ -8556,7 +8548,7 @@
       <c r="K129" s="111"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="107"/>
       <c r="C130" s="108"/>
       <c r="D130" s="109"/>
@@ -8569,20 +8561,20 @@
       <c r="K130" s="108"/>
       <c r="L130" s="109"/>
     </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="119"/>
-      <c r="C131" s="120"/>
-      <c r="D131" s="121"/>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="125"/>
+      <c r="C131" s="126"/>
+      <c r="D131" s="127"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="119"/>
-      <c r="G131" s="120"/>
-      <c r="H131" s="121"/>
+      <c r="F131" s="125"/>
+      <c r="G131" s="126"/>
+      <c r="H131" s="127"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="119"/>
-      <c r="K131" s="120"/>
-      <c r="L131" s="121"/>
-    </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J131" s="125"/>
+      <c r="K131" s="126"/>
+      <c r="L131" s="127"/>
+    </row>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="82"/>
       <c r="C132" s="83"/>
       <c r="D132" s="84"/>
@@ -8595,18 +8587,18 @@
       <c r="K132" s="83"/>
       <c r="L132" s="84"/>
     </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="116"/>
-      <c r="C133" s="117"/>
-      <c r="D133" s="118"/>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="118"/>
+      <c r="C133" s="119"/>
+      <c r="D133" s="120"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="116"/>
-      <c r="G133" s="117"/>
-      <c r="H133" s="118"/>
+      <c r="F133" s="118"/>
+      <c r="G133" s="119"/>
+      <c r="H133" s="120"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="116"/>
-      <c r="K133" s="117"/>
-      <c r="L133" s="118"/>
+      <c r="J133" s="118"/>
+      <c r="K133" s="119"/>
+      <c r="L133" s="120"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
@@ -8629,6 +8621,13 @@
     <mergeCell ref="B90:D90"/>
     <mergeCell ref="B88:D88"/>
     <mergeCell ref="B87:D87"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
     <mergeCell ref="AD97:AF97"/>
     <mergeCell ref="Z52:AA52"/>
     <mergeCell ref="B37:D37"/>
@@ -8663,6 +8662,7 @@
     <mergeCell ref="AH80:AI80"/>
     <mergeCell ref="AH74:AI74"/>
     <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="Z92:AA92"/>
     <mergeCell ref="V97:X97"/>
     <mergeCell ref="V98:X98"/>
     <mergeCell ref="Z97:AB97"/>
@@ -8687,6 +8687,9 @@
     <mergeCell ref="N77:P77"/>
     <mergeCell ref="N78:P78"/>
     <mergeCell ref="J60:K60"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N46:P46"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B48:D48"/>
@@ -8699,22 +8702,15 @@
     <mergeCell ref="J43:L43"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="J48:L48"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="N53:P53"/>
     <mergeCell ref="F63:H63"/>
     <mergeCell ref="J63:L63"/>
     <mergeCell ref="N59:O59"/>
@@ -8724,13 +8720,9 @@
     <mergeCell ref="N55:P55"/>
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="R54:T54"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="R59:S59"/>
     <mergeCell ref="J106:L106"/>
     <mergeCell ref="J101:L101"/>
     <mergeCell ref="J94:L94"/>
@@ -8887,8 +8879,6 @@
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="AH10:AJ10"/>
     <mergeCell ref="J24:K24"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="N20:O20"/>
     <mergeCell ref="Z9:AB9"/>
     <mergeCell ref="R10:T10"/>
     <mergeCell ref="V10:X10"/>
@@ -8935,12 +8925,6 @@
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="AD20:AE20"/>
     <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="R22:S22"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="R42:T42"/>
@@ -8959,13 +8943,12 @@
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="N27:O27"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N26:O26"/>
     <mergeCell ref="J35:L35"/>
     <mergeCell ref="J36:L36"/>
     <mergeCell ref="J42:L42"/>
@@ -8978,10 +8961,18 @@
     <mergeCell ref="F43:H43"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="F56:H56"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="F50:H50"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="Z81:AB81"/>
     <mergeCell ref="B75:D75"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="N83:P83"/>
@@ -8999,30 +8990,6 @@
     <mergeCell ref="J75:L75"/>
     <mergeCell ref="Z75:AB75"/>
     <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="J50:L50"/>
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="F106:H106"/>
     <mergeCell ref="F105:G105"/>
@@ -9119,14 +9086,6 @@
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="AD23:AE23"/>
     <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AD60:AF60"/>
     <mergeCell ref="Z71:AB71"/>
     <mergeCell ref="N61:P61"/>
     <mergeCell ref="AD26:AE26"/>
@@ -9143,6 +9102,41 @@
     <mergeCell ref="AH25:AI25"/>
     <mergeCell ref="AD24:AE24"/>
     <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AH60:AJ60"/>
     <mergeCell ref="AH72:AJ72"/>
     <mergeCell ref="AD72:AF72"/>
     <mergeCell ref="AH71:AJ71"/>
@@ -9164,11 +9158,12 @@
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="N14:P14"/>
     <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL52:AM52"/>
     <mergeCell ref="AL76:AN76"/>
     <mergeCell ref="AD57:AF57"/>
     <mergeCell ref="AH57:AJ57"/>
@@ -9187,21 +9182,22 @@
     <mergeCell ref="AL59:AM59"/>
     <mergeCell ref="AD68:AE68"/>
     <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AD69:AF69"/>
     <mergeCell ref="AL81:AN81"/>
     <mergeCell ref="AL77:AN77"/>
     <mergeCell ref="AL78:AN78"/>
     <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AH94:AJ94"/>
     <mergeCell ref="AL82:AN82"/>
     <mergeCell ref="V62:X62"/>
     <mergeCell ref="V63:X63"/>
@@ -9221,11 +9217,11 @@
     <mergeCell ref="AH64:AJ64"/>
     <mergeCell ref="AL72:AN72"/>
     <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AD98:AF98"/>
     <mergeCell ref="AL102:AN102"/>
     <mergeCell ref="AL101:AN101"/>
     <mergeCell ref="AD87:AF87"/>
@@ -9245,11 +9241,11 @@
     <mergeCell ref="AH98:AI98"/>
     <mergeCell ref="AD99:AF99"/>
     <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="N74:O74"/>
     <mergeCell ref="AL100:AN100"/>
     <mergeCell ref="AH83:AJ83"/>
     <mergeCell ref="AD84:AF84"/>
@@ -9269,12 +9265,11 @@
     <mergeCell ref="AL89:AN89"/>
     <mergeCell ref="AL92:AM92"/>
     <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AD98:AF98"/>
-    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
     <mergeCell ref="N72:P72"/>
     <mergeCell ref="N71:P71"/>
     <mergeCell ref="J71:L71"/>
@@ -9282,27 +9277,15 @@
     <mergeCell ref="J68:K68"/>
     <mergeCell ref="J76:L76"/>
     <mergeCell ref="N76:P76"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J74:K74"/>
     <mergeCell ref="Z88:AB88"/>
     <mergeCell ref="R90:T90"/>
     <mergeCell ref="R87:T87"/>
@@ -9311,6 +9294,10 @@
     <mergeCell ref="Z94:AB94"/>
     <mergeCell ref="V93:X93"/>
     <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="Z74:AA74"/>
     <mergeCell ref="J93:L93"/>
     <mergeCell ref="Z83:AB83"/>
     <mergeCell ref="V84:X84"/>
@@ -9331,8 +9318,10 @@
     <mergeCell ref="Z90:AB90"/>
     <mergeCell ref="R93:T93"/>
     <mergeCell ref="N81:P81"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="Z89:AB89"/>
     <mergeCell ref="Z59:AA59"/>
     <mergeCell ref="R77:T77"/>
     <mergeCell ref="Z54:AB54"/>
@@ -9353,6 +9342,10 @@
     <mergeCell ref="V64:X64"/>
     <mergeCell ref="V69:X69"/>
     <mergeCell ref="R69:T69"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N68:O68"/>
     <mergeCell ref="Z48:AB48"/>
     <mergeCell ref="Z53:AB53"/>
     <mergeCell ref="Z57:AB57"/>
@@ -9395,17 +9388,7 @@
     <mergeCell ref="AD52:AE52"/>
     <mergeCell ref="AD49:AF49"/>
     <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AL48:AN48"/>
     <mergeCell ref="R33:T33"/>
     <mergeCell ref="AD35:AF35"/>
     <mergeCell ref="AH35:AJ35"/>
@@ -9419,7 +9402,7 @@
     <mergeCell ref="R34:T34"/>
     <mergeCell ref="AL43:AN43"/>
     <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="Z33:AB33"/>
     <mergeCell ref="Z47:AB47"/>
     <mergeCell ref="Z43:AB43"/>
     <mergeCell ref="V47:X47"/>
@@ -9434,7 +9417,9 @@
     <mergeCell ref="R45:S45"/>
     <mergeCell ref="N36:P36"/>
     <mergeCell ref="N40:P40"/>
-    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="Z34:AB34"/>
     <mergeCell ref="AL27:AM27"/>
     <mergeCell ref="AL26:AM26"/>
     <mergeCell ref="AL33:AN33"/>
@@ -9451,6 +9436,13 @@
     <mergeCell ref="V33:X33"/>
     <mergeCell ref="AH42:AJ42"/>
     <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="AH36:AJ36"/>
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="F33:H33"/>
     <mergeCell ref="J31:K31"/>
@@ -9504,7 +9496,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="AJ22:AJ27 X22:X27 H94:H98 P22:P27 AF22:AF27 AB22:AB27 T22:T27 D22:D27 H22:H27 D94:D98 L22:L27 AN22:AN27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="Z55:AB57 AH14:AJ16 N77:P78 AL101:AN102 V71:X72 R95:T102 N22:O27 J132:L133 AD71:AF72 R22:S27 V83:X84 AL62:AN64 V22:W27 AD83:AF84 AL71:AN72 AD41:AF43 V48:X50 AH41:AJ43 F8:H10 Z77:AB78 V8:X10 AL22:AM27 AL48:AN50 J114:L115 AD8:AF10 AL89:AN90 AH83:AJ84 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 AH48:AJ50 R14:T16 AH55:AJ57 AL14:AN16 AH95:AJ96 AD77:AF78 V41:X43 AL77:AN78 V62:X64 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X36 AH101:AJ102 V55:X57 Z41:AB43 V77:X78 AD89:AF90 V14:X16 AH22:AI27 F108:H109 R77:T78 AL34:AN36 N55:P57 Z48:AB50 AL55:AN57 AH62:AJ64 R83:T84 N62:P64 R41:T43 N89:P90 N83:P84 AH89:AJ90 AD22:AE27 R55:T57 N48:P50 N41:P43 R71:T72 AH34:AJ36 N14:P16 N34:P36 AH8:AJ10 N71:P72 Z95:AB102 AH77:AJ78 AD95:AF102 AD34:AF36 V89:X90 AL83:AN84 Z71:AB72 Z22:AA27 AD48:AF50 Z89:AB90 N95:P102 Z62:AB64 AH71:AJ72 AL95:AN96 Z34:AB36 Z83:AB84 V95:X102 Z8:AB10 AL41:AN43 AL8:AN10 R89:T90 R62:T64 N8:P10 AD55:AF57 F83:H84 F63:H64 J56:L58 B56:D58 B22:C27 J77:L78 B89:D90 F42:H44 J89:L90 B83:D84 F14:H16 B34:D37 B8:D10 J14:L16 F22:G27 J101:L102 J49:L51 J8:L10 J83:L84 B71:D72 F34:H37 B63:D65 F77:H78 J95:L96 F102:H102 B94:C98 B42:D44 F71:H72 J22:K27 F49:H51 J71:L72 B77:D78 B14:D16 J63:L64 J42:L44 F56:H58 F94:G98 B49:D51 B102:D102 F89:H90 J34:L37 AD62:AF64">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="Z55:AB57 AH14:AJ16 N77:P78 AL101:AN102 V71:X72 R95:T102 N22:O27 J132:L133 AD71:AF72 R22:S27 V83:X84 AL62:AN64 V22:W27 AD83:AF84 AL71:AN72 AD41:AF43 V48:X50 AH41:AJ43 F8:H10 Z77:AB78 V8:X10 AL22:AM27 J71:L72 J114:L115 AD8:AF10 AL89:AN90 AH83:AJ84 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 AH48:AJ50 R14:T16 AH55:AJ57 AL14:AN16 AH95:AJ96 AD77:AF78 V41:X43 AL77:AN78 V62:X64 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X36 AH101:AJ102 V55:X57 Z41:AB43 V77:X78 AD89:AF90 V14:X16 AH22:AI27 F108:H109 R77:T78 AL34:AN36 N55:P57 Z48:AB50 AL55:AN57 AH62:AJ64 R83:T84 N62:P64 R41:T43 N89:P90 N83:P84 AH89:AJ90 AD22:AE27 R55:T57 N48:P50 N41:P43 R71:T72 AH34:AJ36 N14:P16 N34:P36 AH8:AJ10 N71:P72 Z95:AB102 AH77:AJ78 AD95:AF102 AD34:AF36 V89:X90 AL83:AN84 Z71:AB72 Z22:AA27 AD48:AF50 Z89:AB90 N95:P102 Z62:AB64 AH71:AJ72 AL95:AN96 Z34:AB36 Z83:AB84 V95:X102 Z8:AB10 AL48:AN50 AL8:AN10 R89:T90 R62:T64 N8:P10 AD55:AF57 F83:H84 F63:H64 J56:L58 B56:D58 B22:C27 J77:L78 B89:D90 F42:H44 J89:L90 B83:D84 F14:H16 B34:D37 B8:D10 J14:L16 F22:G27 J101:L102 J49:L51 J8:L10 J83:L84 B71:D72 F34:H37 B63:D65 F77:H78 J95:L96 F102:H102 B94:C98 B42:D44 F71:H72 J22:K27 F49:H51 AD62:AF64 B77:D78 B14:D16 J63:L64 J42:L44 F56:H58 F94:G98 B49:D51 B102:D102 F89:H90 J34:L37 AL41:AN43">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="94">
   <si>
     <t>CUMA</t>
   </si>
@@ -297,6 +297,15 @@
   </si>
   <si>
     <t>Çekmeköy</t>
+  </si>
+  <si>
+    <t>A.DEMİRKAYA.</t>
+  </si>
+  <si>
+    <t>Ç.TAŞ.</t>
+  </si>
+  <si>
+    <t>TOPLANTI</t>
   </si>
 </sst>
 </file>
@@ -848,7 +857,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1287,6 +1296,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1350,7 +1370,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1569,6 +1589,15 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1587,15 +1616,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1632,6 +1652,24 @@
     <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="11" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="13" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1730,6 +1768,9 @@
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="12" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2103,7 +2144,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="181" row="3" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2129,197 +2170,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" customWidth="1"/>
-    <col min="17" max="17" width="1.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="1.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" customWidth="1"/>
-    <col min="23" max="23" width="20.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="1.6640625" customWidth="1"/>
-    <col min="26" max="26" width="2.6640625" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" customWidth="1"/>
-    <col min="29" max="29" width="1.6640625" customWidth="1"/>
-    <col min="30" max="30" width="2.6640625" customWidth="1"/>
-    <col min="31" max="31" width="20.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.6640625" customWidth="1"/>
-    <col min="33" max="33" width="1.6640625" customWidth="1"/>
-    <col min="34" max="34" width="2.6640625" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" customWidth="1"/>
-    <col min="36" max="36" width="6.6640625" customWidth="1"/>
-    <col min="37" max="37" width="1.6640625" customWidth="1"/>
-    <col min="38" max="38" width="2.6640625" customWidth="1"/>
-    <col min="39" max="39" width="20.6640625" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" customWidth="1"/>
-    <col min="41" max="41" width="2.6640625" customWidth="1"/>
-    <col min="42" max="42" width="16.6640625" customWidth="1"/>
-    <col min="43" max="43" width="3.6640625" customWidth="1"/>
-    <col min="44" max="44" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="1.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="1.7109375" customWidth="1"/>
+    <col min="26" max="26" width="2.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" customWidth="1"/>
+    <col min="29" max="29" width="1.7109375" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" customWidth="1"/>
+    <col min="31" max="31" width="20.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.7109375" customWidth="1"/>
+    <col min="33" max="33" width="1.7109375" customWidth="1"/>
+    <col min="34" max="34" width="2.7109375" customWidth="1"/>
+    <col min="35" max="35" width="20.7109375" customWidth="1"/>
+    <col min="36" max="36" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="1.7109375" customWidth="1"/>
+    <col min="38" max="38" width="2.7109375" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="41" max="41" width="2.7109375" customWidth="1"/>
+    <col min="42" max="42" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="3.7109375" customWidth="1"/>
+    <col min="44" max="44" width="8.28515625" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="119" t="s">
+      <c r="B1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="120" t="s">
+      <c r="F1" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="120" t="s">
+      <c r="J1" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="120"/>
-      <c r="L1" s="121"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="127"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="124" t="s">
+      <c r="N1" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="114" t="s">
+      <c r="R1" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="114" t="s">
+      <c r="V1" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="114" t="s">
+      <c r="Z1" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="114" t="s">
+      <c r="AD1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="114"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="114" t="s">
+      <c r="AH1" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="114"/>
-      <c r="AJ1" s="114"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="114" t="s">
+      <c r="AL1" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="114"/>
-      <c r="AN1" s="115"/>
+      <c r="AM1" s="120"/>
+      <c r="AN1" s="121"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="122">
+      <c r="B2" s="128">
         <f>N2-3</f>
         <v>46199</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="123">
+      <c r="F2" s="129">
         <f>N2-2</f>
         <v>46200</v>
       </c>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="123">
+      <c r="J2" s="129">
         <f>N2-1</f>
         <v>46201</v>
       </c>
-      <c r="K2" s="123"/>
-      <c r="L2" s="126"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="132"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="125">
+      <c r="N2" s="131">
         <v>46202</v>
       </c>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="116">
+      <c r="R2" s="122">
         <f>N2+1</f>
         <v>46203</v>
       </c>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="116">
+      <c r="V2" s="122">
         <f>N2+2</f>
         <v>46204</v>
       </c>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="116">
+      <c r="Z2" s="122">
         <f>N2+3</f>
         <v>46205</v>
       </c>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
+      <c r="AA2" s="122"/>
+      <c r="AB2" s="122"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="116">
+      <c r="AD2" s="122">
         <f>N2+4</f>
         <v>46206</v>
       </c>
-      <c r="AE2" s="116"/>
-      <c r="AF2" s="116"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="122"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="116">
+      <c r="AH2" s="122">
         <f>N2+5</f>
         <v>46207</v>
       </c>
-      <c r="AI2" s="116"/>
-      <c r="AJ2" s="116"/>
+      <c r="AI2" s="122"/>
+      <c r="AJ2" s="122"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="116">
+      <c r="AL2" s="122">
         <f>N2+6</f>
         <v>46208</v>
       </c>
-      <c r="AM2" s="116"/>
-      <c r="AN2" s="117"/>
+      <c r="AM2" s="122"/>
+      <c r="AN2" s="123"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2365,101 +2406,101 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="108" t="s">
+      <c r="N4" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="108"/>
-      <c r="U4" s="108"/>
-      <c r="V4" s="108"/>
-      <c r="W4" s="108"/>
-      <c r="X4" s="108"/>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="108"/>
-      <c r="AA4" s="108"/>
-      <c r="AB4" s="108"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="118"/>
-      <c r="AE4" s="118"/>
-      <c r="AF4" s="118"/>
-      <c r="AG4" s="118"/>
-      <c r="AH4" s="118"/>
-      <c r="AI4" s="118"/>
-      <c r="AJ4" s="118"/>
-      <c r="AK4" s="118"/>
-      <c r="AL4" s="118"/>
-      <c r="AM4" s="118"/>
-      <c r="AN4" s="118"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="124"/>
+      <c r="AF4" s="124"/>
+      <c r="AG4" s="124"/>
+      <c r="AH4" s="124"/>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="124"/>
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
+      <c r="AN4" s="124"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="108"/>
-      <c r="Y5" s="108"/>
-      <c r="Z5" s="108"/>
-      <c r="AA5" s="108"/>
-      <c r="AB5" s="108"/>
+      <c r="N5" s="114"/>
+      <c r="O5" s="114"/>
+      <c r="P5" s="114"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="114"/>
+      <c r="W5" s="114"/>
+      <c r="X5" s="114"/>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="114"/>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="118"/>
-      <c r="AE5" s="118"/>
-      <c r="AF5" s="118"/>
-      <c r="AG5" s="118"/>
-      <c r="AH5" s="118"/>
-      <c r="AI5" s="118"/>
-      <c r="AJ5" s="118"/>
-      <c r="AK5" s="118"/>
-      <c r="AL5" s="118"/>
-      <c r="AM5" s="118"/>
-      <c r="AN5" s="118"/>
+      <c r="AD5" s="124"/>
+      <c r="AE5" s="124"/>
+      <c r="AF5" s="124"/>
+      <c r="AG5" s="124"/>
+      <c r="AH5" s="124"/>
+      <c r="AI5" s="124"/>
+      <c r="AJ5" s="124"/>
+      <c r="AK5" s="124"/>
+      <c r="AL5" s="124"/>
+      <c r="AM5" s="124"/>
+      <c r="AN5" s="124"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="66" t="s">
         <v>57</v>
       </c>
@@ -2512,7 +2553,7 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="68"/>
       <c r="C7" s="69"/>
       <c r="D7" s="61"/>
@@ -2561,48 +2602,48 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="88" t="s">
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="89"/>
-      <c r="D8" s="90"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="84"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="90"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="84"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="90"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="84"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="88"/>
-      <c r="O8" s="89"/>
-      <c r="P8" s="90"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="84"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="89"/>
-      <c r="T8" s="90"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="84"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="89"/>
-      <c r="X8" s="90"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="83"/>
+      <c r="X8" s="84"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="88"/>
-      <c r="AA8" s="89"/>
-      <c r="AB8" s="90"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="83"/>
+      <c r="AB8" s="84"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="88"/>
-      <c r="AE8" s="89"/>
-      <c r="AF8" s="90"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="83"/>
+      <c r="AF8" s="84"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="88"/>
-      <c r="AI8" s="89"/>
-      <c r="AJ8" s="90"/>
+      <c r="AH8" s="82"/>
+      <c r="AI8" s="83"/>
+      <c r="AJ8" s="84"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="88"/>
-      <c r="AM8" s="89"/>
-      <c r="AN8" s="90"/>
+      <c r="AL8" s="82"/>
+      <c r="AM8" s="83"/>
+      <c r="AN8" s="84"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
@@ -2612,46 +2653,46 @@
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="85"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="87"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="90"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="87"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="90"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="85"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="87"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="90"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="86"/>
-      <c r="P9" s="87"/>
+      <c r="N9" s="88"/>
+      <c r="O9" s="89"/>
+      <c r="P9" s="90"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="85"/>
-      <c r="S9" s="86"/>
-      <c r="T9" s="87"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="89"/>
+      <c r="T9" s="90"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="85"/>
-      <c r="W9" s="86"/>
-      <c r="X9" s="87"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="89"/>
+      <c r="X9" s="90"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="85"/>
-      <c r="AA9" s="86"/>
-      <c r="AB9" s="87"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="89"/>
+      <c r="AB9" s="90"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="85"/>
-      <c r="AE9" s="86"/>
-      <c r="AF9" s="87"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="89"/>
+      <c r="AF9" s="90"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="85"/>
-      <c r="AI9" s="86"/>
-      <c r="AJ9" s="87"/>
+      <c r="AH9" s="88"/>
+      <c r="AI9" s="89"/>
+      <c r="AJ9" s="90"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="85"/>
-      <c r="AM9" s="86"/>
-      <c r="AN9" s="87"/>
+      <c r="AL9" s="88"/>
+      <c r="AM9" s="89"/>
+      <c r="AN9" s="90"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2661,46 +2702,46 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="103"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="105"/>
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="109"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="111"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="105"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="111"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="105"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="111"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="103"/>
-      <c r="O10" s="104"/>
-      <c r="P10" s="105"/>
+      <c r="N10" s="109"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="111"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="103"/>
-      <c r="S10" s="104"/>
-      <c r="T10" s="105"/>
+      <c r="R10" s="109"/>
+      <c r="S10" s="110"/>
+      <c r="T10" s="111"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="103"/>
-      <c r="W10" s="104"/>
-      <c r="X10" s="105"/>
+      <c r="V10" s="109"/>
+      <c r="W10" s="110"/>
+      <c r="X10" s="111"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="103"/>
-      <c r="AA10" s="104"/>
-      <c r="AB10" s="105"/>
+      <c r="Z10" s="109"/>
+      <c r="AA10" s="110"/>
+      <c r="AB10" s="111"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="103"/>
-      <c r="AE10" s="104"/>
-      <c r="AF10" s="105"/>
+      <c r="AD10" s="109"/>
+      <c r="AE10" s="110"/>
+      <c r="AF10" s="111"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="103"/>
-      <c r="AI10" s="104"/>
-      <c r="AJ10" s="105"/>
+      <c r="AH10" s="109"/>
+      <c r="AI10" s="110"/>
+      <c r="AJ10" s="111"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="103"/>
-      <c r="AM10" s="104"/>
-      <c r="AN10" s="105"/>
+      <c r="AL10" s="109"/>
+      <c r="AM10" s="110"/>
+      <c r="AN10" s="111"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2710,7 +2751,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2759,7 +2800,7 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="66"/>
       <c r="C12" s="67"/>
       <c r="D12" s="60"/>
@@ -2804,11 +2845,11 @@
       </c>
       <c r="AQ12" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="68"/>
       <c r="C13" s="69"/>
       <c r="D13" s="61"/>
@@ -2857,46 +2898,46 @@
       </c>
       <c r="AR13" s="30"/>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="88"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="90"/>
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="82"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="84"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="90"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="84"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="90"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="84"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="88"/>
-      <c r="O14" s="89"/>
-      <c r="P14" s="90"/>
+      <c r="N14" s="82"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="84"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="88"/>
-      <c r="S14" s="89"/>
-      <c r="T14" s="90"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="84"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="89"/>
-      <c r="X14" s="90"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="84"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="88"/>
-      <c r="AA14" s="89"/>
-      <c r="AB14" s="90"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="83"/>
+      <c r="AB14" s="84"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="88"/>
-      <c r="AE14" s="89"/>
-      <c r="AF14" s="90"/>
+      <c r="AD14" s="82"/>
+      <c r="AE14" s="83"/>
+      <c r="AF14" s="84"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="88"/>
-      <c r="AI14" s="89"/>
-      <c r="AJ14" s="90"/>
+      <c r="AH14" s="82"/>
+      <c r="AI14" s="83"/>
+      <c r="AJ14" s="84"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="88"/>
-      <c r="AM14" s="89"/>
-      <c r="AN14" s="90"/>
+      <c r="AL14" s="82"/>
+      <c r="AM14" s="83"/>
+      <c r="AN14" s="84"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -2906,95 +2947,95 @@
       </c>
       <c r="AR14" s="30"/>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="87"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="88"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="90"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="87"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="90"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="87"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="90"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="86"/>
-      <c r="P15" s="87"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="90"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="85"/>
-      <c r="S15" s="86"/>
-      <c r="T15" s="87"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="89"/>
+      <c r="T15" s="90"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="85"/>
-      <c r="W15" s="86"/>
-      <c r="X15" s="87"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="89"/>
+      <c r="X15" s="90"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="85"/>
-      <c r="AA15" s="86"/>
-      <c r="AB15" s="87"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="89"/>
+      <c r="AB15" s="90"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="85"/>
-      <c r="AE15" s="86"/>
-      <c r="AF15" s="87"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="89"/>
+      <c r="AF15" s="90"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="85"/>
-      <c r="AI15" s="86"/>
-      <c r="AJ15" s="87"/>
+      <c r="AH15" s="88"/>
+      <c r="AI15" s="89"/>
+      <c r="AJ15" s="90"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="85"/>
-      <c r="AM15" s="86"/>
-      <c r="AN15" s="87"/>
+      <c r="AL15" s="88"/>
+      <c r="AM15" s="89"/>
+      <c r="AN15" s="90"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
       <c r="AQ15" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="103"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="105"/>
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="109"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="105"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="111"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="103"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="105"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="111"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="103"/>
-      <c r="O16" s="104"/>
-      <c r="P16" s="105"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="111"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="103"/>
-      <c r="S16" s="104"/>
-      <c r="T16" s="105"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="110"/>
+      <c r="T16" s="111"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="103"/>
-      <c r="W16" s="104"/>
-      <c r="X16" s="105"/>
+      <c r="V16" s="109"/>
+      <c r="W16" s="110"/>
+      <c r="X16" s="111"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="103"/>
-      <c r="AA16" s="104"/>
-      <c r="AB16" s="105"/>
+      <c r="Z16" s="109"/>
+      <c r="AA16" s="110"/>
+      <c r="AB16" s="111"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="103"/>
-      <c r="AE16" s="104"/>
-      <c r="AF16" s="105"/>
+      <c r="AD16" s="109"/>
+      <c r="AE16" s="110"/>
+      <c r="AF16" s="111"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="103"/>
-      <c r="AI16" s="104"/>
-      <c r="AJ16" s="105"/>
+      <c r="AH16" s="109"/>
+      <c r="AI16" s="110"/>
+      <c r="AJ16" s="111"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="103"/>
-      <c r="AM16" s="104"/>
-      <c r="AN16" s="105"/>
+      <c r="AL16" s="109"/>
+      <c r="AM16" s="110"/>
+      <c r="AN16" s="111"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3004,7 +3045,7 @@
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3053,7 +3094,7 @@
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3066,23 +3107,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="108" t="s">
+      <c r="N18" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="108"/>
-      <c r="P18" s="108"/>
-      <c r="Q18" s="108"/>
-      <c r="R18" s="108"/>
-      <c r="S18" s="108"/>
-      <c r="T18" s="108"/>
-      <c r="U18" s="108"/>
-      <c r="V18" s="108"/>
-      <c r="W18" s="108"/>
-      <c r="X18" s="108"/>
-      <c r="Y18" s="108"/>
-      <c r="Z18" s="108"/>
-      <c r="AA18" s="108"/>
-      <c r="AB18" s="108"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
+      <c r="U18" s="114"/>
+      <c r="V18" s="114"/>
+      <c r="W18" s="114"/>
+      <c r="X18" s="114"/>
+      <c r="Y18" s="114"/>
+      <c r="Z18" s="114"/>
+      <c r="AA18" s="114"/>
+      <c r="AB18" s="114"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3104,7 +3145,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3117,21 +3158,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="108"/>
-      <c r="S19" s="108"/>
-      <c r="T19" s="108"/>
-      <c r="U19" s="108"/>
-      <c r="V19" s="108"/>
-      <c r="W19" s="108"/>
-      <c r="X19" s="108"/>
-      <c r="Y19" s="108"/>
-      <c r="Z19" s="108"/>
-      <c r="AA19" s="108"/>
-      <c r="AB19" s="108"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="114"/>
+      <c r="V19" s="114"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="114"/>
+      <c r="Y19" s="114"/>
+      <c r="Z19" s="114"/>
+      <c r="AA19" s="114"/>
+      <c r="AB19" s="114"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3153,7 +3194,7 @@
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="66" t="s">
         <v>53</v>
       </c>
@@ -3186,26 +3227,26 @@
         <v>47</v>
       </c>
       <c r="Q20" s="36"/>
-      <c r="R20" s="106" t="s">
+      <c r="R20" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="S20" s="107"/>
+      <c r="S20" s="113"/>
       <c r="T20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="U20" s="36"/>
-      <c r="V20" s="106" t="s">
+      <c r="V20" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="W20" s="107"/>
+      <c r="W20" s="113"/>
       <c r="X20" s="56" t="s">
         <v>41</v>
       </c>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="106" t="s">
+      <c r="Z20" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="AA20" s="107"/>
+      <c r="AA20" s="113"/>
       <c r="AB20" s="56" t="s">
         <v>43</v>
       </c>
@@ -3234,7 +3275,7 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="68" t="s">
         <v>80</v>
       </c>
@@ -3259,12 +3300,12 @@
       <c r="S21" s="80"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="112"/>
-      <c r="W21" s="113"/>
+      <c r="V21" s="118"/>
+      <c r="W21" s="119"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="113"/>
+      <c r="Z21" s="118"/>
+      <c r="AA21" s="119"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="36"/>
       <c r="AD21" s="79"/>
@@ -3287,7 +3328,7 @@
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="70" t="s">
         <v>7</v>
       </c>
@@ -3312,34 +3353,34 @@
         <v>32</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="127" t="s">
+      <c r="N22" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="128"/>
+      <c r="O22" s="134"/>
       <c r="P22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="Q22" s="35"/>
-      <c r="R22" s="127" t="s">
+      <c r="R22" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="S22" s="128"/>
+      <c r="S22" s="134"/>
       <c r="T22" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U22" s="37"/>
-      <c r="V22" s="127" t="s">
+      <c r="V22" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="128"/>
+      <c r="W22" s="134"/>
       <c r="X22" s="58" t="s">
         <v>32</v>
       </c>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="127" t="s">
+      <c r="Z22" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="AA22" s="128"/>
+      <c r="AA22" s="134"/>
       <c r="AB22" s="58" t="s">
         <v>32</v>
       </c>
@@ -3352,10 +3393,10 @@
       <c r="AI22" s="71"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="127" t="s">
+      <c r="AL22" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="AM22" s="128"/>
+      <c r="AM22" s="134"/>
       <c r="AN22" s="41" t="s">
         <v>32</v>
       </c>
@@ -3364,11 +3405,11 @@
       </c>
       <c r="AQ22" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="72" t="s">
         <v>17</v>
       </c>
@@ -3449,7 +3490,7 @@
       </c>
       <c r="AR23" s="30"/>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="62" t="s">
         <v>8</v>
       </c>
@@ -3530,7 +3571,7 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="62" t="s">
         <v>21</v>
       </c>
@@ -3539,10 +3580,10 @@
         <v>35</v>
       </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="134" t="s">
+      <c r="F25" s="140" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="135"/>
+      <c r="G25" s="141"/>
       <c r="H25" s="45" t="s">
         <v>35</v>
       </c>
@@ -3611,7 +3652,7 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="62" t="s">
         <v>20</v>
       </c>
@@ -3692,7 +3733,7 @@
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B27" s="64"/>
       <c r="C27" s="65"/>
       <c r="D27" s="42"/>
@@ -3737,11 +3778,11 @@
       </c>
       <c r="AQ27" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
@@ -3790,7 +3831,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
@@ -3803,23 +3844,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="108" t="s">
+      <c r="N29" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="108"/>
-      <c r="U29" s="108"/>
-      <c r="V29" s="108"/>
-      <c r="W29" s="108"/>
-      <c r="X29" s="108"/>
-      <c r="Y29" s="108"/>
-      <c r="Z29" s="108"/>
-      <c r="AA29" s="108"/>
-      <c r="AB29" s="108"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="114"/>
+      <c r="T29" s="114"/>
+      <c r="U29" s="114"/>
+      <c r="V29" s="114"/>
+      <c r="W29" s="114"/>
+      <c r="X29" s="114"/>
+      <c r="Y29" s="114"/>
+      <c r="Z29" s="114"/>
+      <c r="AA29" s="114"/>
+      <c r="AB29" s="114"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3841,7 +3882,7 @@
       </c>
       <c r="AR29" s="30"/>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
@@ -3854,21 +3895,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="108"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="108"/>
-      <c r="Q30" s="108"/>
-      <c r="R30" s="108"/>
-      <c r="S30" s="108"/>
-      <c r="T30" s="108"/>
-      <c r="U30" s="108"/>
-      <c r="V30" s="108"/>
-      <c r="W30" s="108"/>
-      <c r="X30" s="108"/>
-      <c r="Y30" s="108"/>
-      <c r="Z30" s="108"/>
-      <c r="AA30" s="108"/>
-      <c r="AB30" s="108"/>
+      <c r="N30" s="114"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="114"/>
+      <c r="Q30" s="114"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="114"/>
+      <c r="T30" s="114"/>
+      <c r="U30" s="114"/>
+      <c r="V30" s="114"/>
+      <c r="W30" s="114"/>
+      <c r="X30" s="114"/>
+      <c r="Y30" s="114"/>
+      <c r="Z30" s="114"/>
+      <c r="AA30" s="114"/>
+      <c r="AB30" s="114"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3890,7 +3931,7 @@
       </c>
       <c r="AR30" s="30"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="66" t="s">
         <v>51</v>
       </c>
@@ -3952,7 +3993,7 @@
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="91" t="s">
         <v>55</v>
       </c>
@@ -4014,7 +4055,7 @@
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="68"/>
       <c r="C33" s="69"/>
       <c r="D33" s="94"/>
@@ -4066,156 +4107,156 @@
       <c r="AN33" s="81"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="86"/>
-      <c r="D34" s="87"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="90"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="85" t="s">
+      <c r="F34" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="86"/>
-      <c r="H34" s="87"/>
+      <c r="G34" s="89"/>
+      <c r="H34" s="90"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="85" t="s">
+      <c r="J34" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="K34" s="86"/>
-      <c r="L34" s="87"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="88" t="s">
+      <c r="N34" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="O34" s="89"/>
-      <c r="P34" s="90"/>
+      <c r="O34" s="83"/>
+      <c r="P34" s="84"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="88"/>
-      <c r="S34" s="89"/>
-      <c r="T34" s="90"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="84"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="88" t="s">
+      <c r="V34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="W34" s="89"/>
-      <c r="X34" s="90"/>
+      <c r="W34" s="83"/>
+      <c r="X34" s="84"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="88" t="s">
+      <c r="Z34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AA34" s="89"/>
-      <c r="AB34" s="90"/>
+      <c r="AA34" s="83"/>
+      <c r="AB34" s="84"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="88" t="s">
+      <c r="AD34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AE34" s="89"/>
-      <c r="AF34" s="90"/>
+      <c r="AE34" s="83"/>
+      <c r="AF34" s="84"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="88" t="s">
+      <c r="AH34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AI34" s="89"/>
-      <c r="AJ34" s="90"/>
+      <c r="AI34" s="83"/>
+      <c r="AJ34" s="84"/>
       <c r="AK34" s="37"/>
-      <c r="AL34" s="88" t="s">
+      <c r="AL34" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="AM34" s="89"/>
-      <c r="AN34" s="90"/>
+      <c r="AM34" s="83"/>
+      <c r="AN34" s="84"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="86"/>
-      <c r="D35" s="87"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="90"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="85" t="s">
+      <c r="F35" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="G35" s="86"/>
-      <c r="H35" s="87"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="90"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="85" t="s">
+      <c r="J35" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="86"/>
-      <c r="L35" s="87"/>
+      <c r="K35" s="89"/>
+      <c r="L35" s="90"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="85" t="s">
+      <c r="N35" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="O35" s="86"/>
-      <c r="P35" s="87"/>
+      <c r="O35" s="89"/>
+      <c r="P35" s="90"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="85"/>
-      <c r="S35" s="86"/>
-      <c r="T35" s="87"/>
+      <c r="R35" s="88"/>
+      <c r="S35" s="89"/>
+      <c r="T35" s="90"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="82" t="s">
+      <c r="V35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="83"/>
-      <c r="X35" s="84"/>
+      <c r="W35" s="86"/>
+      <c r="X35" s="87"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="82" t="s">
+      <c r="Z35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="83"/>
-      <c r="AB35" s="84"/>
+      <c r="AA35" s="86"/>
+      <c r="AB35" s="87"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="82" t="s">
+      <c r="AD35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AE35" s="83"/>
-      <c r="AF35" s="84"/>
+      <c r="AE35" s="86"/>
+      <c r="AF35" s="87"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="82" t="s">
+      <c r="AH35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AI35" s="83"/>
-      <c r="AJ35" s="84"/>
+      <c r="AI35" s="86"/>
+      <c r="AJ35" s="87"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="82" t="s">
+      <c r="AL35" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AM35" s="83"/>
-      <c r="AN35" s="84"/>
+      <c r="AM35" s="86"/>
+      <c r="AN35" s="87"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="82"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="84"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="87"/>
       <c r="E36" s="44"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="84"/>
+      <c r="F36" s="85"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="87"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="82"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="84"/>
+      <c r="J36" s="85"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="87"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="82" t="s">
+      <c r="N36" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="O36" s="83"/>
-      <c r="P36" s="84"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="87"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="82"/>
-      <c r="S36" s="83"/>
-      <c r="T36" s="84"/>
+      <c r="R36" s="85"/>
+      <c r="S36" s="86"/>
+      <c r="T36" s="87"/>
       <c r="U36" s="40"/>
       <c r="V36" s="35"/>
       <c r="W36" s="35"/>
@@ -4241,7 +4282,7 @@
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>
       <c r="B37" s="35"/>
       <c r="C37" s="35"/>
@@ -4297,7 +4338,7 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
       <c r="B38" s="66"/>
       <c r="C38" s="67"/>
@@ -4317,10 +4358,10 @@
       <c r="K38" s="67"/>
       <c r="L38" s="60"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="132" t="s">
+      <c r="N38" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="O38" s="133"/>
+      <c r="O38" s="139"/>
       <c r="P38" s="59"/>
       <c r="Q38" s="36"/>
       <c r="R38" s="74"/>
@@ -4361,7 +4402,7 @@
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
       <c r="B39" s="91"/>
       <c r="C39" s="92"/>
@@ -4379,11 +4420,11 @@
       <c r="K39" s="92"/>
       <c r="L39" s="93"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="129" t="s">
+      <c r="N39" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="O39" s="130"/>
-      <c r="P39" s="131"/>
+      <c r="O39" s="136"/>
+      <c r="P39" s="137"/>
       <c r="Q39" s="43"/>
       <c r="R39" s="76"/>
       <c r="S39" s="77"/>
@@ -4423,7 +4464,7 @@
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
       <c r="B40" s="68"/>
       <c r="C40" s="69"/>
@@ -4437,61 +4478,61 @@
       <c r="K40" s="69"/>
       <c r="L40" s="94"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="109" t="s">
+      <c r="N40" s="115" t="s">
         <v>79</v>
       </c>
-      <c r="O40" s="110"/>
-      <c r="P40" s="111"/>
+      <c r="O40" s="116"/>
+      <c r="P40" s="117"/>
       <c r="Q40" s="37"/>
       <c r="R40" s="79"/>
       <c r="S40" s="80"/>
       <c r="T40" s="81"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="88" t="s">
+      <c r="V40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="W40" s="89"/>
-      <c r="X40" s="90"/>
+      <c r="W40" s="83"/>
+      <c r="X40" s="84"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="88" t="s">
+      <c r="Z40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AA40" s="89"/>
-      <c r="AB40" s="90"/>
+      <c r="AA40" s="83"/>
+      <c r="AB40" s="84"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="88" t="s">
+      <c r="AD40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AE40" s="89"/>
-      <c r="AF40" s="90"/>
+      <c r="AE40" s="83"/>
+      <c r="AF40" s="84"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="88" t="s">
+      <c r="AH40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AI40" s="89"/>
-      <c r="AJ40" s="90"/>
+      <c r="AI40" s="83"/>
+      <c r="AJ40" s="84"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="88" t="s">
+      <c r="AL40" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="AM40" s="89"/>
-      <c r="AN40" s="90"/>
+      <c r="AM40" s="83"/>
+      <c r="AN40" s="84"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="85"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="87"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="90"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="88" t="s">
+      <c r="F41" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="G41" s="89"/>
-      <c r="H41" s="90"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="84"/>
       <c r="I41" s="37"/>
       <c r="J41" s="95" t="s">
         <v>9</v>
@@ -4499,77 +4540,77 @@
       <c r="K41" s="96"/>
       <c r="L41" s="97"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="O41" s="89"/>
-      <c r="P41" s="90"/>
+      <c r="N41" s="106" t="s">
+        <v>91</v>
+      </c>
+      <c r="O41" s="107"/>
+      <c r="P41" s="108"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="88"/>
-      <c r="S41" s="89"/>
-      <c r="T41" s="90"/>
+      <c r="R41" s="82"/>
+      <c r="S41" s="83"/>
+      <c r="T41" s="84"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="82" t="s">
+      <c r="V41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="W41" s="83"/>
-      <c r="X41" s="84"/>
+      <c r="W41" s="86"/>
+      <c r="X41" s="87"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="82" t="s">
+      <c r="Z41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="83"/>
-      <c r="AB41" s="84"/>
+      <c r="AA41" s="86"/>
+      <c r="AB41" s="87"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="82" t="s">
+      <c r="AD41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AE41" s="83"/>
-      <c r="AF41" s="84"/>
+      <c r="AE41" s="86"/>
+      <c r="AF41" s="87"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="82" t="s">
+      <c r="AH41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AI41" s="83"/>
-      <c r="AJ41" s="84"/>
+      <c r="AI41" s="86"/>
+      <c r="AJ41" s="87"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="82" t="s">
+      <c r="AL41" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AM41" s="83"/>
-      <c r="AN41" s="84"/>
+      <c r="AM41" s="86"/>
+      <c r="AN41" s="87"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="85"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="87"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="90"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="85" t="s">
+      <c r="F42" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="86"/>
-      <c r="H42" s="87"/>
+      <c r="G42" s="89"/>
+      <c r="H42" s="90"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="85" t="s">
+      <c r="J42" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="86"/>
-      <c r="L42" s="87"/>
+      <c r="K42" s="89"/>
+      <c r="L42" s="90"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="O42" s="86"/>
-      <c r="P42" s="87"/>
+      <c r="N42" s="103" t="s">
+        <v>92</v>
+      </c>
+      <c r="O42" s="104"/>
+      <c r="P42" s="105"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="85"/>
-      <c r="S42" s="86"/>
-      <c r="T42" s="87"/>
+      <c r="R42" s="88"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="90"/>
       <c r="U42" s="44"/>
       <c r="V42" s="35"/>
       <c r="W42" s="35"/>
@@ -4595,15 +4636,15 @@
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="84"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="87"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="84"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="87"/>
       <c r="I43" s="44"/>
       <c r="J43" s="98" t="s">
         <v>88</v>
@@ -4611,13 +4652,13 @@
       <c r="K43" s="99"/>
       <c r="L43" s="100"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="82"/>
-      <c r="O43" s="83"/>
-      <c r="P43" s="84"/>
+      <c r="N43" s="98"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="100"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="82"/>
-      <c r="S43" s="83"/>
-      <c r="T43" s="84"/>
+      <c r="R43" s="85"/>
+      <c r="S43" s="86"/>
+      <c r="T43" s="87"/>
       <c r="U43" s="50"/>
       <c r="V43" s="74" t="s">
         <v>71</v>
@@ -4653,7 +4694,7 @@
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35"/>
@@ -4709,7 +4750,7 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
       <c r="B45" s="66"/>
       <c r="C45" s="67"/>
@@ -4767,7 +4808,7 @@
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
       <c r="B46" s="91"/>
       <c r="C46" s="92"/>
@@ -4791,41 +4832,41 @@
       <c r="S46" s="77"/>
       <c r="T46" s="78"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="85" t="s">
+      <c r="V46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="W46" s="86"/>
-      <c r="X46" s="87"/>
+      <c r="W46" s="89"/>
+      <c r="X46" s="90"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="85" t="s">
+      <c r="Z46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AA46" s="86"/>
-      <c r="AB46" s="87"/>
+      <c r="AA46" s="89"/>
+      <c r="AB46" s="90"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="85" t="s">
+      <c r="AD46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AE46" s="86"/>
-      <c r="AF46" s="87"/>
+      <c r="AE46" s="89"/>
+      <c r="AF46" s="90"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="85" t="s">
+      <c r="AH46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AI46" s="86"/>
-      <c r="AJ46" s="87"/>
+      <c r="AI46" s="89"/>
+      <c r="AJ46" s="90"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="85" t="s">
+      <c r="AL46" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AM46" s="86"/>
-      <c r="AN46" s="87"/>
+      <c r="AM46" s="89"/>
+      <c r="AN46" s="90"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
       <c r="B47" s="68"/>
       <c r="C47" s="69"/>
@@ -4849,175 +4890,175 @@
       <c r="S47" s="80"/>
       <c r="T47" s="81"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="85" t="s">
+      <c r="V47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="W47" s="86"/>
-      <c r="X47" s="87"/>
+      <c r="W47" s="89"/>
+      <c r="X47" s="90"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="85" t="s">
+      <c r="Z47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AA47" s="86"/>
-      <c r="AB47" s="87"/>
+      <c r="AA47" s="89"/>
+      <c r="AB47" s="90"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="85" t="s">
+      <c r="AD47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AE47" s="86"/>
-      <c r="AF47" s="87"/>
+      <c r="AE47" s="89"/>
+      <c r="AF47" s="90"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="85" t="s">
+      <c r="AH47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AI47" s="86"/>
-      <c r="AJ47" s="87"/>
+      <c r="AI47" s="89"/>
+      <c r="AJ47" s="90"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="85" t="s">
+      <c r="AL47" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AM47" s="86"/>
-      <c r="AN47" s="87"/>
+      <c r="AM47" s="89"/>
+      <c r="AN47" s="90"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="88"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="90"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="85"/>
-      <c r="G48" s="86"/>
-      <c r="H48" s="87"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="90"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="85" t="s">
+      <c r="J48" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="K48" s="86"/>
-      <c r="L48" s="87"/>
+      <c r="K48" s="89"/>
+      <c r="L48" s="90"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="85"/>
-      <c r="O48" s="86"/>
-      <c r="P48" s="87"/>
+      <c r="N48" s="88"/>
+      <c r="O48" s="89"/>
+      <c r="P48" s="90"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="85"/>
-      <c r="S48" s="86"/>
-      <c r="T48" s="87"/>
+      <c r="R48" s="88"/>
+      <c r="S48" s="89"/>
+      <c r="T48" s="90"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="85" t="s">
+      <c r="V48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="86"/>
-      <c r="X48" s="87"/>
+      <c r="W48" s="89"/>
+      <c r="X48" s="90"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="85" t="s">
+      <c r="Z48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="86"/>
-      <c r="AB48" s="87"/>
+      <c r="AA48" s="89"/>
+      <c r="AB48" s="90"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="85" t="s">
+      <c r="AD48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AE48" s="86"/>
-      <c r="AF48" s="87"/>
+      <c r="AE48" s="89"/>
+      <c r="AF48" s="90"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="85" t="s">
+      <c r="AH48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AI48" s="86"/>
-      <c r="AJ48" s="87"/>
+      <c r="AI48" s="89"/>
+      <c r="AJ48" s="90"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="85" t="s">
+      <c r="AL48" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="AM48" s="86"/>
-      <c r="AN48" s="87"/>
+      <c r="AM48" s="89"/>
+      <c r="AN48" s="90"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="85"/>
-      <c r="C49" s="86"/>
-      <c r="D49" s="87"/>
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="88"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="90"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="85"/>
-      <c r="G49" s="86"/>
-      <c r="H49" s="87"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="90"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="85" t="s">
+      <c r="J49" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="K49" s="86"/>
-      <c r="L49" s="87"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="90"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="86"/>
-      <c r="P49" s="87"/>
+      <c r="N49" s="88"/>
+      <c r="O49" s="89"/>
+      <c r="P49" s="90"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="85"/>
-      <c r="S49" s="86"/>
-      <c r="T49" s="87"/>
+      <c r="R49" s="88"/>
+      <c r="S49" s="89"/>
+      <c r="T49" s="90"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="82" t="s">
+      <c r="V49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="W49" s="83"/>
-      <c r="X49" s="84"/>
+      <c r="W49" s="86"/>
+      <c r="X49" s="87"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="82" t="s">
+      <c r="Z49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AA49" s="83"/>
-      <c r="AB49" s="84"/>
+      <c r="AA49" s="86"/>
+      <c r="AB49" s="87"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="82" t="s">
+      <c r="AD49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AE49" s="83"/>
-      <c r="AF49" s="84"/>
+      <c r="AE49" s="86"/>
+      <c r="AF49" s="87"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="82" t="s">
+      <c r="AH49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AI49" s="83"/>
-      <c r="AJ49" s="84"/>
+      <c r="AI49" s="86"/>
+      <c r="AJ49" s="87"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="82" t="s">
+      <c r="AL49" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AM49" s="83"/>
-      <c r="AN49" s="84"/>
+      <c r="AM49" s="86"/>
+      <c r="AN49" s="87"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="82"/>
-      <c r="C50" s="83"/>
-      <c r="D50" s="84"/>
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="85"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="87"/>
       <c r="E50" s="44"/>
-      <c r="F50" s="82"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="84"/>
+      <c r="F50" s="85"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="87"/>
       <c r="I50" s="44"/>
-      <c r="J50" s="82"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="84"/>
+      <c r="J50" s="85"/>
+      <c r="K50" s="86"/>
+      <c r="L50" s="87"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="82"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="84"/>
+      <c r="N50" s="85"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="87"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="82"/>
-      <c r="S50" s="83"/>
-      <c r="T50" s="84"/>
+      <c r="R50" s="85"/>
+      <c r="S50" s="86"/>
+      <c r="T50" s="87"/>
       <c r="U50" s="35"/>
       <c r="V50" s="35"/>
       <c r="W50" s="35"/>
@@ -5043,7 +5084,7 @@
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="35"/>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -5094,7 +5135,7 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="66"/>
       <c r="C52" s="67"/>
       <c r="D52" s="60"/>
@@ -5146,7 +5187,7 @@
       <c r="AN52" s="78"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="91"/>
       <c r="C53" s="92"/>
       <c r="D53" s="93"/>
@@ -5196,7 +5237,7 @@
       <c r="AN53" s="81"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="68"/>
       <c r="C54" s="69"/>
       <c r="D54" s="94"/>
@@ -5217,153 +5258,153 @@
       <c r="S54" s="80"/>
       <c r="T54" s="81"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="88"/>
-      <c r="W54" s="89"/>
-      <c r="X54" s="90"/>
+      <c r="V54" s="82"/>
+      <c r="W54" s="83"/>
+      <c r="X54" s="84"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="88"/>
-      <c r="AA54" s="89"/>
-      <c r="AB54" s="90"/>
+      <c r="Z54" s="82"/>
+      <c r="AA54" s="83"/>
+      <c r="AB54" s="84"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="88" t="s">
+      <c r="AD54" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="AE54" s="89"/>
-      <c r="AF54" s="90"/>
+      <c r="AE54" s="83"/>
+      <c r="AF54" s="84"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="88" t="s">
+      <c r="AH54" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="AI54" s="89"/>
-      <c r="AJ54" s="90"/>
+      <c r="AI54" s="83"/>
+      <c r="AJ54" s="84"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="88" t="s">
+      <c r="AL54" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="AM54" s="89"/>
-      <c r="AN54" s="90"/>
+      <c r="AM54" s="83"/>
+      <c r="AN54" s="84"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="88"/>
-      <c r="C55" s="89"/>
-      <c r="D55" s="90"/>
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="82"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="84"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="89"/>
-      <c r="H55" s="90"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="84"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="85" t="s">
+      <c r="J55" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="K55" s="86"/>
-      <c r="L55" s="87"/>
+      <c r="K55" s="89"/>
+      <c r="L55" s="90"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="88"/>
-      <c r="O55" s="89"/>
-      <c r="P55" s="90"/>
+      <c r="N55" s="82"/>
+      <c r="O55" s="83"/>
+      <c r="P55" s="84"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="88"/>
-      <c r="S55" s="89"/>
-      <c r="T55" s="90"/>
+      <c r="R55" s="82"/>
+      <c r="S55" s="83"/>
+      <c r="T55" s="84"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="85"/>
-      <c r="W55" s="86"/>
-      <c r="X55" s="87"/>
+      <c r="V55" s="88"/>
+      <c r="W55" s="89"/>
+      <c r="X55" s="90"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="85"/>
-      <c r="AA55" s="86"/>
-      <c r="AB55" s="87"/>
+      <c r="Z55" s="88"/>
+      <c r="AA55" s="89"/>
+      <c r="AB55" s="90"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="85" t="s">
+      <c r="AD55" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AE55" s="86"/>
-      <c r="AF55" s="87"/>
+      <c r="AE55" s="89"/>
+      <c r="AF55" s="90"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="85" t="s">
+      <c r="AH55" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AI55" s="86"/>
-      <c r="AJ55" s="87"/>
+      <c r="AI55" s="89"/>
+      <c r="AJ55" s="90"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="85" t="s">
+      <c r="AL55" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AM55" s="86"/>
-      <c r="AN55" s="87"/>
+      <c r="AM55" s="89"/>
+      <c r="AN55" s="90"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="85"/>
-      <c r="C56" s="86"/>
-      <c r="D56" s="87"/>
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="88"/>
+      <c r="C56" s="89"/>
+      <c r="D56" s="90"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="86"/>
-      <c r="H56" s="87"/>
+      <c r="F56" s="88"/>
+      <c r="G56" s="89"/>
+      <c r="H56" s="90"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="85" t="s">
+      <c r="J56" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="K56" s="86"/>
-      <c r="L56" s="87"/>
+      <c r="K56" s="89"/>
+      <c r="L56" s="90"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="85"/>
-      <c r="O56" s="86"/>
-      <c r="P56" s="87"/>
+      <c r="N56" s="88"/>
+      <c r="O56" s="89"/>
+      <c r="P56" s="90"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="85"/>
-      <c r="S56" s="86"/>
-      <c r="T56" s="87"/>
+      <c r="R56" s="88"/>
+      <c r="S56" s="89"/>
+      <c r="T56" s="90"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="82"/>
-      <c r="W56" s="83"/>
-      <c r="X56" s="84"/>
+      <c r="V56" s="85"/>
+      <c r="W56" s="86"/>
+      <c r="X56" s="87"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="82"/>
-      <c r="AA56" s="83"/>
-      <c r="AB56" s="84"/>
+      <c r="Z56" s="85"/>
+      <c r="AA56" s="86"/>
+      <c r="AB56" s="87"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="82" t="s">
+      <c r="AD56" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="AE56" s="83"/>
-      <c r="AF56" s="84"/>
+      <c r="AE56" s="86"/>
+      <c r="AF56" s="87"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="82" t="s">
+      <c r="AH56" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="AI56" s="83"/>
-      <c r="AJ56" s="84"/>
+      <c r="AI56" s="86"/>
+      <c r="AJ56" s="87"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="82" t="s">
+      <c r="AL56" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="AM56" s="83"/>
-      <c r="AN56" s="84"/>
+      <c r="AM56" s="86"/>
+      <c r="AN56" s="87"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="82"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="84"/>
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="85"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="87"/>
       <c r="E57" s="44"/>
-      <c r="F57" s="82"/>
-      <c r="G57" s="83"/>
-      <c r="H57" s="84"/>
+      <c r="F57" s="85"/>
+      <c r="G57" s="86"/>
+      <c r="H57" s="87"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="82"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="84"/>
+      <c r="J57" s="85"/>
+      <c r="K57" s="86"/>
+      <c r="L57" s="87"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="82"/>
-      <c r="O57" s="83"/>
-      <c r="P57" s="84"/>
+      <c r="N57" s="85"/>
+      <c r="O57" s="86"/>
+      <c r="P57" s="87"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="82"/>
-      <c r="S57" s="83"/>
-      <c r="T57" s="84"/>
+      <c r="R57" s="85"/>
+      <c r="S57" s="86"/>
+      <c r="T57" s="87"/>
       <c r="U57" s="50"/>
       <c r="V57" s="35"/>
       <c r="W57" s="35"/>
@@ -5386,7 +5427,7 @@
       <c r="AN57" s="35"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -5415,9 +5456,11 @@
       <c r="AA58" s="75"/>
       <c r="AB58" s="34"/>
       <c r="AC58" s="50"/>
-      <c r="AD58" s="74"/>
-      <c r="AE58" s="75"/>
-      <c r="AF58" s="34"/>
+      <c r="AD58" s="101" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE58" s="102"/>
+      <c r="AF58" s="55"/>
       <c r="AG58" s="50"/>
       <c r="AH58" s="74"/>
       <c r="AI58" s="75"/>
@@ -5430,7 +5473,7 @@
       <c r="AN58" s="34"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="66"/>
       <c r="C59" s="67"/>
       <c r="D59" s="60"/>
@@ -5461,7 +5504,9 @@
       <c r="AA59" s="77"/>
       <c r="AB59" s="78"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="76"/>
+      <c r="AD59" s="76" t="s">
+        <v>72</v>
+      </c>
       <c r="AE59" s="77"/>
       <c r="AF59" s="78"/>
       <c r="AG59" s="36"/>
@@ -5476,7 +5521,7 @@
       <c r="AN59" s="78"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="91"/>
       <c r="C60" s="92"/>
       <c r="D60" s="93"/>
@@ -5507,7 +5552,9 @@
       <c r="AA60" s="80"/>
       <c r="AB60" s="81"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="79"/>
+      <c r="AD60" s="79" t="s">
+        <v>93</v>
+      </c>
       <c r="AE60" s="80"/>
       <c r="AF60" s="81"/>
       <c r="AG60" s="36"/>
@@ -5522,7 +5569,7 @@
       <c r="AN60" s="81"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="68"/>
       <c r="C61" s="69"/>
       <c r="D61" s="94"/>
@@ -5543,160 +5590,164 @@
       <c r="S61" s="80"/>
       <c r="T61" s="81"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="88"/>
-      <c r="W61" s="89"/>
-      <c r="X61" s="90"/>
+      <c r="V61" s="82"/>
+      <c r="W61" s="83"/>
+      <c r="X61" s="84"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="88"/>
-      <c r="AA61" s="89"/>
-      <c r="AB61" s="90"/>
+      <c r="Z61" s="82"/>
+      <c r="AA61" s="83"/>
+      <c r="AB61" s="84"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="88"/>
-      <c r="AE61" s="89"/>
-      <c r="AF61" s="90"/>
+      <c r="AD61" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE61" s="83"/>
+      <c r="AF61" s="84"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="88"/>
-      <c r="AI61" s="89"/>
-      <c r="AJ61" s="90"/>
+      <c r="AH61" s="82"/>
+      <c r="AI61" s="83"/>
+      <c r="AJ61" s="84"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="88" t="s">
+      <c r="AL61" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="AM61" s="89"/>
-      <c r="AN61" s="90"/>
+      <c r="AM61" s="83"/>
+      <c r="AN61" s="84"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="88"/>
-      <c r="C62" s="89"/>
-      <c r="D62" s="90"/>
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="82"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="84"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="89"/>
-      <c r="H62" s="90"/>
+      <c r="F62" s="82"/>
+      <c r="G62" s="83"/>
+      <c r="H62" s="84"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="88"/>
-      <c r="K62" s="89"/>
-      <c r="L62" s="90"/>
+      <c r="J62" s="82"/>
+      <c r="K62" s="83"/>
+      <c r="L62" s="84"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="85"/>
-      <c r="O62" s="86"/>
-      <c r="P62" s="87"/>
+      <c r="N62" s="88"/>
+      <c r="O62" s="89"/>
+      <c r="P62" s="90"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="85" t="s">
+      <c r="R62" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="S62" s="86"/>
-      <c r="T62" s="87"/>
+      <c r="S62" s="89"/>
+      <c r="T62" s="90"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="85"/>
-      <c r="W62" s="86"/>
-      <c r="X62" s="87"/>
+      <c r="V62" s="88"/>
+      <c r="W62" s="89"/>
+      <c r="X62" s="90"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="85"/>
-      <c r="AA62" s="86"/>
-      <c r="AB62" s="87"/>
+      <c r="Z62" s="88"/>
+      <c r="AA62" s="89"/>
+      <c r="AB62" s="90"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="85"/>
-      <c r="AE62" s="86"/>
-      <c r="AF62" s="87"/>
+      <c r="AD62" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE62" s="89"/>
+      <c r="AF62" s="90"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="85"/>
-      <c r="AI62" s="86"/>
-      <c r="AJ62" s="87"/>
+      <c r="AH62" s="88"/>
+      <c r="AI62" s="89"/>
+      <c r="AJ62" s="90"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="85" t="s">
+      <c r="AL62" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="AM62" s="86"/>
-      <c r="AN62" s="87"/>
+      <c r="AM62" s="89"/>
+      <c r="AN62" s="90"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="85"/>
-      <c r="C63" s="86"/>
-      <c r="D63" s="87"/>
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="88"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="90"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="85"/>
-      <c r="G63" s="86"/>
-      <c r="H63" s="87"/>
+      <c r="F63" s="88"/>
+      <c r="G63" s="89"/>
+      <c r="H63" s="90"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="85"/>
-      <c r="K63" s="86"/>
-      <c r="L63" s="87"/>
+      <c r="J63" s="88"/>
+      <c r="K63" s="89"/>
+      <c r="L63" s="90"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="85"/>
-      <c r="O63" s="86"/>
-      <c r="P63" s="87"/>
+      <c r="N63" s="88"/>
+      <c r="O63" s="89"/>
+      <c r="P63" s="90"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="85"/>
-      <c r="S63" s="86"/>
-      <c r="T63" s="87"/>
+      <c r="R63" s="88"/>
+      <c r="S63" s="89"/>
+      <c r="T63" s="90"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="85"/>
-      <c r="W63" s="86"/>
-      <c r="X63" s="87"/>
+      <c r="V63" s="88"/>
+      <c r="W63" s="89"/>
+      <c r="X63" s="90"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="85"/>
-      <c r="AA63" s="86"/>
-      <c r="AB63" s="87"/>
+      <c r="Z63" s="88"/>
+      <c r="AA63" s="89"/>
+      <c r="AB63" s="90"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="85"/>
-      <c r="AE63" s="86"/>
-      <c r="AF63" s="87"/>
+      <c r="AD63" s="88"/>
+      <c r="AE63" s="89"/>
+      <c r="AF63" s="90"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="85"/>
-      <c r="AI63" s="86"/>
-      <c r="AJ63" s="87"/>
+      <c r="AH63" s="88"/>
+      <c r="AI63" s="89"/>
+      <c r="AJ63" s="90"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="85"/>
-      <c r="AM63" s="86"/>
-      <c r="AN63" s="87"/>
+      <c r="AL63" s="88"/>
+      <c r="AM63" s="89"/>
+      <c r="AN63" s="90"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="82"/>
-      <c r="C64" s="83"/>
-      <c r="D64" s="84"/>
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="85"/>
+      <c r="C64" s="86"/>
+      <c r="D64" s="87"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="82"/>
-      <c r="G64" s="83"/>
-      <c r="H64" s="84"/>
+      <c r="F64" s="85"/>
+      <c r="G64" s="86"/>
+      <c r="H64" s="87"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="82"/>
-      <c r="K64" s="83"/>
-      <c r="L64" s="84"/>
+      <c r="J64" s="85"/>
+      <c r="K64" s="86"/>
+      <c r="L64" s="87"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="82"/>
-      <c r="O64" s="83"/>
-      <c r="P64" s="84"/>
+      <c r="N64" s="85"/>
+      <c r="O64" s="86"/>
+      <c r="P64" s="87"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="82"/>
-      <c r="S64" s="83"/>
-      <c r="T64" s="84"/>
+      <c r="R64" s="85"/>
+      <c r="S64" s="86"/>
+      <c r="T64" s="87"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="82"/>
-      <c r="W64" s="83"/>
-      <c r="X64" s="84"/>
+      <c r="V64" s="85"/>
+      <c r="W64" s="86"/>
+      <c r="X64" s="87"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="82"/>
-      <c r="AA64" s="83"/>
-      <c r="AB64" s="84"/>
+      <c r="Z64" s="85"/>
+      <c r="AA64" s="86"/>
+      <c r="AB64" s="87"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="82"/>
-      <c r="AE64" s="83"/>
-      <c r="AF64" s="84"/>
+      <c r="AD64" s="85"/>
+      <c r="AE64" s="86"/>
+      <c r="AF64" s="87"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="82"/>
-      <c r="AI64" s="83"/>
-      <c r="AJ64" s="84"/>
+      <c r="AH64" s="85"/>
+      <c r="AI64" s="86"/>
+      <c r="AJ64" s="87"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="82"/>
-      <c r="AM64" s="83"/>
-      <c r="AN64" s="84"/>
+      <c r="AL64" s="85"/>
+      <c r="AM64" s="86"/>
+      <c r="AN64" s="87"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
       <c r="B65" s="33"/>
       <c r="C65" s="33"/>
@@ -5742,7 +5793,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
       <c r="B66" s="40"/>
       <c r="C66" s="33"/>
@@ -5756,23 +5807,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="108" t="s">
+      <c r="N66" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="108"/>
-      <c r="P66" s="108"/>
-      <c r="Q66" s="108"/>
-      <c r="R66" s="108"/>
-      <c r="S66" s="108"/>
-      <c r="T66" s="108"/>
-      <c r="U66" s="108"/>
-      <c r="V66" s="108"/>
-      <c r="W66" s="108"/>
-      <c r="X66" s="108"/>
-      <c r="Y66" s="108"/>
-      <c r="Z66" s="108"/>
-      <c r="AA66" s="108"/>
-      <c r="AB66" s="108"/>
+      <c r="O66" s="114"/>
+      <c r="P66" s="114"/>
+      <c r="Q66" s="114"/>
+      <c r="R66" s="114"/>
+      <c r="S66" s="114"/>
+      <c r="T66" s="114"/>
+      <c r="U66" s="114"/>
+      <c r="V66" s="114"/>
+      <c r="W66" s="114"/>
+      <c r="X66" s="114"/>
+      <c r="Y66" s="114"/>
+      <c r="Z66" s="114"/>
+      <c r="AA66" s="114"/>
+      <c r="AB66" s="114"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5789,7 +5840,7 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
       <c r="B67" s="33"/>
       <c r="C67" s="33"/>
@@ -5803,21 +5854,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="108"/>
-      <c r="O67" s="108"/>
-      <c r="P67" s="108"/>
-      <c r="Q67" s="108"/>
-      <c r="R67" s="108"/>
-      <c r="S67" s="108"/>
-      <c r="T67" s="108"/>
-      <c r="U67" s="108"/>
-      <c r="V67" s="108"/>
-      <c r="W67" s="108"/>
-      <c r="X67" s="108"/>
-      <c r="Y67" s="108"/>
-      <c r="Z67" s="108"/>
-      <c r="AA67" s="108"/>
-      <c r="AB67" s="108"/>
+      <c r="N67" s="114"/>
+      <c r="O67" s="114"/>
+      <c r="P67" s="114"/>
+      <c r="Q67" s="114"/>
+      <c r="R67" s="114"/>
+      <c r="S67" s="114"/>
+      <c r="T67" s="114"/>
+      <c r="U67" s="114"/>
+      <c r="V67" s="114"/>
+      <c r="W67" s="114"/>
+      <c r="X67" s="114"/>
+      <c r="Y67" s="114"/>
+      <c r="Z67" s="114"/>
+      <c r="AA67" s="114"/>
+      <c r="AB67" s="114"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5835,7 +5886,7 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
       <c r="B68" s="66" t="s">
         <v>48</v>
@@ -5895,7 +5946,7 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
       <c r="B69" s="91" t="s">
         <v>60</v>
@@ -5955,7 +6006,7 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
       <c r="B70" s="68" t="s">
         <v>39</v>
@@ -6015,59 +6066,59 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="88" t="s">
+      <c r="B71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="89"/>
-      <c r="D71" s="90"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="84"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="88" t="s">
+      <c r="F71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="G71" s="89"/>
-      <c r="H71" s="90"/>
+      <c r="G71" s="83"/>
+      <c r="H71" s="84"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="88" t="s">
+      <c r="J71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="K71" s="89"/>
-      <c r="L71" s="90"/>
+      <c r="K71" s="83"/>
+      <c r="L71" s="84"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="88" t="s">
+      <c r="N71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="O71" s="89"/>
-      <c r="P71" s="90"/>
+      <c r="O71" s="83"/>
+      <c r="P71" s="84"/>
       <c r="Q71" s="32"/>
-      <c r="R71" s="88" t="s">
+      <c r="R71" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="S71" s="89"/>
-      <c r="T71" s="90"/>
+      <c r="S71" s="83"/>
+      <c r="T71" s="84"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="88"/>
-      <c r="W71" s="89"/>
-      <c r="X71" s="90"/>
+      <c r="V71" s="82"/>
+      <c r="W71" s="83"/>
+      <c r="X71" s="84"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="88"/>
-      <c r="AA71" s="89"/>
-      <c r="AB71" s="90"/>
+      <c r="Z71" s="82"/>
+      <c r="AA71" s="83"/>
+      <c r="AB71" s="84"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="88"/>
-      <c r="AE71" s="89"/>
-      <c r="AF71" s="90"/>
+      <c r="AD71" s="82"/>
+      <c r="AE71" s="83"/>
+      <c r="AF71" s="84"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="88"/>
-      <c r="AI71" s="89"/>
-      <c r="AJ71" s="90"/>
+      <c r="AH71" s="82"/>
+      <c r="AI71" s="83"/>
+      <c r="AJ71" s="84"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="88" t="s">
+      <c r="AL71" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="AM71" s="89"/>
-      <c r="AN71" s="90"/>
+      <c r="AM71" s="83"/>
+      <c r="AN71" s="84"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -6075,55 +6126,55 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="82"/>
-      <c r="C72" s="83"/>
-      <c r="D72" s="84"/>
+      <c r="B72" s="85"/>
+      <c r="C72" s="86"/>
+      <c r="D72" s="87"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="82"/>
-      <c r="G72" s="83"/>
-      <c r="H72" s="84"/>
+      <c r="F72" s="85"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="87"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="82"/>
-      <c r="K72" s="83"/>
-      <c r="L72" s="84"/>
+      <c r="J72" s="85"/>
+      <c r="K72" s="86"/>
+      <c r="L72" s="87"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="82"/>
-      <c r="O72" s="83"/>
-      <c r="P72" s="84"/>
+      <c r="N72" s="85"/>
+      <c r="O72" s="86"/>
+      <c r="P72" s="87"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="82"/>
-      <c r="S72" s="83"/>
-      <c r="T72" s="84"/>
+      <c r="R72" s="85"/>
+      <c r="S72" s="86"/>
+      <c r="T72" s="87"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="82"/>
-      <c r="W72" s="83"/>
-      <c r="X72" s="84"/>
+      <c r="V72" s="85"/>
+      <c r="W72" s="86"/>
+      <c r="X72" s="87"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="82"/>
-      <c r="AA72" s="83"/>
-      <c r="AB72" s="84"/>
+      <c r="Z72" s="85"/>
+      <c r="AA72" s="86"/>
+      <c r="AB72" s="87"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="82"/>
-      <c r="AE72" s="83"/>
-      <c r="AF72" s="84"/>
+      <c r="AD72" s="85"/>
+      <c r="AE72" s="86"/>
+      <c r="AF72" s="87"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="82"/>
-      <c r="AI72" s="83"/>
-      <c r="AJ72" s="84"/>
+      <c r="AH72" s="85"/>
+      <c r="AI72" s="86"/>
+      <c r="AJ72" s="87"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="82" t="s">
+      <c r="AL72" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="AM72" s="83"/>
-      <c r="AN72" s="84"/>
+      <c r="AM72" s="86"/>
+      <c r="AN72" s="87"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -6169,7 +6220,7 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
       <c r="B74" s="66" t="s">
         <v>54</v>
@@ -6229,7 +6280,7 @@
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
       <c r="B75" s="91" t="s">
         <v>59</v>
@@ -6279,7 +6330,7 @@
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
       <c r="B76" s="68" t="s">
         <v>39</v>
@@ -6339,23 +6390,23 @@
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="88" t="s">
+      <c r="B77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="89"/>
-      <c r="D77" s="90"/>
+      <c r="C77" s="83"/>
+      <c r="D77" s="84"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="88" t="s">
+      <c r="F77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="G77" s="89"/>
-      <c r="H77" s="90"/>
+      <c r="G77" s="83"/>
+      <c r="H77" s="84"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="88"/>
-      <c r="K77" s="89"/>
-      <c r="L77" s="90"/>
+      <c r="J77" s="82"/>
+      <c r="K77" s="83"/>
+      <c r="L77" s="84"/>
       <c r="M77" s="4"/>
       <c r="N77" s="95" t="s">
         <v>30</v>
@@ -6363,55 +6414,55 @@
       <c r="O77" s="96"/>
       <c r="P77" s="97"/>
       <c r="Q77" s="37"/>
-      <c r="R77" s="88" t="s">
+      <c r="R77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="S77" s="89"/>
-      <c r="T77" s="90"/>
+      <c r="S77" s="83"/>
+      <c r="T77" s="84"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="88"/>
-      <c r="W77" s="89"/>
-      <c r="X77" s="90"/>
+      <c r="V77" s="82"/>
+      <c r="W77" s="83"/>
+      <c r="X77" s="84"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="88" t="s">
+      <c r="Z77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="AA77" s="89"/>
-      <c r="AB77" s="90"/>
+      <c r="AA77" s="83"/>
+      <c r="AB77" s="84"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="88" t="s">
+      <c r="AD77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="AE77" s="89"/>
-      <c r="AF77" s="90"/>
+      <c r="AE77" s="83"/>
+      <c r="AF77" s="84"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="88" t="s">
+      <c r="AH77" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="AI77" s="89"/>
-      <c r="AJ77" s="90"/>
+      <c r="AI77" s="83"/>
+      <c r="AJ77" s="84"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="88"/>
-      <c r="AM77" s="89"/>
-      <c r="AN77" s="90"/>
+      <c r="AL77" s="82"/>
+      <c r="AM77" s="83"/>
+      <c r="AN77" s="84"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="82"/>
-      <c r="C78" s="83"/>
-      <c r="D78" s="84"/>
+      <c r="B78" s="85"/>
+      <c r="C78" s="86"/>
+      <c r="D78" s="87"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="82"/>
-      <c r="G78" s="83"/>
-      <c r="H78" s="84"/>
+      <c r="F78" s="85"/>
+      <c r="G78" s="86"/>
+      <c r="H78" s="87"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="82"/>
-      <c r="K78" s="83"/>
-      <c r="L78" s="84"/>
+      <c r="J78" s="85"/>
+      <c r="K78" s="86"/>
+      <c r="L78" s="87"/>
       <c r="M78" s="5"/>
       <c r="N78" s="98" t="s">
         <v>81</v>
@@ -6419,35 +6470,35 @@
       <c r="O78" s="99"/>
       <c r="P78" s="100"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="82"/>
-      <c r="S78" s="83"/>
-      <c r="T78" s="84"/>
+      <c r="R78" s="85"/>
+      <c r="S78" s="86"/>
+      <c r="T78" s="87"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="82"/>
-      <c r="W78" s="83"/>
-      <c r="X78" s="84"/>
+      <c r="V78" s="85"/>
+      <c r="W78" s="86"/>
+      <c r="X78" s="87"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="82"/>
-      <c r="AA78" s="83"/>
-      <c r="AB78" s="84"/>
+      <c r="Z78" s="85"/>
+      <c r="AA78" s="86"/>
+      <c r="AB78" s="87"/>
       <c r="AC78" s="31"/>
-      <c r="AD78" s="82"/>
-      <c r="AE78" s="83"/>
-      <c r="AF78" s="84"/>
+      <c r="AD78" s="85"/>
+      <c r="AE78" s="86"/>
+      <c r="AF78" s="87"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="82"/>
-      <c r="AI78" s="83"/>
-      <c r="AJ78" s="84"/>
+      <c r="AH78" s="85"/>
+      <c r="AI78" s="86"/>
+      <c r="AJ78" s="87"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="82"/>
-      <c r="AM78" s="83"/>
-      <c r="AN78" s="84"/>
+      <c r="AL78" s="85"/>
+      <c r="AM78" s="86"/>
+      <c r="AN78" s="87"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="16"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -6493,7 +6544,7 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
       <c r="B80" s="66"/>
       <c r="C80" s="67"/>
@@ -6551,7 +6602,7 @@
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
       <c r="B81" s="91"/>
       <c r="C81" s="92"/>
@@ -6597,7 +6648,7 @@
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
       <c r="B82" s="68"/>
       <c r="C82" s="69"/>
@@ -6655,11 +6706,11 @@
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="88"/>
-      <c r="C83" s="89"/>
-      <c r="D83" s="90"/>
+      <c r="B83" s="82"/>
+      <c r="C83" s="83"/>
+      <c r="D83" s="84"/>
       <c r="E83" s="32"/>
       <c r="F83" s="95" t="s">
         <v>14</v>
@@ -6667,57 +6718,57 @@
       <c r="G83" s="96"/>
       <c r="H83" s="97"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="88" t="s">
+      <c r="J83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="K83" s="89"/>
-      <c r="L83" s="90"/>
+      <c r="K83" s="83"/>
+      <c r="L83" s="84"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="88" t="s">
+      <c r="N83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="O83" s="89"/>
-      <c r="P83" s="90"/>
+      <c r="O83" s="83"/>
+      <c r="P83" s="84"/>
       <c r="Q83" s="44"/>
-      <c r="R83" s="88" t="s">
+      <c r="R83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="S83" s="89"/>
-      <c r="T83" s="90"/>
+      <c r="S83" s="83"/>
+      <c r="T83" s="84"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="88"/>
-      <c r="W83" s="89"/>
-      <c r="X83" s="90"/>
+      <c r="V83" s="82"/>
+      <c r="W83" s="83"/>
+      <c r="X83" s="84"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="88" t="s">
+      <c r="Z83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="AA83" s="89"/>
-      <c r="AB83" s="90"/>
+      <c r="AA83" s="83"/>
+      <c r="AB83" s="84"/>
       <c r="AC83" s="43"/>
-      <c r="AD83" s="88" t="s">
+      <c r="AD83" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="AE83" s="89"/>
-      <c r="AF83" s="90"/>
+      <c r="AE83" s="83"/>
+      <c r="AF83" s="84"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="88"/>
-      <c r="AI83" s="89"/>
-      <c r="AJ83" s="90"/>
+      <c r="AH83" s="82"/>
+      <c r="AI83" s="83"/>
+      <c r="AJ83" s="84"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="88"/>
-      <c r="AM83" s="89"/>
-      <c r="AN83" s="90"/>
+      <c r="AL83" s="82"/>
+      <c r="AM83" s="83"/>
+      <c r="AN83" s="84"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="82"/>
-      <c r="C84" s="83"/>
-      <c r="D84" s="84"/>
+      <c r="B84" s="85"/>
+      <c r="C84" s="86"/>
+      <c r="D84" s="87"/>
       <c r="E84" s="31"/>
       <c r="F84" s="98" t="s">
         <v>85</v>
@@ -6731,39 +6782,39 @@
       <c r="K84" s="99"/>
       <c r="L84" s="100"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="82"/>
-      <c r="O84" s="83"/>
-      <c r="P84" s="84"/>
+      <c r="N84" s="85"/>
+      <c r="O84" s="86"/>
+      <c r="P84" s="87"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="82"/>
-      <c r="S84" s="83"/>
-      <c r="T84" s="84"/>
+      <c r="R84" s="85"/>
+      <c r="S84" s="86"/>
+      <c r="T84" s="87"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="82"/>
-      <c r="W84" s="83"/>
-      <c r="X84" s="84"/>
+      <c r="V84" s="85"/>
+      <c r="W84" s="86"/>
+      <c r="X84" s="87"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="82"/>
-      <c r="AA84" s="83"/>
-      <c r="AB84" s="84"/>
+      <c r="Z84" s="85"/>
+      <c r="AA84" s="86"/>
+      <c r="AB84" s="87"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="82"/>
-      <c r="AE84" s="83"/>
-      <c r="AF84" s="84"/>
+      <c r="AD84" s="85"/>
+      <c r="AE84" s="86"/>
+      <c r="AF84" s="87"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="82"/>
-      <c r="AI84" s="83"/>
-      <c r="AJ84" s="84"/>
+      <c r="AH84" s="85"/>
+      <c r="AI84" s="86"/>
+      <c r="AJ84" s="87"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="82"/>
-      <c r="AM84" s="83"/>
-      <c r="AN84" s="84"/>
+      <c r="AL84" s="85"/>
+      <c r="AM84" s="86"/>
+      <c r="AN84" s="87"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -6809,7 +6860,7 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
       <c r="B86" s="66" t="s">
         <v>53</v>
@@ -6863,7 +6914,7 @@
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
       <c r="B87" s="68" t="s">
         <v>87</v>
@@ -6913,7 +6964,7 @@
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
       <c r="B88" s="70" t="s">
         <v>19</v>
@@ -6971,7 +7022,7 @@
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
       <c r="B89" s="72" t="s">
         <v>29</v>
@@ -6989,9 +7040,9 @@
         <v>33</v>
       </c>
       <c r="I89" s="31"/>
-      <c r="J89" s="88"/>
-      <c r="K89" s="89"/>
-      <c r="L89" s="90"/>
+      <c r="J89" s="82"/>
+      <c r="K89" s="83"/>
+      <c r="L89" s="84"/>
       <c r="M89" s="6"/>
       <c r="N89" s="95" t="s">
         <v>14</v>
@@ -6999,37 +7050,37 @@
       <c r="O89" s="96"/>
       <c r="P89" s="97"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="88"/>
-      <c r="S89" s="89"/>
-      <c r="T89" s="90"/>
+      <c r="R89" s="82"/>
+      <c r="S89" s="83"/>
+      <c r="T89" s="84"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="88" t="s">
+      <c r="V89" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="W89" s="89"/>
-      <c r="X89" s="90"/>
+      <c r="W89" s="83"/>
+      <c r="X89" s="84"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="88"/>
-      <c r="AA89" s="89"/>
-      <c r="AB89" s="90"/>
+      <c r="Z89" s="82"/>
+      <c r="AA89" s="83"/>
+      <c r="AB89" s="84"/>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="88"/>
-      <c r="AE89" s="89"/>
-      <c r="AF89" s="90"/>
+      <c r="AD89" s="82"/>
+      <c r="AE89" s="83"/>
+      <c r="AF89" s="84"/>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="88"/>
-      <c r="AI89" s="89"/>
-      <c r="AJ89" s="90"/>
+      <c r="AH89" s="82"/>
+      <c r="AI89" s="83"/>
+      <c r="AJ89" s="84"/>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="88"/>
-      <c r="AM89" s="89"/>
-      <c r="AN89" s="90"/>
+      <c r="AL89" s="82"/>
+      <c r="AM89" s="83"/>
+      <c r="AN89" s="84"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
       <c r="B90" s="62" t="s">
         <v>11</v>
@@ -7047,9 +7098,9 @@
         <v>34</v>
       </c>
       <c r="I90" s="32"/>
-      <c r="J90" s="82"/>
-      <c r="K90" s="83"/>
-      <c r="L90" s="84"/>
+      <c r="J90" s="85"/>
+      <c r="K90" s="86"/>
+      <c r="L90" s="87"/>
       <c r="M90" s="6"/>
       <c r="N90" s="98" t="s">
         <v>86</v>
@@ -7057,35 +7108,35 @@
       <c r="O90" s="99"/>
       <c r="P90" s="100"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="82"/>
-      <c r="S90" s="83"/>
-      <c r="T90" s="84"/>
+      <c r="R90" s="85"/>
+      <c r="S90" s="86"/>
+      <c r="T90" s="87"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="82"/>
-      <c r="W90" s="83"/>
-      <c r="X90" s="84"/>
+      <c r="V90" s="85"/>
+      <c r="W90" s="86"/>
+      <c r="X90" s="87"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="82"/>
-      <c r="AA90" s="83"/>
-      <c r="AB90" s="84"/>
+      <c r="Z90" s="85"/>
+      <c r="AA90" s="86"/>
+      <c r="AB90" s="87"/>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="82"/>
-      <c r="AE90" s="83"/>
-      <c r="AF90" s="84"/>
+      <c r="AD90" s="85"/>
+      <c r="AE90" s="86"/>
+      <c r="AF90" s="87"/>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="82"/>
-      <c r="AI90" s="83"/>
-      <c r="AJ90" s="84"/>
+      <c r="AH90" s="85"/>
+      <c r="AI90" s="86"/>
+      <c r="AJ90" s="87"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="82"/>
-      <c r="AM90" s="83"/>
-      <c r="AN90" s="84"/>
+      <c r="AL90" s="85"/>
+      <c r="AM90" s="86"/>
+      <c r="AN90" s="87"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
       <c r="B91" s="62" t="s">
         <v>27</v>
@@ -7121,12 +7172,12 @@
       <c r="Y91" s="35"/>
       <c r="Z91" s="35"/>
       <c r="AA91" s="35"/>
-      <c r="AB91" s="35"/>
-      <c r="AC91" s="44"/>
+      <c r="AB91" s="142"/>
+      <c r="AC91" s="50"/>
       <c r="AD91" s="35"/>
       <c r="AE91" s="35"/>
-      <c r="AF91" s="35"/>
-      <c r="AG91" s="44"/>
+      <c r="AF91" s="142"/>
+      <c r="AG91" s="50"/>
       <c r="AH91" s="35"/>
       <c r="AI91" s="35"/>
       <c r="AJ91" s="35"/>
@@ -7139,7 +7190,7 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
       <c r="B92" s="62" t="s">
         <v>13</v>
@@ -7193,7 +7244,7 @@
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
       <c r="B93" s="62"/>
       <c r="C93" s="63"/>
@@ -7239,7 +7290,7 @@
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
       <c r="B94" s="62"/>
       <c r="C94" s="63"/>
@@ -7285,7 +7336,7 @@
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
       <c r="B95" s="62"/>
       <c r="C95" s="63"/>
@@ -7295,43 +7346,43 @@
       <c r="G95" s="63"/>
       <c r="H95" s="45"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="88"/>
-      <c r="K95" s="89"/>
-      <c r="L95" s="90"/>
+      <c r="J95" s="82"/>
+      <c r="K95" s="83"/>
+      <c r="L95" s="84"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="88"/>
-      <c r="O95" s="89"/>
-      <c r="P95" s="90"/>
+      <c r="N95" s="82"/>
+      <c r="O95" s="83"/>
+      <c r="P95" s="84"/>
       <c r="Q95" s="37"/>
-      <c r="R95" s="88"/>
-      <c r="S95" s="89"/>
-      <c r="T95" s="90"/>
+      <c r="R95" s="82"/>
+      <c r="S95" s="83"/>
+      <c r="T95" s="84"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="88"/>
-      <c r="W95" s="89"/>
-      <c r="X95" s="90"/>
+      <c r="V95" s="82"/>
+      <c r="W95" s="83"/>
+      <c r="X95" s="84"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="88"/>
-      <c r="AA95" s="89"/>
-      <c r="AB95" s="90"/>
+      <c r="Z95" s="82"/>
+      <c r="AA95" s="83"/>
+      <c r="AB95" s="84"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="88"/>
-      <c r="AE95" s="89"/>
-      <c r="AF95" s="90"/>
+      <c r="AD95" s="82"/>
+      <c r="AE95" s="83"/>
+      <c r="AF95" s="84"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="88"/>
-      <c r="AI95" s="89"/>
-      <c r="AJ95" s="90"/>
+      <c r="AH95" s="82"/>
+      <c r="AI95" s="83"/>
+      <c r="AJ95" s="84"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="88"/>
-      <c r="AM95" s="89"/>
-      <c r="AN95" s="90"/>
+      <c r="AL95" s="82"/>
+      <c r="AM95" s="83"/>
+      <c r="AN95" s="84"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="64"/>
       <c r="C96" s="65"/>
@@ -7341,43 +7392,43 @@
       <c r="G96" s="65"/>
       <c r="H96" s="42"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="82"/>
-      <c r="K96" s="83"/>
-      <c r="L96" s="84"/>
+      <c r="J96" s="85"/>
+      <c r="K96" s="86"/>
+      <c r="L96" s="87"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="82"/>
-      <c r="O96" s="83"/>
-      <c r="P96" s="84"/>
+      <c r="N96" s="85"/>
+      <c r="O96" s="86"/>
+      <c r="P96" s="87"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="82"/>
-      <c r="S96" s="83"/>
-      <c r="T96" s="84"/>
+      <c r="R96" s="85"/>
+      <c r="S96" s="86"/>
+      <c r="T96" s="87"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="82"/>
-      <c r="W96" s="83"/>
-      <c r="X96" s="84"/>
+      <c r="V96" s="85"/>
+      <c r="W96" s="86"/>
+      <c r="X96" s="87"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="82"/>
-      <c r="AA96" s="83"/>
-      <c r="AB96" s="84"/>
+      <c r="Z96" s="85"/>
+      <c r="AA96" s="86"/>
+      <c r="AB96" s="87"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="82"/>
-      <c r="AE96" s="83"/>
-      <c r="AF96" s="84"/>
+      <c r="AD96" s="85"/>
+      <c r="AE96" s="86"/>
+      <c r="AF96" s="87"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="82"/>
-      <c r="AI96" s="83"/>
-      <c r="AJ96" s="84"/>
+      <c r="AH96" s="85"/>
+      <c r="AI96" s="86"/>
+      <c r="AJ96" s="87"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="82"/>
-      <c r="AM96" s="83"/>
-      <c r="AN96" s="84"/>
+      <c r="AL96" s="85"/>
+      <c r="AM96" s="86"/>
+      <c r="AN96" s="87"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35"/>
@@ -7423,7 +7474,7 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
       <c r="B98" s="66" t="s">
         <v>50</v>
@@ -7471,7 +7522,7 @@
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
       <c r="B99" s="91" t="s">
         <v>61</v>
@@ -7519,7 +7570,7 @@
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
       <c r="B100" s="68"/>
       <c r="C100" s="69"/>
@@ -7565,101 +7616,101 @@
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="88" t="s">
+      <c r="B101" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="89"/>
-      <c r="D101" s="90"/>
+      <c r="C101" s="83"/>
+      <c r="D101" s="84"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="88"/>
-      <c r="G101" s="89"/>
-      <c r="H101" s="90"/>
+      <c r="F101" s="82"/>
+      <c r="G101" s="83"/>
+      <c r="H101" s="84"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="88"/>
-      <c r="K101" s="89"/>
-      <c r="L101" s="90"/>
+      <c r="J101" s="82"/>
+      <c r="K101" s="83"/>
+      <c r="L101" s="84"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="88"/>
-      <c r="O101" s="89"/>
-      <c r="P101" s="90"/>
+      <c r="N101" s="82"/>
+      <c r="O101" s="83"/>
+      <c r="P101" s="84"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="88"/>
-      <c r="S101" s="89"/>
-      <c r="T101" s="90"/>
+      <c r="R101" s="82"/>
+      <c r="S101" s="83"/>
+      <c r="T101" s="84"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="88"/>
-      <c r="W101" s="89"/>
-      <c r="X101" s="90"/>
+      <c r="V101" s="82"/>
+      <c r="W101" s="83"/>
+      <c r="X101" s="84"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="88"/>
-      <c r="AA101" s="89"/>
-      <c r="AB101" s="90"/>
+      <c r="Z101" s="82"/>
+      <c r="AA101" s="83"/>
+      <c r="AB101" s="84"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="88"/>
-      <c r="AE101" s="89"/>
-      <c r="AF101" s="90"/>
+      <c r="AD101" s="82"/>
+      <c r="AE101" s="83"/>
+      <c r="AF101" s="84"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="88"/>
-      <c r="AI101" s="89"/>
-      <c r="AJ101" s="90"/>
+      <c r="AH101" s="82"/>
+      <c r="AI101" s="83"/>
+      <c r="AJ101" s="84"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="88"/>
-      <c r="AM101" s="89"/>
-      <c r="AN101" s="90"/>
+      <c r="AL101" s="82"/>
+      <c r="AM101" s="83"/>
+      <c r="AN101" s="84"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="82"/>
-      <c r="C102" s="83"/>
-      <c r="D102" s="84"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="86"/>
+      <c r="D102" s="87"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="82"/>
-      <c r="G102" s="83"/>
-      <c r="H102" s="84"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="86"/>
+      <c r="H102" s="87"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="82"/>
-      <c r="K102" s="83"/>
-      <c r="L102" s="84"/>
+      <c r="J102" s="85"/>
+      <c r="K102" s="86"/>
+      <c r="L102" s="87"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="82"/>
-      <c r="O102" s="83"/>
-      <c r="P102" s="84"/>
+      <c r="N102" s="85"/>
+      <c r="O102" s="86"/>
+      <c r="P102" s="87"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="82"/>
-      <c r="S102" s="83"/>
-      <c r="T102" s="84"/>
+      <c r="R102" s="85"/>
+      <c r="S102" s="86"/>
+      <c r="T102" s="87"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="82"/>
-      <c r="W102" s="83"/>
-      <c r="X102" s="84"/>
+      <c r="V102" s="85"/>
+      <c r="W102" s="86"/>
+      <c r="X102" s="87"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="82"/>
-      <c r="AA102" s="83"/>
-      <c r="AB102" s="84"/>
+      <c r="Z102" s="85"/>
+      <c r="AA102" s="86"/>
+      <c r="AB102" s="87"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="82"/>
-      <c r="AE102" s="83"/>
-      <c r="AF102" s="84"/>
+      <c r="AD102" s="85"/>
+      <c r="AE102" s="86"/>
+      <c r="AF102" s="87"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="82"/>
-      <c r="AI102" s="83"/>
-      <c r="AJ102" s="84"/>
+      <c r="AH102" s="85"/>
+      <c r="AI102" s="86"/>
+      <c r="AJ102" s="87"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="82"/>
-      <c r="AM102" s="83"/>
-      <c r="AN102" s="84"/>
+      <c r="AL102" s="85"/>
+      <c r="AM102" s="86"/>
+      <c r="AN102" s="87"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7705,7 +7756,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7722,7 +7773,7 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="74"/>
       <c r="C105" s="75"/>
       <c r="D105" s="34"/>
@@ -7736,7 +7787,7 @@
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="76"/>
       <c r="C106" s="77"/>
       <c r="D106" s="78"/>
@@ -7749,7 +7800,7 @@
       <c r="K106" s="77"/>
       <c r="L106" s="78"/>
     </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="79"/>
       <c r="C107" s="80"/>
       <c r="D107" s="81"/>
@@ -7762,33 +7813,33 @@
       <c r="K107" s="80"/>
       <c r="L107" s="81"/>
     </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="88"/>
-      <c r="C108" s="89"/>
-      <c r="D108" s="90"/>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="82"/>
+      <c r="C108" s="83"/>
+      <c r="D108" s="84"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="88"/>
-      <c r="G108" s="89"/>
-      <c r="H108" s="90"/>
+      <c r="F108" s="82"/>
+      <c r="G108" s="83"/>
+      <c r="H108" s="84"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="88"/>
-      <c r="K108" s="89"/>
-      <c r="L108" s="90"/>
-    </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="82"/>
-      <c r="C109" s="83"/>
-      <c r="D109" s="84"/>
+      <c r="J108" s="82"/>
+      <c r="K108" s="83"/>
+      <c r="L108" s="84"/>
+    </row>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="85"/>
+      <c r="C109" s="86"/>
+      <c r="D109" s="87"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="82"/>
-      <c r="G109" s="83"/>
-      <c r="H109" s="84"/>
+      <c r="F109" s="85"/>
+      <c r="G109" s="86"/>
+      <c r="H109" s="87"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="82"/>
-      <c r="K109" s="83"/>
-      <c r="L109" s="84"/>
-    </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J109" s="85"/>
+      <c r="K109" s="86"/>
+      <c r="L109" s="87"/>
+    </row>
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7801,7 +7852,7 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="74"/>
       <c r="C111" s="75"/>
       <c r="D111" s="34"/>
@@ -7814,7 +7865,7 @@
       <c r="K111" s="75"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="76"/>
       <c r="C112" s="77"/>
       <c r="D112" s="78"/>
@@ -7827,7 +7878,7 @@
       <c r="K112" s="77"/>
       <c r="L112" s="78"/>
     </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="79"/>
       <c r="C113" s="80"/>
       <c r="D113" s="81"/>
@@ -7840,33 +7891,33 @@
       <c r="K113" s="80"/>
       <c r="L113" s="81"/>
     </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="88"/>
-      <c r="C114" s="89"/>
-      <c r="D114" s="90"/>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="82"/>
+      <c r="C114" s="83"/>
+      <c r="D114" s="84"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="88"/>
-      <c r="G114" s="89"/>
-      <c r="H114" s="90"/>
+      <c r="F114" s="82"/>
+      <c r="G114" s="83"/>
+      <c r="H114" s="84"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="88"/>
-      <c r="K114" s="89"/>
-      <c r="L114" s="90"/>
-    </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="82"/>
-      <c r="C115" s="83"/>
-      <c r="D115" s="84"/>
+      <c r="J114" s="82"/>
+      <c r="K114" s="83"/>
+      <c r="L114" s="84"/>
+    </row>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="85"/>
+      <c r="C115" s="86"/>
+      <c r="D115" s="87"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="82"/>
-      <c r="G115" s="83"/>
-      <c r="H115" s="84"/>
+      <c r="F115" s="85"/>
+      <c r="G115" s="86"/>
+      <c r="H115" s="87"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="82"/>
-      <c r="K115" s="83"/>
-      <c r="L115" s="84"/>
-    </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J115" s="85"/>
+      <c r="K115" s="86"/>
+      <c r="L115" s="87"/>
+    </row>
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -7879,7 +7930,7 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B117" s="74"/>
       <c r="C117" s="75"/>
       <c r="D117" s="34"/>
@@ -7892,7 +7943,7 @@
       <c r="K117" s="75"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B118" s="76"/>
       <c r="C118" s="77"/>
       <c r="D118" s="78"/>
@@ -7905,7 +7956,7 @@
       <c r="K118" s="77"/>
       <c r="L118" s="78"/>
     </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B119" s="79"/>
       <c r="C119" s="80"/>
       <c r="D119" s="81"/>
@@ -7918,33 +7969,33 @@
       <c r="K119" s="80"/>
       <c r="L119" s="81"/>
     </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="88"/>
-      <c r="C120" s="89"/>
-      <c r="D120" s="90"/>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="82"/>
+      <c r="C120" s="83"/>
+      <c r="D120" s="84"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="88"/>
-      <c r="G120" s="89"/>
-      <c r="H120" s="90"/>
+      <c r="F120" s="82"/>
+      <c r="G120" s="83"/>
+      <c r="H120" s="84"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="88"/>
-      <c r="K120" s="89"/>
-      <c r="L120" s="90"/>
-    </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="82"/>
-      <c r="C121" s="83"/>
-      <c r="D121" s="84"/>
+      <c r="J120" s="82"/>
+      <c r="K120" s="83"/>
+      <c r="L120" s="84"/>
+    </row>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="85"/>
+      <c r="C121" s="86"/>
+      <c r="D121" s="87"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="82"/>
-      <c r="G121" s="83"/>
-      <c r="H121" s="84"/>
+      <c r="F121" s="85"/>
+      <c r="G121" s="86"/>
+      <c r="H121" s="87"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="82"/>
-      <c r="K121" s="83"/>
-      <c r="L121" s="84"/>
-    </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J121" s="85"/>
+      <c r="K121" s="86"/>
+      <c r="L121" s="87"/>
+    </row>
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -7957,7 +8008,7 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B123" s="74"/>
       <c r="C123" s="75"/>
       <c r="D123" s="34"/>
@@ -7970,7 +8021,7 @@
       <c r="K123" s="75"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="76"/>
       <c r="C124" s="77"/>
       <c r="D124" s="78"/>
@@ -7983,7 +8034,7 @@
       <c r="K124" s="77"/>
       <c r="L124" s="78"/>
     </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="79"/>
       <c r="C125" s="80"/>
       <c r="D125" s="81"/>
@@ -7996,33 +8047,33 @@
       <c r="K125" s="80"/>
       <c r="L125" s="81"/>
     </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="88"/>
-      <c r="C126" s="89"/>
-      <c r="D126" s="90"/>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="82"/>
+      <c r="C126" s="83"/>
+      <c r="D126" s="84"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="88"/>
-      <c r="G126" s="89"/>
-      <c r="H126" s="90"/>
+      <c r="F126" s="82"/>
+      <c r="G126" s="83"/>
+      <c r="H126" s="84"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="88"/>
-      <c r="K126" s="89"/>
-      <c r="L126" s="90"/>
-    </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="82"/>
-      <c r="C127" s="83"/>
-      <c r="D127" s="84"/>
+      <c r="J126" s="82"/>
+      <c r="K126" s="83"/>
+      <c r="L126" s="84"/>
+    </row>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="85"/>
+      <c r="C127" s="86"/>
+      <c r="D127" s="87"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="82"/>
-      <c r="G127" s="83"/>
-      <c r="H127" s="84"/>
+      <c r="F127" s="85"/>
+      <c r="G127" s="86"/>
+      <c r="H127" s="87"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="82"/>
-      <c r="K127" s="83"/>
-      <c r="L127" s="84"/>
-    </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J127" s="85"/>
+      <c r="K127" s="86"/>
+      <c r="L127" s="87"/>
+    </row>
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -8035,7 +8086,7 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B129" s="74"/>
       <c r="C129" s="75"/>
       <c r="D129" s="34"/>
@@ -8048,7 +8099,7 @@
       <c r="K129" s="75"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B130" s="76"/>
       <c r="C130" s="77"/>
       <c r="D130" s="78"/>
@@ -8061,7 +8112,7 @@
       <c r="K130" s="77"/>
       <c r="L130" s="78"/>
     </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B131" s="79"/>
       <c r="C131" s="80"/>
       <c r="D131" s="81"/>
@@ -8074,36 +8125,40 @@
       <c r="K131" s="80"/>
       <c r="L131" s="81"/>
     </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="88"/>
-      <c r="C132" s="89"/>
-      <c r="D132" s="90"/>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="82"/>
+      <c r="C132" s="83"/>
+      <c r="D132" s="84"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="88"/>
-      <c r="G132" s="89"/>
-      <c r="H132" s="90"/>
+      <c r="F132" s="82"/>
+      <c r="G132" s="83"/>
+      <c r="H132" s="84"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="88"/>
-      <c r="K132" s="89"/>
-      <c r="L132" s="90"/>
-    </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="82"/>
-      <c r="C133" s="83"/>
-      <c r="D133" s="84"/>
+      <c r="J132" s="82"/>
+      <c r="K132" s="83"/>
+      <c r="L132" s="84"/>
+    </row>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="85"/>
+      <c r="C133" s="86"/>
+      <c r="D133" s="87"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="82"/>
-      <c r="G133" s="83"/>
-      <c r="H133" s="84"/>
+      <c r="F133" s="85"/>
+      <c r="G133" s="86"/>
+      <c r="H133" s="87"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="82"/>
-      <c r="K133" s="83"/>
-      <c r="L133" s="84"/>
+      <c r="J133" s="85"/>
+      <c r="K133" s="86"/>
+      <c r="L133" s="87"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="883">
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="Z98:AA98"/>
     <mergeCell ref="AD98:AE98"/>
     <mergeCell ref="V93:X93"/>
@@ -8124,34 +8179,17 @@
     <mergeCell ref="Z47:AB47"/>
     <mergeCell ref="F39:H39"/>
     <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:H40"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:K25"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B25:C25"/>
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="F36:H36"/>
@@ -8165,15 +8203,12 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J33:L33"/>
     <mergeCell ref="R26:S26"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="R25:S25"/>
@@ -8182,18 +8217,22 @@
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N21:O21"/>
     <mergeCell ref="AL20:AM20"/>
     <mergeCell ref="Z33:AB33"/>
     <mergeCell ref="AL27:AM27"/>
@@ -8206,10 +8245,19 @@
     <mergeCell ref="AH27:AI27"/>
     <mergeCell ref="AD26:AE26"/>
     <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AD39:AF39"/>
     <mergeCell ref="Z34:AB34"/>
     <mergeCell ref="R33:T33"/>
     <mergeCell ref="AD35:AF35"/>
@@ -8220,10 +8268,38 @@
     <mergeCell ref="R35:T35"/>
     <mergeCell ref="R34:T34"/>
     <mergeCell ref="V33:X33"/>
-    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="AD53:AF53"/>
     <mergeCell ref="Z54:AB54"/>
     <mergeCell ref="V55:X55"/>
     <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="R77:T77"/>
     <mergeCell ref="Z69:AB69"/>
     <mergeCell ref="Z70:AB70"/>
     <mergeCell ref="R71:T71"/>
@@ -8233,36 +8309,10 @@
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Z72:AB72"/>
     <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="Z61:AB61"/>
     <mergeCell ref="R70:T70"/>
     <mergeCell ref="R64:T64"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="Z93:AB93"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z84:AB84"/>
     <mergeCell ref="N76:P76"/>
     <mergeCell ref="N55:P55"/>
     <mergeCell ref="N57:P57"/>
@@ -8271,21 +8321,21 @@
     <mergeCell ref="N59:O59"/>
     <mergeCell ref="V78:X78"/>
     <mergeCell ref="V80:W80"/>
-    <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="Z52:AB52"/>
     <mergeCell ref="V70:X70"/>
     <mergeCell ref="R62:T62"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="N83:P83"/>
     <mergeCell ref="Z89:AB89"/>
     <mergeCell ref="Z90:AB90"/>
     <mergeCell ref="N88:P88"/>
@@ -8296,13 +8346,17 @@
     <mergeCell ref="R90:T90"/>
     <mergeCell ref="R87:T87"/>
     <mergeCell ref="R89:T89"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
     <mergeCell ref="F75:H75"/>
     <mergeCell ref="R75:T75"/>
     <mergeCell ref="V68:W68"/>
@@ -8312,14 +8366,6 @@
     <mergeCell ref="R69:T69"/>
     <mergeCell ref="N70:P70"/>
     <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R61:T61"/>
     <mergeCell ref="AH83:AJ83"/>
     <mergeCell ref="AD84:AF84"/>
     <mergeCell ref="AH84:AJ84"/>
@@ -8338,6 +8384,12 @@
     <mergeCell ref="AH94:AJ94"/>
     <mergeCell ref="AH95:AJ95"/>
     <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD87:AF87"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AD94:AF94"/>
     <mergeCell ref="AL102:AN102"/>
     <mergeCell ref="AL101:AN101"/>
     <mergeCell ref="AL96:AN96"/>
@@ -8386,6 +8438,11 @@
     <mergeCell ref="AL69:AN69"/>
     <mergeCell ref="AL68:AM68"/>
     <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
     <mergeCell ref="AL81:AN81"/>
     <mergeCell ref="AL77:AN77"/>
     <mergeCell ref="AL78:AN78"/>
@@ -8401,45 +8458,37 @@
     <mergeCell ref="AL60:AN60"/>
     <mergeCell ref="AL64:AN64"/>
     <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="Z51:AA51"/>
+    <mergeCell ref="Z52:AB52"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="AD48:AF48"/>
     <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="Z25:AA25"/>
     <mergeCell ref="AD25:AE25"/>
     <mergeCell ref="AH25:AI25"/>
     <mergeCell ref="AD24:AE24"/>
     <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
     <mergeCell ref="AH23:AI23"/>
     <mergeCell ref="AD22:AE22"/>
     <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
     <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N72:P72"/>
     <mergeCell ref="V9:X9"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="N4:AB5"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
     <mergeCell ref="N9:P9"/>
     <mergeCell ref="R12:S12"/>
     <mergeCell ref="V12:W12"/>
@@ -8448,6 +8497,14 @@
     <mergeCell ref="V1:X1"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="R15:T15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="R8:T8"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="J1:L1"/>
@@ -8489,6 +8546,8 @@
     <mergeCell ref="AD4:AN5"/>
     <mergeCell ref="Z6:AA6"/>
     <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="F106:H106"/>
     <mergeCell ref="F105:G105"/>
@@ -8513,14 +8572,6 @@
     <mergeCell ref="F101:H101"/>
     <mergeCell ref="F99:H99"/>
     <mergeCell ref="B92:C92"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD46:AF46"/>
     <mergeCell ref="AD31:AE31"/>
     <mergeCell ref="V21:W21"/>
     <mergeCell ref="Z21:AA21"/>
@@ -8537,6 +8588,14 @@
     <mergeCell ref="Z41:AB41"/>
     <mergeCell ref="Z40:AB40"/>
     <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="V38:X38"/>
+    <mergeCell ref="V43:W43"/>
+    <mergeCell ref="V44:X44"/>
+    <mergeCell ref="V45:X45"/>
+    <mergeCell ref="V25:W25"/>
     <mergeCell ref="F92:G92"/>
     <mergeCell ref="AH34:AJ34"/>
     <mergeCell ref="AH41:AJ41"/>
@@ -8561,15 +8620,6 @@
     <mergeCell ref="AH48:AJ48"/>
     <mergeCell ref="AH46:AJ46"/>
     <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="V15:X15"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="B13:C13"/>
@@ -8584,9 +8634,9 @@
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="R20:S20"/>
     <mergeCell ref="V20:W20"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="Z9:AB9"/>
     <mergeCell ref="R10:T10"/>
@@ -8609,10 +8659,8 @@
     <mergeCell ref="N13:P13"/>
     <mergeCell ref="R13:T13"/>
     <mergeCell ref="N14:P14"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
     <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="J9:L9"/>
     <mergeCell ref="AL9:AN9"/>
     <mergeCell ref="AD9:AF9"/>
     <mergeCell ref="AH16:AJ16"/>
@@ -8629,10 +8677,10 @@
     <mergeCell ref="AH14:AJ14"/>
     <mergeCell ref="Z14:AB14"/>
     <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="N12:O12"/>
     <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="AL13:AN13"/>
     <mergeCell ref="F107:H107"/>
     <mergeCell ref="B118:D118"/>
     <mergeCell ref="F118:H118"/>
@@ -8706,6 +8754,15 @@
     <mergeCell ref="J115:L115"/>
     <mergeCell ref="B112:D112"/>
     <mergeCell ref="F112:H112"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N100:P100"/>
     <mergeCell ref="N96:P96"/>
     <mergeCell ref="R96:T96"/>
     <mergeCell ref="J99:L99"/>
@@ -8718,8 +8775,9 @@
     <mergeCell ref="R98:S98"/>
     <mergeCell ref="V98:W98"/>
     <mergeCell ref="J95:L95"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="V84:X84"/>
     <mergeCell ref="J100:L100"/>
     <mergeCell ref="N80:O80"/>
     <mergeCell ref="J80:K80"/>
@@ -8732,16 +8790,17 @@
     <mergeCell ref="J86:K86"/>
     <mergeCell ref="J81:L81"/>
     <mergeCell ref="R80:S80"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="R93:T93"/>
     <mergeCell ref="J106:L106"/>
     <mergeCell ref="Z100:AB100"/>
     <mergeCell ref="N92:O92"/>
@@ -8758,14 +8817,14 @@
     <mergeCell ref="N95:P95"/>
     <mergeCell ref="V101:X101"/>
     <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="R57:T57"/>
     <mergeCell ref="R102:T102"/>
     <mergeCell ref="R100:T100"/>
     <mergeCell ref="J94:L94"/>
-    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="Z99:AB99"/>
     <mergeCell ref="R36:T36"/>
     <mergeCell ref="R38:S38"/>
     <mergeCell ref="N54:P54"/>
@@ -8777,7 +8836,8 @@
     <mergeCell ref="R41:T41"/>
     <mergeCell ref="N41:P41"/>
     <mergeCell ref="R40:T40"/>
-    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="N39:P39"/>
     <mergeCell ref="R24:S24"/>
     <mergeCell ref="R31:S31"/>
     <mergeCell ref="R32:T32"/>
@@ -8801,11 +8861,7 @@
     <mergeCell ref="J48:L48"/>
     <mergeCell ref="N50:P50"/>
     <mergeCell ref="J52:K52"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="R42:T42"/>
     <mergeCell ref="J70:L70"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="J64:L64"/>
@@ -8814,8 +8870,10 @@
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B57:D57"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="F42:H42"/>
     <mergeCell ref="N56:P56"/>
     <mergeCell ref="N47:P47"/>
     <mergeCell ref="B50:D50"/>
@@ -8849,11 +8907,6 @@
     <mergeCell ref="AH82:AJ82"/>
     <mergeCell ref="AH81:AJ81"/>
     <mergeCell ref="V75:X75"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="Z76:AB76"/>
     <mergeCell ref="Z78:AB78"/>
     <mergeCell ref="AD75:AF75"/>
     <mergeCell ref="Z74:AA74"/>
@@ -8870,6 +8923,14 @@
     <mergeCell ref="AH55:AJ55"/>
     <mergeCell ref="AH61:AJ61"/>
     <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="AH74:AI74"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="F47:H47"/>
@@ -8915,15 +8976,9 @@
     <mergeCell ref="J55:L55"/>
     <mergeCell ref="F57:H57"/>
     <mergeCell ref="J75:L75"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="AD87:AF87"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="AD95:AF95"/>
     <mergeCell ref="AD96:AF96"/>
     <mergeCell ref="AH51:AI51"/>
@@ -8948,11 +9003,6 @@
     <mergeCell ref="AD52:AF52"/>
     <mergeCell ref="AD58:AE58"/>
     <mergeCell ref="AD59:AF59"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="V38:X38"/>
-    <mergeCell ref="V43:W43"/>
-    <mergeCell ref="V44:X44"/>
-    <mergeCell ref="V45:X45"/>
     <mergeCell ref="V51:W51"/>
     <mergeCell ref="V52:X52"/>
     <mergeCell ref="V58:W58"/>
@@ -8968,6 +9018,7 @@
     <mergeCell ref="Z43:AA43"/>
     <mergeCell ref="Z44:AB44"/>
     <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="AD46:AF46"/>
     <mergeCell ref="B87:C87"/>
     <mergeCell ref="F87:G87"/>
     <mergeCell ref="B88:C88"/>
@@ -8992,7 +9043,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AB22:AB27 AJ22:AJ27 AF22:AF27 AN22:AN27 T22:T27 H88:H96 H22:H27 D22:D27 D88:D96 L22:L27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V40:X41 AH14:AJ16 AL22:AM27 V95:X96 Z77:AB78 R22:S27 V77:X78 J132:L133 AL71:AN72 AL46:AN49 N77:P78 Z95:AB96 V71:X72 R95:T96 AD71:AF72 AD40:AF41 V22:W27 AH40:AJ41 AL101:AN102 N95:P96 V8:X10 Z54:AB56 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 V61:X64 R14:T16 AH34:AJ35 AL14:AN16 AL83:AN84 V46:X49 Z40:AB41 AH46:AJ49 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 Z34:AB35 Z101:AB102 Z46:AB49 AL54:AN56 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 N55:P57 AL34:AN35 V54:X56 AL61:AN64 N62:P64 R41:T43 AD54:AF56 AD77:AF78 AH22:AI27 R55:T57 N48:P50 N41:P43 R89:T90 AD101:AF102 N14:P16 N34:P36 AH8:AJ10 V34:X35 V83:X84 AL40:AN41 N101:P102 AH54:AJ56 AH77:AJ78 R71:T72 Z71:AB72 Z83:AB84 AD34:AF35 Z22:AA27 AH83:AJ84 AD46:AF49 AH71:AJ72 AH101:AJ102 AD61:AF64 AL77:AN78 N71:P72 Z8:AB10 Z61:AB64 AL8:AN10 R62:T64 N8:P10 AH61:AJ64 R101:T102 AL95:AN96 V101:X102 R83:T84 N83:P84 V89:X90 R77:T78 AD83:AF84 F14:H16 F83:H84 J22:K27 B88:C96 J62:L64 J83:L84 F77:H78 B71:D72 B41:D43 J101:L102 B55:D57 B8:D10 J89:L90 B83:D84 F48:H50 F55:H57 J14:L16 F34:H36 B14:D16 B22:C27 F88:G96 F41:H43 F62:H64 J71:L72 F22:G27 B101:D102 F8:H10 B77:D78 B34:D36 J34:L36 B48:D50 B62:D64 F71:H72 F101:H102 J77:L78 J95:L96 J8:L10 J48:L50 J41:L43 J55:L57">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="V40:X41 AH14:AJ16 AL22:AM27 V95:X96 Z77:AB78 R22:S27 V77:X78 J132:L133 AL71:AN72 AL46:AN49 N77:P78 Z95:AB96 V71:X72 R95:T96 AD71:AF72 AD40:AF41 V22:W27 AH40:AJ41 AL101:AN102 N95:P96 V8:X10 Z54:AB56 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 R48:T50 B108:D109 R34:T36 Z14:AB16 V61:X64 R14:T16 AH34:AJ35 AL14:AN16 AL83:AN84 V46:X49 Z40:AB41 AH46:AJ49 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 Z34:AB35 Z101:AB102 Z46:AB49 AL54:AN56 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 N55:P57 AL34:AN35 V54:X56 AL61:AN64 N62:P64 R41:T43 AD54:AF56 AD77:AF78 AH22:AI27 R55:T57 N48:P50 N41:P43 R89:T90 AD101:AF102 N14:P16 N34:P36 AH8:AJ10 V34:X35 V83:X84 AL40:AN41 N101:P102 AH54:AJ56 AH77:AJ78 R71:T72 Z71:AB72 Z83:AB84 AD34:AF35 Z22:AA27 AH83:AJ84 AD46:AF49 AH71:AJ72 AH101:AJ102 J55:L57 AL77:AN78 N71:P72 Z8:AB10 Z61:AB64 AL8:AN10 R62:T64 N8:P10 AH61:AJ64 R101:T102 AL95:AN96 V101:X102 R83:T84 N83:P84 V89:X90 R77:T78 AD83:AF84 F14:H16 F83:H84 J22:K27 B88:C96 J62:L64 J83:L84 F77:H78 B71:D72 B41:D43 J101:L102 B55:D57 B8:D10 J89:L90 B83:D84 F48:H50 F55:H57 J14:L16 F34:H36 B14:D16 B22:C27 F88:G96 F41:H43 F62:H64 J71:L72 F22:G27 B101:D102 F8:H10 B77:D78 B34:D36 J34:L36 B48:D50 B62:D64 F71:H72 F101:H102 J77:L78 J95:L96 J8:L10 J48:L50 J41:L43 AD61:AF64">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="73">
   <si>
     <t>CUMA</t>
   </si>
@@ -224,9 +224,6 @@
     <t>A.C.PEHLİVAN.</t>
   </si>
   <si>
-    <t>PROVA</t>
-  </si>
-  <si>
     <t>CB Külliye   KURULUM</t>
   </si>
   <si>
@@ -237,6 +234,15 @@
   </si>
   <si>
     <t>???</t>
+  </si>
+  <si>
+    <t>HAZIRLIK</t>
+  </si>
+  <si>
+    <t>Çekmeköy Depo</t>
+  </si>
+  <si>
+    <t>KURULUM + PROVA</t>
   </si>
 </sst>
 </file>
@@ -1494,6 +1500,15 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1527,15 +1542,6 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1566,19 +1572,19 @@
     <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2031,7 +2037,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="175" row="2" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2057,56 +2063,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" customWidth="1"/>
-    <col min="17" max="17" width="1.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="1.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" customWidth="1"/>
-    <col min="23" max="23" width="20.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="1.6640625" customWidth="1"/>
-    <col min="26" max="26" width="2.6640625" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" customWidth="1"/>
-    <col min="29" max="29" width="1.6640625" customWidth="1"/>
-    <col min="30" max="30" width="2.6640625" customWidth="1"/>
-    <col min="31" max="31" width="20.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.6640625" customWidth="1"/>
-    <col min="33" max="33" width="1.6640625" customWidth="1"/>
-    <col min="34" max="34" width="2.6640625" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" customWidth="1"/>
-    <col min="36" max="36" width="6.6640625" customWidth="1"/>
-    <col min="37" max="37" width="1.6640625" customWidth="1"/>
-    <col min="38" max="38" width="2.6640625" customWidth="1"/>
-    <col min="39" max="39" width="20.6640625" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" customWidth="1"/>
-    <col min="41" max="41" width="2.6640625" customWidth="1"/>
-    <col min="42" max="42" width="16.6640625" customWidth="1"/>
-    <col min="43" max="43" width="3.6640625" customWidth="1"/>
-    <col min="44" max="44" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="1.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="1.7109375" customWidth="1"/>
+    <col min="26" max="26" width="2.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" customWidth="1"/>
+    <col min="29" max="29" width="1.7109375" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" customWidth="1"/>
+    <col min="31" max="31" width="20.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.7109375" customWidth="1"/>
+    <col min="33" max="33" width="1.7109375" customWidth="1"/>
+    <col min="34" max="34" width="2.7109375" customWidth="1"/>
+    <col min="35" max="35" width="20.7109375" customWidth="1"/>
+    <col min="36" max="36" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="1.7109375" customWidth="1"/>
+    <col min="38" max="38" width="2.7109375" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="41" max="41" width="2.7109375" customWidth="1"/>
+    <col min="42" max="42" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="3.7109375" customWidth="1"/>
+    <col min="44" max="44" width="8.28515625" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
       <c r="B1" s="111" t="s">
         <v>0</v>
@@ -2172,7 +2178,7 @@
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="114">
         <f>N2-3</f>
@@ -2247,7 +2253,7 @@
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2293,7 +2299,7 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="120"/>
       <c r="C4" s="120"/>
@@ -2341,7 +2347,7 @@
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="120"/>
       <c r="C5" s="120"/>
@@ -2387,7 +2393,7 @@
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="75"/>
       <c r="C6" s="76"/>
       <c r="D6" s="59"/>
@@ -2400,32 +2406,32 @@
       <c r="K6" s="76"/>
       <c r="L6" s="59"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="84"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="87"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="84"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="87"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="84"/>
+      <c r="V6" s="86"/>
+      <c r="W6" s="87"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="84"/>
+      <c r="Z6" s="86"/>
+      <c r="AA6" s="87"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="83"/>
-      <c r="AE6" s="84"/>
+      <c r="AD6" s="86"/>
+      <c r="AE6" s="87"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="83"/>
-      <c r="AI6" s="84"/>
+      <c r="AH6" s="86"/>
+      <c r="AI6" s="87"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="83"/>
-      <c r="AM6" s="84"/>
+      <c r="AL6" s="86"/>
+      <c r="AM6" s="87"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="66"/>
       <c r="C7" s="67"/>
       <c r="D7" s="60"/>
@@ -2485,7 +2491,7 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="69"/>
       <c r="C8" s="70"/>
       <c r="D8" s="71"/>
@@ -2534,46 +2540,46 @@
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="90"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="79"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="90"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="90"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="79"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="88"/>
-      <c r="O9" s="89"/>
-      <c r="P9" s="90"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="79"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="88"/>
-      <c r="S9" s="89"/>
-      <c r="T9" s="90"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="78"/>
+      <c r="T9" s="79"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="89"/>
-      <c r="X9" s="90"/>
+      <c r="V9" s="77"/>
+      <c r="W9" s="78"/>
+      <c r="X9" s="79"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="89"/>
-      <c r="AB9" s="90"/>
+      <c r="Z9" s="77"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="79"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="89"/>
-      <c r="AF9" s="90"/>
+      <c r="AD9" s="77"/>
+      <c r="AE9" s="78"/>
+      <c r="AF9" s="79"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="88"/>
-      <c r="AI9" s="89"/>
-      <c r="AJ9" s="90"/>
+      <c r="AH9" s="77"/>
+      <c r="AI9" s="78"/>
+      <c r="AJ9" s="79"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="88"/>
-      <c r="AM9" s="89"/>
-      <c r="AN9" s="90"/>
+      <c r="AL9" s="77"/>
+      <c r="AM9" s="78"/>
+      <c r="AN9" s="79"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2583,7 +2589,7 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="107"/>
       <c r="C10" s="108"/>
       <c r="D10" s="109"/>
@@ -2632,7 +2638,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2681,7 +2687,7 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="75"/>
       <c r="C12" s="76"/>
       <c r="D12" s="59"/>
@@ -2694,43 +2700,43 @@
       <c r="K12" s="76"/>
       <c r="L12" s="59"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="84"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="87"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="84"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="87"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="83"/>
-      <c r="W12" s="84"/>
+      <c r="V12" s="86"/>
+      <c r="W12" s="87"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="83"/>
-      <c r="AA12" s="84"/>
+      <c r="Z12" s="86"/>
+      <c r="AA12" s="87"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="83"/>
-      <c r="AE12" s="84"/>
+      <c r="AD12" s="86"/>
+      <c r="AE12" s="87"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="83"/>
-      <c r="AI12" s="84"/>
+      <c r="AH12" s="86"/>
+      <c r="AI12" s="87"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="83"/>
-      <c r="AM12" s="84"/>
+      <c r="AL12" s="86"/>
+      <c r="AM12" s="87"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
       </c>
       <c r="AQ12" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="66"/>
       <c r="C13" s="67"/>
       <c r="D13" s="60"/>
@@ -2743,17 +2749,17 @@
       <c r="K13" s="64"/>
       <c r="L13" s="65"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="87"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="90"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="85"/>
-      <c r="S13" s="86"/>
-      <c r="T13" s="87"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="89"/>
+      <c r="T13" s="90"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="85"/>
-      <c r="W13" s="86"/>
-      <c r="X13" s="87"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="89"/>
+      <c r="X13" s="90"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="91"/>
       <c r="AA13" s="92"/>
@@ -2763,13 +2769,13 @@
       <c r="AE13" s="92"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="85"/>
-      <c r="AI13" s="86"/>
-      <c r="AJ13" s="87"/>
+      <c r="AH13" s="88"/>
+      <c r="AI13" s="89"/>
+      <c r="AJ13" s="90"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="85"/>
-      <c r="AM13" s="86"/>
-      <c r="AN13" s="87"/>
+      <c r="AL13" s="88"/>
+      <c r="AM13" s="89"/>
+      <c r="AN13" s="90"/>
       <c r="AP13" s="61" t="s">
         <v>22</v>
       </c>
@@ -2781,7 +2787,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="69"/>
       <c r="C14" s="70"/>
       <c r="D14" s="71"/>
@@ -2832,46 +2838,46 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="90"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="90"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="79"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="90"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="79"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="89"/>
-      <c r="P15" s="90"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="79"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="89"/>
-      <c r="T15" s="90"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="79"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="88"/>
-      <c r="W15" s="89"/>
-      <c r="X15" s="90"/>
+      <c r="V15" s="77"/>
+      <c r="W15" s="78"/>
+      <c r="X15" s="79"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="88"/>
-      <c r="AA15" s="89"/>
-      <c r="AB15" s="90"/>
+      <c r="Z15" s="77"/>
+      <c r="AA15" s="78"/>
+      <c r="AB15" s="79"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="88"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="90"/>
+      <c r="AD15" s="77"/>
+      <c r="AE15" s="78"/>
+      <c r="AF15" s="79"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="88"/>
-      <c r="AI15" s="89"/>
-      <c r="AJ15" s="90"/>
+      <c r="AH15" s="77"/>
+      <c r="AI15" s="78"/>
+      <c r="AJ15" s="79"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="88"/>
-      <c r="AM15" s="89"/>
-      <c r="AN15" s="90"/>
+      <c r="AL15" s="77"/>
+      <c r="AM15" s="78"/>
+      <c r="AN15" s="79"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2881,7 +2887,7 @@
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="107"/>
       <c r="C16" s="108"/>
       <c r="D16" s="109"/>
@@ -2926,11 +2932,11 @@
       </c>
       <c r="AQ16" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -2979,7 +2985,7 @@
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3030,7 +3036,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3079,7 +3085,7 @@
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="75"/>
       <c r="C20" s="76"/>
       <c r="D20" s="59"/>
@@ -3092,8 +3098,8 @@
       <c r="K20" s="76"/>
       <c r="L20" s="59"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="84"/>
+      <c r="N20" s="86"/>
+      <c r="O20" s="87"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
       <c r="R20" s="125"/>
@@ -3108,16 +3114,16 @@
       <c r="AA20" s="126"/>
       <c r="AB20" s="56"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="83"/>
-      <c r="AE20" s="84"/>
+      <c r="AD20" s="86"/>
+      <c r="AE20" s="87"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="83"/>
-      <c r="AI20" s="84"/>
+      <c r="AH20" s="86"/>
+      <c r="AI20" s="87"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="83"/>
-      <c r="AM20" s="84"/>
+      <c r="AL20" s="86"/>
+      <c r="AM20" s="87"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3128,7 +3134,7 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="66"/>
       <c r="C21" s="67"/>
       <c r="D21" s="60"/>
@@ -3177,17 +3183,17 @@
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="77"/>
-      <c r="C22" s="78"/>
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="80"/>
+      <c r="C22" s="81"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="78"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="81"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="78"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="81"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
       <c r="N22" s="94"/>
@@ -3206,12 +3212,12 @@
       <c r="AA22" s="95"/>
       <c r="AB22" s="58"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="78"/>
+      <c r="AD22" s="80"/>
+      <c r="AE22" s="81"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="77"/>
-      <c r="AI22" s="78"/>
+      <c r="AH22" s="80"/>
+      <c r="AI22" s="81"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
       <c r="AL22" s="94"/>
@@ -3226,7 +3232,7 @@
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="96"/>
       <c r="C23" s="97"/>
       <c r="D23" s="45"/>
@@ -3271,98 +3277,98 @@
       </c>
       <c r="AQ23" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR23" s="30"/>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="81"/>
-      <c r="C24" s="82"/>
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="84"/>
+      <c r="C24" s="85"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="82"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="85"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="82"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="85"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="81"/>
-      <c r="O24" s="82"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="85"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="82"/>
+      <c r="R24" s="84"/>
+      <c r="S24" s="85"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="82"/>
+      <c r="V24" s="84"/>
+      <c r="W24" s="85"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="82"/>
+      <c r="Z24" s="84"/>
+      <c r="AA24" s="85"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="82"/>
+      <c r="AD24" s="84"/>
+      <c r="AE24" s="85"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="82"/>
+      <c r="AH24" s="84"/>
+      <c r="AI24" s="85"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="81"/>
-      <c r="AM24" s="82"/>
+      <c r="AL24" s="84"/>
+      <c r="AM24" s="85"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
       </c>
       <c r="AQ24" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="81"/>
-      <c r="C25" s="82"/>
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="84"/>
+      <c r="C25" s="85"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="82"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="85"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="82"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="85"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="82"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="85"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="82"/>
+      <c r="R25" s="84"/>
+      <c r="S25" s="85"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="81"/>
-      <c r="W25" s="82"/>
+      <c r="V25" s="84"/>
+      <c r="W25" s="85"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="81"/>
-      <c r="AA25" s="82"/>
+      <c r="Z25" s="84"/>
+      <c r="AA25" s="85"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="82"/>
+      <c r="AD25" s="84"/>
+      <c r="AE25" s="85"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="82"/>
+      <c r="AH25" s="84"/>
+      <c r="AI25" s="85"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="81"/>
-      <c r="AM25" s="82"/>
+      <c r="AL25" s="84"/>
+      <c r="AM25" s="85"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="46" t="s">
         <v>21</v>
@@ -3373,94 +3379,94 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="81"/>
-      <c r="C26" s="82"/>
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="84"/>
+      <c r="C26" s="85"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="82"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="85"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="82"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="85"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="82"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="85"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="82"/>
+      <c r="R26" s="84"/>
+      <c r="S26" s="85"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="81"/>
-      <c r="W26" s="82"/>
+      <c r="V26" s="84"/>
+      <c r="W26" s="85"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="81"/>
-      <c r="AA26" s="82"/>
+      <c r="Z26" s="84"/>
+      <c r="AA26" s="85"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="82"/>
+      <c r="AD26" s="84"/>
+      <c r="AE26" s="85"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="82"/>
+      <c r="AH26" s="84"/>
+      <c r="AI26" s="85"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="81"/>
-      <c r="AM26" s="82"/>
+      <c r="AL26" s="84"/>
+      <c r="AM26" s="85"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
       </c>
       <c r="AQ26" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="79"/>
-      <c r="C27" s="80"/>
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="82"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="80"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="83"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="80"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="83"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="79"/>
-      <c r="O27" s="80"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="83"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="79"/>
-      <c r="S27" s="80"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="83"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="79"/>
-      <c r="W27" s="80"/>
+      <c r="V27" s="82"/>
+      <c r="W27" s="83"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="79"/>
-      <c r="AA27" s="80"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="83"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="79"/>
-      <c r="AE27" s="80"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="83"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="79"/>
-      <c r="AI27" s="80"/>
+      <c r="AH27" s="82"/>
+      <c r="AI27" s="83"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="79"/>
-      <c r="AM27" s="80"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="83"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3471,7 +3477,7 @@
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
@@ -3520,7 +3526,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
@@ -3571,7 +3577,7 @@
       </c>
       <c r="AR29" s="30"/>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
@@ -3620,7 +3626,7 @@
       </c>
       <c r="AR30" s="30"/>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="75" t="s">
         <v>45</v>
       </c>
@@ -3639,52 +3645,50 @@
       <c r="K31" s="76"/>
       <c r="L31" s="59"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="83" t="s">
+      <c r="N31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O31" s="84"/>
+      <c r="O31" s="87"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="83" t="s">
+      <c r="R31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S31" s="84"/>
+      <c r="S31" s="87"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="83" t="s">
+      <c r="V31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W31" s="84"/>
+      <c r="W31" s="87"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="83" t="s">
+      <c r="Z31" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA31" s="84"/>
+      <c r="AA31" s="87"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="101" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE31" s="102"/>
+      <c r="AD31" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE31" s="105"/>
       <c r="AF31" s="62"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI31" s="84"/>
+      <c r="AH31" s="86"/>
+      <c r="AI31" s="87"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="83" t="s">
+      <c r="AL31" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="AM31" s="84"/>
+      <c r="AM31" s="87"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="63" t="s">
         <v>46</v>
       </c>
@@ -3703,52 +3707,50 @@
       <c r="K32" s="64"/>
       <c r="L32" s="65"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="85" t="s">
+      <c r="N32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O32" s="86"/>
-      <c r="P32" s="87"/>
+      <c r="O32" s="89"/>
+      <c r="P32" s="90"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="85" t="s">
+      <c r="R32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S32" s="86"/>
-      <c r="T32" s="87"/>
+      <c r="S32" s="89"/>
+      <c r="T32" s="90"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="85" t="s">
+      <c r="V32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W32" s="86"/>
-      <c r="X32" s="87"/>
+      <c r="W32" s="89"/>
+      <c r="X32" s="90"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="85" t="s">
+      <c r="Z32" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA32" s="86"/>
-      <c r="AB32" s="87"/>
+      <c r="AA32" s="89"/>
+      <c r="AB32" s="90"/>
       <c r="AC32" s="36"/>
       <c r="AD32" s="98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AE32" s="99"/>
       <c r="AF32" s="100"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="85" t="s">
+      <c r="AH32" s="88"/>
+      <c r="AI32" s="89"/>
+      <c r="AJ32" s="90"/>
+      <c r="AK32" s="36"/>
+      <c r="AL32" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="AI32" s="86"/>
-      <c r="AJ32" s="87"/>
-      <c r="AK32" s="36"/>
-      <c r="AL32" s="85" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM32" s="86"/>
-      <c r="AN32" s="87"/>
+      <c r="AM32" s="89"/>
+      <c r="AN32" s="90"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="66" t="s">
         <v>47</v>
       </c>
@@ -3791,24 +3793,24 @@
       <c r="AA33" s="92"/>
       <c r="AB33" s="93"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="103"/>
-      <c r="AE33" s="104"/>
-      <c r="AF33" s="105"/>
+      <c r="AD33" s="101" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE33" s="102"/>
+      <c r="AF33" s="103"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="91" t="s">
-        <v>58</v>
-      </c>
+      <c r="AH33" s="91"/>
       <c r="AI33" s="92"/>
       <c r="AJ33" s="93"/>
       <c r="AK33" s="32"/>
       <c r="AL33" s="91" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AM33" s="92"/>
       <c r="AN33" s="93"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
       <c r="B34" s="69" t="s">
         <v>7</v>
@@ -3853,14 +3855,12 @@
       <c r="AB34" s="71"/>
       <c r="AC34" s="32"/>
       <c r="AD34" s="69" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE34" s="70"/>
       <c r="AF34" s="71"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="69" t="s">
-        <v>24</v>
-      </c>
+      <c r="AH34" s="69"/>
       <c r="AI34" s="70"/>
       <c r="AJ34" s="71"/>
       <c r="AK34" s="35"/>
@@ -3874,7 +3874,7 @@
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="72" t="s">
         <v>17</v>
@@ -3918,28 +3918,26 @@
       <c r="AA35" s="73"/>
       <c r="AB35" s="74"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="88" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE35" s="89"/>
-      <c r="AF35" s="90"/>
+      <c r="AD35" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE35" s="78"/>
+      <c r="AF35" s="79"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="88" t="s">
+      <c r="AH35" s="77"/>
+      <c r="AI35" s="78"/>
+      <c r="AJ35" s="79"/>
+      <c r="AK35" s="44"/>
+      <c r="AL35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AI35" s="89"/>
-      <c r="AJ35" s="90"/>
-      <c r="AK35" s="44"/>
-      <c r="AL35" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM35" s="89"/>
-      <c r="AN35" s="90"/>
+      <c r="AM35" s="78"/>
+      <c r="AN35" s="79"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="35"/>
       <c r="C36" s="35"/>
@@ -3973,9 +3971,7 @@
       <c r="AE36" s="73"/>
       <c r="AF36" s="74"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="72" t="s">
-        <v>27</v>
-      </c>
+      <c r="AH36" s="72"/>
       <c r="AI36" s="73"/>
       <c r="AJ36" s="74"/>
       <c r="AK36" s="35"/>
@@ -3989,7 +3985,7 @@
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>
       <c r="B37" s="75" t="s">
         <v>45</v>
@@ -4009,28 +4005,28 @@
       <c r="K37" s="76"/>
       <c r="L37" s="59"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="83" t="s">
+      <c r="N37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O37" s="84"/>
+      <c r="O37" s="87"/>
       <c r="P37" s="34"/>
       <c r="Q37" s="36"/>
-      <c r="R37" s="83" t="s">
+      <c r="R37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S37" s="84"/>
+      <c r="S37" s="87"/>
       <c r="T37" s="34"/>
       <c r="U37" s="50"/>
-      <c r="V37" s="83" t="s">
+      <c r="V37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W37" s="84"/>
+      <c r="W37" s="87"/>
       <c r="X37" s="34"/>
       <c r="Y37" s="32"/>
-      <c r="Z37" s="83" t="s">
+      <c r="Z37" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA37" s="84"/>
+      <c r="AA37" s="87"/>
       <c r="AB37" s="34"/>
       <c r="AC37" s="36"/>
       <c r="AD37" s="35"/>
@@ -4049,7 +4045,7 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
       <c r="B38" s="63" t="s">
         <v>46</v>
@@ -4069,51 +4065,51 @@
       <c r="K38" s="64"/>
       <c r="L38" s="65"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="85" t="s">
+      <c r="N38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O38" s="86"/>
-      <c r="P38" s="87"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="90"/>
       <c r="Q38" s="36"/>
-      <c r="R38" s="85" t="s">
+      <c r="R38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S38" s="86"/>
-      <c r="T38" s="87"/>
+      <c r="S38" s="89"/>
+      <c r="T38" s="90"/>
       <c r="U38" s="32"/>
-      <c r="V38" s="85" t="s">
+      <c r="V38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W38" s="86"/>
-      <c r="X38" s="87"/>
+      <c r="W38" s="89"/>
+      <c r="X38" s="90"/>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="85" t="s">
+      <c r="Z38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA38" s="86"/>
-      <c r="AB38" s="87"/>
+      <c r="AA38" s="89"/>
+      <c r="AB38" s="90"/>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="83"/>
-      <c r="AE38" s="84"/>
+      <c r="AD38" s="86"/>
+      <c r="AE38" s="87"/>
       <c r="AF38" s="34"/>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="101" t="s">
+      <c r="AH38" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="AI38" s="102"/>
+      <c r="AI38" s="105"/>
       <c r="AJ38" s="62"/>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="83" t="s">
+      <c r="AL38" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="AM38" s="84"/>
+      <c r="AM38" s="87"/>
       <c r="AN38" s="34"/>
       <c r="AO38" s="31"/>
       <c r="AP38" s="31"/>
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
       <c r="B39" s="66" t="s">
         <v>48</v>
@@ -4157,9 +4153,9 @@
       <c r="AA39" s="92"/>
       <c r="AB39" s="93"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="85"/>
-      <c r="AE39" s="86"/>
-      <c r="AF39" s="87"/>
+      <c r="AD39" s="88"/>
+      <c r="AE39" s="89"/>
+      <c r="AF39" s="90"/>
       <c r="AG39" s="36"/>
       <c r="AH39" s="98" t="s">
         <v>59</v>
@@ -4167,17 +4163,17 @@
       <c r="AI39" s="99"/>
       <c r="AJ39" s="100"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="85" t="s">
+      <c r="AL39" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="AM39" s="86"/>
-      <c r="AN39" s="87"/>
+      <c r="AM39" s="89"/>
+      <c r="AN39" s="90"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
       <c r="B40" s="69" t="s">
         <v>9</v>
@@ -4225,11 +4221,11 @@
       <c r="AE40" s="92"/>
       <c r="AF40" s="93"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="103" t="s">
+      <c r="AH40" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="AI40" s="104"/>
-      <c r="AJ40" s="105"/>
+      <c r="AI40" s="102"/>
+      <c r="AJ40" s="103"/>
       <c r="AK40" s="32"/>
       <c r="AL40" s="91"/>
       <c r="AM40" s="92"/>
@@ -4239,7 +4235,7 @@
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="72" t="s">
         <v>8</v>
@@ -4303,7 +4299,7 @@
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35"/>
@@ -4333,27 +4329,27 @@
       <c r="AA42" s="35"/>
       <c r="AB42" s="35"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="88"/>
-      <c r="AE42" s="89"/>
-      <c r="AF42" s="90"/>
+      <c r="AD42" s="77"/>
+      <c r="AE42" s="78"/>
+      <c r="AF42" s="79"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="88" t="s">
+      <c r="AH42" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="AI42" s="89"/>
-      <c r="AJ42" s="90"/>
+      <c r="AI42" s="78"/>
+      <c r="AJ42" s="79"/>
       <c r="AK42" s="35"/>
-      <c r="AL42" s="88" t="s">
+      <c r="AL42" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="AM42" s="89"/>
-      <c r="AN42" s="90"/>
+      <c r="AM42" s="78"/>
+      <c r="AN42" s="79"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="75" t="s">
         <v>45</v>
@@ -4373,28 +4369,28 @@
       <c r="K43" s="76"/>
       <c r="L43" s="59"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="83" t="s">
+      <c r="N43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O43" s="84"/>
+      <c r="O43" s="87"/>
       <c r="P43" s="34"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="83" t="s">
+      <c r="R43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S43" s="84"/>
+      <c r="S43" s="87"/>
       <c r="T43" s="34"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="83" t="s">
+      <c r="V43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W43" s="84"/>
+      <c r="W43" s="87"/>
       <c r="X43" s="34"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="83" t="s">
+      <c r="Z43" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA43" s="84"/>
+      <c r="AA43" s="87"/>
       <c r="AB43" s="34"/>
       <c r="AC43" s="50"/>
       <c r="AD43" s="72"/>
@@ -4417,7 +4413,7 @@
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="63" t="s">
         <v>46</v>
@@ -4437,29 +4433,29 @@
       <c r="K44" s="64"/>
       <c r="L44" s="65"/>
       <c r="M44" s="14"/>
-      <c r="N44" s="85" t="s">
+      <c r="N44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O44" s="86"/>
-      <c r="P44" s="87"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="90"/>
       <c r="Q44" s="35"/>
-      <c r="R44" s="85" t="s">
+      <c r="R44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S44" s="86"/>
-      <c r="T44" s="87"/>
+      <c r="S44" s="89"/>
+      <c r="T44" s="90"/>
       <c r="U44" s="36"/>
-      <c r="V44" s="85" t="s">
+      <c r="V44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W44" s="86"/>
-      <c r="X44" s="87"/>
+      <c r="W44" s="89"/>
+      <c r="X44" s="90"/>
       <c r="Y44" s="36"/>
-      <c r="Z44" s="85" t="s">
+      <c r="Z44" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA44" s="86"/>
-      <c r="AB44" s="87"/>
+      <c r="AA44" s="89"/>
+      <c r="AB44" s="90"/>
       <c r="AC44" s="36"/>
       <c r="AD44" s="35"/>
       <c r="AE44" s="35"/>
@@ -4477,7 +4473,7 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
       <c r="B45" s="66" t="s">
         <v>49</v>
@@ -4521,18 +4517,20 @@
       <c r="AA45" s="92"/>
       <c r="AB45" s="93"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="83"/>
-      <c r="AE45" s="84"/>
+      <c r="AD45" s="86"/>
+      <c r="AE45" s="87"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="83"/>
-      <c r="AI45" s="84"/>
-      <c r="AJ45" s="34"/>
+      <c r="AH45" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI45" s="105"/>
+      <c r="AJ45" s="62"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="83" t="s">
+      <c r="AL45" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="AM45" s="84"/>
+      <c r="AM45" s="87"/>
       <c r="AN45" s="34" t="s">
         <v>43</v>
       </c>
@@ -4541,119 +4539,121 @@
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="88" t="s">
+      <c r="B46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="89"/>
-      <c r="D46" s="90"/>
+      <c r="C46" s="78"/>
+      <c r="D46" s="79"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="88" t="s">
+      <c r="F46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="G46" s="89"/>
-      <c r="H46" s="90"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="79"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="88" t="s">
+      <c r="J46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="K46" s="89"/>
-      <c r="L46" s="90"/>
+      <c r="K46" s="78"/>
+      <c r="L46" s="79"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="88" t="s">
+      <c r="N46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="O46" s="89"/>
-      <c r="P46" s="90"/>
+      <c r="O46" s="78"/>
+      <c r="P46" s="79"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="88" t="s">
+      <c r="R46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="S46" s="89"/>
-      <c r="T46" s="90"/>
+      <c r="S46" s="78"/>
+      <c r="T46" s="79"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="88" t="s">
+      <c r="V46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="W46" s="89"/>
-      <c r="X46" s="90"/>
+      <c r="W46" s="78"/>
+      <c r="X46" s="79"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="88" t="s">
+      <c r="Z46" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="AA46" s="89"/>
-      <c r="AB46" s="90"/>
+      <c r="AA46" s="78"/>
+      <c r="AB46" s="79"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="85"/>
-      <c r="AE46" s="86"/>
-      <c r="AF46" s="87"/>
+      <c r="AD46" s="88"/>
+      <c r="AE46" s="89"/>
+      <c r="AF46" s="90"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="85"/>
-      <c r="AI46" s="86"/>
-      <c r="AJ46" s="87"/>
+      <c r="AH46" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI46" s="99"/>
+      <c r="AJ46" s="100"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="85" t="s">
+      <c r="AL46" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="AM46" s="86"/>
-      <c r="AN46" s="87"/>
+      <c r="AM46" s="89"/>
+      <c r="AN46" s="90"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="88" t="s">
+      <c r="B47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="89"/>
-      <c r="D47" s="90"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="79"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="88" t="s">
+      <c r="F47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="G47" s="89"/>
-      <c r="H47" s="90"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="88" t="s">
+      <c r="J47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="89"/>
-      <c r="L47" s="90"/>
+      <c r="K47" s="78"/>
+      <c r="L47" s="79"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="88" t="s">
+      <c r="N47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="O47" s="89"/>
-      <c r="P47" s="90"/>
+      <c r="O47" s="78"/>
+      <c r="P47" s="79"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="88" t="s">
+      <c r="R47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="S47" s="89"/>
-      <c r="T47" s="90"/>
+      <c r="S47" s="78"/>
+      <c r="T47" s="79"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="88" t="s">
+      <c r="V47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="W47" s="89"/>
-      <c r="X47" s="90"/>
+      <c r="W47" s="78"/>
+      <c r="X47" s="79"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="88" t="s">
+      <c r="Z47" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AA47" s="89"/>
-      <c r="AB47" s="90"/>
+      <c r="AA47" s="78"/>
+      <c r="AB47" s="79"/>
       <c r="AC47" s="31"/>
       <c r="AD47" s="91"/>
       <c r="AE47" s="92"/>
       <c r="AF47" s="93"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="91"/>
-      <c r="AI47" s="92"/>
-      <c r="AJ47" s="93"/>
+      <c r="AH47" s="101"/>
+      <c r="AI47" s="102"/>
+      <c r="AJ47" s="103"/>
       <c r="AK47" s="32"/>
       <c r="AL47" s="91"/>
       <c r="AM47" s="92"/>
@@ -4663,57 +4663,59 @@
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="88" t="s">
+      <c r="B48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="89"/>
-      <c r="D48" s="90"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="79"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="88" t="s">
+      <c r="F48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="G48" s="89"/>
-      <c r="H48" s="90"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="79"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="88" t="s">
+      <c r="J48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K48" s="89"/>
-      <c r="L48" s="90"/>
+      <c r="K48" s="78"/>
+      <c r="L48" s="79"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="88" t="s">
+      <c r="N48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="O48" s="89"/>
-      <c r="P48" s="90"/>
+      <c r="O48" s="78"/>
+      <c r="P48" s="79"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="88" t="s">
+      <c r="R48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="S48" s="89"/>
-      <c r="T48" s="90"/>
+      <c r="S48" s="78"/>
+      <c r="T48" s="79"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="88" t="s">
+      <c r="V48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="89"/>
-      <c r="X48" s="90"/>
+      <c r="W48" s="78"/>
+      <c r="X48" s="79"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="88" t="s">
+      <c r="Z48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="89"/>
-      <c r="AB48" s="90"/>
+      <c r="AA48" s="78"/>
+      <c r="AB48" s="79"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="88"/>
-      <c r="AE48" s="89"/>
-      <c r="AF48" s="90"/>
+      <c r="AD48" s="77"/>
+      <c r="AE48" s="78"/>
+      <c r="AF48" s="79"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="88"/>
-      <c r="AI48" s="89"/>
-      <c r="AJ48" s="90"/>
+      <c r="AH48" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI48" s="70"/>
+      <c r="AJ48" s="71"/>
       <c r="AK48" s="37"/>
       <c r="AL48" s="69" t="s">
         <v>16</v>
@@ -4725,7 +4727,7 @@
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B49" s="72" t="s">
         <v>26</v>
       </c>
@@ -4768,25 +4770,27 @@
       <c r="AA49" s="73"/>
       <c r="AB49" s="74"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="88"/>
-      <c r="AE49" s="89"/>
-      <c r="AF49" s="90"/>
+      <c r="AD49" s="77"/>
+      <c r="AE49" s="78"/>
+      <c r="AF49" s="79"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="88"/>
-      <c r="AI49" s="89"/>
-      <c r="AJ49" s="90"/>
+      <c r="AH49" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI49" s="78"/>
+      <c r="AJ49" s="79"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="88" t="s">
+      <c r="AL49" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="AM49" s="89"/>
-      <c r="AN49" s="90"/>
+      <c r="AM49" s="78"/>
+      <c r="AN49" s="79"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="35"/>
       <c r="C50" s="35"/>
       <c r="D50" s="35"/>
@@ -4831,7 +4835,7 @@
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="75" t="s">
         <v>45</v>
       </c>
@@ -4850,28 +4854,28 @@
       <c r="K51" s="76"/>
       <c r="L51" s="59"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="83" t="s">
+      <c r="N51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O51" s="84"/>
+      <c r="O51" s="87"/>
       <c r="P51" s="34"/>
       <c r="Q51" s="40"/>
-      <c r="R51" s="83" t="s">
+      <c r="R51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S51" s="84"/>
+      <c r="S51" s="87"/>
       <c r="T51" s="34"/>
       <c r="U51" s="40"/>
-      <c r="V51" s="83" t="s">
+      <c r="V51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W51" s="84"/>
+      <c r="W51" s="87"/>
       <c r="X51" s="34"/>
       <c r="Y51" s="32"/>
-      <c r="Z51" s="83" t="s">
+      <c r="Z51" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA51" s="84"/>
+      <c r="AA51" s="87"/>
       <c r="AB51" s="34"/>
       <c r="AC51" s="40"/>
       <c r="AD51" s="35"/>
@@ -4890,7 +4894,7 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="63" t="s">
         <v>46</v>
       </c>
@@ -4909,44 +4913,44 @@
       <c r="K52" s="64"/>
       <c r="L52" s="65"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="85" t="s">
+      <c r="N52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O52" s="86"/>
-      <c r="P52" s="87"/>
+      <c r="O52" s="89"/>
+      <c r="P52" s="90"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="85" t="s">
+      <c r="R52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S52" s="86"/>
-      <c r="T52" s="87"/>
+      <c r="S52" s="89"/>
+      <c r="T52" s="90"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="85" t="s">
+      <c r="V52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W52" s="86"/>
-      <c r="X52" s="87"/>
+      <c r="W52" s="89"/>
+      <c r="X52" s="90"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="85" t="s">
+      <c r="Z52" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA52" s="86"/>
-      <c r="AB52" s="87"/>
+      <c r="AA52" s="89"/>
+      <c r="AB52" s="90"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="83"/>
-      <c r="AE52" s="84"/>
+      <c r="AD52" s="86"/>
+      <c r="AE52" s="87"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="83"/>
-      <c r="AI52" s="84"/>
+      <c r="AH52" s="86"/>
+      <c r="AI52" s="87"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="83"/>
-      <c r="AM52" s="84"/>
+      <c r="AL52" s="86"/>
+      <c r="AM52" s="87"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="66" t="s">
         <v>50</v>
       </c>
@@ -4989,20 +4993,20 @@
       <c r="AA53" s="92"/>
       <c r="AB53" s="93"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="85"/>
-      <c r="AE53" s="86"/>
-      <c r="AF53" s="87"/>
+      <c r="AD53" s="88"/>
+      <c r="AE53" s="89"/>
+      <c r="AF53" s="90"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="85"/>
-      <c r="AI53" s="86"/>
-      <c r="AJ53" s="87"/>
+      <c r="AH53" s="88"/>
+      <c r="AI53" s="89"/>
+      <c r="AJ53" s="90"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="85"/>
-      <c r="AM53" s="86"/>
-      <c r="AN53" s="87"/>
+      <c r="AL53" s="88"/>
+      <c r="AM53" s="89"/>
+      <c r="AN53" s="90"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="69" t="s">
         <v>24</v>
       </c>
@@ -5058,48 +5062,48 @@
       <c r="AN54" s="93"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="88" t="s">
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="89"/>
-      <c r="D55" s="90"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="79"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="88" t="s">
+      <c r="F55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="89"/>
-      <c r="H55" s="90"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="79"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="88" t="s">
+      <c r="J55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="K55" s="89"/>
-      <c r="L55" s="90"/>
+      <c r="K55" s="78"/>
+      <c r="L55" s="79"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="88" t="s">
+      <c r="N55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="O55" s="89"/>
-      <c r="P55" s="90"/>
+      <c r="O55" s="78"/>
+      <c r="P55" s="79"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="88" t="s">
+      <c r="R55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="S55" s="89"/>
-      <c r="T55" s="90"/>
+      <c r="S55" s="78"/>
+      <c r="T55" s="79"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="88" t="s">
+      <c r="V55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="W55" s="89"/>
-      <c r="X55" s="90"/>
+      <c r="W55" s="78"/>
+      <c r="X55" s="79"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="88" t="s">
+      <c r="Z55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AA55" s="89"/>
-      <c r="AB55" s="90"/>
+      <c r="AA55" s="78"/>
+      <c r="AB55" s="79"/>
       <c r="AC55" s="43"/>
       <c r="AD55" s="69"/>
       <c r="AE55" s="70"/>
@@ -5114,7 +5118,7 @@
       <c r="AN55" s="71"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B56" s="72" t="s">
         <v>21</v>
       </c>
@@ -5157,20 +5161,20 @@
       <c r="AA56" s="73"/>
       <c r="AB56" s="74"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="88"/>
-      <c r="AE56" s="89"/>
-      <c r="AF56" s="90"/>
+      <c r="AD56" s="77"/>
+      <c r="AE56" s="78"/>
+      <c r="AF56" s="79"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="88"/>
-      <c r="AI56" s="89"/>
-      <c r="AJ56" s="90"/>
+      <c r="AH56" s="77"/>
+      <c r="AI56" s="78"/>
+      <c r="AJ56" s="79"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="88"/>
-      <c r="AM56" s="89"/>
-      <c r="AN56" s="90"/>
+      <c r="AL56" s="77"/>
+      <c r="AM56" s="78"/>
+      <c r="AN56" s="79"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="35"/>
       <c r="C57" s="35"/>
       <c r="D57" s="35"/>
@@ -5212,7 +5216,7 @@
       <c r="AN57" s="74"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="127" t="s">
         <v>45</v>
       </c>
@@ -5229,28 +5233,28 @@
       <c r="K58" s="76"/>
       <c r="L58" s="59"/>
       <c r="M58" s="5"/>
-      <c r="N58" s="83" t="s">
+      <c r="N58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="O58" s="84"/>
+      <c r="O58" s="87"/>
       <c r="P58" s="34"/>
       <c r="Q58" s="31"/>
-      <c r="R58" s="83" t="s">
+      <c r="R58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S58" s="84"/>
+      <c r="S58" s="87"/>
       <c r="T58" s="34"/>
       <c r="U58" s="50"/>
-      <c r="V58" s="83" t="s">
+      <c r="V58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="W58" s="84"/>
+      <c r="W58" s="87"/>
       <c r="X58" s="34"/>
       <c r="Y58" s="35"/>
-      <c r="Z58" s="83" t="s">
+      <c r="Z58" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="AA58" s="84"/>
+      <c r="AA58" s="87"/>
       <c r="AB58" s="34"/>
       <c r="AC58" s="50"/>
       <c r="AD58" s="35"/>
@@ -5266,7 +5270,7 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="63" t="s">
         <v>46</v>
       </c>
@@ -5283,44 +5287,44 @@
       <c r="K59" s="64"/>
       <c r="L59" s="65"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="85" t="s">
+      <c r="N59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="O59" s="86"/>
-      <c r="P59" s="87"/>
+      <c r="O59" s="89"/>
+      <c r="P59" s="90"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="85" t="s">
+      <c r="R59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S59" s="86"/>
-      <c r="T59" s="87"/>
+      <c r="S59" s="89"/>
+      <c r="T59" s="90"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="85" t="s">
+      <c r="V59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="W59" s="86"/>
-      <c r="X59" s="87"/>
+      <c r="W59" s="89"/>
+      <c r="X59" s="90"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="85" t="s">
+      <c r="Z59" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="AA59" s="86"/>
-      <c r="AB59" s="87"/>
+      <c r="AA59" s="89"/>
+      <c r="AB59" s="90"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="83"/>
-      <c r="AE59" s="84"/>
+      <c r="AD59" s="86"/>
+      <c r="AE59" s="87"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="83"/>
-      <c r="AI59" s="84"/>
+      <c r="AH59" s="86"/>
+      <c r="AI59" s="87"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="83"/>
-      <c r="AM59" s="84"/>
+      <c r="AL59" s="86"/>
+      <c r="AM59" s="87"/>
       <c r="AN59" s="34"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="66" t="s">
         <v>61</v>
       </c>
@@ -5361,20 +5365,20 @@
       <c r="AA60" s="92"/>
       <c r="AB60" s="93"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="85"/>
-      <c r="AE60" s="86"/>
-      <c r="AF60" s="87"/>
+      <c r="AD60" s="88"/>
+      <c r="AE60" s="89"/>
+      <c r="AF60" s="90"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="85"/>
-      <c r="AI60" s="86"/>
-      <c r="AJ60" s="87"/>
+      <c r="AH60" s="88"/>
+      <c r="AI60" s="89"/>
+      <c r="AJ60" s="90"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="85"/>
-      <c r="AM60" s="86"/>
-      <c r="AN60" s="87"/>
+      <c r="AL60" s="88"/>
+      <c r="AM60" s="89"/>
+      <c r="AN60" s="90"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="69" t="s">
         <v>18</v>
       </c>
@@ -5428,103 +5432,103 @@
       <c r="AN61" s="93"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="88" t="s">
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="89"/>
-      <c r="D62" s="90"/>
+      <c r="C62" s="78"/>
+      <c r="D62" s="79"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="89"/>
-      <c r="H62" s="90"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="78"/>
+      <c r="H62" s="79"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="88" t="s">
+      <c r="J62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="K62" s="89"/>
-      <c r="L62" s="90"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="79"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="88" t="s">
+      <c r="N62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="O62" s="89"/>
-      <c r="P62" s="90"/>
+      <c r="O62" s="78"/>
+      <c r="P62" s="79"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="88" t="s">
+      <c r="R62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="S62" s="89"/>
-      <c r="T62" s="90"/>
+      <c r="S62" s="78"/>
+      <c r="T62" s="79"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="88" t="s">
+      <c r="V62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="W62" s="89"/>
-      <c r="X62" s="90"/>
+      <c r="W62" s="78"/>
+      <c r="X62" s="79"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="88" t="s">
+      <c r="Z62" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="AA62" s="89"/>
-      <c r="AB62" s="90"/>
+      <c r="AA62" s="78"/>
+      <c r="AB62" s="79"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="88"/>
-      <c r="AE62" s="89"/>
-      <c r="AF62" s="90"/>
+      <c r="AD62" s="77"/>
+      <c r="AE62" s="78"/>
+      <c r="AF62" s="79"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="88"/>
-      <c r="AI62" s="89"/>
-      <c r="AJ62" s="90"/>
+      <c r="AH62" s="77"/>
+      <c r="AI62" s="78"/>
+      <c r="AJ62" s="79"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="88"/>
-      <c r="AM62" s="89"/>
-      <c r="AN62" s="90"/>
+      <c r="AL62" s="77"/>
+      <c r="AM62" s="78"/>
+      <c r="AN62" s="79"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="88"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="90"/>
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="77"/>
+      <c r="C63" s="78"/>
+      <c r="D63" s="79"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="89"/>
-      <c r="H63" s="90"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="78"/>
+      <c r="H63" s="79"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="88"/>
-      <c r="K63" s="89"/>
-      <c r="L63" s="90"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="78"/>
+      <c r="L63" s="79"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="88"/>
-      <c r="O63" s="89"/>
-      <c r="P63" s="90"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="78"/>
+      <c r="P63" s="79"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="88"/>
-      <c r="S63" s="89"/>
-      <c r="T63" s="90"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="78"/>
+      <c r="T63" s="79"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="88"/>
-      <c r="W63" s="89"/>
-      <c r="X63" s="90"/>
+      <c r="V63" s="77"/>
+      <c r="W63" s="78"/>
+      <c r="X63" s="79"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="88"/>
-      <c r="AA63" s="89"/>
-      <c r="AB63" s="90"/>
+      <c r="Z63" s="77"/>
+      <c r="AA63" s="78"/>
+      <c r="AB63" s="79"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="88"/>
-      <c r="AE63" s="89"/>
-      <c r="AF63" s="90"/>
+      <c r="AD63" s="77"/>
+      <c r="AE63" s="78"/>
+      <c r="AF63" s="79"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="88"/>
-      <c r="AI63" s="89"/>
-      <c r="AJ63" s="90"/>
+      <c r="AH63" s="77"/>
+      <c r="AI63" s="78"/>
+      <c r="AJ63" s="79"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="88"/>
-      <c r="AM63" s="89"/>
-      <c r="AN63" s="90"/>
+      <c r="AL63" s="77"/>
+      <c r="AM63" s="78"/>
+      <c r="AN63" s="79"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B64" s="72"/>
       <c r="C64" s="73"/>
       <c r="D64" s="74"/>
@@ -5566,7 +5570,7 @@
       <c r="AN64" s="74"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
       <c r="B65" s="33"/>
       <c r="C65" s="33"/>
@@ -5612,7 +5616,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
       <c r="B66" s="40"/>
       <c r="C66" s="33"/>
@@ -5659,7 +5663,7 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
       <c r="B67" s="33"/>
       <c r="C67" s="33"/>
@@ -5705,7 +5709,7 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
       <c r="B68" s="127" t="s">
         <v>45</v>
@@ -5713,46 +5717,46 @@
       <c r="C68" s="128"/>
       <c r="D68" s="55"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="101" t="s">
+      <c r="F68" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="G68" s="102"/>
+      <c r="G68" s="105"/>
       <c r="H68" s="62"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="101" t="s">
+      <c r="J68" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="K68" s="102"/>
+      <c r="K68" s="105"/>
       <c r="L68" s="62"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="83"/>
-      <c r="O68" s="84"/>
+      <c r="N68" s="86"/>
+      <c r="O68" s="87"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="32"/>
-      <c r="R68" s="83" t="s">
+      <c r="R68" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="S68" s="84"/>
+      <c r="S68" s="87"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="83"/>
-      <c r="W68" s="84"/>
+      <c r="V68" s="86"/>
+      <c r="W68" s="87"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="83"/>
-      <c r="AA68" s="84"/>
+      <c r="Z68" s="86"/>
+      <c r="AA68" s="87"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="83"/>
-      <c r="AE68" s="84"/>
+      <c r="AD68" s="86"/>
+      <c r="AE68" s="87"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="83"/>
-      <c r="AI68" s="84"/>
+      <c r="AH68" s="86"/>
+      <c r="AI68" s="87"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="83"/>
-      <c r="AM68" s="84"/>
+      <c r="AL68" s="86"/>
+      <c r="AM68" s="87"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5761,7 +5765,7 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
       <c r="B69" s="63" t="s">
         <v>46</v>
@@ -5781,35 +5785,35 @@
       <c r="K69" s="99"/>
       <c r="L69" s="100"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="85"/>
-      <c r="O69" s="86"/>
-      <c r="P69" s="87"/>
+      <c r="N69" s="88"/>
+      <c r="O69" s="89"/>
+      <c r="P69" s="90"/>
       <c r="Q69" s="35"/>
-      <c r="R69" s="85" t="s">
+      <c r="R69" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S69" s="86"/>
-      <c r="T69" s="87"/>
+      <c r="S69" s="89"/>
+      <c r="T69" s="90"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="85"/>
-      <c r="W69" s="86"/>
-      <c r="X69" s="87"/>
+      <c r="V69" s="88"/>
+      <c r="W69" s="89"/>
+      <c r="X69" s="90"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="85"/>
-      <c r="AA69" s="86"/>
-      <c r="AB69" s="87"/>
+      <c r="Z69" s="88"/>
+      <c r="AA69" s="89"/>
+      <c r="AB69" s="90"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="85"/>
-      <c r="AE69" s="86"/>
-      <c r="AF69" s="87"/>
+      <c r="AD69" s="88"/>
+      <c r="AE69" s="89"/>
+      <c r="AF69" s="90"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="85"/>
-      <c r="AI69" s="86"/>
-      <c r="AJ69" s="87"/>
+      <c r="AH69" s="88"/>
+      <c r="AI69" s="89"/>
+      <c r="AJ69" s="90"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="85"/>
-      <c r="AM69" s="86"/>
-      <c r="AN69" s="87"/>
+      <c r="AL69" s="88"/>
+      <c r="AM69" s="89"/>
+      <c r="AN69" s="90"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5817,23 +5821,23 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
       <c r="B70" s="66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" s="67"/>
       <c r="D70" s="68"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="103"/>
-      <c r="G70" s="104"/>
-      <c r="H70" s="105"/>
+      <c r="F70" s="101"/>
+      <c r="G70" s="102"/>
+      <c r="H70" s="103"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="103" t="s">
+      <c r="J70" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="K70" s="104"/>
-      <c r="L70" s="105"/>
+      <c r="K70" s="102"/>
+      <c r="L70" s="103"/>
       <c r="M70" s="9"/>
       <c r="N70" s="91"/>
       <c r="O70" s="92"/>
@@ -5871,7 +5875,7 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
       <c r="B71" s="69" t="s">
         <v>64</v>
@@ -5886,7 +5890,7 @@
       <c r="H71" s="71"/>
       <c r="I71" s="32"/>
       <c r="J71" s="129" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K71" s="130"/>
       <c r="L71" s="131"/>
@@ -5927,7 +5931,7 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="72" t="s">
         <v>65</v>
@@ -5979,7 +5983,7 @@
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -6025,7 +6029,7 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
       <c r="B74" s="75" t="s">
         <v>62</v>
@@ -6045,45 +6049,45 @@
       <c r="K74" s="128"/>
       <c r="L74" s="55"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="83"/>
-      <c r="O74" s="84"/>
+      <c r="N74" s="86"/>
+      <c r="O74" s="87"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="44"/>
-      <c r="R74" s="83" t="s">
+      <c r="R74" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="S74" s="84"/>
+      <c r="S74" s="87"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="83"/>
-      <c r="W74" s="84"/>
+      <c r="V74" s="86"/>
+      <c r="W74" s="87"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="83" t="s">
+      <c r="Z74" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="AA74" s="84"/>
+      <c r="AA74" s="87"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="83"/>
-      <c r="AE74" s="84"/>
+      <c r="AD74" s="86"/>
+      <c r="AE74" s="87"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="83" t="s">
+      <c r="AH74" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="AI74" s="84"/>
+      <c r="AI74" s="87"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="83"/>
-      <c r="AM74" s="84"/>
+      <c r="AL74" s="86"/>
+      <c r="AM74" s="87"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
       <c r="B75" s="63"/>
       <c r="C75" s="64"/>
@@ -6097,39 +6101,39 @@
       <c r="K75" s="64"/>
       <c r="L75" s="65"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="85"/>
-      <c r="O75" s="86"/>
-      <c r="P75" s="87"/>
+      <c r="N75" s="88"/>
+      <c r="O75" s="89"/>
+      <c r="P75" s="90"/>
       <c r="Q75" s="44"/>
-      <c r="R75" s="85"/>
-      <c r="S75" s="86"/>
-      <c r="T75" s="87"/>
+      <c r="R75" s="88"/>
+      <c r="S75" s="89"/>
+      <c r="T75" s="90"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="85"/>
-      <c r="W75" s="86"/>
-      <c r="X75" s="87"/>
+      <c r="V75" s="88"/>
+      <c r="W75" s="89"/>
+      <c r="X75" s="90"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="85"/>
-      <c r="AA75" s="86"/>
-      <c r="AB75" s="87"/>
+      <c r="Z75" s="88"/>
+      <c r="AA75" s="89"/>
+      <c r="AB75" s="90"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="85"/>
-      <c r="AE75" s="86"/>
-      <c r="AF75" s="87"/>
+      <c r="AD75" s="88"/>
+      <c r="AE75" s="89"/>
+      <c r="AF75" s="90"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="85"/>
-      <c r="AI75" s="86"/>
-      <c r="AJ75" s="87"/>
+      <c r="AH75" s="88"/>
+      <c r="AI75" s="89"/>
+      <c r="AJ75" s="90"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="85"/>
-      <c r="AM75" s="86"/>
-      <c r="AN75" s="87"/>
+      <c r="AL75" s="88"/>
+      <c r="AM75" s="89"/>
+      <c r="AN75" s="90"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
       <c r="B76" s="66" t="s">
         <v>39</v>
@@ -6187,7 +6191,7 @@
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
       <c r="B77" s="69" t="s">
         <v>30</v>
@@ -6245,7 +6249,7 @@
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
       <c r="B78" s="72"/>
       <c r="C78" s="73"/>
@@ -6291,7 +6295,7 @@
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="16"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -6337,7 +6341,7 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
       <c r="B80" s="75" t="s">
         <v>42</v>
@@ -6353,47 +6357,47 @@
       <c r="K80" s="76"/>
       <c r="L80" s="59"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="83" t="s">
+      <c r="N80" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="O80" s="84"/>
+      <c r="O80" s="87"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="44"/>
-      <c r="R80" s="83" t="s">
+      <c r="R80" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="S80" s="84"/>
+      <c r="S80" s="87"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="83"/>
-      <c r="W80" s="84"/>
+      <c r="V80" s="86"/>
+      <c r="W80" s="87"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="83" t="s">
+      <c r="Z80" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="AA80" s="84"/>
+      <c r="AA80" s="87"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="83" t="s">
+      <c r="AD80" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="AE80" s="84"/>
+      <c r="AE80" s="87"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="83"/>
-      <c r="AI80" s="84"/>
+      <c r="AH80" s="86"/>
+      <c r="AI80" s="87"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="83"/>
-      <c r="AM80" s="84"/>
+      <c r="AL80" s="86"/>
+      <c r="AM80" s="87"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
       <c r="B81" s="63"/>
       <c r="C81" s="64"/>
@@ -6407,39 +6411,39 @@
       <c r="K81" s="64"/>
       <c r="L81" s="65"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="85"/>
-      <c r="O81" s="86"/>
-      <c r="P81" s="87"/>
+      <c r="N81" s="88"/>
+      <c r="O81" s="89"/>
+      <c r="P81" s="90"/>
       <c r="Q81" s="44"/>
-      <c r="R81" s="85"/>
-      <c r="S81" s="86"/>
-      <c r="T81" s="87"/>
+      <c r="R81" s="88"/>
+      <c r="S81" s="89"/>
+      <c r="T81" s="90"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="85"/>
-      <c r="W81" s="86"/>
-      <c r="X81" s="87"/>
+      <c r="V81" s="88"/>
+      <c r="W81" s="89"/>
+      <c r="X81" s="90"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="85"/>
-      <c r="AA81" s="86"/>
-      <c r="AB81" s="87"/>
+      <c r="Z81" s="88"/>
+      <c r="AA81" s="89"/>
+      <c r="AB81" s="90"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="85"/>
-      <c r="AE81" s="86"/>
-      <c r="AF81" s="87"/>
+      <c r="AD81" s="88"/>
+      <c r="AE81" s="89"/>
+      <c r="AF81" s="90"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="85"/>
-      <c r="AI81" s="86"/>
-      <c r="AJ81" s="87"/>
+      <c r="AH81" s="88"/>
+      <c r="AI81" s="89"/>
+      <c r="AJ81" s="90"/>
       <c r="AK81" s="35"/>
-      <c r="AL81" s="85"/>
-      <c r="AM81" s="86"/>
-      <c r="AN81" s="87"/>
+      <c r="AL81" s="88"/>
+      <c r="AM81" s="89"/>
+      <c r="AN81" s="90"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
       <c r="B82" s="66" t="s">
         <v>39</v>
@@ -6495,7 +6499,7 @@
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
       <c r="B83" s="69" t="s">
         <v>12</v>
@@ -6551,7 +6555,7 @@
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
       <c r="B84" s="72"/>
       <c r="C84" s="73"/>
@@ -6597,7 +6601,7 @@
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -6643,7 +6647,7 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
       <c r="B86" s="75"/>
       <c r="C86" s="76"/>
@@ -6657,43 +6661,43 @@
       <c r="K86" s="76"/>
       <c r="L86" s="59"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="83" t="s">
+      <c r="N86" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="O86" s="84"/>
+      <c r="O86" s="87"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="83" t="s">
+      <c r="R86" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="S86" s="84"/>
+      <c r="S86" s="87"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="83"/>
-      <c r="W86" s="84"/>
+      <c r="V86" s="86"/>
+      <c r="W86" s="87"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="83"/>
-      <c r="AA86" s="84"/>
+      <c r="Z86" s="86"/>
+      <c r="AA86" s="87"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="83"/>
-      <c r="AE86" s="84"/>
+      <c r="AD86" s="86"/>
+      <c r="AE86" s="87"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="83"/>
-      <c r="AI86" s="84"/>
+      <c r="AH86" s="86"/>
+      <c r="AI86" s="87"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="83"/>
-      <c r="AM86" s="84"/>
+      <c r="AL86" s="86"/>
+      <c r="AM86" s="87"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
       <c r="B87" s="63"/>
       <c r="C87" s="64"/>
@@ -6707,39 +6711,39 @@
       <c r="K87" s="64"/>
       <c r="L87" s="65"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="85"/>
-      <c r="O87" s="86"/>
-      <c r="P87" s="87"/>
+      <c r="N87" s="88"/>
+      <c r="O87" s="89"/>
+      <c r="P87" s="90"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="85"/>
-      <c r="S87" s="86"/>
-      <c r="T87" s="87"/>
+      <c r="R87" s="88"/>
+      <c r="S87" s="89"/>
+      <c r="T87" s="90"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="85"/>
-      <c r="W87" s="86"/>
-      <c r="X87" s="87"/>
+      <c r="V87" s="88"/>
+      <c r="W87" s="89"/>
+      <c r="X87" s="90"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="85"/>
-      <c r="AA87" s="86"/>
-      <c r="AB87" s="87"/>
+      <c r="Z87" s="88"/>
+      <c r="AA87" s="89"/>
+      <c r="AB87" s="90"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="85"/>
-      <c r="AE87" s="86"/>
-      <c r="AF87" s="87"/>
+      <c r="AD87" s="88"/>
+      <c r="AE87" s="89"/>
+      <c r="AF87" s="90"/>
       <c r="AG87" s="38"/>
-      <c r="AH87" s="85"/>
-      <c r="AI87" s="86"/>
-      <c r="AJ87" s="87"/>
+      <c r="AH87" s="88"/>
+      <c r="AI87" s="89"/>
+      <c r="AJ87" s="90"/>
       <c r="AK87" s="35"/>
-      <c r="AL87" s="85"/>
-      <c r="AM87" s="86"/>
-      <c r="AN87" s="87"/>
+      <c r="AL87" s="88"/>
+      <c r="AM87" s="89"/>
+      <c r="AN87" s="90"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
       <c r="B88" s="66"/>
       <c r="C88" s="67"/>
@@ -6789,7 +6793,7 @@
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
       <c r="B89" s="69"/>
       <c r="C89" s="70"/>
@@ -6839,7 +6843,7 @@
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
       <c r="B90" s="72"/>
       <c r="C90" s="73"/>
@@ -6885,7 +6889,7 @@
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35"/>
@@ -6931,7 +6935,7 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
       <c r="B92" s="75"/>
       <c r="C92" s="76"/>
@@ -6945,39 +6949,39 @@
       <c r="K92" s="76"/>
       <c r="L92" s="59"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="83"/>
-      <c r="O92" s="84"/>
+      <c r="N92" s="86"/>
+      <c r="O92" s="87"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="32"/>
-      <c r="R92" s="83"/>
-      <c r="S92" s="84"/>
+      <c r="R92" s="86"/>
+      <c r="S92" s="87"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="83"/>
-      <c r="W92" s="84"/>
+      <c r="V92" s="86"/>
+      <c r="W92" s="87"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="83"/>
-      <c r="AA92" s="84"/>
+      <c r="Z92" s="86"/>
+      <c r="AA92" s="87"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="83"/>
-      <c r="AE92" s="84"/>
+      <c r="AD92" s="86"/>
+      <c r="AE92" s="87"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="83"/>
-      <c r="AI92" s="84"/>
+      <c r="AH92" s="86"/>
+      <c r="AI92" s="87"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="83"/>
-      <c r="AM92" s="84"/>
+      <c r="AL92" s="86"/>
+      <c r="AM92" s="87"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
       <c r="B93" s="63"/>
       <c r="C93" s="64"/>
@@ -6991,39 +6995,39 @@
       <c r="K93" s="64"/>
       <c r="L93" s="65"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="85"/>
-      <c r="O93" s="86"/>
-      <c r="P93" s="87"/>
+      <c r="N93" s="88"/>
+      <c r="O93" s="89"/>
+      <c r="P93" s="90"/>
       <c r="Q93" s="35"/>
-      <c r="R93" s="85"/>
-      <c r="S93" s="86"/>
-      <c r="T93" s="87"/>
+      <c r="R93" s="88"/>
+      <c r="S93" s="89"/>
+      <c r="T93" s="90"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="85"/>
-      <c r="W93" s="86"/>
-      <c r="X93" s="87"/>
+      <c r="V93" s="88"/>
+      <c r="W93" s="89"/>
+      <c r="X93" s="90"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="85"/>
-      <c r="AA93" s="86"/>
-      <c r="AB93" s="87"/>
+      <c r="Z93" s="88"/>
+      <c r="AA93" s="89"/>
+      <c r="AB93" s="90"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="85"/>
-      <c r="AE93" s="86"/>
-      <c r="AF93" s="87"/>
+      <c r="AD93" s="88"/>
+      <c r="AE93" s="89"/>
+      <c r="AF93" s="90"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="85"/>
-      <c r="AI93" s="86"/>
-      <c r="AJ93" s="87"/>
+      <c r="AH93" s="88"/>
+      <c r="AI93" s="89"/>
+      <c r="AJ93" s="90"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="85"/>
-      <c r="AM93" s="86"/>
-      <c r="AN93" s="87"/>
+      <c r="AL93" s="88"/>
+      <c r="AM93" s="89"/>
+      <c r="AN93" s="90"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
       <c r="B94" s="66"/>
       <c r="C94" s="67"/>
@@ -7069,7 +7073,7 @@
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
       <c r="B95" s="69"/>
       <c r="C95" s="70"/>
@@ -7115,7 +7119,7 @@
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="72"/>
       <c r="C96" s="73"/>
@@ -7161,7 +7165,7 @@
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35"/>
@@ -7207,7 +7211,7 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
       <c r="B98" s="75"/>
       <c r="C98" s="76"/>
@@ -7221,47 +7225,47 @@
       <c r="K98" s="76"/>
       <c r="L98" s="59"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="101" t="s">
+      <c r="N98" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="O98" s="102"/>
+      <c r="O98" s="105"/>
       <c r="P98" s="62"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="101" t="s">
+      <c r="R98" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="S98" s="102"/>
+      <c r="S98" s="105"/>
       <c r="T98" s="62"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="101" t="s">
+      <c r="V98" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="W98" s="102"/>
+      <c r="W98" s="105"/>
       <c r="X98" s="62"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="101" t="s">
+      <c r="Z98" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="AA98" s="102"/>
+      <c r="AA98" s="105"/>
       <c r="AB98" s="62"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="83"/>
-      <c r="AE98" s="84"/>
+      <c r="AD98" s="86"/>
+      <c r="AE98" s="87"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="83"/>
-      <c r="AI98" s="84"/>
+      <c r="AH98" s="86"/>
+      <c r="AI98" s="87"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="83"/>
-      <c r="AM98" s="84"/>
+      <c r="AL98" s="86"/>
+      <c r="AM98" s="87"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
       <c r="B99" s="63"/>
       <c r="C99" s="64"/>
@@ -7299,23 +7303,23 @@
       <c r="AA99" s="99"/>
       <c r="AB99" s="100"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="85"/>
-      <c r="AE99" s="86"/>
-      <c r="AF99" s="87"/>
+      <c r="AD99" s="88"/>
+      <c r="AE99" s="89"/>
+      <c r="AF99" s="90"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="85"/>
-      <c r="AI99" s="86"/>
-      <c r="AJ99" s="87"/>
+      <c r="AH99" s="88"/>
+      <c r="AI99" s="89"/>
+      <c r="AJ99" s="90"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="85"/>
-      <c r="AM99" s="86"/>
-      <c r="AN99" s="87"/>
+      <c r="AL99" s="88"/>
+      <c r="AM99" s="89"/>
+      <c r="AN99" s="90"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
       <c r="B100" s="66"/>
       <c r="C100" s="67"/>
@@ -7329,21 +7333,21 @@
       <c r="K100" s="67"/>
       <c r="L100" s="68"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="103"/>
-      <c r="O100" s="104"/>
-      <c r="P100" s="105"/>
+      <c r="N100" s="101"/>
+      <c r="O100" s="102"/>
+      <c r="P100" s="103"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="103"/>
-      <c r="S100" s="104"/>
-      <c r="T100" s="105"/>
+      <c r="R100" s="101"/>
+      <c r="S100" s="102"/>
+      <c r="T100" s="103"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="103"/>
-      <c r="W100" s="104"/>
-      <c r="X100" s="105"/>
+      <c r="V100" s="101"/>
+      <c r="W100" s="102"/>
+      <c r="X100" s="103"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="103"/>
-      <c r="AA100" s="104"/>
-      <c r="AB100" s="105"/>
+      <c r="Z100" s="101"/>
+      <c r="AA100" s="102"/>
+      <c r="AB100" s="103"/>
       <c r="AC100" s="36"/>
       <c r="AD100" s="91"/>
       <c r="AE100" s="92"/>
@@ -7361,7 +7365,7 @@
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
       <c r="B101" s="69"/>
       <c r="C101" s="70"/>
@@ -7415,7 +7419,7 @@
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
       <c r="B102" s="72"/>
       <c r="C102" s="73"/>
@@ -7461,7 +7465,7 @@
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7507,7 +7511,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7524,34 +7528,34 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="83"/>
-      <c r="C105" s="84"/>
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="86"/>
+      <c r="C105" s="87"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="83"/>
-      <c r="G105" s="84"/>
+      <c r="F105" s="86"/>
+      <c r="G105" s="87"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="83"/>
-      <c r="K105" s="84"/>
+      <c r="J105" s="86"/>
+      <c r="K105" s="87"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="85"/>
-      <c r="C106" s="86"/>
-      <c r="D106" s="87"/>
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="88"/>
+      <c r="C106" s="89"/>
+      <c r="D106" s="90"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="85"/>
-      <c r="G106" s="86"/>
-      <c r="H106" s="87"/>
+      <c r="F106" s="88"/>
+      <c r="G106" s="89"/>
+      <c r="H106" s="90"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="85"/>
-      <c r="K106" s="86"/>
-      <c r="L106" s="87"/>
-    </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J106" s="88"/>
+      <c r="K106" s="89"/>
+      <c r="L106" s="90"/>
+    </row>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="91"/>
       <c r="C107" s="92"/>
       <c r="D107" s="93"/>
@@ -7564,7 +7568,7 @@
       <c r="K107" s="92"/>
       <c r="L107" s="93"/>
     </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="69"/>
       <c r="C108" s="70"/>
       <c r="D108" s="71"/>
@@ -7577,7 +7581,7 @@
       <c r="K108" s="70"/>
       <c r="L108" s="71"/>
     </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="72"/>
       <c r="C109" s="73"/>
       <c r="D109" s="74"/>
@@ -7590,7 +7594,7 @@
       <c r="K109" s="73"/>
       <c r="L109" s="74"/>
     </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7603,33 +7607,33 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="83"/>
-      <c r="C111" s="84"/>
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="86"/>
+      <c r="C111" s="87"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="83"/>
-      <c r="G111" s="84"/>
+      <c r="F111" s="86"/>
+      <c r="G111" s="87"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="83"/>
-      <c r="K111" s="84"/>
+      <c r="J111" s="86"/>
+      <c r="K111" s="87"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="85"/>
-      <c r="C112" s="86"/>
-      <c r="D112" s="87"/>
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="88"/>
+      <c r="C112" s="89"/>
+      <c r="D112" s="90"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="85"/>
-      <c r="G112" s="86"/>
-      <c r="H112" s="87"/>
+      <c r="F112" s="88"/>
+      <c r="G112" s="89"/>
+      <c r="H112" s="90"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="85"/>
-      <c r="K112" s="86"/>
-      <c r="L112" s="87"/>
-    </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J112" s="88"/>
+      <c r="K112" s="89"/>
+      <c r="L112" s="90"/>
+    </row>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="91"/>
       <c r="C113" s="92"/>
       <c r="D113" s="93"/>
@@ -7642,7 +7646,7 @@
       <c r="K113" s="92"/>
       <c r="L113" s="93"/>
     </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B114" s="69"/>
       <c r="C114" s="70"/>
       <c r="D114" s="71"/>
@@ -7655,7 +7659,7 @@
       <c r="K114" s="70"/>
       <c r="L114" s="71"/>
     </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" s="72"/>
       <c r="C115" s="73"/>
       <c r="D115" s="74"/>
@@ -7668,7 +7672,7 @@
       <c r="K115" s="73"/>
       <c r="L115" s="74"/>
     </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -7681,33 +7685,33 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="83"/>
-      <c r="C117" s="84"/>
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="86"/>
+      <c r="C117" s="87"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="83"/>
-      <c r="G117" s="84"/>
+      <c r="F117" s="86"/>
+      <c r="G117" s="87"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="83"/>
-      <c r="K117" s="84"/>
+      <c r="J117" s="86"/>
+      <c r="K117" s="87"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="85"/>
-      <c r="C118" s="86"/>
-      <c r="D118" s="87"/>
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="88"/>
+      <c r="C118" s="89"/>
+      <c r="D118" s="90"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="85"/>
-      <c r="G118" s="86"/>
-      <c r="H118" s="87"/>
+      <c r="F118" s="88"/>
+      <c r="G118" s="89"/>
+      <c r="H118" s="90"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="85"/>
-      <c r="K118" s="86"/>
-      <c r="L118" s="87"/>
-    </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J118" s="88"/>
+      <c r="K118" s="89"/>
+      <c r="L118" s="90"/>
+    </row>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B119" s="91"/>
       <c r="C119" s="92"/>
       <c r="D119" s="93"/>
@@ -7720,7 +7724,7 @@
       <c r="K119" s="92"/>
       <c r="L119" s="93"/>
     </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B120" s="69"/>
       <c r="C120" s="70"/>
       <c r="D120" s="71"/>
@@ -7733,7 +7737,7 @@
       <c r="K120" s="70"/>
       <c r="L120" s="71"/>
     </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B121" s="72"/>
       <c r="C121" s="73"/>
       <c r="D121" s="74"/>
@@ -7746,7 +7750,7 @@
       <c r="K121" s="73"/>
       <c r="L121" s="74"/>
     </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -7759,33 +7763,33 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="83"/>
-      <c r="C123" s="84"/>
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="86"/>
+      <c r="C123" s="87"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="83"/>
-      <c r="G123" s="84"/>
+      <c r="F123" s="86"/>
+      <c r="G123" s="87"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="83"/>
-      <c r="K123" s="84"/>
+      <c r="J123" s="86"/>
+      <c r="K123" s="87"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="85"/>
-      <c r="C124" s="86"/>
-      <c r="D124" s="87"/>
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="88"/>
+      <c r="C124" s="89"/>
+      <c r="D124" s="90"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="85"/>
-      <c r="G124" s="86"/>
-      <c r="H124" s="87"/>
+      <c r="F124" s="88"/>
+      <c r="G124" s="89"/>
+      <c r="H124" s="90"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="85"/>
-      <c r="K124" s="86"/>
-      <c r="L124" s="87"/>
-    </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J124" s="88"/>
+      <c r="K124" s="89"/>
+      <c r="L124" s="90"/>
+    </row>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="91"/>
       <c r="C125" s="92"/>
       <c r="D125" s="93"/>
@@ -7798,7 +7802,7 @@
       <c r="K125" s="92"/>
       <c r="L125" s="93"/>
     </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B126" s="69"/>
       <c r="C126" s="70"/>
       <c r="D126" s="71"/>
@@ -7811,7 +7815,7 @@
       <c r="K126" s="70"/>
       <c r="L126" s="71"/>
     </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B127" s="72"/>
       <c r="C127" s="73"/>
       <c r="D127" s="74"/>
@@ -7824,7 +7828,7 @@
       <c r="K127" s="73"/>
       <c r="L127" s="74"/>
     </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -7837,33 +7841,33 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="83"/>
-      <c r="C129" s="84"/>
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="86"/>
+      <c r="C129" s="87"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="83"/>
-      <c r="G129" s="84"/>
+      <c r="F129" s="86"/>
+      <c r="G129" s="87"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="83"/>
-      <c r="K129" s="84"/>
+      <c r="J129" s="86"/>
+      <c r="K129" s="87"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="85"/>
-      <c r="C130" s="86"/>
-      <c r="D130" s="87"/>
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="88"/>
+      <c r="C130" s="89"/>
+      <c r="D130" s="90"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="85"/>
-      <c r="G130" s="86"/>
-      <c r="H130" s="87"/>
+      <c r="F130" s="88"/>
+      <c r="G130" s="89"/>
+      <c r="H130" s="90"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="85"/>
-      <c r="K130" s="86"/>
-      <c r="L130" s="87"/>
-    </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J130" s="88"/>
+      <c r="K130" s="89"/>
+      <c r="L130" s="90"/>
+    </row>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B131" s="91"/>
       <c r="C131" s="92"/>
       <c r="D131" s="93"/>
@@ -7876,7 +7880,7 @@
       <c r="K131" s="92"/>
       <c r="L131" s="93"/>
     </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B132" s="69"/>
       <c r="C132" s="70"/>
       <c r="D132" s="71"/>
@@ -7889,7 +7893,7 @@
       <c r="K132" s="70"/>
       <c r="L132" s="71"/>
     </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B133" s="72"/>
       <c r="C133" s="73"/>
       <c r="D133" s="74"/>
@@ -7927,6 +7931,8 @@
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="F64:H64"/>
     <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="F52:H52"/>
     <mergeCell ref="AD50:AF50"/>
     <mergeCell ref="AD52:AE52"/>
     <mergeCell ref="V47:X47"/>
@@ -7951,8 +7957,6 @@
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="J69:L69"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="F52:H52"/>
     <mergeCell ref="AD90:AF90"/>
     <mergeCell ref="AD93:AF93"/>
     <mergeCell ref="AD94:AF94"/>
@@ -7972,6 +7976,10 @@
     <mergeCell ref="AD87:AF87"/>
     <mergeCell ref="AD88:AF88"/>
     <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AD83:AF83"/>
     <mergeCell ref="B76:D76"/>
     <mergeCell ref="B70:D70"/>
     <mergeCell ref="J70:L70"/>
@@ -8006,8 +8014,20 @@
     <mergeCell ref="J54:L54"/>
     <mergeCell ref="N54:P54"/>
     <mergeCell ref="F54:H54"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="Z64:AB64"/>
     <mergeCell ref="F53:H53"/>
     <mergeCell ref="J53:L53"/>
     <mergeCell ref="V54:X54"/>
@@ -8020,20 +8040,16 @@
     <mergeCell ref="R52:T52"/>
     <mergeCell ref="R58:S58"/>
     <mergeCell ref="R59:T59"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F58:G58"/>
     <mergeCell ref="J52:L52"/>
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="J46:L46"/>
@@ -8042,27 +8058,8 @@
     <mergeCell ref="R43:S43"/>
     <mergeCell ref="R44:T44"/>
     <mergeCell ref="R45:T45"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="J59:L59"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:P52"/>
     <mergeCell ref="J106:L106"/>
     <mergeCell ref="Z100:AB100"/>
     <mergeCell ref="N92:O92"/>
@@ -8135,6 +8132,8 @@
     <mergeCell ref="V88:X88"/>
     <mergeCell ref="V89:X89"/>
     <mergeCell ref="R90:T90"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="R88:T88"/>
     <mergeCell ref="B126:D126"/>
     <mergeCell ref="F126:H126"/>
     <mergeCell ref="J126:L126"/>
@@ -8232,7 +8231,6 @@
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="AH10:AJ10"/>
     <mergeCell ref="R27:S27"/>
-    <mergeCell ref="J16:L16"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="Z12:AA12"/>
@@ -8251,14 +8249,6 @@
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="J13:L13"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
     <mergeCell ref="F62:H62"/>
     <mergeCell ref="F61:H61"/>
     <mergeCell ref="Z23:AA23"/>
@@ -8275,11 +8265,33 @@
     <mergeCell ref="N33:P33"/>
     <mergeCell ref="N41:P41"/>
     <mergeCell ref="V33:X33"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
     <mergeCell ref="AD20:AE20"/>
     <mergeCell ref="AH20:AI20"/>
     <mergeCell ref="N20:O20"/>
@@ -8293,11 +8305,6 @@
     <mergeCell ref="Z21:AA21"/>
     <mergeCell ref="V32:X32"/>
     <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH46:AJ46"/>
     <mergeCell ref="AD27:AE27"/>
     <mergeCell ref="AH54:AJ54"/>
     <mergeCell ref="AD54:AF54"/>
@@ -8317,6 +8324,11 @@
     <mergeCell ref="AH74:AI74"/>
     <mergeCell ref="AH71:AJ71"/>
     <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD40:AF40"/>
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="F106:H106"/>
     <mergeCell ref="F105:G105"/>
@@ -8551,10 +8563,6 @@
     <mergeCell ref="V83:X83"/>
     <mergeCell ref="Z81:AB81"/>
     <mergeCell ref="V77:X77"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N76:P76"/>
     <mergeCell ref="N55:P55"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="V78:X78"/>
@@ -8571,16 +8579,9 @@
     <mergeCell ref="V74:W74"/>
     <mergeCell ref="V60:X60"/>
     <mergeCell ref="R55:T55"/>
-    <mergeCell ref="R88:T88"/>
     <mergeCell ref="R75:T75"/>
     <mergeCell ref="V68:W68"/>
     <mergeCell ref="R63:T63"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AH40:AJ40"/>
     <mergeCell ref="N86:O86"/>
     <mergeCell ref="R86:S86"/>
     <mergeCell ref="Z87:AB87"/>
@@ -8594,6 +8595,9 @@
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Z72:AB72"/>
     <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N76:P76"/>
     <mergeCell ref="AH80:AI80"/>
     <mergeCell ref="AH82:AJ82"/>
     <mergeCell ref="AH81:AJ81"/>
@@ -8606,12 +8610,8 @@
     <mergeCell ref="Z44:AB44"/>
     <mergeCell ref="Z45:AB45"/>
     <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="R41:T41"/>
     <mergeCell ref="Z41:AB41"/>
     <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="R40:T40"/>
     <mergeCell ref="AH38:AI38"/>
     <mergeCell ref="AH42:AJ42"/>
     <mergeCell ref="AH43:AJ43"/>
@@ -8620,6 +8620,8 @@
     <mergeCell ref="AH45:AI45"/>
     <mergeCell ref="AD43:AF43"/>
     <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH46:AJ46"/>
     <mergeCell ref="AL34:AN34"/>
     <mergeCell ref="AL35:AN35"/>
     <mergeCell ref="AL39:AN39"/>
@@ -8688,7 +8690,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F26:G26"/>
-    <mergeCell ref="V27:W27"/>
     <mergeCell ref="Z27:AA27"/>
     <mergeCell ref="V35:X35"/>
     <mergeCell ref="V39:X39"/>
@@ -8704,6 +8705,8 @@
     <mergeCell ref="V38:X38"/>
     <mergeCell ref="R38:T38"/>
     <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="F40:H40"/>
@@ -8770,6 +8773,7 @@
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="F46:H46"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="J49:L49"/>
     <mergeCell ref="B87:D87"/>
     <mergeCell ref="B88:D88"/>
     <mergeCell ref="B89:D89"/>
@@ -8792,7 +8796,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AB22:AB27 AJ22:AJ27 AF22:AF27 AN22:AN27 T22:T27 L22:L27 H22:H27 D22:D27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R46:T49 AH14:AJ16 AL22:AM27 V95:X96 AD77:AF78 R22:S27 V77:X78 J132:L133 AL71:AN72 AH48:AJ50 N77:P78 Z95:AB96 R71:T72 N95:P96 AD71:AF72 Z46:AB49 V22:W27 AD48:AF50 AL101:AN102 J14:L16 V8:X10 V46:X49 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 N46:P49 B108:D109 N54:P56 Z14:AB16 R54:T56 R14:T16 R101:T102 AL14:AN16 AH83:AJ84 R34:T35 V54:X56 AD41:AF43 R89:T90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X35 V101:X102 V61:X64 AL83:AN84 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 J95:L96 AL48:AN50 R61:T64 AH55:AJ57 J8:L10 N34:P35 Z54:AB56 R77:T78 AH22:AI27 N61:P64 AL41:AN43 B14:D16 J77:L78 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 R40:T41 AH34:AJ36 AH62:AJ64 Z101:AB102 AD55:AF57 Z77:AB78 Z83:AB84 N71:P72 V83:X84 Z34:AB35 Z22:AA27 AD83:AF84 Z61:AB64 AH71:AJ72 AH101:AJ102 Z40:AB41 AL77:AN78 AL62:AN64 Z8:AB10 V40:X41 AL8:AN10 N40:P41 N8:P10 AD62:AF64 Z71:AB72 AL95:AN96 AD34:AF36 F22:G27 R83:T84 V89:X90 AL34:AN36 N83:P84 F14:H16 B22:C27 J22:K27 F89:H90 F95:H96 V71:X72 AH41:AJ43 AL55:AN57 B89:D90 J101:L102 B95:D96 B8:D10 J89:L90 F8:H10 F101:H102 AH77:AJ78 B101:D102 N89:P90 J71:L72 J46:L49 B71:D72 B40:D41 F40:H41 F34:H35 J83:L84 F46:H49 J54:L56 J34:L35 J61:L64 B54:D56 B77:D78 J40:L41 F54:H56 F77:H78 B34:D35 F83:H84 B46:D49 F71:H72 B61:D64 F61:H64 B83:D84 N101:P102">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R46:T49 AH14:AJ16 AL22:AM27 V95:X96 AD77:AF78 R22:S27 V77:X78 J132:L133 AL71:AN72 N101:P102 N77:P78 Z95:AB96 R71:T72 N95:P96 AD71:AF72 Z46:AB49 V22:W27 AD48:AF50 AL101:AN102 J14:L16 V8:X10 V46:X49 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 N46:P49 B108:D109 N54:P56 Z14:AB16 R54:T56 R14:T16 R101:T102 AL14:AN16 AH83:AJ84 R34:T35 V54:X56 AD41:AF43 R89:T90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 V34:X35 V101:X102 V61:X64 AL83:AN84 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 J95:L96 AL48:AN50 R61:T64 AH55:AJ57 J8:L10 N34:P35 Z54:AB56 R77:T78 AH22:AI27 N61:P64 AL41:AN43 B14:D16 J77:L78 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 R40:T41 AD34:AF36 AH62:AJ64 Z101:AB102 AD55:AF57 Z77:AB78 Z83:AB84 N71:P72 V83:X84 Z34:AB35 Z22:AA27 AD83:AF84 Z61:AB64 AH71:AJ72 AH101:AJ102 Z40:AB41 AL77:AN78 AL62:AN64 Z8:AB10 V40:X41 AL8:AN10 N40:P41 N8:P10 AD62:AF64 Z71:AB72 AL95:AN96 AH48:AJ50 F22:G27 R83:T84 V89:X90 AL34:AN36 N83:P84 F14:H16 B22:C27 J22:K27 F89:H90 F95:H96 V71:X72 AH41:AJ43 AL55:AN57 B89:D90 J101:L102 B95:D96 B8:D10 J89:L90 F8:H10 F101:H102 AH77:AJ78 B101:D102 N89:P90 J71:L72 J46:L49 B71:D72 B40:D41 F40:H41 F34:H35 J83:L84 F46:H49 J54:L56 J34:L35 J61:L64 B54:D56 B77:D78 J40:L41 F54:H56 F77:H78 B34:D35 F83:H84 B46:D49 F71:H72 B61:D64 F61:H64 B83:D84 AH34:AJ36">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="90">
   <si>
     <t>CUMA</t>
   </si>
@@ -276,6 +276,24 @@
   </si>
   <si>
     <t>E.DÖNMEZ.</t>
+  </si>
+  <si>
+    <t>E.SAVAŞ.</t>
+  </si>
+  <si>
+    <t>İLETİŞİM BAŞKANI</t>
+  </si>
+  <si>
+    <t>Sultanahmet</t>
+  </si>
+  <si>
+    <t>16.00</t>
+  </si>
+  <si>
+    <t>Ç.TAŞ.</t>
+  </si>
+  <si>
+    <t>M.DİNER.</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1347,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1491,6 +1509,93 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1503,93 +1608,6 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1602,9 +1620,51 @@
     <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1683,46 +1743,31 @@
     <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2097,7 +2142,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="177" row="3" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2123,197 +2168,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" customWidth="1"/>
-    <col min="17" max="17" width="1.6640625" customWidth="1"/>
-    <col min="18" max="18" width="2.6640625" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="1.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" customWidth="1"/>
-    <col min="23" max="23" width="20.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="1.6640625" customWidth="1"/>
-    <col min="26" max="26" width="2.6640625" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" customWidth="1"/>
-    <col min="29" max="29" width="1.6640625" customWidth="1"/>
-    <col min="30" max="30" width="2.6640625" customWidth="1"/>
-    <col min="31" max="31" width="20.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.6640625" customWidth="1"/>
-    <col min="33" max="33" width="1.6640625" customWidth="1"/>
-    <col min="34" max="34" width="2.6640625" customWidth="1"/>
-    <col min="35" max="35" width="20.6640625" customWidth="1"/>
-    <col min="36" max="36" width="6.6640625" customWidth="1"/>
-    <col min="37" max="37" width="1.6640625" customWidth="1"/>
-    <col min="38" max="38" width="2.6640625" customWidth="1"/>
-    <col min="39" max="39" width="20.6640625" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" customWidth="1"/>
-    <col min="41" max="41" width="2.6640625" customWidth="1"/>
-    <col min="42" max="42" width="16.6640625" customWidth="1"/>
-    <col min="43" max="43" width="3.6640625" customWidth="1"/>
-    <col min="44" max="44" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="17" max="17" width="1.7109375" customWidth="1"/>
+    <col min="18" max="18" width="2.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="1.7109375" customWidth="1"/>
+    <col min="26" max="26" width="2.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" customWidth="1"/>
+    <col min="29" max="29" width="1.7109375" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" customWidth="1"/>
+    <col min="31" max="31" width="20.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.7109375" customWidth="1"/>
+    <col min="33" max="33" width="1.7109375" customWidth="1"/>
+    <col min="34" max="34" width="2.7109375" customWidth="1"/>
+    <col min="35" max="35" width="20.7109375" customWidth="1"/>
+    <col min="36" max="36" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="1.7109375" customWidth="1"/>
+    <col min="38" max="38" width="2.7109375" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="41" max="41" width="2.7109375" customWidth="1"/>
+    <col min="42" max="42" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="3.7109375" customWidth="1"/>
+    <col min="44" max="44" width="8.28515625" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="112" t="s">
+      <c r="B1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="113" t="s">
+      <c r="F1" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="113" t="s">
+      <c r="J1" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="113"/>
-      <c r="L1" s="114"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="128"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="117" t="s">
+      <c r="N1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="125"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="111" t="s">
+      <c r="R1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="111" t="s">
+      <c r="V1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="111" t="s">
+      <c r="Z1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="111" t="s">
+      <c r="AD1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="111"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="111" t="s">
+      <c r="AH1" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="111"/>
-      <c r="AJ1" s="111"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="111" t="s">
+      <c r="AL1" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="111"/>
-      <c r="AN1" s="121"/>
+      <c r="AM1" s="125"/>
+      <c r="AN1" s="135"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="115">
+      <c r="B2" s="129">
         <f>N2-3</f>
         <v>46213</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="116">
+      <c r="F2" s="130">
         <f>N2-2</f>
         <v>46214</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="116">
+      <c r="J2" s="130">
         <f>N2-1</f>
         <v>46215</v>
       </c>
-      <c r="K2" s="116"/>
-      <c r="L2" s="119"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="133"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="118">
+      <c r="N2" s="132">
         <v>46216</v>
       </c>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="107">
+      <c r="R2" s="121">
         <f>N2+1</f>
         <v>46217</v>
       </c>
-      <c r="S2" s="107"/>
-      <c r="T2" s="107"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="107">
+      <c r="V2" s="121">
         <f>N2+2</f>
         <v>46218</v>
       </c>
-      <c r="W2" s="107"/>
-      <c r="X2" s="107"/>
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="107">
+      <c r="Z2" s="121">
         <f>N2+3</f>
         <v>46219</v>
       </c>
-      <c r="AA2" s="107"/>
-      <c r="AB2" s="107"/>
+      <c r="AA2" s="121"/>
+      <c r="AB2" s="121"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="107">
+      <c r="AD2" s="121">
         <f>N2+4</f>
         <v>46220</v>
       </c>
-      <c r="AE2" s="107"/>
-      <c r="AF2" s="107"/>
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="121"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="107">
+      <c r="AH2" s="121">
         <f>N2+5</f>
         <v>46221</v>
       </c>
-      <c r="AI2" s="107"/>
-      <c r="AJ2" s="107"/>
+      <c r="AI2" s="121"/>
+      <c r="AJ2" s="121"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="107">
+      <c r="AL2" s="121">
         <f>N2+6</f>
         <v>46222</v>
       </c>
-      <c r="AM2" s="107"/>
-      <c r="AN2" s="122"/>
+      <c r="AM2" s="121"/>
+      <c r="AN2" s="136"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2359,139 +2404,139 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="100" t="s">
+      <c r="N4" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="100"/>
-      <c r="W4" s="100"/>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="109"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="109"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="109"/>
+      <c r="U4" s="109"/>
+      <c r="V4" s="109"/>
+      <c r="W4" s="109"/>
+      <c r="X4" s="109"/>
+      <c r="Y4" s="109"/>
+      <c r="Z4" s="109"/>
+      <c r="AA4" s="109"/>
+      <c r="AB4" s="109"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="120"/>
-      <c r="AE4" s="120"/>
-      <c r="AF4" s="120"/>
-      <c r="AG4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120"/>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
+      <c r="AD4" s="134"/>
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="134"/>
+      <c r="AG4" s="134"/>
+      <c r="AH4" s="134"/>
+      <c r="AI4" s="134"/>
+      <c r="AJ4" s="134"/>
+      <c r="AK4" s="134"/>
+      <c r="AL4" s="134"/>
+      <c r="AM4" s="134"/>
+      <c r="AN4" s="134"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="120"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="100"/>
-      <c r="U5" s="100"/>
-      <c r="V5" s="100"/>
-      <c r="W5" s="100"/>
-      <c r="X5" s="100"/>
-      <c r="Y5" s="100"/>
-      <c r="Z5" s="100"/>
-      <c r="AA5" s="100"/>
-      <c r="AB5" s="100"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="109"/>
+      <c r="T5" s="109"/>
+      <c r="U5" s="109"/>
+      <c r="V5" s="109"/>
+      <c r="W5" s="109"/>
+      <c r="X5" s="109"/>
+      <c r="Y5" s="109"/>
+      <c r="Z5" s="109"/>
+      <c r="AA5" s="109"/>
+      <c r="AB5" s="109"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="120"/>
-      <c r="AE5" s="120"/>
-      <c r="AF5" s="120"/>
-      <c r="AG5" s="120"/>
-      <c r="AH5" s="120"/>
-      <c r="AI5" s="120"/>
-      <c r="AJ5" s="120"/>
-      <c r="AK5" s="120"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="120"/>
-      <c r="AN5" s="120"/>
+      <c r="AD5" s="134"/>
+      <c r="AE5" s="134"/>
+      <c r="AF5" s="134"/>
+      <c r="AG5" s="134"/>
+      <c r="AH5" s="134"/>
+      <c r="AI5" s="134"/>
+      <c r="AJ5" s="134"/>
+      <c r="AK5" s="134"/>
+      <c r="AL5" s="134"/>
+      <c r="AM5" s="134"/>
+      <c r="AN5" s="134"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="71"/>
-      <c r="C6" s="72"/>
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
       <c r="D6" s="60"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="84"/>
       <c r="H6" s="60"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="84"/>
       <c r="L6" s="60"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="78"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="78"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="68"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="77"/>
-      <c r="W6" s="78"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="68"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="77"/>
-      <c r="AA6" s="78"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="68"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="77"/>
-      <c r="AE6" s="78"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="68"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="77"/>
-      <c r="AI6" s="78"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="68"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="77"/>
-      <c r="AM6" s="78"/>
+      <c r="AL6" s="67"/>
+      <c r="AM6" s="68"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2502,45 +2547,45 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="67"/>
-      <c r="C7" s="68"/>
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="68"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="81"/>
       <c r="H7" s="61"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="68"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="81"/>
       <c r="L7" s="61"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="64"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="93"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="64"/>
+      <c r="R7" s="92"/>
+      <c r="S7" s="93"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="63"/>
-      <c r="W7" s="64"/>
+      <c r="V7" s="92"/>
+      <c r="W7" s="93"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="63"/>
-      <c r="AA7" s="64"/>
+      <c r="Z7" s="92"/>
+      <c r="AA7" s="93"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="63"/>
-      <c r="AE7" s="64"/>
+      <c r="AD7" s="92"/>
+      <c r="AE7" s="93"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="63"/>
-      <c r="AI7" s="64"/>
+      <c r="AH7" s="92"/>
+      <c r="AI7" s="93"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="63"/>
-      <c r="AM7" s="64"/>
+      <c r="AL7" s="92"/>
+      <c r="AM7" s="93"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2551,95 +2596,95 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="89"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="91"/>
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="74"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="76"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="91"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="76"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="91"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="76"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="89"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="91"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="76"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="91"/>
+      <c r="R8" s="74"/>
+      <c r="S8" s="75"/>
+      <c r="T8" s="76"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="91"/>
+      <c r="V8" s="74"/>
+      <c r="W8" s="75"/>
+      <c r="X8" s="76"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="89"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="91"/>
+      <c r="Z8" s="74"/>
+      <c r="AA8" s="75"/>
+      <c r="AB8" s="76"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="91"/>
+      <c r="AD8" s="74"/>
+      <c r="AE8" s="75"/>
+      <c r="AF8" s="76"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="89"/>
-      <c r="AI8" s="90"/>
-      <c r="AJ8" s="91"/>
+      <c r="AH8" s="74"/>
+      <c r="AI8" s="75"/>
+      <c r="AJ8" s="76"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="89"/>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="91"/>
+      <c r="AL8" s="74"/>
+      <c r="AM8" s="75"/>
+      <c r="AN8" s="76"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
       <c r="AQ8" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR8" s="30"/>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="82"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="87"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="89"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="84"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="89"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="84"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="88"/>
+      <c r="L9" s="89"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="84"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="89"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="84"/>
+      <c r="R9" s="87"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="89"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="82"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="84"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="89"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="83"/>
-      <c r="AB9" s="84"/>
+      <c r="Z9" s="87"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="89"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="83"/>
-      <c r="AF9" s="84"/>
+      <c r="AD9" s="87"/>
+      <c r="AE9" s="88"/>
+      <c r="AF9" s="89"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="82"/>
-      <c r="AI9" s="83"/>
-      <c r="AJ9" s="84"/>
+      <c r="AH9" s="87"/>
+      <c r="AI9" s="88"/>
+      <c r="AJ9" s="89"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="82"/>
-      <c r="AM9" s="83"/>
-      <c r="AN9" s="84"/>
+      <c r="AL9" s="87"/>
+      <c r="AM9" s="88"/>
+      <c r="AN9" s="89"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2649,46 +2694,46 @@
       </c>
       <c r="AR9" s="30"/>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="108"/>
-      <c r="C10" s="109"/>
-      <c r="D10" s="110"/>
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="122"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="124"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="110"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="123"/>
+      <c r="H10" s="124"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="109"/>
-      <c r="L10" s="110"/>
+      <c r="J10" s="122"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="124"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="108"/>
-      <c r="O10" s="109"/>
-      <c r="P10" s="110"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="124"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="108"/>
-      <c r="S10" s="109"/>
-      <c r="T10" s="110"/>
+      <c r="R10" s="122"/>
+      <c r="S10" s="123"/>
+      <c r="T10" s="124"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="108"/>
-      <c r="W10" s="109"/>
-      <c r="X10" s="110"/>
+      <c r="V10" s="122"/>
+      <c r="W10" s="123"/>
+      <c r="X10" s="124"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="108"/>
-      <c r="AA10" s="109"/>
-      <c r="AB10" s="110"/>
+      <c r="Z10" s="122"/>
+      <c r="AA10" s="123"/>
+      <c r="AB10" s="124"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="108"/>
-      <c r="AE10" s="109"/>
-      <c r="AF10" s="110"/>
+      <c r="AD10" s="122"/>
+      <c r="AE10" s="123"/>
+      <c r="AF10" s="124"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="108"/>
-      <c r="AI10" s="109"/>
-      <c r="AJ10" s="110"/>
+      <c r="AH10" s="122"/>
+      <c r="AI10" s="123"/>
+      <c r="AJ10" s="124"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="108"/>
-      <c r="AM10" s="109"/>
-      <c r="AN10" s="110"/>
+      <c r="AL10" s="122"/>
+      <c r="AM10" s="123"/>
+      <c r="AN10" s="124"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2698,7 +2743,7 @@
       </c>
       <c r="AR10" s="30"/>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2747,45 +2792,45 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="71"/>
-      <c r="C12" s="72"/>
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="83"/>
+      <c r="C12" s="84"/>
       <c r="D12" s="60"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="72"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="84"/>
       <c r="H12" s="60"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="72"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="84"/>
       <c r="L12" s="60"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="78"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="68"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="78"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="68"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="77"/>
-      <c r="W12" s="78"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="68"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="77"/>
-      <c r="AA12" s="78"/>
+      <c r="Z12" s="67"/>
+      <c r="AA12" s="68"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="77"/>
-      <c r="AE12" s="78"/>
+      <c r="AD12" s="67"/>
+      <c r="AE12" s="68"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="77"/>
-      <c r="AI12" s="78"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="68"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="77"/>
-      <c r="AM12" s="78"/>
+      <c r="AL12" s="67"/>
+      <c r="AM12" s="68"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2796,18 +2841,18 @@
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="67"/>
-      <c r="C13" s="68"/>
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="81"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="73"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="81"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="73"/>
       <c r="M13" s="5"/>
       <c r="N13" s="96"/>
       <c r="O13" s="97"/>
@@ -2821,12 +2866,12 @@
       <c r="W13" s="97"/>
       <c r="X13" s="98"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="63"/>
-      <c r="AA13" s="64"/>
+      <c r="Z13" s="92"/>
+      <c r="AA13" s="93"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="63"/>
-      <c r="AE13" s="64"/>
+      <c r="AD13" s="92"/>
+      <c r="AE13" s="93"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
       <c r="AH13" s="96"/>
@@ -2847,46 +2892,46 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="76"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="91"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="76"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="91"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="75"/>
+      <c r="P14" s="76"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="91"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="75"/>
+      <c r="T14" s="76"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="89"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="91"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="75"/>
+      <c r="X14" s="76"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="89"/>
-      <c r="AA14" s="90"/>
-      <c r="AB14" s="91"/>
+      <c r="Z14" s="74"/>
+      <c r="AA14" s="75"/>
+      <c r="AB14" s="76"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="89"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="91"/>
+      <c r="AD14" s="74"/>
+      <c r="AE14" s="75"/>
+      <c r="AF14" s="76"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="89"/>
-      <c r="AI14" s="90"/>
-      <c r="AJ14" s="91"/>
+      <c r="AH14" s="74"/>
+      <c r="AI14" s="75"/>
+      <c r="AJ14" s="76"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="89"/>
-      <c r="AM14" s="90"/>
-      <c r="AN14" s="91"/>
+      <c r="AL14" s="74"/>
+      <c r="AM14" s="75"/>
+      <c r="AN14" s="76"/>
       <c r="AP14" s="62" t="s">
         <v>23</v>
       </c>
@@ -2898,95 +2943,95 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="82"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="84"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="87"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="84"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="89"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="84"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="89"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="84"/>
+      <c r="N15" s="87"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="89"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="82"/>
-      <c r="S15" s="83"/>
-      <c r="T15" s="84"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="89"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="82"/>
-      <c r="W15" s="83"/>
-      <c r="X15" s="84"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="89"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="82"/>
-      <c r="AA15" s="83"/>
-      <c r="AB15" s="84"/>
+      <c r="Z15" s="87"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="89"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="82"/>
-      <c r="AE15" s="83"/>
-      <c r="AF15" s="84"/>
+      <c r="AD15" s="87"/>
+      <c r="AE15" s="88"/>
+      <c r="AF15" s="89"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="82"/>
-      <c r="AI15" s="83"/>
-      <c r="AJ15" s="84"/>
+      <c r="AH15" s="87"/>
+      <c r="AI15" s="88"/>
+      <c r="AJ15" s="89"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="82"/>
-      <c r="AM15" s="83"/>
-      <c r="AN15" s="84"/>
+      <c r="AL15" s="87"/>
+      <c r="AM15" s="88"/>
+      <c r="AN15" s="89"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
       <c r="AQ15" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="108"/>
-      <c r="C16" s="109"/>
-      <c r="D16" s="110"/>
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="122"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="124"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="110"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="124"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="110"/>
+      <c r="J16" s="122"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="124"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="110"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="123"/>
+      <c r="P16" s="124"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="108"/>
-      <c r="S16" s="109"/>
-      <c r="T16" s="110"/>
+      <c r="R16" s="122"/>
+      <c r="S16" s="123"/>
+      <c r="T16" s="124"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="108"/>
-      <c r="W16" s="109"/>
-      <c r="X16" s="110"/>
+      <c r="V16" s="122"/>
+      <c r="W16" s="123"/>
+      <c r="X16" s="124"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="108"/>
-      <c r="AA16" s="109"/>
-      <c r="AB16" s="110"/>
+      <c r="Z16" s="122"/>
+      <c r="AA16" s="123"/>
+      <c r="AB16" s="124"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="108"/>
-      <c r="AE16" s="109"/>
-      <c r="AF16" s="110"/>
+      <c r="AD16" s="122"/>
+      <c r="AE16" s="123"/>
+      <c r="AF16" s="124"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="108"/>
-      <c r="AI16" s="109"/>
-      <c r="AJ16" s="110"/>
+      <c r="AH16" s="122"/>
+      <c r="AI16" s="123"/>
+      <c r="AJ16" s="124"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="108"/>
-      <c r="AM16" s="109"/>
-      <c r="AN16" s="110"/>
+      <c r="AL16" s="122"/>
+      <c r="AM16" s="123"/>
+      <c r="AN16" s="124"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -2996,7 +3041,7 @@
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3045,7 +3090,7 @@
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3058,23 +3103,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="100" t="s">
+      <c r="N18" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="100"/>
-      <c r="T18" s="100"/>
-      <c r="U18" s="100"/>
-      <c r="V18" s="100"/>
-      <c r="W18" s="100"/>
-      <c r="X18" s="100"/>
-      <c r="Y18" s="100"/>
-      <c r="Z18" s="100"/>
-      <c r="AA18" s="100"/>
-      <c r="AB18" s="100"/>
+      <c r="O18" s="109"/>
+      <c r="P18" s="109"/>
+      <c r="Q18" s="109"/>
+      <c r="R18" s="109"/>
+      <c r="S18" s="109"/>
+      <c r="T18" s="109"/>
+      <c r="U18" s="109"/>
+      <c r="V18" s="109"/>
+      <c r="W18" s="109"/>
+      <c r="X18" s="109"/>
+      <c r="Y18" s="109"/>
+      <c r="Z18" s="109"/>
+      <c r="AA18" s="109"/>
+      <c r="AB18" s="109"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3098,7 +3143,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3111,21 +3156,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="100"/>
-      <c r="T19" s="100"/>
-      <c r="U19" s="100"/>
-      <c r="V19" s="100"/>
-      <c r="W19" s="100"/>
-      <c r="X19" s="100"/>
-      <c r="Y19" s="100"/>
-      <c r="Z19" s="100"/>
-      <c r="AA19" s="100"/>
-      <c r="AB19" s="100"/>
+      <c r="N19" s="109"/>
+      <c r="O19" s="109"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="109"/>
+      <c r="S19" s="109"/>
+      <c r="T19" s="109"/>
+      <c r="U19" s="109"/>
+      <c r="V19" s="109"/>
+      <c r="W19" s="109"/>
+      <c r="X19" s="109"/>
+      <c r="Y19" s="109"/>
+      <c r="Z19" s="109"/>
+      <c r="AA19" s="109"/>
+      <c r="AB19" s="109"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3149,45 +3194,45 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="83"/>
+      <c r="C20" s="84"/>
       <c r="D20" s="60"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="72"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="84"/>
       <c r="H20" s="60"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="84"/>
       <c r="L20" s="60"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="77"/>
-      <c r="O20" s="78"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="68"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="126"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="140"/>
       <c r="T20" s="56"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="125"/>
-      <c r="W20" s="126"/>
+      <c r="V20" s="139"/>
+      <c r="W20" s="140"/>
       <c r="X20" s="56"/>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="125"/>
-      <c r="AA20" s="126"/>
+      <c r="Z20" s="139"/>
+      <c r="AA20" s="140"/>
       <c r="AB20" s="56"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="77"/>
-      <c r="AE20" s="78"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="68"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="77"/>
-      <c r="AI20" s="78"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="68"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="77"/>
-      <c r="AM20" s="78"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="68"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3198,45 +3243,45 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="67"/>
-      <c r="C21" s="68"/>
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="80"/>
+      <c r="C21" s="81"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="68"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="81"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="68"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="81"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="64"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="93"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="63"/>
-      <c r="S21" s="64"/>
+      <c r="R21" s="92"/>
+      <c r="S21" s="93"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="123"/>
-      <c r="W21" s="124"/>
+      <c r="V21" s="137"/>
+      <c r="W21" s="138"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="123"/>
-      <c r="AA21" s="124"/>
+      <c r="Z21" s="137"/>
+      <c r="AA21" s="138"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="63"/>
-      <c r="AE21" s="64"/>
+      <c r="AD21" s="92"/>
+      <c r="AE21" s="93"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="63"/>
-      <c r="AI21" s="64"/>
+      <c r="AH21" s="92"/>
+      <c r="AI21" s="93"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="63"/>
-      <c r="AM21" s="64"/>
+      <c r="AL21" s="92"/>
+      <c r="AM21" s="93"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="62" t="s">
         <v>12</v>
@@ -3249,45 +3294,45 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="85"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="93"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="86"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="93"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="86"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="66"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="95"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="66"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="95"/>
       <c r="T22" s="41"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="66"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="95"/>
       <c r="X22" s="58"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="66"/>
+      <c r="Z22" s="94"/>
+      <c r="AA22" s="95"/>
       <c r="AB22" s="58"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="92"/>
-      <c r="AE22" s="93"/>
+      <c r="AD22" s="85"/>
+      <c r="AE22" s="86"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="92"/>
-      <c r="AI22" s="93"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="86"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="65"/>
-      <c r="AM22" s="66"/>
+      <c r="AL22" s="94"/>
+      <c r="AM22" s="95"/>
       <c r="AN22" s="41"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
@@ -3298,45 +3343,45 @@
       </c>
       <c r="AR22" s="30"/>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="75"/>
-      <c r="C23" s="76"/>
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="69"/>
+      <c r="C23" s="70"/>
       <c r="D23" s="45"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="76"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="70"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="76"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="70"/>
       <c r="L23" s="45"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="75"/>
-      <c r="O23" s="76"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="70"/>
       <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="75"/>
-      <c r="S23" s="76"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="70"/>
       <c r="T23" s="45"/>
       <c r="U23" s="43"/>
-      <c r="V23" s="75"/>
-      <c r="W23" s="76"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="70"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="75"/>
-      <c r="AA23" s="76"/>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="70"/>
       <c r="AB23" s="45"/>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="75"/>
-      <c r="AE23" s="76"/>
+      <c r="AD23" s="69"/>
+      <c r="AE23" s="70"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="75"/>
-      <c r="AI23" s="76"/>
+      <c r="AH23" s="69"/>
+      <c r="AI23" s="70"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="75"/>
-      <c r="AM23" s="76"/>
+      <c r="AL23" s="69"/>
+      <c r="AM23" s="70"/>
       <c r="AN23" s="45"/>
       <c r="AP23" s="46" t="s">
         <v>20</v>
@@ -3347,45 +3392,45 @@
       </c>
       <c r="AR23" s="30"/>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="69"/>
-      <c r="C24" s="70"/>
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="63"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="70"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="64"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="70"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="64"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="70"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="64"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="70"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="64"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="70"/>
+      <c r="Z24" s="63"/>
+      <c r="AA24" s="64"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="69"/>
-      <c r="AE24" s="70"/>
+      <c r="AD24" s="63"/>
+      <c r="AE24" s="64"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="69"/>
-      <c r="AI24" s="70"/>
+      <c r="AH24" s="63"/>
+      <c r="AI24" s="64"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="69"/>
-      <c r="AM24" s="70"/>
+      <c r="AL24" s="63"/>
+      <c r="AM24" s="64"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
@@ -3396,45 +3441,45 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="69"/>
-      <c r="C25" s="70"/>
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="63"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="64"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="70"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="64"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="70"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="64"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="70"/>
+      <c r="R25" s="63"/>
+      <c r="S25" s="64"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="70"/>
+      <c r="V25" s="63"/>
+      <c r="W25" s="64"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="70"/>
+      <c r="Z25" s="63"/>
+      <c r="AA25" s="64"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="69"/>
-      <c r="AE25" s="70"/>
+      <c r="AD25" s="63"/>
+      <c r="AE25" s="64"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="69"/>
-      <c r="AI25" s="70"/>
+      <c r="AH25" s="63"/>
+      <c r="AI25" s="64"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="69"/>
-      <c r="AM25" s="70"/>
+      <c r="AL25" s="63"/>
+      <c r="AM25" s="64"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="46" t="s">
         <v>21</v>
@@ -3445,45 +3490,45 @@
       </c>
       <c r="AR25" s="30"/>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="69"/>
-      <c r="C26" s="70"/>
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="63"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="64"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="70"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="64"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="70"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="64"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="70"/>
+      <c r="R26" s="63"/>
+      <c r="S26" s="64"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="69"/>
-      <c r="W26" s="70"/>
+      <c r="V26" s="63"/>
+      <c r="W26" s="64"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="69"/>
-      <c r="AA26" s="70"/>
+      <c r="Z26" s="63"/>
+      <c r="AA26" s="64"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="69"/>
-      <c r="AE26" s="70"/>
+      <c r="AD26" s="63"/>
+      <c r="AE26" s="64"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="69"/>
-      <c r="AI26" s="70"/>
+      <c r="AH26" s="63"/>
+      <c r="AI26" s="64"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="69"/>
-      <c r="AM26" s="70"/>
+      <c r="AL26" s="63"/>
+      <c r="AM26" s="64"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
@@ -3494,56 +3539,56 @@
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="73"/>
-      <c r="C27" s="74"/>
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="65"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="66"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="73"/>
-      <c r="K27" s="74"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="66"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="73"/>
-      <c r="O27" s="74"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="66"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="73"/>
-      <c r="S27" s="74"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="66"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="73"/>
-      <c r="W27" s="74"/>
+      <c r="V27" s="65"/>
+      <c r="W27" s="66"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="73"/>
-      <c r="AA27" s="74"/>
+      <c r="Z27" s="65"/>
+      <c r="AA27" s="66"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="73"/>
-      <c r="AE27" s="74"/>
+      <c r="AD27" s="65"/>
+      <c r="AE27" s="66"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="73"/>
-      <c r="AI27" s="74"/>
+      <c r="AH27" s="65"/>
+      <c r="AI27" s="66"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="73"/>
-      <c r="AM27" s="74"/>
+      <c r="AL27" s="65"/>
+      <c r="AM27" s="66"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
       </c>
       <c r="AQ27" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
@@ -3592,7 +3637,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
@@ -3605,23 +3650,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="100" t="s">
+      <c r="N29" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="100"/>
-      <c r="P29" s="100"/>
-      <c r="Q29" s="100"/>
-      <c r="R29" s="100"/>
-      <c r="S29" s="100"/>
-      <c r="T29" s="100"/>
-      <c r="U29" s="100"/>
-      <c r="V29" s="100"/>
-      <c r="W29" s="100"/>
-      <c r="X29" s="100"/>
-      <c r="Y29" s="100"/>
-      <c r="Z29" s="100"/>
-      <c r="AA29" s="100"/>
-      <c r="AB29" s="100"/>
+      <c r="O29" s="109"/>
+      <c r="P29" s="109"/>
+      <c r="Q29" s="109"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="109"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="109"/>
+      <c r="Y29" s="109"/>
+      <c r="Z29" s="109"/>
+      <c r="AA29" s="109"/>
+      <c r="AB29" s="109"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3645,7 +3690,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
@@ -3658,21 +3703,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="100"/>
-      <c r="Q30" s="100"/>
-      <c r="R30" s="100"/>
-      <c r="S30" s="100"/>
-      <c r="T30" s="100"/>
-      <c r="U30" s="100"/>
-      <c r="V30" s="100"/>
-      <c r="W30" s="100"/>
-      <c r="X30" s="100"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="100"/>
-      <c r="AA30" s="100"/>
-      <c r="AB30" s="100"/>
+      <c r="N30" s="109"/>
+      <c r="O30" s="109"/>
+      <c r="P30" s="109"/>
+      <c r="Q30" s="109"/>
+      <c r="R30" s="109"/>
+      <c r="S30" s="109"/>
+      <c r="T30" s="109"/>
+      <c r="U30" s="109"/>
+      <c r="V30" s="109"/>
+      <c r="W30" s="109"/>
+      <c r="X30" s="109"/>
+      <c r="Y30" s="109"/>
+      <c r="Z30" s="109"/>
+      <c r="AA30" s="109"/>
+      <c r="AB30" s="109"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3690,75 +3735,75 @@
       </c>
       <c r="AQ30" s="47">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR30" s="30" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="71" t="s">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="72"/>
+      <c r="C31" s="84"/>
       <c r="D31" s="60"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="71" t="s">
+      <c r="F31" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="G31" s="72"/>
+      <c r="G31" s="84"/>
       <c r="H31" s="60" t="s">
         <v>66</v>
       </c>
       <c r="I31" s="36"/>
-      <c r="J31" s="71" t="s">
+      <c r="J31" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="72"/>
+      <c r="K31" s="84"/>
       <c r="L31" s="60"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="77" t="s">
+      <c r="N31" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="O31" s="78"/>
+      <c r="O31" s="68"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="77" t="s">
+      <c r="R31" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="S31" s="78"/>
+      <c r="S31" s="68"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="77" t="s">
+      <c r="V31" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="W31" s="78"/>
+      <c r="W31" s="68"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="77" t="s">
+      <c r="Z31" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="AA31" s="78"/>
+      <c r="AA31" s="68"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="77" t="s">
+      <c r="AD31" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="AE31" s="78"/>
+      <c r="AE31" s="68"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="77" t="s">
+      <c r="AH31" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="AI31" s="78"/>
+      <c r="AI31" s="68"/>
       <c r="AJ31" s="34" t="s">
         <v>42</v>
       </c>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="77" t="s">
+      <c r="AL31" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="AM31" s="78"/>
+      <c r="AM31" s="68"/>
       <c r="AN31" s="34" t="s">
         <v>56</v>
       </c>
@@ -3766,24 +3811,24 @@
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="79" t="s">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="80"/>
-      <c r="D32" s="81"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="73"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="79" t="s">
+      <c r="F32" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="80"/>
-      <c r="H32" s="81"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="73"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="79" t="s">
+      <c r="J32" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="80"/>
-      <c r="L32" s="81"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="73"/>
       <c r="M32" s="5"/>
       <c r="N32" s="96" t="s">
         <v>46</v>
@@ -3830,242 +3875,242 @@
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="67" t="s">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="88"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="82"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="88"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="82"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="67" t="s">
+      <c r="J33" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="K33" s="68"/>
-      <c r="L33" s="88"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="82"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="63"/>
-      <c r="O33" s="64"/>
+      <c r="N33" s="92"/>
+      <c r="O33" s="93"/>
       <c r="P33" s="99"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="63"/>
-      <c r="S33" s="64"/>
+      <c r="R33" s="92"/>
+      <c r="S33" s="93"/>
       <c r="T33" s="99"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="63"/>
-      <c r="W33" s="64"/>
+      <c r="V33" s="92"/>
+      <c r="W33" s="93"/>
       <c r="X33" s="99"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="63"/>
-      <c r="AA33" s="64"/>
+      <c r="Z33" s="92"/>
+      <c r="AA33" s="93"/>
       <c r="AB33" s="99"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="63"/>
-      <c r="AE33" s="64"/>
+      <c r="AD33" s="92"/>
+      <c r="AE33" s="93"/>
       <c r="AF33" s="99"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="63"/>
-      <c r="AI33" s="64"/>
+      <c r="AH33" s="92"/>
+      <c r="AI33" s="93"/>
       <c r="AJ33" s="99"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="63"/>
-      <c r="AM33" s="64"/>
+      <c r="AL33" s="92"/>
+      <c r="AM33" s="93"/>
       <c r="AN33" s="99"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="90"/>
-      <c r="D34" s="91"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="76"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="89" t="s">
+      <c r="F34" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="76"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="89" t="s">
+      <c r="J34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="90"/>
-      <c r="L34" s="91"/>
+      <c r="K34" s="75"/>
+      <c r="L34" s="76"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="89" t="s">
+      <c r="N34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="O34" s="90"/>
-      <c r="P34" s="91"/>
+      <c r="O34" s="75"/>
+      <c r="P34" s="76"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="89" t="s">
+      <c r="R34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="S34" s="90"/>
-      <c r="T34" s="91"/>
+      <c r="S34" s="75"/>
+      <c r="T34" s="76"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="89" t="s">
+      <c r="V34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="W34" s="90"/>
-      <c r="X34" s="91"/>
+      <c r="W34" s="75"/>
+      <c r="X34" s="76"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="89" t="s">
+      <c r="Z34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="AA34" s="90"/>
-      <c r="AB34" s="91"/>
+      <c r="AA34" s="75"/>
+      <c r="AB34" s="76"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="89" t="s">
+      <c r="AD34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="AE34" s="90"/>
-      <c r="AF34" s="91"/>
+      <c r="AE34" s="75"/>
+      <c r="AF34" s="76"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="89" t="s">
+      <c r="AH34" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="AI34" s="90"/>
-      <c r="AJ34" s="91"/>
+      <c r="AI34" s="75"/>
+      <c r="AJ34" s="76"/>
       <c r="AK34" s="35"/>
-      <c r="AL34" s="89" t="s">
+      <c r="AL34" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="AM34" s="90"/>
-      <c r="AN34" s="91"/>
+      <c r="AM34" s="75"/>
+      <c r="AN34" s="76"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="83"/>
-      <c r="D35" s="84"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="89"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="82" t="s">
+      <c r="F35" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="83"/>
-      <c r="H35" s="84"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="89"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="82" t="s">
+      <c r="J35" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="83"/>
-      <c r="L35" s="84"/>
+      <c r="K35" s="88"/>
+      <c r="L35" s="89"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="82" t="s">
+      <c r="N35" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="O35" s="83"/>
-      <c r="P35" s="84"/>
+      <c r="O35" s="88"/>
+      <c r="P35" s="89"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="82" t="s">
+      <c r="R35" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="S35" s="83"/>
-      <c r="T35" s="84"/>
+      <c r="S35" s="88"/>
+      <c r="T35" s="89"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="82" t="s">
+      <c r="V35" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="W35" s="83"/>
-      <c r="X35" s="84"/>
+      <c r="W35" s="88"/>
+      <c r="X35" s="89"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="82" t="s">
+      <c r="Z35" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="AA35" s="83"/>
-      <c r="AB35" s="84"/>
+      <c r="AA35" s="88"/>
+      <c r="AB35" s="89"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="82" t="s">
+      <c r="AD35" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="AE35" s="83"/>
-      <c r="AF35" s="84"/>
+      <c r="AE35" s="88"/>
+      <c r="AF35" s="89"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="82" t="s">
+      <c r="AH35" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="AI35" s="83"/>
-      <c r="AJ35" s="84"/>
+      <c r="AI35" s="88"/>
+      <c r="AJ35" s="89"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="82" t="s">
+      <c r="AL35" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="AM35" s="83"/>
-      <c r="AN35" s="84"/>
+      <c r="AM35" s="88"/>
+      <c r="AN35" s="89"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="87"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="79"/>
       <c r="E36" s="35"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="86"/>
-      <c r="H36" s="87"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="79"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="85" t="s">
+      <c r="J36" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="86"/>
-      <c r="L36" s="87"/>
+      <c r="K36" s="78"/>
+      <c r="L36" s="79"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="85" t="s">
+      <c r="N36" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="O36" s="86"/>
-      <c r="P36" s="87"/>
+      <c r="O36" s="78"/>
+      <c r="P36" s="79"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="85" t="s">
+      <c r="R36" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="S36" s="86"/>
-      <c r="T36" s="87"/>
+      <c r="S36" s="78"/>
+      <c r="T36" s="79"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="85" t="s">
+      <c r="V36" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="W36" s="86"/>
-      <c r="X36" s="87"/>
+      <c r="W36" s="78"/>
+      <c r="X36" s="79"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="85" t="s">
+      <c r="Z36" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="AA36" s="86"/>
-      <c r="AB36" s="87"/>
+      <c r="AA36" s="78"/>
+      <c r="AB36" s="79"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="85" t="s">
+      <c r="AD36" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="AE36" s="86"/>
-      <c r="AF36" s="87"/>
+      <c r="AE36" s="78"/>
+      <c r="AF36" s="79"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="85"/>
-      <c r="AI36" s="86"/>
-      <c r="AJ36" s="87"/>
+      <c r="AH36" s="77"/>
+      <c r="AI36" s="78"/>
+      <c r="AJ36" s="79"/>
       <c r="AK36" s="35"/>
-      <c r="AL36" s="85"/>
-      <c r="AM36" s="86"/>
-      <c r="AN36" s="87"/>
+      <c r="AL36" s="77"/>
+      <c r="AM36" s="78"/>
+      <c r="AN36" s="79"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>
       <c r="B37" s="35"/>
       <c r="C37" s="35"/>
@@ -4111,82 +4156,82 @@
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="94" t="s">
+      <c r="B38" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="95"/>
+      <c r="C38" s="91"/>
       <c r="D38" s="55" t="s">
         <v>68</v>
       </c>
       <c r="E38" s="36"/>
-      <c r="F38" s="71" t="s">
+      <c r="F38" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="G38" s="72"/>
+      <c r="G38" s="84"/>
       <c r="H38" s="60"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="71" t="s">
+      <c r="J38" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="K38" s="72"/>
+      <c r="K38" s="84"/>
       <c r="L38" s="60" t="s">
         <v>68</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="77" t="s">
+      <c r="N38" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="O38" s="78"/>
+      <c r="O38" s="68"/>
       <c r="P38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="Q38" s="36"/>
-      <c r="R38" s="77" t="s">
+      <c r="R38" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="S38" s="78"/>
+      <c r="S38" s="68"/>
       <c r="T38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="U38" s="32"/>
-      <c r="V38" s="77" t="s">
+      <c r="V38" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="W38" s="78"/>
+      <c r="W38" s="68"/>
       <c r="X38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="77" t="s">
+      <c r="Z38" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="AA38" s="78"/>
+      <c r="AA38" s="68"/>
       <c r="AB38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="77" t="s">
+      <c r="AD38" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="AE38" s="78"/>
+      <c r="AE38" s="68"/>
       <c r="AF38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="77" t="s">
+      <c r="AH38" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="AI38" s="78"/>
+      <c r="AI38" s="68"/>
       <c r="AJ38" s="34" t="s">
         <v>56</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="77" t="s">
+      <c r="AL38" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="AM38" s="78"/>
+      <c r="AM38" s="68"/>
       <c r="AN38" s="34" t="s">
         <v>43</v>
       </c>
@@ -4195,25 +4240,25 @@
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="79" t="s">
+      <c r="B39" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="80"/>
-      <c r="D39" s="81"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="73"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="79" t="s">
+      <c r="F39" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="G39" s="80"/>
-      <c r="H39" s="81"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="73"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="79" t="s">
+      <c r="J39" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="K39" s="80"/>
-      <c r="L39" s="81"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="73"/>
       <c r="M39" s="5"/>
       <c r="N39" s="96" t="s">
         <v>58</v>
@@ -4261,241 +4306,241 @@
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="88"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="82"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="67" t="s">
+      <c r="F40" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="G40" s="68"/>
-      <c r="H40" s="88"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="82"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="88"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="82"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="63"/>
-      <c r="O40" s="64"/>
+      <c r="N40" s="92"/>
+      <c r="O40" s="93"/>
       <c r="P40" s="99"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="63"/>
-      <c r="S40" s="64"/>
+      <c r="R40" s="92"/>
+      <c r="S40" s="93"/>
       <c r="T40" s="99"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="63"/>
-      <c r="W40" s="64"/>
+      <c r="V40" s="92"/>
+      <c r="W40" s="93"/>
       <c r="X40" s="99"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="63"/>
-      <c r="AA40" s="64"/>
+      <c r="Z40" s="92"/>
+      <c r="AA40" s="93"/>
       <c r="AB40" s="99"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="63"/>
-      <c r="AE40" s="64"/>
+      <c r="AD40" s="92"/>
+      <c r="AE40" s="93"/>
       <c r="AF40" s="99"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="63"/>
-      <c r="AI40" s="64"/>
+      <c r="AH40" s="92"/>
+      <c r="AI40" s="93"/>
       <c r="AJ40" s="99"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="63"/>
-      <c r="AM40" s="64"/>
+      <c r="AL40" s="92"/>
+      <c r="AM40" s="93"/>
       <c r="AN40" s="99"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="89" t="s">
+      <c r="B41" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="91"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="76"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="89" t="s">
+      <c r="F41" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="G41" s="90"/>
-      <c r="H41" s="91"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="76"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="89" t="s">
+      <c r="J41" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="90"/>
-      <c r="L41" s="91"/>
+      <c r="K41" s="75"/>
+      <c r="L41" s="76"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="89" t="s">
+      <c r="N41" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="O41" s="90"/>
-      <c r="P41" s="91"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="76"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="89" t="s">
+      <c r="R41" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="S41" s="90"/>
-      <c r="T41" s="91"/>
+      <c r="S41" s="75"/>
+      <c r="T41" s="76"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="89" t="s">
+      <c r="V41" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="W41" s="90"/>
-      <c r="X41" s="91"/>
+      <c r="W41" s="75"/>
+      <c r="X41" s="76"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="89" t="s">
+      <c r="Z41" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="90"/>
-      <c r="AB41" s="91"/>
+      <c r="AA41" s="75"/>
+      <c r="AB41" s="76"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="89" t="s">
+      <c r="AD41" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="AE41" s="90"/>
-      <c r="AF41" s="91"/>
+      <c r="AE41" s="75"/>
+      <c r="AF41" s="76"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="89" t="s">
+      <c r="AH41" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="AI41" s="90"/>
-      <c r="AJ41" s="91"/>
+      <c r="AI41" s="75"/>
+      <c r="AJ41" s="76"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="89" t="s">
+      <c r="AL41" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="AM41" s="90"/>
-      <c r="AN41" s="91"/>
+      <c r="AM41" s="75"/>
+      <c r="AN41" s="76"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="82" t="s">
+      <c r="B42" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="83"/>
-      <c r="D42" s="84"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="89"/>
       <c r="E42" s="35"/>
-      <c r="F42" s="82" t="s">
+      <c r="F42" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="G42" s="83"/>
-      <c r="H42" s="84"/>
+      <c r="G42" s="88"/>
+      <c r="H42" s="89"/>
       <c r="I42" s="35"/>
-      <c r="J42" s="82" t="s">
+      <c r="J42" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="K42" s="83"/>
-      <c r="L42" s="84"/>
+      <c r="K42" s="88"/>
+      <c r="L42" s="89"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="82" t="s">
+      <c r="N42" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="O42" s="83"/>
-      <c r="P42" s="84"/>
+      <c r="O42" s="88"/>
+      <c r="P42" s="89"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="82" t="s">
+      <c r="R42" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="S42" s="83"/>
-      <c r="T42" s="84"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="89"/>
       <c r="U42" s="44"/>
-      <c r="V42" s="82" t="s">
+      <c r="V42" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="W42" s="83"/>
-      <c r="X42" s="84"/>
+      <c r="W42" s="88"/>
+      <c r="X42" s="89"/>
       <c r="Y42" s="44"/>
-      <c r="Z42" s="82" t="s">
+      <c r="Z42" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="AA42" s="83"/>
-      <c r="AB42" s="84"/>
+      <c r="AA42" s="88"/>
+      <c r="AB42" s="89"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="82" t="s">
+      <c r="AD42" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="AE42" s="83"/>
-      <c r="AF42" s="84"/>
+      <c r="AE42" s="88"/>
+      <c r="AF42" s="89"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="82" t="s">
+      <c r="AH42" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="AI42" s="83"/>
-      <c r="AJ42" s="84"/>
+      <c r="AI42" s="88"/>
+      <c r="AJ42" s="89"/>
       <c r="AK42" s="35"/>
-      <c r="AL42" s="82" t="s">
+      <c r="AL42" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="AM42" s="83"/>
-      <c r="AN42" s="84"/>
+      <c r="AM42" s="88"/>
+      <c r="AN42" s="89"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="87"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="79"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="85" t="s">
+      <c r="F43" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="G43" s="86"/>
-      <c r="H43" s="87"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="79"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="85" t="s">
+      <c r="J43" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="K43" s="86"/>
-      <c r="L43" s="87"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="79"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="86"/>
-      <c r="P43" s="87"/>
+      <c r="N43" s="77"/>
+      <c r="O43" s="78"/>
+      <c r="P43" s="79"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="85"/>
-      <c r="S43" s="86"/>
-      <c r="T43" s="87"/>
+      <c r="R43" s="77"/>
+      <c r="S43" s="78"/>
+      <c r="T43" s="79"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="85"/>
-      <c r="W43" s="86"/>
-      <c r="X43" s="87"/>
+      <c r="V43" s="77"/>
+      <c r="W43" s="78"/>
+      <c r="X43" s="79"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="85"/>
-      <c r="AA43" s="86"/>
-      <c r="AB43" s="87"/>
+      <c r="Z43" s="77"/>
+      <c r="AA43" s="78"/>
+      <c r="AB43" s="79"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="85"/>
-      <c r="AE43" s="86"/>
-      <c r="AF43" s="87"/>
+      <c r="AD43" s="77"/>
+      <c r="AE43" s="78"/>
+      <c r="AF43" s="79"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="85" t="s">
+      <c r="AH43" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="AI43" s="86"/>
-      <c r="AJ43" s="87"/>
+      <c r="AI43" s="78"/>
+      <c r="AJ43" s="79"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="85" t="s">
+      <c r="AL43" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="AM43" s="86"/>
-      <c r="AN43" s="87"/>
+      <c r="AM43" s="78"/>
+      <c r="AN43" s="79"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35"/>
@@ -4541,79 +4586,79 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="71"/>
-      <c r="C45" s="72"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="84"/>
       <c r="D45" s="60"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="71"/>
-      <c r="G45" s="72"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="84"/>
       <c r="H45" s="60"/>
       <c r="I45" s="50"/>
-      <c r="J45" s="71" t="s">
+      <c r="J45" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="K45" s="72"/>
+      <c r="K45" s="84"/>
       <c r="L45" s="55" t="s">
         <v>77</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="77"/>
-      <c r="O45" s="78"/>
+      <c r="N45" s="67"/>
+      <c r="O45" s="68"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="77" t="s">
+      <c r="R45" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="S45" s="78"/>
+      <c r="S45" s="68"/>
       <c r="T45" s="34" t="s">
         <v>42</v>
       </c>
       <c r="U45" s="36"/>
-      <c r="V45" s="77" t="s">
+      <c r="V45" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="W45" s="78"/>
+      <c r="W45" s="68"/>
       <c r="X45" s="34" t="s">
         <v>69</v>
       </c>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="77"/>
-      <c r="AA45" s="78"/>
+      <c r="Z45" s="67"/>
+      <c r="AA45" s="68"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="77"/>
-      <c r="AE45" s="78"/>
+      <c r="AD45" s="67"/>
+      <c r="AE45" s="68"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="77"/>
-      <c r="AI45" s="78"/>
+      <c r="AH45" s="67"/>
+      <c r="AI45" s="68"/>
       <c r="AJ45" s="34"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="77"/>
-      <c r="AM45" s="78"/>
+      <c r="AL45" s="67"/>
+      <c r="AM45" s="68"/>
       <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="79"/>
-      <c r="C46" s="80"/>
-      <c r="D46" s="81"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="73"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="79"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="81"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="72"/>
+      <c r="H46" s="73"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="79" t="s">
+      <c r="J46" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="K46" s="80"/>
-      <c r="L46" s="81"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="73"/>
       <c r="M46" s="4"/>
       <c r="N46" s="96"/>
       <c r="O46" s="97"/>
@@ -4651,203 +4696,203 @@
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="67"/>
-      <c r="C47" s="68"/>
-      <c r="D47" s="88"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="81"/>
+      <c r="D47" s="82"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="88"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="82"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="88"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="82"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="63"/>
-      <c r="O47" s="64"/>
+      <c r="N47" s="92"/>
+      <c r="O47" s="93"/>
       <c r="P47" s="99"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="63"/>
-      <c r="S47" s="64"/>
+      <c r="R47" s="92"/>
+      <c r="S47" s="93"/>
       <c r="T47" s="99"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="63" t="s">
+      <c r="V47" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="W47" s="64"/>
+      <c r="W47" s="93"/>
       <c r="X47" s="99"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="63"/>
-      <c r="AA47" s="64"/>
+      <c r="Z47" s="92"/>
+      <c r="AA47" s="93"/>
       <c r="AB47" s="99"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="63"/>
-      <c r="AE47" s="64"/>
+      <c r="AD47" s="92"/>
+      <c r="AE47" s="93"/>
       <c r="AF47" s="99"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="63"/>
-      <c r="AI47" s="64"/>
+      <c r="AH47" s="92"/>
+      <c r="AI47" s="93"/>
       <c r="AJ47" s="99"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="63"/>
-      <c r="AM47" s="64"/>
+      <c r="AL47" s="92"/>
+      <c r="AM47" s="93"/>
       <c r="AN47" s="99"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="82"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="84"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="89"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="82"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="84"/>
+      <c r="F48" s="87"/>
+      <c r="G48" s="88"/>
+      <c r="H48" s="89"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="89" t="s">
+      <c r="J48" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="K48" s="90"/>
-      <c r="L48" s="91"/>
+      <c r="K48" s="75"/>
+      <c r="L48" s="76"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="82"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="84"/>
+      <c r="N48" s="87"/>
+      <c r="O48" s="88"/>
+      <c r="P48" s="89"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="89" t="s">
+      <c r="R48" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="S48" s="90"/>
-      <c r="T48" s="91"/>
+      <c r="S48" s="75"/>
+      <c r="T48" s="76"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="89" t="s">
+      <c r="V48" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="W48" s="90"/>
-      <c r="X48" s="91"/>
+      <c r="W48" s="75"/>
+      <c r="X48" s="76"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="82"/>
-      <c r="AA48" s="83"/>
-      <c r="AB48" s="84"/>
+      <c r="Z48" s="87"/>
+      <c r="AA48" s="88"/>
+      <c r="AB48" s="89"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="82"/>
-      <c r="AE48" s="83"/>
-      <c r="AF48" s="84"/>
+      <c r="AD48" s="87"/>
+      <c r="AE48" s="88"/>
+      <c r="AF48" s="89"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="82"/>
-      <c r="AI48" s="83"/>
-      <c r="AJ48" s="84"/>
+      <c r="AH48" s="87"/>
+      <c r="AI48" s="88"/>
+      <c r="AJ48" s="89"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="82"/>
-      <c r="AM48" s="83"/>
-      <c r="AN48" s="84"/>
+      <c r="AL48" s="87"/>
+      <c r="AM48" s="88"/>
+      <c r="AN48" s="89"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="82"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="84"/>
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="87"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="89"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="82"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="84"/>
+      <c r="F49" s="87"/>
+      <c r="G49" s="88"/>
+      <c r="H49" s="89"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="82" t="s">
+      <c r="J49" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="K49" s="83"/>
-      <c r="L49" s="84"/>
+      <c r="K49" s="88"/>
+      <c r="L49" s="89"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="82"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="84"/>
+      <c r="N49" s="87"/>
+      <c r="O49" s="88"/>
+      <c r="P49" s="89"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="82" t="s">
+      <c r="R49" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="S49" s="83"/>
-      <c r="T49" s="84"/>
+      <c r="S49" s="88"/>
+      <c r="T49" s="89"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="82" t="s">
+      <c r="V49" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="W49" s="83"/>
-      <c r="X49" s="84"/>
+      <c r="W49" s="88"/>
+      <c r="X49" s="89"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="82"/>
-      <c r="AA49" s="83"/>
-      <c r="AB49" s="84"/>
+      <c r="Z49" s="87"/>
+      <c r="AA49" s="88"/>
+      <c r="AB49" s="89"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="82"/>
-      <c r="AE49" s="83"/>
-      <c r="AF49" s="84"/>
+      <c r="AD49" s="87"/>
+      <c r="AE49" s="88"/>
+      <c r="AF49" s="89"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="82"/>
-      <c r="AI49" s="83"/>
-      <c r="AJ49" s="84"/>
+      <c r="AH49" s="87"/>
+      <c r="AI49" s="88"/>
+      <c r="AJ49" s="89"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="82"/>
-      <c r="AM49" s="83"/>
-      <c r="AN49" s="84"/>
+      <c r="AL49" s="87"/>
+      <c r="AM49" s="88"/>
+      <c r="AN49" s="89"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="85"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="87"/>
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="77"/>
+      <c r="C50" s="78"/>
+      <c r="D50" s="79"/>
       <c r="E50" s="35"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="87"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="78"/>
+      <c r="H50" s="79"/>
       <c r="I50" s="35"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="86"/>
-      <c r="L50" s="87"/>
+      <c r="J50" s="77"/>
+      <c r="K50" s="78"/>
+      <c r="L50" s="79"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="85"/>
-      <c r="O50" s="86"/>
-      <c r="P50" s="87"/>
+      <c r="N50" s="77"/>
+      <c r="O50" s="78"/>
+      <c r="P50" s="79"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="85"/>
-      <c r="S50" s="86"/>
-      <c r="T50" s="87"/>
+      <c r="R50" s="77"/>
+      <c r="S50" s="78"/>
+      <c r="T50" s="79"/>
       <c r="U50" s="35"/>
-      <c r="V50" s="85"/>
-      <c r="W50" s="86"/>
-      <c r="X50" s="87"/>
+      <c r="V50" s="77"/>
+      <c r="W50" s="78"/>
+      <c r="X50" s="79"/>
       <c r="Y50" s="35"/>
-      <c r="Z50" s="85"/>
-      <c r="AA50" s="86"/>
-      <c r="AB50" s="87"/>
+      <c r="Z50" s="77"/>
+      <c r="AA50" s="78"/>
+      <c r="AB50" s="79"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="85"/>
-      <c r="AE50" s="86"/>
-      <c r="AF50" s="87"/>
+      <c r="AD50" s="77"/>
+      <c r="AE50" s="78"/>
+      <c r="AF50" s="79"/>
       <c r="AG50" s="35"/>
-      <c r="AH50" s="85"/>
-      <c r="AI50" s="86"/>
-      <c r="AJ50" s="87"/>
+      <c r="AH50" s="77"/>
+      <c r="AI50" s="78"/>
+      <c r="AJ50" s="79"/>
       <c r="AK50" s="35"/>
-      <c r="AL50" s="85"/>
-      <c r="AM50" s="86"/>
-      <c r="AN50" s="87"/>
+      <c r="AL50" s="77"/>
+      <c r="AM50" s="78"/>
+      <c r="AN50" s="79"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="35"/>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -4892,68 +4937,70 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="71"/>
-      <c r="C52" s="72"/>
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="83"/>
+      <c r="C52" s="84"/>
       <c r="D52" s="60"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="71"/>
-      <c r="G52" s="72"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="84"/>
       <c r="H52" s="60"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="94" t="s">
+      <c r="J52" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="K52" s="95"/>
+      <c r="K52" s="91"/>
       <c r="L52" s="55" t="s">
         <v>79</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="77"/>
-      <c r="O52" s="78"/>
+      <c r="N52" s="67"/>
+      <c r="O52" s="68"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="77"/>
-      <c r="S52" s="78"/>
+      <c r="R52" s="67"/>
+      <c r="S52" s="68"/>
       <c r="T52" s="34"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="77" t="s">
+      <c r="V52" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="W52" s="78"/>
-      <c r="X52" s="34"/>
+      <c r="W52" s="68"/>
+      <c r="X52" s="34" t="s">
+        <v>87</v>
+      </c>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="77"/>
-      <c r="AA52" s="78"/>
+      <c r="Z52" s="67"/>
+      <c r="AA52" s="68"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="77"/>
-      <c r="AE52" s="78"/>
+      <c r="AD52" s="67"/>
+      <c r="AE52" s="68"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="77"/>
-      <c r="AI52" s="78"/>
+      <c r="AH52" s="67"/>
+      <c r="AI52" s="68"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="77"/>
-      <c r="AM52" s="78"/>
+      <c r="AL52" s="67"/>
+      <c r="AM52" s="68"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="79"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="81"/>
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="71"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="73"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="79"/>
-      <c r="G53" s="80"/>
-      <c r="H53" s="81"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="72"/>
+      <c r="H53" s="73"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="79" t="s">
+      <c r="J53" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="K53" s="80"/>
-      <c r="L53" s="81"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="73"/>
       <c r="M53" s="4"/>
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
@@ -4986,185 +5033,183 @@
       <c r="AN53" s="98"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="67"/>
-      <c r="C54" s="68"/>
-      <c r="D54" s="88"/>
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="80"/>
+      <c r="C54" s="81"/>
+      <c r="D54" s="82"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="67"/>
-      <c r="G54" s="68"/>
-      <c r="H54" s="88"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="82"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="67"/>
-      <c r="K54" s="68"/>
-      <c r="L54" s="88"/>
+      <c r="J54" s="80"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="82"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="63"/>
-      <c r="O54" s="64"/>
+      <c r="N54" s="92"/>
+      <c r="O54" s="93"/>
       <c r="P54" s="99"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="63"/>
-      <c r="S54" s="64"/>
+      <c r="R54" s="92"/>
+      <c r="S54" s="93"/>
       <c r="T54" s="99"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="W54" s="64"/>
+      <c r="V54" s="92"/>
+      <c r="W54" s="93"/>
       <c r="X54" s="99"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="63"/>
-      <c r="AA54" s="64"/>
+      <c r="Z54" s="92"/>
+      <c r="AA54" s="93"/>
       <c r="AB54" s="99"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="63"/>
-      <c r="AE54" s="64"/>
+      <c r="AD54" s="92"/>
+      <c r="AE54" s="93"/>
       <c r="AF54" s="99"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="63"/>
-      <c r="AI54" s="64"/>
+      <c r="AH54" s="92"/>
+      <c r="AI54" s="93"/>
       <c r="AJ54" s="99"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="63"/>
-      <c r="AM54" s="64"/>
+      <c r="AL54" s="92"/>
+      <c r="AM54" s="93"/>
       <c r="AN54" s="99"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="89"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="91"/>
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="74"/>
+      <c r="C55" s="75"/>
+      <c r="D55" s="76"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="89"/>
-      <c r="G55" s="90"/>
-      <c r="H55" s="91"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="75"/>
+      <c r="H55" s="76"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="89" t="s">
+      <c r="J55" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="K55" s="90"/>
-      <c r="L55" s="91"/>
+      <c r="K55" s="75"/>
+      <c r="L55" s="76"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="89"/>
-      <c r="O55" s="90"/>
-      <c r="P55" s="91"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="75"/>
+      <c r="P55" s="76"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="89"/>
-      <c r="S55" s="90"/>
-      <c r="T55" s="91"/>
+      <c r="R55" s="74"/>
+      <c r="S55" s="75"/>
+      <c r="T55" s="76"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="89" t="s">
+      <c r="V55" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="W55" s="90"/>
-      <c r="X55" s="91"/>
+      <c r="W55" s="75"/>
+      <c r="X55" s="76"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="89"/>
-      <c r="AA55" s="90"/>
-      <c r="AB55" s="91"/>
+      <c r="Z55" s="74"/>
+      <c r="AA55" s="75"/>
+      <c r="AB55" s="76"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="89"/>
-      <c r="AE55" s="90"/>
-      <c r="AF55" s="91"/>
+      <c r="AD55" s="74"/>
+      <c r="AE55" s="75"/>
+      <c r="AF55" s="76"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="89"/>
-      <c r="AI55" s="90"/>
-      <c r="AJ55" s="91"/>
+      <c r="AH55" s="74"/>
+      <c r="AI55" s="75"/>
+      <c r="AJ55" s="76"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="89"/>
-      <c r="AM55" s="90"/>
-      <c r="AN55" s="91"/>
+      <c r="AL55" s="74"/>
+      <c r="AM55" s="75"/>
+      <c r="AN55" s="76"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="82"/>
-      <c r="C56" s="83"/>
-      <c r="D56" s="84"/>
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="87"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="89"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="82"/>
-      <c r="G56" s="83"/>
-      <c r="H56" s="84"/>
+      <c r="F56" s="87"/>
+      <c r="G56" s="88"/>
+      <c r="H56" s="89"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="82" t="s">
+      <c r="J56" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="K56" s="83"/>
-      <c r="L56" s="84"/>
+      <c r="K56" s="88"/>
+      <c r="L56" s="89"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="82"/>
-      <c r="O56" s="83"/>
-      <c r="P56" s="84"/>
+      <c r="N56" s="87"/>
+      <c r="O56" s="88"/>
+      <c r="P56" s="89"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="82"/>
-      <c r="S56" s="83"/>
-      <c r="T56" s="84"/>
+      <c r="R56" s="87"/>
+      <c r="S56" s="88"/>
+      <c r="T56" s="89"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="82" t="s">
+      <c r="V56" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="W56" s="83"/>
-      <c r="X56" s="84"/>
+      <c r="W56" s="88"/>
+      <c r="X56" s="89"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="82"/>
-      <c r="AA56" s="83"/>
-      <c r="AB56" s="84"/>
+      <c r="Z56" s="87"/>
+      <c r="AA56" s="88"/>
+      <c r="AB56" s="89"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="82"/>
-      <c r="AE56" s="83"/>
-      <c r="AF56" s="84"/>
+      <c r="AD56" s="87"/>
+      <c r="AE56" s="88"/>
+      <c r="AF56" s="89"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="82"/>
-      <c r="AI56" s="83"/>
-      <c r="AJ56" s="84"/>
+      <c r="AH56" s="87"/>
+      <c r="AI56" s="88"/>
+      <c r="AJ56" s="89"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="82"/>
-      <c r="AM56" s="83"/>
-      <c r="AN56" s="84"/>
+      <c r="AL56" s="87"/>
+      <c r="AM56" s="88"/>
+      <c r="AN56" s="89"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="85"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="87"/>
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="77"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="79"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="87"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="79"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="85"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="87"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="78"/>
+      <c r="L57" s="79"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="85"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="87"/>
+      <c r="N57" s="77"/>
+      <c r="O57" s="78"/>
+      <c r="P57" s="79"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="85"/>
-      <c r="S57" s="86"/>
-      <c r="T57" s="87"/>
+      <c r="R57" s="77"/>
+      <c r="S57" s="78"/>
+      <c r="T57" s="79"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="85"/>
-      <c r="W57" s="86"/>
-      <c r="X57" s="87"/>
+      <c r="V57" s="77"/>
+      <c r="W57" s="78"/>
+      <c r="X57" s="79"/>
       <c r="Y57" s="50"/>
-      <c r="Z57" s="85"/>
-      <c r="AA57" s="86"/>
-      <c r="AB57" s="87"/>
+      <c r="Z57" s="77"/>
+      <c r="AA57" s="78"/>
+      <c r="AB57" s="79"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="85"/>
-      <c r="AE57" s="86"/>
-      <c r="AF57" s="87"/>
+      <c r="AD57" s="77"/>
+      <c r="AE57" s="78"/>
+      <c r="AF57" s="79"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="85"/>
-      <c r="AI57" s="86"/>
-      <c r="AJ57" s="87"/>
+      <c r="AH57" s="77"/>
+      <c r="AI57" s="78"/>
+      <c r="AJ57" s="79"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="85"/>
-      <c r="AM57" s="86"/>
-      <c r="AN57" s="87"/>
+      <c r="AL57" s="77"/>
+      <c r="AM57" s="78"/>
+      <c r="AN57" s="79"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -5206,64 +5251,64 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="71"/>
-      <c r="C59" s="72"/>
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="83"/>
+      <c r="C59" s="84"/>
       <c r="D59" s="60"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="71"/>
-      <c r="G59" s="72"/>
+      <c r="F59" s="83"/>
+      <c r="G59" s="84"/>
       <c r="H59" s="60"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="71"/>
-      <c r="K59" s="72"/>
+      <c r="J59" s="83"/>
+      <c r="K59" s="84"/>
       <c r="L59" s="60"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="77"/>
-      <c r="O59" s="78"/>
+      <c r="N59" s="67"/>
+      <c r="O59" s="68"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="77"/>
-      <c r="S59" s="78"/>
+      <c r="R59" s="67"/>
+      <c r="S59" s="68"/>
       <c r="T59" s="34"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="77" t="s">
+      <c r="V59" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="W59" s="78"/>
+      <c r="W59" s="68"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="77"/>
-      <c r="AA59" s="78"/>
+      <c r="Z59" s="67"/>
+      <c r="AA59" s="68"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="77"/>
-      <c r="AE59" s="78"/>
+      <c r="AD59" s="67"/>
+      <c r="AE59" s="68"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="77"/>
-      <c r="AI59" s="78"/>
+      <c r="AH59" s="67"/>
+      <c r="AI59" s="68"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="127" t="s">
+      <c r="AL59" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="AM59" s="128"/>
+      <c r="AM59" s="111"/>
       <c r="AN59" s="59"/>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="79"/>
-      <c r="C60" s="80"/>
-      <c r="D60" s="81"/>
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="71"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="73"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="80"/>
-      <c r="H60" s="81"/>
+      <c r="F60" s="71"/>
+      <c r="G60" s="72"/>
+      <c r="H60" s="73"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="79"/>
-      <c r="K60" s="80"/>
-      <c r="L60" s="81"/>
+      <c r="J60" s="71"/>
+      <c r="K60" s="72"/>
+      <c r="L60" s="73"/>
       <c r="M60" s="4"/>
       <c r="N60" s="96"/>
       <c r="O60" s="97"/>
@@ -5291,196 +5336,196 @@
       <c r="AI60" s="97"/>
       <c r="AJ60" s="98"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="101" t="s">
+      <c r="AL60" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="AM60" s="102"/>
-      <c r="AN60" s="103"/>
+      <c r="AM60" s="116"/>
+      <c r="AN60" s="117"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="67"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="88"/>
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="80"/>
+      <c r="C61" s="81"/>
+      <c r="D61" s="82"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="88"/>
+      <c r="F61" s="80"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="82"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="68"/>
-      <c r="L61" s="88"/>
+      <c r="J61" s="80"/>
+      <c r="K61" s="81"/>
+      <c r="L61" s="82"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="63"/>
-      <c r="O61" s="64"/>
+      <c r="N61" s="92"/>
+      <c r="O61" s="93"/>
       <c r="P61" s="99"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="63"/>
-      <c r="S61" s="64"/>
+      <c r="R61" s="92"/>
+      <c r="S61" s="93"/>
       <c r="T61" s="99"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="63" t="s">
+      <c r="V61" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="W61" s="64"/>
+      <c r="W61" s="93"/>
       <c r="X61" s="99"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="63"/>
-      <c r="AA61" s="64"/>
+      <c r="Z61" s="92"/>
+      <c r="AA61" s="93"/>
       <c r="AB61" s="99"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="63"/>
-      <c r="AE61" s="64"/>
+      <c r="AD61" s="92"/>
+      <c r="AE61" s="93"/>
       <c r="AF61" s="99"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="63"/>
-      <c r="AI61" s="64"/>
+      <c r="AH61" s="92"/>
+      <c r="AI61" s="93"/>
       <c r="AJ61" s="99"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="104" t="s">
+      <c r="AL61" s="118" t="s">
         <v>61</v>
       </c>
-      <c r="AM61" s="105"/>
-      <c r="AN61" s="106"/>
+      <c r="AM61" s="119"/>
+      <c r="AN61" s="120"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="89"/>
-      <c r="C62" s="90"/>
-      <c r="D62" s="91"/>
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="74"/>
+      <c r="C62" s="75"/>
+      <c r="D62" s="76"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="89"/>
-      <c r="G62" s="90"/>
-      <c r="H62" s="91"/>
+      <c r="F62" s="74"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="76"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="89"/>
-      <c r="K62" s="90"/>
-      <c r="L62" s="91"/>
+      <c r="J62" s="74"/>
+      <c r="K62" s="75"/>
+      <c r="L62" s="76"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="82"/>
-      <c r="O62" s="83"/>
-      <c r="P62" s="84"/>
+      <c r="N62" s="87"/>
+      <c r="O62" s="88"/>
+      <c r="P62" s="89"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="82"/>
-      <c r="S62" s="83"/>
-      <c r="T62" s="84"/>
+      <c r="R62" s="87"/>
+      <c r="S62" s="88"/>
+      <c r="T62" s="89"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="89" t="s">
+      <c r="V62" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="W62" s="90"/>
-      <c r="X62" s="91"/>
+      <c r="W62" s="75"/>
+      <c r="X62" s="76"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="82"/>
-      <c r="AA62" s="83"/>
-      <c r="AB62" s="84"/>
+      <c r="Z62" s="87"/>
+      <c r="AA62" s="88"/>
+      <c r="AB62" s="89"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="82"/>
-      <c r="AE62" s="83"/>
-      <c r="AF62" s="84"/>
+      <c r="AD62" s="87"/>
+      <c r="AE62" s="88"/>
+      <c r="AF62" s="89"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="82"/>
-      <c r="AI62" s="83"/>
-      <c r="AJ62" s="84"/>
+      <c r="AH62" s="87"/>
+      <c r="AI62" s="88"/>
+      <c r="AJ62" s="89"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="82" t="s">
+      <c r="AL62" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="AM62" s="83"/>
-      <c r="AN62" s="84"/>
+      <c r="AM62" s="88"/>
+      <c r="AN62" s="89"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="82"/>
-      <c r="C63" s="83"/>
-      <c r="D63" s="84"/>
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="87"/>
+      <c r="C63" s="88"/>
+      <c r="D63" s="89"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="83"/>
-      <c r="H63" s="84"/>
+      <c r="F63" s="87"/>
+      <c r="G63" s="88"/>
+      <c r="H63" s="89"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="82"/>
-      <c r="K63" s="83"/>
-      <c r="L63" s="84"/>
+      <c r="J63" s="87"/>
+      <c r="K63" s="88"/>
+      <c r="L63" s="89"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="82"/>
-      <c r="O63" s="83"/>
-      <c r="P63" s="84"/>
+      <c r="N63" s="87"/>
+      <c r="O63" s="88"/>
+      <c r="P63" s="89"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="82"/>
-      <c r="S63" s="83"/>
-      <c r="T63" s="84"/>
+      <c r="R63" s="87"/>
+      <c r="S63" s="88"/>
+      <c r="T63" s="89"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="82" t="s">
+      <c r="V63" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="W63" s="83"/>
-      <c r="X63" s="84"/>
+      <c r="W63" s="88"/>
+      <c r="X63" s="89"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="82"/>
-      <c r="AA63" s="83"/>
-      <c r="AB63" s="84"/>
+      <c r="Z63" s="87"/>
+      <c r="AA63" s="88"/>
+      <c r="AB63" s="89"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="82"/>
-      <c r="AE63" s="83"/>
-      <c r="AF63" s="84"/>
+      <c r="AD63" s="87"/>
+      <c r="AE63" s="88"/>
+      <c r="AF63" s="89"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="82"/>
-      <c r="AI63" s="83"/>
-      <c r="AJ63" s="84"/>
+      <c r="AH63" s="87"/>
+      <c r="AI63" s="88"/>
+      <c r="AJ63" s="89"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="82" t="s">
+      <c r="AL63" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="AM63" s="83"/>
-      <c r="AN63" s="84"/>
+      <c r="AM63" s="88"/>
+      <c r="AN63" s="89"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="85"/>
-      <c r="C64" s="86"/>
-      <c r="D64" s="87"/>
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="77"/>
+      <c r="C64" s="78"/>
+      <c r="D64" s="79"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="86"/>
-      <c r="H64" s="87"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="78"/>
+      <c r="H64" s="79"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="85"/>
-      <c r="K64" s="86"/>
-      <c r="L64" s="87"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="78"/>
+      <c r="L64" s="79"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="85"/>
-      <c r="O64" s="86"/>
-      <c r="P64" s="87"/>
+      <c r="N64" s="77"/>
+      <c r="O64" s="78"/>
+      <c r="P64" s="79"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="85"/>
-      <c r="S64" s="86"/>
-      <c r="T64" s="87"/>
+      <c r="R64" s="77"/>
+      <c r="S64" s="78"/>
+      <c r="T64" s="79"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="85"/>
-      <c r="W64" s="86"/>
-      <c r="X64" s="87"/>
+      <c r="V64" s="77"/>
+      <c r="W64" s="78"/>
+      <c r="X64" s="79"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="85"/>
-      <c r="AA64" s="86"/>
-      <c r="AB64" s="87"/>
+      <c r="Z64" s="77"/>
+      <c r="AA64" s="78"/>
+      <c r="AB64" s="79"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="85"/>
-      <c r="AE64" s="86"/>
-      <c r="AF64" s="87"/>
+      <c r="AD64" s="77"/>
+      <c r="AE64" s="78"/>
+      <c r="AF64" s="79"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="85"/>
-      <c r="AI64" s="86"/>
-      <c r="AJ64" s="87"/>
+      <c r="AH64" s="77"/>
+      <c r="AI64" s="78"/>
+      <c r="AJ64" s="79"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="85" t="s">
+      <c r="AL64" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="AM64" s="86"/>
-      <c r="AN64" s="87"/>
+      <c r="AM64" s="78"/>
+      <c r="AN64" s="79"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
       <c r="B65" s="33"/>
       <c r="C65" s="33"/>
@@ -5526,7 +5571,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
       <c r="B66" s="40"/>
       <c r="C66" s="33"/>
@@ -5540,23 +5585,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="100" t="s">
+      <c r="N66" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="100"/>
-      <c r="P66" s="100"/>
-      <c r="Q66" s="100"/>
-      <c r="R66" s="100"/>
-      <c r="S66" s="100"/>
-      <c r="T66" s="100"/>
-      <c r="U66" s="100"/>
-      <c r="V66" s="100"/>
-      <c r="W66" s="100"/>
-      <c r="X66" s="100"/>
-      <c r="Y66" s="100"/>
-      <c r="Z66" s="100"/>
-      <c r="AA66" s="100"/>
-      <c r="AB66" s="100"/>
+      <c r="O66" s="109"/>
+      <c r="P66" s="109"/>
+      <c r="Q66" s="109"/>
+      <c r="R66" s="109"/>
+      <c r="S66" s="109"/>
+      <c r="T66" s="109"/>
+      <c r="U66" s="109"/>
+      <c r="V66" s="109"/>
+      <c r="W66" s="109"/>
+      <c r="X66" s="109"/>
+      <c r="Y66" s="109"/>
+      <c r="Z66" s="109"/>
+      <c r="AA66" s="109"/>
+      <c r="AB66" s="109"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5573,7 +5618,7 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
       <c r="B67" s="33"/>
       <c r="C67" s="33"/>
@@ -5587,21 +5632,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="100"/>
-      <c r="O67" s="100"/>
-      <c r="P67" s="100"/>
-      <c r="Q67" s="100"/>
-      <c r="R67" s="100"/>
-      <c r="S67" s="100"/>
-      <c r="T67" s="100"/>
-      <c r="U67" s="100"/>
-      <c r="V67" s="100"/>
-      <c r="W67" s="100"/>
-      <c r="X67" s="100"/>
-      <c r="Y67" s="100"/>
-      <c r="Z67" s="100"/>
-      <c r="AA67" s="100"/>
-      <c r="AB67" s="100"/>
+      <c r="N67" s="109"/>
+      <c r="O67" s="109"/>
+      <c r="P67" s="109"/>
+      <c r="Q67" s="109"/>
+      <c r="R67" s="109"/>
+      <c r="S67" s="109"/>
+      <c r="T67" s="109"/>
+      <c r="U67" s="109"/>
+      <c r="V67" s="109"/>
+      <c r="W67" s="109"/>
+      <c r="X67" s="109"/>
+      <c r="Y67" s="109"/>
+      <c r="Z67" s="109"/>
+      <c r="AA67" s="109"/>
+      <c r="AB67" s="109"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5619,60 +5664,60 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="71"/>
-      <c r="C68" s="72"/>
+      <c r="B68" s="83"/>
+      <c r="C68" s="84"/>
       <c r="D68" s="60"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="71"/>
-      <c r="G68" s="72"/>
+      <c r="F68" s="83"/>
+      <c r="G68" s="84"/>
       <c r="H68" s="60"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="71"/>
-      <c r="K68" s="72"/>
+      <c r="J68" s="83"/>
+      <c r="K68" s="84"/>
       <c r="L68" s="60"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="77" t="s">
+      <c r="N68" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="O68" s="78"/>
+      <c r="O68" s="68"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="44"/>
-      <c r="R68" s="77" t="s">
+      <c r="R68" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="S68" s="78"/>
-      <c r="T68" s="34"/>
+      <c r="S68" s="111"/>
+      <c r="T68" s="59"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="77" t="s">
+      <c r="V68" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="W68" s="78"/>
+      <c r="W68" s="68"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="77" t="s">
+      <c r="Z68" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="AA68" s="78"/>
+      <c r="AA68" s="68"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="77" t="s">
+      <c r="AD68" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="AE68" s="78"/>
+      <c r="AE68" s="68"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="77" t="s">
+      <c r="AH68" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="AI68" s="78"/>
+      <c r="AI68" s="68"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="77" t="s">
+      <c r="AL68" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="AM68" s="78"/>
+      <c r="AM68" s="68"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5681,27 +5726,29 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="79"/>
-      <c r="C69" s="80"/>
-      <c r="D69" s="81"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="73"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="80"/>
-      <c r="H69" s="81"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="72"/>
+      <c r="H69" s="73"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="79"/>
-      <c r="K69" s="80"/>
-      <c r="L69" s="81"/>
+      <c r="J69" s="71"/>
+      <c r="K69" s="72"/>
+      <c r="L69" s="73"/>
       <c r="M69" s="4"/>
       <c r="N69" s="96"/>
       <c r="O69" s="97"/>
       <c r="P69" s="98"/>
       <c r="Q69" s="44"/>
-      <c r="R69" s="96"/>
-      <c r="S69" s="97"/>
-      <c r="T69" s="98"/>
+      <c r="R69" s="112" t="s">
+        <v>82</v>
+      </c>
+      <c r="S69" s="113"/>
+      <c r="T69" s="114"/>
       <c r="U69" s="32"/>
       <c r="V69" s="96" t="s">
         <v>52</v>
@@ -5739,60 +5786,60 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="68"/>
-      <c r="D70" s="88"/>
+      <c r="B70" s="80"/>
+      <c r="C70" s="81"/>
+      <c r="D70" s="82"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="88"/>
+      <c r="F70" s="80"/>
+      <c r="G70" s="81"/>
+      <c r="H70" s="82"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="68"/>
-      <c r="L70" s="88"/>
+      <c r="J70" s="80"/>
+      <c r="K70" s="81"/>
+      <c r="L70" s="82"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="63" t="s">
+      <c r="N70" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="64"/>
+      <c r="O70" s="93"/>
       <c r="P70" s="99"/>
       <c r="Q70" s="44"/>
-      <c r="R70" s="63" t="s">
+      <c r="R70" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="S70" s="64"/>
-      <c r="T70" s="99"/>
+      <c r="S70" s="104"/>
+      <c r="T70" s="105"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="63" t="s">
+      <c r="V70" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="W70" s="64"/>
+      <c r="W70" s="93"/>
       <c r="X70" s="99"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="63" t="s">
+      <c r="Z70" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="AA70" s="64"/>
+      <c r="AA70" s="93"/>
       <c r="AB70" s="99"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="63" t="s">
+      <c r="AD70" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="AE70" s="64"/>
+      <c r="AE70" s="93"/>
       <c r="AF70" s="99"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="63" t="s">
+      <c r="AH70" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="AI70" s="64"/>
+      <c r="AI70" s="93"/>
       <c r="AJ70" s="99"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="63" t="s">
+      <c r="AL70" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="AM70" s="64"/>
+      <c r="AM70" s="93"/>
       <c r="AN70" s="99"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
@@ -5801,61 +5848,61 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="89"/>
-      <c r="C71" s="90"/>
-      <c r="D71" s="91"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="75"/>
+      <c r="D71" s="76"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="89"/>
-      <c r="G71" s="90"/>
-      <c r="H71" s="91"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="76"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="89"/>
-      <c r="K71" s="90"/>
-      <c r="L71" s="91"/>
+      <c r="J71" s="74"/>
+      <c r="K71" s="75"/>
+      <c r="L71" s="76"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="89" t="s">
+      <c r="N71" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="O71" s="90"/>
-      <c r="P71" s="91"/>
+      <c r="O71" s="75"/>
+      <c r="P71" s="76"/>
       <c r="Q71" s="37"/>
-      <c r="R71" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="S71" s="90"/>
-      <c r="T71" s="91"/>
+      <c r="R71" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="S71" s="101"/>
+      <c r="T71" s="102"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="89" t="s">
+      <c r="V71" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="W71" s="90"/>
-      <c r="X71" s="91"/>
+      <c r="W71" s="75"/>
+      <c r="X71" s="76"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="89" t="s">
+      <c r="Z71" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="AA71" s="90"/>
-      <c r="AB71" s="91"/>
+      <c r="AA71" s="75"/>
+      <c r="AB71" s="76"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="89" t="s">
+      <c r="AD71" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="AE71" s="90"/>
-      <c r="AF71" s="91"/>
+      <c r="AE71" s="75"/>
+      <c r="AF71" s="76"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="89" t="s">
+      <c r="AH71" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="AI71" s="90"/>
-      <c r="AJ71" s="91"/>
+      <c r="AI71" s="75"/>
+      <c r="AJ71" s="76"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="89" t="s">
+      <c r="AL71" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="AM71" s="90"/>
-      <c r="AN71" s="91"/>
+      <c r="AM71" s="75"/>
+      <c r="AN71" s="76"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -5863,55 +5910,55 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="85"/>
-      <c r="C72" s="86"/>
-      <c r="D72" s="87"/>
+      <c r="B72" s="77"/>
+      <c r="C72" s="78"/>
+      <c r="D72" s="79"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="86"/>
-      <c r="H72" s="87"/>
+      <c r="F72" s="77"/>
+      <c r="G72" s="78"/>
+      <c r="H72" s="79"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="85"/>
-      <c r="K72" s="86"/>
-      <c r="L72" s="87"/>
+      <c r="J72" s="77"/>
+      <c r="K72" s="78"/>
+      <c r="L72" s="79"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="85"/>
-      <c r="O72" s="86"/>
-      <c r="P72" s="87"/>
+      <c r="N72" s="77"/>
+      <c r="O72" s="78"/>
+      <c r="P72" s="79"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="85"/>
-      <c r="S72" s="86"/>
-      <c r="T72" s="87"/>
+      <c r="R72" s="106"/>
+      <c r="S72" s="107"/>
+      <c r="T72" s="108"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="85" t="s">
+      <c r="V72" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="W72" s="86"/>
-      <c r="X72" s="87"/>
+      <c r="W72" s="78"/>
+      <c r="X72" s="79"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="85"/>
-      <c r="AA72" s="86"/>
-      <c r="AB72" s="87"/>
+      <c r="Z72" s="77"/>
+      <c r="AA72" s="78"/>
+      <c r="AB72" s="79"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="85"/>
-      <c r="AE72" s="86"/>
-      <c r="AF72" s="87"/>
+      <c r="AD72" s="77"/>
+      <c r="AE72" s="78"/>
+      <c r="AF72" s="79"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="85"/>
-      <c r="AI72" s="86"/>
-      <c r="AJ72" s="87"/>
+      <c r="AH72" s="77"/>
+      <c r="AI72" s="78"/>
+      <c r="AJ72" s="79"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="85"/>
-      <c r="AM72" s="86"/>
-      <c r="AN72" s="87"/>
+      <c r="AL72" s="77"/>
+      <c r="AM72" s="78"/>
+      <c r="AN72" s="79"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -5957,73 +6004,79 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="71"/>
-      <c r="C74" s="72"/>
+      <c r="B74" s="83"/>
+      <c r="C74" s="84"/>
       <c r="D74" s="60"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="71" t="s">
+      <c r="F74" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="G74" s="72"/>
+      <c r="G74" s="84"/>
       <c r="H74" s="60"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="71"/>
-      <c r="K74" s="72"/>
+      <c r="J74" s="83"/>
+      <c r="K74" s="84"/>
       <c r="L74" s="60"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="77"/>
-      <c r="O74" s="78"/>
-      <c r="P74" s="34"/>
+      <c r="N74" s="90" t="s">
+        <v>85</v>
+      </c>
+      <c r="O74" s="91"/>
+      <c r="P74" s="55" t="s">
+        <v>79</v>
+      </c>
       <c r="Q74" s="44"/>
-      <c r="R74" s="77"/>
-      <c r="S74" s="78"/>
+      <c r="R74" s="67"/>
+      <c r="S74" s="68"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="77" t="s">
+      <c r="V74" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="W74" s="78"/>
-      <c r="X74" s="34"/>
+      <c r="W74" s="111"/>
+      <c r="X74" s="59"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="77" t="s">
+      <c r="Z74" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="AA74" s="78"/>
+      <c r="AA74" s="68"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="77"/>
-      <c r="AE74" s="78"/>
+      <c r="AD74" s="67"/>
+      <c r="AE74" s="68"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="77"/>
-      <c r="AI74" s="78"/>
+      <c r="AH74" s="67"/>
+      <c r="AI74" s="68"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="77"/>
-      <c r="AM74" s="78"/>
+      <c r="AL74" s="67"/>
+      <c r="AM74" s="68"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="79"/>
-      <c r="C75" s="80"/>
-      <c r="D75" s="81"/>
+      <c r="B75" s="71"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="73"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="79"/>
-      <c r="G75" s="80"/>
-      <c r="H75" s="81"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="72"/>
+      <c r="H75" s="73"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="79"/>
-      <c r="K75" s="80"/>
-      <c r="L75" s="81"/>
+      <c r="J75" s="71"/>
+      <c r="K75" s="72"/>
+      <c r="L75" s="73"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="96"/>
+      <c r="N75" s="96" t="s">
+        <v>86</v>
+      </c>
       <c r="O75" s="97"/>
       <c r="P75" s="98"/>
       <c r="Q75" s="44"/>
@@ -6031,11 +6084,11 @@
       <c r="S75" s="97"/>
       <c r="T75" s="98"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="96" t="s">
+      <c r="V75" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="W75" s="97"/>
-      <c r="X75" s="98"/>
+      <c r="W75" s="116"/>
+      <c r="X75" s="117"/>
       <c r="Y75" s="32"/>
       <c r="Z75" s="96"/>
       <c r="AA75" s="97"/>
@@ -6057,159 +6110,163 @@
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="68"/>
-      <c r="D76" s="88"/>
+      <c r="B76" s="80"/>
+      <c r="C76" s="81"/>
+      <c r="D76" s="82"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="67" t="s">
+      <c r="F76" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="68"/>
-      <c r="H76" s="88"/>
+      <c r="G76" s="81"/>
+      <c r="H76" s="82"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="67"/>
-      <c r="K76" s="68"/>
-      <c r="L76" s="88"/>
+      <c r="J76" s="80"/>
+      <c r="K76" s="81"/>
+      <c r="L76" s="82"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="63"/>
-      <c r="O76" s="64"/>
+      <c r="N76" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="O76" s="93"/>
       <c r="P76" s="99"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="63"/>
-      <c r="S76" s="64"/>
+      <c r="R76" s="92"/>
+      <c r="S76" s="93"/>
       <c r="T76" s="99"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="63" t="s">
+      <c r="V76" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="W76" s="64"/>
-      <c r="X76" s="99"/>
+      <c r="W76" s="104"/>
+      <c r="X76" s="105"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="63" t="s">
+      <c r="Z76" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="AA76" s="64"/>
+      <c r="AA76" s="93"/>
       <c r="AB76" s="99"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="63"/>
-      <c r="AE76" s="64"/>
+      <c r="AD76" s="92"/>
+      <c r="AE76" s="93"/>
       <c r="AF76" s="99"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="63"/>
-      <c r="AI76" s="64"/>
+      <c r="AH76" s="92"/>
+      <c r="AI76" s="93"/>
       <c r="AJ76" s="99"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="63"/>
-      <c r="AM76" s="64"/>
+      <c r="AL76" s="92"/>
+      <c r="AM76" s="93"/>
       <c r="AN76" s="99"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="89"/>
-      <c r="C77" s="90"/>
-      <c r="D77" s="91"/>
+      <c r="B77" s="74"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="76"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="89" t="s">
+      <c r="F77" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="G77" s="90"/>
-      <c r="H77" s="91"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="76"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="89"/>
-      <c r="K77" s="90"/>
-      <c r="L77" s="91"/>
+      <c r="J77" s="74"/>
+      <c r="K77" s="75"/>
+      <c r="L77" s="76"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="89"/>
-      <c r="O77" s="90"/>
-      <c r="P77" s="91"/>
+      <c r="N77" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="O77" s="75"/>
+      <c r="P77" s="76"/>
       <c r="Q77" s="37"/>
-      <c r="R77" s="89"/>
-      <c r="S77" s="90"/>
-      <c r="T77" s="91"/>
+      <c r="R77" s="74"/>
+      <c r="S77" s="75"/>
+      <c r="T77" s="76"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="89" t="s">
-        <v>10</v>
-      </c>
-      <c r="W77" s="90"/>
-      <c r="X77" s="91"/>
+      <c r="V77" s="141" t="s">
+        <v>89</v>
+      </c>
+      <c r="W77" s="142"/>
+      <c r="X77" s="143"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="89" t="s">
+      <c r="Z77" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="AA77" s="90"/>
-      <c r="AB77" s="91"/>
+      <c r="AA77" s="75"/>
+      <c r="AB77" s="76"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="89"/>
-      <c r="AE77" s="90"/>
-      <c r="AF77" s="91"/>
+      <c r="AD77" s="74"/>
+      <c r="AE77" s="75"/>
+      <c r="AF77" s="76"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="89"/>
-      <c r="AI77" s="90"/>
-      <c r="AJ77" s="91"/>
+      <c r="AH77" s="74"/>
+      <c r="AI77" s="75"/>
+      <c r="AJ77" s="76"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="89"/>
-      <c r="AM77" s="90"/>
-      <c r="AN77" s="91"/>
+      <c r="AL77" s="74"/>
+      <c r="AM77" s="75"/>
+      <c r="AN77" s="76"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="85"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="87"/>
+      <c r="B78" s="77"/>
+      <c r="C78" s="78"/>
+      <c r="D78" s="79"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="85"/>
-      <c r="G78" s="86"/>
-      <c r="H78" s="87"/>
+      <c r="F78" s="77"/>
+      <c r="G78" s="78"/>
+      <c r="H78" s="79"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="85"/>
-      <c r="K78" s="86"/>
-      <c r="L78" s="87"/>
+      <c r="J78" s="77"/>
+      <c r="K78" s="78"/>
+      <c r="L78" s="79"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="85"/>
-      <c r="O78" s="86"/>
-      <c r="P78" s="87"/>
+      <c r="N78" s="77"/>
+      <c r="O78" s="78"/>
+      <c r="P78" s="79"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="85"/>
-      <c r="S78" s="86"/>
-      <c r="T78" s="87"/>
+      <c r="R78" s="77"/>
+      <c r="S78" s="78"/>
+      <c r="T78" s="79"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="W78" s="86"/>
-      <c r="X78" s="87"/>
+      <c r="V78" s="144" t="s">
+        <v>88</v>
+      </c>
+      <c r="W78" s="145"/>
+      <c r="X78" s="146"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="85"/>
-      <c r="AA78" s="86"/>
-      <c r="AB78" s="87"/>
+      <c r="Z78" s="77"/>
+      <c r="AA78" s="78"/>
+      <c r="AB78" s="79"/>
       <c r="AC78" s="31"/>
-      <c r="AD78" s="85"/>
-      <c r="AE78" s="86"/>
-      <c r="AF78" s="87"/>
+      <c r="AD78" s="77"/>
+      <c r="AE78" s="78"/>
+      <c r="AF78" s="79"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="85"/>
-      <c r="AI78" s="86"/>
-      <c r="AJ78" s="87"/>
+      <c r="AH78" s="77"/>
+      <c r="AI78" s="78"/>
+      <c r="AJ78" s="79"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="85"/>
-      <c r="AM78" s="86"/>
-      <c r="AN78" s="87"/>
+      <c r="AL78" s="77"/>
+      <c r="AM78" s="78"/>
+      <c r="AN78" s="79"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="16"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -6255,71 +6312,71 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="127" t="s">
+      <c r="B80" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="128"/>
+      <c r="C80" s="111"/>
       <c r="D80" s="59"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="72"/>
+      <c r="F80" s="83"/>
+      <c r="G80" s="84"/>
       <c r="H80" s="60"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="71"/>
-      <c r="K80" s="72"/>
+      <c r="J80" s="83"/>
+      <c r="K80" s="84"/>
       <c r="L80" s="60"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="77"/>
-      <c r="O80" s="78"/>
+      <c r="N80" s="67"/>
+      <c r="O80" s="68"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="44"/>
-      <c r="R80" s="77"/>
-      <c r="S80" s="78"/>
+      <c r="R80" s="67"/>
+      <c r="S80" s="68"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="77" t="s">
+      <c r="V80" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="W80" s="78"/>
+      <c r="W80" s="68"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="77"/>
-      <c r="AA80" s="78"/>
+      <c r="Z80" s="67"/>
+      <c r="AA80" s="68"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="77"/>
-      <c r="AE80" s="78"/>
+      <c r="AD80" s="67"/>
+      <c r="AE80" s="68"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="77"/>
-      <c r="AI80" s="78"/>
+      <c r="AH80" s="67"/>
+      <c r="AI80" s="68"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="77"/>
-      <c r="AM80" s="78"/>
+      <c r="AL80" s="67"/>
+      <c r="AM80" s="68"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="129" t="s">
+      <c r="B81" s="112" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="130"/>
-      <c r="D81" s="131"/>
+      <c r="C81" s="113"/>
+      <c r="D81" s="114"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="79"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="81"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="73"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="79"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="81"/>
+      <c r="J81" s="71"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="73"/>
       <c r="M81" s="5"/>
       <c r="N81" s="96"/>
       <c r="O81" s="97"/>
@@ -6355,155 +6412,155 @@
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="132" t="s">
+      <c r="B82" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="C82" s="133"/>
-      <c r="D82" s="134"/>
+      <c r="C82" s="104"/>
+      <c r="D82" s="105"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="68"/>
-      <c r="H82" s="88"/>
+      <c r="F82" s="80"/>
+      <c r="G82" s="81"/>
+      <c r="H82" s="82"/>
       <c r="I82" s="31"/>
-      <c r="J82" s="67"/>
-      <c r="K82" s="68"/>
-      <c r="L82" s="88"/>
+      <c r="J82" s="80"/>
+      <c r="K82" s="81"/>
+      <c r="L82" s="82"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="63"/>
-      <c r="O82" s="64"/>
+      <c r="N82" s="92"/>
+      <c r="O82" s="93"/>
       <c r="P82" s="99"/>
       <c r="Q82" s="44"/>
-      <c r="R82" s="63"/>
-      <c r="S82" s="64"/>
+      <c r="R82" s="92"/>
+      <c r="S82" s="93"/>
       <c r="T82" s="99"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="63" t="s">
+      <c r="V82" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="W82" s="64"/>
+      <c r="W82" s="93"/>
       <c r="X82" s="99"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="63"/>
-      <c r="AA82" s="64"/>
+      <c r="Z82" s="92"/>
+      <c r="AA82" s="93"/>
       <c r="AB82" s="99"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="63"/>
-      <c r="AE82" s="64"/>
+      <c r="AD82" s="92"/>
+      <c r="AE82" s="93"/>
       <c r="AF82" s="99"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="63"/>
-      <c r="AI82" s="64"/>
+      <c r="AH82" s="92"/>
+      <c r="AI82" s="93"/>
       <c r="AJ82" s="99"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="63"/>
-      <c r="AM82" s="64"/>
+      <c r="AL82" s="92"/>
+      <c r="AM82" s="93"/>
       <c r="AN82" s="99"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="135" t="s">
+      <c r="B83" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="136"/>
-      <c r="D83" s="137"/>
+      <c r="C83" s="101"/>
+      <c r="D83" s="102"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="89"/>
-      <c r="G83" s="90"/>
-      <c r="H83" s="91"/>
+      <c r="F83" s="74"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="76"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="89"/>
-      <c r="K83" s="90"/>
-      <c r="L83" s="91"/>
+      <c r="J83" s="74"/>
+      <c r="K83" s="75"/>
+      <c r="L83" s="76"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="89"/>
-      <c r="O83" s="90"/>
-      <c r="P83" s="91"/>
+      <c r="N83" s="74"/>
+      <c r="O83" s="75"/>
+      <c r="P83" s="76"/>
       <c r="Q83" s="44"/>
-      <c r="R83" s="89"/>
-      <c r="S83" s="90"/>
-      <c r="T83" s="91"/>
+      <c r="R83" s="74"/>
+      <c r="S83" s="75"/>
+      <c r="T83" s="76"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="89" t="s">
-        <v>16</v>
-      </c>
-      <c r="W83" s="90"/>
-      <c r="X83" s="91"/>
+      <c r="V83" s="147" t="s">
+        <v>10</v>
+      </c>
+      <c r="W83" s="148"/>
+      <c r="X83" s="149"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="89"/>
-      <c r="AA83" s="90"/>
-      <c r="AB83" s="91"/>
+      <c r="Z83" s="74"/>
+      <c r="AA83" s="75"/>
+      <c r="AB83" s="76"/>
       <c r="AC83" s="43"/>
-      <c r="AD83" s="89"/>
-      <c r="AE83" s="90"/>
-      <c r="AF83" s="91"/>
+      <c r="AD83" s="74"/>
+      <c r="AE83" s="75"/>
+      <c r="AF83" s="76"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="89"/>
-      <c r="AI83" s="90"/>
-      <c r="AJ83" s="91"/>
+      <c r="AH83" s="74"/>
+      <c r="AI83" s="75"/>
+      <c r="AJ83" s="76"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="89"/>
-      <c r="AM83" s="90"/>
-      <c r="AN83" s="91"/>
+      <c r="AL83" s="74"/>
+      <c r="AM83" s="75"/>
+      <c r="AN83" s="76"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="138"/>
-      <c r="C84" s="139"/>
-      <c r="D84" s="140"/>
+      <c r="B84" s="106"/>
+      <c r="C84" s="107"/>
+      <c r="D84" s="108"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="85"/>
-      <c r="G84" s="86"/>
-      <c r="H84" s="87"/>
+      <c r="F84" s="77"/>
+      <c r="G84" s="78"/>
+      <c r="H84" s="79"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="85"/>
-      <c r="K84" s="86"/>
-      <c r="L84" s="87"/>
+      <c r="J84" s="77"/>
+      <c r="K84" s="78"/>
+      <c r="L84" s="79"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="85"/>
-      <c r="O84" s="86"/>
-      <c r="P84" s="87"/>
+      <c r="N84" s="77"/>
+      <c r="O84" s="78"/>
+      <c r="P84" s="79"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="85"/>
-      <c r="S84" s="86"/>
-      <c r="T84" s="87"/>
+      <c r="R84" s="77"/>
+      <c r="S84" s="78"/>
+      <c r="T84" s="79"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="85" t="s">
+      <c r="V84" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="W84" s="86"/>
-      <c r="X84" s="87"/>
+      <c r="W84" s="78"/>
+      <c r="X84" s="79"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="85"/>
-      <c r="AA84" s="86"/>
-      <c r="AB84" s="87"/>
+      <c r="Z84" s="77"/>
+      <c r="AA84" s="78"/>
+      <c r="AB84" s="79"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="85"/>
-      <c r="AE84" s="86"/>
-      <c r="AF84" s="87"/>
+      <c r="AD84" s="77"/>
+      <c r="AE84" s="78"/>
+      <c r="AF84" s="79"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="85"/>
-      <c r="AI84" s="86"/>
-      <c r="AJ84" s="87"/>
+      <c r="AH84" s="77"/>
+      <c r="AI84" s="78"/>
+      <c r="AJ84" s="79"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="85"/>
-      <c r="AM84" s="86"/>
-      <c r="AN84" s="87"/>
+      <c r="AL84" s="77"/>
+      <c r="AM84" s="78"/>
+      <c r="AN84" s="79"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -6549,65 +6606,65 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="71"/>
-      <c r="C86" s="72"/>
+      <c r="B86" s="83"/>
+      <c r="C86" s="84"/>
       <c r="D86" s="60"/>
       <c r="E86" s="36"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="72"/>
+      <c r="F86" s="83"/>
+      <c r="G86" s="84"/>
       <c r="H86" s="60"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="71"/>
-      <c r="K86" s="72"/>
+      <c r="J86" s="83"/>
+      <c r="K86" s="84"/>
       <c r="L86" s="60"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="77"/>
-      <c r="O86" s="78"/>
+      <c r="N86" s="67"/>
+      <c r="O86" s="68"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="77"/>
-      <c r="S86" s="78"/>
+      <c r="R86" s="67"/>
+      <c r="S86" s="68"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="77"/>
-      <c r="W86" s="78"/>
+      <c r="V86" s="67"/>
+      <c r="W86" s="68"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="77"/>
-      <c r="AA86" s="78"/>
+      <c r="Z86" s="67"/>
+      <c r="AA86" s="68"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="77"/>
-      <c r="AE86" s="78"/>
+      <c r="AD86" s="67"/>
+      <c r="AE86" s="68"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="77"/>
-      <c r="AI86" s="78"/>
+      <c r="AH86" s="67"/>
+      <c r="AI86" s="68"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="77"/>
-      <c r="AM86" s="78"/>
+      <c r="AL86" s="67"/>
+      <c r="AM86" s="68"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="79"/>
-      <c r="C87" s="80"/>
-      <c r="D87" s="81"/>
+      <c r="B87" s="71"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="73"/>
       <c r="E87" s="38"/>
-      <c r="F87" s="79"/>
-      <c r="G87" s="80"/>
-      <c r="H87" s="81"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="72"/>
+      <c r="H87" s="73"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="79"/>
-      <c r="K87" s="80"/>
-      <c r="L87" s="81"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="72"/>
+      <c r="L87" s="73"/>
       <c r="M87" s="6"/>
       <c r="N87" s="96"/>
       <c r="O87" s="97"/>
@@ -6641,145 +6698,145 @@
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="68"/>
-      <c r="D88" s="88"/>
+      <c r="B88" s="80"/>
+      <c r="C88" s="81"/>
+      <c r="D88" s="82"/>
       <c r="E88" s="37"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="68"/>
-      <c r="H88" s="88"/>
+      <c r="F88" s="80"/>
+      <c r="G88" s="81"/>
+      <c r="H88" s="82"/>
       <c r="I88" s="31"/>
-      <c r="J88" s="67"/>
-      <c r="K88" s="68"/>
-      <c r="L88" s="88"/>
+      <c r="J88" s="80"/>
+      <c r="K88" s="81"/>
+      <c r="L88" s="82"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="63"/>
-      <c r="O88" s="64"/>
+      <c r="N88" s="92"/>
+      <c r="O88" s="93"/>
       <c r="P88" s="99"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="63"/>
-      <c r="S88" s="64"/>
+      <c r="R88" s="92"/>
+      <c r="S88" s="93"/>
       <c r="T88" s="99"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="63"/>
-      <c r="W88" s="64"/>
+      <c r="V88" s="92"/>
+      <c r="W88" s="93"/>
       <c r="X88" s="99"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="63"/>
-      <c r="AA88" s="64"/>
+      <c r="Z88" s="92"/>
+      <c r="AA88" s="93"/>
       <c r="AB88" s="99"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="63"/>
-      <c r="AE88" s="64"/>
+      <c r="AD88" s="92"/>
+      <c r="AE88" s="93"/>
       <c r="AF88" s="99"/>
       <c r="AG88" s="37"/>
-      <c r="AH88" s="63"/>
-      <c r="AI88" s="64"/>
+      <c r="AH88" s="92"/>
+      <c r="AI88" s="93"/>
       <c r="AJ88" s="99"/>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="63"/>
-      <c r="AM88" s="64"/>
+      <c r="AL88" s="92"/>
+      <c r="AM88" s="93"/>
       <c r="AN88" s="99"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="89"/>
-      <c r="C89" s="90"/>
-      <c r="D89" s="91"/>
+      <c r="B89" s="74"/>
+      <c r="C89" s="75"/>
+      <c r="D89" s="76"/>
       <c r="E89" s="43"/>
-      <c r="F89" s="89"/>
-      <c r="G89" s="90"/>
-      <c r="H89" s="91"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="75"/>
+      <c r="H89" s="76"/>
       <c r="I89" s="31"/>
-      <c r="J89" s="89"/>
-      <c r="K89" s="90"/>
-      <c r="L89" s="91"/>
+      <c r="J89" s="74"/>
+      <c r="K89" s="75"/>
+      <c r="L89" s="76"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="89"/>
-      <c r="O89" s="90"/>
-      <c r="P89" s="91"/>
+      <c r="N89" s="74"/>
+      <c r="O89" s="75"/>
+      <c r="P89" s="76"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="89"/>
-      <c r="S89" s="90"/>
-      <c r="T89" s="91"/>
+      <c r="R89" s="74"/>
+      <c r="S89" s="75"/>
+      <c r="T89" s="76"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="89"/>
-      <c r="W89" s="90"/>
-      <c r="X89" s="91"/>
+      <c r="V89" s="74"/>
+      <c r="W89" s="75"/>
+      <c r="X89" s="76"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="89"/>
-      <c r="AA89" s="90"/>
-      <c r="AB89" s="91"/>
+      <c r="Z89" s="74"/>
+      <c r="AA89" s="75"/>
+      <c r="AB89" s="76"/>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="89"/>
-      <c r="AE89" s="90"/>
-      <c r="AF89" s="91"/>
+      <c r="AD89" s="74"/>
+      <c r="AE89" s="75"/>
+      <c r="AF89" s="76"/>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="89"/>
-      <c r="AI89" s="90"/>
-      <c r="AJ89" s="91"/>
+      <c r="AH89" s="74"/>
+      <c r="AI89" s="75"/>
+      <c r="AJ89" s="76"/>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="89"/>
-      <c r="AM89" s="90"/>
-      <c r="AN89" s="91"/>
+      <c r="AL89" s="74"/>
+      <c r="AM89" s="75"/>
+      <c r="AN89" s="76"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="85"/>
-      <c r="C90" s="86"/>
-      <c r="D90" s="87"/>
+      <c r="B90" s="77"/>
+      <c r="C90" s="78"/>
+      <c r="D90" s="79"/>
       <c r="E90" s="43"/>
-      <c r="F90" s="85"/>
-      <c r="G90" s="86"/>
-      <c r="H90" s="87"/>
+      <c r="F90" s="77"/>
+      <c r="G90" s="78"/>
+      <c r="H90" s="79"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="85"/>
-      <c r="K90" s="86"/>
-      <c r="L90" s="87"/>
+      <c r="J90" s="77"/>
+      <c r="K90" s="78"/>
+      <c r="L90" s="79"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="85"/>
-      <c r="O90" s="86"/>
-      <c r="P90" s="87"/>
+      <c r="N90" s="77"/>
+      <c r="O90" s="78"/>
+      <c r="P90" s="79"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="85"/>
-      <c r="S90" s="86"/>
-      <c r="T90" s="87"/>
+      <c r="R90" s="77"/>
+      <c r="S90" s="78"/>
+      <c r="T90" s="79"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="85"/>
-      <c r="W90" s="86"/>
-      <c r="X90" s="87"/>
+      <c r="V90" s="77"/>
+      <c r="W90" s="78"/>
+      <c r="X90" s="79"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="85"/>
-      <c r="AA90" s="86"/>
-      <c r="AB90" s="87"/>
+      <c r="Z90" s="77"/>
+      <c r="AA90" s="78"/>
+      <c r="AB90" s="79"/>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="85"/>
-      <c r="AE90" s="86"/>
-      <c r="AF90" s="87"/>
+      <c r="AD90" s="77"/>
+      <c r="AE90" s="78"/>
+      <c r="AF90" s="79"/>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="85"/>
-      <c r="AI90" s="86"/>
-      <c r="AJ90" s="87"/>
+      <c r="AH90" s="77"/>
+      <c r="AI90" s="78"/>
+      <c r="AJ90" s="79"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="85"/>
-      <c r="AM90" s="86"/>
-      <c r="AN90" s="87"/>
+      <c r="AL90" s="77"/>
+      <c r="AM90" s="78"/>
+      <c r="AN90" s="79"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35"/>
@@ -6825,65 +6882,65 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="71"/>
-      <c r="C92" s="72"/>
+      <c r="B92" s="83"/>
+      <c r="C92" s="84"/>
       <c r="D92" s="60"/>
       <c r="E92" s="44"/>
-      <c r="F92" s="71"/>
-      <c r="G92" s="72"/>
+      <c r="F92" s="83"/>
+      <c r="G92" s="84"/>
       <c r="H92" s="60"/>
       <c r="I92" s="32"/>
-      <c r="J92" s="71"/>
-      <c r="K92" s="72"/>
+      <c r="J92" s="83"/>
+      <c r="K92" s="84"/>
       <c r="L92" s="60"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="77"/>
-      <c r="O92" s="78"/>
+      <c r="N92" s="67"/>
+      <c r="O92" s="68"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="32"/>
-      <c r="R92" s="77"/>
-      <c r="S92" s="78"/>
+      <c r="R92" s="67"/>
+      <c r="S92" s="68"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="77"/>
-      <c r="W92" s="78"/>
+      <c r="V92" s="67"/>
+      <c r="W92" s="68"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="77"/>
-      <c r="AA92" s="78"/>
+      <c r="Z92" s="67"/>
+      <c r="AA92" s="68"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="77"/>
-      <c r="AE92" s="78"/>
+      <c r="AD92" s="67"/>
+      <c r="AE92" s="68"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="77"/>
-      <c r="AI92" s="78"/>
+      <c r="AH92" s="67"/>
+      <c r="AI92" s="68"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="77"/>
-      <c r="AM92" s="78"/>
+      <c r="AL92" s="67"/>
+      <c r="AM92" s="68"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="79"/>
-      <c r="C93" s="80"/>
-      <c r="D93" s="81"/>
+      <c r="B93" s="71"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="73"/>
       <c r="E93" s="43"/>
-      <c r="F93" s="79"/>
-      <c r="G93" s="80"/>
-      <c r="H93" s="81"/>
+      <c r="F93" s="71"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="73"/>
       <c r="I93" s="35"/>
-      <c r="J93" s="79"/>
-      <c r="K93" s="80"/>
-      <c r="L93" s="81"/>
+      <c r="J93" s="71"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="73"/>
       <c r="M93" s="6"/>
       <c r="N93" s="96"/>
       <c r="O93" s="97"/>
@@ -6917,145 +6974,145 @@
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="68"/>
-      <c r="D94" s="88"/>
+      <c r="B94" s="80"/>
+      <c r="C94" s="81"/>
+      <c r="D94" s="82"/>
       <c r="E94" s="44"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="68"/>
-      <c r="H94" s="88"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="81"/>
+      <c r="H94" s="82"/>
       <c r="I94" s="31"/>
-      <c r="J94" s="67"/>
-      <c r="K94" s="68"/>
-      <c r="L94" s="88"/>
+      <c r="J94" s="80"/>
+      <c r="K94" s="81"/>
+      <c r="L94" s="82"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="63"/>
-      <c r="O94" s="64"/>
+      <c r="N94" s="92"/>
+      <c r="O94" s="93"/>
       <c r="P94" s="99"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="63"/>
-      <c r="S94" s="64"/>
+      <c r="R94" s="92"/>
+      <c r="S94" s="93"/>
       <c r="T94" s="99"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="63"/>
-      <c r="W94" s="64"/>
+      <c r="V94" s="92"/>
+      <c r="W94" s="93"/>
       <c r="X94" s="99"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="63"/>
-      <c r="AA94" s="64"/>
+      <c r="Z94" s="92"/>
+      <c r="AA94" s="93"/>
       <c r="AB94" s="99"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="63"/>
-      <c r="AE94" s="64"/>
+      <c r="AD94" s="92"/>
+      <c r="AE94" s="93"/>
       <c r="AF94" s="99"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="63"/>
-      <c r="AI94" s="64"/>
+      <c r="AH94" s="92"/>
+      <c r="AI94" s="93"/>
       <c r="AJ94" s="99"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="63"/>
-      <c r="AM94" s="64"/>
+      <c r="AL94" s="92"/>
+      <c r="AM94" s="93"/>
       <c r="AN94" s="99"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="89"/>
-      <c r="C95" s="90"/>
-      <c r="D95" s="91"/>
+      <c r="B95" s="74"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="76"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="89"/>
-      <c r="G95" s="90"/>
-      <c r="H95" s="91"/>
+      <c r="F95" s="74"/>
+      <c r="G95" s="75"/>
+      <c r="H95" s="76"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="89"/>
-      <c r="K95" s="90"/>
-      <c r="L95" s="91"/>
+      <c r="J95" s="74"/>
+      <c r="K95" s="75"/>
+      <c r="L95" s="76"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="89"/>
-      <c r="O95" s="90"/>
-      <c r="P95" s="91"/>
+      <c r="N95" s="74"/>
+      <c r="O95" s="75"/>
+      <c r="P95" s="76"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="89"/>
-      <c r="S95" s="90"/>
-      <c r="T95" s="91"/>
+      <c r="R95" s="74"/>
+      <c r="S95" s="75"/>
+      <c r="T95" s="76"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="89"/>
-      <c r="W95" s="90"/>
-      <c r="X95" s="91"/>
+      <c r="V95" s="74"/>
+      <c r="W95" s="75"/>
+      <c r="X95" s="76"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="89"/>
-      <c r="AA95" s="90"/>
-      <c r="AB95" s="91"/>
+      <c r="Z95" s="74"/>
+      <c r="AA95" s="75"/>
+      <c r="AB95" s="76"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="89"/>
-      <c r="AE95" s="90"/>
-      <c r="AF95" s="91"/>
+      <c r="AD95" s="74"/>
+      <c r="AE95" s="75"/>
+      <c r="AF95" s="76"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="89"/>
-      <c r="AI95" s="90"/>
-      <c r="AJ95" s="91"/>
+      <c r="AH95" s="74"/>
+      <c r="AI95" s="75"/>
+      <c r="AJ95" s="76"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="89"/>
-      <c r="AM95" s="90"/>
-      <c r="AN95" s="91"/>
+      <c r="AL95" s="74"/>
+      <c r="AM95" s="75"/>
+      <c r="AN95" s="76"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="85"/>
-      <c r="C96" s="86"/>
-      <c r="D96" s="87"/>
+      <c r="B96" s="77"/>
+      <c r="C96" s="78"/>
+      <c r="D96" s="79"/>
       <c r="E96" s="44"/>
-      <c r="F96" s="85"/>
-      <c r="G96" s="86"/>
-      <c r="H96" s="87"/>
+      <c r="F96" s="77"/>
+      <c r="G96" s="78"/>
+      <c r="H96" s="79"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="85"/>
-      <c r="K96" s="86"/>
-      <c r="L96" s="87"/>
+      <c r="J96" s="77"/>
+      <c r="K96" s="78"/>
+      <c r="L96" s="79"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="85"/>
-      <c r="O96" s="86"/>
-      <c r="P96" s="87"/>
+      <c r="N96" s="77"/>
+      <c r="O96" s="78"/>
+      <c r="P96" s="79"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="85"/>
-      <c r="S96" s="86"/>
-      <c r="T96" s="87"/>
+      <c r="R96" s="77"/>
+      <c r="S96" s="78"/>
+      <c r="T96" s="79"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="85"/>
-      <c r="W96" s="86"/>
-      <c r="X96" s="87"/>
+      <c r="V96" s="77"/>
+      <c r="W96" s="78"/>
+      <c r="X96" s="79"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="85"/>
-      <c r="AA96" s="86"/>
-      <c r="AB96" s="87"/>
+      <c r="Z96" s="77"/>
+      <c r="AA96" s="78"/>
+      <c r="AB96" s="79"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="85"/>
-      <c r="AE96" s="86"/>
-      <c r="AF96" s="87"/>
+      <c r="AD96" s="77"/>
+      <c r="AE96" s="78"/>
+      <c r="AF96" s="79"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="85"/>
-      <c r="AI96" s="86"/>
-      <c r="AJ96" s="87"/>
+      <c r="AH96" s="77"/>
+      <c r="AI96" s="78"/>
+      <c r="AJ96" s="79"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="85"/>
-      <c r="AM96" s="86"/>
-      <c r="AN96" s="87"/>
+      <c r="AL96" s="77"/>
+      <c r="AM96" s="78"/>
+      <c r="AN96" s="79"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35"/>
@@ -7101,69 +7158,69 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="71"/>
-      <c r="C98" s="72"/>
+      <c r="B98" s="83"/>
+      <c r="C98" s="84"/>
       <c r="D98" s="60"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="71"/>
-      <c r="G98" s="72"/>
+      <c r="F98" s="83"/>
+      <c r="G98" s="84"/>
       <c r="H98" s="60"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="71"/>
-      <c r="K98" s="72"/>
+      <c r="J98" s="83"/>
+      <c r="K98" s="84"/>
       <c r="L98" s="60"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="77" t="s">
+      <c r="N98" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="O98" s="78"/>
+      <c r="O98" s="68"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="77" t="s">
+      <c r="R98" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="S98" s="78"/>
+      <c r="S98" s="68"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="77"/>
-      <c r="W98" s="78"/>
+      <c r="V98" s="67"/>
+      <c r="W98" s="68"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="77"/>
-      <c r="AA98" s="78"/>
+      <c r="Z98" s="67"/>
+      <c r="AA98" s="68"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="77"/>
-      <c r="AE98" s="78"/>
+      <c r="AD98" s="67"/>
+      <c r="AE98" s="68"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="77"/>
-      <c r="AI98" s="78"/>
+      <c r="AH98" s="67"/>
+      <c r="AI98" s="68"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="77"/>
-      <c r="AM98" s="78"/>
+      <c r="AL98" s="67"/>
+      <c r="AM98" s="68"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="79"/>
-      <c r="C99" s="80"/>
-      <c r="D99" s="81"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="73"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="79"/>
-      <c r="G99" s="80"/>
-      <c r="H99" s="81"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="72"/>
+      <c r="H99" s="73"/>
       <c r="I99" s="35"/>
-      <c r="J99" s="79"/>
-      <c r="K99" s="80"/>
-      <c r="L99" s="81"/>
+      <c r="J99" s="71"/>
+      <c r="K99" s="72"/>
+      <c r="L99" s="73"/>
       <c r="M99" s="26"/>
       <c r="N99" s="96"/>
       <c r="O99" s="97"/>
@@ -7197,149 +7254,149 @@
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="68"/>
-      <c r="D100" s="88"/>
+      <c r="B100" s="80"/>
+      <c r="C100" s="81"/>
+      <c r="D100" s="82"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="68"/>
-      <c r="H100" s="88"/>
+      <c r="F100" s="80"/>
+      <c r="G100" s="81"/>
+      <c r="H100" s="82"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="67"/>
-      <c r="K100" s="68"/>
-      <c r="L100" s="88"/>
+      <c r="J100" s="80"/>
+      <c r="K100" s="81"/>
+      <c r="L100" s="82"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="63"/>
-      <c r="O100" s="64"/>
+      <c r="N100" s="92"/>
+      <c r="O100" s="93"/>
       <c r="P100" s="99"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="63"/>
-      <c r="S100" s="64"/>
+      <c r="R100" s="92"/>
+      <c r="S100" s="93"/>
       <c r="T100" s="99"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="63"/>
-      <c r="W100" s="64"/>
+      <c r="V100" s="92"/>
+      <c r="W100" s="93"/>
       <c r="X100" s="99"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="63"/>
-      <c r="AA100" s="64"/>
+      <c r="Z100" s="92"/>
+      <c r="AA100" s="93"/>
       <c r="AB100" s="99"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="63"/>
-      <c r="AE100" s="64"/>
+      <c r="AD100" s="92"/>
+      <c r="AE100" s="93"/>
       <c r="AF100" s="99"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="63"/>
-      <c r="AI100" s="64"/>
+      <c r="AH100" s="92"/>
+      <c r="AI100" s="93"/>
       <c r="AJ100" s="99"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="63"/>
-      <c r="AM100" s="64"/>
+      <c r="AL100" s="92"/>
+      <c r="AM100" s="93"/>
       <c r="AN100" s="99"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="89"/>
-      <c r="C101" s="90"/>
-      <c r="D101" s="91"/>
+      <c r="B101" s="74"/>
+      <c r="C101" s="75"/>
+      <c r="D101" s="76"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="89"/>
-      <c r="G101" s="90"/>
-      <c r="H101" s="91"/>
+      <c r="F101" s="74"/>
+      <c r="G101" s="75"/>
+      <c r="H101" s="76"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="89"/>
-      <c r="K101" s="90"/>
-      <c r="L101" s="91"/>
+      <c r="J101" s="74"/>
+      <c r="K101" s="75"/>
+      <c r="L101" s="76"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="89" t="s">
+      <c r="N101" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="O101" s="90"/>
-      <c r="P101" s="91"/>
+      <c r="O101" s="75"/>
+      <c r="P101" s="76"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="89" t="s">
+      <c r="R101" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="S101" s="90"/>
-      <c r="T101" s="91"/>
+      <c r="S101" s="75"/>
+      <c r="T101" s="76"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="89"/>
-      <c r="W101" s="90"/>
-      <c r="X101" s="91"/>
+      <c r="V101" s="74"/>
+      <c r="W101" s="75"/>
+      <c r="X101" s="76"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="89"/>
-      <c r="AA101" s="90"/>
-      <c r="AB101" s="91"/>
+      <c r="Z101" s="74"/>
+      <c r="AA101" s="75"/>
+      <c r="AB101" s="76"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="89"/>
-      <c r="AE101" s="90"/>
-      <c r="AF101" s="91"/>
+      <c r="AD101" s="74"/>
+      <c r="AE101" s="75"/>
+      <c r="AF101" s="76"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="89"/>
-      <c r="AI101" s="90"/>
-      <c r="AJ101" s="91"/>
+      <c r="AH101" s="74"/>
+      <c r="AI101" s="75"/>
+      <c r="AJ101" s="76"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="89"/>
-      <c r="AM101" s="90"/>
-      <c r="AN101" s="91"/>
+      <c r="AL101" s="74"/>
+      <c r="AM101" s="75"/>
+      <c r="AN101" s="76"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="85"/>
-      <c r="C102" s="86"/>
-      <c r="D102" s="87"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="78"/>
+      <c r="D102" s="79"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="86"/>
-      <c r="H102" s="87"/>
+      <c r="F102" s="77"/>
+      <c r="G102" s="78"/>
+      <c r="H102" s="79"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="85"/>
-      <c r="K102" s="86"/>
-      <c r="L102" s="87"/>
+      <c r="J102" s="77"/>
+      <c r="K102" s="78"/>
+      <c r="L102" s="79"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="85"/>
-      <c r="O102" s="86"/>
-      <c r="P102" s="87"/>
+      <c r="N102" s="77"/>
+      <c r="O102" s="78"/>
+      <c r="P102" s="79"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="85"/>
-      <c r="S102" s="86"/>
-      <c r="T102" s="87"/>
+      <c r="R102" s="77"/>
+      <c r="S102" s="78"/>
+      <c r="T102" s="79"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="85"/>
-      <c r="W102" s="86"/>
-      <c r="X102" s="87"/>
+      <c r="V102" s="77"/>
+      <c r="W102" s="78"/>
+      <c r="X102" s="79"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="85"/>
-      <c r="AA102" s="86"/>
-      <c r="AB102" s="87"/>
+      <c r="Z102" s="77"/>
+      <c r="AA102" s="78"/>
+      <c r="AB102" s="79"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="85"/>
-      <c r="AE102" s="86"/>
-      <c r="AF102" s="87"/>
+      <c r="AD102" s="77"/>
+      <c r="AE102" s="78"/>
+      <c r="AF102" s="79"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="85"/>
-      <c r="AI102" s="86"/>
-      <c r="AJ102" s="87"/>
+      <c r="AH102" s="77"/>
+      <c r="AI102" s="78"/>
+      <c r="AJ102" s="79"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="85"/>
-      <c r="AM102" s="86"/>
-      <c r="AN102" s="87"/>
+      <c r="AL102" s="77"/>
+      <c r="AM102" s="78"/>
+      <c r="AN102" s="79"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7385,7 +7442,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7402,21 +7459,21 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="77"/>
-      <c r="C105" s="78"/>
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="67"/>
+      <c r="C105" s="68"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="77"/>
-      <c r="G105" s="78"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="68"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="77"/>
-      <c r="K105" s="78"/>
+      <c r="J105" s="67"/>
+      <c r="K105" s="68"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="96"/>
       <c r="C106" s="97"/>
       <c r="D106" s="98"/>
@@ -7429,46 +7486,46 @@
       <c r="K106" s="97"/>
       <c r="L106" s="98"/>
     </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="63"/>
-      <c r="C107" s="64"/>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="92"/>
+      <c r="C107" s="93"/>
       <c r="D107" s="99"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="63"/>
-      <c r="G107" s="64"/>
+      <c r="F107" s="92"/>
+      <c r="G107" s="93"/>
       <c r="H107" s="99"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="63"/>
-      <c r="K107" s="64"/>
+      <c r="J107" s="92"/>
+      <c r="K107" s="93"/>
       <c r="L107" s="99"/>
     </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="89"/>
-      <c r="C108" s="90"/>
-      <c r="D108" s="91"/>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="74"/>
+      <c r="C108" s="75"/>
+      <c r="D108" s="76"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="89"/>
-      <c r="G108" s="90"/>
-      <c r="H108" s="91"/>
+      <c r="F108" s="74"/>
+      <c r="G108" s="75"/>
+      <c r="H108" s="76"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="89"/>
-      <c r="K108" s="90"/>
-      <c r="L108" s="91"/>
-    </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="85"/>
-      <c r="C109" s="86"/>
-      <c r="D109" s="87"/>
+      <c r="J108" s="74"/>
+      <c r="K108" s="75"/>
+      <c r="L108" s="76"/>
+    </row>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="77"/>
+      <c r="C109" s="78"/>
+      <c r="D109" s="79"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="85"/>
-      <c r="G109" s="86"/>
-      <c r="H109" s="87"/>
+      <c r="F109" s="77"/>
+      <c r="G109" s="78"/>
+      <c r="H109" s="79"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="85"/>
-      <c r="K109" s="86"/>
-      <c r="L109" s="87"/>
-    </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J109" s="77"/>
+      <c r="K109" s="78"/>
+      <c r="L109" s="79"/>
+    </row>
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7481,20 +7538,20 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="77"/>
-      <c r="C111" s="78"/>
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="67"/>
+      <c r="C111" s="68"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="77"/>
-      <c r="G111" s="78"/>
+      <c r="F111" s="67"/>
+      <c r="G111" s="68"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="77"/>
-      <c r="K111" s="78"/>
+      <c r="J111" s="67"/>
+      <c r="K111" s="68"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="96"/>
       <c r="C112" s="97"/>
       <c r="D112" s="98"/>
@@ -7507,46 +7564,46 @@
       <c r="K112" s="97"/>
       <c r="L112" s="98"/>
     </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="63"/>
-      <c r="C113" s="64"/>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="92"/>
+      <c r="C113" s="93"/>
       <c r="D113" s="99"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="63"/>
-      <c r="G113" s="64"/>
+      <c r="F113" s="92"/>
+      <c r="G113" s="93"/>
       <c r="H113" s="99"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="63"/>
-      <c r="K113" s="64"/>
+      <c r="J113" s="92"/>
+      <c r="K113" s="93"/>
       <c r="L113" s="99"/>
     </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="89"/>
-      <c r="C114" s="90"/>
-      <c r="D114" s="91"/>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="74"/>
+      <c r="C114" s="75"/>
+      <c r="D114" s="76"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="89"/>
-      <c r="G114" s="90"/>
-      <c r="H114" s="91"/>
+      <c r="F114" s="74"/>
+      <c r="G114" s="75"/>
+      <c r="H114" s="76"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="89"/>
-      <c r="K114" s="90"/>
-      <c r="L114" s="91"/>
-    </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="85"/>
-      <c r="C115" s="86"/>
-      <c r="D115" s="87"/>
+      <c r="J114" s="74"/>
+      <c r="K114" s="75"/>
+      <c r="L114" s="76"/>
+    </row>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="77"/>
+      <c r="C115" s="78"/>
+      <c r="D115" s="79"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="85"/>
-      <c r="G115" s="86"/>
-      <c r="H115" s="87"/>
+      <c r="F115" s="77"/>
+      <c r="G115" s="78"/>
+      <c r="H115" s="79"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="85"/>
-      <c r="K115" s="86"/>
-      <c r="L115" s="87"/>
-    </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J115" s="77"/>
+      <c r="K115" s="78"/>
+      <c r="L115" s="79"/>
+    </row>
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -7559,20 +7616,20 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="77"/>
-      <c r="C117" s="78"/>
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="67"/>
+      <c r="C117" s="68"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="77"/>
-      <c r="G117" s="78"/>
+      <c r="F117" s="67"/>
+      <c r="G117" s="68"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="77"/>
-      <c r="K117" s="78"/>
+      <c r="J117" s="67"/>
+      <c r="K117" s="68"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B118" s="96"/>
       <c r="C118" s="97"/>
       <c r="D118" s="98"/>
@@ -7585,46 +7642,46 @@
       <c r="K118" s="97"/>
       <c r="L118" s="98"/>
     </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="63"/>
-      <c r="C119" s="64"/>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="92"/>
+      <c r="C119" s="93"/>
       <c r="D119" s="99"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="63"/>
-      <c r="G119" s="64"/>
+      <c r="F119" s="92"/>
+      <c r="G119" s="93"/>
       <c r="H119" s="99"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="63"/>
-      <c r="K119" s="64"/>
+      <c r="J119" s="92"/>
+      <c r="K119" s="93"/>
       <c r="L119" s="99"/>
     </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="89"/>
-      <c r="C120" s="90"/>
-      <c r="D120" s="91"/>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="74"/>
+      <c r="C120" s="75"/>
+      <c r="D120" s="76"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="89"/>
-      <c r="G120" s="90"/>
-      <c r="H120" s="91"/>
+      <c r="F120" s="74"/>
+      <c r="G120" s="75"/>
+      <c r="H120" s="76"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="89"/>
-      <c r="K120" s="90"/>
-      <c r="L120" s="91"/>
-    </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="85"/>
-      <c r="C121" s="86"/>
-      <c r="D121" s="87"/>
+      <c r="J120" s="74"/>
+      <c r="K120" s="75"/>
+      <c r="L120" s="76"/>
+    </row>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="77"/>
+      <c r="C121" s="78"/>
+      <c r="D121" s="79"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="85"/>
-      <c r="G121" s="86"/>
-      <c r="H121" s="87"/>
+      <c r="F121" s="77"/>
+      <c r="G121" s="78"/>
+      <c r="H121" s="79"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="85"/>
-      <c r="K121" s="86"/>
-      <c r="L121" s="87"/>
-    </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J121" s="77"/>
+      <c r="K121" s="78"/>
+      <c r="L121" s="79"/>
+    </row>
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -7637,20 +7694,20 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="77"/>
-      <c r="C123" s="78"/>
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="67"/>
+      <c r="C123" s="68"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="77"/>
-      <c r="G123" s="78"/>
+      <c r="F123" s="67"/>
+      <c r="G123" s="68"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="77"/>
-      <c r="K123" s="78"/>
+      <c r="J123" s="67"/>
+      <c r="K123" s="68"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="96"/>
       <c r="C124" s="97"/>
       <c r="D124" s="98"/>
@@ -7663,46 +7720,46 @@
       <c r="K124" s="97"/>
       <c r="L124" s="98"/>
     </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="63"/>
-      <c r="C125" s="64"/>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="92"/>
+      <c r="C125" s="93"/>
       <c r="D125" s="99"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="63"/>
-      <c r="G125" s="64"/>
+      <c r="F125" s="92"/>
+      <c r="G125" s="93"/>
       <c r="H125" s="99"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="63"/>
-      <c r="K125" s="64"/>
+      <c r="J125" s="92"/>
+      <c r="K125" s="93"/>
       <c r="L125" s="99"/>
     </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="89"/>
-      <c r="C126" s="90"/>
-      <c r="D126" s="91"/>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="74"/>
+      <c r="C126" s="75"/>
+      <c r="D126" s="76"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="89"/>
-      <c r="G126" s="90"/>
-      <c r="H126" s="91"/>
+      <c r="F126" s="74"/>
+      <c r="G126" s="75"/>
+      <c r="H126" s="76"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="89"/>
-      <c r="K126" s="90"/>
-      <c r="L126" s="91"/>
-    </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="85"/>
-      <c r="C127" s="86"/>
-      <c r="D127" s="87"/>
+      <c r="J126" s="74"/>
+      <c r="K126" s="75"/>
+      <c r="L126" s="76"/>
+    </row>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="77"/>
+      <c r="C127" s="78"/>
+      <c r="D127" s="79"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="85"/>
-      <c r="G127" s="86"/>
-      <c r="H127" s="87"/>
+      <c r="F127" s="77"/>
+      <c r="G127" s="78"/>
+      <c r="H127" s="79"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="85"/>
-      <c r="K127" s="86"/>
-      <c r="L127" s="87"/>
-    </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J127" s="77"/>
+      <c r="K127" s="78"/>
+      <c r="L127" s="79"/>
+    </row>
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -7715,20 +7772,20 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="77"/>
-      <c r="C129" s="78"/>
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="67"/>
+      <c r="C129" s="68"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="77"/>
-      <c r="G129" s="78"/>
+      <c r="F129" s="67"/>
+      <c r="G129" s="68"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="77"/>
-      <c r="K129" s="78"/>
+      <c r="J129" s="67"/>
+      <c r="K129" s="68"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B130" s="96"/>
       <c r="C130" s="97"/>
       <c r="D130" s="98"/>
@@ -7741,44 +7798,44 @@
       <c r="K130" s="97"/>
       <c r="L130" s="98"/>
     </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="63"/>
-      <c r="C131" s="64"/>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="92"/>
+      <c r="C131" s="93"/>
       <c r="D131" s="99"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="63"/>
-      <c r="G131" s="64"/>
+      <c r="F131" s="92"/>
+      <c r="G131" s="93"/>
       <c r="H131" s="99"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="63"/>
-      <c r="K131" s="64"/>
+      <c r="J131" s="92"/>
+      <c r="K131" s="93"/>
       <c r="L131" s="99"/>
     </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="89"/>
-      <c r="C132" s="90"/>
-      <c r="D132" s="91"/>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="74"/>
+      <c r="C132" s="75"/>
+      <c r="D132" s="76"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="89"/>
-      <c r="G132" s="90"/>
-      <c r="H132" s="91"/>
+      <c r="F132" s="74"/>
+      <c r="G132" s="75"/>
+      <c r="H132" s="76"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="89"/>
-      <c r="K132" s="90"/>
-      <c r="L132" s="91"/>
-    </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="85"/>
-      <c r="C133" s="86"/>
-      <c r="D133" s="87"/>
+      <c r="J132" s="74"/>
+      <c r="K132" s="75"/>
+      <c r="L132" s="76"/>
+    </row>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="77"/>
+      <c r="C133" s="78"/>
+      <c r="D133" s="79"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="85"/>
-      <c r="G133" s="86"/>
-      <c r="H133" s="87"/>
+      <c r="F133" s="77"/>
+      <c r="G133" s="78"/>
+      <c r="H133" s="79"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="85"/>
-      <c r="K133" s="86"/>
-      <c r="L133" s="87"/>
+      <c r="J133" s="77"/>
+      <c r="K133" s="78"/>
+      <c r="L133" s="79"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
@@ -7860,17 +7917,6 @@
     <mergeCell ref="N78:P78"/>
     <mergeCell ref="Z80:AA80"/>
     <mergeCell ref="R78:T78"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="V81:X81"/>
     <mergeCell ref="J77:L77"/>
     <mergeCell ref="J72:L72"/>
     <mergeCell ref="J74:K74"/>
@@ -7881,6 +7927,10 @@
     <mergeCell ref="J64:L64"/>
     <mergeCell ref="F69:H69"/>
     <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="J76:L76"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B57:D57"/>
@@ -7943,7 +7993,6 @@
     <mergeCell ref="J48:L48"/>
     <mergeCell ref="N50:P50"/>
     <mergeCell ref="J52:K52"/>
-    <mergeCell ref="R42:T42"/>
     <mergeCell ref="N47:P47"/>
     <mergeCell ref="N46:P46"/>
     <mergeCell ref="R45:S45"/>
@@ -7967,6 +8016,7 @@
     <mergeCell ref="J90:L90"/>
     <mergeCell ref="J100:L100"/>
     <mergeCell ref="J88:L88"/>
+    <mergeCell ref="V81:X81"/>
     <mergeCell ref="J89:L89"/>
     <mergeCell ref="N56:P56"/>
     <mergeCell ref="J61:L61"/>
@@ -7978,6 +8028,19 @@
     <mergeCell ref="R94:T94"/>
     <mergeCell ref="R92:S92"/>
     <mergeCell ref="N93:P93"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="V88:X88"/>
     <mergeCell ref="Z102:AB102"/>
     <mergeCell ref="N99:P99"/>
     <mergeCell ref="R99:T99"/>
@@ -8436,6 +8499,11 @@
     <mergeCell ref="V74:W74"/>
     <mergeCell ref="AD77:AF77"/>
     <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="Z76:AB76"/>
     <mergeCell ref="AL102:AN102"/>
     <mergeCell ref="AL101:AN101"/>
     <mergeCell ref="AL96:AN96"/>
@@ -8508,20 +8576,6 @@
     <mergeCell ref="V82:X82"/>
     <mergeCell ref="N80:O80"/>
     <mergeCell ref="J80:K80"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="V88:X88"/>
     <mergeCell ref="V89:X89"/>
     <mergeCell ref="N59:O59"/>
     <mergeCell ref="V78:X78"/>
@@ -8535,6 +8589,8 @@
     <mergeCell ref="N68:O68"/>
     <mergeCell ref="R68:S68"/>
     <mergeCell ref="R77:T77"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N74:O74"/>
     <mergeCell ref="V55:X55"/>
     <mergeCell ref="Z64:AB64"/>
     <mergeCell ref="Z69:AB69"/>
@@ -8615,6 +8671,21 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="J22:K22"/>
     <mergeCell ref="J33:L33"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B24:C24"/>
@@ -8633,30 +8704,8 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="F34:H34"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J24:K24"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N24:O24"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="R27:S27"/>
@@ -8665,6 +8714,14 @@
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="R23:S23"/>
     <mergeCell ref="F23:G23"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="R42:T42"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AB22:AB27 AJ22:AJ27 AF22:AF27 AN22:AN27 T22:T27 L22:L27 H22:H27 D22:D27">

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="87">
   <si>
     <t>CUMA</t>
   </si>
@@ -285,15 +285,6 @@
   </si>
   <si>
     <t>Sultanahmet</t>
-  </si>
-  <si>
-    <t>16.00</t>
-  </si>
-  <si>
-    <t>Ç.TAŞ.</t>
-  </si>
-  <si>
-    <t>M.DİNER.</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1338,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1509,23 +1500,209 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1533,136 +1710,19 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="12" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="13" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="14" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="15" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="8" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1672,102 +1732,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="9" borderId="14" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="9" borderId="15" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="9" borderId="16" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="8" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="9" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="9" borderId="10" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2219,65 +2183,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="126" t="s">
+      <c r="B1" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="127" t="s">
+      <c r="F1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="127" t="s">
+      <c r="J1" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="127"/>
-      <c r="L1" s="128"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="123"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="131" t="s">
+      <c r="N1" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="125" t="s">
+      <c r="R1" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="125" t="s">
+      <c r="V1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="125" t="s">
+      <c r="Z1" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="125" t="s">
+      <c r="AD1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
+      <c r="AE1" s="116"/>
+      <c r="AF1" s="116"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="125" t="s">
+      <c r="AH1" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
+      <c r="AI1" s="116"/>
+      <c r="AJ1" s="116"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="125"/>
-      <c r="AN1" s="135"/>
+      <c r="AM1" s="116"/>
+      <c r="AN1" s="117"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2285,74 +2249,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="129">
+      <c r="B2" s="124">
         <f>N2-3</f>
         <v>46213</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="130">
+      <c r="F2" s="125">
         <f>N2-2</f>
         <v>46214</v>
       </c>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="130">
+      <c r="J2" s="125">
         <f>N2-1</f>
         <v>46215</v>
       </c>
-      <c r="K2" s="130"/>
-      <c r="L2" s="133"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="128"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="132">
+      <c r="N2" s="127">
         <v>46216</v>
       </c>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="118"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="121">
+      <c r="R2" s="118">
         <f>N2+1</f>
         <v>46217</v>
       </c>
-      <c r="S2" s="121"/>
-      <c r="T2" s="121"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="121">
+      <c r="V2" s="118">
         <f>N2+2</f>
         <v>46218</v>
       </c>
-      <c r="W2" s="121"/>
-      <c r="X2" s="121"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="118"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="121">
+      <c r="Z2" s="118">
         <f>N2+3</f>
         <v>46219</v>
       </c>
-      <c r="AA2" s="121"/>
-      <c r="AB2" s="121"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="121">
+      <c r="AD2" s="118">
         <f>N2+4</f>
         <v>46220</v>
       </c>
-      <c r="AE2" s="121"/>
-      <c r="AF2" s="121"/>
+      <c r="AE2" s="118"/>
+      <c r="AF2" s="118"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="121">
+      <c r="AH2" s="118">
         <f>N2+5</f>
         <v>46221</v>
       </c>
-      <c r="AI2" s="121"/>
-      <c r="AJ2" s="121"/>
+      <c r="AI2" s="118"/>
+      <c r="AJ2" s="118"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="121">
+      <c r="AL2" s="118">
         <f>N2+6</f>
         <v>46222</v>
       </c>
-      <c r="AM2" s="121"/>
-      <c r="AN2" s="136"/>
+      <c r="AM2" s="118"/>
+      <c r="AN2" s="119"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2406,47 +2370,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="109" t="s">
+      <c r="N4" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="109"/>
-      <c r="P4" s="109"/>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="109"/>
-      <c r="S4" s="109"/>
-      <c r="T4" s="109"/>
-      <c r="U4" s="109"/>
-      <c r="V4" s="109"/>
-      <c r="W4" s="109"/>
-      <c r="X4" s="109"/>
-      <c r="Y4" s="109"/>
-      <c r="Z4" s="109"/>
-      <c r="AA4" s="109"/>
-      <c r="AB4" s="109"/>
+      <c r="O4" s="100"/>
+      <c r="P4" s="100"/>
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="100"/>
+      <c r="W4" s="100"/>
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="134"/>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="134"/>
-      <c r="AG4" s="134"/>
-      <c r="AH4" s="134"/>
-      <c r="AI4" s="134"/>
-      <c r="AJ4" s="134"/>
-      <c r="AK4" s="134"/>
-      <c r="AL4" s="134"/>
-      <c r="AM4" s="134"/>
-      <c r="AN4" s="134"/>
+      <c r="AD4" s="120"/>
+      <c r="AE4" s="120"/>
+      <c r="AF4" s="120"/>
+      <c r="AG4" s="120"/>
+      <c r="AH4" s="120"/>
+      <c r="AI4" s="120"/>
+      <c r="AJ4" s="120"/>
+      <c r="AK4" s="120"/>
+      <c r="AL4" s="120"/>
+      <c r="AM4" s="120"/>
+      <c r="AN4" s="120"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2454,89 +2418,89 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="109"/>
-      <c r="S5" s="109"/>
-      <c r="T5" s="109"/>
-      <c r="U5" s="109"/>
-      <c r="V5" s="109"/>
-      <c r="W5" s="109"/>
-      <c r="X5" s="109"/>
-      <c r="Y5" s="109"/>
-      <c r="Z5" s="109"/>
-      <c r="AA5" s="109"/>
-      <c r="AB5" s="109"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="100"/>
+      <c r="U5" s="100"/>
+      <c r="V5" s="100"/>
+      <c r="W5" s="100"/>
+      <c r="X5" s="100"/>
+      <c r="Y5" s="100"/>
+      <c r="Z5" s="100"/>
+      <c r="AA5" s="100"/>
+      <c r="AB5" s="100"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="134"/>
-      <c r="AE5" s="134"/>
-      <c r="AF5" s="134"/>
-      <c r="AG5" s="134"/>
-      <c r="AH5" s="134"/>
-      <c r="AI5" s="134"/>
-      <c r="AJ5" s="134"/>
-      <c r="AK5" s="134"/>
-      <c r="AL5" s="134"/>
-      <c r="AM5" s="134"/>
-      <c r="AN5" s="134"/>
+      <c r="AD5" s="120"/>
+      <c r="AE5" s="120"/>
+      <c r="AF5" s="120"/>
+      <c r="AG5" s="120"/>
+      <c r="AH5" s="120"/>
+      <c r="AI5" s="120"/>
+      <c r="AJ5" s="120"/>
+      <c r="AK5" s="120"/>
+      <c r="AL5" s="120"/>
+      <c r="AM5" s="120"/>
+      <c r="AN5" s="120"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="83"/>
-      <c r="C6" s="84"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="89"/>
       <c r="D6" s="60"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="84"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="89"/>
       <c r="H6" s="60"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="84"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="89"/>
       <c r="L6" s="60"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="68"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="76"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="68"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="76"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="68"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="76"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="68"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="76"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="68"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="76"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="68"/>
+      <c r="AH6" s="75"/>
+      <c r="AI6" s="76"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="67"/>
-      <c r="AM6" s="68"/>
+      <c r="AL6" s="75"/>
+      <c r="AM6" s="76"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2548,44 +2512,44 @@
       <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="61"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="81"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="64"/>
       <c r="H7" s="61"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="81"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="64"/>
       <c r="L7" s="61"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="93"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="86"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="92"/>
-      <c r="S7" s="93"/>
+      <c r="R7" s="85"/>
+      <c r="S7" s="86"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="92"/>
-      <c r="W7" s="93"/>
+      <c r="V7" s="85"/>
+      <c r="W7" s="86"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="92"/>
-      <c r="AA7" s="93"/>
+      <c r="Z7" s="85"/>
+      <c r="AA7" s="86"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="92"/>
-      <c r="AE7" s="93"/>
+      <c r="AD7" s="85"/>
+      <c r="AE7" s="86"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="92"/>
-      <c r="AI7" s="93"/>
+      <c r="AH7" s="85"/>
+      <c r="AI7" s="86"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="92"/>
-      <c r="AM7" s="93"/>
+      <c r="AL7" s="85"/>
+      <c r="AM7" s="86"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2597,94 +2561,94 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="74"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="76"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="68"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="76"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="68"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="76"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="68"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="76"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="67"/>
+      <c r="P8" s="68"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="74"/>
-      <c r="S8" s="75"/>
-      <c r="T8" s="76"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="68"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="75"/>
-      <c r="X8" s="76"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="68"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="74"/>
-      <c r="AA8" s="75"/>
-      <c r="AB8" s="76"/>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="68"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="74"/>
-      <c r="AE8" s="75"/>
-      <c r="AF8" s="76"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="68"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="74"/>
-      <c r="AI8" s="75"/>
-      <c r="AJ8" s="76"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="68"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="74"/>
-      <c r="AM8" s="75"/>
-      <c r="AN8" s="76"/>
+      <c r="AL8" s="66"/>
+      <c r="AM8" s="67"/>
+      <c r="AN8" s="68"/>
       <c r="AP8" s="46" t="s">
         <v>16</v>
       </c>
       <c r="AQ8" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="87"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="89"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="79"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="89"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="88"/>
-      <c r="L9" s="89"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="79"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="87"/>
-      <c r="O9" s="88"/>
-      <c r="P9" s="89"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="79"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="87"/>
-      <c r="S9" s="88"/>
-      <c r="T9" s="89"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="78"/>
+      <c r="T9" s="79"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="88"/>
-      <c r="X9" s="89"/>
+      <c r="V9" s="77"/>
+      <c r="W9" s="78"/>
+      <c r="X9" s="79"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="87"/>
-      <c r="AA9" s="88"/>
-      <c r="AB9" s="89"/>
+      <c r="Z9" s="77"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="79"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="87"/>
-      <c r="AE9" s="88"/>
-      <c r="AF9" s="89"/>
+      <c r="AD9" s="77"/>
+      <c r="AE9" s="78"/>
+      <c r="AF9" s="79"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="87"/>
-      <c r="AI9" s="88"/>
-      <c r="AJ9" s="89"/>
+      <c r="AH9" s="77"/>
+      <c r="AI9" s="78"/>
+      <c r="AJ9" s="79"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="87"/>
-      <c r="AM9" s="88"/>
-      <c r="AN9" s="89"/>
+      <c r="AL9" s="77"/>
+      <c r="AM9" s="78"/>
+      <c r="AN9" s="79"/>
       <c r="AP9" s="46" t="s">
         <v>11</v>
       </c>
@@ -2695,45 +2659,45 @@
       <c r="AR9" s="30"/>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="122"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="124"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="97"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="123"/>
-      <c r="H10" s="124"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="97"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="122"/>
-      <c r="K10" s="123"/>
-      <c r="L10" s="124"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="97"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="122"/>
-      <c r="O10" s="123"/>
-      <c r="P10" s="124"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="97"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="122"/>
-      <c r="S10" s="123"/>
-      <c r="T10" s="124"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="97"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="122"/>
-      <c r="W10" s="123"/>
-      <c r="X10" s="124"/>
+      <c r="V10" s="95"/>
+      <c r="W10" s="96"/>
+      <c r="X10" s="97"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="122"/>
-      <c r="AA10" s="123"/>
-      <c r="AB10" s="124"/>
+      <c r="Z10" s="95"/>
+      <c r="AA10" s="96"/>
+      <c r="AB10" s="97"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="122"/>
-      <c r="AE10" s="123"/>
-      <c r="AF10" s="124"/>
+      <c r="AD10" s="95"/>
+      <c r="AE10" s="96"/>
+      <c r="AF10" s="97"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="122"/>
-      <c r="AI10" s="123"/>
-      <c r="AJ10" s="124"/>
+      <c r="AH10" s="95"/>
+      <c r="AI10" s="96"/>
+      <c r="AJ10" s="97"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="122"/>
-      <c r="AM10" s="123"/>
-      <c r="AN10" s="124"/>
+      <c r="AL10" s="95"/>
+      <c r="AM10" s="96"/>
+      <c r="AN10" s="97"/>
       <c r="AP10" s="46" t="s">
         <v>8</v>
       </c>
@@ -2793,44 +2757,44 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="83"/>
-      <c r="C12" s="84"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="89"/>
       <c r="D12" s="60"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="84"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="89"/>
       <c r="H12" s="60"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="84"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="89"/>
       <c r="L12" s="60"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="68"/>
+      <c r="N12" s="75"/>
+      <c r="O12" s="76"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="67"/>
-      <c r="S12" s="68"/>
+      <c r="R12" s="75"/>
+      <c r="S12" s="76"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="67"/>
-      <c r="W12" s="68"/>
+      <c r="V12" s="75"/>
+      <c r="W12" s="76"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="67"/>
-      <c r="AA12" s="68"/>
+      <c r="Z12" s="75"/>
+      <c r="AA12" s="76"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="67"/>
-      <c r="AE12" s="68"/>
+      <c r="AD12" s="75"/>
+      <c r="AE12" s="76"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="67"/>
-      <c r="AI12" s="68"/>
+      <c r="AH12" s="75"/>
+      <c r="AI12" s="76"/>
       <c r="AJ12" s="34"/>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="67"/>
-      <c r="AM12" s="68"/>
+      <c r="AL12" s="75"/>
+      <c r="AM12" s="76"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2842,45 +2806,45 @@
       <c r="AR12" s="30"/>
     </row>
     <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="61"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="73"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="74"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="73"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="74"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="98"/>
+      <c r="N13" s="82"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="84"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="97"/>
-      <c r="T13" s="98"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="84"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="97"/>
-      <c r="X13" s="98"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="83"/>
+      <c r="X13" s="84"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="92"/>
-      <c r="AA13" s="93"/>
+      <c r="Z13" s="85"/>
+      <c r="AA13" s="86"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="92"/>
-      <c r="AE13" s="93"/>
+      <c r="AD13" s="85"/>
+      <c r="AE13" s="86"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="96"/>
-      <c r="AI13" s="97"/>
-      <c r="AJ13" s="98"/>
+      <c r="AH13" s="82"/>
+      <c r="AI13" s="83"/>
+      <c r="AJ13" s="84"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="96"/>
-      <c r="AM13" s="97"/>
-      <c r="AN13" s="98"/>
+      <c r="AL13" s="82"/>
+      <c r="AM13" s="83"/>
+      <c r="AN13" s="84"/>
       <c r="AP13" s="62" t="s">
         <v>22</v>
       </c>
@@ -2893,45 +2857,45 @@
       </c>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="74"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="76"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="68"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="76"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="76"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="68"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="76"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="68"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="76"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="68"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="74"/>
-      <c r="W14" s="75"/>
-      <c r="X14" s="76"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="67"/>
+      <c r="X14" s="68"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="74"/>
-      <c r="AA14" s="75"/>
-      <c r="AB14" s="76"/>
+      <c r="Z14" s="66"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="68"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="74"/>
-      <c r="AE14" s="75"/>
-      <c r="AF14" s="76"/>
+      <c r="AD14" s="66"/>
+      <c r="AE14" s="67"/>
+      <c r="AF14" s="68"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="74"/>
-      <c r="AI14" s="75"/>
-      <c r="AJ14" s="76"/>
+      <c r="AH14" s="66"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="68"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="74"/>
-      <c r="AM14" s="75"/>
-      <c r="AN14" s="76"/>
+      <c r="AL14" s="66"/>
+      <c r="AM14" s="67"/>
+      <c r="AN14" s="68"/>
       <c r="AP14" s="62" t="s">
         <v>23</v>
       </c>
@@ -2944,45 +2908,45 @@
       </c>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="87"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="89"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="89"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="79"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="89"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="79"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="87"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="89"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="79"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="87"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="89"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="79"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="88"/>
-      <c r="X15" s="89"/>
+      <c r="V15" s="77"/>
+      <c r="W15" s="78"/>
+      <c r="X15" s="79"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="87"/>
-      <c r="AA15" s="88"/>
-      <c r="AB15" s="89"/>
+      <c r="Z15" s="77"/>
+      <c r="AA15" s="78"/>
+      <c r="AB15" s="79"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="87"/>
-      <c r="AE15" s="88"/>
-      <c r="AF15" s="89"/>
+      <c r="AD15" s="77"/>
+      <c r="AE15" s="78"/>
+      <c r="AF15" s="79"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="87"/>
-      <c r="AI15" s="88"/>
-      <c r="AJ15" s="89"/>
+      <c r="AH15" s="77"/>
+      <c r="AI15" s="78"/>
+      <c r="AJ15" s="79"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="87"/>
-      <c r="AM15" s="88"/>
-      <c r="AN15" s="89"/>
+      <c r="AL15" s="77"/>
+      <c r="AM15" s="78"/>
+      <c r="AN15" s="79"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2993,45 +2957,45 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="122"/>
-      <c r="C16" s="123"/>
-      <c r="D16" s="124"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="97"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="123"/>
-      <c r="H16" s="124"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="97"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="122"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="124"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="97"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="122"/>
-      <c r="O16" s="123"/>
-      <c r="P16" s="124"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="97"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="122"/>
-      <c r="S16" s="123"/>
-      <c r="T16" s="124"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="97"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="122"/>
-      <c r="W16" s="123"/>
-      <c r="X16" s="124"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="96"/>
+      <c r="X16" s="97"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="122"/>
-      <c r="AA16" s="123"/>
-      <c r="AB16" s="124"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="96"/>
+      <c r="AB16" s="97"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="122"/>
-      <c r="AE16" s="123"/>
-      <c r="AF16" s="124"/>
+      <c r="AD16" s="95"/>
+      <c r="AE16" s="96"/>
+      <c r="AF16" s="97"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="122"/>
-      <c r="AI16" s="123"/>
-      <c r="AJ16" s="124"/>
+      <c r="AH16" s="95"/>
+      <c r="AI16" s="96"/>
+      <c r="AJ16" s="97"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="122"/>
-      <c r="AM16" s="123"/>
-      <c r="AN16" s="124"/>
+      <c r="AL16" s="95"/>
+      <c r="AM16" s="96"/>
+      <c r="AN16" s="97"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3103,23 +3067,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="109" t="s">
+      <c r="N18" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="109"/>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="109"/>
-      <c r="R18" s="109"/>
-      <c r="S18" s="109"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="109"/>
-      <c r="W18" s="109"/>
-      <c r="X18" s="109"/>
-      <c r="Y18" s="109"/>
-      <c r="Z18" s="109"/>
-      <c r="AA18" s="109"/>
-      <c r="AB18" s="109"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3156,21 +3120,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="109"/>
-      <c r="O19" s="109"/>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="109"/>
-      <c r="R19" s="109"/>
-      <c r="S19" s="109"/>
-      <c r="T19" s="109"/>
-      <c r="U19" s="109"/>
-      <c r="V19" s="109"/>
-      <c r="W19" s="109"/>
-      <c r="X19" s="109"/>
-      <c r="Y19" s="109"/>
-      <c r="Z19" s="109"/>
-      <c r="AA19" s="109"/>
-      <c r="AB19" s="109"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="100"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="100"/>
+      <c r="AB19" s="100"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3195,44 +3159,44 @@
       </c>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="83"/>
-      <c r="C20" s="84"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="89"/>
       <c r="D20" s="60"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="84"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="89"/>
       <c r="H20" s="60"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="89"/>
       <c r="L20" s="60"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="68"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="76"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="140"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="99"/>
       <c r="T20" s="56"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="139"/>
-      <c r="W20" s="140"/>
+      <c r="V20" s="98"/>
+      <c r="W20" s="99"/>
       <c r="X20" s="56"/>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="139"/>
-      <c r="AA20" s="140"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="99"/>
       <c r="AB20" s="56"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="67"/>
-      <c r="AE20" s="68"/>
+      <c r="AD20" s="75"/>
+      <c r="AE20" s="76"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="67"/>
-      <c r="AI20" s="68"/>
+      <c r="AH20" s="75"/>
+      <c r="AI20" s="76"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="67"/>
-      <c r="AM20" s="68"/>
+      <c r="AL20" s="75"/>
+      <c r="AM20" s="76"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3244,44 +3208,44 @@
       <c r="AR20" s="30"/>
     </row>
     <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="80"/>
-      <c r="C21" s="81"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="64"/>
       <c r="D21" s="61"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="81"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="64"/>
       <c r="H21" s="61"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="81"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="64"/>
       <c r="L21" s="61"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="93"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="86"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="92"/>
-      <c r="S21" s="93"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="86"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="137"/>
-      <c r="W21" s="138"/>
+      <c r="V21" s="105"/>
+      <c r="W21" s="106"/>
       <c r="X21" s="57"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="137"/>
-      <c r="AA21" s="138"/>
+      <c r="Z21" s="105"/>
+      <c r="AA21" s="106"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="92"/>
-      <c r="AE21" s="93"/>
+      <c r="AD21" s="85"/>
+      <c r="AE21" s="86"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="92"/>
-      <c r="AI21" s="93"/>
+      <c r="AH21" s="85"/>
+      <c r="AI21" s="86"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="92"/>
-      <c r="AM21" s="93"/>
+      <c r="AL21" s="85"/>
+      <c r="AM21" s="86"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="62" t="s">
         <v>12</v>
@@ -3295,44 +3259,44 @@
       </c>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="85"/>
-      <c r="C22" s="86"/>
+      <c r="B22" s="133"/>
+      <c r="C22" s="134"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="86"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="134"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="85"/>
-      <c r="K22" s="86"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="134"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="95"/>
+      <c r="N22" s="129"/>
+      <c r="O22" s="130"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="95"/>
+      <c r="R22" s="129"/>
+      <c r="S22" s="130"/>
       <c r="T22" s="41"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="94"/>
-      <c r="W22" s="95"/>
+      <c r="V22" s="129"/>
+      <c r="W22" s="130"/>
       <c r="X22" s="58"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="94"/>
-      <c r="AA22" s="95"/>
+      <c r="Z22" s="129"/>
+      <c r="AA22" s="130"/>
       <c r="AB22" s="58"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="85"/>
-      <c r="AE22" s="86"/>
+      <c r="AD22" s="133"/>
+      <c r="AE22" s="134"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="85"/>
-      <c r="AI22" s="86"/>
+      <c r="AH22" s="133"/>
+      <c r="AI22" s="134"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="94"/>
-      <c r="AM22" s="95"/>
+      <c r="AL22" s="129"/>
+      <c r="AM22" s="130"/>
       <c r="AN22" s="41"/>
       <c r="AP22" s="46" t="s">
         <v>15</v>
@@ -3344,44 +3308,44 @@
       <c r="AR22" s="30"/>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="69"/>
-      <c r="C23" s="70"/>
+      <c r="B23" s="131"/>
+      <c r="C23" s="132"/>
       <c r="D23" s="45"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="70"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="132"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="70"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="132"/>
       <c r="L23" s="45"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="70"/>
+      <c r="N23" s="131"/>
+      <c r="O23" s="132"/>
       <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="70"/>
+      <c r="R23" s="131"/>
+      <c r="S23" s="132"/>
       <c r="T23" s="45"/>
       <c r="U23" s="43"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="70"/>
+      <c r="V23" s="131"/>
+      <c r="W23" s="132"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="69"/>
-      <c r="AA23" s="70"/>
+      <c r="Z23" s="131"/>
+      <c r="AA23" s="132"/>
       <c r="AB23" s="45"/>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="69"/>
-      <c r="AE23" s="70"/>
+      <c r="AD23" s="131"/>
+      <c r="AE23" s="132"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="69"/>
-      <c r="AI23" s="70"/>
+      <c r="AH23" s="131"/>
+      <c r="AI23" s="132"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="69"/>
-      <c r="AM23" s="70"/>
+      <c r="AL23" s="131"/>
+      <c r="AM23" s="132"/>
       <c r="AN23" s="45"/>
       <c r="AP23" s="46" t="s">
         <v>20</v>
@@ -3393,44 +3357,44 @@
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="63"/>
-      <c r="C24" s="64"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="64"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="64"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="104"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="64"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="104"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="64"/>
+      <c r="R24" s="103"/>
+      <c r="S24" s="104"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="64"/>
+      <c r="V24" s="103"/>
+      <c r="W24" s="104"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="63"/>
-      <c r="AA24" s="64"/>
+      <c r="Z24" s="103"/>
+      <c r="AA24" s="104"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="63"/>
-      <c r="AE24" s="64"/>
+      <c r="AD24" s="103"/>
+      <c r="AE24" s="104"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="63"/>
-      <c r="AI24" s="64"/>
+      <c r="AH24" s="103"/>
+      <c r="AI24" s="104"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="63"/>
-      <c r="AM24" s="64"/>
+      <c r="AL24" s="103"/>
+      <c r="AM24" s="104"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
@@ -3442,44 +3406,44 @@
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="63"/>
-      <c r="C25" s="64"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="64"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="104"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="63"/>
-      <c r="K25" s="64"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="104"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="64"/>
+      <c r="N25" s="103"/>
+      <c r="O25" s="104"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="63"/>
-      <c r="S25" s="64"/>
+      <c r="R25" s="103"/>
+      <c r="S25" s="104"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="63"/>
-      <c r="W25" s="64"/>
+      <c r="V25" s="103"/>
+      <c r="W25" s="104"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="63"/>
-      <c r="AA25" s="64"/>
+      <c r="Z25" s="103"/>
+      <c r="AA25" s="104"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="63"/>
-      <c r="AE25" s="64"/>
+      <c r="AD25" s="103"/>
+      <c r="AE25" s="104"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="63"/>
-      <c r="AI25" s="64"/>
+      <c r="AH25" s="103"/>
+      <c r="AI25" s="104"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="63"/>
-      <c r="AM25" s="64"/>
+      <c r="AL25" s="103"/>
+      <c r="AM25" s="104"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="46" t="s">
         <v>21</v>
@@ -3491,44 +3455,44 @@
       <c r="AR25" s="30"/>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="63"/>
-      <c r="C26" s="64"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="104"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="64"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="64"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="104"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="64"/>
+      <c r="N26" s="103"/>
+      <c r="O26" s="104"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="64"/>
+      <c r="R26" s="103"/>
+      <c r="S26" s="104"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="63"/>
-      <c r="W26" s="64"/>
+      <c r="V26" s="103"/>
+      <c r="W26" s="104"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="63"/>
-      <c r="AA26" s="64"/>
+      <c r="Z26" s="103"/>
+      <c r="AA26" s="104"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="63"/>
-      <c r="AE26" s="64"/>
+      <c r="AD26" s="103"/>
+      <c r="AE26" s="104"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="63"/>
-      <c r="AI26" s="64"/>
+      <c r="AH26" s="103"/>
+      <c r="AI26" s="104"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="63"/>
-      <c r="AM26" s="64"/>
+      <c r="AL26" s="103"/>
+      <c r="AM26" s="104"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
@@ -3540,51 +3504,51 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="65"/>
-      <c r="C27" s="66"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="102"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="66"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="102"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="66"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="102"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="65"/>
-      <c r="S27" s="66"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="102"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="65"/>
-      <c r="W27" s="66"/>
+      <c r="V27" s="101"/>
+      <c r="W27" s="102"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="65"/>
-      <c r="AA27" s="66"/>
+      <c r="Z27" s="101"/>
+      <c r="AA27" s="102"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="65"/>
-      <c r="AE27" s="66"/>
+      <c r="AD27" s="101"/>
+      <c r="AE27" s="102"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="65"/>
-      <c r="AI27" s="66"/>
+      <c r="AH27" s="101"/>
+      <c r="AI27" s="102"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="65"/>
-      <c r="AM27" s="66"/>
+      <c r="AL27" s="101"/>
+      <c r="AM27" s="102"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
       </c>
       <c r="AQ27" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR27" s="30"/>
     </row>
@@ -3650,23 +3614,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="109" t="s">
+      <c r="N29" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="109"/>
-      <c r="P29" s="109"/>
-      <c r="Q29" s="109"/>
-      <c r="R29" s="109"/>
-      <c r="S29" s="109"/>
-      <c r="T29" s="109"/>
-      <c r="U29" s="109"/>
-      <c r="V29" s="109"/>
-      <c r="W29" s="109"/>
-      <c r="X29" s="109"/>
-      <c r="Y29" s="109"/>
-      <c r="Z29" s="109"/>
-      <c r="AA29" s="109"/>
-      <c r="AB29" s="109"/>
+      <c r="O29" s="100"/>
+      <c r="P29" s="100"/>
+      <c r="Q29" s="100"/>
+      <c r="R29" s="100"/>
+      <c r="S29" s="100"/>
+      <c r="T29" s="100"/>
+      <c r="U29" s="100"/>
+      <c r="V29" s="100"/>
+      <c r="W29" s="100"/>
+      <c r="X29" s="100"/>
+      <c r="Y29" s="100"/>
+      <c r="Z29" s="100"/>
+      <c r="AA29" s="100"/>
+      <c r="AB29" s="100"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3703,21 +3667,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="109"/>
-      <c r="O30" s="109"/>
-      <c r="P30" s="109"/>
-      <c r="Q30" s="109"/>
-      <c r="R30" s="109"/>
-      <c r="S30" s="109"/>
-      <c r="T30" s="109"/>
-      <c r="U30" s="109"/>
-      <c r="V30" s="109"/>
-      <c r="W30" s="109"/>
-      <c r="X30" s="109"/>
-      <c r="Y30" s="109"/>
-      <c r="Z30" s="109"/>
-      <c r="AA30" s="109"/>
-      <c r="AB30" s="109"/>
+      <c r="N30" s="100"/>
+      <c r="O30" s="100"/>
+      <c r="P30" s="100"/>
+      <c r="Q30" s="100"/>
+      <c r="R30" s="100"/>
+      <c r="S30" s="100"/>
+      <c r="T30" s="100"/>
+      <c r="U30" s="100"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="100"/>
+      <c r="X30" s="100"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="100"/>
+      <c r="AB30" s="100"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3742,68 +3706,68 @@
       </c>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="83" t="s">
+      <c r="B31" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="84"/>
+      <c r="C31" s="89"/>
       <c r="D31" s="60"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="83" t="s">
+      <c r="F31" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="G31" s="84"/>
+      <c r="G31" s="89"/>
       <c r="H31" s="60" t="s">
         <v>66</v>
       </c>
       <c r="I31" s="36"/>
-      <c r="J31" s="83" t="s">
+      <c r="J31" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="84"/>
+      <c r="K31" s="89"/>
       <c r="L31" s="60"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="67" t="s">
+      <c r="N31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="O31" s="68"/>
+      <c r="O31" s="76"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="67" t="s">
+      <c r="R31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="S31" s="68"/>
+      <c r="S31" s="76"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="67" t="s">
+      <c r="V31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="W31" s="68"/>
+      <c r="W31" s="76"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="67" t="s">
+      <c r="Z31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="AA31" s="68"/>
+      <c r="AA31" s="76"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="67" t="s">
+      <c r="AD31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="AE31" s="68"/>
+      <c r="AE31" s="76"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="67" t="s">
+      <c r="AH31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="AI31" s="68"/>
+      <c r="AI31" s="76"/>
       <c r="AJ31" s="34" t="s">
         <v>42</v>
       </c>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="67" t="s">
+      <c r="AL31" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="AM31" s="68"/>
+      <c r="AM31" s="76"/>
       <c r="AN31" s="34" t="s">
         <v>56</v>
       </c>
@@ -3812,176 +3776,176 @@
       <c r="AR31" s="30"/>
     </row>
     <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="71" t="s">
+      <c r="B32" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="72"/>
-      <c r="D32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="74"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="71" t="s">
+      <c r="F32" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="72"/>
-      <c r="H32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="74"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="71" t="s">
+      <c r="J32" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="72"/>
-      <c r="L32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="74"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="96" t="s">
+      <c r="N32" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="O32" s="97"/>
-      <c r="P32" s="98"/>
+      <c r="O32" s="83"/>
+      <c r="P32" s="84"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="96" t="s">
+      <c r="R32" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="S32" s="97"/>
-      <c r="T32" s="98"/>
+      <c r="S32" s="83"/>
+      <c r="T32" s="84"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="96" t="s">
+      <c r="V32" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="W32" s="97"/>
-      <c r="X32" s="98"/>
+      <c r="W32" s="83"/>
+      <c r="X32" s="84"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="96" t="s">
+      <c r="Z32" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="AA32" s="97"/>
-      <c r="AB32" s="98"/>
+      <c r="AA32" s="83"/>
+      <c r="AB32" s="84"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="96" t="s">
+      <c r="AD32" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="AE32" s="97"/>
-      <c r="AF32" s="98"/>
+      <c r="AE32" s="83"/>
+      <c r="AF32" s="84"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="96" t="s">
+      <c r="AH32" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="AI32" s="97"/>
-      <c r="AJ32" s="98"/>
+      <c r="AI32" s="83"/>
+      <c r="AJ32" s="84"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="96" t="s">
+      <c r="AL32" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="AM32" s="97"/>
-      <c r="AN32" s="98"/>
+      <c r="AM32" s="83"/>
+      <c r="AN32" s="84"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
     <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="81"/>
-      <c r="D33" s="82"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="65"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="82"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="65"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="80" t="s">
+      <c r="J33" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="K33" s="81"/>
-      <c r="L33" s="82"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="65"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="92"/>
-      <c r="O33" s="93"/>
-      <c r="P33" s="99"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="86"/>
+      <c r="P33" s="87"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="92"/>
-      <c r="S33" s="93"/>
-      <c r="T33" s="99"/>
+      <c r="R33" s="85"/>
+      <c r="S33" s="86"/>
+      <c r="T33" s="87"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="92"/>
-      <c r="W33" s="93"/>
-      <c r="X33" s="99"/>
+      <c r="V33" s="85"/>
+      <c r="W33" s="86"/>
+      <c r="X33" s="87"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="92"/>
-      <c r="AA33" s="93"/>
-      <c r="AB33" s="99"/>
+      <c r="Z33" s="85"/>
+      <c r="AA33" s="86"/>
+      <c r="AB33" s="87"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="92"/>
-      <c r="AE33" s="93"/>
-      <c r="AF33" s="99"/>
+      <c r="AD33" s="85"/>
+      <c r="AE33" s="86"/>
+      <c r="AF33" s="87"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="92"/>
-      <c r="AI33" s="93"/>
-      <c r="AJ33" s="99"/>
+      <c r="AH33" s="85"/>
+      <c r="AI33" s="86"/>
+      <c r="AJ33" s="87"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="92"/>
-      <c r="AM33" s="93"/>
-      <c r="AN33" s="99"/>
+      <c r="AL33" s="85"/>
+      <c r="AM33" s="86"/>
+      <c r="AN33" s="87"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="76"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="68"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="74" t="s">
+      <c r="F34" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="75"/>
-      <c r="H34" s="76"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="68"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="74" t="s">
+      <c r="J34" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="75"/>
-      <c r="L34" s="76"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="68"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="74" t="s">
+      <c r="N34" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="O34" s="75"/>
-      <c r="P34" s="76"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="68"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="74" t="s">
+      <c r="R34" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="S34" s="75"/>
-      <c r="T34" s="76"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="68"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="74" t="s">
+      <c r="V34" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="W34" s="75"/>
-      <c r="X34" s="76"/>
+      <c r="W34" s="67"/>
+      <c r="X34" s="68"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="74" t="s">
+      <c r="Z34" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="AA34" s="75"/>
-      <c r="AB34" s="76"/>
+      <c r="AA34" s="67"/>
+      <c r="AB34" s="68"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="74" t="s">
+      <c r="AD34" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="AE34" s="75"/>
-      <c r="AF34" s="76"/>
+      <c r="AE34" s="67"/>
+      <c r="AF34" s="68"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="74" t="s">
+      <c r="AH34" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="AI34" s="75"/>
-      <c r="AJ34" s="76"/>
+      <c r="AI34" s="67"/>
+      <c r="AJ34" s="68"/>
       <c r="AK34" s="35"/>
-      <c r="AL34" s="74" t="s">
+      <c r="AL34" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="AM34" s="75"/>
-      <c r="AN34" s="76"/>
+      <c r="AM34" s="67"/>
+      <c r="AN34" s="68"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -3989,122 +3953,122 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
-      <c r="B35" s="87" t="s">
+      <c r="B35" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="88"/>
-      <c r="D35" s="89"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="79"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="87" t="s">
+      <c r="F35" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="88"/>
-      <c r="H35" s="89"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="79"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="87" t="s">
+      <c r="J35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="88"/>
-      <c r="L35" s="89"/>
+      <c r="K35" s="78"/>
+      <c r="L35" s="79"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="87" t="s">
+      <c r="N35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="O35" s="88"/>
-      <c r="P35" s="89"/>
+      <c r="O35" s="78"/>
+      <c r="P35" s="79"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="87" t="s">
+      <c r="R35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="S35" s="88"/>
-      <c r="T35" s="89"/>
+      <c r="S35" s="78"/>
+      <c r="T35" s="79"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="87" t="s">
+      <c r="V35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="W35" s="88"/>
-      <c r="X35" s="89"/>
+      <c r="W35" s="78"/>
+      <c r="X35" s="79"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="87" t="s">
+      <c r="Z35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AA35" s="88"/>
-      <c r="AB35" s="89"/>
+      <c r="AA35" s="78"/>
+      <c r="AB35" s="79"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="87" t="s">
+      <c r="AD35" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AE35" s="88"/>
-      <c r="AF35" s="89"/>
+      <c r="AE35" s="78"/>
+      <c r="AF35" s="79"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="87" t="s">
+      <c r="AH35" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="AI35" s="88"/>
-      <c r="AJ35" s="89"/>
+      <c r="AI35" s="78"/>
+      <c r="AJ35" s="79"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="87" t="s">
+      <c r="AL35" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="AM35" s="88"/>
-      <c r="AN35" s="89"/>
+      <c r="AM35" s="78"/>
+      <c r="AN35" s="79"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="77"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="79"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="71"/>
       <c r="E36" s="35"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="79"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="71"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="77" t="s">
+      <c r="J36" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="78"/>
-      <c r="L36" s="79"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="71"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="77" t="s">
+      <c r="N36" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="O36" s="78"/>
-      <c r="P36" s="79"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="71"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="77" t="s">
+      <c r="R36" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="S36" s="78"/>
-      <c r="T36" s="79"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="71"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="77" t="s">
+      <c r="V36" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="W36" s="78"/>
-      <c r="X36" s="79"/>
+      <c r="W36" s="70"/>
+      <c r="X36" s="71"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="77" t="s">
+      <c r="Z36" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="AA36" s="78"/>
-      <c r="AB36" s="79"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="71"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="77" t="s">
+      <c r="AD36" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="AE36" s="78"/>
-      <c r="AF36" s="79"/>
+      <c r="AE36" s="70"/>
+      <c r="AF36" s="71"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="77"/>
-      <c r="AI36" s="78"/>
-      <c r="AJ36" s="79"/>
+      <c r="AH36" s="69"/>
+      <c r="AI36" s="70"/>
+      <c r="AJ36" s="71"/>
       <c r="AK36" s="35"/>
-      <c r="AL36" s="77"/>
-      <c r="AM36" s="78"/>
-      <c r="AN36" s="79"/>
+      <c r="AL36" s="69"/>
+      <c r="AM36" s="70"/>
+      <c r="AN36" s="71"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
@@ -4158,80 +4122,80 @@
     </row>
     <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="90" t="s">
+      <c r="B38" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="91"/>
+      <c r="C38" s="94"/>
       <c r="D38" s="55" t="s">
         <v>68</v>
       </c>
       <c r="E38" s="36"/>
-      <c r="F38" s="83" t="s">
+      <c r="F38" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="G38" s="84"/>
+      <c r="G38" s="89"/>
       <c r="H38" s="60"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="83" t="s">
+      <c r="J38" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="K38" s="84"/>
+      <c r="K38" s="89"/>
       <c r="L38" s="60" t="s">
         <v>68</v>
       </c>
       <c r="M38" s="5"/>
-      <c r="N38" s="67" t="s">
+      <c r="N38" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O38" s="68"/>
+      <c r="O38" s="76"/>
       <c r="P38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="Q38" s="36"/>
-      <c r="R38" s="67" t="s">
+      <c r="R38" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="S38" s="68"/>
+      <c r="S38" s="76"/>
       <c r="T38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="U38" s="32"/>
-      <c r="V38" s="67" t="s">
+      <c r="V38" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="W38" s="68"/>
+      <c r="W38" s="76"/>
       <c r="X38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="Y38" s="54"/>
-      <c r="Z38" s="67" t="s">
+      <c r="Z38" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="AA38" s="68"/>
+      <c r="AA38" s="76"/>
       <c r="AB38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="AC38" s="36"/>
-      <c r="AD38" s="67" t="s">
+      <c r="AD38" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="AE38" s="68"/>
+      <c r="AE38" s="76"/>
       <c r="AF38" s="34" t="s">
         <v>68</v>
       </c>
       <c r="AG38" s="36"/>
-      <c r="AH38" s="67" t="s">
+      <c r="AH38" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="AI38" s="68"/>
+      <c r="AI38" s="76"/>
       <c r="AJ38" s="34" t="s">
         <v>56</v>
       </c>
       <c r="AK38" s="36"/>
-      <c r="AL38" s="67" t="s">
+      <c r="AL38" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="AM38" s="68"/>
+      <c r="AM38" s="76"/>
       <c r="AN38" s="34" t="s">
         <v>43</v>
       </c>
@@ -4242,65 +4206,65 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="71" t="s">
+      <c r="B39" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="72"/>
-      <c r="D39" s="73"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="74"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="G39" s="72"/>
-      <c r="H39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="74"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="71" t="s">
+      <c r="J39" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="K39" s="72"/>
-      <c r="L39" s="73"/>
+      <c r="K39" s="73"/>
+      <c r="L39" s="74"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="96" t="s">
+      <c r="N39" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O39" s="97"/>
-      <c r="P39" s="98"/>
+      <c r="O39" s="83"/>
+      <c r="P39" s="84"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="96" t="s">
+      <c r="R39" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="S39" s="97"/>
-      <c r="T39" s="98"/>
+      <c r="S39" s="83"/>
+      <c r="T39" s="84"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="96" t="s">
+      <c r="V39" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="W39" s="97"/>
-      <c r="X39" s="98"/>
+      <c r="W39" s="83"/>
+      <c r="X39" s="84"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="96" t="s">
+      <c r="Z39" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="AA39" s="97"/>
-      <c r="AB39" s="98"/>
+      <c r="AA39" s="83"/>
+      <c r="AB39" s="84"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="96" t="s">
+      <c r="AD39" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="AE39" s="97"/>
-      <c r="AF39" s="98"/>
+      <c r="AE39" s="83"/>
+      <c r="AF39" s="84"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="96" t="s">
+      <c r="AH39" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="AI39" s="97"/>
-      <c r="AJ39" s="98"/>
+      <c r="AI39" s="83"/>
+      <c r="AJ39" s="84"/>
       <c r="AK39" s="36"/>
-      <c r="AL39" s="96" t="s">
+      <c r="AL39" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="AM39" s="97"/>
-      <c r="AN39" s="98"/>
+      <c r="AM39" s="83"/>
+      <c r="AN39" s="84"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
@@ -4308,47 +4272,47 @@
     </row>
     <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="82"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="65"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="80" t="s">
+      <c r="F40" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="G40" s="81"/>
-      <c r="H40" s="82"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="65"/>
       <c r="I40" s="32"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="81"/>
-      <c r="L40" s="82"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="65"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="92"/>
-      <c r="O40" s="93"/>
-      <c r="P40" s="99"/>
+      <c r="N40" s="85"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="87"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="92"/>
-      <c r="S40" s="93"/>
-      <c r="T40" s="99"/>
+      <c r="R40" s="85"/>
+      <c r="S40" s="86"/>
+      <c r="T40" s="87"/>
       <c r="U40" s="37"/>
-      <c r="V40" s="92"/>
-      <c r="W40" s="93"/>
-      <c r="X40" s="99"/>
+      <c r="V40" s="85"/>
+      <c r="W40" s="86"/>
+      <c r="X40" s="87"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="92"/>
-      <c r="AA40" s="93"/>
-      <c r="AB40" s="99"/>
+      <c r="Z40" s="85"/>
+      <c r="AA40" s="86"/>
+      <c r="AB40" s="87"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="92"/>
-      <c r="AE40" s="93"/>
-      <c r="AF40" s="99"/>
+      <c r="AD40" s="85"/>
+      <c r="AE40" s="86"/>
+      <c r="AF40" s="87"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="92"/>
-      <c r="AI40" s="93"/>
-      <c r="AJ40" s="99"/>
+      <c r="AH40" s="85"/>
+      <c r="AI40" s="86"/>
+      <c r="AJ40" s="87"/>
       <c r="AK40" s="32"/>
-      <c r="AL40" s="92"/>
-      <c r="AM40" s="93"/>
-      <c r="AN40" s="99"/>
+      <c r="AL40" s="85"/>
+      <c r="AM40" s="86"/>
+      <c r="AN40" s="87"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4356,65 +4320,65 @@
     </row>
     <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="75"/>
-      <c r="D41" s="76"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="68"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="74" t="s">
+      <c r="F41" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="G41" s="75"/>
-      <c r="H41" s="76"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="68"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="74" t="s">
+      <c r="J41" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="75"/>
-      <c r="L41" s="76"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="68"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="74" t="s">
+      <c r="N41" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="O41" s="75"/>
-      <c r="P41" s="76"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="68"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="74" t="s">
+      <c r="R41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="S41" s="75"/>
-      <c r="T41" s="76"/>
+      <c r="S41" s="67"/>
+      <c r="T41" s="68"/>
       <c r="U41" s="44"/>
-      <c r="V41" s="74" t="s">
+      <c r="V41" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="W41" s="75"/>
-      <c r="X41" s="76"/>
+      <c r="W41" s="67"/>
+      <c r="X41" s="68"/>
       <c r="Y41" s="40"/>
-      <c r="Z41" s="74" t="s">
+      <c r="Z41" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="75"/>
-      <c r="AB41" s="76"/>
+      <c r="AA41" s="67"/>
+      <c r="AB41" s="68"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="74" t="s">
+      <c r="AD41" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="AE41" s="75"/>
-      <c r="AF41" s="76"/>
+      <c r="AE41" s="67"/>
+      <c r="AF41" s="68"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="74" t="s">
+      <c r="AH41" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="AI41" s="75"/>
-      <c r="AJ41" s="76"/>
+      <c r="AI41" s="67"/>
+      <c r="AJ41" s="68"/>
       <c r="AK41" s="37"/>
-      <c r="AL41" s="74" t="s">
+      <c r="AL41" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="AM41" s="75"/>
-      <c r="AN41" s="76"/>
+      <c r="AM41" s="67"/>
+      <c r="AN41" s="68"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4422,65 +4386,65 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="87" t="s">
+      <c r="B42" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="88"/>
-      <c r="D42" s="89"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="79"/>
       <c r="E42" s="35"/>
-      <c r="F42" s="87" t="s">
+      <c r="F42" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="G42" s="88"/>
-      <c r="H42" s="89"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="79"/>
       <c r="I42" s="35"/>
-      <c r="J42" s="87" t="s">
+      <c r="J42" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="K42" s="88"/>
-      <c r="L42" s="89"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="79"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="87" t="s">
+      <c r="N42" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="O42" s="88"/>
-      <c r="P42" s="89"/>
+      <c r="O42" s="78"/>
+      <c r="P42" s="79"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="87" t="s">
+      <c r="R42" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="89"/>
+      <c r="S42" s="78"/>
+      <c r="T42" s="79"/>
       <c r="U42" s="44"/>
-      <c r="V42" s="87" t="s">
+      <c r="V42" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="W42" s="88"/>
-      <c r="X42" s="89"/>
+      <c r="W42" s="78"/>
+      <c r="X42" s="79"/>
       <c r="Y42" s="44"/>
-      <c r="Z42" s="87" t="s">
+      <c r="Z42" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="AA42" s="88"/>
-      <c r="AB42" s="89"/>
+      <c r="AA42" s="78"/>
+      <c r="AB42" s="79"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="87" t="s">
+      <c r="AD42" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="AE42" s="88"/>
-      <c r="AF42" s="89"/>
+      <c r="AE42" s="78"/>
+      <c r="AF42" s="79"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="87" t="s">
+      <c r="AH42" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="AI42" s="88"/>
-      <c r="AJ42" s="89"/>
+      <c r="AI42" s="78"/>
+      <c r="AJ42" s="79"/>
       <c r="AK42" s="35"/>
-      <c r="AL42" s="87" t="s">
+      <c r="AL42" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="AM42" s="88"/>
-      <c r="AN42" s="89"/>
+      <c r="AM42" s="78"/>
+      <c r="AN42" s="79"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4488,53 +4452,53 @@
     </row>
     <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="77"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="79"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="71"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="77" t="s">
+      <c r="F43" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="G43" s="78"/>
-      <c r="H43" s="79"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="71"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="77" t="s">
+      <c r="J43" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="K43" s="78"/>
-      <c r="L43" s="79"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="71"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="77"/>
-      <c r="O43" s="78"/>
-      <c r="P43" s="79"/>
+      <c r="N43" s="69"/>
+      <c r="O43" s="70"/>
+      <c r="P43" s="71"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="77"/>
-      <c r="S43" s="78"/>
-      <c r="T43" s="79"/>
+      <c r="R43" s="69"/>
+      <c r="S43" s="70"/>
+      <c r="T43" s="71"/>
       <c r="U43" s="50"/>
-      <c r="V43" s="77"/>
-      <c r="W43" s="78"/>
-      <c r="X43" s="79"/>
+      <c r="V43" s="69"/>
+      <c r="W43" s="70"/>
+      <c r="X43" s="71"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="77"/>
-      <c r="AA43" s="78"/>
-      <c r="AB43" s="79"/>
+      <c r="Z43" s="69"/>
+      <c r="AA43" s="70"/>
+      <c r="AB43" s="71"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="77"/>
-      <c r="AE43" s="78"/>
-      <c r="AF43" s="79"/>
+      <c r="AD43" s="69"/>
+      <c r="AE43" s="70"/>
+      <c r="AF43" s="71"/>
       <c r="AG43" s="44"/>
-      <c r="AH43" s="77" t="s">
+      <c r="AH43" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AI43" s="78"/>
-      <c r="AJ43" s="79"/>
+      <c r="AI43" s="70"/>
+      <c r="AJ43" s="71"/>
       <c r="AK43" s="44"/>
-      <c r="AL43" s="77" t="s">
+      <c r="AL43" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="AM43" s="78"/>
-      <c r="AN43" s="79"/>
+      <c r="AM43" s="70"/>
+      <c r="AN43" s="71"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
@@ -4588,56 +4552,56 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="83"/>
-      <c r="C45" s="84"/>
+      <c r="B45" s="88"/>
+      <c r="C45" s="89"/>
       <c r="D45" s="60"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="84"/>
+      <c r="F45" s="88"/>
+      <c r="G45" s="89"/>
       <c r="H45" s="60"/>
       <c r="I45" s="50"/>
-      <c r="J45" s="83" t="s">
+      <c r="J45" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="K45" s="84"/>
+      <c r="K45" s="89"/>
       <c r="L45" s="55" t="s">
         <v>77</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="67"/>
-      <c r="O45" s="68"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="76"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="67" t="s">
+      <c r="R45" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="S45" s="68"/>
+      <c r="S45" s="76"/>
       <c r="T45" s="34" t="s">
         <v>42</v>
       </c>
       <c r="U45" s="36"/>
-      <c r="V45" s="67" t="s">
+      <c r="V45" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="W45" s="68"/>
+      <c r="W45" s="76"/>
       <c r="X45" s="34" t="s">
         <v>69</v>
       </c>
       <c r="Y45" s="37"/>
-      <c r="Z45" s="67"/>
-      <c r="AA45" s="68"/>
+      <c r="Z45" s="75"/>
+      <c r="AA45" s="76"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="67"/>
-      <c r="AE45" s="68"/>
+      <c r="AD45" s="75"/>
+      <c r="AE45" s="76"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="67"/>
-      <c r="AI45" s="68"/>
+      <c r="AH45" s="75"/>
+      <c r="AI45" s="76"/>
       <c r="AJ45" s="34"/>
       <c r="AK45" s="50"/>
-      <c r="AL45" s="67"/>
-      <c r="AM45" s="68"/>
+      <c r="AL45" s="75"/>
+      <c r="AM45" s="76"/>
       <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
@@ -4646,51 +4610,51 @@
     </row>
     <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="73"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="74"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="72"/>
-      <c r="H46" s="73"/>
+      <c r="F46" s="72"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="74"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="71" t="s">
+      <c r="J46" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="K46" s="72"/>
-      <c r="L46" s="73"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="74"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="96"/>
-      <c r="O46" s="97"/>
-      <c r="P46" s="98"/>
+      <c r="N46" s="82"/>
+      <c r="O46" s="83"/>
+      <c r="P46" s="84"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="96" t="s">
+      <c r="R46" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="S46" s="97"/>
-      <c r="T46" s="98"/>
+      <c r="S46" s="83"/>
+      <c r="T46" s="84"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="96" t="s">
+      <c r="V46" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="W46" s="97"/>
-      <c r="X46" s="98"/>
+      <c r="W46" s="83"/>
+      <c r="X46" s="84"/>
       <c r="Y46" s="36"/>
-      <c r="Z46" s="96"/>
-      <c r="AA46" s="97"/>
-      <c r="AB46" s="98"/>
+      <c r="Z46" s="82"/>
+      <c r="AA46" s="83"/>
+      <c r="AB46" s="84"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="96"/>
-      <c r="AE46" s="97"/>
-      <c r="AF46" s="98"/>
+      <c r="AD46" s="82"/>
+      <c r="AE46" s="83"/>
+      <c r="AF46" s="84"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="96"/>
-      <c r="AI46" s="97"/>
-      <c r="AJ46" s="98"/>
+      <c r="AH46" s="82"/>
+      <c r="AI46" s="83"/>
+      <c r="AJ46" s="84"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="96"/>
-      <c r="AM46" s="97"/>
-      <c r="AN46" s="98"/>
+      <c r="AL46" s="82"/>
+      <c r="AM46" s="83"/>
+      <c r="AN46" s="84"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4698,47 +4662,47 @@
     </row>
     <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="81"/>
-      <c r="D47" s="82"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="82"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="65"/>
       <c r="I47" s="32"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="81"/>
-      <c r="L47" s="82"/>
+      <c r="J47" s="63"/>
+      <c r="K47" s="64"/>
+      <c r="L47" s="65"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="92"/>
-      <c r="O47" s="93"/>
-      <c r="P47" s="99"/>
+      <c r="N47" s="85"/>
+      <c r="O47" s="86"/>
+      <c r="P47" s="87"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="92"/>
-      <c r="S47" s="93"/>
-      <c r="T47" s="99"/>
+      <c r="R47" s="85"/>
+      <c r="S47" s="86"/>
+      <c r="T47" s="87"/>
       <c r="U47" s="32"/>
-      <c r="V47" s="92" t="s">
+      <c r="V47" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="W47" s="93"/>
-      <c r="X47" s="99"/>
+      <c r="W47" s="86"/>
+      <c r="X47" s="87"/>
       <c r="Y47" s="32"/>
-      <c r="Z47" s="92"/>
-      <c r="AA47" s="93"/>
-      <c r="AB47" s="99"/>
+      <c r="Z47" s="85"/>
+      <c r="AA47" s="86"/>
+      <c r="AB47" s="87"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="92"/>
-      <c r="AE47" s="93"/>
-      <c r="AF47" s="99"/>
+      <c r="AD47" s="85"/>
+      <c r="AE47" s="86"/>
+      <c r="AF47" s="87"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="92"/>
-      <c r="AI47" s="93"/>
-      <c r="AJ47" s="99"/>
+      <c r="AH47" s="85"/>
+      <c r="AI47" s="86"/>
+      <c r="AJ47" s="87"/>
       <c r="AK47" s="32"/>
-      <c r="AL47" s="92"/>
-      <c r="AM47" s="93"/>
-      <c r="AN47" s="99"/>
+      <c r="AL47" s="85"/>
+      <c r="AM47" s="86"/>
+      <c r="AN47" s="87"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4746,147 +4710,147 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="88"/>
-      <c r="D48" s="89"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="79"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="87"/>
-      <c r="G48" s="88"/>
-      <c r="H48" s="89"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="79"/>
       <c r="I48" s="37"/>
-      <c r="J48" s="74" t="s">
+      <c r="J48" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="K48" s="75"/>
-      <c r="L48" s="76"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="68"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="87"/>
-      <c r="O48" s="88"/>
-      <c r="P48" s="89"/>
+      <c r="N48" s="77"/>
+      <c r="O48" s="78"/>
+      <c r="P48" s="79"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="74" t="s">
+      <c r="R48" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="S48" s="75"/>
-      <c r="T48" s="76"/>
+      <c r="S48" s="67"/>
+      <c r="T48" s="68"/>
       <c r="U48" s="35"/>
-      <c r="V48" s="74" t="s">
+      <c r="V48" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="W48" s="75"/>
-      <c r="X48" s="76"/>
+      <c r="W48" s="67"/>
+      <c r="X48" s="68"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="87"/>
-      <c r="AA48" s="88"/>
-      <c r="AB48" s="89"/>
+      <c r="Z48" s="77"/>
+      <c r="AA48" s="78"/>
+      <c r="AB48" s="79"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="87"/>
-      <c r="AE48" s="88"/>
-      <c r="AF48" s="89"/>
+      <c r="AD48" s="77"/>
+      <c r="AE48" s="78"/>
+      <c r="AF48" s="79"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="87"/>
-      <c r="AI48" s="88"/>
-      <c r="AJ48" s="89"/>
+      <c r="AH48" s="77"/>
+      <c r="AI48" s="78"/>
+      <c r="AJ48" s="79"/>
       <c r="AK48" s="37"/>
-      <c r="AL48" s="87"/>
-      <c r="AM48" s="88"/>
-      <c r="AN48" s="89"/>
+      <c r="AL48" s="77"/>
+      <c r="AM48" s="78"/>
+      <c r="AN48" s="79"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="87"/>
-      <c r="C49" s="88"/>
-      <c r="D49" s="89"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="78"/>
+      <c r="D49" s="79"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="87"/>
-      <c r="G49" s="88"/>
-      <c r="H49" s="89"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="78"/>
+      <c r="H49" s="79"/>
       <c r="I49" s="44"/>
-      <c r="J49" s="87" t="s">
+      <c r="J49" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="K49" s="88"/>
-      <c r="L49" s="89"/>
+      <c r="K49" s="78"/>
+      <c r="L49" s="79"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="87"/>
-      <c r="O49" s="88"/>
-      <c r="P49" s="89"/>
+      <c r="N49" s="77"/>
+      <c r="O49" s="78"/>
+      <c r="P49" s="79"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="87" t="s">
+      <c r="R49" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="S49" s="88"/>
-      <c r="T49" s="89"/>
+      <c r="S49" s="78"/>
+      <c r="T49" s="79"/>
       <c r="U49" s="35"/>
-      <c r="V49" s="87" t="s">
+      <c r="V49" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="W49" s="88"/>
-      <c r="X49" s="89"/>
+      <c r="W49" s="78"/>
+      <c r="X49" s="79"/>
       <c r="Y49" s="32"/>
-      <c r="Z49" s="87"/>
-      <c r="AA49" s="88"/>
-      <c r="AB49" s="89"/>
+      <c r="Z49" s="77"/>
+      <c r="AA49" s="78"/>
+      <c r="AB49" s="79"/>
       <c r="AC49" s="44"/>
-      <c r="AD49" s="87"/>
-      <c r="AE49" s="88"/>
-      <c r="AF49" s="89"/>
+      <c r="AD49" s="77"/>
+      <c r="AE49" s="78"/>
+      <c r="AF49" s="79"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="87"/>
-      <c r="AI49" s="88"/>
-      <c r="AJ49" s="89"/>
+      <c r="AH49" s="77"/>
+      <c r="AI49" s="78"/>
+      <c r="AJ49" s="79"/>
       <c r="AK49" s="44"/>
-      <c r="AL49" s="87"/>
-      <c r="AM49" s="88"/>
-      <c r="AN49" s="89"/>
+      <c r="AL49" s="77"/>
+      <c r="AM49" s="78"/>
+      <c r="AN49" s="79"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
     <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="77"/>
-      <c r="C50" s="78"/>
-      <c r="D50" s="79"/>
+      <c r="B50" s="69"/>
+      <c r="C50" s="70"/>
+      <c r="D50" s="71"/>
       <c r="E50" s="35"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="78"/>
-      <c r="H50" s="79"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="71"/>
       <c r="I50" s="35"/>
-      <c r="J50" s="77"/>
-      <c r="K50" s="78"/>
-      <c r="L50" s="79"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="70"/>
+      <c r="L50" s="71"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="77"/>
-      <c r="O50" s="78"/>
-      <c r="P50" s="79"/>
+      <c r="N50" s="69"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="71"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="77"/>
-      <c r="S50" s="78"/>
-      <c r="T50" s="79"/>
+      <c r="R50" s="69"/>
+      <c r="S50" s="70"/>
+      <c r="T50" s="71"/>
       <c r="U50" s="35"/>
-      <c r="V50" s="77"/>
-      <c r="W50" s="78"/>
-      <c r="X50" s="79"/>
+      <c r="V50" s="69"/>
+      <c r="W50" s="70"/>
+      <c r="X50" s="71"/>
       <c r="Y50" s="35"/>
-      <c r="Z50" s="77"/>
-      <c r="AA50" s="78"/>
-      <c r="AB50" s="79"/>
+      <c r="Z50" s="69"/>
+      <c r="AA50" s="70"/>
+      <c r="AB50" s="71"/>
       <c r="AC50" s="50"/>
-      <c r="AD50" s="77"/>
-      <c r="AE50" s="78"/>
-      <c r="AF50" s="79"/>
+      <c r="AD50" s="69"/>
+      <c r="AE50" s="70"/>
+      <c r="AF50" s="71"/>
       <c r="AG50" s="35"/>
-      <c r="AH50" s="77"/>
-      <c r="AI50" s="78"/>
-      <c r="AJ50" s="79"/>
+      <c r="AH50" s="69"/>
+      <c r="AI50" s="70"/>
+      <c r="AJ50" s="71"/>
       <c r="AK50" s="35"/>
-      <c r="AL50" s="77"/>
-      <c r="AM50" s="78"/>
-      <c r="AN50" s="79"/>
+      <c r="AL50" s="69"/>
+      <c r="AM50" s="70"/>
+      <c r="AN50" s="71"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
@@ -4938,275 +4902,273 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="83"/>
-      <c r="C52" s="84"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="89"/>
       <c r="D52" s="60"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="84"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="89"/>
       <c r="H52" s="60"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="90" t="s">
+      <c r="J52" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="K52" s="91"/>
+      <c r="K52" s="94"/>
       <c r="L52" s="55" t="s">
         <v>79</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="67"/>
-      <c r="O52" s="68"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="76"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="67"/>
-      <c r="S52" s="68"/>
+      <c r="R52" s="75"/>
+      <c r="S52" s="76"/>
       <c r="T52" s="34"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="67" t="s">
+      <c r="V52" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="W52" s="68"/>
-      <c r="X52" s="34" t="s">
-        <v>87</v>
-      </c>
+      <c r="W52" s="76"/>
+      <c r="X52" s="34"/>
       <c r="Y52" s="54"/>
-      <c r="Z52" s="67"/>
-      <c r="AA52" s="68"/>
+      <c r="Z52" s="75"/>
+      <c r="AA52" s="76"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="36"/>
-      <c r="AD52" s="67"/>
-      <c r="AE52" s="68"/>
+      <c r="AD52" s="75"/>
+      <c r="AE52" s="76"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="67"/>
-      <c r="AI52" s="68"/>
+      <c r="AH52" s="75"/>
+      <c r="AI52" s="76"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="67"/>
-      <c r="AM52" s="68"/>
+      <c r="AL52" s="75"/>
+      <c r="AM52" s="76"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
     <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="71"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="73"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="74"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="71"/>
-      <c r="G53" s="72"/>
-      <c r="H53" s="73"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="74"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="71" t="s">
+      <c r="J53" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="K53" s="72"/>
-      <c r="L53" s="73"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="74"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="96"/>
-      <c r="O53" s="97"/>
-      <c r="P53" s="98"/>
+      <c r="N53" s="82"/>
+      <c r="O53" s="83"/>
+      <c r="P53" s="84"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="96"/>
-      <c r="S53" s="97"/>
-      <c r="T53" s="98"/>
+      <c r="R53" s="82"/>
+      <c r="S53" s="83"/>
+      <c r="T53" s="84"/>
       <c r="U53" s="32"/>
-      <c r="V53" s="96" t="s">
+      <c r="V53" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="W53" s="97"/>
-      <c r="X53" s="98"/>
+      <c r="W53" s="83"/>
+      <c r="X53" s="84"/>
       <c r="Y53" s="35"/>
-      <c r="Z53" s="96"/>
-      <c r="AA53" s="97"/>
-      <c r="AB53" s="98"/>
+      <c r="Z53" s="82"/>
+      <c r="AA53" s="83"/>
+      <c r="AB53" s="84"/>
       <c r="AC53" s="36"/>
-      <c r="AD53" s="96"/>
-      <c r="AE53" s="97"/>
-      <c r="AF53" s="98"/>
+      <c r="AD53" s="82"/>
+      <c r="AE53" s="83"/>
+      <c r="AF53" s="84"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="96"/>
-      <c r="AI53" s="97"/>
-      <c r="AJ53" s="98"/>
+      <c r="AH53" s="82"/>
+      <c r="AI53" s="83"/>
+      <c r="AJ53" s="84"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="96"/>
-      <c r="AM53" s="97"/>
-      <c r="AN53" s="98"/>
+      <c r="AL53" s="82"/>
+      <c r="AM53" s="83"/>
+      <c r="AN53" s="84"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="80"/>
-      <c r="C54" s="81"/>
-      <c r="D54" s="82"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="64"/>
+      <c r="D54" s="65"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="82"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="64"/>
+      <c r="H54" s="65"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="80"/>
-      <c r="K54" s="81"/>
-      <c r="L54" s="82"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="64"/>
+      <c r="L54" s="65"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="92"/>
-      <c r="O54" s="93"/>
-      <c r="P54" s="99"/>
+      <c r="N54" s="85"/>
+      <c r="O54" s="86"/>
+      <c r="P54" s="87"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="92"/>
-      <c r="S54" s="93"/>
-      <c r="T54" s="99"/>
+      <c r="R54" s="85"/>
+      <c r="S54" s="86"/>
+      <c r="T54" s="87"/>
       <c r="U54" s="37"/>
-      <c r="V54" s="92"/>
-      <c r="W54" s="93"/>
-      <c r="X54" s="99"/>
+      <c r="V54" s="85"/>
+      <c r="W54" s="86"/>
+      <c r="X54" s="87"/>
       <c r="Y54" s="35"/>
-      <c r="Z54" s="92"/>
-      <c r="AA54" s="93"/>
-      <c r="AB54" s="99"/>
+      <c r="Z54" s="85"/>
+      <c r="AA54" s="86"/>
+      <c r="AB54" s="87"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="92"/>
-      <c r="AE54" s="93"/>
-      <c r="AF54" s="99"/>
+      <c r="AD54" s="85"/>
+      <c r="AE54" s="86"/>
+      <c r="AF54" s="87"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="92"/>
-      <c r="AI54" s="93"/>
-      <c r="AJ54" s="99"/>
+      <c r="AH54" s="85"/>
+      <c r="AI54" s="86"/>
+      <c r="AJ54" s="87"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="92"/>
-      <c r="AM54" s="93"/>
-      <c r="AN54" s="99"/>
+      <c r="AL54" s="85"/>
+      <c r="AM54" s="86"/>
+      <c r="AN54" s="87"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="74"/>
-      <c r="C55" s="75"/>
-      <c r="D55" s="76"/>
+      <c r="B55" s="66"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="68"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="75"/>
-      <c r="H55" s="76"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="68"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="74" t="s">
+      <c r="J55" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="K55" s="75"/>
-      <c r="L55" s="76"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="68"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="74"/>
-      <c r="O55" s="75"/>
-      <c r="P55" s="76"/>
+      <c r="N55" s="66"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="68"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="74"/>
-      <c r="S55" s="75"/>
-      <c r="T55" s="76"/>
+      <c r="R55" s="66"/>
+      <c r="S55" s="67"/>
+      <c r="T55" s="68"/>
       <c r="U55" s="44"/>
-      <c r="V55" s="74" t="s">
+      <c r="V55" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="W55" s="75"/>
-      <c r="X55" s="76"/>
+      <c r="W55" s="67"/>
+      <c r="X55" s="68"/>
       <c r="Y55" s="40"/>
-      <c r="Z55" s="74"/>
-      <c r="AA55" s="75"/>
-      <c r="AB55" s="76"/>
+      <c r="Z55" s="66"/>
+      <c r="AA55" s="67"/>
+      <c r="AB55" s="68"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="74"/>
-      <c r="AE55" s="75"/>
-      <c r="AF55" s="76"/>
+      <c r="AD55" s="66"/>
+      <c r="AE55" s="67"/>
+      <c r="AF55" s="68"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="74"/>
-      <c r="AI55" s="75"/>
-      <c r="AJ55" s="76"/>
+      <c r="AH55" s="66"/>
+      <c r="AI55" s="67"/>
+      <c r="AJ55" s="68"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="74"/>
-      <c r="AM55" s="75"/>
-      <c r="AN55" s="76"/>
+      <c r="AL55" s="66"/>
+      <c r="AM55" s="67"/>
+      <c r="AN55" s="68"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="87"/>
-      <c r="C56" s="88"/>
-      <c r="D56" s="89"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="79"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="87"/>
-      <c r="G56" s="88"/>
-      <c r="H56" s="89"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="78"/>
+      <c r="H56" s="79"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="87" t="s">
+      <c r="J56" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="K56" s="88"/>
-      <c r="L56" s="89"/>
+      <c r="K56" s="78"/>
+      <c r="L56" s="79"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="87"/>
-      <c r="O56" s="88"/>
-      <c r="P56" s="89"/>
+      <c r="N56" s="77"/>
+      <c r="O56" s="78"/>
+      <c r="P56" s="79"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="87"/>
-      <c r="S56" s="88"/>
-      <c r="T56" s="89"/>
+      <c r="R56" s="77"/>
+      <c r="S56" s="78"/>
+      <c r="T56" s="79"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="87" t="s">
+      <c r="V56" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="W56" s="88"/>
-      <c r="X56" s="89"/>
+      <c r="W56" s="78"/>
+      <c r="X56" s="79"/>
       <c r="Y56" s="50"/>
-      <c r="Z56" s="87"/>
-      <c r="AA56" s="88"/>
-      <c r="AB56" s="89"/>
+      <c r="Z56" s="77"/>
+      <c r="AA56" s="78"/>
+      <c r="AB56" s="79"/>
       <c r="AC56" s="44"/>
-      <c r="AD56" s="87"/>
-      <c r="AE56" s="88"/>
-      <c r="AF56" s="89"/>
+      <c r="AD56" s="77"/>
+      <c r="AE56" s="78"/>
+      <c r="AF56" s="79"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="87"/>
-      <c r="AI56" s="88"/>
-      <c r="AJ56" s="89"/>
+      <c r="AH56" s="77"/>
+      <c r="AI56" s="78"/>
+      <c r="AJ56" s="79"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="87"/>
-      <c r="AM56" s="88"/>
-      <c r="AN56" s="89"/>
+      <c r="AL56" s="77"/>
+      <c r="AM56" s="78"/>
+      <c r="AN56" s="79"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="77"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="79"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="71"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="79"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="71"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="77"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="79"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="70"/>
+      <c r="L57" s="71"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="77"/>
-      <c r="O57" s="78"/>
-      <c r="P57" s="79"/>
+      <c r="N57" s="69"/>
+      <c r="O57" s="70"/>
+      <c r="P57" s="71"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="77"/>
-      <c r="S57" s="78"/>
-      <c r="T57" s="79"/>
+      <c r="R57" s="69"/>
+      <c r="S57" s="70"/>
+      <c r="T57" s="71"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="77"/>
-      <c r="W57" s="78"/>
-      <c r="X57" s="79"/>
+      <c r="V57" s="69"/>
+      <c r="W57" s="70"/>
+      <c r="X57" s="71"/>
       <c r="Y57" s="50"/>
-      <c r="Z57" s="77"/>
-      <c r="AA57" s="78"/>
-      <c r="AB57" s="79"/>
+      <c r="Z57" s="69"/>
+      <c r="AA57" s="70"/>
+      <c r="AB57" s="71"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="77"/>
-      <c r="AE57" s="78"/>
-      <c r="AF57" s="79"/>
+      <c r="AD57" s="69"/>
+      <c r="AE57" s="70"/>
+      <c r="AF57" s="71"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="77"/>
-      <c r="AI57" s="78"/>
-      <c r="AJ57" s="79"/>
+      <c r="AH57" s="69"/>
+      <c r="AI57" s="70"/>
+      <c r="AJ57" s="71"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="77"/>
-      <c r="AM57" s="78"/>
-      <c r="AN57" s="79"/>
+      <c r="AL57" s="69"/>
+      <c r="AM57" s="70"/>
+      <c r="AN57" s="71"/>
       <c r="AR57" s="13"/>
     </row>
     <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5252,277 +5214,277 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="83"/>
-      <c r="C59" s="84"/>
+      <c r="B59" s="88"/>
+      <c r="C59" s="89"/>
       <c r="D59" s="60"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="83"/>
-      <c r="G59" s="84"/>
+      <c r="F59" s="88"/>
+      <c r="G59" s="89"/>
       <c r="H59" s="60"/>
       <c r="I59" s="32"/>
-      <c r="J59" s="83"/>
-      <c r="K59" s="84"/>
+      <c r="J59" s="88"/>
+      <c r="K59" s="89"/>
       <c r="L59" s="60"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="67"/>
-      <c r="O59" s="68"/>
+      <c r="N59" s="75"/>
+      <c r="O59" s="76"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="67"/>
-      <c r="S59" s="68"/>
+      <c r="R59" s="75"/>
+      <c r="S59" s="76"/>
       <c r="T59" s="34"/>
       <c r="U59" s="32"/>
-      <c r="V59" s="67" t="s">
+      <c r="V59" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="W59" s="68"/>
+      <c r="W59" s="76"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="54"/>
-      <c r="Z59" s="67"/>
-      <c r="AA59" s="68"/>
+      <c r="Z59" s="75"/>
+      <c r="AA59" s="76"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="67"/>
-      <c r="AE59" s="68"/>
+      <c r="AD59" s="75"/>
+      <c r="AE59" s="76"/>
       <c r="AF59" s="34"/>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="67"/>
-      <c r="AI59" s="68"/>
+      <c r="AH59" s="75"/>
+      <c r="AI59" s="76"/>
       <c r="AJ59" s="34"/>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="110" t="s">
+      <c r="AL59" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AM59" s="111"/>
+      <c r="AM59" s="81"/>
       <c r="AN59" s="59"/>
       <c r="AR59" s="13"/>
     </row>
     <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="71"/>
-      <c r="C60" s="72"/>
-      <c r="D60" s="73"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="74"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="71"/>
-      <c r="G60" s="72"/>
-      <c r="H60" s="73"/>
+      <c r="F60" s="72"/>
+      <c r="G60" s="73"/>
+      <c r="H60" s="74"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="71"/>
-      <c r="K60" s="72"/>
-      <c r="L60" s="73"/>
+      <c r="J60" s="72"/>
+      <c r="K60" s="73"/>
+      <c r="L60" s="74"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="96"/>
-      <c r="O60" s="97"/>
-      <c r="P60" s="98"/>
+      <c r="N60" s="82"/>
+      <c r="O60" s="83"/>
+      <c r="P60" s="84"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="96"/>
-      <c r="S60" s="97"/>
-      <c r="T60" s="98"/>
+      <c r="R60" s="82"/>
+      <c r="S60" s="83"/>
+      <c r="T60" s="84"/>
       <c r="U60" s="32"/>
-      <c r="V60" s="96" t="s">
+      <c r="V60" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="W60" s="97"/>
-      <c r="X60" s="98"/>
+      <c r="W60" s="83"/>
+      <c r="X60" s="84"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="96"/>
-      <c r="AA60" s="97"/>
-      <c r="AB60" s="98"/>
+      <c r="Z60" s="82"/>
+      <c r="AA60" s="83"/>
+      <c r="AB60" s="84"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="96"/>
-      <c r="AE60" s="97"/>
-      <c r="AF60" s="98"/>
+      <c r="AD60" s="82"/>
+      <c r="AE60" s="83"/>
+      <c r="AF60" s="84"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="96"/>
-      <c r="AI60" s="97"/>
-      <c r="AJ60" s="98"/>
+      <c r="AH60" s="82"/>
+      <c r="AI60" s="83"/>
+      <c r="AJ60" s="84"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="115" t="s">
+      <c r="AL60" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="AM60" s="116"/>
-      <c r="AN60" s="117"/>
+      <c r="AM60" s="139"/>
+      <c r="AN60" s="140"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="80"/>
-      <c r="C61" s="81"/>
-      <c r="D61" s="82"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="64"/>
+      <c r="D61" s="65"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="80"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="82"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="64"/>
+      <c r="H61" s="65"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="80"/>
-      <c r="K61" s="81"/>
-      <c r="L61" s="82"/>
+      <c r="J61" s="63"/>
+      <c r="K61" s="64"/>
+      <c r="L61" s="65"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="92"/>
-      <c r="O61" s="93"/>
-      <c r="P61" s="99"/>
+      <c r="N61" s="85"/>
+      <c r="O61" s="86"/>
+      <c r="P61" s="87"/>
       <c r="Q61" s="37"/>
-      <c r="R61" s="92"/>
-      <c r="S61" s="93"/>
-      <c r="T61" s="99"/>
+      <c r="R61" s="85"/>
+      <c r="S61" s="86"/>
+      <c r="T61" s="87"/>
       <c r="U61" s="37"/>
-      <c r="V61" s="92" t="s">
+      <c r="V61" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="W61" s="93"/>
-      <c r="X61" s="99"/>
+      <c r="W61" s="86"/>
+      <c r="X61" s="87"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="92"/>
-      <c r="AA61" s="93"/>
-      <c r="AB61" s="99"/>
+      <c r="Z61" s="85"/>
+      <c r="AA61" s="86"/>
+      <c r="AB61" s="87"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="92"/>
-      <c r="AE61" s="93"/>
-      <c r="AF61" s="99"/>
+      <c r="AD61" s="85"/>
+      <c r="AE61" s="86"/>
+      <c r="AF61" s="87"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="92"/>
-      <c r="AI61" s="93"/>
-      <c r="AJ61" s="99"/>
+      <c r="AH61" s="85"/>
+      <c r="AI61" s="86"/>
+      <c r="AJ61" s="87"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="118" t="s">
+      <c r="AL61" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="AM61" s="119"/>
-      <c r="AN61" s="120"/>
+      <c r="AM61" s="136"/>
+      <c r="AN61" s="137"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="74"/>
-      <c r="C62" s="75"/>
-      <c r="D62" s="76"/>
+      <c r="B62" s="66"/>
+      <c r="C62" s="67"/>
+      <c r="D62" s="68"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="74"/>
-      <c r="G62" s="75"/>
-      <c r="H62" s="76"/>
+      <c r="F62" s="66"/>
+      <c r="G62" s="67"/>
+      <c r="H62" s="68"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="74"/>
-      <c r="K62" s="75"/>
-      <c r="L62" s="76"/>
+      <c r="J62" s="66"/>
+      <c r="K62" s="67"/>
+      <c r="L62" s="68"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="87"/>
-      <c r="O62" s="88"/>
-      <c r="P62" s="89"/>
+      <c r="N62" s="77"/>
+      <c r="O62" s="78"/>
+      <c r="P62" s="79"/>
       <c r="Q62" s="44"/>
-      <c r="R62" s="87"/>
-      <c r="S62" s="88"/>
-      <c r="T62" s="89"/>
+      <c r="R62" s="77"/>
+      <c r="S62" s="78"/>
+      <c r="T62" s="79"/>
       <c r="U62" s="44"/>
-      <c r="V62" s="74" t="s">
+      <c r="V62" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="W62" s="75"/>
-      <c r="X62" s="76"/>
+      <c r="W62" s="67"/>
+      <c r="X62" s="68"/>
       <c r="Y62" s="40"/>
-      <c r="Z62" s="87"/>
-      <c r="AA62" s="88"/>
-      <c r="AB62" s="89"/>
+      <c r="Z62" s="77"/>
+      <c r="AA62" s="78"/>
+      <c r="AB62" s="79"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="87"/>
-      <c r="AE62" s="88"/>
-      <c r="AF62" s="89"/>
+      <c r="AD62" s="77"/>
+      <c r="AE62" s="78"/>
+      <c r="AF62" s="79"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="87"/>
-      <c r="AI62" s="88"/>
-      <c r="AJ62" s="89"/>
+      <c r="AH62" s="77"/>
+      <c r="AI62" s="78"/>
+      <c r="AJ62" s="79"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="87" t="s">
+      <c r="AL62" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AM62" s="88"/>
-      <c r="AN62" s="89"/>
+      <c r="AM62" s="78"/>
+      <c r="AN62" s="79"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="87"/>
-      <c r="C63" s="88"/>
-      <c r="D63" s="89"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="78"/>
+      <c r="D63" s="79"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="87"/>
-      <c r="G63" s="88"/>
-      <c r="H63" s="89"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="78"/>
+      <c r="H63" s="79"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="87"/>
-      <c r="K63" s="88"/>
-      <c r="L63" s="89"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="78"/>
+      <c r="L63" s="79"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="87"/>
-      <c r="O63" s="88"/>
-      <c r="P63" s="89"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="78"/>
+      <c r="P63" s="79"/>
       <c r="Q63" s="44"/>
-      <c r="R63" s="87"/>
-      <c r="S63" s="88"/>
-      <c r="T63" s="89"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="78"/>
+      <c r="T63" s="79"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="87" t="s">
+      <c r="V63" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="W63" s="88"/>
-      <c r="X63" s="89"/>
+      <c r="W63" s="78"/>
+      <c r="X63" s="79"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="87"/>
-      <c r="AA63" s="88"/>
-      <c r="AB63" s="89"/>
+      <c r="Z63" s="77"/>
+      <c r="AA63" s="78"/>
+      <c r="AB63" s="79"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="87"/>
-      <c r="AE63" s="88"/>
-      <c r="AF63" s="89"/>
+      <c r="AD63" s="77"/>
+      <c r="AE63" s="78"/>
+      <c r="AF63" s="79"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="87"/>
-      <c r="AI63" s="88"/>
-      <c r="AJ63" s="89"/>
+      <c r="AH63" s="77"/>
+      <c r="AI63" s="78"/>
+      <c r="AJ63" s="79"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="87" t="s">
+      <c r="AL63" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="AM63" s="88"/>
-      <c r="AN63" s="89"/>
+      <c r="AM63" s="78"/>
+      <c r="AN63" s="79"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="77"/>
-      <c r="C64" s="78"/>
-      <c r="D64" s="79"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="71"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="77"/>
-      <c r="G64" s="78"/>
-      <c r="H64" s="79"/>
+      <c r="F64" s="69"/>
+      <c r="G64" s="70"/>
+      <c r="H64" s="71"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="77"/>
-      <c r="K64" s="78"/>
-      <c r="L64" s="79"/>
+      <c r="J64" s="69"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="71"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="77"/>
-      <c r="O64" s="78"/>
-      <c r="P64" s="79"/>
+      <c r="N64" s="69"/>
+      <c r="O64" s="70"/>
+      <c r="P64" s="71"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="77"/>
-      <c r="S64" s="78"/>
-      <c r="T64" s="79"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="70"/>
+      <c r="T64" s="71"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="77"/>
-      <c r="W64" s="78"/>
-      <c r="X64" s="79"/>
+      <c r="V64" s="69"/>
+      <c r="W64" s="70"/>
+      <c r="X64" s="71"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="77"/>
-      <c r="AA64" s="78"/>
-      <c r="AB64" s="79"/>
+      <c r="Z64" s="69"/>
+      <c r="AA64" s="70"/>
+      <c r="AB64" s="71"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="77"/>
-      <c r="AE64" s="78"/>
-      <c r="AF64" s="79"/>
+      <c r="AD64" s="69"/>
+      <c r="AE64" s="70"/>
+      <c r="AF64" s="71"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="77"/>
-      <c r="AI64" s="78"/>
-      <c r="AJ64" s="79"/>
+      <c r="AH64" s="69"/>
+      <c r="AI64" s="70"/>
+      <c r="AJ64" s="71"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="77" t="s">
+      <c r="AL64" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="AM64" s="78"/>
-      <c r="AN64" s="79"/>
+      <c r="AM64" s="70"/>
+      <c r="AN64" s="71"/>
       <c r="AR64" s="13"/>
     </row>
     <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5585,23 +5547,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="109" t="s">
+      <c r="N66" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="109"/>
-      <c r="P66" s="109"/>
-      <c r="Q66" s="109"/>
-      <c r="R66" s="109"/>
-      <c r="S66" s="109"/>
-      <c r="T66" s="109"/>
-      <c r="U66" s="109"/>
-      <c r="V66" s="109"/>
-      <c r="W66" s="109"/>
-      <c r="X66" s="109"/>
-      <c r="Y66" s="109"/>
-      <c r="Z66" s="109"/>
-      <c r="AA66" s="109"/>
-      <c r="AB66" s="109"/>
+      <c r="O66" s="100"/>
+      <c r="P66" s="100"/>
+      <c r="Q66" s="100"/>
+      <c r="R66" s="100"/>
+      <c r="S66" s="100"/>
+      <c r="T66" s="100"/>
+      <c r="U66" s="100"/>
+      <c r="V66" s="100"/>
+      <c r="W66" s="100"/>
+      <c r="X66" s="100"/>
+      <c r="Y66" s="100"/>
+      <c r="Z66" s="100"/>
+      <c r="AA66" s="100"/>
+      <c r="AB66" s="100"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5632,21 +5594,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="109"/>
-      <c r="O67" s="109"/>
-      <c r="P67" s="109"/>
-      <c r="Q67" s="109"/>
-      <c r="R67" s="109"/>
-      <c r="S67" s="109"/>
-      <c r="T67" s="109"/>
-      <c r="U67" s="109"/>
-      <c r="V67" s="109"/>
-      <c r="W67" s="109"/>
-      <c r="X67" s="109"/>
-      <c r="Y67" s="109"/>
-      <c r="Z67" s="109"/>
-      <c r="AA67" s="109"/>
-      <c r="AB67" s="109"/>
+      <c r="N67" s="100"/>
+      <c r="O67" s="100"/>
+      <c r="P67" s="100"/>
+      <c r="Q67" s="100"/>
+      <c r="R67" s="100"/>
+      <c r="S67" s="100"/>
+      <c r="T67" s="100"/>
+      <c r="U67" s="100"/>
+      <c r="V67" s="100"/>
+      <c r="W67" s="100"/>
+      <c r="X67" s="100"/>
+      <c r="Y67" s="100"/>
+      <c r="Z67" s="100"/>
+      <c r="AA67" s="100"/>
+      <c r="AB67" s="100"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5666,58 +5628,58 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="83"/>
-      <c r="C68" s="84"/>
+      <c r="B68" s="88"/>
+      <c r="C68" s="89"/>
       <c r="D68" s="60"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="83"/>
-      <c r="G68" s="84"/>
+      <c r="F68" s="88"/>
+      <c r="G68" s="89"/>
       <c r="H68" s="60"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="83"/>
-      <c r="K68" s="84"/>
+      <c r="J68" s="88"/>
+      <c r="K68" s="89"/>
       <c r="L68" s="60"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="67" t="s">
+      <c r="N68" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="O68" s="68"/>
+      <c r="O68" s="76"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="44"/>
-      <c r="R68" s="110" t="s">
+      <c r="R68" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="S68" s="111"/>
+      <c r="S68" s="81"/>
       <c r="T68" s="59"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="67" t="s">
+      <c r="V68" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="W68" s="68"/>
+      <c r="W68" s="76"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="67" t="s">
+      <c r="Z68" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="AA68" s="68"/>
+      <c r="AA68" s="76"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="67" t="s">
+      <c r="AD68" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="AE68" s="68"/>
+      <c r="AE68" s="76"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="67" t="s">
+      <c r="AH68" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="AI68" s="68"/>
+      <c r="AI68" s="76"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="67" t="s">
+      <c r="AL68" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="AM68" s="68"/>
+      <c r="AM68" s="76"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5728,57 +5690,57 @@
     </row>
     <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12"/>
-      <c r="B69" s="71"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="73"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="73"/>
+      <c r="D69" s="74"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="72"/>
-      <c r="H69" s="73"/>
+      <c r="F69" s="72"/>
+      <c r="G69" s="73"/>
+      <c r="H69" s="74"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="71"/>
-      <c r="K69" s="72"/>
-      <c r="L69" s="73"/>
+      <c r="J69" s="72"/>
+      <c r="K69" s="73"/>
+      <c r="L69" s="74"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="96"/>
-      <c r="O69" s="97"/>
-      <c r="P69" s="98"/>
+      <c r="N69" s="82"/>
+      <c r="O69" s="83"/>
+      <c r="P69" s="84"/>
       <c r="Q69" s="44"/>
-      <c r="R69" s="112" t="s">
+      <c r="R69" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="S69" s="113"/>
-      <c r="T69" s="114"/>
+      <c r="S69" s="114"/>
+      <c r="T69" s="115"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="96" t="s">
+      <c r="V69" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="W69" s="97"/>
-      <c r="X69" s="98"/>
+      <c r="W69" s="83"/>
+      <c r="X69" s="84"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="96" t="s">
+      <c r="Z69" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="AA69" s="97"/>
-      <c r="AB69" s="98"/>
+      <c r="AA69" s="83"/>
+      <c r="AB69" s="84"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="96" t="s">
+      <c r="AD69" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="AE69" s="97"/>
-      <c r="AF69" s="98"/>
+      <c r="AE69" s="83"/>
+      <c r="AF69" s="84"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="96" t="s">
+      <c r="AH69" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="AI69" s="97"/>
-      <c r="AJ69" s="98"/>
+      <c r="AI69" s="83"/>
+      <c r="AJ69" s="84"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="96" t="s">
+      <c r="AL69" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="AM69" s="97"/>
-      <c r="AN69" s="98"/>
+      <c r="AM69" s="83"/>
+      <c r="AN69" s="84"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5788,59 +5750,59 @@
     </row>
     <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12"/>
-      <c r="B70" s="80"/>
-      <c r="C70" s="81"/>
-      <c r="D70" s="82"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="64"/>
+      <c r="D70" s="65"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="80"/>
-      <c r="G70" s="81"/>
-      <c r="H70" s="82"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="65"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="80"/>
-      <c r="K70" s="81"/>
-      <c r="L70" s="82"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="64"/>
+      <c r="L70" s="65"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="92" t="s">
+      <c r="N70" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="O70" s="93"/>
-      <c r="P70" s="99"/>
+      <c r="O70" s="86"/>
+      <c r="P70" s="87"/>
       <c r="Q70" s="44"/>
-      <c r="R70" s="103" t="s">
+      <c r="R70" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="S70" s="104"/>
-      <c r="T70" s="105"/>
+      <c r="S70" s="91"/>
+      <c r="T70" s="92"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="92" t="s">
+      <c r="V70" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="W70" s="93"/>
-      <c r="X70" s="99"/>
+      <c r="W70" s="86"/>
+      <c r="X70" s="87"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="92" t="s">
+      <c r="Z70" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="AA70" s="93"/>
-      <c r="AB70" s="99"/>
+      <c r="AA70" s="86"/>
+      <c r="AB70" s="87"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="92" t="s">
+      <c r="AD70" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="AE70" s="93"/>
-      <c r="AF70" s="99"/>
+      <c r="AE70" s="86"/>
+      <c r="AF70" s="87"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="92" t="s">
+      <c r="AH70" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="AI70" s="93"/>
-      <c r="AJ70" s="99"/>
+      <c r="AI70" s="86"/>
+      <c r="AJ70" s="87"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="92" t="s">
+      <c r="AL70" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="AM70" s="93"/>
-      <c r="AN70" s="99"/>
+      <c r="AM70" s="86"/>
+      <c r="AN70" s="87"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5850,59 +5812,59 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="74"/>
-      <c r="C71" s="75"/>
-      <c r="D71" s="76"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="67"/>
+      <c r="D71" s="68"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
-      <c r="H71" s="76"/>
+      <c r="F71" s="66"/>
+      <c r="G71" s="67"/>
+      <c r="H71" s="68"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="74"/>
-      <c r="K71" s="75"/>
-      <c r="L71" s="76"/>
+      <c r="J71" s="66"/>
+      <c r="K71" s="67"/>
+      <c r="L71" s="68"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="74" t="s">
+      <c r="N71" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="O71" s="75"/>
-      <c r="P71" s="76"/>
+      <c r="O71" s="67"/>
+      <c r="P71" s="68"/>
       <c r="Q71" s="37"/>
-      <c r="R71" s="100" t="s">
+      <c r="R71" s="107" t="s">
         <v>84</v>
       </c>
-      <c r="S71" s="101"/>
-      <c r="T71" s="102"/>
+      <c r="S71" s="108"/>
+      <c r="T71" s="109"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="74" t="s">
+      <c r="V71" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="W71" s="75"/>
-      <c r="X71" s="76"/>
+      <c r="W71" s="67"/>
+      <c r="X71" s="68"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="74" t="s">
+      <c r="Z71" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AA71" s="75"/>
-      <c r="AB71" s="76"/>
+      <c r="AA71" s="67"/>
+      <c r="AB71" s="68"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="74" t="s">
+      <c r="AD71" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AE71" s="75"/>
-      <c r="AF71" s="76"/>
+      <c r="AE71" s="67"/>
+      <c r="AF71" s="68"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="74" t="s">
+      <c r="AH71" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AI71" s="75"/>
-      <c r="AJ71" s="76"/>
+      <c r="AI71" s="67"/>
+      <c r="AJ71" s="68"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="74" t="s">
+      <c r="AL71" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AM71" s="75"/>
-      <c r="AN71" s="76"/>
+      <c r="AM71" s="67"/>
+      <c r="AN71" s="68"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -5912,47 +5874,47 @@
     </row>
     <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="77"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="79"/>
+      <c r="B72" s="69"/>
+      <c r="C72" s="70"/>
+      <c r="D72" s="71"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="77"/>
-      <c r="G72" s="78"/>
-      <c r="H72" s="79"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="71"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="77"/>
-      <c r="K72" s="78"/>
-      <c r="L72" s="79"/>
+      <c r="J72" s="69"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="71"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="77"/>
-      <c r="O72" s="78"/>
-      <c r="P72" s="79"/>
+      <c r="N72" s="69"/>
+      <c r="O72" s="70"/>
+      <c r="P72" s="71"/>
       <c r="Q72" s="32"/>
-      <c r="R72" s="106"/>
-      <c r="S72" s="107"/>
-      <c r="T72" s="108"/>
+      <c r="R72" s="110"/>
+      <c r="S72" s="111"/>
+      <c r="T72" s="112"/>
       <c r="U72" s="36"/>
-      <c r="V72" s="77" t="s">
+      <c r="V72" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="W72" s="78"/>
-      <c r="X72" s="79"/>
+      <c r="W72" s="70"/>
+      <c r="X72" s="71"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="77"/>
-      <c r="AA72" s="78"/>
-      <c r="AB72" s="79"/>
+      <c r="Z72" s="69"/>
+      <c r="AA72" s="70"/>
+      <c r="AB72" s="71"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="77"/>
-      <c r="AE72" s="78"/>
-      <c r="AF72" s="79"/>
+      <c r="AD72" s="69"/>
+      <c r="AE72" s="70"/>
+      <c r="AF72" s="71"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="77"/>
-      <c r="AI72" s="78"/>
-      <c r="AJ72" s="79"/>
+      <c r="AH72" s="69"/>
+      <c r="AI72" s="70"/>
+      <c r="AJ72" s="71"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="77"/>
-      <c r="AM72" s="78"/>
-      <c r="AN72" s="79"/>
+      <c r="AL72" s="69"/>
+      <c r="AM72" s="70"/>
+      <c r="AN72" s="71"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
@@ -6006,54 +5968,54 @@
     </row>
     <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="83"/>
-      <c r="C74" s="84"/>
+      <c r="B74" s="88"/>
+      <c r="C74" s="89"/>
       <c r="D74" s="60"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="83" t="s">
+      <c r="F74" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="G74" s="84"/>
+      <c r="G74" s="89"/>
       <c r="H74" s="60"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="83"/>
-      <c r="K74" s="84"/>
+      <c r="J74" s="88"/>
+      <c r="K74" s="89"/>
       <c r="L74" s="60"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="90" t="s">
+      <c r="N74" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="O74" s="91"/>
+      <c r="O74" s="94"/>
       <c r="P74" s="55" t="s">
         <v>79</v>
       </c>
       <c r="Q74" s="44"/>
-      <c r="R74" s="67"/>
-      <c r="S74" s="68"/>
+      <c r="R74" s="75"/>
+      <c r="S74" s="76"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="110" t="s">
+      <c r="V74" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="W74" s="111"/>
-      <c r="X74" s="59"/>
+      <c r="W74" s="76"/>
+      <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="67" t="s">
+      <c r="Z74" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="AA74" s="68"/>
+      <c r="AA74" s="76"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="67"/>
-      <c r="AE74" s="68"/>
+      <c r="AD74" s="75"/>
+      <c r="AE74" s="76"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="67"/>
-      <c r="AI74" s="68"/>
+      <c r="AH74" s="75"/>
+      <c r="AI74" s="76"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="67"/>
-      <c r="AM74" s="68"/>
+      <c r="AL74" s="75"/>
+      <c r="AM74" s="76"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
@@ -6062,49 +6024,49 @@
     </row>
     <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12"/>
-      <c r="B75" s="71"/>
-      <c r="C75" s="72"/>
-      <c r="D75" s="73"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="73"/>
+      <c r="D75" s="74"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="71"/>
-      <c r="G75" s="72"/>
-      <c r="H75" s="73"/>
+      <c r="F75" s="72"/>
+      <c r="G75" s="73"/>
+      <c r="H75" s="74"/>
       <c r="I75" s="32"/>
-      <c r="J75" s="71"/>
-      <c r="K75" s="72"/>
-      <c r="L75" s="73"/>
+      <c r="J75" s="72"/>
+      <c r="K75" s="73"/>
+      <c r="L75" s="74"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="96" t="s">
+      <c r="N75" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="O75" s="97"/>
-      <c r="P75" s="98"/>
+      <c r="O75" s="83"/>
+      <c r="P75" s="84"/>
       <c r="Q75" s="44"/>
-      <c r="R75" s="96"/>
-      <c r="S75" s="97"/>
-      <c r="T75" s="98"/>
+      <c r="R75" s="82"/>
+      <c r="S75" s="83"/>
+      <c r="T75" s="84"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="115" t="s">
+      <c r="V75" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="W75" s="116"/>
-      <c r="X75" s="117"/>
+      <c r="W75" s="83"/>
+      <c r="X75" s="84"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="96"/>
-      <c r="AA75" s="97"/>
-      <c r="AB75" s="98"/>
+      <c r="Z75" s="82"/>
+      <c r="AA75" s="83"/>
+      <c r="AB75" s="84"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="96"/>
-      <c r="AE75" s="97"/>
-      <c r="AF75" s="98"/>
+      <c r="AD75" s="82"/>
+      <c r="AE75" s="83"/>
+      <c r="AF75" s="84"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="96"/>
-      <c r="AI75" s="97"/>
-      <c r="AJ75" s="98"/>
+      <c r="AH75" s="82"/>
+      <c r="AI75" s="83"/>
+      <c r="AJ75" s="84"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="96"/>
-      <c r="AM75" s="97"/>
-      <c r="AN75" s="98"/>
+      <c r="AL75" s="82"/>
+      <c r="AM75" s="83"/>
+      <c r="AN75" s="84"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
@@ -6112,53 +6074,53 @@
     </row>
     <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12"/>
-      <c r="B76" s="80"/>
-      <c r="C76" s="81"/>
-      <c r="D76" s="82"/>
+      <c r="B76" s="63"/>
+      <c r="C76" s="64"/>
+      <c r="D76" s="65"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="80" t="s">
+      <c r="F76" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="81"/>
-      <c r="H76" s="82"/>
+      <c r="G76" s="64"/>
+      <c r="H76" s="65"/>
       <c r="I76" s="32"/>
-      <c r="J76" s="80"/>
-      <c r="K76" s="81"/>
-      <c r="L76" s="82"/>
+      <c r="J76" s="63"/>
+      <c r="K76" s="64"/>
+      <c r="L76" s="65"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="92" t="s">
+      <c r="N76" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="O76" s="93"/>
-      <c r="P76" s="99"/>
+      <c r="O76" s="86"/>
+      <c r="P76" s="87"/>
       <c r="Q76" s="44"/>
-      <c r="R76" s="92"/>
-      <c r="S76" s="93"/>
-      <c r="T76" s="99"/>
+      <c r="R76" s="85"/>
+      <c r="S76" s="86"/>
+      <c r="T76" s="87"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="103" t="s">
+      <c r="V76" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="W76" s="104"/>
-      <c r="X76" s="105"/>
+      <c r="W76" s="86"/>
+      <c r="X76" s="87"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="92" t="s">
+      <c r="Z76" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="AA76" s="93"/>
-      <c r="AB76" s="99"/>
+      <c r="AA76" s="86"/>
+      <c r="AB76" s="87"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="92"/>
-      <c r="AE76" s="93"/>
-      <c r="AF76" s="99"/>
+      <c r="AD76" s="85"/>
+      <c r="AE76" s="86"/>
+      <c r="AF76" s="87"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="92"/>
-      <c r="AI76" s="93"/>
-      <c r="AJ76" s="99"/>
+      <c r="AH76" s="85"/>
+      <c r="AI76" s="86"/>
+      <c r="AJ76" s="87"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="92"/>
-      <c r="AM76" s="93"/>
-      <c r="AN76" s="99"/>
+      <c r="AL76" s="85"/>
+      <c r="AM76" s="86"/>
+      <c r="AN76" s="87"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6166,53 +6128,53 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="74"/>
-      <c r="C77" s="75"/>
-      <c r="D77" s="76"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="67"/>
+      <c r="D77" s="68"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="74" t="s">
+      <c r="F77" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="G77" s="75"/>
-      <c r="H77" s="76"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="68"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="74"/>
-      <c r="K77" s="75"/>
-      <c r="L77" s="76"/>
+      <c r="J77" s="66"/>
+      <c r="K77" s="67"/>
+      <c r="L77" s="68"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="74" t="s">
+      <c r="N77" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="O77" s="75"/>
-      <c r="P77" s="76"/>
+      <c r="O77" s="67"/>
+      <c r="P77" s="68"/>
       <c r="Q77" s="37"/>
-      <c r="R77" s="74"/>
-      <c r="S77" s="75"/>
-      <c r="T77" s="76"/>
+      <c r="R77" s="66"/>
+      <c r="S77" s="67"/>
+      <c r="T77" s="68"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="141" t="s">
-        <v>89</v>
-      </c>
-      <c r="W77" s="142"/>
-      <c r="X77" s="143"/>
+      <c r="V77" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="W77" s="67"/>
+      <c r="X77" s="68"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="74" t="s">
+      <c r="Z77" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="AA77" s="75"/>
-      <c r="AB77" s="76"/>
+      <c r="AA77" s="67"/>
+      <c r="AB77" s="68"/>
       <c r="AC77" s="31"/>
-      <c r="AD77" s="74"/>
-      <c r="AE77" s="75"/>
-      <c r="AF77" s="76"/>
+      <c r="AD77" s="66"/>
+      <c r="AE77" s="67"/>
+      <c r="AF77" s="68"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="74"/>
-      <c r="AI77" s="75"/>
-      <c r="AJ77" s="76"/>
+      <c r="AH77" s="66"/>
+      <c r="AI77" s="67"/>
+      <c r="AJ77" s="68"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="74"/>
-      <c r="AM77" s="75"/>
-      <c r="AN77" s="76"/>
+      <c r="AL77" s="66"/>
+      <c r="AM77" s="67"/>
+      <c r="AN77" s="68"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6220,47 +6182,47 @@
     </row>
     <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="77"/>
-      <c r="C78" s="78"/>
-      <c r="D78" s="79"/>
+      <c r="B78" s="69"/>
+      <c r="C78" s="70"/>
+      <c r="D78" s="71"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="77"/>
-      <c r="G78" s="78"/>
-      <c r="H78" s="79"/>
+      <c r="F78" s="69"/>
+      <c r="G78" s="70"/>
+      <c r="H78" s="71"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="77"/>
-      <c r="K78" s="78"/>
-      <c r="L78" s="79"/>
+      <c r="J78" s="69"/>
+      <c r="K78" s="70"/>
+      <c r="L78" s="71"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="77"/>
-      <c r="O78" s="78"/>
-      <c r="P78" s="79"/>
+      <c r="N78" s="69"/>
+      <c r="O78" s="70"/>
+      <c r="P78" s="71"/>
       <c r="Q78" s="44"/>
-      <c r="R78" s="77"/>
-      <c r="S78" s="78"/>
-      <c r="T78" s="79"/>
+      <c r="R78" s="69"/>
+      <c r="S78" s="70"/>
+      <c r="T78" s="71"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="144" t="s">
-        <v>88</v>
-      </c>
-      <c r="W78" s="145"/>
-      <c r="X78" s="146"/>
+      <c r="V78" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="W78" s="70"/>
+      <c r="X78" s="71"/>
       <c r="Y78" s="31"/>
-      <c r="Z78" s="77"/>
-      <c r="AA78" s="78"/>
-      <c r="AB78" s="79"/>
+      <c r="Z78" s="69"/>
+      <c r="AA78" s="70"/>
+      <c r="AB78" s="71"/>
       <c r="AC78" s="31"/>
-      <c r="AD78" s="77"/>
-      <c r="AE78" s="78"/>
-      <c r="AF78" s="79"/>
+      <c r="AD78" s="69"/>
+      <c r="AE78" s="70"/>
+      <c r="AF78" s="71"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="77"/>
-      <c r="AI78" s="78"/>
-      <c r="AJ78" s="79"/>
+      <c r="AH78" s="69"/>
+      <c r="AI78" s="70"/>
+      <c r="AJ78" s="71"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="77"/>
-      <c r="AM78" s="78"/>
-      <c r="AN78" s="79"/>
+      <c r="AL78" s="69"/>
+      <c r="AM78" s="70"/>
+      <c r="AN78" s="71"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
@@ -6314,48 +6276,48 @@
     </row>
     <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="110" t="s">
+      <c r="B80" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="111"/>
+      <c r="C80" s="81"/>
       <c r="D80" s="59"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="83"/>
-      <c r="G80" s="84"/>
+      <c r="F80" s="88"/>
+      <c r="G80" s="89"/>
       <c r="H80" s="60"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="83"/>
-      <c r="K80" s="84"/>
+      <c r="J80" s="88"/>
+      <c r="K80" s="89"/>
       <c r="L80" s="60"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="67"/>
-      <c r="O80" s="68"/>
+      <c r="N80" s="75"/>
+      <c r="O80" s="76"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="44"/>
-      <c r="R80" s="67"/>
-      <c r="S80" s="68"/>
+      <c r="R80" s="75"/>
+      <c r="S80" s="76"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="67" t="s">
+      <c r="V80" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="W80" s="68"/>
+      <c r="W80" s="76"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="67"/>
-      <c r="AA80" s="68"/>
+      <c r="Z80" s="75"/>
+      <c r="AA80" s="76"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="67"/>
-      <c r="AE80" s="68"/>
+      <c r="AD80" s="75"/>
+      <c r="AE80" s="76"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="67"/>
-      <c r="AI80" s="68"/>
+      <c r="AH80" s="75"/>
+      <c r="AI80" s="76"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="67"/>
-      <c r="AM80" s="68"/>
+      <c r="AL80" s="75"/>
+      <c r="AM80" s="76"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
@@ -6364,49 +6326,49 @@
     </row>
     <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12"/>
-      <c r="B81" s="112" t="s">
+      <c r="B81" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="113"/>
-      <c r="D81" s="114"/>
+      <c r="C81" s="114"/>
+      <c r="D81" s="115"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="72"/>
-      <c r="H81" s="73"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="73"/>
+      <c r="H81" s="74"/>
       <c r="I81" s="35"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="72"/>
-      <c r="L81" s="73"/>
+      <c r="J81" s="72"/>
+      <c r="K81" s="73"/>
+      <c r="L81" s="74"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="96"/>
-      <c r="O81" s="97"/>
-      <c r="P81" s="98"/>
+      <c r="N81" s="82"/>
+      <c r="O81" s="83"/>
+      <c r="P81" s="84"/>
       <c r="Q81" s="44"/>
-      <c r="R81" s="96"/>
-      <c r="S81" s="97"/>
-      <c r="T81" s="98"/>
+      <c r="R81" s="82"/>
+      <c r="S81" s="83"/>
+      <c r="T81" s="84"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="96" t="s">
+      <c r="V81" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="W81" s="97"/>
-      <c r="X81" s="98"/>
+      <c r="W81" s="83"/>
+      <c r="X81" s="84"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="96"/>
-      <c r="AA81" s="97"/>
-      <c r="AB81" s="98"/>
+      <c r="Z81" s="82"/>
+      <c r="AA81" s="83"/>
+      <c r="AB81" s="84"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="96"/>
-      <c r="AE81" s="97"/>
-      <c r="AF81" s="98"/>
+      <c r="AD81" s="82"/>
+      <c r="AE81" s="83"/>
+      <c r="AF81" s="84"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="96"/>
-      <c r="AI81" s="97"/>
-      <c r="AJ81" s="98"/>
+      <c r="AH81" s="82"/>
+      <c r="AI81" s="83"/>
+      <c r="AJ81" s="84"/>
       <c r="AK81" s="35"/>
-      <c r="AL81" s="96"/>
-      <c r="AM81" s="97"/>
-      <c r="AN81" s="98"/>
+      <c r="AL81" s="82"/>
+      <c r="AM81" s="83"/>
+      <c r="AN81" s="84"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
@@ -6414,49 +6376,49 @@
     </row>
     <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12"/>
-      <c r="B82" s="103" t="s">
+      <c r="B82" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="C82" s="104"/>
-      <c r="D82" s="105"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="92"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="80"/>
-      <c r="G82" s="81"/>
-      <c r="H82" s="82"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="64"/>
+      <c r="H82" s="65"/>
       <c r="I82" s="31"/>
-      <c r="J82" s="80"/>
-      <c r="K82" s="81"/>
-      <c r="L82" s="82"/>
+      <c r="J82" s="63"/>
+      <c r="K82" s="64"/>
+      <c r="L82" s="65"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="92"/>
-      <c r="O82" s="93"/>
-      <c r="P82" s="99"/>
+      <c r="N82" s="85"/>
+      <c r="O82" s="86"/>
+      <c r="P82" s="87"/>
       <c r="Q82" s="44"/>
-      <c r="R82" s="92"/>
-      <c r="S82" s="93"/>
-      <c r="T82" s="99"/>
+      <c r="R82" s="85"/>
+      <c r="S82" s="86"/>
+      <c r="T82" s="87"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="92" t="s">
+      <c r="V82" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="W82" s="93"/>
-      <c r="X82" s="99"/>
+      <c r="W82" s="86"/>
+      <c r="X82" s="87"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="92"/>
-      <c r="AA82" s="93"/>
-      <c r="AB82" s="99"/>
+      <c r="Z82" s="85"/>
+      <c r="AA82" s="86"/>
+      <c r="AB82" s="87"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="92"/>
-      <c r="AE82" s="93"/>
-      <c r="AF82" s="99"/>
+      <c r="AD82" s="85"/>
+      <c r="AE82" s="86"/>
+      <c r="AF82" s="87"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="92"/>
-      <c r="AI82" s="93"/>
-      <c r="AJ82" s="99"/>
+      <c r="AH82" s="85"/>
+      <c r="AI82" s="86"/>
+      <c r="AJ82" s="87"/>
       <c r="AK82" s="31"/>
-      <c r="AL82" s="92"/>
-      <c r="AM82" s="93"/>
-      <c r="AN82" s="99"/>
+      <c r="AL82" s="85"/>
+      <c r="AM82" s="86"/>
+      <c r="AN82" s="87"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6464,49 +6426,49 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="100" t="s">
+      <c r="B83" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="101"/>
-      <c r="D83" s="102"/>
+      <c r="C83" s="108"/>
+      <c r="D83" s="109"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="74"/>
-      <c r="G83" s="75"/>
-      <c r="H83" s="76"/>
+      <c r="F83" s="66"/>
+      <c r="G83" s="67"/>
+      <c r="H83" s="68"/>
       <c r="I83" s="31"/>
-      <c r="J83" s="74"/>
-      <c r="K83" s="75"/>
-      <c r="L83" s="76"/>
+      <c r="J83" s="66"/>
+      <c r="K83" s="67"/>
+      <c r="L83" s="68"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="74"/>
-      <c r="O83" s="75"/>
-      <c r="P83" s="76"/>
+      <c r="N83" s="66"/>
+      <c r="O83" s="67"/>
+      <c r="P83" s="68"/>
       <c r="Q83" s="44"/>
-      <c r="R83" s="74"/>
-      <c r="S83" s="75"/>
-      <c r="T83" s="76"/>
+      <c r="R83" s="66"/>
+      <c r="S83" s="67"/>
+      <c r="T83" s="68"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="147" t="s">
-        <v>10</v>
-      </c>
-      <c r="W83" s="148"/>
-      <c r="X83" s="149"/>
+      <c r="V83" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="W83" s="67"/>
+      <c r="X83" s="68"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="74"/>
-      <c r="AA83" s="75"/>
-      <c r="AB83" s="76"/>
+      <c r="Z83" s="66"/>
+      <c r="AA83" s="67"/>
+      <c r="AB83" s="68"/>
       <c r="AC83" s="43"/>
-      <c r="AD83" s="74"/>
-      <c r="AE83" s="75"/>
-      <c r="AF83" s="76"/>
+      <c r="AD83" s="66"/>
+      <c r="AE83" s="67"/>
+      <c r="AF83" s="68"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="74"/>
-      <c r="AI83" s="75"/>
-      <c r="AJ83" s="76"/>
+      <c r="AH83" s="66"/>
+      <c r="AI83" s="67"/>
+      <c r="AJ83" s="68"/>
       <c r="AK83" s="31"/>
-      <c r="AL83" s="74"/>
-      <c r="AM83" s="75"/>
-      <c r="AN83" s="76"/>
+      <c r="AL83" s="66"/>
+      <c r="AM83" s="67"/>
+      <c r="AN83" s="68"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6514,47 +6476,47 @@
     </row>
     <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
-      <c r="B84" s="106"/>
-      <c r="C84" s="107"/>
-      <c r="D84" s="108"/>
+      <c r="B84" s="110"/>
+      <c r="C84" s="111"/>
+      <c r="D84" s="112"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="77"/>
-      <c r="G84" s="78"/>
-      <c r="H84" s="79"/>
+      <c r="F84" s="69"/>
+      <c r="G84" s="70"/>
+      <c r="H84" s="71"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="77"/>
-      <c r="K84" s="78"/>
-      <c r="L84" s="79"/>
+      <c r="J84" s="69"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="71"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="77"/>
-      <c r="O84" s="78"/>
-      <c r="P84" s="79"/>
+      <c r="N84" s="69"/>
+      <c r="O84" s="70"/>
+      <c r="P84" s="71"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="77"/>
-      <c r="S84" s="78"/>
-      <c r="T84" s="79"/>
+      <c r="R84" s="69"/>
+      <c r="S84" s="70"/>
+      <c r="T84" s="71"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="77" t="s">
+      <c r="V84" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="W84" s="78"/>
-      <c r="X84" s="79"/>
+      <c r="W84" s="70"/>
+      <c r="X84" s="71"/>
       <c r="Y84" s="32"/>
-      <c r="Z84" s="77"/>
-      <c r="AA84" s="78"/>
-      <c r="AB84" s="79"/>
+      <c r="Z84" s="69"/>
+      <c r="AA84" s="70"/>
+      <c r="AB84" s="71"/>
       <c r="AC84" s="43"/>
-      <c r="AD84" s="77"/>
-      <c r="AE84" s="78"/>
-      <c r="AF84" s="79"/>
+      <c r="AD84" s="69"/>
+      <c r="AE84" s="70"/>
+      <c r="AF84" s="71"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="77"/>
-      <c r="AI84" s="78"/>
-      <c r="AJ84" s="79"/>
+      <c r="AH84" s="69"/>
+      <c r="AI84" s="70"/>
+      <c r="AJ84" s="71"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="77"/>
-      <c r="AM84" s="78"/>
-      <c r="AN84" s="79"/>
+      <c r="AL84" s="69"/>
+      <c r="AM84" s="70"/>
+      <c r="AN84" s="71"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
@@ -6608,44 +6570,44 @@
     </row>
     <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="83"/>
-      <c r="C86" s="84"/>
+      <c r="B86" s="88"/>
+      <c r="C86" s="89"/>
       <c r="D86" s="60"/>
       <c r="E86" s="36"/>
-      <c r="F86" s="83"/>
-      <c r="G86" s="84"/>
+      <c r="F86" s="88"/>
+      <c r="G86" s="89"/>
       <c r="H86" s="60"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="83"/>
-      <c r="K86" s="84"/>
+      <c r="J86" s="88"/>
+      <c r="K86" s="89"/>
       <c r="L86" s="60"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="67"/>
-      <c r="O86" s="68"/>
+      <c r="N86" s="75"/>
+      <c r="O86" s="76"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="67"/>
-      <c r="S86" s="68"/>
+      <c r="R86" s="75"/>
+      <c r="S86" s="76"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="67"/>
-      <c r="W86" s="68"/>
+      <c r="V86" s="75"/>
+      <c r="W86" s="76"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="67"/>
-      <c r="AA86" s="68"/>
+      <c r="Z86" s="75"/>
+      <c r="AA86" s="76"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="67"/>
-      <c r="AE86" s="68"/>
+      <c r="AD86" s="75"/>
+      <c r="AE86" s="76"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="36"/>
-      <c r="AH86" s="67"/>
-      <c r="AI86" s="68"/>
+      <c r="AH86" s="75"/>
+      <c r="AI86" s="76"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="67"/>
-      <c r="AM86" s="68"/>
+      <c r="AL86" s="75"/>
+      <c r="AM86" s="76"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
@@ -6654,45 +6616,45 @@
     </row>
     <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12"/>
-      <c r="B87" s="71"/>
-      <c r="C87" s="72"/>
-      <c r="D87" s="73"/>
+      <c r="B87" s="72"/>
+      <c r="C87" s="73"/>
+      <c r="D87" s="74"/>
       <c r="E87" s="38"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="72"/>
-      <c r="H87" s="73"/>
+      <c r="F87" s="72"/>
+      <c r="G87" s="73"/>
+      <c r="H87" s="74"/>
       <c r="I87" s="35"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="72"/>
-      <c r="L87" s="73"/>
+      <c r="J87" s="72"/>
+      <c r="K87" s="73"/>
+      <c r="L87" s="74"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="96"/>
-      <c r="O87" s="97"/>
-      <c r="P87" s="98"/>
+      <c r="N87" s="82"/>
+      <c r="O87" s="83"/>
+      <c r="P87" s="84"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="96"/>
-      <c r="S87" s="97"/>
-      <c r="T87" s="98"/>
+      <c r="R87" s="82"/>
+      <c r="S87" s="83"/>
+      <c r="T87" s="84"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="96"/>
-      <c r="W87" s="97"/>
-      <c r="X87" s="98"/>
+      <c r="V87" s="82"/>
+      <c r="W87" s="83"/>
+      <c r="X87" s="84"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="96"/>
-      <c r="AA87" s="97"/>
-      <c r="AB87" s="98"/>
+      <c r="Z87" s="82"/>
+      <c r="AA87" s="83"/>
+      <c r="AB87" s="84"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="96"/>
-      <c r="AE87" s="97"/>
-      <c r="AF87" s="98"/>
+      <c r="AD87" s="82"/>
+      <c r="AE87" s="83"/>
+      <c r="AF87" s="84"/>
       <c r="AG87" s="38"/>
-      <c r="AH87" s="96"/>
-      <c r="AI87" s="97"/>
-      <c r="AJ87" s="98"/>
+      <c r="AH87" s="82"/>
+      <c r="AI87" s="83"/>
+      <c r="AJ87" s="84"/>
       <c r="AK87" s="35"/>
-      <c r="AL87" s="96"/>
-      <c r="AM87" s="97"/>
-      <c r="AN87" s="98"/>
+      <c r="AL87" s="82"/>
+      <c r="AM87" s="83"/>
+      <c r="AN87" s="84"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
@@ -6700,45 +6662,45 @@
     </row>
     <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12"/>
-      <c r="B88" s="80"/>
-      <c r="C88" s="81"/>
-      <c r="D88" s="82"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="64"/>
+      <c r="D88" s="65"/>
       <c r="E88" s="37"/>
-      <c r="F88" s="80"/>
-      <c r="G88" s="81"/>
-      <c r="H88" s="82"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="64"/>
+      <c r="H88" s="65"/>
       <c r="I88" s="31"/>
-      <c r="J88" s="80"/>
-      <c r="K88" s="81"/>
-      <c r="L88" s="82"/>
+      <c r="J88" s="63"/>
+      <c r="K88" s="64"/>
+      <c r="L88" s="65"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="92"/>
-      <c r="O88" s="93"/>
-      <c r="P88" s="99"/>
+      <c r="N88" s="85"/>
+      <c r="O88" s="86"/>
+      <c r="P88" s="87"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="92"/>
-      <c r="S88" s="93"/>
-      <c r="T88" s="99"/>
+      <c r="R88" s="85"/>
+      <c r="S88" s="86"/>
+      <c r="T88" s="87"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="92"/>
-      <c r="W88" s="93"/>
-      <c r="X88" s="99"/>
+      <c r="V88" s="85"/>
+      <c r="W88" s="86"/>
+      <c r="X88" s="87"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="92"/>
-      <c r="AA88" s="93"/>
-      <c r="AB88" s="99"/>
+      <c r="Z88" s="85"/>
+      <c r="AA88" s="86"/>
+      <c r="AB88" s="87"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="92"/>
-      <c r="AE88" s="93"/>
-      <c r="AF88" s="99"/>
+      <c r="AD88" s="85"/>
+      <c r="AE88" s="86"/>
+      <c r="AF88" s="87"/>
       <c r="AG88" s="37"/>
-      <c r="AH88" s="92"/>
-      <c r="AI88" s="93"/>
-      <c r="AJ88" s="99"/>
+      <c r="AH88" s="85"/>
+      <c r="AI88" s="86"/>
+      <c r="AJ88" s="87"/>
       <c r="AK88" s="31"/>
-      <c r="AL88" s="92"/>
-      <c r="AM88" s="93"/>
-      <c r="AN88" s="99"/>
+      <c r="AL88" s="85"/>
+      <c r="AM88" s="86"/>
+      <c r="AN88" s="87"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -6746,45 +6708,45 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="74"/>
-      <c r="C89" s="75"/>
-      <c r="D89" s="76"/>
+      <c r="B89" s="66"/>
+      <c r="C89" s="67"/>
+      <c r="D89" s="68"/>
       <c r="E89" s="43"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
-      <c r="H89" s="76"/>
+      <c r="F89" s="66"/>
+      <c r="G89" s="67"/>
+      <c r="H89" s="68"/>
       <c r="I89" s="31"/>
-      <c r="J89" s="74"/>
-      <c r="K89" s="75"/>
-      <c r="L89" s="76"/>
+      <c r="J89" s="66"/>
+      <c r="K89" s="67"/>
+      <c r="L89" s="68"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="74"/>
-      <c r="O89" s="75"/>
-      <c r="P89" s="76"/>
+      <c r="N89" s="66"/>
+      <c r="O89" s="67"/>
+      <c r="P89" s="68"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="74"/>
-      <c r="S89" s="75"/>
-      <c r="T89" s="76"/>
+      <c r="R89" s="66"/>
+      <c r="S89" s="67"/>
+      <c r="T89" s="68"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="74"/>
-      <c r="W89" s="75"/>
-      <c r="X89" s="76"/>
+      <c r="V89" s="66"/>
+      <c r="W89" s="67"/>
+      <c r="X89" s="68"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="74"/>
-      <c r="AA89" s="75"/>
-      <c r="AB89" s="76"/>
+      <c r="Z89" s="66"/>
+      <c r="AA89" s="67"/>
+      <c r="AB89" s="68"/>
       <c r="AC89" s="43"/>
-      <c r="AD89" s="74"/>
-      <c r="AE89" s="75"/>
-      <c r="AF89" s="76"/>
+      <c r="AD89" s="66"/>
+      <c r="AE89" s="67"/>
+      <c r="AF89" s="68"/>
       <c r="AG89" s="43"/>
-      <c r="AH89" s="74"/>
-      <c r="AI89" s="75"/>
-      <c r="AJ89" s="76"/>
+      <c r="AH89" s="66"/>
+      <c r="AI89" s="67"/>
+      <c r="AJ89" s="68"/>
       <c r="AK89" s="31"/>
-      <c r="AL89" s="74"/>
-      <c r="AM89" s="75"/>
-      <c r="AN89" s="76"/>
+      <c r="AL89" s="66"/>
+      <c r="AM89" s="67"/>
+      <c r="AN89" s="68"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -6792,45 +6754,45 @@
     </row>
     <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
-      <c r="B90" s="77"/>
-      <c r="C90" s="78"/>
-      <c r="D90" s="79"/>
+      <c r="B90" s="69"/>
+      <c r="C90" s="70"/>
+      <c r="D90" s="71"/>
       <c r="E90" s="43"/>
-      <c r="F90" s="77"/>
-      <c r="G90" s="78"/>
-      <c r="H90" s="79"/>
+      <c r="F90" s="69"/>
+      <c r="G90" s="70"/>
+      <c r="H90" s="71"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="77"/>
-      <c r="K90" s="78"/>
-      <c r="L90" s="79"/>
+      <c r="J90" s="69"/>
+      <c r="K90" s="70"/>
+      <c r="L90" s="71"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="77"/>
-      <c r="O90" s="78"/>
-      <c r="P90" s="79"/>
+      <c r="N90" s="69"/>
+      <c r="O90" s="70"/>
+      <c r="P90" s="71"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="77"/>
-      <c r="S90" s="78"/>
-      <c r="T90" s="79"/>
+      <c r="R90" s="69"/>
+      <c r="S90" s="70"/>
+      <c r="T90" s="71"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="77"/>
-      <c r="W90" s="78"/>
-      <c r="X90" s="79"/>
+      <c r="V90" s="69"/>
+      <c r="W90" s="70"/>
+      <c r="X90" s="71"/>
       <c r="Y90" s="32"/>
-      <c r="Z90" s="77"/>
-      <c r="AA90" s="78"/>
-      <c r="AB90" s="79"/>
+      <c r="Z90" s="69"/>
+      <c r="AA90" s="70"/>
+      <c r="AB90" s="71"/>
       <c r="AC90" s="43"/>
-      <c r="AD90" s="77"/>
-      <c r="AE90" s="78"/>
-      <c r="AF90" s="79"/>
+      <c r="AD90" s="69"/>
+      <c r="AE90" s="70"/>
+      <c r="AF90" s="71"/>
       <c r="AG90" s="43"/>
-      <c r="AH90" s="77"/>
-      <c r="AI90" s="78"/>
-      <c r="AJ90" s="79"/>
+      <c r="AH90" s="69"/>
+      <c r="AI90" s="70"/>
+      <c r="AJ90" s="71"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="77"/>
-      <c r="AM90" s="78"/>
-      <c r="AN90" s="79"/>
+      <c r="AL90" s="69"/>
+      <c r="AM90" s="70"/>
+      <c r="AN90" s="71"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
@@ -6884,44 +6846,44 @@
     </row>
     <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="83"/>
-      <c r="C92" s="84"/>
+      <c r="B92" s="88"/>
+      <c r="C92" s="89"/>
       <c r="D92" s="60"/>
       <c r="E92" s="44"/>
-      <c r="F92" s="83"/>
-      <c r="G92" s="84"/>
+      <c r="F92" s="88"/>
+      <c r="G92" s="89"/>
       <c r="H92" s="60"/>
       <c r="I92" s="32"/>
-      <c r="J92" s="83"/>
-      <c r="K92" s="84"/>
+      <c r="J92" s="88"/>
+      <c r="K92" s="89"/>
       <c r="L92" s="60"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="67"/>
-      <c r="O92" s="68"/>
+      <c r="N92" s="75"/>
+      <c r="O92" s="76"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="32"/>
-      <c r="R92" s="67"/>
-      <c r="S92" s="68"/>
+      <c r="R92" s="75"/>
+      <c r="S92" s="76"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="67"/>
-      <c r="W92" s="68"/>
+      <c r="V92" s="75"/>
+      <c r="W92" s="76"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="67"/>
-      <c r="AA92" s="68"/>
+      <c r="Z92" s="75"/>
+      <c r="AA92" s="76"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="67"/>
-      <c r="AE92" s="68"/>
+      <c r="AD92" s="75"/>
+      <c r="AE92" s="76"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="67"/>
-      <c r="AI92" s="68"/>
+      <c r="AH92" s="75"/>
+      <c r="AI92" s="76"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="67"/>
-      <c r="AM92" s="68"/>
+      <c r="AL92" s="75"/>
+      <c r="AM92" s="76"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
@@ -6930,45 +6892,45 @@
     </row>
     <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12"/>
-      <c r="B93" s="71"/>
-      <c r="C93" s="72"/>
-      <c r="D93" s="73"/>
+      <c r="B93" s="72"/>
+      <c r="C93" s="73"/>
+      <c r="D93" s="74"/>
       <c r="E93" s="43"/>
-      <c r="F93" s="71"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="73"/>
+      <c r="F93" s="72"/>
+      <c r="G93" s="73"/>
+      <c r="H93" s="74"/>
       <c r="I93" s="35"/>
-      <c r="J93" s="71"/>
-      <c r="K93" s="72"/>
-      <c r="L93" s="73"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="73"/>
+      <c r="L93" s="74"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="96"/>
-      <c r="O93" s="97"/>
-      <c r="P93" s="98"/>
+      <c r="N93" s="82"/>
+      <c r="O93" s="83"/>
+      <c r="P93" s="84"/>
       <c r="Q93" s="35"/>
-      <c r="R93" s="96"/>
-      <c r="S93" s="97"/>
-      <c r="T93" s="98"/>
+      <c r="R93" s="82"/>
+      <c r="S93" s="83"/>
+      <c r="T93" s="84"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="96"/>
-      <c r="W93" s="97"/>
-      <c r="X93" s="98"/>
+      <c r="V93" s="82"/>
+      <c r="W93" s="83"/>
+      <c r="X93" s="84"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="96"/>
-      <c r="AA93" s="97"/>
-      <c r="AB93" s="98"/>
+      <c r="Z93" s="82"/>
+      <c r="AA93" s="83"/>
+      <c r="AB93" s="84"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="96"/>
-      <c r="AE93" s="97"/>
-      <c r="AF93" s="98"/>
+      <c r="AD93" s="82"/>
+      <c r="AE93" s="83"/>
+      <c r="AF93" s="84"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="96"/>
-      <c r="AI93" s="97"/>
-      <c r="AJ93" s="98"/>
+      <c r="AH93" s="82"/>
+      <c r="AI93" s="83"/>
+      <c r="AJ93" s="84"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="96"/>
-      <c r="AM93" s="97"/>
-      <c r="AN93" s="98"/>
+      <c r="AL93" s="82"/>
+      <c r="AM93" s="83"/>
+      <c r="AN93" s="84"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
@@ -6976,45 +6938,45 @@
     </row>
     <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12"/>
-      <c r="B94" s="80"/>
-      <c r="C94" s="81"/>
-      <c r="D94" s="82"/>
+      <c r="B94" s="63"/>
+      <c r="C94" s="64"/>
+      <c r="D94" s="65"/>
       <c r="E94" s="44"/>
-      <c r="F94" s="80"/>
-      <c r="G94" s="81"/>
-      <c r="H94" s="82"/>
+      <c r="F94" s="63"/>
+      <c r="G94" s="64"/>
+      <c r="H94" s="65"/>
       <c r="I94" s="31"/>
-      <c r="J94" s="80"/>
-      <c r="K94" s="81"/>
-      <c r="L94" s="82"/>
+      <c r="J94" s="63"/>
+      <c r="K94" s="64"/>
+      <c r="L94" s="65"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="92"/>
-      <c r="O94" s="93"/>
-      <c r="P94" s="99"/>
+      <c r="N94" s="85"/>
+      <c r="O94" s="86"/>
+      <c r="P94" s="87"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="92"/>
-      <c r="S94" s="93"/>
-      <c r="T94" s="99"/>
+      <c r="R94" s="85"/>
+      <c r="S94" s="86"/>
+      <c r="T94" s="87"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="92"/>
-      <c r="W94" s="93"/>
-      <c r="X94" s="99"/>
+      <c r="V94" s="85"/>
+      <c r="W94" s="86"/>
+      <c r="X94" s="87"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="92"/>
-      <c r="AA94" s="93"/>
-      <c r="AB94" s="99"/>
+      <c r="Z94" s="85"/>
+      <c r="AA94" s="86"/>
+      <c r="AB94" s="87"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="92"/>
-      <c r="AE94" s="93"/>
-      <c r="AF94" s="99"/>
+      <c r="AD94" s="85"/>
+      <c r="AE94" s="86"/>
+      <c r="AF94" s="87"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="92"/>
-      <c r="AI94" s="93"/>
-      <c r="AJ94" s="99"/>
+      <c r="AH94" s="85"/>
+      <c r="AI94" s="86"/>
+      <c r="AJ94" s="87"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="92"/>
-      <c r="AM94" s="93"/>
-      <c r="AN94" s="99"/>
+      <c r="AL94" s="85"/>
+      <c r="AM94" s="86"/>
+      <c r="AN94" s="87"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -7022,45 +6984,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="74"/>
-      <c r="C95" s="75"/>
-      <c r="D95" s="76"/>
+      <c r="B95" s="66"/>
+      <c r="C95" s="67"/>
+      <c r="D95" s="68"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="74"/>
-      <c r="G95" s="75"/>
-      <c r="H95" s="76"/>
+      <c r="F95" s="66"/>
+      <c r="G95" s="67"/>
+      <c r="H95" s="68"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="74"/>
-      <c r="K95" s="75"/>
-      <c r="L95" s="76"/>
+      <c r="J95" s="66"/>
+      <c r="K95" s="67"/>
+      <c r="L95" s="68"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="74"/>
-      <c r="O95" s="75"/>
-      <c r="P95" s="76"/>
+      <c r="N95" s="66"/>
+      <c r="O95" s="67"/>
+      <c r="P95" s="68"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="74"/>
-      <c r="S95" s="75"/>
-      <c r="T95" s="76"/>
+      <c r="R95" s="66"/>
+      <c r="S95" s="67"/>
+      <c r="T95" s="68"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="74"/>
-      <c r="W95" s="75"/>
-      <c r="X95" s="76"/>
+      <c r="V95" s="66"/>
+      <c r="W95" s="67"/>
+      <c r="X95" s="68"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="74"/>
-      <c r="AA95" s="75"/>
-      <c r="AB95" s="76"/>
+      <c r="Z95" s="66"/>
+      <c r="AA95" s="67"/>
+      <c r="AB95" s="68"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="74"/>
-      <c r="AE95" s="75"/>
-      <c r="AF95" s="76"/>
+      <c r="AD95" s="66"/>
+      <c r="AE95" s="67"/>
+      <c r="AF95" s="68"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="74"/>
-      <c r="AI95" s="75"/>
-      <c r="AJ95" s="76"/>
+      <c r="AH95" s="66"/>
+      <c r="AI95" s="67"/>
+      <c r="AJ95" s="68"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="74"/>
-      <c r="AM95" s="75"/>
-      <c r="AN95" s="76"/>
+      <c r="AL95" s="66"/>
+      <c r="AM95" s="67"/>
+      <c r="AN95" s="68"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7068,45 +7030,45 @@
     </row>
     <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
-      <c r="B96" s="77"/>
-      <c r="C96" s="78"/>
-      <c r="D96" s="79"/>
+      <c r="B96" s="69"/>
+      <c r="C96" s="70"/>
+      <c r="D96" s="71"/>
       <c r="E96" s="44"/>
-      <c r="F96" s="77"/>
-      <c r="G96" s="78"/>
-      <c r="H96" s="79"/>
+      <c r="F96" s="69"/>
+      <c r="G96" s="70"/>
+      <c r="H96" s="71"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="77"/>
-      <c r="K96" s="78"/>
-      <c r="L96" s="79"/>
+      <c r="J96" s="69"/>
+      <c r="K96" s="70"/>
+      <c r="L96" s="71"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="77"/>
-      <c r="O96" s="78"/>
-      <c r="P96" s="79"/>
+      <c r="N96" s="69"/>
+      <c r="O96" s="70"/>
+      <c r="P96" s="71"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="77"/>
-      <c r="S96" s="78"/>
-      <c r="T96" s="79"/>
+      <c r="R96" s="69"/>
+      <c r="S96" s="70"/>
+      <c r="T96" s="71"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="77"/>
-      <c r="W96" s="78"/>
-      <c r="X96" s="79"/>
+      <c r="V96" s="69"/>
+      <c r="W96" s="70"/>
+      <c r="X96" s="71"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="77"/>
-      <c r="AA96" s="78"/>
-      <c r="AB96" s="79"/>
+      <c r="Z96" s="69"/>
+      <c r="AA96" s="70"/>
+      <c r="AB96" s="71"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="77"/>
-      <c r="AE96" s="78"/>
-      <c r="AF96" s="79"/>
+      <c r="AD96" s="69"/>
+      <c r="AE96" s="70"/>
+      <c r="AF96" s="71"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="77"/>
-      <c r="AI96" s="78"/>
-      <c r="AJ96" s="79"/>
+      <c r="AH96" s="69"/>
+      <c r="AI96" s="70"/>
+      <c r="AJ96" s="71"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="77"/>
-      <c r="AM96" s="78"/>
-      <c r="AN96" s="79"/>
+      <c r="AL96" s="69"/>
+      <c r="AM96" s="70"/>
+      <c r="AN96" s="71"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
@@ -7160,48 +7122,48 @@
     </row>
     <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="83"/>
-      <c r="C98" s="84"/>
+      <c r="B98" s="88"/>
+      <c r="C98" s="89"/>
       <c r="D98" s="60"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="83"/>
-      <c r="G98" s="84"/>
+      <c r="F98" s="88"/>
+      <c r="G98" s="89"/>
       <c r="H98" s="60"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="83"/>
-      <c r="K98" s="84"/>
+      <c r="J98" s="88"/>
+      <c r="K98" s="89"/>
       <c r="L98" s="60"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="67" t="s">
+      <c r="N98" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="O98" s="68"/>
+      <c r="O98" s="76"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="67" t="s">
+      <c r="R98" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="S98" s="68"/>
+      <c r="S98" s="76"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="67"/>
-      <c r="W98" s="68"/>
+      <c r="V98" s="75"/>
+      <c r="W98" s="76"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="67"/>
-      <c r="AA98" s="68"/>
+      <c r="Z98" s="75"/>
+      <c r="AA98" s="76"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="67"/>
-      <c r="AE98" s="68"/>
+      <c r="AD98" s="75"/>
+      <c r="AE98" s="76"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="67"/>
-      <c r="AI98" s="68"/>
+      <c r="AH98" s="75"/>
+      <c r="AI98" s="76"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="67"/>
-      <c r="AM98" s="68"/>
+      <c r="AL98" s="75"/>
+      <c r="AM98" s="76"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
@@ -7210,45 +7172,45 @@
     </row>
     <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12"/>
-      <c r="B99" s="71"/>
-      <c r="C99" s="72"/>
-      <c r="D99" s="73"/>
+      <c r="B99" s="72"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="74"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="72"/>
-      <c r="H99" s="73"/>
+      <c r="F99" s="72"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="74"/>
       <c r="I99" s="35"/>
-      <c r="J99" s="71"/>
-      <c r="K99" s="72"/>
-      <c r="L99" s="73"/>
+      <c r="J99" s="72"/>
+      <c r="K99" s="73"/>
+      <c r="L99" s="74"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="96"/>
-      <c r="O99" s="97"/>
-      <c r="P99" s="98"/>
+      <c r="N99" s="82"/>
+      <c r="O99" s="83"/>
+      <c r="P99" s="84"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="96"/>
-      <c r="S99" s="97"/>
-      <c r="T99" s="98"/>
+      <c r="R99" s="82"/>
+      <c r="S99" s="83"/>
+      <c r="T99" s="84"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="96"/>
-      <c r="W99" s="97"/>
-      <c r="X99" s="98"/>
+      <c r="V99" s="82"/>
+      <c r="W99" s="83"/>
+      <c r="X99" s="84"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="96"/>
-      <c r="AA99" s="97"/>
-      <c r="AB99" s="98"/>
+      <c r="Z99" s="82"/>
+      <c r="AA99" s="83"/>
+      <c r="AB99" s="84"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="96"/>
-      <c r="AE99" s="97"/>
-      <c r="AF99" s="98"/>
+      <c r="AD99" s="82"/>
+      <c r="AE99" s="83"/>
+      <c r="AF99" s="84"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="96"/>
-      <c r="AI99" s="97"/>
-      <c r="AJ99" s="98"/>
+      <c r="AH99" s="82"/>
+      <c r="AI99" s="83"/>
+      <c r="AJ99" s="84"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="96"/>
-      <c r="AM99" s="97"/>
-      <c r="AN99" s="98"/>
+      <c r="AL99" s="82"/>
+      <c r="AM99" s="83"/>
+      <c r="AN99" s="84"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
@@ -7256,45 +7218,45 @@
     </row>
     <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12"/>
-      <c r="B100" s="80"/>
-      <c r="C100" s="81"/>
-      <c r="D100" s="82"/>
+      <c r="B100" s="63"/>
+      <c r="C100" s="64"/>
+      <c r="D100" s="65"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="80"/>
-      <c r="G100" s="81"/>
-      <c r="H100" s="82"/>
+      <c r="F100" s="63"/>
+      <c r="G100" s="64"/>
+      <c r="H100" s="65"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="80"/>
-      <c r="K100" s="81"/>
-      <c r="L100" s="82"/>
+      <c r="J100" s="63"/>
+      <c r="K100" s="64"/>
+      <c r="L100" s="65"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="92"/>
-      <c r="O100" s="93"/>
-      <c r="P100" s="99"/>
+      <c r="N100" s="85"/>
+      <c r="O100" s="86"/>
+      <c r="P100" s="87"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="92"/>
-      <c r="S100" s="93"/>
-      <c r="T100" s="99"/>
+      <c r="R100" s="85"/>
+      <c r="S100" s="86"/>
+      <c r="T100" s="87"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="92"/>
-      <c r="W100" s="93"/>
-      <c r="X100" s="99"/>
+      <c r="V100" s="85"/>
+      <c r="W100" s="86"/>
+      <c r="X100" s="87"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="92"/>
-      <c r="AA100" s="93"/>
-      <c r="AB100" s="99"/>
+      <c r="Z100" s="85"/>
+      <c r="AA100" s="86"/>
+      <c r="AB100" s="87"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="92"/>
-      <c r="AE100" s="93"/>
-      <c r="AF100" s="99"/>
+      <c r="AD100" s="85"/>
+      <c r="AE100" s="86"/>
+      <c r="AF100" s="87"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="92"/>
-      <c r="AI100" s="93"/>
-      <c r="AJ100" s="99"/>
+      <c r="AH100" s="85"/>
+      <c r="AI100" s="86"/>
+      <c r="AJ100" s="87"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="92"/>
-      <c r="AM100" s="93"/>
-      <c r="AN100" s="99"/>
+      <c r="AL100" s="85"/>
+      <c r="AM100" s="86"/>
+      <c r="AN100" s="87"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7302,49 +7264,49 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="74"/>
-      <c r="C101" s="75"/>
-      <c r="D101" s="76"/>
+      <c r="B101" s="66"/>
+      <c r="C101" s="67"/>
+      <c r="D101" s="68"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="74"/>
-      <c r="G101" s="75"/>
-      <c r="H101" s="76"/>
+      <c r="F101" s="66"/>
+      <c r="G101" s="67"/>
+      <c r="H101" s="68"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="74"/>
-      <c r="K101" s="75"/>
-      <c r="L101" s="76"/>
+      <c r="J101" s="66"/>
+      <c r="K101" s="67"/>
+      <c r="L101" s="68"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="74" t="s">
+      <c r="N101" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="O101" s="75"/>
-      <c r="P101" s="76"/>
+      <c r="O101" s="67"/>
+      <c r="P101" s="68"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="74" t="s">
+      <c r="R101" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="S101" s="75"/>
-      <c r="T101" s="76"/>
+      <c r="S101" s="67"/>
+      <c r="T101" s="68"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="74"/>
-      <c r="W101" s="75"/>
-      <c r="X101" s="76"/>
+      <c r="V101" s="66"/>
+      <c r="W101" s="67"/>
+      <c r="X101" s="68"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="74"/>
-      <c r="AA101" s="75"/>
-      <c r="AB101" s="76"/>
+      <c r="Z101" s="66"/>
+      <c r="AA101" s="67"/>
+      <c r="AB101" s="68"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="74"/>
-      <c r="AE101" s="75"/>
-      <c r="AF101" s="76"/>
+      <c r="AD101" s="66"/>
+      <c r="AE101" s="67"/>
+      <c r="AF101" s="68"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="74"/>
-      <c r="AI101" s="75"/>
-      <c r="AJ101" s="76"/>
+      <c r="AH101" s="66"/>
+      <c r="AI101" s="67"/>
+      <c r="AJ101" s="68"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="74"/>
-      <c r="AM101" s="75"/>
-      <c r="AN101" s="76"/>
+      <c r="AL101" s="66"/>
+      <c r="AM101" s="67"/>
+      <c r="AN101" s="68"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7352,45 +7314,45 @@
     </row>
     <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="78"/>
-      <c r="D102" s="79"/>
+      <c r="B102" s="69"/>
+      <c r="C102" s="70"/>
+      <c r="D102" s="71"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="77"/>
-      <c r="G102" s="78"/>
-      <c r="H102" s="79"/>
+      <c r="F102" s="69"/>
+      <c r="G102" s="70"/>
+      <c r="H102" s="71"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="77"/>
-      <c r="K102" s="78"/>
-      <c r="L102" s="79"/>
+      <c r="J102" s="69"/>
+      <c r="K102" s="70"/>
+      <c r="L102" s="71"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="77"/>
-      <c r="O102" s="78"/>
-      <c r="P102" s="79"/>
+      <c r="N102" s="69"/>
+      <c r="O102" s="70"/>
+      <c r="P102" s="71"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="77"/>
-      <c r="S102" s="78"/>
-      <c r="T102" s="79"/>
+      <c r="R102" s="69"/>
+      <c r="S102" s="70"/>
+      <c r="T102" s="71"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="77"/>
-      <c r="W102" s="78"/>
-      <c r="X102" s="79"/>
+      <c r="V102" s="69"/>
+      <c r="W102" s="70"/>
+      <c r="X102" s="71"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="77"/>
-      <c r="AA102" s="78"/>
-      <c r="AB102" s="79"/>
+      <c r="Z102" s="69"/>
+      <c r="AA102" s="70"/>
+      <c r="AB102" s="71"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="77"/>
-      <c r="AE102" s="78"/>
-      <c r="AF102" s="79"/>
+      <c r="AD102" s="69"/>
+      <c r="AE102" s="70"/>
+      <c r="AF102" s="71"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="77"/>
-      <c r="AI102" s="78"/>
-      <c r="AJ102" s="79"/>
+      <c r="AH102" s="69"/>
+      <c r="AI102" s="70"/>
+      <c r="AJ102" s="71"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="77"/>
-      <c r="AM102" s="78"/>
-      <c r="AN102" s="79"/>
+      <c r="AL102" s="69"/>
+      <c r="AM102" s="70"/>
+      <c r="AN102" s="71"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
@@ -7460,70 +7422,70 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="67"/>
-      <c r="C105" s="68"/>
+      <c r="B105" s="75"/>
+      <c r="C105" s="76"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="68"/>
+      <c r="F105" s="75"/>
+      <c r="G105" s="76"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="67"/>
-      <c r="K105" s="68"/>
+      <c r="J105" s="75"/>
+      <c r="K105" s="76"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="96"/>
-      <c r="C106" s="97"/>
-      <c r="D106" s="98"/>
+      <c r="B106" s="82"/>
+      <c r="C106" s="83"/>
+      <c r="D106" s="84"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="96"/>
-      <c r="G106" s="97"/>
-      <c r="H106" s="98"/>
+      <c r="F106" s="82"/>
+      <c r="G106" s="83"/>
+      <c r="H106" s="84"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="96"/>
-      <c r="K106" s="97"/>
-      <c r="L106" s="98"/>
+      <c r="J106" s="82"/>
+      <c r="K106" s="83"/>
+      <c r="L106" s="84"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="92"/>
-      <c r="C107" s="93"/>
-      <c r="D107" s="99"/>
+      <c r="B107" s="85"/>
+      <c r="C107" s="86"/>
+      <c r="D107" s="87"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="92"/>
-      <c r="G107" s="93"/>
-      <c r="H107" s="99"/>
+      <c r="F107" s="85"/>
+      <c r="G107" s="86"/>
+      <c r="H107" s="87"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="92"/>
-      <c r="K107" s="93"/>
-      <c r="L107" s="99"/>
+      <c r="J107" s="85"/>
+      <c r="K107" s="86"/>
+      <c r="L107" s="87"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="74"/>
-      <c r="C108" s="75"/>
-      <c r="D108" s="76"/>
+      <c r="B108" s="66"/>
+      <c r="C108" s="67"/>
+      <c r="D108" s="68"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="74"/>
-      <c r="G108" s="75"/>
-      <c r="H108" s="76"/>
+      <c r="F108" s="66"/>
+      <c r="G108" s="67"/>
+      <c r="H108" s="68"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="74"/>
-      <c r="K108" s="75"/>
-      <c r="L108" s="76"/>
+      <c r="J108" s="66"/>
+      <c r="K108" s="67"/>
+      <c r="L108" s="68"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="77"/>
-      <c r="C109" s="78"/>
-      <c r="D109" s="79"/>
+      <c r="B109" s="69"/>
+      <c r="C109" s="70"/>
+      <c r="D109" s="71"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="77"/>
-      <c r="G109" s="78"/>
-      <c r="H109" s="79"/>
+      <c r="F109" s="69"/>
+      <c r="G109" s="70"/>
+      <c r="H109" s="71"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="77"/>
-      <c r="K109" s="78"/>
-      <c r="L109" s="79"/>
+      <c r="J109" s="69"/>
+      <c r="K109" s="70"/>
+      <c r="L109" s="71"/>
     </row>
     <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="35"/>
@@ -7539,69 +7501,69 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="67"/>
-      <c r="C111" s="68"/>
+      <c r="B111" s="75"/>
+      <c r="C111" s="76"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="67"/>
-      <c r="G111" s="68"/>
+      <c r="F111" s="75"/>
+      <c r="G111" s="76"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="67"/>
-      <c r="K111" s="68"/>
+      <c r="J111" s="75"/>
+      <c r="K111" s="76"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="96"/>
-      <c r="C112" s="97"/>
-      <c r="D112" s="98"/>
+      <c r="B112" s="82"/>
+      <c r="C112" s="83"/>
+      <c r="D112" s="84"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="96"/>
-      <c r="G112" s="97"/>
-      <c r="H112" s="98"/>
+      <c r="F112" s="82"/>
+      <c r="G112" s="83"/>
+      <c r="H112" s="84"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="96"/>
-      <c r="K112" s="97"/>
-      <c r="L112" s="98"/>
+      <c r="J112" s="82"/>
+      <c r="K112" s="83"/>
+      <c r="L112" s="84"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="92"/>
-      <c r="C113" s="93"/>
-      <c r="D113" s="99"/>
+      <c r="B113" s="85"/>
+      <c r="C113" s="86"/>
+      <c r="D113" s="87"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="92"/>
-      <c r="G113" s="93"/>
-      <c r="H113" s="99"/>
+      <c r="F113" s="85"/>
+      <c r="G113" s="86"/>
+      <c r="H113" s="87"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="92"/>
-      <c r="K113" s="93"/>
-      <c r="L113" s="99"/>
+      <c r="J113" s="85"/>
+      <c r="K113" s="86"/>
+      <c r="L113" s="87"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="74"/>
-      <c r="C114" s="75"/>
-      <c r="D114" s="76"/>
+      <c r="B114" s="66"/>
+      <c r="C114" s="67"/>
+      <c r="D114" s="68"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="74"/>
-      <c r="G114" s="75"/>
-      <c r="H114" s="76"/>
+      <c r="F114" s="66"/>
+      <c r="G114" s="67"/>
+      <c r="H114" s="68"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="74"/>
-      <c r="K114" s="75"/>
-      <c r="L114" s="76"/>
+      <c r="J114" s="66"/>
+      <c r="K114" s="67"/>
+      <c r="L114" s="68"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="77"/>
-      <c r="C115" s="78"/>
-      <c r="D115" s="79"/>
+      <c r="B115" s="69"/>
+      <c r="C115" s="70"/>
+      <c r="D115" s="71"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="77"/>
-      <c r="G115" s="78"/>
-      <c r="H115" s="79"/>
+      <c r="F115" s="69"/>
+      <c r="G115" s="70"/>
+      <c r="H115" s="71"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="77"/>
-      <c r="K115" s="78"/>
-      <c r="L115" s="79"/>
+      <c r="J115" s="69"/>
+      <c r="K115" s="70"/>
+      <c r="L115" s="71"/>
     </row>
     <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="35"/>
@@ -7617,69 +7579,69 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="67"/>
-      <c r="C117" s="68"/>
+      <c r="B117" s="75"/>
+      <c r="C117" s="76"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="67"/>
-      <c r="G117" s="68"/>
+      <c r="F117" s="75"/>
+      <c r="G117" s="76"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="67"/>
-      <c r="K117" s="68"/>
+      <c r="J117" s="75"/>
+      <c r="K117" s="76"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="96"/>
-      <c r="C118" s="97"/>
-      <c r="D118" s="98"/>
+      <c r="B118" s="82"/>
+      <c r="C118" s="83"/>
+      <c r="D118" s="84"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="96"/>
-      <c r="G118" s="97"/>
-      <c r="H118" s="98"/>
+      <c r="F118" s="82"/>
+      <c r="G118" s="83"/>
+      <c r="H118" s="84"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="96"/>
-      <c r="K118" s="97"/>
-      <c r="L118" s="98"/>
+      <c r="J118" s="82"/>
+      <c r="K118" s="83"/>
+      <c r="L118" s="84"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="92"/>
-      <c r="C119" s="93"/>
-      <c r="D119" s="99"/>
+      <c r="B119" s="85"/>
+      <c r="C119" s="86"/>
+      <c r="D119" s="87"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="92"/>
-      <c r="G119" s="93"/>
-      <c r="H119" s="99"/>
+      <c r="F119" s="85"/>
+      <c r="G119" s="86"/>
+      <c r="H119" s="87"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="92"/>
-      <c r="K119" s="93"/>
-      <c r="L119" s="99"/>
+      <c r="J119" s="85"/>
+      <c r="K119" s="86"/>
+      <c r="L119" s="87"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="74"/>
-      <c r="C120" s="75"/>
-      <c r="D120" s="76"/>
+      <c r="B120" s="66"/>
+      <c r="C120" s="67"/>
+      <c r="D120" s="68"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="74"/>
-      <c r="G120" s="75"/>
-      <c r="H120" s="76"/>
+      <c r="F120" s="66"/>
+      <c r="G120" s="67"/>
+      <c r="H120" s="68"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="74"/>
-      <c r="K120" s="75"/>
-      <c r="L120" s="76"/>
+      <c r="J120" s="66"/>
+      <c r="K120" s="67"/>
+      <c r="L120" s="68"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="77"/>
-      <c r="C121" s="78"/>
-      <c r="D121" s="79"/>
+      <c r="B121" s="69"/>
+      <c r="C121" s="70"/>
+      <c r="D121" s="71"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="77"/>
-      <c r="G121" s="78"/>
-      <c r="H121" s="79"/>
+      <c r="F121" s="69"/>
+      <c r="G121" s="70"/>
+      <c r="H121" s="71"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="77"/>
-      <c r="K121" s="78"/>
-      <c r="L121" s="79"/>
+      <c r="J121" s="69"/>
+      <c r="K121" s="70"/>
+      <c r="L121" s="71"/>
     </row>
     <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="35"/>
@@ -7695,69 +7657,69 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="67"/>
-      <c r="C123" s="68"/>
+      <c r="B123" s="75"/>
+      <c r="C123" s="76"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="67"/>
-      <c r="G123" s="68"/>
+      <c r="F123" s="75"/>
+      <c r="G123" s="76"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="67"/>
-      <c r="K123" s="68"/>
+      <c r="J123" s="75"/>
+      <c r="K123" s="76"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="96"/>
-      <c r="C124" s="97"/>
-      <c r="D124" s="98"/>
+      <c r="B124" s="82"/>
+      <c r="C124" s="83"/>
+      <c r="D124" s="84"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="96"/>
-      <c r="G124" s="97"/>
-      <c r="H124" s="98"/>
+      <c r="F124" s="82"/>
+      <c r="G124" s="83"/>
+      <c r="H124" s="84"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="96"/>
-      <c r="K124" s="97"/>
-      <c r="L124" s="98"/>
+      <c r="J124" s="82"/>
+      <c r="K124" s="83"/>
+      <c r="L124" s="84"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="92"/>
-      <c r="C125" s="93"/>
-      <c r="D125" s="99"/>
+      <c r="B125" s="85"/>
+      <c r="C125" s="86"/>
+      <c r="D125" s="87"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="92"/>
-      <c r="G125" s="93"/>
-      <c r="H125" s="99"/>
+      <c r="F125" s="85"/>
+      <c r="G125" s="86"/>
+      <c r="H125" s="87"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="92"/>
-      <c r="K125" s="93"/>
-      <c r="L125" s="99"/>
+      <c r="J125" s="85"/>
+      <c r="K125" s="86"/>
+      <c r="L125" s="87"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="74"/>
-      <c r="C126" s="75"/>
-      <c r="D126" s="76"/>
+      <c r="B126" s="66"/>
+      <c r="C126" s="67"/>
+      <c r="D126" s="68"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="74"/>
-      <c r="G126" s="75"/>
-      <c r="H126" s="76"/>
+      <c r="F126" s="66"/>
+      <c r="G126" s="67"/>
+      <c r="H126" s="68"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="74"/>
-      <c r="K126" s="75"/>
-      <c r="L126" s="76"/>
+      <c r="J126" s="66"/>
+      <c r="K126" s="67"/>
+      <c r="L126" s="68"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="77"/>
-      <c r="C127" s="78"/>
-      <c r="D127" s="79"/>
+      <c r="B127" s="69"/>
+      <c r="C127" s="70"/>
+      <c r="D127" s="71"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="77"/>
-      <c r="G127" s="78"/>
-      <c r="H127" s="79"/>
+      <c r="F127" s="69"/>
+      <c r="G127" s="70"/>
+      <c r="H127" s="71"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="77"/>
-      <c r="K127" s="78"/>
-      <c r="L127" s="79"/>
+      <c r="J127" s="69"/>
+      <c r="K127" s="70"/>
+      <c r="L127" s="71"/>
     </row>
     <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="35"/>
@@ -7773,126 +7735,879 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="67"/>
-      <c r="C129" s="68"/>
+      <c r="B129" s="75"/>
+      <c r="C129" s="76"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="67"/>
-      <c r="G129" s="68"/>
+      <c r="F129" s="75"/>
+      <c r="G129" s="76"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="67"/>
-      <c r="K129" s="68"/>
+      <c r="J129" s="75"/>
+      <c r="K129" s="76"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="96"/>
-      <c r="C130" s="97"/>
-      <c r="D130" s="98"/>
+      <c r="B130" s="82"/>
+      <c r="C130" s="83"/>
+      <c r="D130" s="84"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="96"/>
-      <c r="G130" s="97"/>
-      <c r="H130" s="98"/>
+      <c r="F130" s="82"/>
+      <c r="G130" s="83"/>
+      <c r="H130" s="84"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="96"/>
-      <c r="K130" s="97"/>
-      <c r="L130" s="98"/>
+      <c r="J130" s="82"/>
+      <c r="K130" s="83"/>
+      <c r="L130" s="84"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="92"/>
-      <c r="C131" s="93"/>
-      <c r="D131" s="99"/>
+      <c r="B131" s="85"/>
+      <c r="C131" s="86"/>
+      <c r="D131" s="87"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="92"/>
-      <c r="G131" s="93"/>
-      <c r="H131" s="99"/>
+      <c r="F131" s="85"/>
+      <c r="G131" s="86"/>
+      <c r="H131" s="87"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="92"/>
-      <c r="K131" s="93"/>
-      <c r="L131" s="99"/>
+      <c r="J131" s="85"/>
+      <c r="K131" s="86"/>
+      <c r="L131" s="87"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="74"/>
-      <c r="C132" s="75"/>
-      <c r="D132" s="76"/>
+      <c r="B132" s="66"/>
+      <c r="C132" s="67"/>
+      <c r="D132" s="68"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="74"/>
-      <c r="G132" s="75"/>
-      <c r="H132" s="76"/>
+      <c r="F132" s="66"/>
+      <c r="G132" s="67"/>
+      <c r="H132" s="68"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="74"/>
-      <c r="K132" s="75"/>
-      <c r="L132" s="76"/>
+      <c r="J132" s="66"/>
+      <c r="K132" s="67"/>
+      <c r="L132" s="68"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="77"/>
-      <c r="C133" s="78"/>
-      <c r="D133" s="79"/>
+      <c r="B133" s="69"/>
+      <c r="C133" s="70"/>
+      <c r="D133" s="71"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="77"/>
-      <c r="G133" s="78"/>
-      <c r="H133" s="79"/>
+      <c r="F133" s="69"/>
+      <c r="G133" s="70"/>
+      <c r="H133" s="71"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="77"/>
-      <c r="K133" s="78"/>
-      <c r="L133" s="79"/>
+      <c r="J133" s="69"/>
+      <c r="K133" s="70"/>
+      <c r="L133" s="71"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="881">
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AD39:AF39"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH39:AJ39"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AH93:AJ93"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="AD87:AF87"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AH87:AJ87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD81:AF81"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AL75:AN75"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="AH72:AJ72"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="AH38:AI38"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="J76:L76"/>
     <mergeCell ref="AD94:AF94"/>
     <mergeCell ref="AD95:AF95"/>
     <mergeCell ref="AD96:AF96"/>
@@ -7917,817 +8632,64 @@
     <mergeCell ref="N78:P78"/>
     <mergeCell ref="Z80:AA80"/>
     <mergeCell ref="R78:T78"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="V93:X93"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="Z93:AB93"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="AH38:AI38"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="AH72:AJ72"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD81:AF81"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AH87:AJ87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AH93:AJ93"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="AD87:AF87"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH39:AJ39"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL39:AN39"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AD39:AF39"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="F93:H93"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="P22:P27 X22:X27 AB22:AB27 AJ22:AJ27 AF22:AF27 AN22:AN27 T22:T27 L22:L27 H22:H27 D22:D27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="N48:P50 AH14:AJ16 AL22:AM27 V83:X84 AD62:AF64 R22:S27 V77:X78 J132:L133 AH71:AJ72 AH48:AJ50 R77:T78 Z95:AB96 Z77:AB78 N95:P96 AH41:AJ43 V22:W27 Z48:AB50 AL101:AN102 Z41:AB43 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 AL48:AN50 B108:D109 Z71:AB72 Z14:AB16 R71:T72 R14:T16 V55:X57 AL14:AN16 AH83:AJ84 N55:P57 AL71:AN72 Z55:AB57 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 R55:T57 Z101:AB102 R34:T36 AL83:AN84 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 J55:L57 R41:T43 N34:P36 AH55:AJ57 J8:L10 N71:P72 V41:X43 AL41:AN43 AH22:AI27 AL55:AN57 R48:T50 B62:D64 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 N62:P64 AH34:AJ36 AH62:AJ64 N101:P102 Z34:AB36 AH77:AJ78 V95:X96 V71:X72 V89:X90 V62:X64 Z22:AA27 AD83:AF84 V34:X36 AD71:AF72 AH101:AJ102 N77:P78 AL77:AN78 AL62:AN64 Z8:AB10 R62:T64 AL8:AN10 AD77:AF78 N8:P10 Z62:AB64 AD41:AF43 AL95:AN96 V101:X102 R83:T84 N83:P84 AL34:AN36 V48:X50 Z83:AB84 F14:H16 F8:H10 J22:K27 F22:G27 J62:L64 AD34:AF36 B48:D50 F48:H50 J48:L50 F55:H57 J41:L43 B8:D10 B34:D36 B55:D57 F34:H36 AD48:AF50 J14:L16 N41:P43 B14:D16 B22:C27 J34:L36 AD55:AF57 F62:H64 F41:H43 B41:D43 B77:D78 J71:L72 B71:D72 J101:L102 B95:D96 J89:L90 F95:H96 F83:H84 J83:L84 F89:H90 B89:D90 B101:D102 B83:D84 F71:H72 F101:H102 J77:L78 J95:L96 F77:H78">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="N48:P50 AH14:AJ16 AL22:AM27 F77:H78 AD62:AF64 R22:S27 V77:X78 J132:L133 AH71:AJ72 AH48:AJ50 R77:T78 Z95:AB96 Z77:AB78 N95:P96 AH41:AJ43 V22:W27 Z48:AB50 AL101:AN102 Z41:AB43 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 AL89:AN90 AH95:AJ96 R8:T10 AL48:AN50 B108:D109 Z71:AB72 Z14:AB16 R71:T72 R14:T16 V55:X57 AL14:AN16 AH83:AJ84 N55:P57 AL71:AN72 Z55:AB57 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 R55:T57 Z101:AB102 R34:T36 AL83:AN84 AH89:AJ90 AD22:AE27 V14:X16 AD89:AF90 F108:H109 Z89:AB90 N22:O27 J55:L57 R41:T43 N34:P36 AH55:AJ57 J8:L10 N71:P72 V41:X43 AL41:AN43 AH22:AI27 AL55:AN57 R48:T50 B62:D64 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 N62:P64 AH34:AJ36 AH62:AJ64 N101:P102 Z34:AB36 AH77:AJ78 V95:X96 V71:X72 V89:X90 V62:X64 Z22:AA27 AD83:AF84 V34:X36 AD71:AF72 AH101:AJ102 N77:P78 AL77:AN78 AL62:AN64 Z8:AB10 R62:T64 AL8:AN10 AD77:AF78 N8:P10 Z62:AB64 AD41:AF43 AL95:AN96 V101:X102 R83:T84 N83:P84 AL34:AN36 V48:X50 Z83:AB84 F14:H16 F8:H10 J22:K27 F22:G27 J62:L64 AD34:AF36 B48:D50 F48:H50 J48:L50 F55:H57 J41:L43 B8:D10 B34:D36 B55:D57 F34:H36 AD48:AF50 J14:L16 N41:P43 B14:D16 B22:C27 J34:L36 AD55:AF57 F62:H64 F41:H43 B41:D43 B77:D78 J71:L72 B71:D72 J101:L102 B95:D96 J89:L90 F95:H96 F83:H84 J83:L84 F89:H90 B89:D90 B101:D102 B83:D84 F71:H72 F101:H102 J77:L78 J95:L96 V83:X84">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="74">
   <si>
     <t>CUMA</t>
   </si>
@@ -237,6 +237,15 @@
   </si>
   <si>
     <t>KURULUM + KAYIT</t>
+  </si>
+  <si>
+    <t>KEŞİF</t>
+  </si>
+  <si>
+    <t>Yıldız Teknik Üniversitesi</t>
+  </si>
+  <si>
+    <t>YENİ PROGRAM</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1287,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1440,12 +1449,45 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1455,39 +1497,6 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1506,16 +1515,118 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
@@ -1523,117 +1634,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="11" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="12" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="13" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2084,65 +2084,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12"/>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="107" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="107" t="s">
+      <c r="J1" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="107"/>
-      <c r="L1" s="108"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="113"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="111" t="s">
+      <c r="N1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="105" t="s">
+      <c r="R1" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="105" t="s">
+      <c r="V1" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="105" t="s">
+      <c r="Z1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="105"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="105" t="s">
+      <c r="AD1" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="105"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="105" t="s">
+      <c r="AH1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="106"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="105" t="s">
+      <c r="AL1" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="115"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="107"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2150,74 +2150,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="109">
+      <c r="B2" s="114">
         <f>N2-3</f>
         <v>46255</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="110">
+      <c r="F2" s="115">
         <f>N2-2</f>
         <v>46256</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="110">
+      <c r="J2" s="115">
         <f>N2-1</f>
         <v>46257</v>
       </c>
-      <c r="K2" s="110"/>
-      <c r="L2" s="113"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="118"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="112">
+      <c r="N2" s="117">
         <v>46258</v>
       </c>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="101">
+      <c r="R2" s="108">
         <f>N2+1</f>
         <v>46259</v>
       </c>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="108"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="101">
+      <c r="V2" s="108">
         <f>N2+2</f>
         <v>46260</v>
       </c>
-      <c r="W2" s="101"/>
-      <c r="X2" s="101"/>
+      <c r="W2" s="108"/>
+      <c r="X2" s="108"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="101">
+      <c r="Z2" s="108">
         <f>N2+3</f>
         <v>46261</v>
       </c>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="101"/>
+      <c r="AA2" s="108"/>
+      <c r="AB2" s="108"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="101">
+      <c r="AD2" s="108">
         <f>N2+4</f>
         <v>46262</v>
       </c>
-      <c r="AE2" s="101"/>
-      <c r="AF2" s="101"/>
+      <c r="AE2" s="108"/>
+      <c r="AF2" s="108"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="101">
+      <c r="AH2" s="108">
         <f>N2+5</f>
         <v>46263</v>
       </c>
-      <c r="AI2" s="101"/>
-      <c r="AJ2" s="101"/>
+      <c r="AI2" s="108"/>
+      <c r="AJ2" s="108"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="101">
+      <c r="AL2" s="108">
         <f>N2+6</f>
         <v>46264</v>
       </c>
-      <c r="AM2" s="101"/>
-      <c r="AN2" s="116"/>
+      <c r="AM2" s="108"/>
+      <c r="AN2" s="109"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2271,47 +2271,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="100" t="s">
+      <c r="N4" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="100"/>
-      <c r="W4" s="100"/>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="114"/>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
+      <c r="AD4" s="110"/>
+      <c r="AE4" s="110"/>
+      <c r="AF4" s="110"/>
+      <c r="AG4" s="110"/>
+      <c r="AH4" s="110"/>
+      <c r="AI4" s="110"/>
+      <c r="AJ4" s="110"/>
+      <c r="AK4" s="110"/>
+      <c r="AL4" s="110"/>
+      <c r="AM4" s="110"/>
+      <c r="AN4" s="110"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2319,89 +2319,89 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="114"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="100"/>
-      <c r="U5" s="100"/>
-      <c r="V5" s="100"/>
-      <c r="W5" s="100"/>
-      <c r="X5" s="100"/>
-      <c r="Y5" s="100"/>
-      <c r="Z5" s="100"/>
-      <c r="AA5" s="100"/>
-      <c r="AB5" s="100"/>
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="94"/>
+      <c r="V5" s="94"/>
+      <c r="W5" s="94"/>
+      <c r="X5" s="94"/>
+      <c r="Y5" s="94"/>
+      <c r="Z5" s="94"/>
+      <c r="AA5" s="94"/>
+      <c r="AB5" s="94"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="114"/>
-      <c r="AE5" s="114"/>
-      <c r="AF5" s="114"/>
-      <c r="AG5" s="114"/>
-      <c r="AH5" s="114"/>
-      <c r="AI5" s="114"/>
-      <c r="AJ5" s="114"/>
-      <c r="AK5" s="114"/>
-      <c r="AL5" s="114"/>
-      <c r="AM5" s="114"/>
-      <c r="AN5" s="114"/>
+      <c r="AD5" s="110"/>
+      <c r="AE5" s="110"/>
+      <c r="AF5" s="110"/>
+      <c r="AG5" s="110"/>
+      <c r="AH5" s="110"/>
+      <c r="AI5" s="110"/>
+      <c r="AJ5" s="110"/>
+      <c r="AK5" s="110"/>
+      <c r="AL5" s="110"/>
+      <c r="AM5" s="110"/>
+      <c r="AN5" s="110"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="77"/>
-      <c r="C6" s="78"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="57"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="78"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
       <c r="H6" s="57"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="78"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
       <c r="L6" s="57"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="64"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="63"/>
-      <c r="S6" s="64"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="66"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="63"/>
-      <c r="W6" s="64"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="66"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="63"/>
-      <c r="AA6" s="64"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="66"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="64"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="66"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="63"/>
-      <c r="AI6" s="64"/>
+      <c r="AH6" s="65"/>
+      <c r="AI6" s="66"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="63"/>
-      <c r="AM6" s="64"/>
+      <c r="AL6" s="65"/>
+      <c r="AM6" s="66"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2425,32 +2425,32 @@
       <c r="K7" s="83"/>
       <c r="L7" s="58"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="69"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="71"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="69"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="71"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="68"/>
-      <c r="W7" s="69"/>
+      <c r="V7" s="70"/>
+      <c r="W7" s="71"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="68"/>
-      <c r="AA7" s="69"/>
+      <c r="Z7" s="70"/>
+      <c r="AA7" s="71"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="68"/>
-      <c r="AE7" s="69"/>
+      <c r="AD7" s="70"/>
+      <c r="AE7" s="71"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="68"/>
-      <c r="AI7" s="69"/>
+      <c r="AH7" s="70"/>
+      <c r="AI7" s="71"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="68"/>
-      <c r="AM7" s="69"/>
+      <c r="AL7" s="70"/>
+      <c r="AM7" s="71"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2462,45 +2462,45 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="65"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="67"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="78"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="67"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="78"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="67"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="78"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="67"/>
+      <c r="N8" s="76"/>
+      <c r="O8" s="77"/>
+      <c r="P8" s="78"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="66"/>
-      <c r="T8" s="67"/>
+      <c r="R8" s="76"/>
+      <c r="S8" s="77"/>
+      <c r="T8" s="78"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="66"/>
-      <c r="X8" s="67"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="77"/>
+      <c r="X8" s="78"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="65"/>
-      <c r="AA8" s="66"/>
-      <c r="AB8" s="67"/>
+      <c r="Z8" s="76"/>
+      <c r="AA8" s="77"/>
+      <c r="AB8" s="78"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="65"/>
-      <c r="AE8" s="66"/>
-      <c r="AF8" s="67"/>
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="77"/>
+      <c r="AF8" s="78"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="65"/>
-      <c r="AI8" s="66"/>
-      <c r="AJ8" s="67"/>
+      <c r="AH8" s="76"/>
+      <c r="AI8" s="77"/>
+      <c r="AJ8" s="78"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="65"/>
-      <c r="AM8" s="66"/>
-      <c r="AN8" s="67"/>
+      <c r="AL8" s="76"/>
+      <c r="AM8" s="77"/>
+      <c r="AN8" s="78"/>
       <c r="AP8" s="59" t="s">
         <v>16</v>
       </c>
@@ -2513,45 +2513,45 @@
       </c>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="71"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="73"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="75"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="75"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="75"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="74"/>
+      <c r="P9" s="75"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="73"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="74"/>
+      <c r="T9" s="75"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="72"/>
-      <c r="X9" s="73"/>
+      <c r="V9" s="73"/>
+      <c r="W9" s="74"/>
+      <c r="X9" s="75"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="71"/>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="73"/>
+      <c r="Z9" s="73"/>
+      <c r="AA9" s="74"/>
+      <c r="AB9" s="75"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="71"/>
-      <c r="AE9" s="72"/>
-      <c r="AF9" s="73"/>
+      <c r="AD9" s="73"/>
+      <c r="AE9" s="74"/>
+      <c r="AF9" s="75"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="71"/>
-      <c r="AI9" s="72"/>
-      <c r="AJ9" s="73"/>
+      <c r="AH9" s="73"/>
+      <c r="AI9" s="74"/>
+      <c r="AJ9" s="75"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="71"/>
-      <c r="AM9" s="72"/>
-      <c r="AN9" s="73"/>
+      <c r="AL9" s="73"/>
+      <c r="AM9" s="74"/>
+      <c r="AN9" s="75"/>
       <c r="AP9" s="59" t="s">
         <v>11</v>
       </c>
@@ -2564,45 +2564,45 @@
       </c>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="102"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="104"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="97"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="104"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="97"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="103"/>
-      <c r="L10" s="104"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="97"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="104"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="97"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="102"/>
-      <c r="S10" s="103"/>
-      <c r="T10" s="104"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="97"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="102"/>
-      <c r="W10" s="103"/>
-      <c r="X10" s="104"/>
+      <c r="V10" s="95"/>
+      <c r="W10" s="96"/>
+      <c r="X10" s="97"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="102"/>
-      <c r="AA10" s="103"/>
-      <c r="AB10" s="104"/>
+      <c r="Z10" s="95"/>
+      <c r="AA10" s="96"/>
+      <c r="AB10" s="97"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="102"/>
-      <c r="AE10" s="103"/>
-      <c r="AF10" s="104"/>
+      <c r="AD10" s="95"/>
+      <c r="AE10" s="96"/>
+      <c r="AF10" s="97"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="102"/>
-      <c r="AI10" s="103"/>
-      <c r="AJ10" s="104"/>
+      <c r="AH10" s="95"/>
+      <c r="AI10" s="96"/>
+      <c r="AJ10" s="97"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="102"/>
-      <c r="AM10" s="103"/>
-      <c r="AN10" s="104"/>
+      <c r="AL10" s="95"/>
+      <c r="AM10" s="96"/>
+      <c r="AN10" s="97"/>
       <c r="AP10" s="59" t="s">
         <v>8</v>
       </c>
@@ -2664,52 +2664,52 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="77"/>
-      <c r="C12" s="78"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="57"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="78"/>
+      <c r="G12" s="64"/>
       <c r="H12" s="57" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="78"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="64"/>
       <c r="L12" s="57"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="63"/>
-      <c r="O12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="63"/>
-      <c r="S12" s="64"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="66"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="63"/>
-      <c r="W12" s="64"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="66"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="63"/>
-      <c r="AA12" s="64"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="66"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="63"/>
-      <c r="AE12" s="64"/>
+      <c r="AD12" s="65"/>
+      <c r="AE12" s="66"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="63" t="s">
+      <c r="AH12" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="64"/>
+      <c r="AI12" s="66"/>
       <c r="AJ12" s="34" t="s">
         <v>46</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="63"/>
-      <c r="AM12" s="64"/>
+      <c r="AL12" s="65"/>
+      <c r="AM12" s="66"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2733,33 +2733,33 @@
       <c r="K13" s="80"/>
       <c r="L13" s="81"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="76"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="69"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="74"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="76"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="68"/>
+      <c r="T13" s="69"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="74"/>
-      <c r="W13" s="75"/>
-      <c r="X13" s="76"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="68"/>
+      <c r="X13" s="69"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="68"/>
-      <c r="AA13" s="69"/>
+      <c r="Z13" s="70"/>
+      <c r="AA13" s="71"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="68"/>
-      <c r="AE13" s="69"/>
+      <c r="AD13" s="70"/>
+      <c r="AE13" s="71"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="74"/>
-      <c r="AI13" s="75"/>
-      <c r="AJ13" s="76"/>
+      <c r="AH13" s="67"/>
+      <c r="AI13" s="68"/>
+      <c r="AJ13" s="69"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="74"/>
-      <c r="AM13" s="75"/>
-      <c r="AN13" s="76"/>
+      <c r="AL13" s="67"/>
+      <c r="AM13" s="68"/>
+      <c r="AN13" s="69"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
@@ -2770,49 +2770,49 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="78"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="65" t="s">
+      <c r="F14" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="66"/>
-      <c r="H14" s="67"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="78"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="78"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="67"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="77"/>
+      <c r="P14" s="78"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="67"/>
+      <c r="R14" s="76"/>
+      <c r="S14" s="77"/>
+      <c r="T14" s="78"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="66"/>
-      <c r="X14" s="67"/>
+      <c r="V14" s="76"/>
+      <c r="W14" s="77"/>
+      <c r="X14" s="78"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="65"/>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="67"/>
+      <c r="Z14" s="76"/>
+      <c r="AA14" s="77"/>
+      <c r="AB14" s="78"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="65"/>
-      <c r="AE14" s="66"/>
-      <c r="AF14" s="67"/>
+      <c r="AD14" s="76"/>
+      <c r="AE14" s="77"/>
+      <c r="AF14" s="78"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="65" t="s">
+      <c r="AH14" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="AI14" s="66"/>
-      <c r="AJ14" s="67"/>
+      <c r="AI14" s="77"/>
+      <c r="AJ14" s="78"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="65"/>
-      <c r="AM14" s="66"/>
-      <c r="AN14" s="67"/>
+      <c r="AL14" s="76"/>
+      <c r="AM14" s="77"/>
+      <c r="AN14" s="78"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -2823,49 +2823,49 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="72"/>
-      <c r="H15" s="73"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="75"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="75"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="73"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="74"/>
+      <c r="T15" s="75"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="71"/>
-      <c r="W15" s="72"/>
-      <c r="X15" s="73"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="74"/>
+      <c r="X15" s="75"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="72"/>
-      <c r="AB15" s="73"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="74"/>
+      <c r="AB15" s="75"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="71"/>
-      <c r="AE15" s="72"/>
-      <c r="AF15" s="73"/>
+      <c r="AD15" s="73"/>
+      <c r="AE15" s="74"/>
+      <c r="AF15" s="75"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="71" t="s">
+      <c r="AH15" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="AI15" s="72"/>
-      <c r="AJ15" s="73"/>
+      <c r="AI15" s="74"/>
+      <c r="AJ15" s="75"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="71"/>
-      <c r="AM15" s="72"/>
-      <c r="AN15" s="73"/>
+      <c r="AL15" s="73"/>
+      <c r="AM15" s="74"/>
+      <c r="AN15" s="75"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2876,45 +2876,45 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="102"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="104"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="97"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="104"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="97"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="103"/>
-      <c r="L16" s="104"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="97"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="103"/>
-      <c r="P16" s="104"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="97"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="102"/>
-      <c r="S16" s="103"/>
-      <c r="T16" s="104"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="97"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="102"/>
-      <c r="W16" s="103"/>
-      <c r="X16" s="104"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="96"/>
+      <c r="X16" s="97"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="102"/>
-      <c r="AA16" s="103"/>
-      <c r="AB16" s="104"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="96"/>
+      <c r="AB16" s="97"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="102"/>
-      <c r="AE16" s="103"/>
-      <c r="AF16" s="104"/>
+      <c r="AD16" s="95"/>
+      <c r="AE16" s="96"/>
+      <c r="AF16" s="97"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="102"/>
-      <c r="AI16" s="103"/>
-      <c r="AJ16" s="104"/>
+      <c r="AH16" s="95"/>
+      <c r="AI16" s="96"/>
+      <c r="AJ16" s="97"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="102"/>
-      <c r="AM16" s="103"/>
-      <c r="AN16" s="104"/>
+      <c r="AL16" s="95"/>
+      <c r="AM16" s="96"/>
+      <c r="AN16" s="97"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -2986,23 +2986,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="100" t="s">
+      <c r="N18" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="100"/>
-      <c r="T18" s="100"/>
-      <c r="U18" s="100"/>
-      <c r="V18" s="100"/>
-      <c r="W18" s="100"/>
-      <c r="X18" s="100"/>
-      <c r="Y18" s="100"/>
-      <c r="Z18" s="100"/>
-      <c r="AA18" s="100"/>
-      <c r="AB18" s="100"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+      <c r="T18" s="94"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="94"/>
+      <c r="W18" s="94"/>
+      <c r="X18" s="94"/>
+      <c r="Y18" s="94"/>
+      <c r="Z18" s="94"/>
+      <c r="AA18" s="94"/>
+      <c r="AB18" s="94"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3037,21 +3037,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="100"/>
-      <c r="T19" s="100"/>
-      <c r="U19" s="100"/>
-      <c r="V19" s="100"/>
-      <c r="W19" s="100"/>
-      <c r="X19" s="100"/>
-      <c r="Y19" s="100"/>
-      <c r="Z19" s="100"/>
-      <c r="AA19" s="100"/>
-      <c r="AB19" s="100"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+      <c r="T19" s="94"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="94"/>
+      <c r="W19" s="94"/>
+      <c r="X19" s="94"/>
+      <c r="Y19" s="94"/>
+      <c r="Z19" s="94"/>
+      <c r="AA19" s="94"/>
+      <c r="AB19" s="94"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3074,20 +3074,20 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="77"/>
-      <c r="C20" s="78"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="57"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="78"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="64"/>
       <c r="H20" s="57"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="78"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="64"/>
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="64"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="66"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
       <c r="R20" s="98"/>
@@ -3102,16 +3102,16 @@
       <c r="AA20" s="99"/>
       <c r="AB20" s="55"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="63"/>
-      <c r="AE20" s="64"/>
+      <c r="AD20" s="65"/>
+      <c r="AE20" s="66"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="63"/>
-      <c r="AI20" s="64"/>
+      <c r="AH20" s="65"/>
+      <c r="AI20" s="66"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="63"/>
-      <c r="AM20" s="64"/>
+      <c r="AL20" s="65"/>
+      <c r="AM20" s="66"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3135,32 +3135,32 @@
       <c r="K21" s="83"/>
       <c r="L21" s="58"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="69"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="71"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="69"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="71"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="117"/>
-      <c r="W21" s="118"/>
+      <c r="V21" s="104"/>
+      <c r="W21" s="105"/>
       <c r="X21" s="56"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="117"/>
-      <c r="AA21" s="118"/>
+      <c r="Z21" s="104"/>
+      <c r="AA21" s="105"/>
       <c r="AB21" s="56"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="68"/>
-      <c r="AE21" s="69"/>
+      <c r="AD21" s="70"/>
+      <c r="AE21" s="71"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="68"/>
-      <c r="AI21" s="69"/>
+      <c r="AH21" s="70"/>
+      <c r="AI21" s="71"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="68"/>
-      <c r="AM21" s="69"/>
+      <c r="AL21" s="70"/>
+      <c r="AM21" s="71"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3172,44 +3172,44 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="89"/>
-      <c r="C22" s="90"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="124"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="90"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="124"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="90"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="124"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="94"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="120"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="93"/>
-      <c r="S22" s="94"/>
+      <c r="R22" s="119"/>
+      <c r="S22" s="120"/>
       <c r="T22" s="41"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="93"/>
-      <c r="W22" s="94"/>
+      <c r="V22" s="119"/>
+      <c r="W22" s="120"/>
       <c r="X22" s="41"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="93"/>
-      <c r="AA22" s="94"/>
+      <c r="Z22" s="119"/>
+      <c r="AA22" s="120"/>
       <c r="AB22" s="41"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="93"/>
-      <c r="AE22" s="94"/>
+      <c r="AD22" s="119"/>
+      <c r="AE22" s="120"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="93"/>
-      <c r="AI22" s="94"/>
+      <c r="AH22" s="119"/>
+      <c r="AI22" s="120"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="93"/>
-      <c r="AM22" s="94"/>
+      <c r="AL22" s="119"/>
+      <c r="AM22" s="120"/>
       <c r="AN22" s="41"/>
       <c r="AP22" s="59" t="s">
         <v>15</v>
@@ -3223,44 +3223,44 @@
       </c>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="91"/>
-      <c r="C23" s="92"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="45"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="92"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="122"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="92"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="122"/>
       <c r="L23" s="45"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="92"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="122"/>
       <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="92"/>
+      <c r="R23" s="121"/>
+      <c r="S23" s="122"/>
       <c r="T23" s="45"/>
       <c r="U23" s="43"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="92"/>
+      <c r="V23" s="121"/>
+      <c r="W23" s="122"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="91"/>
-      <c r="AA23" s="92"/>
+      <c r="Z23" s="121"/>
+      <c r="AA23" s="122"/>
       <c r="AB23" s="45"/>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="91"/>
-      <c r="AE23" s="92"/>
+      <c r="AD23" s="121"/>
+      <c r="AE23" s="122"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="91"/>
-      <c r="AI23" s="92"/>
+      <c r="AH23" s="121"/>
+      <c r="AI23" s="122"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="91"/>
-      <c r="AM23" s="92"/>
+      <c r="AL23" s="121"/>
+      <c r="AM23" s="122"/>
       <c r="AN23" s="45"/>
       <c r="AP23" s="46" t="s">
         <v>20</v>
@@ -3272,44 +3272,44 @@
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="85"/>
-      <c r="C24" s="86"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="103"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="86"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="103"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="85"/>
-      <c r="K24" s="86"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="103"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="86"/>
+      <c r="N24" s="102"/>
+      <c r="O24" s="103"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="85"/>
-      <c r="S24" s="86"/>
+      <c r="R24" s="102"/>
+      <c r="S24" s="103"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="85"/>
-      <c r="W24" s="86"/>
+      <c r="V24" s="102"/>
+      <c r="W24" s="103"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="85"/>
-      <c r="AA24" s="86"/>
+      <c r="Z24" s="102"/>
+      <c r="AA24" s="103"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="85"/>
-      <c r="AE24" s="86"/>
+      <c r="AD24" s="102"/>
+      <c r="AE24" s="103"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="85"/>
-      <c r="AI24" s="86"/>
+      <c r="AH24" s="102"/>
+      <c r="AI24" s="103"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="85"/>
-      <c r="AM24" s="86"/>
+      <c r="AL24" s="102"/>
+      <c r="AM24" s="103"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
@@ -3321,44 +3321,44 @@
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="85"/>
-      <c r="C25" s="86"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="103"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="86"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="86"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="103"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="86"/>
+      <c r="N25" s="102"/>
+      <c r="O25" s="103"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="85"/>
-      <c r="S25" s="86"/>
+      <c r="R25" s="102"/>
+      <c r="S25" s="103"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="85"/>
-      <c r="W25" s="86"/>
+      <c r="V25" s="102"/>
+      <c r="W25" s="103"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="85"/>
-      <c r="AA25" s="86"/>
+      <c r="Z25" s="102"/>
+      <c r="AA25" s="103"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="85"/>
-      <c r="AE25" s="86"/>
+      <c r="AD25" s="102"/>
+      <c r="AE25" s="103"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="85"/>
-      <c r="AI25" s="86"/>
+      <c r="AH25" s="102"/>
+      <c r="AI25" s="103"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="85"/>
-      <c r="AM25" s="86"/>
+      <c r="AL25" s="102"/>
+      <c r="AM25" s="103"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="59" t="s">
         <v>21</v>
@@ -3372,44 +3372,44 @@
       </c>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="85"/>
-      <c r="C26" s="86"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="103"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="86"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="103"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="86"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="103"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="86"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="103"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="85"/>
-      <c r="S26" s="86"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="103"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="85"/>
-      <c r="W26" s="86"/>
+      <c r="V26" s="102"/>
+      <c r="W26" s="103"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="85"/>
-      <c r="AA26" s="86"/>
+      <c r="Z26" s="102"/>
+      <c r="AA26" s="103"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="85"/>
-      <c r="AE26" s="86"/>
+      <c r="AD26" s="102"/>
+      <c r="AE26" s="103"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="85"/>
-      <c r="AI26" s="86"/>
+      <c r="AH26" s="102"/>
+      <c r="AI26" s="103"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="85"/>
-      <c r="AM26" s="86"/>
+      <c r="AL26" s="102"/>
+      <c r="AM26" s="103"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
@@ -3421,44 +3421,44 @@
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="87"/>
-      <c r="C27" s="88"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="88"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="101"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="88"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="101"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="88"/>
+      <c r="N27" s="100"/>
+      <c r="O27" s="101"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="87"/>
-      <c r="S27" s="88"/>
+      <c r="R27" s="100"/>
+      <c r="S27" s="101"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="87"/>
-      <c r="W27" s="88"/>
+      <c r="V27" s="100"/>
+      <c r="W27" s="101"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="87"/>
-      <c r="AA27" s="88"/>
+      <c r="Z27" s="100"/>
+      <c r="AA27" s="101"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="87"/>
-      <c r="AE27" s="88"/>
+      <c r="AD27" s="100"/>
+      <c r="AE27" s="101"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="87"/>
-      <c r="AI27" s="88"/>
+      <c r="AH27" s="100"/>
+      <c r="AI27" s="101"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="87"/>
-      <c r="AM27" s="88"/>
+      <c r="AL27" s="100"/>
+      <c r="AM27" s="101"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="AQ28" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR28" s="30"/>
     </row>
@@ -3531,23 +3531,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="100" t="s">
+      <c r="N29" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="100"/>
-      <c r="P29" s="100"/>
-      <c r="Q29" s="100"/>
-      <c r="R29" s="100"/>
-      <c r="S29" s="100"/>
-      <c r="T29" s="100"/>
-      <c r="U29" s="100"/>
-      <c r="V29" s="100"/>
-      <c r="W29" s="100"/>
-      <c r="X29" s="100"/>
-      <c r="Y29" s="100"/>
-      <c r="Z29" s="100"/>
-      <c r="AA29" s="100"/>
-      <c r="AB29" s="100"/>
+      <c r="O29" s="94"/>
+      <c r="P29" s="94"/>
+      <c r="Q29" s="94"/>
+      <c r="R29" s="94"/>
+      <c r="S29" s="94"/>
+      <c r="T29" s="94"/>
+      <c r="U29" s="94"/>
+      <c r="V29" s="94"/>
+      <c r="W29" s="94"/>
+      <c r="X29" s="94"/>
+      <c r="Y29" s="94"/>
+      <c r="Z29" s="94"/>
+      <c r="AA29" s="94"/>
+      <c r="AB29" s="94"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3582,21 +3582,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="100"/>
-      <c r="Q30" s="100"/>
-      <c r="R30" s="100"/>
-      <c r="S30" s="100"/>
-      <c r="T30" s="100"/>
-      <c r="U30" s="100"/>
-      <c r="V30" s="100"/>
-      <c r="W30" s="100"/>
-      <c r="X30" s="100"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="100"/>
-      <c r="AA30" s="100"/>
-      <c r="AB30" s="100"/>
+      <c r="N30" s="94"/>
+      <c r="O30" s="94"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="94"/>
+      <c r="R30" s="94"/>
+      <c r="S30" s="94"/>
+      <c r="T30" s="94"/>
+      <c r="U30" s="94"/>
+      <c r="V30" s="94"/>
+      <c r="W30" s="94"/>
+      <c r="X30" s="94"/>
+      <c r="Y30" s="94"/>
+      <c r="Z30" s="94"/>
+      <c r="AA30" s="94"/>
+      <c r="AB30" s="94"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3621,64 +3621,64 @@
       </c>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="78"/>
+      <c r="C31" s="64"/>
       <c r="D31" s="57"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="77" t="s">
+      <c r="F31" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="78"/>
+      <c r="G31" s="64"/>
       <c r="H31" s="57"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="77" t="s">
+      <c r="J31" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="K31" s="78"/>
+      <c r="K31" s="64"/>
       <c r="L31" s="57"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="63" t="s">
+      <c r="N31" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="O31" s="64"/>
+      <c r="O31" s="66"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="63" t="s">
+      <c r="R31" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="S31" s="64"/>
+      <c r="S31" s="66"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="63" t="s">
+      <c r="V31" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="W31" s="64"/>
+      <c r="W31" s="66"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="63" t="s">
+      <c r="Z31" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="AA31" s="64"/>
+      <c r="AA31" s="66"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="63" t="s">
+      <c r="AD31" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="AE31" s="64"/>
+      <c r="AE31" s="66"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="63" t="s">
+      <c r="AH31" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="AI31" s="64"/>
+      <c r="AI31" s="66"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="63" t="s">
+      <c r="AL31" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="AM31" s="64"/>
+      <c r="AM31" s="66"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
@@ -3703,47 +3703,47 @@
       <c r="K32" s="80"/>
       <c r="L32" s="81"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="74" t="s">
+      <c r="N32" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="O32" s="75"/>
-      <c r="P32" s="76"/>
+      <c r="O32" s="68"/>
+      <c r="P32" s="69"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="74" t="s">
+      <c r="R32" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="S32" s="75"/>
-      <c r="T32" s="76"/>
+      <c r="S32" s="68"/>
+      <c r="T32" s="69"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="74" t="s">
+      <c r="V32" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="W32" s="75"/>
-      <c r="X32" s="76"/>
+      <c r="W32" s="68"/>
+      <c r="X32" s="69"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="74" t="s">
+      <c r="Z32" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="AA32" s="75"/>
-      <c r="AB32" s="76"/>
+      <c r="AA32" s="68"/>
+      <c r="AB32" s="69"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="74" t="s">
+      <c r="AD32" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="AE32" s="75"/>
-      <c r="AF32" s="76"/>
+      <c r="AE32" s="68"/>
+      <c r="AF32" s="69"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="74" t="s">
+      <c r="AH32" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="AI32" s="75"/>
-      <c r="AJ32" s="76"/>
+      <c r="AI32" s="68"/>
+      <c r="AJ32" s="69"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="74" t="s">
+      <c r="AL32" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="AM32" s="75"/>
-      <c r="AN32" s="76"/>
+      <c r="AM32" s="68"/>
+      <c r="AN32" s="69"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
@@ -3767,110 +3767,110 @@
       <c r="K33" s="83"/>
       <c r="L33" s="84"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="68" t="s">
+      <c r="N33" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="O33" s="69"/>
-      <c r="P33" s="70"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="68" t="s">
+      <c r="R33" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="S33" s="69"/>
-      <c r="T33" s="70"/>
+      <c r="S33" s="71"/>
+      <c r="T33" s="72"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="68" t="s">
+      <c r="V33" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="W33" s="69"/>
-      <c r="X33" s="70"/>
+      <c r="W33" s="71"/>
+      <c r="X33" s="72"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="68" t="s">
+      <c r="Z33" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="AA33" s="69"/>
-      <c r="AB33" s="70"/>
+      <c r="AA33" s="71"/>
+      <c r="AB33" s="72"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="68" t="s">
+      <c r="AD33" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="AE33" s="69"/>
-      <c r="AF33" s="70"/>
+      <c r="AE33" s="71"/>
+      <c r="AF33" s="72"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="68" t="s">
+      <c r="AH33" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="AI33" s="69"/>
-      <c r="AJ33" s="70"/>
+      <c r="AI33" s="71"/>
+      <c r="AJ33" s="72"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="68" t="s">
+      <c r="AL33" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="AM33" s="69"/>
-      <c r="AN33" s="70"/>
+      <c r="AM33" s="71"/>
+      <c r="AN33" s="72"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="71" t="s">
+      <c r="B34" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="73"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="75"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="71" t="s">
+      <c r="F34" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="72"/>
-      <c r="H34" s="73"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="75"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="71" t="s">
+      <c r="J34" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="72"/>
-      <c r="L34" s="73"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="75"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="71" t="s">
+      <c r="N34" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="O34" s="72"/>
-      <c r="P34" s="73"/>
+      <c r="O34" s="74"/>
+      <c r="P34" s="75"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="71" t="s">
+      <c r="R34" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="S34" s="72"/>
-      <c r="T34" s="73"/>
+      <c r="S34" s="74"/>
+      <c r="T34" s="75"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="71" t="s">
+      <c r="V34" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="W34" s="72"/>
-      <c r="X34" s="73"/>
+      <c r="W34" s="74"/>
+      <c r="X34" s="75"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="71" t="s">
+      <c r="Z34" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="AA34" s="72"/>
-      <c r="AB34" s="73"/>
+      <c r="AA34" s="74"/>
+      <c r="AB34" s="75"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="71" t="s">
+      <c r="AD34" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="AE34" s="72"/>
-      <c r="AF34" s="73"/>
+      <c r="AE34" s="74"/>
+      <c r="AF34" s="75"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="71" t="s">
+      <c r="AH34" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="AI34" s="72"/>
-      <c r="AJ34" s="73"/>
+      <c r="AI34" s="74"/>
+      <c r="AJ34" s="75"/>
       <c r="AK34" s="32"/>
-      <c r="AL34" s="71" t="s">
+      <c r="AL34" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="AM34" s="72"/>
-      <c r="AN34" s="73"/>
+      <c r="AM34" s="74"/>
+      <c r="AN34" s="75"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -3878,122 +3878,122 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="73"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="75"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="71" t="s">
+      <c r="F35" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="72"/>
-      <c r="H35" s="73"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="75"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="71" t="s">
+      <c r="J35" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="K35" s="72"/>
-      <c r="L35" s="73"/>
+      <c r="K35" s="74"/>
+      <c r="L35" s="75"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="71" t="s">
+      <c r="N35" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="O35" s="72"/>
-      <c r="P35" s="73"/>
+      <c r="O35" s="74"/>
+      <c r="P35" s="75"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="71" t="s">
+      <c r="R35" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="S35" s="72"/>
-      <c r="T35" s="73"/>
+      <c r="S35" s="74"/>
+      <c r="T35" s="75"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="71" t="s">
+      <c r="V35" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="72"/>
-      <c r="X35" s="73"/>
+      <c r="W35" s="74"/>
+      <c r="X35" s="75"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="71" t="s">
+      <c r="Z35" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="72"/>
-      <c r="AB35" s="73"/>
+      <c r="AA35" s="74"/>
+      <c r="AB35" s="75"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="71" t="s">
+      <c r="AD35" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AE35" s="72"/>
-      <c r="AF35" s="73"/>
+      <c r="AE35" s="74"/>
+      <c r="AF35" s="75"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="71" t="s">
+      <c r="AH35" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="AI35" s="72"/>
-      <c r="AJ35" s="73"/>
+      <c r="AI35" s="74"/>
+      <c r="AJ35" s="75"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="71" t="s">
+      <c r="AL35" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="AM35" s="72"/>
-      <c r="AN35" s="73"/>
+      <c r="AM35" s="74"/>
+      <c r="AN35" s="75"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12"/>
-      <c r="B36" s="71" t="s">
+      <c r="B36" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="72"/>
-      <c r="D36" s="73"/>
+      <c r="C36" s="74"/>
+      <c r="D36" s="75"/>
       <c r="E36" s="35"/>
-      <c r="F36" s="71" t="s">
+      <c r="F36" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="72"/>
-      <c r="H36" s="73"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="75"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="71" t="s">
+      <c r="J36" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="K36" s="72"/>
-      <c r="L36" s="73"/>
+      <c r="K36" s="74"/>
+      <c r="L36" s="75"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="71" t="s">
+      <c r="N36" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="O36" s="72"/>
-      <c r="P36" s="73"/>
+      <c r="O36" s="74"/>
+      <c r="P36" s="75"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="71"/>
-      <c r="S36" s="72"/>
-      <c r="T36" s="73"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="74"/>
+      <c r="T36" s="75"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="71" t="s">
+      <c r="V36" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="W36" s="72"/>
-      <c r="X36" s="73"/>
+      <c r="W36" s="74"/>
+      <c r="X36" s="75"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="71"/>
-      <c r="AA36" s="72"/>
-      <c r="AB36" s="73"/>
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="74"/>
+      <c r="AB36" s="75"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="71" t="s">
+      <c r="AD36" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="AE36" s="72"/>
-      <c r="AF36" s="73"/>
+      <c r="AE36" s="74"/>
+      <c r="AF36" s="75"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="71"/>
-      <c r="AI36" s="72"/>
-      <c r="AJ36" s="73"/>
+      <c r="AH36" s="73"/>
+      <c r="AI36" s="74"/>
+      <c r="AJ36" s="75"/>
       <c r="AK36" s="35"/>
-      <c r="AL36" s="71"/>
-      <c r="AM36" s="72"/>
-      <c r="AN36" s="73"/>
+      <c r="AL36" s="73"/>
+      <c r="AM36" s="74"/>
+      <c r="AN36" s="75"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
@@ -4049,11 +4049,11 @@
       <c r="AI37" s="61"/>
       <c r="AJ37" s="62"/>
       <c r="AK37" s="32"/>
-      <c r="AL37" s="125" t="s">
+      <c r="AL37" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="AM37" s="126"/>
-      <c r="AN37" s="127"/>
+      <c r="AM37" s="86"/>
+      <c r="AN37" s="87"/>
       <c r="AO37" s="31"/>
       <c r="AP37" s="22"/>
       <c r="AQ37" s="31"/>
@@ -4107,54 +4107,54 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="78"/>
+      <c r="C39" s="64"/>
       <c r="D39" s="57"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="78"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="64"/>
       <c r="H39" s="57"/>
       <c r="I39" s="43"/>
-      <c r="J39" s="77" t="s">
+      <c r="J39" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="K39" s="78"/>
+      <c r="K39" s="64"/>
       <c r="L39" s="57"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="63" t="s">
+      <c r="N39" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="O39" s="64"/>
+      <c r="O39" s="66"/>
       <c r="P39" s="34"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="63"/>
-      <c r="S39" s="64"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="66"/>
       <c r="T39" s="34"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="63" t="s">
+      <c r="V39" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="W39" s="64"/>
+      <c r="W39" s="66"/>
       <c r="X39" s="34"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="63"/>
-      <c r="AA39" s="64"/>
+      <c r="Z39" s="65"/>
+      <c r="AA39" s="66"/>
       <c r="AB39" s="34"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="63" t="s">
+      <c r="AD39" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="AE39" s="64"/>
+      <c r="AE39" s="66"/>
       <c r="AF39" s="34"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="63"/>
-      <c r="AI39" s="64"/>
+      <c r="AH39" s="65"/>
+      <c r="AI39" s="66"/>
       <c r="AJ39" s="34"/>
       <c r="AK39" s="43"/>
-      <c r="AL39" s="63"/>
-      <c r="AM39" s="64"/>
+      <c r="AL39" s="65"/>
+      <c r="AM39" s="66"/>
       <c r="AN39" s="34"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
@@ -4179,39 +4179,39 @@
       <c r="K40" s="80"/>
       <c r="L40" s="81"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="74" t="s">
+      <c r="N40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="O40" s="75"/>
-      <c r="P40" s="76"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="69"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="74"/>
-      <c r="S40" s="75"/>
-      <c r="T40" s="76"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="68"/>
+      <c r="T40" s="69"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="74" t="s">
+      <c r="V40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="W40" s="75"/>
-      <c r="X40" s="76"/>
+      <c r="W40" s="68"/>
+      <c r="X40" s="69"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="74"/>
-      <c r="AA40" s="75"/>
-      <c r="AB40" s="76"/>
+      <c r="Z40" s="67"/>
+      <c r="AA40" s="68"/>
+      <c r="AB40" s="69"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="74" t="s">
+      <c r="AD40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="AE40" s="75"/>
-      <c r="AF40" s="76"/>
+      <c r="AE40" s="68"/>
+      <c r="AF40" s="69"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="74"/>
-      <c r="AI40" s="75"/>
-      <c r="AJ40" s="76"/>
+      <c r="AH40" s="67"/>
+      <c r="AI40" s="68"/>
+      <c r="AJ40" s="69"/>
       <c r="AK40" s="37"/>
-      <c r="AL40" s="74"/>
-      <c r="AM40" s="75"/>
-      <c r="AN40" s="76"/>
+      <c r="AL40" s="67"/>
+      <c r="AM40" s="68"/>
+      <c r="AN40" s="69"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4231,33 +4231,33 @@
       <c r="K41" s="83"/>
       <c r="L41" s="84"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="68"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="70"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="72"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="68"/>
-      <c r="S41" s="69"/>
-      <c r="T41" s="70"/>
+      <c r="R41" s="70"/>
+      <c r="S41" s="71"/>
+      <c r="T41" s="72"/>
       <c r="U41" s="37"/>
-      <c r="V41" s="68"/>
-      <c r="W41" s="69"/>
-      <c r="X41" s="70"/>
+      <c r="V41" s="70"/>
+      <c r="W41" s="71"/>
+      <c r="X41" s="72"/>
       <c r="Y41" s="44"/>
-      <c r="Z41" s="68"/>
-      <c r="AA41" s="69"/>
-      <c r="AB41" s="70"/>
+      <c r="Z41" s="70"/>
+      <c r="AA41" s="71"/>
+      <c r="AB41" s="72"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="68"/>
-      <c r="AE41" s="69"/>
-      <c r="AF41" s="70"/>
+      <c r="AD41" s="70"/>
+      <c r="AE41" s="71"/>
+      <c r="AF41" s="72"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="68"/>
-      <c r="AI41" s="69"/>
-      <c r="AJ41" s="70"/>
+      <c r="AH41" s="70"/>
+      <c r="AI41" s="71"/>
+      <c r="AJ41" s="72"/>
       <c r="AK41" s="44"/>
-      <c r="AL41" s="68"/>
-      <c r="AM41" s="69"/>
-      <c r="AN41" s="70"/>
+      <c r="AL41" s="70"/>
+      <c r="AM41" s="71"/>
+      <c r="AN41" s="72"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4265,55 +4265,55 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="65" t="s">
+      <c r="B42" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="66"/>
-      <c r="D42" s="67"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="78"/>
       <c r="E42" s="35"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="67"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="78"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="65" t="s">
+      <c r="J42" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="K42" s="66"/>
-      <c r="L42" s="67"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="78"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="65" t="s">
+      <c r="N42" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="O42" s="66"/>
-      <c r="P42" s="67"/>
+      <c r="O42" s="77"/>
+      <c r="P42" s="78"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="65"/>
-      <c r="S42" s="66"/>
-      <c r="T42" s="67"/>
+      <c r="R42" s="76"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="78"/>
       <c r="U42" s="35"/>
-      <c r="V42" s="65" t="s">
+      <c r="V42" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="W42" s="66"/>
-      <c r="X42" s="67"/>
+      <c r="W42" s="77"/>
+      <c r="X42" s="78"/>
       <c r="Y42" s="44"/>
-      <c r="Z42" s="65"/>
-      <c r="AA42" s="66"/>
-      <c r="AB42" s="67"/>
+      <c r="Z42" s="76"/>
+      <c r="AA42" s="77"/>
+      <c r="AB42" s="78"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="65" t="s">
+      <c r="AD42" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="AE42" s="66"/>
-      <c r="AF42" s="67"/>
+      <c r="AE42" s="77"/>
+      <c r="AF42" s="78"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="65"/>
-      <c r="AI42" s="66"/>
-      <c r="AJ42" s="67"/>
+      <c r="AH42" s="76"/>
+      <c r="AI42" s="77"/>
+      <c r="AJ42" s="78"/>
       <c r="AK42" s="44"/>
-      <c r="AL42" s="65"/>
-      <c r="AM42" s="66"/>
-      <c r="AN42" s="67"/>
+      <c r="AL42" s="76"/>
+      <c r="AM42" s="77"/>
+      <c r="AN42" s="78"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4423,64 +4423,64 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="78"/>
+      <c r="C45" s="64"/>
       <c r="D45" s="57"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="77" t="s">
+      <c r="F45" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G45" s="78"/>
+      <c r="G45" s="64"/>
       <c r="H45" s="57"/>
       <c r="I45" s="31"/>
-      <c r="J45" s="77" t="s">
+      <c r="J45" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="K45" s="78"/>
+      <c r="K45" s="64"/>
       <c r="L45" s="57"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="63" t="s">
+      <c r="N45" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="O45" s="64"/>
+      <c r="O45" s="66"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="63" t="s">
+      <c r="R45" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="S45" s="64"/>
+      <c r="S45" s="66"/>
       <c r="T45" s="34"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="63" t="s">
+      <c r="V45" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="W45" s="64"/>
+      <c r="W45" s="66"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="54"/>
-      <c r="Z45" s="63" t="s">
+      <c r="Z45" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="AA45" s="64"/>
+      <c r="AA45" s="66"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="63" t="s">
+      <c r="AD45" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="AE45" s="64"/>
+      <c r="AE45" s="66"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="63" t="s">
+      <c r="AH45" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="AI45" s="64"/>
+      <c r="AI45" s="66"/>
       <c r="AJ45" s="34"/>
       <c r="AK45" s="31"/>
-      <c r="AL45" s="63" t="s">
+      <c r="AL45" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="AM45" s="64"/>
+      <c r="AM45" s="66"/>
       <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
@@ -4507,47 +4507,47 @@
       <c r="K46" s="80"/>
       <c r="L46" s="81"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="74" t="s">
+      <c r="N46" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="O46" s="75"/>
-      <c r="P46" s="76"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="69"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="74" t="s">
+      <c r="R46" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="S46" s="75"/>
-      <c r="T46" s="76"/>
+      <c r="S46" s="68"/>
+      <c r="T46" s="69"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="74" t="s">
+      <c r="V46" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="W46" s="75"/>
-      <c r="X46" s="76"/>
+      <c r="W46" s="68"/>
+      <c r="X46" s="69"/>
       <c r="Y46" s="35"/>
-      <c r="Z46" s="74" t="s">
+      <c r="Z46" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="AA46" s="75"/>
-      <c r="AB46" s="76"/>
+      <c r="AA46" s="68"/>
+      <c r="AB46" s="69"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="74" t="s">
+      <c r="AD46" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="AE46" s="75"/>
-      <c r="AF46" s="76"/>
+      <c r="AE46" s="68"/>
+      <c r="AF46" s="69"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="74" t="s">
+      <c r="AH46" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="AI46" s="75"/>
-      <c r="AJ46" s="76"/>
+      <c r="AI46" s="68"/>
+      <c r="AJ46" s="69"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="74" t="s">
+      <c r="AL46" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="AM46" s="75"/>
-      <c r="AN46" s="76"/>
+      <c r="AM46" s="68"/>
+      <c r="AN46" s="69"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4567,33 +4567,33 @@
       <c r="K47" s="83"/>
       <c r="L47" s="84"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="68"/>
-      <c r="O47" s="69"/>
-      <c r="P47" s="70"/>
+      <c r="N47" s="70"/>
+      <c r="O47" s="71"/>
+      <c r="P47" s="72"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="68"/>
-      <c r="S47" s="69"/>
-      <c r="T47" s="70"/>
+      <c r="R47" s="70"/>
+      <c r="S47" s="71"/>
+      <c r="T47" s="72"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="68"/>
-      <c r="W47" s="69"/>
-      <c r="X47" s="70"/>
+      <c r="V47" s="70"/>
+      <c r="W47" s="71"/>
+      <c r="X47" s="72"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="68"/>
-      <c r="AA47" s="69"/>
-      <c r="AB47" s="70"/>
+      <c r="Z47" s="70"/>
+      <c r="AA47" s="71"/>
+      <c r="AB47" s="72"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="68"/>
-      <c r="AE47" s="69"/>
-      <c r="AF47" s="70"/>
+      <c r="AD47" s="70"/>
+      <c r="AE47" s="71"/>
+      <c r="AF47" s="72"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="68"/>
-      <c r="AI47" s="69"/>
-      <c r="AJ47" s="70"/>
+      <c r="AH47" s="70"/>
+      <c r="AI47" s="71"/>
+      <c r="AJ47" s="72"/>
       <c r="AK47" s="43"/>
-      <c r="AL47" s="68"/>
-      <c r="AM47" s="69"/>
-      <c r="AN47" s="70"/>
+      <c r="AL47" s="70"/>
+      <c r="AM47" s="71"/>
+      <c r="AN47" s="72"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4601,130 +4601,130 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
-      <c r="B48" s="71" t="s">
+      <c r="B48" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="72"/>
-      <c r="D48" s="73"/>
+      <c r="C48" s="74"/>
+      <c r="D48" s="75"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="71" t="s">
+      <c r="F48" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="G48" s="72"/>
-      <c r="H48" s="73"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="75"/>
       <c r="I48" s="43"/>
-      <c r="J48" s="71" t="s">
+      <c r="J48" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="K48" s="72"/>
-      <c r="L48" s="73"/>
+      <c r="K48" s="74"/>
+      <c r="L48" s="75"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="65" t="s">
+      <c r="N48" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="O48" s="66"/>
-      <c r="P48" s="67"/>
+      <c r="O48" s="77"/>
+      <c r="P48" s="78"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="71" t="s">
+      <c r="R48" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="S48" s="72"/>
-      <c r="T48" s="73"/>
+      <c r="S48" s="74"/>
+      <c r="T48" s="75"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="71" t="s">
+      <c r="V48" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="W48" s="72"/>
-      <c r="X48" s="73"/>
+      <c r="W48" s="74"/>
+      <c r="X48" s="75"/>
       <c r="Y48" s="40"/>
-      <c r="Z48" s="71" t="s">
+      <c r="Z48" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="AA48" s="72"/>
-      <c r="AB48" s="73"/>
+      <c r="AA48" s="74"/>
+      <c r="AB48" s="75"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="71" t="s">
+      <c r="AD48" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="AE48" s="72"/>
-      <c r="AF48" s="73"/>
+      <c r="AE48" s="74"/>
+      <c r="AF48" s="75"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="71" t="s">
+      <c r="AH48" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="AI48" s="72"/>
-      <c r="AJ48" s="73"/>
+      <c r="AI48" s="74"/>
+      <c r="AJ48" s="75"/>
       <c r="AK48" s="43"/>
-      <c r="AL48" s="71" t="s">
+      <c r="AL48" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="AM48" s="72"/>
-      <c r="AN48" s="73"/>
+      <c r="AM48" s="74"/>
+      <c r="AN48" s="75"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="71" t="s">
+      <c r="B49" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="72"/>
-      <c r="D49" s="73"/>
+      <c r="C49" s="74"/>
+      <c r="D49" s="75"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="71" t="s">
+      <c r="F49" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="72"/>
-      <c r="H49" s="73"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="75"/>
       <c r="I49" s="43"/>
-      <c r="J49" s="71" t="s">
+      <c r="J49" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="72"/>
-      <c r="L49" s="73"/>
+      <c r="K49" s="74"/>
+      <c r="L49" s="75"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="71" t="s">
+      <c r="N49" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="O49" s="72"/>
-      <c r="P49" s="73"/>
+      <c r="O49" s="74"/>
+      <c r="P49" s="75"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="71" t="s">
+      <c r="R49" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="S49" s="72"/>
-      <c r="T49" s="73"/>
+      <c r="S49" s="74"/>
+      <c r="T49" s="75"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="71" t="s">
+      <c r="V49" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="W49" s="72"/>
-      <c r="X49" s="73"/>
+      <c r="W49" s="74"/>
+      <c r="X49" s="75"/>
       <c r="Y49" s="44"/>
-      <c r="Z49" s="71" t="s">
+      <c r="Z49" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AA49" s="72"/>
-      <c r="AB49" s="73"/>
+      <c r="AA49" s="74"/>
+      <c r="AB49" s="75"/>
       <c r="AC49" s="43"/>
-      <c r="AD49" s="71" t="s">
+      <c r="AD49" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AE49" s="72"/>
-      <c r="AF49" s="73"/>
+      <c r="AE49" s="74"/>
+      <c r="AF49" s="75"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="71" t="s">
+      <c r="AH49" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AI49" s="72"/>
-      <c r="AJ49" s="73"/>
+      <c r="AI49" s="74"/>
+      <c r="AJ49" s="75"/>
       <c r="AK49" s="43"/>
-      <c r="AL49" s="71" t="s">
+      <c r="AL49" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="AM49" s="72"/>
-      <c r="AN49" s="73"/>
+      <c r="AM49" s="74"/>
+      <c r="AN49" s="75"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
@@ -4827,64 +4827,64 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="77" t="s">
+      <c r="B52" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="78"/>
+      <c r="C52" s="64"/>
       <c r="D52" s="57"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="77" t="s">
+      <c r="F52" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="G52" s="78"/>
+      <c r="G52" s="64"/>
       <c r="H52" s="57"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="77" t="s">
+      <c r="J52" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="K52" s="78"/>
+      <c r="K52" s="64"/>
       <c r="L52" s="57"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="63" t="s">
+      <c r="N52" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="O52" s="64"/>
+      <c r="O52" s="66"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="63" t="s">
+      <c r="R52" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="S52" s="64"/>
+      <c r="S52" s="66"/>
       <c r="T52" s="34"/>
       <c r="U52" s="36"/>
-      <c r="V52" s="63" t="s">
+      <c r="V52" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="W52" s="64"/>
+      <c r="W52" s="66"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="37"/>
-      <c r="Z52" s="63" t="s">
+      <c r="Z52" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="AA52" s="64"/>
+      <c r="AA52" s="66"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="32"/>
-      <c r="AD52" s="63" t="s">
+      <c r="AD52" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="AE52" s="64"/>
+      <c r="AE52" s="66"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="63" t="s">
+      <c r="AH52" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="AI52" s="64"/>
+      <c r="AI52" s="66"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="63" t="s">
+      <c r="AL52" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="AM52" s="64"/>
+      <c r="AM52" s="66"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
@@ -4907,47 +4907,47 @@
       <c r="K53" s="80"/>
       <c r="L53" s="81"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="74" t="s">
+      <c r="N53" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="O53" s="75"/>
-      <c r="P53" s="76"/>
+      <c r="O53" s="68"/>
+      <c r="P53" s="69"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="74" t="s">
+      <c r="R53" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="S53" s="75"/>
-      <c r="T53" s="76"/>
+      <c r="S53" s="68"/>
+      <c r="T53" s="69"/>
       <c r="U53" s="36"/>
-      <c r="V53" s="74" t="s">
+      <c r="V53" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="W53" s="75"/>
-      <c r="X53" s="76"/>
+      <c r="W53" s="68"/>
+      <c r="X53" s="69"/>
       <c r="Y53" s="50"/>
-      <c r="Z53" s="74" t="s">
+      <c r="Z53" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="AA53" s="75"/>
-      <c r="AB53" s="76"/>
+      <c r="AA53" s="68"/>
+      <c r="AB53" s="69"/>
       <c r="AC53" s="54"/>
-      <c r="AD53" s="74" t="s">
+      <c r="AD53" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="AE53" s="75"/>
-      <c r="AF53" s="76"/>
+      <c r="AE53" s="68"/>
+      <c r="AF53" s="69"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="74" t="s">
+      <c r="AH53" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="AI53" s="75"/>
-      <c r="AJ53" s="76"/>
+      <c r="AI53" s="68"/>
+      <c r="AJ53" s="69"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="74" t="s">
+      <c r="AL53" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="AM53" s="75"/>
-      <c r="AN53" s="76"/>
+      <c r="AM53" s="68"/>
+      <c r="AN53" s="69"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4963,159 +4963,159 @@
       <c r="K54" s="83"/>
       <c r="L54" s="84"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="68"/>
-      <c r="O54" s="69"/>
-      <c r="P54" s="70"/>
+      <c r="N54" s="70"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="68" t="s">
+      <c r="R54" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="S54" s="69"/>
-      <c r="T54" s="70"/>
+      <c r="S54" s="71"/>
+      <c r="T54" s="72"/>
       <c r="U54" s="43"/>
-      <c r="V54" s="68"/>
-      <c r="W54" s="69"/>
-      <c r="X54" s="70"/>
+      <c r="V54" s="70"/>
+      <c r="W54" s="71"/>
+      <c r="X54" s="72"/>
       <c r="Y54" s="50"/>
-      <c r="Z54" s="68"/>
-      <c r="AA54" s="69"/>
-      <c r="AB54" s="70"/>
+      <c r="Z54" s="70"/>
+      <c r="AA54" s="71"/>
+      <c r="AB54" s="72"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="68"/>
-      <c r="AE54" s="69"/>
-      <c r="AF54" s="70"/>
+      <c r="AD54" s="70"/>
+      <c r="AE54" s="71"/>
+      <c r="AF54" s="72"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="68"/>
-      <c r="AI54" s="69"/>
-      <c r="AJ54" s="70"/>
+      <c r="AH54" s="70"/>
+      <c r="AI54" s="71"/>
+      <c r="AJ54" s="72"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="68"/>
-      <c r="AM54" s="69"/>
-      <c r="AN54" s="70"/>
+      <c r="AL54" s="70"/>
+      <c r="AM54" s="71"/>
+      <c r="AN54" s="72"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="65" t="s">
+      <c r="B55" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="66"/>
-      <c r="D55" s="67"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="78"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="65" t="s">
+      <c r="F55" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="G55" s="66"/>
-      <c r="H55" s="67"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="78"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="65" t="s">
+      <c r="J55" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="K55" s="66"/>
-      <c r="L55" s="67"/>
+      <c r="K55" s="77"/>
+      <c r="L55" s="78"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="65" t="s">
+      <c r="N55" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O55" s="66"/>
-      <c r="P55" s="67"/>
+      <c r="O55" s="77"/>
+      <c r="P55" s="78"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="65" t="s">
+      <c r="R55" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="S55" s="66"/>
-      <c r="T55" s="67"/>
+      <c r="S55" s="77"/>
+      <c r="T55" s="78"/>
       <c r="U55" s="43"/>
-      <c r="V55" s="65" t="s">
+      <c r="V55" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="W55" s="66"/>
-      <c r="X55" s="67"/>
+      <c r="W55" s="77"/>
+      <c r="X55" s="78"/>
       <c r="Y55" s="32"/>
-      <c r="Z55" s="65" t="s">
+      <c r="Z55" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="AA55" s="66"/>
-      <c r="AB55" s="67"/>
+      <c r="AA55" s="77"/>
+      <c r="AB55" s="78"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="65" t="s">
+      <c r="AD55" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="AE55" s="66"/>
-      <c r="AF55" s="67"/>
+      <c r="AE55" s="77"/>
+      <c r="AF55" s="78"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="65" t="s">
+      <c r="AH55" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="AI55" s="66"/>
-      <c r="AJ55" s="67"/>
+      <c r="AI55" s="77"/>
+      <c r="AJ55" s="78"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="65" t="s">
+      <c r="AL55" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="AM55" s="66"/>
-      <c r="AN55" s="67"/>
+      <c r="AM55" s="77"/>
+      <c r="AN55" s="78"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="71" t="s">
+      <c r="B56" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="72"/>
-      <c r="D56" s="73"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="75"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="71" t="s">
+      <c r="F56" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="G56" s="72"/>
-      <c r="H56" s="73"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="75"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="71" t="s">
+      <c r="J56" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K56" s="72"/>
-      <c r="L56" s="73"/>
+      <c r="K56" s="74"/>
+      <c r="L56" s="75"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="71" t="s">
+      <c r="N56" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="O56" s="72"/>
-      <c r="P56" s="73"/>
+      <c r="O56" s="74"/>
+      <c r="P56" s="75"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="71" t="s">
+      <c r="R56" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="S56" s="72"/>
-      <c r="T56" s="73"/>
+      <c r="S56" s="74"/>
+      <c r="T56" s="75"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="71" t="s">
+      <c r="V56" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="W56" s="72"/>
-      <c r="X56" s="73"/>
+      <c r="W56" s="74"/>
+      <c r="X56" s="75"/>
       <c r="Y56" s="32"/>
-      <c r="Z56" s="71" t="s">
+      <c r="Z56" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="AA56" s="72"/>
-      <c r="AB56" s="73"/>
+      <c r="AA56" s="74"/>
+      <c r="AB56" s="75"/>
       <c r="AC56" s="40"/>
-      <c r="AD56" s="71" t="s">
+      <c r="AD56" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="AE56" s="72"/>
-      <c r="AF56" s="73"/>
+      <c r="AE56" s="74"/>
+      <c r="AF56" s="75"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="71" t="s">
+      <c r="AH56" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="AI56" s="72"/>
-      <c r="AJ56" s="73"/>
+      <c r="AI56" s="74"/>
+      <c r="AJ56" s="75"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="71" t="s">
+      <c r="AL56" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="AM56" s="72"/>
-      <c r="AN56" s="73"/>
+      <c r="AM56" s="74"/>
+      <c r="AN56" s="75"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5209,64 +5209,64 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="77" t="s">
+      <c r="B59" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="C59" s="78"/>
+      <c r="C59" s="64"/>
       <c r="D59" s="57" t="s">
         <v>66</v>
       </c>
       <c r="E59" s="36"/>
-      <c r="F59" s="77" t="s">
+      <c r="F59" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G59" s="78"/>
+      <c r="G59" s="64"/>
       <c r="H59" s="57" t="s">
         <v>53</v>
       </c>
       <c r="I59" s="32"/>
-      <c r="J59" s="77" t="s">
+      <c r="J59" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K59" s="78"/>
+      <c r="K59" s="64"/>
       <c r="L59" s="57"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="63"/>
-      <c r="O59" s="64"/>
+      <c r="N59" s="65"/>
+      <c r="O59" s="66"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="63"/>
-      <c r="S59" s="64"/>
+      <c r="R59" s="65"/>
+      <c r="S59" s="66"/>
       <c r="T59" s="34"/>
       <c r="U59" s="36"/>
-      <c r="V59" s="63"/>
-      <c r="W59" s="64"/>
+      <c r="V59" s="65"/>
+      <c r="W59" s="66"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="36"/>
-      <c r="Z59" s="63"/>
-      <c r="AA59" s="64"/>
+      <c r="Z59" s="65"/>
+      <c r="AA59" s="66"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="63" t="s">
+      <c r="AD59" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="AE59" s="64"/>
+      <c r="AE59" s="66"/>
       <c r="AF59" s="34" t="s">
         <v>53</v>
       </c>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="63" t="s">
+      <c r="AH59" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="AI59" s="64"/>
+      <c r="AI59" s="66"/>
       <c r="AJ59" s="34" t="s">
         <v>53</v>
       </c>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="63" t="s">
+      <c r="AL59" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="AM59" s="64"/>
+      <c r="AM59" s="66"/>
       <c r="AN59" s="34" t="s">
         <v>53</v>
       </c>
@@ -5291,39 +5291,39 @@
       <c r="K60" s="80"/>
       <c r="L60" s="81"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="74"/>
-      <c r="O60" s="75"/>
-      <c r="P60" s="76"/>
+      <c r="N60" s="67"/>
+      <c r="O60" s="68"/>
+      <c r="P60" s="69"/>
       <c r="Q60" s="37"/>
-      <c r="R60" s="74"/>
-      <c r="S60" s="75"/>
-      <c r="T60" s="76"/>
+      <c r="R60" s="67"/>
+      <c r="S60" s="68"/>
+      <c r="T60" s="69"/>
       <c r="U60" s="36"/>
-      <c r="V60" s="74"/>
-      <c r="W60" s="75"/>
-      <c r="X60" s="76"/>
+      <c r="V60" s="67"/>
+      <c r="W60" s="68"/>
+      <c r="X60" s="69"/>
       <c r="Y60" s="37"/>
-      <c r="Z60" s="74"/>
-      <c r="AA60" s="75"/>
-      <c r="AB60" s="76"/>
+      <c r="Z60" s="67"/>
+      <c r="AA60" s="68"/>
+      <c r="AB60" s="69"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="74" t="s">
+      <c r="AD60" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="AE60" s="75"/>
-      <c r="AF60" s="76"/>
+      <c r="AE60" s="68"/>
+      <c r="AF60" s="69"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="74" t="s">
+      <c r="AH60" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="AI60" s="75"/>
-      <c r="AJ60" s="76"/>
+      <c r="AI60" s="68"/>
+      <c r="AJ60" s="69"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="74" t="s">
+      <c r="AL60" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="AM60" s="75"/>
-      <c r="AN60" s="76"/>
+      <c r="AM60" s="68"/>
+      <c r="AN60" s="69"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5341,141 +5341,141 @@
       <c r="K61" s="83"/>
       <c r="L61" s="84"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="68"/>
-      <c r="O61" s="69"/>
-      <c r="P61" s="70"/>
+      <c r="N61" s="70"/>
+      <c r="O61" s="71"/>
+      <c r="P61" s="72"/>
       <c r="Q61" s="36"/>
-      <c r="R61" s="68"/>
-      <c r="S61" s="69"/>
-      <c r="T61" s="70"/>
+      <c r="R61" s="70"/>
+      <c r="S61" s="71"/>
+      <c r="T61" s="72"/>
       <c r="U61" s="35"/>
-      <c r="V61" s="68"/>
-      <c r="W61" s="69"/>
-      <c r="X61" s="70"/>
+      <c r="V61" s="70"/>
+      <c r="W61" s="71"/>
+      <c r="X61" s="72"/>
       <c r="Y61" s="36"/>
-      <c r="Z61" s="68"/>
-      <c r="AA61" s="69"/>
-      <c r="AB61" s="70"/>
+      <c r="Z61" s="70"/>
+      <c r="AA61" s="71"/>
+      <c r="AB61" s="72"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="68"/>
-      <c r="AE61" s="69"/>
-      <c r="AF61" s="70"/>
+      <c r="AD61" s="70"/>
+      <c r="AE61" s="71"/>
+      <c r="AF61" s="72"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="68"/>
-      <c r="AI61" s="69"/>
-      <c r="AJ61" s="70"/>
+      <c r="AH61" s="70"/>
+      <c r="AI61" s="71"/>
+      <c r="AJ61" s="72"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="68"/>
-      <c r="AM61" s="69"/>
-      <c r="AN61" s="70"/>
+      <c r="AL61" s="70"/>
+      <c r="AM61" s="71"/>
+      <c r="AN61" s="72"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="119" t="s">
+      <c r="B62" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="120"/>
-      <c r="D62" s="121"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="93"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="119" t="s">
+      <c r="F62" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="G62" s="120"/>
-      <c r="H62" s="121"/>
+      <c r="G62" s="92"/>
+      <c r="H62" s="93"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="65" t="s">
+      <c r="J62" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="K62" s="66"/>
-      <c r="L62" s="67"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="78"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="71"/>
-      <c r="O62" s="72"/>
-      <c r="P62" s="73"/>
+      <c r="N62" s="73"/>
+      <c r="O62" s="74"/>
+      <c r="P62" s="75"/>
       <c r="Q62" s="43"/>
-      <c r="R62" s="71"/>
-      <c r="S62" s="72"/>
-      <c r="T62" s="73"/>
+      <c r="R62" s="73"/>
+      <c r="S62" s="74"/>
+      <c r="T62" s="75"/>
       <c r="U62" s="43"/>
-      <c r="V62" s="71"/>
-      <c r="W62" s="72"/>
-      <c r="X62" s="73"/>
+      <c r="V62" s="73"/>
+      <c r="W62" s="74"/>
+      <c r="X62" s="75"/>
       <c r="Y62" s="43"/>
-      <c r="Z62" s="71"/>
-      <c r="AA62" s="72"/>
-      <c r="AB62" s="73"/>
+      <c r="Z62" s="73"/>
+      <c r="AA62" s="74"/>
+      <c r="AB62" s="75"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="71" t="s">
+      <c r="AD62" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="AE62" s="72"/>
-      <c r="AF62" s="73"/>
+      <c r="AE62" s="74"/>
+      <c r="AF62" s="75"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="71" t="s">
+      <c r="AH62" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="AI62" s="72"/>
-      <c r="AJ62" s="73"/>
+      <c r="AI62" s="74"/>
+      <c r="AJ62" s="75"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="71" t="s">
+      <c r="AL62" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="AM62" s="72"/>
-      <c r="AN62" s="73"/>
+      <c r="AM62" s="74"/>
+      <c r="AN62" s="75"/>
       <c r="AR62" s="13"/>
     </row>
     <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="71" t="s">
+      <c r="B63" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="72"/>
-      <c r="D63" s="73"/>
+      <c r="C63" s="74"/>
+      <c r="D63" s="75"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="71" t="s">
+      <c r="F63" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="G63" s="72"/>
-      <c r="H63" s="73"/>
+      <c r="G63" s="74"/>
+      <c r="H63" s="75"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="122" t="s">
+      <c r="J63" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="K63" s="123"/>
-      <c r="L63" s="124"/>
+      <c r="K63" s="89"/>
+      <c r="L63" s="90"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="71"/>
-      <c r="O63" s="72"/>
-      <c r="P63" s="73"/>
+      <c r="N63" s="73"/>
+      <c r="O63" s="74"/>
+      <c r="P63" s="75"/>
       <c r="Q63" s="50"/>
-      <c r="R63" s="71"/>
-      <c r="S63" s="72"/>
-      <c r="T63" s="73"/>
+      <c r="R63" s="73"/>
+      <c r="S63" s="74"/>
+      <c r="T63" s="75"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="71"/>
-      <c r="W63" s="72"/>
-      <c r="X63" s="73"/>
+      <c r="V63" s="73"/>
+      <c r="W63" s="74"/>
+      <c r="X63" s="75"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="71"/>
-      <c r="AA63" s="72"/>
-      <c r="AB63" s="73"/>
+      <c r="Z63" s="73"/>
+      <c r="AA63" s="74"/>
+      <c r="AB63" s="75"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="71" t="s">
+      <c r="AD63" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="AE63" s="72"/>
-      <c r="AF63" s="73"/>
+      <c r="AE63" s="74"/>
+      <c r="AF63" s="75"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="95" t="s">
+      <c r="AH63" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="AI63" s="96"/>
-      <c r="AJ63" s="97"/>
+      <c r="AI63" s="74"/>
+      <c r="AJ63" s="75"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="71" t="s">
+      <c r="AL63" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="AM63" s="72"/>
-      <c r="AN63" s="73"/>
+      <c r="AM63" s="74"/>
+      <c r="AN63" s="75"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5592,23 +5592,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="100" t="s">
+      <c r="N66" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="100"/>
-      <c r="P66" s="100"/>
-      <c r="Q66" s="100"/>
-      <c r="R66" s="100"/>
-      <c r="S66" s="100"/>
-      <c r="T66" s="100"/>
-      <c r="U66" s="100"/>
-      <c r="V66" s="100"/>
-      <c r="W66" s="100"/>
-      <c r="X66" s="100"/>
-      <c r="Y66" s="100"/>
-      <c r="Z66" s="100"/>
-      <c r="AA66" s="100"/>
-      <c r="AB66" s="100"/>
+      <c r="O66" s="94"/>
+      <c r="P66" s="94"/>
+      <c r="Q66" s="94"/>
+      <c r="R66" s="94"/>
+      <c r="S66" s="94"/>
+      <c r="T66" s="94"/>
+      <c r="U66" s="94"/>
+      <c r="V66" s="94"/>
+      <c r="W66" s="94"/>
+      <c r="X66" s="94"/>
+      <c r="Y66" s="94"/>
+      <c r="Z66" s="94"/>
+      <c r="AA66" s="94"/>
+      <c r="AB66" s="94"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5639,21 +5639,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="100"/>
-      <c r="O67" s="100"/>
-      <c r="P67" s="100"/>
-      <c r="Q67" s="100"/>
-      <c r="R67" s="100"/>
-      <c r="S67" s="100"/>
-      <c r="T67" s="100"/>
-      <c r="U67" s="100"/>
-      <c r="V67" s="100"/>
-      <c r="W67" s="100"/>
-      <c r="X67" s="100"/>
-      <c r="Y67" s="100"/>
-      <c r="Z67" s="100"/>
-      <c r="AA67" s="100"/>
-      <c r="AB67" s="100"/>
+      <c r="N67" s="94"/>
+      <c r="O67" s="94"/>
+      <c r="P67" s="94"/>
+      <c r="Q67" s="94"/>
+      <c r="R67" s="94"/>
+      <c r="S67" s="94"/>
+      <c r="T67" s="94"/>
+      <c r="U67" s="94"/>
+      <c r="V67" s="94"/>
+      <c r="W67" s="94"/>
+      <c r="X67" s="94"/>
+      <c r="Y67" s="94"/>
+      <c r="Z67" s="94"/>
+      <c r="AA67" s="94"/>
+      <c r="AB67" s="94"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5673,48 +5673,50 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="77"/>
-      <c r="C68" s="78"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="64"/>
       <c r="D68" s="57"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="77"/>
-      <c r="G68" s="78"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="64"/>
       <c r="H68" s="57"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="77"/>
-      <c r="K68" s="78"/>
+      <c r="J68" s="63"/>
+      <c r="K68" s="64"/>
       <c r="L68" s="57"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="63"/>
-      <c r="O68" s="64"/>
+      <c r="N68" s="65"/>
+      <c r="O68" s="66"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="44"/>
-      <c r="R68" s="63"/>
-      <c r="S68" s="64"/>
+      <c r="R68" s="65"/>
+      <c r="S68" s="66"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="63"/>
-      <c r="W68" s="64"/>
+      <c r="V68" s="65"/>
+      <c r="W68" s="66"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="63"/>
-      <c r="AA68" s="64"/>
+      <c r="Z68" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA68" s="66"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="63" t="s">
+      <c r="AD68" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="AE68" s="64"/>
+      <c r="AE68" s="66"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="63" t="s">
+      <c r="AH68" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="AI68" s="64"/>
+      <c r="AI68" s="66"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="63"/>
-      <c r="AM68" s="64"/>
+      <c r="AL68" s="65"/>
+      <c r="AM68" s="66"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5737,37 +5739,39 @@
       <c r="K69" s="80"/>
       <c r="L69" s="81"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="74"/>
-      <c r="O69" s="75"/>
-      <c r="P69" s="76"/>
+      <c r="N69" s="67"/>
+      <c r="O69" s="68"/>
+      <c r="P69" s="69"/>
       <c r="Q69" s="44"/>
-      <c r="R69" s="74"/>
-      <c r="S69" s="75"/>
-      <c r="T69" s="76"/>
+      <c r="R69" s="67"/>
+      <c r="S69" s="68"/>
+      <c r="T69" s="69"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="74"/>
-      <c r="W69" s="75"/>
-      <c r="X69" s="76"/>
+      <c r="V69" s="67"/>
+      <c r="W69" s="68"/>
+      <c r="X69" s="69"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="74"/>
-      <c r="AA69" s="75"/>
-      <c r="AB69" s="76"/>
+      <c r="Z69" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA69" s="68"/>
+      <c r="AB69" s="69"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="74" t="s">
+      <c r="AD69" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="AE69" s="75"/>
-      <c r="AF69" s="76"/>
+      <c r="AE69" s="68"/>
+      <c r="AF69" s="69"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="74" t="s">
+      <c r="AH69" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="AI69" s="75"/>
-      <c r="AJ69" s="76"/>
+      <c r="AI69" s="68"/>
+      <c r="AJ69" s="69"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="74"/>
-      <c r="AM69" s="75"/>
-      <c r="AN69" s="76"/>
+      <c r="AL69" s="67"/>
+      <c r="AM69" s="68"/>
+      <c r="AN69" s="69"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5789,37 +5793,39 @@
       <c r="K70" s="83"/>
       <c r="L70" s="84"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="68"/>
-      <c r="O70" s="69"/>
-      <c r="P70" s="70"/>
+      <c r="N70" s="70"/>
+      <c r="O70" s="71"/>
+      <c r="P70" s="72"/>
       <c r="Q70" s="44"/>
-      <c r="R70" s="68"/>
-      <c r="S70" s="69"/>
-      <c r="T70" s="70"/>
+      <c r="R70" s="70"/>
+      <c r="S70" s="71"/>
+      <c r="T70" s="72"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="68"/>
-      <c r="W70" s="69"/>
-      <c r="X70" s="70"/>
+      <c r="V70" s="70"/>
+      <c r="W70" s="71"/>
+      <c r="X70" s="72"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="68"/>
-      <c r="AA70" s="69"/>
-      <c r="AB70" s="70"/>
+      <c r="Z70" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA70" s="71"/>
+      <c r="AB70" s="72"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="68" t="s">
+      <c r="AD70" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="AE70" s="69"/>
-      <c r="AF70" s="70"/>
+      <c r="AE70" s="71"/>
+      <c r="AF70" s="72"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="68" t="s">
+      <c r="AH70" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="AI70" s="69"/>
-      <c r="AJ70" s="70"/>
+      <c r="AI70" s="71"/>
+      <c r="AJ70" s="72"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="68"/>
-      <c r="AM70" s="69"/>
-      <c r="AN70" s="70"/>
+      <c r="AL70" s="70"/>
+      <c r="AM70" s="71"/>
+      <c r="AN70" s="72"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5829,49 +5835,51 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12"/>
-      <c r="B71" s="65"/>
-      <c r="C71" s="66"/>
-      <c r="D71" s="67"/>
+      <c r="B71" s="76"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="78"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="65"/>
-      <c r="G71" s="66"/>
-      <c r="H71" s="67"/>
+      <c r="F71" s="76"/>
+      <c r="G71" s="77"/>
+      <c r="H71" s="78"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="65"/>
-      <c r="K71" s="66"/>
-      <c r="L71" s="67"/>
+      <c r="J71" s="76"/>
+      <c r="K71" s="77"/>
+      <c r="L71" s="78"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="65"/>
-      <c r="O71" s="66"/>
-      <c r="P71" s="67"/>
+      <c r="N71" s="76"/>
+      <c r="O71" s="77"/>
+      <c r="P71" s="78"/>
       <c r="Q71" s="44"/>
-      <c r="R71" s="65"/>
-      <c r="S71" s="66"/>
-      <c r="T71" s="67"/>
+      <c r="R71" s="76"/>
+      <c r="S71" s="77"/>
+      <c r="T71" s="78"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="65"/>
-      <c r="W71" s="66"/>
-      <c r="X71" s="67"/>
+      <c r="V71" s="76"/>
+      <c r="W71" s="77"/>
+      <c r="X71" s="78"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="65"/>
-      <c r="AA71" s="66"/>
-      <c r="AB71" s="67"/>
+      <c r="Z71" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA71" s="77"/>
+      <c r="AB71" s="78"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="65" t="s">
+      <c r="AD71" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="AE71" s="66"/>
-      <c r="AF71" s="67"/>
+      <c r="AE71" s="77"/>
+      <c r="AF71" s="78"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="65" t="s">
+      <c r="AH71" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="AI71" s="66"/>
-      <c r="AJ71" s="67"/>
+      <c r="AI71" s="77"/>
+      <c r="AJ71" s="78"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="65"/>
-      <c r="AM71" s="66"/>
-      <c r="AN71" s="67"/>
+      <c r="AL71" s="76"/>
+      <c r="AM71" s="77"/>
+      <c r="AN71" s="78"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -5977,44 +5985,44 @@
     </row>
     <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12"/>
-      <c r="B74" s="77"/>
-      <c r="C74" s="78"/>
+      <c r="B74" s="63"/>
+      <c r="C74" s="64"/>
       <c r="D74" s="57"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="77"/>
-      <c r="G74" s="78"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="64"/>
       <c r="H74" s="57"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="77"/>
-      <c r="K74" s="78"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="64"/>
       <c r="L74" s="57"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="63"/>
-      <c r="O74" s="64"/>
+      <c r="N74" s="65"/>
+      <c r="O74" s="66"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="32"/>
-      <c r="R74" s="63"/>
-      <c r="S74" s="64"/>
+      <c r="R74" s="65"/>
+      <c r="S74" s="66"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="63"/>
-      <c r="W74" s="64"/>
+      <c r="V74" s="65"/>
+      <c r="W74" s="66"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="63"/>
-      <c r="AA74" s="64"/>
+      <c r="Z74" s="65"/>
+      <c r="AA74" s="66"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="63"/>
-      <c r="AE74" s="64"/>
+      <c r="AD74" s="65"/>
+      <c r="AE74" s="66"/>
       <c r="AF74" s="34"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="63"/>
-      <c r="AI74" s="64"/>
+      <c r="AH74" s="65"/>
+      <c r="AI74" s="66"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="63"/>
-      <c r="AM74" s="64"/>
+      <c r="AL74" s="65"/>
+      <c r="AM74" s="66"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
@@ -6035,33 +6043,33 @@
       <c r="K75" s="80"/>
       <c r="L75" s="81"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="74"/>
-      <c r="O75" s="75"/>
-      <c r="P75" s="76"/>
+      <c r="N75" s="67"/>
+      <c r="O75" s="68"/>
+      <c r="P75" s="69"/>
       <c r="Q75" s="35"/>
-      <c r="R75" s="74"/>
-      <c r="S75" s="75"/>
-      <c r="T75" s="76"/>
+      <c r="R75" s="67"/>
+      <c r="S75" s="68"/>
+      <c r="T75" s="69"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="74"/>
-      <c r="W75" s="75"/>
-      <c r="X75" s="76"/>
+      <c r="V75" s="67"/>
+      <c r="W75" s="68"/>
+      <c r="X75" s="69"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="74"/>
-      <c r="AA75" s="75"/>
-      <c r="AB75" s="76"/>
+      <c r="Z75" s="67"/>
+      <c r="AA75" s="68"/>
+      <c r="AB75" s="69"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="74"/>
-      <c r="AE75" s="75"/>
-      <c r="AF75" s="76"/>
+      <c r="AD75" s="67"/>
+      <c r="AE75" s="68"/>
+      <c r="AF75" s="69"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="74"/>
-      <c r="AI75" s="75"/>
-      <c r="AJ75" s="76"/>
+      <c r="AH75" s="67"/>
+      <c r="AI75" s="68"/>
+      <c r="AJ75" s="69"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="74"/>
-      <c r="AM75" s="75"/>
-      <c r="AN75" s="76"/>
+      <c r="AL75" s="67"/>
+      <c r="AM75" s="68"/>
+      <c r="AN75" s="69"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
@@ -6081,33 +6089,33 @@
       <c r="K76" s="83"/>
       <c r="L76" s="84"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="68"/>
-      <c r="O76" s="69"/>
-      <c r="P76" s="70"/>
+      <c r="N76" s="70"/>
+      <c r="O76" s="71"/>
+      <c r="P76" s="72"/>
       <c r="Q76" s="31"/>
-      <c r="R76" s="68"/>
-      <c r="S76" s="69"/>
-      <c r="T76" s="70"/>
+      <c r="R76" s="70"/>
+      <c r="S76" s="71"/>
+      <c r="T76" s="72"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="68"/>
-      <c r="W76" s="69"/>
-      <c r="X76" s="70"/>
+      <c r="V76" s="70"/>
+      <c r="W76" s="71"/>
+      <c r="X76" s="72"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="68"/>
-      <c r="AA76" s="69"/>
-      <c r="AB76" s="70"/>
+      <c r="Z76" s="70"/>
+      <c r="AA76" s="71"/>
+      <c r="AB76" s="72"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="68"/>
-      <c r="AE76" s="69"/>
-      <c r="AF76" s="70"/>
+      <c r="AD76" s="70"/>
+      <c r="AE76" s="71"/>
+      <c r="AF76" s="72"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="68"/>
-      <c r="AI76" s="69"/>
-      <c r="AJ76" s="70"/>
+      <c r="AH76" s="70"/>
+      <c r="AI76" s="71"/>
+      <c r="AJ76" s="72"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="68"/>
-      <c r="AM76" s="69"/>
-      <c r="AN76" s="70"/>
+      <c r="AL76" s="70"/>
+      <c r="AM76" s="71"/>
+      <c r="AN76" s="72"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6115,45 +6123,45 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16"/>
-      <c r="B77" s="65"/>
-      <c r="C77" s="66"/>
-      <c r="D77" s="67"/>
+      <c r="B77" s="76"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="78"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="65"/>
-      <c r="G77" s="66"/>
-      <c r="H77" s="67"/>
+      <c r="F77" s="76"/>
+      <c r="G77" s="77"/>
+      <c r="H77" s="78"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="65"/>
-      <c r="K77" s="66"/>
-      <c r="L77" s="67"/>
+      <c r="J77" s="76"/>
+      <c r="K77" s="77"/>
+      <c r="L77" s="78"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="65"/>
-      <c r="O77" s="66"/>
-      <c r="P77" s="67"/>
+      <c r="N77" s="76"/>
+      <c r="O77" s="77"/>
+      <c r="P77" s="78"/>
       <c r="Q77" s="32"/>
-      <c r="R77" s="65"/>
-      <c r="S77" s="66"/>
-      <c r="T77" s="67"/>
+      <c r="R77" s="76"/>
+      <c r="S77" s="77"/>
+      <c r="T77" s="78"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="65"/>
-      <c r="W77" s="66"/>
-      <c r="X77" s="67"/>
+      <c r="V77" s="76"/>
+      <c r="W77" s="77"/>
+      <c r="X77" s="78"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="65"/>
-      <c r="AA77" s="66"/>
-      <c r="AB77" s="67"/>
+      <c r="Z77" s="76"/>
+      <c r="AA77" s="77"/>
+      <c r="AB77" s="78"/>
       <c r="AC77" s="43"/>
-      <c r="AD77" s="65"/>
-      <c r="AE77" s="66"/>
-      <c r="AF77" s="67"/>
+      <c r="AD77" s="76"/>
+      <c r="AE77" s="77"/>
+      <c r="AF77" s="78"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="65"/>
-      <c r="AI77" s="66"/>
-      <c r="AJ77" s="67"/>
+      <c r="AH77" s="76"/>
+      <c r="AI77" s="77"/>
+      <c r="AJ77" s="78"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="65"/>
-      <c r="AM77" s="66"/>
-      <c r="AN77" s="67"/>
+      <c r="AL77" s="76"/>
+      <c r="AM77" s="77"/>
+      <c r="AN77" s="78"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6253,44 +6261,44 @@
     </row>
     <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12"/>
-      <c r="B80" s="77"/>
-      <c r="C80" s="78"/>
+      <c r="B80" s="63"/>
+      <c r="C80" s="64"/>
       <c r="D80" s="57"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="77"/>
-      <c r="G80" s="78"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="64"/>
       <c r="H80" s="57"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="77"/>
-      <c r="K80" s="78"/>
+      <c r="J80" s="63"/>
+      <c r="K80" s="64"/>
       <c r="L80" s="57"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="63"/>
-      <c r="O80" s="64"/>
+      <c r="N80" s="65"/>
+      <c r="O80" s="66"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="32"/>
-      <c r="R80" s="63"/>
-      <c r="S80" s="64"/>
+      <c r="R80" s="65"/>
+      <c r="S80" s="66"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="63"/>
-      <c r="W80" s="64"/>
+      <c r="V80" s="65"/>
+      <c r="W80" s="66"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="63"/>
-      <c r="AA80" s="64"/>
+      <c r="Z80" s="65"/>
+      <c r="AA80" s="66"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="63"/>
-      <c r="AE80" s="64"/>
+      <c r="AD80" s="65"/>
+      <c r="AE80" s="66"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="63"/>
-      <c r="AI80" s="64"/>
+      <c r="AH80" s="65"/>
+      <c r="AI80" s="66"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="63"/>
-      <c r="AM80" s="64"/>
+      <c r="AL80" s="65"/>
+      <c r="AM80" s="66"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
@@ -6311,33 +6319,33 @@
       <c r="K81" s="80"/>
       <c r="L81" s="81"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="74"/>
-      <c r="O81" s="75"/>
-      <c r="P81" s="76"/>
+      <c r="N81" s="67"/>
+      <c r="O81" s="68"/>
+      <c r="P81" s="69"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="74"/>
-      <c r="S81" s="75"/>
-      <c r="T81" s="76"/>
+      <c r="R81" s="67"/>
+      <c r="S81" s="68"/>
+      <c r="T81" s="69"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="74"/>
-      <c r="W81" s="75"/>
-      <c r="X81" s="76"/>
+      <c r="V81" s="67"/>
+      <c r="W81" s="68"/>
+      <c r="X81" s="69"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="74"/>
-      <c r="AA81" s="75"/>
-      <c r="AB81" s="76"/>
+      <c r="Z81" s="67"/>
+      <c r="AA81" s="68"/>
+      <c r="AB81" s="69"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="74"/>
-      <c r="AE81" s="75"/>
-      <c r="AF81" s="76"/>
+      <c r="AD81" s="67"/>
+      <c r="AE81" s="68"/>
+      <c r="AF81" s="69"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="74"/>
-      <c r="AI81" s="75"/>
-      <c r="AJ81" s="76"/>
+      <c r="AH81" s="67"/>
+      <c r="AI81" s="68"/>
+      <c r="AJ81" s="69"/>
       <c r="AK81" s="32"/>
-      <c r="AL81" s="74"/>
-      <c r="AM81" s="75"/>
-      <c r="AN81" s="76"/>
+      <c r="AL81" s="67"/>
+      <c r="AM81" s="68"/>
+      <c r="AN81" s="69"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
@@ -6357,33 +6365,33 @@
       <c r="K82" s="83"/>
       <c r="L82" s="84"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="68"/>
-      <c r="O82" s="69"/>
-      <c r="P82" s="70"/>
+      <c r="N82" s="70"/>
+      <c r="O82" s="71"/>
+      <c r="P82" s="72"/>
       <c r="Q82" s="32"/>
-      <c r="R82" s="68"/>
-      <c r="S82" s="69"/>
-      <c r="T82" s="70"/>
+      <c r="R82" s="70"/>
+      <c r="S82" s="71"/>
+      <c r="T82" s="72"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="68"/>
-      <c r="W82" s="69"/>
-      <c r="X82" s="70"/>
+      <c r="V82" s="70"/>
+      <c r="W82" s="71"/>
+      <c r="X82" s="72"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="68"/>
-      <c r="AA82" s="69"/>
-      <c r="AB82" s="70"/>
+      <c r="Z82" s="70"/>
+      <c r="AA82" s="71"/>
+      <c r="AB82" s="72"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="68"/>
-      <c r="AE82" s="69"/>
-      <c r="AF82" s="70"/>
+      <c r="AD82" s="70"/>
+      <c r="AE82" s="71"/>
+      <c r="AF82" s="72"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="68"/>
-      <c r="AI82" s="69"/>
-      <c r="AJ82" s="70"/>
+      <c r="AH82" s="70"/>
+      <c r="AI82" s="71"/>
+      <c r="AJ82" s="72"/>
       <c r="AK82" s="32"/>
-      <c r="AL82" s="68"/>
-      <c r="AM82" s="69"/>
-      <c r="AN82" s="70"/>
+      <c r="AL82" s="70"/>
+      <c r="AM82" s="71"/>
+      <c r="AN82" s="72"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6391,45 +6399,45 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12"/>
-      <c r="B83" s="65"/>
-      <c r="C83" s="66"/>
-      <c r="D83" s="67"/>
+      <c r="B83" s="76"/>
+      <c r="C83" s="77"/>
+      <c r="D83" s="78"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="66"/>
-      <c r="H83" s="67"/>
+      <c r="F83" s="76"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="78"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="65"/>
-      <c r="K83" s="66"/>
-      <c r="L83" s="67"/>
+      <c r="J83" s="76"/>
+      <c r="K83" s="77"/>
+      <c r="L83" s="78"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="65"/>
-      <c r="O83" s="66"/>
-      <c r="P83" s="67"/>
+      <c r="N83" s="76"/>
+      <c r="O83" s="77"/>
+      <c r="P83" s="78"/>
       <c r="Q83" s="32"/>
-      <c r="R83" s="65"/>
-      <c r="S83" s="66"/>
-      <c r="T83" s="67"/>
+      <c r="R83" s="76"/>
+      <c r="S83" s="77"/>
+      <c r="T83" s="78"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="65"/>
-      <c r="W83" s="66"/>
-      <c r="X83" s="67"/>
+      <c r="V83" s="76"/>
+      <c r="W83" s="77"/>
+      <c r="X83" s="78"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="65"/>
-      <c r="AA83" s="66"/>
-      <c r="AB83" s="67"/>
+      <c r="Z83" s="76"/>
+      <c r="AA83" s="77"/>
+      <c r="AB83" s="78"/>
       <c r="AC83" s="31"/>
-      <c r="AD83" s="65"/>
-      <c r="AE83" s="66"/>
-      <c r="AF83" s="67"/>
+      <c r="AD83" s="76"/>
+      <c r="AE83" s="77"/>
+      <c r="AF83" s="78"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="65"/>
-      <c r="AI83" s="66"/>
-      <c r="AJ83" s="67"/>
+      <c r="AH83" s="76"/>
+      <c r="AI83" s="77"/>
+      <c r="AJ83" s="78"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="65"/>
-      <c r="AM83" s="66"/>
-      <c r="AN83" s="67"/>
+      <c r="AL83" s="76"/>
+      <c r="AM83" s="77"/>
+      <c r="AN83" s="78"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6529,44 +6537,44 @@
     </row>
     <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12"/>
-      <c r="B86" s="77"/>
-      <c r="C86" s="78"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="64"/>
       <c r="D86" s="57"/>
       <c r="E86" s="32"/>
-      <c r="F86" s="77"/>
-      <c r="G86" s="78"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="64"/>
       <c r="H86" s="57"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="77"/>
-      <c r="K86" s="78"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="64"/>
       <c r="L86" s="57"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="63"/>
-      <c r="O86" s="64"/>
+      <c r="N86" s="65"/>
+      <c r="O86" s="66"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="63"/>
-      <c r="S86" s="64"/>
+      <c r="R86" s="65"/>
+      <c r="S86" s="66"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="63"/>
-      <c r="W86" s="64"/>
+      <c r="V86" s="65"/>
+      <c r="W86" s="66"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="63"/>
-      <c r="AA86" s="64"/>
+      <c r="Z86" s="65"/>
+      <c r="AA86" s="66"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="63"/>
-      <c r="AE86" s="64"/>
+      <c r="AD86" s="65"/>
+      <c r="AE86" s="66"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="32"/>
-      <c r="AH86" s="63"/>
-      <c r="AI86" s="64"/>
+      <c r="AH86" s="65"/>
+      <c r="AI86" s="66"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="63"/>
-      <c r="AM86" s="64"/>
+      <c r="AL86" s="65"/>
+      <c r="AM86" s="66"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
@@ -6587,33 +6595,33 @@
       <c r="K87" s="80"/>
       <c r="L87" s="81"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="74"/>
-      <c r="O87" s="75"/>
-      <c r="P87" s="76"/>
+      <c r="N87" s="67"/>
+      <c r="O87" s="68"/>
+      <c r="P87" s="69"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="74"/>
-      <c r="S87" s="75"/>
-      <c r="T87" s="76"/>
+      <c r="R87" s="67"/>
+      <c r="S87" s="68"/>
+      <c r="T87" s="69"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="74"/>
-      <c r="W87" s="75"/>
-      <c r="X87" s="76"/>
+      <c r="V87" s="67"/>
+      <c r="W87" s="68"/>
+      <c r="X87" s="69"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="74"/>
-      <c r="AA87" s="75"/>
-      <c r="AB87" s="76"/>
+      <c r="Z87" s="67"/>
+      <c r="AA87" s="68"/>
+      <c r="AB87" s="69"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="74"/>
-      <c r="AE87" s="75"/>
-      <c r="AF87" s="76"/>
+      <c r="AD87" s="67"/>
+      <c r="AE87" s="68"/>
+      <c r="AF87" s="69"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="74"/>
-      <c r="AI87" s="75"/>
-      <c r="AJ87" s="76"/>
+      <c r="AH87" s="67"/>
+      <c r="AI87" s="68"/>
+      <c r="AJ87" s="69"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="74"/>
-      <c r="AM87" s="75"/>
-      <c r="AN87" s="76"/>
+      <c r="AL87" s="67"/>
+      <c r="AM87" s="68"/>
+      <c r="AN87" s="69"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
@@ -6633,33 +6641,33 @@
       <c r="K88" s="83"/>
       <c r="L88" s="84"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="68"/>
-      <c r="O88" s="69"/>
-      <c r="P88" s="70"/>
+      <c r="N88" s="70"/>
+      <c r="O88" s="71"/>
+      <c r="P88" s="72"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="68"/>
-      <c r="S88" s="69"/>
-      <c r="T88" s="70"/>
+      <c r="R88" s="70"/>
+      <c r="S88" s="71"/>
+      <c r="T88" s="72"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="68"/>
-      <c r="W88" s="69"/>
-      <c r="X88" s="70"/>
+      <c r="V88" s="70"/>
+      <c r="W88" s="71"/>
+      <c r="X88" s="72"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="68"/>
-      <c r="AA88" s="69"/>
-      <c r="AB88" s="70"/>
+      <c r="Z88" s="70"/>
+      <c r="AA88" s="71"/>
+      <c r="AB88" s="72"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="68"/>
-      <c r="AE88" s="69"/>
-      <c r="AF88" s="70"/>
+      <c r="AD88" s="70"/>
+      <c r="AE88" s="71"/>
+      <c r="AF88" s="72"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="68"/>
-      <c r="AI88" s="69"/>
-      <c r="AJ88" s="70"/>
+      <c r="AH88" s="70"/>
+      <c r="AI88" s="71"/>
+      <c r="AJ88" s="72"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="68"/>
-      <c r="AM88" s="69"/>
-      <c r="AN88" s="70"/>
+      <c r="AL88" s="70"/>
+      <c r="AM88" s="71"/>
+      <c r="AN88" s="72"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -6667,45 +6675,45 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12"/>
-      <c r="B89" s="65"/>
-      <c r="C89" s="66"/>
-      <c r="D89" s="67"/>
+      <c r="B89" s="76"/>
+      <c r="C89" s="77"/>
+      <c r="D89" s="78"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="65"/>
-      <c r="G89" s="66"/>
-      <c r="H89" s="67"/>
+      <c r="F89" s="76"/>
+      <c r="G89" s="77"/>
+      <c r="H89" s="78"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="65"/>
-      <c r="K89" s="66"/>
-      <c r="L89" s="67"/>
+      <c r="J89" s="76"/>
+      <c r="K89" s="77"/>
+      <c r="L89" s="78"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="65"/>
-      <c r="O89" s="66"/>
-      <c r="P89" s="67"/>
+      <c r="N89" s="76"/>
+      <c r="O89" s="77"/>
+      <c r="P89" s="78"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="65"/>
-      <c r="S89" s="66"/>
-      <c r="T89" s="67"/>
+      <c r="R89" s="76"/>
+      <c r="S89" s="77"/>
+      <c r="T89" s="78"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="65"/>
-      <c r="W89" s="66"/>
-      <c r="X89" s="67"/>
+      <c r="V89" s="76"/>
+      <c r="W89" s="77"/>
+      <c r="X89" s="78"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="65"/>
-      <c r="AA89" s="66"/>
-      <c r="AB89" s="67"/>
+      <c r="Z89" s="76"/>
+      <c r="AA89" s="77"/>
+      <c r="AB89" s="78"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="65"/>
-      <c r="AE89" s="66"/>
-      <c r="AF89" s="67"/>
+      <c r="AD89" s="76"/>
+      <c r="AE89" s="77"/>
+      <c r="AF89" s="78"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="65"/>
-      <c r="AI89" s="66"/>
-      <c r="AJ89" s="67"/>
+      <c r="AH89" s="76"/>
+      <c r="AI89" s="77"/>
+      <c r="AJ89" s="78"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="65"/>
-      <c r="AM89" s="66"/>
-      <c r="AN89" s="67"/>
+      <c r="AL89" s="76"/>
+      <c r="AM89" s="77"/>
+      <c r="AN89" s="78"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -6805,44 +6813,44 @@
     </row>
     <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="78"/>
+      <c r="B92" s="63"/>
+      <c r="C92" s="64"/>
       <c r="D92" s="57"/>
       <c r="E92" s="44"/>
-      <c r="F92" s="77"/>
-      <c r="G92" s="78"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="64"/>
       <c r="H92" s="57"/>
       <c r="I92" s="32"/>
-      <c r="J92" s="77"/>
-      <c r="K92" s="78"/>
+      <c r="J92" s="63"/>
+      <c r="K92" s="64"/>
       <c r="L92" s="57"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="63"/>
-      <c r="O92" s="64"/>
+      <c r="N92" s="65"/>
+      <c r="O92" s="66"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="32"/>
-      <c r="R92" s="63"/>
-      <c r="S92" s="64"/>
+      <c r="R92" s="65"/>
+      <c r="S92" s="66"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="63"/>
-      <c r="W92" s="64"/>
+      <c r="V92" s="65"/>
+      <c r="W92" s="66"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="63"/>
-      <c r="AA92" s="64"/>
+      <c r="Z92" s="65"/>
+      <c r="AA92" s="66"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="63"/>
-      <c r="AE92" s="64"/>
+      <c r="AD92" s="65"/>
+      <c r="AE92" s="66"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="63"/>
-      <c r="AI92" s="64"/>
+      <c r="AH92" s="65"/>
+      <c r="AI92" s="66"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="63"/>
-      <c r="AM92" s="64"/>
+      <c r="AL92" s="65"/>
+      <c r="AM92" s="66"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
@@ -6863,33 +6871,33 @@
       <c r="K93" s="80"/>
       <c r="L93" s="81"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="74"/>
-      <c r="O93" s="75"/>
-      <c r="P93" s="76"/>
+      <c r="N93" s="67"/>
+      <c r="O93" s="68"/>
+      <c r="P93" s="69"/>
       <c r="Q93" s="35"/>
-      <c r="R93" s="74"/>
-      <c r="S93" s="75"/>
-      <c r="T93" s="76"/>
+      <c r="R93" s="67"/>
+      <c r="S93" s="68"/>
+      <c r="T93" s="69"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="74"/>
-      <c r="W93" s="75"/>
-      <c r="X93" s="76"/>
+      <c r="V93" s="67"/>
+      <c r="W93" s="68"/>
+      <c r="X93" s="69"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="74"/>
-      <c r="AA93" s="75"/>
-      <c r="AB93" s="76"/>
+      <c r="Z93" s="67"/>
+      <c r="AA93" s="68"/>
+      <c r="AB93" s="69"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="74"/>
-      <c r="AE93" s="75"/>
-      <c r="AF93" s="76"/>
+      <c r="AD93" s="67"/>
+      <c r="AE93" s="68"/>
+      <c r="AF93" s="69"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="74"/>
-      <c r="AI93" s="75"/>
-      <c r="AJ93" s="76"/>
+      <c r="AH93" s="67"/>
+      <c r="AI93" s="68"/>
+      <c r="AJ93" s="69"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="74"/>
-      <c r="AM93" s="75"/>
-      <c r="AN93" s="76"/>
+      <c r="AL93" s="67"/>
+      <c r="AM93" s="68"/>
+      <c r="AN93" s="69"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
@@ -6909,33 +6917,33 @@
       <c r="K94" s="83"/>
       <c r="L94" s="84"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="68"/>
-      <c r="O94" s="69"/>
-      <c r="P94" s="70"/>
+      <c r="N94" s="70"/>
+      <c r="O94" s="71"/>
+      <c r="P94" s="72"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="68"/>
-      <c r="S94" s="69"/>
-      <c r="T94" s="70"/>
+      <c r="R94" s="70"/>
+      <c r="S94" s="71"/>
+      <c r="T94" s="72"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="68"/>
-      <c r="W94" s="69"/>
-      <c r="X94" s="70"/>
+      <c r="V94" s="70"/>
+      <c r="W94" s="71"/>
+      <c r="X94" s="72"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="68"/>
-      <c r="AA94" s="69"/>
-      <c r="AB94" s="70"/>
+      <c r="Z94" s="70"/>
+      <c r="AA94" s="71"/>
+      <c r="AB94" s="72"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="68"/>
-      <c r="AE94" s="69"/>
-      <c r="AF94" s="70"/>
+      <c r="AD94" s="70"/>
+      <c r="AE94" s="71"/>
+      <c r="AF94" s="72"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="68"/>
-      <c r="AI94" s="69"/>
-      <c r="AJ94" s="70"/>
+      <c r="AH94" s="70"/>
+      <c r="AI94" s="71"/>
+      <c r="AJ94" s="72"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="68"/>
-      <c r="AM94" s="69"/>
-      <c r="AN94" s="70"/>
+      <c r="AL94" s="70"/>
+      <c r="AM94" s="71"/>
+      <c r="AN94" s="72"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -6943,45 +6951,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12"/>
-      <c r="B95" s="65"/>
-      <c r="C95" s="66"/>
-      <c r="D95" s="67"/>
+      <c r="B95" s="76"/>
+      <c r="C95" s="77"/>
+      <c r="D95" s="78"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="65"/>
-      <c r="G95" s="66"/>
-      <c r="H95" s="67"/>
+      <c r="F95" s="76"/>
+      <c r="G95" s="77"/>
+      <c r="H95" s="78"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="65"/>
-      <c r="K95" s="66"/>
-      <c r="L95" s="67"/>
+      <c r="J95" s="76"/>
+      <c r="K95" s="77"/>
+      <c r="L95" s="78"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="65"/>
-      <c r="O95" s="66"/>
-      <c r="P95" s="67"/>
+      <c r="N95" s="76"/>
+      <c r="O95" s="77"/>
+      <c r="P95" s="78"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="65"/>
-      <c r="S95" s="66"/>
-      <c r="T95" s="67"/>
+      <c r="R95" s="76"/>
+      <c r="S95" s="77"/>
+      <c r="T95" s="78"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="65"/>
-      <c r="W95" s="66"/>
-      <c r="X95" s="67"/>
+      <c r="V95" s="76"/>
+      <c r="W95" s="77"/>
+      <c r="X95" s="78"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="65"/>
-      <c r="AA95" s="66"/>
-      <c r="AB95" s="67"/>
+      <c r="Z95" s="76"/>
+      <c r="AA95" s="77"/>
+      <c r="AB95" s="78"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="65"/>
-      <c r="AE95" s="66"/>
-      <c r="AF95" s="67"/>
+      <c r="AD95" s="76"/>
+      <c r="AE95" s="77"/>
+      <c r="AF95" s="78"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="65"/>
-      <c r="AI95" s="66"/>
-      <c r="AJ95" s="67"/>
+      <c r="AH95" s="76"/>
+      <c r="AI95" s="77"/>
+      <c r="AJ95" s="78"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="65"/>
-      <c r="AM95" s="66"/>
-      <c r="AN95" s="67"/>
+      <c r="AL95" s="76"/>
+      <c r="AM95" s="77"/>
+      <c r="AN95" s="78"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7081,44 +7089,44 @@
     </row>
     <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12"/>
-      <c r="B98" s="77"/>
-      <c r="C98" s="78"/>
+      <c r="B98" s="63"/>
+      <c r="C98" s="64"/>
       <c r="D98" s="57"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="77"/>
-      <c r="G98" s="78"/>
+      <c r="F98" s="63"/>
+      <c r="G98" s="64"/>
       <c r="H98" s="57"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="77"/>
-      <c r="K98" s="78"/>
+      <c r="J98" s="63"/>
+      <c r="K98" s="64"/>
       <c r="L98" s="57"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="63"/>
-      <c r="O98" s="64"/>
+      <c r="N98" s="65"/>
+      <c r="O98" s="66"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="63"/>
-      <c r="S98" s="64"/>
+      <c r="R98" s="65"/>
+      <c r="S98" s="66"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="63"/>
-      <c r="W98" s="64"/>
+      <c r="V98" s="65"/>
+      <c r="W98" s="66"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="63"/>
-      <c r="AA98" s="64"/>
+      <c r="Z98" s="65"/>
+      <c r="AA98" s="66"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="63"/>
-      <c r="AE98" s="64"/>
+      <c r="AD98" s="65"/>
+      <c r="AE98" s="66"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="63"/>
-      <c r="AI98" s="64"/>
+      <c r="AH98" s="65"/>
+      <c r="AI98" s="66"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="63"/>
-      <c r="AM98" s="64"/>
+      <c r="AL98" s="65"/>
+      <c r="AM98" s="66"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
@@ -7139,33 +7147,33 @@
       <c r="K99" s="80"/>
       <c r="L99" s="81"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="74"/>
-      <c r="O99" s="75"/>
-      <c r="P99" s="76"/>
+      <c r="N99" s="67"/>
+      <c r="O99" s="68"/>
+      <c r="P99" s="69"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="74"/>
-      <c r="S99" s="75"/>
-      <c r="T99" s="76"/>
+      <c r="R99" s="67"/>
+      <c r="S99" s="68"/>
+      <c r="T99" s="69"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="74"/>
-      <c r="W99" s="75"/>
-      <c r="X99" s="76"/>
+      <c r="V99" s="67"/>
+      <c r="W99" s="68"/>
+      <c r="X99" s="69"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="74"/>
-      <c r="AA99" s="75"/>
-      <c r="AB99" s="76"/>
+      <c r="Z99" s="67"/>
+      <c r="AA99" s="68"/>
+      <c r="AB99" s="69"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="74"/>
-      <c r="AE99" s="75"/>
-      <c r="AF99" s="76"/>
+      <c r="AD99" s="67"/>
+      <c r="AE99" s="68"/>
+      <c r="AF99" s="69"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="74"/>
-      <c r="AI99" s="75"/>
-      <c r="AJ99" s="76"/>
+      <c r="AH99" s="67"/>
+      <c r="AI99" s="68"/>
+      <c r="AJ99" s="69"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="74"/>
-      <c r="AM99" s="75"/>
-      <c r="AN99" s="76"/>
+      <c r="AL99" s="67"/>
+      <c r="AM99" s="68"/>
+      <c r="AN99" s="69"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
@@ -7185,33 +7193,33 @@
       <c r="K100" s="83"/>
       <c r="L100" s="84"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="68"/>
-      <c r="O100" s="69"/>
-      <c r="P100" s="70"/>
+      <c r="N100" s="70"/>
+      <c r="O100" s="71"/>
+      <c r="P100" s="72"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="68"/>
-      <c r="S100" s="69"/>
-      <c r="T100" s="70"/>
+      <c r="R100" s="70"/>
+      <c r="S100" s="71"/>
+      <c r="T100" s="72"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="68"/>
-      <c r="W100" s="69"/>
-      <c r="X100" s="70"/>
+      <c r="V100" s="70"/>
+      <c r="W100" s="71"/>
+      <c r="X100" s="72"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="68"/>
-      <c r="AA100" s="69"/>
-      <c r="AB100" s="70"/>
+      <c r="Z100" s="70"/>
+      <c r="AA100" s="71"/>
+      <c r="AB100" s="72"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="68"/>
-      <c r="AE100" s="69"/>
-      <c r="AF100" s="70"/>
+      <c r="AD100" s="70"/>
+      <c r="AE100" s="71"/>
+      <c r="AF100" s="72"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="68"/>
-      <c r="AI100" s="69"/>
-      <c r="AJ100" s="70"/>
+      <c r="AH100" s="70"/>
+      <c r="AI100" s="71"/>
+      <c r="AJ100" s="72"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="68"/>
-      <c r="AM100" s="69"/>
-      <c r="AN100" s="70"/>
+      <c r="AL100" s="70"/>
+      <c r="AM100" s="71"/>
+      <c r="AN100" s="72"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7219,45 +7227,45 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12"/>
-      <c r="B101" s="65"/>
-      <c r="C101" s="66"/>
-      <c r="D101" s="67"/>
+      <c r="B101" s="76"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="78"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="65"/>
-      <c r="G101" s="66"/>
-      <c r="H101" s="67"/>
+      <c r="F101" s="76"/>
+      <c r="G101" s="77"/>
+      <c r="H101" s="78"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="65"/>
-      <c r="K101" s="66"/>
-      <c r="L101" s="67"/>
+      <c r="J101" s="76"/>
+      <c r="K101" s="77"/>
+      <c r="L101" s="78"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="65"/>
-      <c r="O101" s="66"/>
-      <c r="P101" s="67"/>
+      <c r="N101" s="76"/>
+      <c r="O101" s="77"/>
+      <c r="P101" s="78"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="65"/>
-      <c r="S101" s="66"/>
-      <c r="T101" s="67"/>
+      <c r="R101" s="76"/>
+      <c r="S101" s="77"/>
+      <c r="T101" s="78"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="65"/>
-      <c r="W101" s="66"/>
-      <c r="X101" s="67"/>
+      <c r="V101" s="76"/>
+      <c r="W101" s="77"/>
+      <c r="X101" s="78"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="65"/>
-      <c r="AA101" s="66"/>
-      <c r="AB101" s="67"/>
+      <c r="Z101" s="76"/>
+      <c r="AA101" s="77"/>
+      <c r="AB101" s="78"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="65"/>
-      <c r="AE101" s="66"/>
-      <c r="AF101" s="67"/>
+      <c r="AD101" s="76"/>
+      <c r="AE101" s="77"/>
+      <c r="AF101" s="78"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="65"/>
-      <c r="AI101" s="66"/>
-      <c r="AJ101" s="67"/>
+      <c r="AH101" s="76"/>
+      <c r="AI101" s="77"/>
+      <c r="AJ101" s="78"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="65"/>
-      <c r="AM101" s="66"/>
-      <c r="AN101" s="67"/>
+      <c r="AL101" s="76"/>
+      <c r="AM101" s="77"/>
+      <c r="AN101" s="78"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7373,57 +7381,57 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="63"/>
-      <c r="C105" s="64"/>
+      <c r="B105" s="65"/>
+      <c r="C105" s="66"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="63"/>
-      <c r="G105" s="64"/>
+      <c r="F105" s="65"/>
+      <c r="G105" s="66"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="63"/>
-      <c r="K105" s="64"/>
+      <c r="J105" s="65"/>
+      <c r="K105" s="66"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="74"/>
-      <c r="C106" s="75"/>
-      <c r="D106" s="76"/>
+      <c r="B106" s="67"/>
+      <c r="C106" s="68"/>
+      <c r="D106" s="69"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="74"/>
-      <c r="G106" s="75"/>
-      <c r="H106" s="76"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="68"/>
+      <c r="H106" s="69"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="74"/>
-      <c r="K106" s="75"/>
-      <c r="L106" s="76"/>
+      <c r="J106" s="67"/>
+      <c r="K106" s="68"/>
+      <c r="L106" s="69"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="68"/>
-      <c r="C107" s="69"/>
-      <c r="D107" s="70"/>
+      <c r="B107" s="70"/>
+      <c r="C107" s="71"/>
+      <c r="D107" s="72"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="69"/>
-      <c r="H107" s="70"/>
+      <c r="F107" s="70"/>
+      <c r="G107" s="71"/>
+      <c r="H107" s="72"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="68"/>
-      <c r="K107" s="69"/>
-      <c r="L107" s="70"/>
+      <c r="J107" s="70"/>
+      <c r="K107" s="71"/>
+      <c r="L107" s="72"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="65"/>
-      <c r="C108" s="66"/>
-      <c r="D108" s="67"/>
+      <c r="B108" s="76"/>
+      <c r="C108" s="77"/>
+      <c r="D108" s="78"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="65"/>
-      <c r="G108" s="66"/>
-      <c r="H108" s="67"/>
+      <c r="F108" s="76"/>
+      <c r="G108" s="77"/>
+      <c r="H108" s="78"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="65"/>
-      <c r="K108" s="66"/>
-      <c r="L108" s="67"/>
+      <c r="J108" s="76"/>
+      <c r="K108" s="77"/>
+      <c r="L108" s="78"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="60"/>
@@ -7452,56 +7460,56 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="63"/>
-      <c r="C111" s="64"/>
+      <c r="B111" s="65"/>
+      <c r="C111" s="66"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="63"/>
-      <c r="G111" s="64"/>
+      <c r="F111" s="65"/>
+      <c r="G111" s="66"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="63"/>
-      <c r="K111" s="64"/>
+      <c r="J111" s="65"/>
+      <c r="K111" s="66"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="74"/>
-      <c r="C112" s="75"/>
-      <c r="D112" s="76"/>
+      <c r="B112" s="67"/>
+      <c r="C112" s="68"/>
+      <c r="D112" s="69"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="74"/>
-      <c r="G112" s="75"/>
-      <c r="H112" s="76"/>
+      <c r="F112" s="67"/>
+      <c r="G112" s="68"/>
+      <c r="H112" s="69"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="74"/>
-      <c r="K112" s="75"/>
-      <c r="L112" s="76"/>
+      <c r="J112" s="67"/>
+      <c r="K112" s="68"/>
+      <c r="L112" s="69"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="68"/>
-      <c r="C113" s="69"/>
-      <c r="D113" s="70"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="72"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="68"/>
-      <c r="G113" s="69"/>
-      <c r="H113" s="70"/>
+      <c r="F113" s="70"/>
+      <c r="G113" s="71"/>
+      <c r="H113" s="72"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="68"/>
-      <c r="K113" s="69"/>
-      <c r="L113" s="70"/>
+      <c r="J113" s="70"/>
+      <c r="K113" s="71"/>
+      <c r="L113" s="72"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="65"/>
-      <c r="C114" s="66"/>
-      <c r="D114" s="67"/>
+      <c r="B114" s="76"/>
+      <c r="C114" s="77"/>
+      <c r="D114" s="78"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="65"/>
-      <c r="G114" s="66"/>
-      <c r="H114" s="67"/>
+      <c r="F114" s="76"/>
+      <c r="G114" s="77"/>
+      <c r="H114" s="78"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="65"/>
-      <c r="K114" s="66"/>
-      <c r="L114" s="67"/>
+      <c r="J114" s="76"/>
+      <c r="K114" s="77"/>
+      <c r="L114" s="78"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" s="60"/>
@@ -7530,56 +7538,56 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="63"/>
-      <c r="C117" s="64"/>
+      <c r="B117" s="65"/>
+      <c r="C117" s="66"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="63"/>
-      <c r="G117" s="64"/>
+      <c r="F117" s="65"/>
+      <c r="G117" s="66"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="63"/>
-      <c r="K117" s="64"/>
+      <c r="J117" s="65"/>
+      <c r="K117" s="66"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="74"/>
-      <c r="C118" s="75"/>
-      <c r="D118" s="76"/>
+      <c r="B118" s="67"/>
+      <c r="C118" s="68"/>
+      <c r="D118" s="69"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="74"/>
-      <c r="G118" s="75"/>
-      <c r="H118" s="76"/>
+      <c r="F118" s="67"/>
+      <c r="G118" s="68"/>
+      <c r="H118" s="69"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="74"/>
-      <c r="K118" s="75"/>
-      <c r="L118" s="76"/>
+      <c r="J118" s="67"/>
+      <c r="K118" s="68"/>
+      <c r="L118" s="69"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="68"/>
-      <c r="C119" s="69"/>
-      <c r="D119" s="70"/>
+      <c r="B119" s="70"/>
+      <c r="C119" s="71"/>
+      <c r="D119" s="72"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="68"/>
-      <c r="G119" s="69"/>
-      <c r="H119" s="70"/>
+      <c r="F119" s="70"/>
+      <c r="G119" s="71"/>
+      <c r="H119" s="72"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="68"/>
-      <c r="K119" s="69"/>
-      <c r="L119" s="70"/>
+      <c r="J119" s="70"/>
+      <c r="K119" s="71"/>
+      <c r="L119" s="72"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="65"/>
-      <c r="C120" s="66"/>
-      <c r="D120" s="67"/>
+      <c r="B120" s="76"/>
+      <c r="C120" s="77"/>
+      <c r="D120" s="78"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="65"/>
-      <c r="G120" s="66"/>
-      <c r="H120" s="67"/>
+      <c r="F120" s="76"/>
+      <c r="G120" s="77"/>
+      <c r="H120" s="78"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="65"/>
-      <c r="K120" s="66"/>
-      <c r="L120" s="67"/>
+      <c r="J120" s="76"/>
+      <c r="K120" s="77"/>
+      <c r="L120" s="78"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B121" s="60"/>
@@ -7608,56 +7616,56 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="63"/>
-      <c r="C123" s="64"/>
+      <c r="B123" s="65"/>
+      <c r="C123" s="66"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="63"/>
-      <c r="G123" s="64"/>
+      <c r="F123" s="65"/>
+      <c r="G123" s="66"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="63"/>
-      <c r="K123" s="64"/>
+      <c r="J123" s="65"/>
+      <c r="K123" s="66"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="74"/>
-      <c r="C124" s="75"/>
-      <c r="D124" s="76"/>
+      <c r="B124" s="67"/>
+      <c r="C124" s="68"/>
+      <c r="D124" s="69"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="74"/>
-      <c r="G124" s="75"/>
-      <c r="H124" s="76"/>
+      <c r="F124" s="67"/>
+      <c r="G124" s="68"/>
+      <c r="H124" s="69"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="74"/>
-      <c r="K124" s="75"/>
-      <c r="L124" s="76"/>
+      <c r="J124" s="67"/>
+      <c r="K124" s="68"/>
+      <c r="L124" s="69"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="68"/>
-      <c r="C125" s="69"/>
-      <c r="D125" s="70"/>
+      <c r="B125" s="70"/>
+      <c r="C125" s="71"/>
+      <c r="D125" s="72"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="68"/>
-      <c r="G125" s="69"/>
-      <c r="H125" s="70"/>
+      <c r="F125" s="70"/>
+      <c r="G125" s="71"/>
+      <c r="H125" s="72"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="68"/>
-      <c r="K125" s="69"/>
-      <c r="L125" s="70"/>
+      <c r="J125" s="70"/>
+      <c r="K125" s="71"/>
+      <c r="L125" s="72"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="65"/>
-      <c r="C126" s="66"/>
-      <c r="D126" s="67"/>
+      <c r="B126" s="76"/>
+      <c r="C126" s="77"/>
+      <c r="D126" s="78"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="65"/>
-      <c r="G126" s="66"/>
-      <c r="H126" s="67"/>
+      <c r="F126" s="76"/>
+      <c r="G126" s="77"/>
+      <c r="H126" s="78"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="65"/>
-      <c r="K126" s="66"/>
-      <c r="L126" s="67"/>
+      <c r="J126" s="76"/>
+      <c r="K126" s="77"/>
+      <c r="L126" s="78"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B127" s="60"/>
@@ -7686,56 +7694,56 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="63"/>
-      <c r="C129" s="64"/>
+      <c r="B129" s="65"/>
+      <c r="C129" s="66"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="63"/>
-      <c r="G129" s="64"/>
+      <c r="F129" s="65"/>
+      <c r="G129" s="66"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="63"/>
-      <c r="K129" s="64"/>
+      <c r="J129" s="65"/>
+      <c r="K129" s="66"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="74"/>
-      <c r="C130" s="75"/>
-      <c r="D130" s="76"/>
+      <c r="B130" s="67"/>
+      <c r="C130" s="68"/>
+      <c r="D130" s="69"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="74"/>
-      <c r="G130" s="75"/>
-      <c r="H130" s="76"/>
+      <c r="F130" s="67"/>
+      <c r="G130" s="68"/>
+      <c r="H130" s="69"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="74"/>
-      <c r="K130" s="75"/>
-      <c r="L130" s="76"/>
+      <c r="J130" s="67"/>
+      <c r="K130" s="68"/>
+      <c r="L130" s="69"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="68"/>
-      <c r="C131" s="69"/>
-      <c r="D131" s="70"/>
+      <c r="B131" s="70"/>
+      <c r="C131" s="71"/>
+      <c r="D131" s="72"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="68"/>
-      <c r="G131" s="69"/>
-      <c r="H131" s="70"/>
+      <c r="F131" s="70"/>
+      <c r="G131" s="71"/>
+      <c r="H131" s="72"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="68"/>
-      <c r="K131" s="69"/>
-      <c r="L131" s="70"/>
+      <c r="J131" s="70"/>
+      <c r="K131" s="71"/>
+      <c r="L131" s="72"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="65"/>
-      <c r="C132" s="66"/>
-      <c r="D132" s="67"/>
+      <c r="B132" s="76"/>
+      <c r="C132" s="77"/>
+      <c r="D132" s="78"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="65"/>
-      <c r="G132" s="66"/>
-      <c r="H132" s="67"/>
+      <c r="F132" s="76"/>
+      <c r="G132" s="77"/>
+      <c r="H132" s="78"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="65"/>
-      <c r="K132" s="66"/>
-      <c r="L132" s="67"/>
+      <c r="J132" s="76"/>
+      <c r="K132" s="77"/>
+      <c r="L132" s="78"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B133" s="60"/>
@@ -7754,6 +7762,863 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="881">
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AH87:AJ87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AH93:AJ93"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="AD87:AF87"/>
+    <mergeCell ref="AL75:AN75"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="AH72:AJ72"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AL37:AN37"/>
+    <mergeCell ref="AL39:AM39"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="V37:X37"/>
+    <mergeCell ref="V39:W39"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="Z48:AB48"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="J37:L37"/>
     <mergeCell ref="B39:C39"/>
@@ -7778,869 +8643,12 @@
     <mergeCell ref="AH50:AJ50"/>
     <mergeCell ref="AH52:AI52"/>
     <mergeCell ref="AH37:AJ37"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="V37:X37"/>
-    <mergeCell ref="V39:W39"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AL37:AN37"/>
-    <mergeCell ref="AL39:AM39"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="V93:X93"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="Z93:AB93"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="AH72:AJ72"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="AD87:AF87"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AH87:AJ87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AH93:AJ93"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="R49:T49"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="T22:T27 AB22:AB27 AF22:AF27 D22:D27 AJ22:AJ27 AN22:AN27 X22:X27 L22:L27 H22:H27 P22:P27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R42:T43 AH14:AJ16 AH22:AI27 N42:P43 R48:T50 R22:S27 B101:D102 J132:L133 AD89:AF90 V62:X64 N77:P78 V42:X43 N95:P96 F14:H16 V22:W27 AH62:AJ64 AL101:AN102 J77:L78 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 V83:X84 AH95:AJ96 R8:T10 F89:H90 B108:D109 AL42:AN43 Z14:AB16 AH42:AJ43 R14:T16 F101:H102 AL14:AN16 J95:L96 AH48:AJ50 AD83:AF84 B71:D72 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 AL83:AN84 Z101:AB102 Z34:AB37 AL89:AN90 Z77:AB78 AD22:AE27 V14:X16 AL22:AM27 F108:H109 AL55:AN57 AL71:AN72 Z62:AB64 AH83:AJ84 J83:L84 AH34:AJ37 J8:L10 AH77:AJ78 R77:T78 J89:L90 AD77:AF78 N22:O27 F62:H64 Z42:AB43 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 V55:X57 N34:P37 Z83:AB84 N101:P102 AH71:AJ72 Z71:AB72 V95:X96 N55:P57 F83:H84 B83:D84 Z22:AA27 N48:P50 Z48:AB50 AD42:AF43 AH101:AJ102 AH89:AJ90 R83:T84 AD48:AF50 Z8:AB10 J62:L64 AL8:AN10 V89:X90 N8:P10 F71:H72 AL62:AN64 AL95:AN96 V101:X102 Z95:AB96 AD34:AF37 B89:D90 Z89:AB90 R62:T64 N71:P72 F77:H78 J22:K27 F22:G27 J101:L102 Z55:AB57 B95:D96 B77:D78 F95:H96 R34:T37 J71:L72 B8:D10 AD71:AF72 AL48:AN50 V77:X78 AD55:AF57 J14:L16 AH55:AJ57 B14:D16 B22:C27 R71:T72 V48:X50 N83:P84 AL34:AN37 V34:X37 AL77:AN78 R55:T57 V71:X72 F8:H10 B62:D64 F55:H57 F42:H43 B34:D37 B55:D57 B42:D43 J34:L37 J42:L43 B48:D50 F48:H50 F34:H37 J55:L57 J48:L50 N62:P64 AD62:AF64">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R42:T43 AH14:AJ16 AH22:AI27 N42:P43 R48:T50 R22:S27 B101:D102 J132:L133 AD89:AF90 V62:X64 N77:P78 V42:X43 N95:P96 F14:H16 V22:W27 AH62:AJ64 AL101:AN102 J77:L78 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 V83:X84 AH95:AJ96 R8:T10 F89:H90 B108:D109 AL42:AN43 Z14:AB16 AH42:AJ43 R14:T16 F101:H102 AL14:AN16 J95:L96 AH48:AJ50 AD83:AF84 B71:D72 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 AL83:AN84 Z101:AB102 Z34:AB37 AL89:AN90 Z77:AB78 AD22:AE27 V14:X16 AL22:AM27 F108:H109 AL55:AN57 AL71:AN72 Z62:AB64 AH83:AJ84 J83:L84 AH34:AJ37 J8:L10 AH77:AJ78 R77:T78 J89:L90 AD77:AF78 N22:O27 F62:H64 Z42:AB43 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 V55:X57 N34:P37 Z83:AB84 N101:P102 AH71:AJ72 AD62:AF64 V95:X96 N55:P57 F83:H84 B83:D84 Z22:AA27 N48:P50 Z48:AB50 AD42:AF43 AH101:AJ102 AH89:AJ90 R83:T84 AD48:AF50 Z8:AB10 J62:L64 AL8:AN10 V89:X90 N8:P10 F71:H72 AL62:AN64 AL95:AN96 V101:X102 Z95:AB96 AD34:AF37 B89:D90 Z89:AB90 R62:T64 N71:P72 F77:H78 J22:K27 F22:G27 J101:L102 Z55:AB57 B95:D96 B77:D78 F95:H96 R34:T37 J71:L72 B8:D10 AD71:AF72 AL48:AN50 V77:X78 AD55:AF57 J14:L16 AH55:AJ57 B14:D16 B22:C27 R71:T72 V48:X50 N83:P84 AL34:AN37 V34:X37 AL77:AN78 R55:T57 V71:X72 F8:H10 B62:D64 F55:H57 F42:H43 B34:D37 B55:D57 B42:D43 J34:L37 J42:L43 B48:D50 F48:H50 F34:H37 J55:L57 J48:L50 N62:P64 Z71:AB72">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="77">
   <si>
     <t>CUMA</t>
   </si>
@@ -246,6 +246,15 @@
   </si>
   <si>
     <t>YENİ PROGRAM</t>
+  </si>
+  <si>
+    <t>HABER HİZMETİ</t>
+  </si>
+  <si>
+    <t>Haliç Kongre Merkezi</t>
+  </si>
+  <si>
+    <t>ANKARA SES</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1296,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1634,6 +1643,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2765,7 +2792,7 @@
       </c>
       <c r="AQ13" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR13" s="30"/>
     </row>
@@ -5513,11 +5540,11 @@
       <c r="AA64" s="61"/>
       <c r="AB64" s="62"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE64" s="61"/>
-      <c r="AF64" s="62"/>
+      <c r="AD64" s="128" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE64" s="129"/>
+      <c r="AF64" s="130"/>
       <c r="AG64" s="44"/>
       <c r="AH64" s="60" t="s">
         <v>27</v>
@@ -6013,9 +6040,11 @@
       <c r="AA74" s="66"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="65"/>
-      <c r="AE74" s="66"/>
-      <c r="AF74" s="34"/>
+      <c r="AD74" s="125" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE74" s="126"/>
+      <c r="AF74" s="127"/>
       <c r="AG74" s="32"/>
       <c r="AH74" s="65"/>
       <c r="AI74" s="66"/>
@@ -6059,7 +6088,9 @@
       <c r="AA75" s="68"/>
       <c r="AB75" s="69"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="67"/>
+      <c r="AD75" s="67" t="s">
+        <v>75</v>
+      </c>
       <c r="AE75" s="68"/>
       <c r="AF75" s="69"/>
       <c r="AG75" s="32"/>
@@ -6151,7 +6182,9 @@
       <c r="AA77" s="77"/>
       <c r="AB77" s="78"/>
       <c r="AC77" s="43"/>
-      <c r="AD77" s="76"/>
+      <c r="AD77" s="76" t="s">
+        <v>76</v>
+      </c>
       <c r="AE77" s="77"/>
       <c r="AF77" s="78"/>
       <c r="AG77" s="32"/>
@@ -6197,7 +6230,9 @@
       <c r="AA78" s="61"/>
       <c r="AB78" s="62"/>
       <c r="AC78" s="43"/>
-      <c r="AD78" s="60"/>
+      <c r="AD78" s="60" t="s">
+        <v>13</v>
+      </c>
       <c r="AE78" s="61"/>
       <c r="AF78" s="62"/>
       <c r="AG78" s="31"/>
@@ -8648,7 +8683,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="T22:T27 AB22:AB27 AF22:AF27 D22:D27 AJ22:AJ27 AN22:AN27 X22:X27 L22:L27 H22:H27 P22:P27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R42:T43 AH14:AJ16 AH22:AI27 N42:P43 R48:T50 R22:S27 B101:D102 J132:L133 AD89:AF90 V62:X64 N77:P78 V42:X43 N95:P96 F14:H16 V22:W27 AH62:AJ64 AL101:AN102 J77:L78 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 V83:X84 AH95:AJ96 R8:T10 F89:H90 B108:D109 AL42:AN43 Z14:AB16 AH42:AJ43 R14:T16 F101:H102 AL14:AN16 J95:L96 AH48:AJ50 AD83:AF84 B71:D72 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 AL83:AN84 Z101:AB102 Z34:AB37 AL89:AN90 Z77:AB78 AD22:AE27 V14:X16 AL22:AM27 F108:H109 AL55:AN57 AL71:AN72 Z62:AB64 AH83:AJ84 J83:L84 AH34:AJ37 J8:L10 AH77:AJ78 R77:T78 J89:L90 AD77:AF78 N22:O27 F62:H64 Z42:AB43 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 V55:X57 N34:P37 Z83:AB84 N101:P102 AH71:AJ72 AD62:AF64 V95:X96 N55:P57 F83:H84 B83:D84 Z22:AA27 N48:P50 Z48:AB50 AD42:AF43 AH101:AJ102 AH89:AJ90 R83:T84 AD48:AF50 Z8:AB10 J62:L64 AL8:AN10 V89:X90 N8:P10 F71:H72 AL62:AN64 AL95:AN96 V101:X102 Z95:AB96 AD34:AF37 B89:D90 Z89:AB90 R62:T64 N71:P72 F77:H78 J22:K27 F22:G27 J101:L102 Z55:AB57 B95:D96 B77:D78 F95:H96 R34:T37 J71:L72 B8:D10 AD71:AF72 AL48:AN50 V77:X78 AD55:AF57 J14:L16 AH55:AJ57 B14:D16 B22:C27 R71:T72 V48:X50 N83:P84 AL34:AN37 V34:X37 AL77:AN78 R55:T57 V71:X72 F8:H10 B62:D64 F55:H57 F42:H43 B34:D37 B55:D57 B42:D43 J34:L37 J42:L43 B48:D50 F48:H50 F34:H37 J55:L57 J48:L50 N62:P64 Z71:AB72">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R42:T43 AH14:AJ16 AH22:AI27 N42:P43 R48:T50 R22:S27 B101:D102 J132:L133 AD89:AF90 V62:X64 N77:P78 V42:X43 N95:P96 F14:H16 V22:W27 AH62:AJ64 AL101:AN102 J77:L78 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 V83:X84 AH95:AJ96 R8:T10 F89:H90 B108:D109 AL42:AN43 Z14:AB16 AH42:AJ43 R14:T16 F101:H102 AL14:AN16 J95:L96 AH48:AJ50 AD83:AF84 B71:D72 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 AL83:AN84 Z101:AB102 Z34:AB37 AL89:AN90 Z77:AB78 AD22:AE27 V14:X16 AL22:AM27 F108:H109 AL55:AN57 AL71:AN72 Z62:AB64 AH83:AJ84 J83:L84 AH34:AJ37 J8:L10 AH77:AJ78 R77:T78 J89:L90 AD62:AF64 N22:O27 F62:H64 Z42:AB43 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 V55:X57 N34:P37 Z83:AB84 N101:P102 AH71:AJ72 Z71:AB72 V95:X96 N55:P57 F83:H84 B83:D84 Z22:AA27 N48:P50 Z48:AB50 AD42:AF43 AH101:AJ102 AH89:AJ90 R83:T84 AD48:AF50 Z8:AB10 J62:L64 AL8:AN10 V89:X90 N8:P10 F71:H72 AL62:AN64 AL95:AN96 V101:X102 Z95:AB96 AD34:AF37 B89:D90 Z89:AB90 R62:T64 N71:P72 F77:H78 J22:K27 F22:G27 J101:L102 Z55:AB57 B95:D96 B77:D78 F95:H96 R34:T37 J71:L72 B8:D10 AD71:AF72 AL48:AN50 V77:X78 AD55:AF57 J14:L16 AH55:AJ57 B14:D16 B22:C27 R71:T72 V48:X50 N83:P84 AL34:AN37 V34:X37 AL77:AN78 R55:T57 V71:X72 F8:H10 B62:D64 F55:H57 F42:H43 B34:D37 B55:D57 B42:D43 J34:L37 J42:L43 B48:D50 F48:H50 F34:H37 J55:L57 J48:L50 N62:P64 AD77:AF78">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23670" windowHeight="10995" tabRatio="515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23676" windowHeight="10992" tabRatio="515"/>
   </bookViews>
   <sheets>
     <sheet name="SES SERVİSİ ÇALIŞMA PLANI" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="78">
   <si>
     <t>CUMA</t>
   </si>
@@ -248,13 +248,16 @@
     <t>YENİ PROGRAM</t>
   </si>
   <si>
-    <t>HABER HİZMETİ</t>
-  </si>
-  <si>
     <t>Haliç Kongre Merkezi</t>
   </si>
   <si>
     <t>ANKARA SES</t>
+  </si>
+  <si>
+    <t>Sheraton Grand Ataşehir</t>
+  </si>
+  <si>
+    <t>HABER HİZMETİ x2</t>
   </si>
 </sst>
 </file>
@@ -1449,6 +1452,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1458,54 +1464,54 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1524,6 +1530,132 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1531,135 +1663,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2034,7 +2037,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="182" row="2" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2060,197 +2063,197 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR133"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="26" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="26" customWidth="1"/>
-    <col min="5" max="5" width="1.7109375" style="26" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" style="26" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" style="26" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" style="26" customWidth="1"/>
-    <col min="10" max="10" width="2.7109375" style="26" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="26" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="26" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="26" customWidth="1"/>
-    <col min="14" max="14" width="2.7109375" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" customWidth="1"/>
-    <col min="17" max="17" width="1.7109375" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" customWidth="1"/>
-    <col min="21" max="21" width="1.7109375" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" customWidth="1"/>
-    <col min="23" max="23" width="20.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="1.7109375" customWidth="1"/>
-    <col min="26" max="26" width="2.7109375" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" customWidth="1"/>
-    <col min="29" max="29" width="1.7109375" customWidth="1"/>
-    <col min="30" max="30" width="2.7109375" customWidth="1"/>
-    <col min="31" max="31" width="20.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.7109375" customWidth="1"/>
-    <col min="33" max="33" width="1.7109375" customWidth="1"/>
-    <col min="34" max="34" width="2.7109375" customWidth="1"/>
-    <col min="35" max="35" width="20.7109375" customWidth="1"/>
-    <col min="36" max="36" width="6.7109375" customWidth="1"/>
-    <col min="37" max="37" width="1.7109375" customWidth="1"/>
-    <col min="38" max="38" width="2.7109375" customWidth="1"/>
-    <col min="39" max="39" width="20.7109375" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" customWidth="1"/>
-    <col min="41" max="41" width="2.7109375" customWidth="1"/>
-    <col min="42" max="42" width="16.7109375" customWidth="1"/>
-    <col min="43" max="43" width="3.7109375" customWidth="1"/>
-    <col min="44" max="44" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="2.6640625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="1.6640625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" style="26" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="26" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" style="26" customWidth="1"/>
+    <col min="13" max="13" width="1.6640625" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.6640625" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" customWidth="1"/>
+    <col min="17" max="17" width="1.6640625" customWidth="1"/>
+    <col min="18" max="18" width="2.6640625" customWidth="1"/>
+    <col min="19" max="19" width="20.6640625" customWidth="1"/>
+    <col min="20" max="20" width="6.6640625" customWidth="1"/>
+    <col min="21" max="21" width="1.6640625" customWidth="1"/>
+    <col min="22" max="22" width="2.6640625" customWidth="1"/>
+    <col min="23" max="23" width="20.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="1.6640625" customWidth="1"/>
+    <col min="26" max="26" width="2.6640625" customWidth="1"/>
+    <col min="27" max="27" width="20.6640625" customWidth="1"/>
+    <col min="28" max="28" width="6.6640625" customWidth="1"/>
+    <col min="29" max="29" width="1.6640625" customWidth="1"/>
+    <col min="30" max="30" width="2.6640625" customWidth="1"/>
+    <col min="31" max="31" width="20.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.6640625" customWidth="1"/>
+    <col min="33" max="33" width="1.6640625" customWidth="1"/>
+    <col min="34" max="34" width="2.6640625" customWidth="1"/>
+    <col min="35" max="35" width="20.6640625" customWidth="1"/>
+    <col min="36" max="36" width="6.6640625" customWidth="1"/>
+    <col min="37" max="37" width="1.6640625" customWidth="1"/>
+    <col min="38" max="38" width="2.6640625" customWidth="1"/>
+    <col min="39" max="39" width="20.6640625" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" customWidth="1"/>
+    <col min="41" max="41" width="2.6640625" customWidth="1"/>
+    <col min="42" max="42" width="16.6640625" customWidth="1"/>
+    <col min="43" max="43" width="3.6640625" customWidth="1"/>
+    <col min="44" max="44" width="8.33203125" customWidth="1"/>
     <col min="45" max="48" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="112" t="s">
+      <c r="F1" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="112" t="s">
+      <c r="J1" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="112"/>
-      <c r="L1" s="113"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="111"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="116" t="s">
+      <c r="N1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="106" t="s">
+      <c r="R1" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="106" t="s">
+      <c r="V1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="106" t="s">
+      <c r="Z1" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="106" t="s">
+      <c r="AD1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="106"/>
-      <c r="AF1" s="106"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="106" t="s">
+      <c r="AH1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="106"/>
-      <c r="AJ1" s="106"/>
+      <c r="AI1" s="108"/>
+      <c r="AJ1" s="108"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="106" t="s">
+      <c r="AL1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="106"/>
-      <c r="AN1" s="107"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="118"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
       <c r="AR1" s="13"/>
     </row>
-    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="114">
+      <c r="B2" s="112">
         <f>N2-3</f>
         <v>46255</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="115">
+      <c r="F2" s="113">
         <f>N2-2</f>
         <v>46256</v>
       </c>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="115">
+      <c r="J2" s="113">
         <f>N2-1</f>
         <v>46257</v>
       </c>
-      <c r="K2" s="115"/>
-      <c r="L2" s="118"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="116"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="117">
+      <c r="N2" s="115">
         <v>46258</v>
       </c>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="108">
+      <c r="R2" s="104">
         <f>N2+1</f>
         <v>46259</v>
       </c>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="108">
+      <c r="V2" s="104">
         <f>N2+2</f>
         <v>46260</v>
       </c>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
+      <c r="W2" s="104"/>
+      <c r="X2" s="104"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="108">
+      <c r="Z2" s="104">
         <f>N2+3</f>
         <v>46261</v>
       </c>
-      <c r="AA2" s="108"/>
-      <c r="AB2" s="108"/>
+      <c r="AA2" s="104"/>
+      <c r="AB2" s="104"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="108">
+      <c r="AD2" s="104">
         <f>N2+4</f>
         <v>46262</v>
       </c>
-      <c r="AE2" s="108"/>
-      <c r="AF2" s="108"/>
+      <c r="AE2" s="104"/>
+      <c r="AF2" s="104"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="108">
+      <c r="AH2" s="104">
         <f>N2+5</f>
         <v>46263</v>
       </c>
-      <c r="AI2" s="108"/>
-      <c r="AJ2" s="108"/>
+      <c r="AI2" s="104"/>
+      <c r="AJ2" s="104"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="108">
+      <c r="AL2" s="104">
         <f>N2+6</f>
         <v>46264</v>
       </c>
-      <c r="AM2" s="108"/>
-      <c r="AN2" s="109"/>
+      <c r="AM2" s="104"/>
+      <c r="AN2" s="119"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
       <c r="AR2" s="13"/>
     </row>
-    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2296,139 +2299,139 @@
       <c r="AQ3" s="12"/>
       <c r="AR3" s="13"/>
     </row>
-    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="94" t="s">
+      <c r="N4" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="94"/>
-      <c r="V4" s="94"/>
-      <c r="W4" s="94"/>
-      <c r="X4" s="94"/>
-      <c r="Y4" s="94"/>
-      <c r="Z4" s="94"/>
-      <c r="AA4" s="94"/>
-      <c r="AB4" s="94"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="103"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="103"/>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="103"/>
+      <c r="Y4" s="103"/>
+      <c r="Z4" s="103"/>
+      <c r="AA4" s="103"/>
+      <c r="AB4" s="103"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="110"/>
-      <c r="AE4" s="110"/>
-      <c r="AF4" s="110"/>
-      <c r="AG4" s="110"/>
-      <c r="AH4" s="110"/>
-      <c r="AI4" s="110"/>
-      <c r="AJ4" s="110"/>
-      <c r="AK4" s="110"/>
-      <c r="AL4" s="110"/>
-      <c r="AM4" s="110"/>
-      <c r="AN4" s="110"/>
+      <c r="AD4" s="117"/>
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
       <c r="AR4" s="13"/>
     </row>
-    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
-      <c r="S5" s="94"/>
-      <c r="T5" s="94"/>
-      <c r="U5" s="94"/>
-      <c r="V5" s="94"/>
-      <c r="W5" s="94"/>
-      <c r="X5" s="94"/>
-      <c r="Y5" s="94"/>
-      <c r="Z5" s="94"/>
-      <c r="AA5" s="94"/>
-      <c r="AB5" s="94"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103"/>
+      <c r="Y5" s="103"/>
+      <c r="Z5" s="103"/>
+      <c r="AA5" s="103"/>
+      <c r="AB5" s="103"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="110"/>
-      <c r="AE5" s="110"/>
-      <c r="AF5" s="110"/>
-      <c r="AG5" s="110"/>
-      <c r="AH5" s="110"/>
-      <c r="AI5" s="110"/>
-      <c r="AJ5" s="110"/>
-      <c r="AK5" s="110"/>
-      <c r="AL5" s="110"/>
-      <c r="AM5" s="110"/>
-      <c r="AN5" s="110"/>
+      <c r="AD5" s="117"/>
+      <c r="AE5" s="117"/>
+      <c r="AF5" s="117"/>
+      <c r="AG5" s="117"/>
+      <c r="AH5" s="117"/>
+      <c r="AI5" s="117"/>
+      <c r="AJ5" s="117"/>
+      <c r="AK5" s="117"/>
+      <c r="AL5" s="117"/>
+      <c r="AM5" s="117"/>
+      <c r="AN5" s="117"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
-    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="63"/>
-      <c r="C6" s="64"/>
+    <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="78"/>
+      <c r="C6" s="79"/>
       <c r="D6" s="57"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="79"/>
       <c r="H6" s="57"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="79"/>
       <c r="L6" s="57"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="66"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="65"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="66"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="65"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="66"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="65"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
+      <c r="Z6" s="64"/>
+      <c r="AA6" s="65"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="66"/>
+      <c r="AD6" s="64"/>
+      <c r="AE6" s="65"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="65"/>
-      <c r="AI6" s="66"/>
+      <c r="AH6" s="64"/>
+      <c r="AI6" s="65"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="65"/>
-      <c r="AM6" s="66"/>
+      <c r="AL6" s="64"/>
+      <c r="AM6" s="65"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2439,45 +2442,45 @@
       </c>
       <c r="AR6" s="30"/>
     </row>
-    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="82"/>
-      <c r="C7" s="83"/>
+    <row r="7" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
       <c r="D7" s="58"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="84"/>
       <c r="H7" s="58"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="84"/>
       <c r="L7" s="58"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="71"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="71"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="70"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="70"/>
-      <c r="W7" s="71"/>
+      <c r="V7" s="69"/>
+      <c r="W7" s="70"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="70"/>
-      <c r="AA7" s="71"/>
+      <c r="Z7" s="69"/>
+      <c r="AA7" s="70"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="70"/>
-      <c r="AE7" s="71"/>
+      <c r="AD7" s="69"/>
+      <c r="AE7" s="70"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="70"/>
-      <c r="AI7" s="71"/>
+      <c r="AH7" s="69"/>
+      <c r="AI7" s="70"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="70"/>
-      <c r="AM7" s="71"/>
+      <c r="AL7" s="69"/>
+      <c r="AM7" s="70"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2488,46 +2491,46 @@
       </c>
       <c r="AR7" s="30"/>
     </row>
-    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="76"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="78"/>
+    <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="68"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="78"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="68"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="78"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="68"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="76"/>
-      <c r="O8" s="77"/>
-      <c r="P8" s="78"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="67"/>
+      <c r="P8" s="68"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="76"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="78"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="68"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="76"/>
-      <c r="W8" s="77"/>
-      <c r="X8" s="78"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="68"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="76"/>
-      <c r="AA8" s="77"/>
-      <c r="AB8" s="78"/>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="68"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="76"/>
-      <c r="AE8" s="77"/>
-      <c r="AF8" s="78"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="68"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="76"/>
-      <c r="AI8" s="77"/>
-      <c r="AJ8" s="78"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="68"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="76"/>
-      <c r="AM8" s="77"/>
-      <c r="AN8" s="78"/>
+      <c r="AL8" s="66"/>
+      <c r="AM8" s="67"/>
+      <c r="AN8" s="68"/>
       <c r="AP8" s="59" t="s">
         <v>16</v>
       </c>
@@ -2539,46 +2542,46 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="73"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="75"/>
+    <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="72"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="74"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="74"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="75"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="74"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="75"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="74"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="73"/>
-      <c r="S9" s="74"/>
-      <c r="T9" s="75"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="73"/>
+      <c r="T9" s="74"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="73"/>
-      <c r="W9" s="74"/>
-      <c r="X9" s="75"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="74"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="73"/>
-      <c r="AA9" s="74"/>
-      <c r="AB9" s="75"/>
+      <c r="Z9" s="72"/>
+      <c r="AA9" s="73"/>
+      <c r="AB9" s="74"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="73"/>
-      <c r="AE9" s="74"/>
-      <c r="AF9" s="75"/>
+      <c r="AD9" s="72"/>
+      <c r="AE9" s="73"/>
+      <c r="AF9" s="74"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="73"/>
-      <c r="AI9" s="74"/>
-      <c r="AJ9" s="75"/>
+      <c r="AH9" s="72"/>
+      <c r="AI9" s="73"/>
+      <c r="AJ9" s="74"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="73"/>
-      <c r="AM9" s="74"/>
-      <c r="AN9" s="75"/>
+      <c r="AL9" s="72"/>
+      <c r="AM9" s="73"/>
+      <c r="AN9" s="74"/>
       <c r="AP9" s="59" t="s">
         <v>11</v>
       </c>
@@ -2590,46 +2593,46 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="95"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="97"/>
+    <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="105"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="107"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="97"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="107"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="97"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="107"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="95"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="97"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="107"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="95"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="97"/>
+      <c r="R10" s="105"/>
+      <c r="S10" s="106"/>
+      <c r="T10" s="107"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="95"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="97"/>
+      <c r="V10" s="105"/>
+      <c r="W10" s="106"/>
+      <c r="X10" s="107"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="95"/>
-      <c r="AA10" s="96"/>
-      <c r="AB10" s="97"/>
+      <c r="Z10" s="105"/>
+      <c r="AA10" s="106"/>
+      <c r="AB10" s="107"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="95"/>
-      <c r="AE10" s="96"/>
-      <c r="AF10" s="97"/>
+      <c r="AD10" s="105"/>
+      <c r="AE10" s="106"/>
+      <c r="AF10" s="107"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="96"/>
-      <c r="AJ10" s="97"/>
+      <c r="AH10" s="105"/>
+      <c r="AI10" s="106"/>
+      <c r="AJ10" s="107"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="95"/>
-      <c r="AM10" s="96"/>
-      <c r="AN10" s="97"/>
+      <c r="AL10" s="105"/>
+      <c r="AM10" s="106"/>
+      <c r="AN10" s="107"/>
       <c r="AP10" s="59" t="s">
         <v>8</v>
       </c>
@@ -2641,7 +2644,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -2690,53 +2693,53 @@
       </c>
       <c r="AR11" s="30"/>
     </row>
-    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="63"/>
-      <c r="C12" s="64"/>
+    <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="78"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="57"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="63" t="s">
+      <c r="F12" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="79"/>
       <c r="H12" s="57" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="64"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="79"/>
       <c r="L12" s="57"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="65"/>
-      <c r="S12" s="66"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="65"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="65"/>
-      <c r="W12" s="66"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="65"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="65"/>
-      <c r="AA12" s="66"/>
+      <c r="Z12" s="64"/>
+      <c r="AA12" s="65"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="65"/>
-      <c r="AE12" s="66"/>
+      <c r="AD12" s="64"/>
+      <c r="AE12" s="65"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="65" t="s">
+      <c r="AH12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="66"/>
+      <c r="AI12" s="65"/>
       <c r="AJ12" s="34" t="s">
         <v>46</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="65"/>
-      <c r="AM12" s="66"/>
+      <c r="AL12" s="64"/>
+      <c r="AM12" s="65"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
@@ -2747,46 +2750,46 @@
       </c>
       <c r="AR12" s="30"/>
     </row>
-    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="82"/>
-      <c r="C13" s="83"/>
+    <row r="13" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="83"/>
+      <c r="C13" s="84"/>
       <c r="D13" s="58"/>
       <c r="E13" s="38"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="81"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="81"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="82"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="67"/>
-      <c r="O13" s="68"/>
-      <c r="P13" s="69"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="76"/>
+      <c r="P13" s="77"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="67"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="69"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="76"/>
+      <c r="T13" s="77"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="67"/>
-      <c r="W13" s="68"/>
-      <c r="X13" s="69"/>
+      <c r="V13" s="75"/>
+      <c r="W13" s="76"/>
+      <c r="X13" s="77"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="70"/>
-      <c r="AA13" s="71"/>
+      <c r="Z13" s="69"/>
+      <c r="AA13" s="70"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="70"/>
-      <c r="AE13" s="71"/>
+      <c r="AD13" s="69"/>
+      <c r="AE13" s="70"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="67"/>
-      <c r="AI13" s="68"/>
-      <c r="AJ13" s="69"/>
+      <c r="AH13" s="75"/>
+      <c r="AI13" s="76"/>
+      <c r="AJ13" s="77"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="67"/>
-      <c r="AM13" s="68"/>
-      <c r="AN13" s="69"/>
+      <c r="AL13" s="75"/>
+      <c r="AM13" s="76"/>
+      <c r="AN13" s="77"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
@@ -2796,50 +2799,50 @@
       </c>
       <c r="AR13" s="30"/>
     </row>
-    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="76"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="78"/>
+    <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="66"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="68"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="78"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="78"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="68"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="76"/>
-      <c r="O14" s="77"/>
-      <c r="P14" s="78"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="68"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="76"/>
-      <c r="S14" s="77"/>
-      <c r="T14" s="78"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="68"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="76"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="78"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="67"/>
+      <c r="X14" s="68"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="76"/>
-      <c r="AA14" s="77"/>
-      <c r="AB14" s="78"/>
+      <c r="Z14" s="66"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="68"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="76"/>
-      <c r="AE14" s="77"/>
-      <c r="AF14" s="78"/>
+      <c r="AD14" s="66"/>
+      <c r="AE14" s="67"/>
+      <c r="AF14" s="68"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="76" t="s">
+      <c r="AH14" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="AI14" s="77"/>
-      <c r="AJ14" s="78"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="68"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="76"/>
-      <c r="AM14" s="77"/>
-      <c r="AN14" s="78"/>
+      <c r="AL14" s="66"/>
+      <c r="AM14" s="67"/>
+      <c r="AN14" s="68"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -2849,50 +2852,50 @@
       </c>
       <c r="AR14" s="30"/>
     </row>
-    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="73"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="75"/>
+    <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="72"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="74"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="74"/>
-      <c r="H15" s="75"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="75"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="74"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="75"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="74"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="73"/>
-      <c r="S15" s="74"/>
-      <c r="T15" s="75"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="73"/>
+      <c r="T15" s="74"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="73"/>
-      <c r="W15" s="74"/>
-      <c r="X15" s="75"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="73"/>
+      <c r="X15" s="74"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="73"/>
-      <c r="AA15" s="74"/>
-      <c r="AB15" s="75"/>
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="73"/>
+      <c r="AB15" s="74"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="73"/>
-      <c r="AE15" s="74"/>
-      <c r="AF15" s="75"/>
+      <c r="AD15" s="72"/>
+      <c r="AE15" s="73"/>
+      <c r="AF15" s="74"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="73" t="s">
+      <c r="AH15" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="AI15" s="74"/>
-      <c r="AJ15" s="75"/>
+      <c r="AI15" s="73"/>
+      <c r="AJ15" s="74"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="73"/>
-      <c r="AM15" s="74"/>
-      <c r="AN15" s="75"/>
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="73"/>
+      <c r="AN15" s="74"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2902,46 +2905,46 @@
       </c>
       <c r="AR15" s="30"/>
     </row>
-    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="95"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="97"/>
+    <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="105"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="107"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="97"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="107"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="97"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="107"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="97"/>
+      <c r="N16" s="105"/>
+      <c r="O16" s="106"/>
+      <c r="P16" s="107"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="95"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="97"/>
+      <c r="R16" s="105"/>
+      <c r="S16" s="106"/>
+      <c r="T16" s="107"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="95"/>
-      <c r="W16" s="96"/>
-      <c r="X16" s="97"/>
+      <c r="V16" s="105"/>
+      <c r="W16" s="106"/>
+      <c r="X16" s="107"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="95"/>
-      <c r="AA16" s="96"/>
-      <c r="AB16" s="97"/>
+      <c r="Z16" s="105"/>
+      <c r="AA16" s="106"/>
+      <c r="AB16" s="107"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="95"/>
-      <c r="AE16" s="96"/>
-      <c r="AF16" s="97"/>
+      <c r="AD16" s="105"/>
+      <c r="AE16" s="106"/>
+      <c r="AF16" s="107"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="95"/>
-      <c r="AI16" s="96"/>
-      <c r="AJ16" s="97"/>
+      <c r="AH16" s="105"/>
+      <c r="AI16" s="106"/>
+      <c r="AJ16" s="107"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="95"/>
-      <c r="AM16" s="96"/>
-      <c r="AN16" s="97"/>
+      <c r="AL16" s="105"/>
+      <c r="AM16" s="106"/>
+      <c r="AN16" s="107"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -2951,7 +2954,7 @@
       </c>
       <c r="AR16" s="30"/>
     </row>
-    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3000,7 +3003,7 @@
       </c>
       <c r="AR17" s="30"/>
     </row>
-    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
@@ -3013,23 +3016,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="94" t="s">
+      <c r="N18" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="O18" s="94"/>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="94"/>
-      <c r="S18" s="94"/>
-      <c r="T18" s="94"/>
-      <c r="U18" s="94"/>
-      <c r="V18" s="94"/>
-      <c r="W18" s="94"/>
-      <c r="X18" s="94"/>
-      <c r="Y18" s="94"/>
-      <c r="Z18" s="94"/>
-      <c r="AA18" s="94"/>
-      <c r="AB18" s="94"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="103"/>
+      <c r="S18" s="103"/>
+      <c r="T18" s="103"/>
+      <c r="U18" s="103"/>
+      <c r="V18" s="103"/>
+      <c r="W18" s="103"/>
+      <c r="X18" s="103"/>
+      <c r="Y18" s="103"/>
+      <c r="Z18" s="103"/>
+      <c r="AA18" s="103"/>
+      <c r="AB18" s="103"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3051,7 +3054,7 @@
       </c>
       <c r="AR18" s="30"/>
     </row>
-    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
       <c r="D19" s="33"/>
@@ -3064,21 +3067,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="94"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
-      <c r="S19" s="94"/>
-      <c r="T19" s="94"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="94"/>
-      <c r="W19" s="94"/>
-      <c r="X19" s="94"/>
-      <c r="Y19" s="94"/>
-      <c r="Z19" s="94"/>
-      <c r="AA19" s="94"/>
-      <c r="AB19" s="94"/>
+      <c r="N19" s="103"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="103"/>
+      <c r="Q19" s="103"/>
+      <c r="R19" s="103"/>
+      <c r="S19" s="103"/>
+      <c r="T19" s="103"/>
+      <c r="U19" s="103"/>
+      <c r="V19" s="103"/>
+      <c r="W19" s="103"/>
+      <c r="X19" s="103"/>
+      <c r="Y19" s="103"/>
+      <c r="Z19" s="103"/>
+      <c r="AA19" s="103"/>
+      <c r="AB19" s="103"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3100,45 +3103,45 @@
       </c>
       <c r="AR19" s="30"/>
     </row>
-    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="63"/>
-      <c r="C20" s="64"/>
+    <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="78"/>
+      <c r="C20" s="79"/>
       <c r="D20" s="57"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="79"/>
       <c r="H20" s="57"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="64"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="79"/>
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="66"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="65"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="99"/>
+      <c r="R20" s="101"/>
+      <c r="S20" s="102"/>
       <c r="T20" s="55"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="98"/>
-      <c r="W20" s="99"/>
+      <c r="V20" s="101"/>
+      <c r="W20" s="102"/>
       <c r="X20" s="55"/>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="98"/>
-      <c r="AA20" s="99"/>
+      <c r="Z20" s="101"/>
+      <c r="AA20" s="102"/>
       <c r="AB20" s="55"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="65"/>
-      <c r="AE20" s="66"/>
+      <c r="AD20" s="64"/>
+      <c r="AE20" s="65"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="65"/>
-      <c r="AI20" s="66"/>
+      <c r="AH20" s="64"/>
+      <c r="AI20" s="65"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="65"/>
-      <c r="AM20" s="66"/>
+      <c r="AL20" s="64"/>
+      <c r="AM20" s="65"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3149,45 +3152,45 @@
       </c>
       <c r="AR20" s="30"/>
     </row>
-    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="82"/>
-      <c r="C21" s="83"/>
+    <row r="21" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="83"/>
+      <c r="C21" s="84"/>
       <c r="D21" s="58"/>
       <c r="E21" s="38"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="84"/>
       <c r="H21" s="58"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="83"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="84"/>
       <c r="L21" s="58"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="71"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="70"/>
-      <c r="S21" s="71"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="70"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="104"/>
-      <c r="W21" s="105"/>
+      <c r="V21" s="120"/>
+      <c r="W21" s="121"/>
       <c r="X21" s="56"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="104"/>
-      <c r="AA21" s="105"/>
+      <c r="Z21" s="120"/>
+      <c r="AA21" s="121"/>
       <c r="AB21" s="56"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="70"/>
-      <c r="AE21" s="71"/>
+      <c r="AD21" s="69"/>
+      <c r="AE21" s="70"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="70"/>
-      <c r="AI21" s="71"/>
+      <c r="AH21" s="69"/>
+      <c r="AI21" s="70"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="70"/>
-      <c r="AM21" s="71"/>
+      <c r="AL21" s="69"/>
+      <c r="AM21" s="70"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3198,45 +3201,45 @@
       </c>
       <c r="AR21" s="30"/>
     </row>
-    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="123"/>
-      <c r="C22" s="124"/>
+    <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="124"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="91"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="123"/>
-      <c r="K22" s="124"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="91"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="120"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="95"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="119"/>
-      <c r="S22" s="120"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="95"/>
       <c r="T22" s="41"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="119"/>
-      <c r="W22" s="120"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="95"/>
       <c r="X22" s="41"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="119"/>
-      <c r="AA22" s="120"/>
+      <c r="Z22" s="94"/>
+      <c r="AA22" s="95"/>
       <c r="AB22" s="41"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="119"/>
-      <c r="AE22" s="120"/>
+      <c r="AD22" s="94"/>
+      <c r="AE22" s="95"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="119"/>
-      <c r="AI22" s="120"/>
+      <c r="AH22" s="94"/>
+      <c r="AI22" s="95"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="119"/>
-      <c r="AM22" s="120"/>
+      <c r="AL22" s="94"/>
+      <c r="AM22" s="95"/>
       <c r="AN22" s="41"/>
       <c r="AP22" s="59" t="s">
         <v>15</v>
@@ -3249,45 +3252,45 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="121"/>
-      <c r="C23" s="122"/>
+    <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="92"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="45"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="122"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="93"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="122"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="93"/>
       <c r="L23" s="45"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="121"/>
-      <c r="O23" s="122"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="93"/>
       <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="121"/>
-      <c r="S23" s="122"/>
+      <c r="R23" s="92"/>
+      <c r="S23" s="93"/>
       <c r="T23" s="45"/>
       <c r="U23" s="43"/>
-      <c r="V23" s="121"/>
-      <c r="W23" s="122"/>
+      <c r="V23" s="92"/>
+      <c r="W23" s="93"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="121"/>
-      <c r="AA23" s="122"/>
+      <c r="Z23" s="92"/>
+      <c r="AA23" s="93"/>
       <c r="AB23" s="45"/>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="121"/>
-      <c r="AE23" s="122"/>
+      <c r="AD23" s="92"/>
+      <c r="AE23" s="93"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="121"/>
-      <c r="AI23" s="122"/>
+      <c r="AH23" s="92"/>
+      <c r="AI23" s="93"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="121"/>
-      <c r="AM23" s="122"/>
+      <c r="AL23" s="92"/>
+      <c r="AM23" s="93"/>
       <c r="AN23" s="45"/>
       <c r="AP23" s="46" t="s">
         <v>20</v>
@@ -3298,45 +3301,45 @@
       </c>
       <c r="AR23" s="30"/>
     </row>
-    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="102"/>
-      <c r="C24" s="103"/>
+    <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="86"/>
+      <c r="C24" s="87"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="103"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="87"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="103"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="87"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="103"/>
+      <c r="N24" s="86"/>
+      <c r="O24" s="87"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="102"/>
-      <c r="S24" s="103"/>
+      <c r="R24" s="86"/>
+      <c r="S24" s="87"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="102"/>
-      <c r="W24" s="103"/>
+      <c r="V24" s="86"/>
+      <c r="W24" s="87"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="102"/>
-      <c r="AA24" s="103"/>
+      <c r="Z24" s="86"/>
+      <c r="AA24" s="87"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="102"/>
-      <c r="AE24" s="103"/>
+      <c r="AD24" s="86"/>
+      <c r="AE24" s="87"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="102"/>
-      <c r="AI24" s="103"/>
+      <c r="AH24" s="86"/>
+      <c r="AI24" s="87"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="102"/>
-      <c r="AM24" s="103"/>
+      <c r="AL24" s="86"/>
+      <c r="AM24" s="87"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
@@ -3347,45 +3350,45 @@
       </c>
       <c r="AR24" s="30"/>
     </row>
-    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="102"/>
-      <c r="C25" s="103"/>
+    <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="86"/>
+      <c r="C25" s="87"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="87"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="103"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="87"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="103"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="87"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="102"/>
-      <c r="S25" s="103"/>
+      <c r="R25" s="86"/>
+      <c r="S25" s="87"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="102"/>
-      <c r="W25" s="103"/>
+      <c r="V25" s="86"/>
+      <c r="W25" s="87"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="102"/>
-      <c r="AA25" s="103"/>
+      <c r="Z25" s="86"/>
+      <c r="AA25" s="87"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="102"/>
-      <c r="AE25" s="103"/>
+      <c r="AD25" s="86"/>
+      <c r="AE25" s="87"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="102"/>
-      <c r="AI25" s="103"/>
+      <c r="AH25" s="86"/>
+      <c r="AI25" s="87"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="102"/>
-      <c r="AM25" s="103"/>
+      <c r="AL25" s="86"/>
+      <c r="AM25" s="87"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="59" t="s">
         <v>21</v>
@@ -3398,45 +3401,45 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="102"/>
-      <c r="C26" s="103"/>
+    <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="86"/>
+      <c r="C26" s="87"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="103"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="87"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="103"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="87"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="103"/>
+      <c r="N26" s="86"/>
+      <c r="O26" s="87"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="102"/>
-      <c r="S26" s="103"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="87"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="102"/>
-      <c r="W26" s="103"/>
+      <c r="V26" s="86"/>
+      <c r="W26" s="87"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="102"/>
-      <c r="AA26" s="103"/>
+      <c r="Z26" s="86"/>
+      <c r="AA26" s="87"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="102"/>
-      <c r="AE26" s="103"/>
+      <c r="AD26" s="86"/>
+      <c r="AE26" s="87"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="102"/>
-      <c r="AI26" s="103"/>
+      <c r="AH26" s="86"/>
+      <c r="AI26" s="87"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="102"/>
-      <c r="AM26" s="103"/>
+      <c r="AL26" s="86"/>
+      <c r="AM26" s="87"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
@@ -3447,45 +3450,45 @@
       </c>
       <c r="AR26" s="30"/>
     </row>
-    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="100"/>
-      <c r="C27" s="101"/>
+    <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="88"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="101"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="101"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="89"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="100"/>
-      <c r="O27" s="101"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="89"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="100"/>
-      <c r="S27" s="101"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="89"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="100"/>
-      <c r="W27" s="101"/>
+      <c r="V27" s="88"/>
+      <c r="W27" s="89"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="100"/>
-      <c r="AA27" s="101"/>
+      <c r="Z27" s="88"/>
+      <c r="AA27" s="89"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="100"/>
-      <c r="AE27" s="101"/>
+      <c r="AD27" s="88"/>
+      <c r="AE27" s="89"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="100"/>
-      <c r="AI27" s="101"/>
+      <c r="AH27" s="88"/>
+      <c r="AI27" s="89"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="100"/>
-      <c r="AM27" s="101"/>
+      <c r="AL27" s="88"/>
+      <c r="AM27" s="89"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3496,7 +3499,7 @@
       </c>
       <c r="AR27" s="30"/>
     </row>
-    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
@@ -3545,7 +3548,7 @@
       </c>
       <c r="AR28" s="30"/>
     </row>
-    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
@@ -3558,23 +3561,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="94" t="s">
+      <c r="N29" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="94"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="94"/>
-      <c r="R29" s="94"/>
-      <c r="S29" s="94"/>
-      <c r="T29" s="94"/>
-      <c r="U29" s="94"/>
-      <c r="V29" s="94"/>
-      <c r="W29" s="94"/>
-      <c r="X29" s="94"/>
-      <c r="Y29" s="94"/>
-      <c r="Z29" s="94"/>
-      <c r="AA29" s="94"/>
-      <c r="AB29" s="94"/>
+      <c r="O29" s="103"/>
+      <c r="P29" s="103"/>
+      <c r="Q29" s="103"/>
+      <c r="R29" s="103"/>
+      <c r="S29" s="103"/>
+      <c r="T29" s="103"/>
+      <c r="U29" s="103"/>
+      <c r="V29" s="103"/>
+      <c r="W29" s="103"/>
+      <c r="X29" s="103"/>
+      <c r="Y29" s="103"/>
+      <c r="Z29" s="103"/>
+      <c r="AA29" s="103"/>
+      <c r="AB29" s="103"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3596,7 +3599,7 @@
       </c>
       <c r="AR29" s="30"/>
     </row>
-    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
@@ -3609,21 +3612,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="94"/>
-      <c r="O30" s="94"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="94"/>
-      <c r="S30" s="94"/>
-      <c r="T30" s="94"/>
-      <c r="U30" s="94"/>
-      <c r="V30" s="94"/>
-      <c r="W30" s="94"/>
-      <c r="X30" s="94"/>
-      <c r="Y30" s="94"/>
-      <c r="Z30" s="94"/>
-      <c r="AA30" s="94"/>
-      <c r="AB30" s="94"/>
+      <c r="N30" s="103"/>
+      <c r="O30" s="103"/>
+      <c r="P30" s="103"/>
+      <c r="Q30" s="103"/>
+      <c r="R30" s="103"/>
+      <c r="S30" s="103"/>
+      <c r="T30" s="103"/>
+      <c r="U30" s="103"/>
+      <c r="V30" s="103"/>
+      <c r="W30" s="103"/>
+      <c r="X30" s="103"/>
+      <c r="Y30" s="103"/>
+      <c r="Z30" s="103"/>
+      <c r="AA30" s="103"/>
+      <c r="AB30" s="103"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3647,446 +3650,446 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="63" t="s">
+    <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="64"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="57"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="63" t="s">
+      <c r="F31" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="64"/>
+      <c r="G31" s="79"/>
       <c r="H31" s="57"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="63" t="s">
+      <c r="J31" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="K31" s="64"/>
+      <c r="K31" s="79"/>
       <c r="L31" s="57"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="65" t="s">
+      <c r="N31" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="O31" s="66"/>
+      <c r="O31" s="65"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="65" t="s">
+      <c r="R31" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="S31" s="66"/>
+      <c r="S31" s="65"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="65" t="s">
+      <c r="V31" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="W31" s="66"/>
+      <c r="W31" s="65"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="65" t="s">
+      <c r="Z31" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="AA31" s="66"/>
+      <c r="AA31" s="65"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="65" t="s">
+      <c r="AD31" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="AE31" s="66"/>
+      <c r="AE31" s="65"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="65" t="s">
+      <c r="AH31" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="AI31" s="66"/>
+      <c r="AI31" s="65"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="65" t="s">
+      <c r="AL31" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="AM31" s="66"/>
+      <c r="AM31" s="65"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
       <c r="AR31" s="30"/>
     </row>
-    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="79" t="s">
+    <row r="32" spans="2:44" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="80"/>
-      <c r="D32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="82"/>
       <c r="E32" s="36"/>
-      <c r="F32" s="79" t="s">
+      <c r="F32" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="G32" s="80"/>
-      <c r="H32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="82"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="79" t="s">
+      <c r="J32" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="K32" s="80"/>
-      <c r="L32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="82"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="67" t="s">
+      <c r="N32" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="O32" s="68"/>
-      <c r="P32" s="69"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="77"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="67" t="s">
+      <c r="R32" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="S32" s="68"/>
-      <c r="T32" s="69"/>
+      <c r="S32" s="76"/>
+      <c r="T32" s="77"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="67" t="s">
+      <c r="V32" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="W32" s="68"/>
-      <c r="X32" s="69"/>
+      <c r="W32" s="76"/>
+      <c r="X32" s="77"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="67" t="s">
+      <c r="Z32" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="AA32" s="68"/>
-      <c r="AB32" s="69"/>
+      <c r="AA32" s="76"/>
+      <c r="AB32" s="77"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="67" t="s">
+      <c r="AD32" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="AE32" s="68"/>
-      <c r="AF32" s="69"/>
+      <c r="AE32" s="76"/>
+      <c r="AF32" s="77"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="67" t="s">
+      <c r="AH32" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="AI32" s="68"/>
-      <c r="AJ32" s="69"/>
+      <c r="AI32" s="76"/>
+      <c r="AJ32" s="77"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="67" t="s">
+      <c r="AL32" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="AM32" s="68"/>
-      <c r="AN32" s="69"/>
+      <c r="AM32" s="76"/>
+      <c r="AN32" s="77"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
     </row>
-    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="82" t="s">
+    <row r="33" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="83"/>
-      <c r="D33" s="84"/>
+      <c r="C33" s="84"/>
+      <c r="D33" s="85"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="82" t="s">
+      <c r="F33" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="83"/>
-      <c r="H33" s="84"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="85"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="82" t="s">
+      <c r="J33" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="83"/>
-      <c r="L33" s="84"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="85"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="70" t="s">
+      <c r="N33" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="O33" s="71"/>
-      <c r="P33" s="72"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="71"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="70" t="s">
+      <c r="R33" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="S33" s="71"/>
-      <c r="T33" s="72"/>
+      <c r="S33" s="70"/>
+      <c r="T33" s="71"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="70" t="s">
+      <c r="V33" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="W33" s="71"/>
-      <c r="X33" s="72"/>
+      <c r="W33" s="70"/>
+      <c r="X33" s="71"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="70" t="s">
+      <c r="Z33" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="AA33" s="71"/>
-      <c r="AB33" s="72"/>
+      <c r="AA33" s="70"/>
+      <c r="AB33" s="71"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="70" t="s">
+      <c r="AD33" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="AE33" s="71"/>
-      <c r="AF33" s="72"/>
+      <c r="AE33" s="70"/>
+      <c r="AF33" s="71"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="70" t="s">
+      <c r="AH33" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="AI33" s="71"/>
-      <c r="AJ33" s="72"/>
+      <c r="AI33" s="70"/>
+      <c r="AJ33" s="71"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="70" t="s">
+      <c r="AL33" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="AM33" s="71"/>
-      <c r="AN33" s="72"/>
+      <c r="AM33" s="70"/>
+      <c r="AN33" s="71"/>
       <c r="AR33" s="13"/>
     </row>
-    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="73" t="s">
+      <c r="B34" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="75"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="74"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="73" t="s">
+      <c r="F34" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="74"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="73" t="s">
+      <c r="J34" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="74"/>
-      <c r="L34" s="75"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="74"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="73" t="s">
+      <c r="N34" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="O34" s="74"/>
-      <c r="P34" s="75"/>
+      <c r="O34" s="73"/>
+      <c r="P34" s="74"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="73" t="s">
+      <c r="R34" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="S34" s="74"/>
-      <c r="T34" s="75"/>
+      <c r="S34" s="73"/>
+      <c r="T34" s="74"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="73" t="s">
+      <c r="V34" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="W34" s="74"/>
-      <c r="X34" s="75"/>
+      <c r="W34" s="73"/>
+      <c r="X34" s="74"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="73" t="s">
+      <c r="Z34" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="AA34" s="74"/>
-      <c r="AB34" s="75"/>
+      <c r="AA34" s="73"/>
+      <c r="AB34" s="74"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="73" t="s">
+      <c r="AD34" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="AE34" s="74"/>
-      <c r="AF34" s="75"/>
+      <c r="AE34" s="73"/>
+      <c r="AF34" s="74"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="73" t="s">
+      <c r="AH34" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="AI34" s="74"/>
-      <c r="AJ34" s="75"/>
+      <c r="AI34" s="73"/>
+      <c r="AJ34" s="74"/>
       <c r="AK34" s="32"/>
-      <c r="AL34" s="73" t="s">
+      <c r="AL34" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="AM34" s="74"/>
-      <c r="AN34" s="75"/>
+      <c r="AM34" s="73"/>
+      <c r="AN34" s="74"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
       <c r="AR34" s="13"/>
     </row>
-    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="73" t="s">
+      <c r="B35" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="75"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="74"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="73" t="s">
+      <c r="F35" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="74"/>
-      <c r="H35" s="75"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="74"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="73" t="s">
+      <c r="J35" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="K35" s="74"/>
-      <c r="L35" s="75"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="74"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="73" t="s">
+      <c r="N35" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="O35" s="74"/>
-      <c r="P35" s="75"/>
+      <c r="O35" s="73"/>
+      <c r="P35" s="74"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="73" t="s">
+      <c r="R35" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="S35" s="74"/>
-      <c r="T35" s="75"/>
+      <c r="S35" s="73"/>
+      <c r="T35" s="74"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="73" t="s">
+      <c r="V35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="74"/>
-      <c r="X35" s="75"/>
+      <c r="W35" s="73"/>
+      <c r="X35" s="74"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="73" t="s">
+      <c r="Z35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="74"/>
-      <c r="AB35" s="75"/>
+      <c r="AA35" s="73"/>
+      <c r="AB35" s="74"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="73" t="s">
+      <c r="AD35" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="AE35" s="74"/>
-      <c r="AF35" s="75"/>
+      <c r="AE35" s="73"/>
+      <c r="AF35" s="74"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="73" t="s">
+      <c r="AH35" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="AI35" s="74"/>
-      <c r="AJ35" s="75"/>
+      <c r="AI35" s="73"/>
+      <c r="AJ35" s="74"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="73" t="s">
+      <c r="AL35" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="AM35" s="74"/>
-      <c r="AN35" s="75"/>
+      <c r="AM35" s="73"/>
+      <c r="AN35" s="74"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
-    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="73" t="s">
+      <c r="B36" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="74"/>
-      <c r="D36" s="75"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="74"/>
       <c r="E36" s="35"/>
-      <c r="F36" s="73" t="s">
+      <c r="F36" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="74"/>
-      <c r="H36" s="75"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="74"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="73" t="s">
+      <c r="J36" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="K36" s="74"/>
-      <c r="L36" s="75"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="74"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="73" t="s">
+      <c r="N36" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="O36" s="74"/>
-      <c r="P36" s="75"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="74"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="73"/>
-      <c r="S36" s="74"/>
-      <c r="T36" s="75"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="73"/>
+      <c r="T36" s="74"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="73" t="s">
+      <c r="V36" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="W36" s="74"/>
-      <c r="X36" s="75"/>
+      <c r="W36" s="73"/>
+      <c r="X36" s="74"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="73"/>
-      <c r="AA36" s="74"/>
-      <c r="AB36" s="75"/>
+      <c r="Z36" s="72"/>
+      <c r="AA36" s="73"/>
+      <c r="AB36" s="74"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="73" t="s">
+      <c r="AD36" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="AE36" s="74"/>
-      <c r="AF36" s="75"/>
+      <c r="AE36" s="73"/>
+      <c r="AF36" s="74"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="73"/>
-      <c r="AI36" s="74"/>
-      <c r="AJ36" s="75"/>
+      <c r="AH36" s="72"/>
+      <c r="AI36" s="73"/>
+      <c r="AJ36" s="74"/>
       <c r="AK36" s="35"/>
-      <c r="AL36" s="73"/>
-      <c r="AM36" s="74"/>
-      <c r="AN36" s="75"/>
+      <c r="AL36" s="72"/>
+      <c r="AM36" s="73"/>
+      <c r="AN36" s="74"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
       <c r="AR36" s="13"/>
     </row>
-    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="61"/>
-      <c r="D37" s="62"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="63"/>
       <c r="E37" s="50"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="62"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="62"/>
+      <c r="H37" s="63"/>
       <c r="I37" s="32"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="62"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="60" t="s">
+      <c r="N37" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="O37" s="61"/>
-      <c r="P37" s="62"/>
+      <c r="O37" s="62"/>
+      <c r="P37" s="63"/>
       <c r="Q37" s="36"/>
-      <c r="R37" s="60" t="s">
+      <c r="R37" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="S37" s="61"/>
-      <c r="T37" s="62"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="63"/>
       <c r="U37" s="50"/>
-      <c r="V37" s="60" t="s">
+      <c r="V37" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="W37" s="61"/>
-      <c r="X37" s="62"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="63"/>
       <c r="Y37" s="32"/>
-      <c r="Z37" s="60" t="s">
+      <c r="Z37" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="AA37" s="61"/>
-      <c r="AB37" s="62"/>
+      <c r="AA37" s="62"/>
+      <c r="AB37" s="63"/>
       <c r="AC37" s="36"/>
-      <c r="AD37" s="60" t="s">
+      <c r="AD37" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="AE37" s="61"/>
-      <c r="AF37" s="62"/>
+      <c r="AE37" s="62"/>
+      <c r="AF37" s="63"/>
       <c r="AG37" s="50"/>
-      <c r="AH37" s="60"/>
-      <c r="AI37" s="61"/>
-      <c r="AJ37" s="62"/>
+      <c r="AH37" s="61"/>
+      <c r="AI37" s="62"/>
+      <c r="AJ37" s="63"/>
       <c r="AK37" s="32"/>
-      <c r="AL37" s="85" t="s">
+      <c r="AL37" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="AM37" s="86"/>
-      <c r="AN37" s="87"/>
+      <c r="AM37" s="129"/>
+      <c r="AN37" s="130"/>
       <c r="AO37" s="31"/>
       <c r="AP37" s="22"/>
       <c r="AQ37" s="31"/>
       <c r="AR37" s="13"/>
     </row>
-    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="35"/>
       <c r="C38" s="35"/>
@@ -4132,277 +4135,277 @@
       <c r="AQ38" s="31"/>
       <c r="AR38" s="13"/>
     </row>
-    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="64"/>
+      <c r="C39" s="79"/>
       <c r="D39" s="57"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="64"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="79"/>
       <c r="H39" s="57"/>
       <c r="I39" s="43"/>
-      <c r="J39" s="63" t="s">
+      <c r="J39" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="K39" s="64"/>
+      <c r="K39" s="79"/>
       <c r="L39" s="57"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="65" t="s">
+      <c r="N39" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="O39" s="66"/>
+      <c r="O39" s="65"/>
       <c r="P39" s="34"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="66"/>
+      <c r="R39" s="64"/>
+      <c r="S39" s="65"/>
       <c r="T39" s="34"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="65" t="s">
+      <c r="V39" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="W39" s="66"/>
+      <c r="W39" s="65"/>
       <c r="X39" s="34"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="65"/>
-      <c r="AA39" s="66"/>
+      <c r="Z39" s="64"/>
+      <c r="AA39" s="65"/>
       <c r="AB39" s="34"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="65" t="s">
+      <c r="AD39" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="AE39" s="66"/>
+      <c r="AE39" s="65"/>
       <c r="AF39" s="34"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="65"/>
-      <c r="AI39" s="66"/>
+      <c r="AH39" s="64"/>
+      <c r="AI39" s="65"/>
       <c r="AJ39" s="34"/>
       <c r="AK39" s="43"/>
-      <c r="AL39" s="65"/>
-      <c r="AM39" s="66"/>
+      <c r="AL39" s="64"/>
+      <c r="AM39" s="65"/>
       <c r="AN39" s="34"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
       <c r="AQ39" s="31"/>
       <c r="AR39" s="13"/>
     </row>
-    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
-      <c r="B40" s="79" t="s">
+      <c r="B40" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="80"/>
-      <c r="D40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="82"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="81"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="82"/>
       <c r="I40" s="37"/>
-      <c r="J40" s="79" t="s">
+      <c r="J40" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="K40" s="80"/>
-      <c r="L40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="82"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="67" t="s">
+      <c r="N40" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="O40" s="68"/>
-      <c r="P40" s="69"/>
+      <c r="O40" s="76"/>
+      <c r="P40" s="77"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="68"/>
-      <c r="T40" s="69"/>
+      <c r="R40" s="75"/>
+      <c r="S40" s="76"/>
+      <c r="T40" s="77"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="67" t="s">
+      <c r="V40" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="W40" s="68"/>
-      <c r="X40" s="69"/>
+      <c r="W40" s="76"/>
+      <c r="X40" s="77"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="67"/>
-      <c r="AA40" s="68"/>
-      <c r="AB40" s="69"/>
+      <c r="Z40" s="75"/>
+      <c r="AA40" s="76"/>
+      <c r="AB40" s="77"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="67" t="s">
+      <c r="AD40" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="AE40" s="68"/>
-      <c r="AF40" s="69"/>
+      <c r="AE40" s="76"/>
+      <c r="AF40" s="77"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="67"/>
-      <c r="AI40" s="68"/>
-      <c r="AJ40" s="69"/>
+      <c r="AH40" s="75"/>
+      <c r="AI40" s="76"/>
+      <c r="AJ40" s="77"/>
       <c r="AK40" s="37"/>
-      <c r="AL40" s="67"/>
-      <c r="AM40" s="68"/>
-      <c r="AN40" s="69"/>
+      <c r="AL40" s="75"/>
+      <c r="AM40" s="76"/>
+      <c r="AN40" s="77"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
       <c r="AR40" s="13"/>
     </row>
-    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="82"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="84"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="85"/>
       <c r="E41" s="37"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="84"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="85"/>
       <c r="I41" s="44"/>
-      <c r="J41" s="82"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="84"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="85"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="72"/>
+      <c r="N41" s="69"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="71"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="70"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="72"/>
+      <c r="R41" s="69"/>
+      <c r="S41" s="70"/>
+      <c r="T41" s="71"/>
       <c r="U41" s="37"/>
-      <c r="V41" s="70"/>
-      <c r="W41" s="71"/>
-      <c r="X41" s="72"/>
+      <c r="V41" s="69"/>
+      <c r="W41" s="70"/>
+      <c r="X41" s="71"/>
       <c r="Y41" s="44"/>
-      <c r="Z41" s="70"/>
-      <c r="AA41" s="71"/>
-      <c r="AB41" s="72"/>
+      <c r="Z41" s="69"/>
+      <c r="AA41" s="70"/>
+      <c r="AB41" s="71"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="70"/>
-      <c r="AE41" s="71"/>
-      <c r="AF41" s="72"/>
+      <c r="AD41" s="69"/>
+      <c r="AE41" s="70"/>
+      <c r="AF41" s="71"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="70"/>
-      <c r="AI41" s="71"/>
-      <c r="AJ41" s="72"/>
+      <c r="AH41" s="69"/>
+      <c r="AI41" s="70"/>
+      <c r="AJ41" s="71"/>
       <c r="AK41" s="44"/>
-      <c r="AL41" s="70"/>
-      <c r="AM41" s="71"/>
-      <c r="AN41" s="72"/>
+      <c r="AL41" s="69"/>
+      <c r="AM41" s="70"/>
+      <c r="AN41" s="71"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
       <c r="AR41" s="13"/>
     </row>
-    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
-      <c r="B42" s="76" t="s">
+      <c r="B42" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="77"/>
-      <c r="D42" s="78"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="68"/>
       <c r="E42" s="35"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="78"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="68"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="76" t="s">
+      <c r="J42" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="K42" s="77"/>
-      <c r="L42" s="78"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="68"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="76" t="s">
+      <c r="N42" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="O42" s="77"/>
-      <c r="P42" s="78"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="68"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="76"/>
-      <c r="S42" s="77"/>
-      <c r="T42" s="78"/>
+      <c r="R42" s="66"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="68"/>
       <c r="U42" s="35"/>
-      <c r="V42" s="76" t="s">
+      <c r="V42" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="W42" s="77"/>
-      <c r="X42" s="78"/>
+      <c r="W42" s="67"/>
+      <c r="X42" s="68"/>
       <c r="Y42" s="44"/>
-      <c r="Z42" s="76"/>
-      <c r="AA42" s="77"/>
-      <c r="AB42" s="78"/>
+      <c r="Z42" s="66"/>
+      <c r="AA42" s="67"/>
+      <c r="AB42" s="68"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="76" t="s">
+      <c r="AD42" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="AE42" s="77"/>
-      <c r="AF42" s="78"/>
+      <c r="AE42" s="67"/>
+      <c r="AF42" s="68"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="76"/>
-      <c r="AI42" s="77"/>
-      <c r="AJ42" s="78"/>
+      <c r="AH42" s="66"/>
+      <c r="AI42" s="67"/>
+      <c r="AJ42" s="68"/>
       <c r="AK42" s="44"/>
-      <c r="AL42" s="76"/>
-      <c r="AM42" s="77"/>
-      <c r="AN42" s="78"/>
+      <c r="AL42" s="66"/>
+      <c r="AM42" s="67"/>
+      <c r="AN42" s="68"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
       <c r="AR42" s="13"/>
     </row>
-    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="61"/>
-      <c r="D43" s="62"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="63"/>
       <c r="E43" s="50"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="62"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="62"/>
+      <c r="H43" s="63"/>
       <c r="I43" s="50"/>
-      <c r="J43" s="60" t="s">
+      <c r="J43" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="K43" s="61"/>
-      <c r="L43" s="62"/>
+      <c r="K43" s="62"/>
+      <c r="L43" s="63"/>
       <c r="M43" s="14"/>
-      <c r="N43" s="60" t="s">
+      <c r="N43" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="O43" s="61"/>
-      <c r="P43" s="62"/>
+      <c r="O43" s="62"/>
+      <c r="P43" s="63"/>
       <c r="Q43" s="50"/>
-      <c r="R43" s="60"/>
-      <c r="S43" s="61"/>
-      <c r="T43" s="62"/>
+      <c r="R43" s="61"/>
+      <c r="S43" s="62"/>
+      <c r="T43" s="63"/>
       <c r="U43" s="44"/>
-      <c r="V43" s="60" t="s">
+      <c r="V43" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="W43" s="61"/>
-      <c r="X43" s="62"/>
+      <c r="W43" s="62"/>
+      <c r="X43" s="63"/>
       <c r="Y43" s="50"/>
-      <c r="Z43" s="60"/>
-      <c r="AA43" s="61"/>
-      <c r="AB43" s="62"/>
+      <c r="Z43" s="61"/>
+      <c r="AA43" s="62"/>
+      <c r="AB43" s="63"/>
       <c r="AC43" s="50"/>
-      <c r="AD43" s="60" t="s">
+      <c r="AD43" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="AE43" s="61"/>
-      <c r="AF43" s="62"/>
+      <c r="AE43" s="62"/>
+      <c r="AF43" s="63"/>
       <c r="AG43" s="50"/>
-      <c r="AH43" s="60"/>
-      <c r="AI43" s="61"/>
-      <c r="AJ43" s="62"/>
+      <c r="AH43" s="61"/>
+      <c r="AI43" s="62"/>
+      <c r="AJ43" s="63"/>
       <c r="AK43" s="50"/>
-      <c r="AL43" s="60"/>
-      <c r="AM43" s="61"/>
-      <c r="AN43" s="62"/>
+      <c r="AL43" s="61"/>
+      <c r="AM43" s="62"/>
+      <c r="AN43" s="63"/>
       <c r="AO43" s="31"/>
       <c r="AP43" s="31"/>
       <c r="AQ43" s="31"/>
       <c r="AR43" s="13"/>
     </row>
-    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35"/>
@@ -4448,367 +4451,367 @@
       <c r="AQ44" s="31"/>
       <c r="AR44" s="13"/>
     </row>
-    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="64"/>
+      <c r="C45" s="79"/>
       <c r="D45" s="57"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="63" t="s">
+      <c r="F45" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="G45" s="64"/>
+      <c r="G45" s="79"/>
       <c r="H45" s="57"/>
       <c r="I45" s="31"/>
-      <c r="J45" s="63" t="s">
+      <c r="J45" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="K45" s="64"/>
+      <c r="K45" s="79"/>
       <c r="L45" s="57"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="65" t="s">
+      <c r="N45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="O45" s="66"/>
+      <c r="O45" s="65"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="65" t="s">
+      <c r="R45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="S45" s="66"/>
+      <c r="S45" s="65"/>
       <c r="T45" s="34"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="65" t="s">
+      <c r="V45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="W45" s="66"/>
+      <c r="W45" s="65"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="54"/>
-      <c r="Z45" s="65" t="s">
+      <c r="Z45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AA45" s="66"/>
+      <c r="AA45" s="65"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="65" t="s">
+      <c r="AD45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AE45" s="66"/>
+      <c r="AE45" s="65"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="65" t="s">
+      <c r="AH45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AI45" s="66"/>
+      <c r="AI45" s="65"/>
       <c r="AJ45" s="34"/>
       <c r="AK45" s="31"/>
-      <c r="AL45" s="65" t="s">
+      <c r="AL45" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="AM45" s="66"/>
+      <c r="AM45" s="65"/>
       <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
       <c r="AQ45" s="31"/>
       <c r="AR45" s="13"/>
     </row>
-    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
-      <c r="B46" s="79" t="s">
+      <c r="B46" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="80"/>
-      <c r="D46" s="81"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="82"/>
       <c r="E46" s="36"/>
-      <c r="F46" s="79" t="s">
+      <c r="F46" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="G46" s="80"/>
-      <c r="H46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="82"/>
       <c r="I46" s="32"/>
-      <c r="J46" s="79" t="s">
+      <c r="J46" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="K46" s="80"/>
-      <c r="L46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="82"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="67" t="s">
+      <c r="N46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="O46" s="68"/>
-      <c r="P46" s="69"/>
+      <c r="O46" s="76"/>
+      <c r="P46" s="77"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="67" t="s">
+      <c r="R46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="S46" s="68"/>
-      <c r="T46" s="69"/>
+      <c r="S46" s="76"/>
+      <c r="T46" s="77"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="67" t="s">
+      <c r="V46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="W46" s="68"/>
-      <c r="X46" s="69"/>
+      <c r="W46" s="76"/>
+      <c r="X46" s="77"/>
       <c r="Y46" s="35"/>
-      <c r="Z46" s="67" t="s">
+      <c r="Z46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="AA46" s="68"/>
-      <c r="AB46" s="69"/>
+      <c r="AA46" s="76"/>
+      <c r="AB46" s="77"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="67" t="s">
+      <c r="AD46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="AE46" s="68"/>
-      <c r="AF46" s="69"/>
+      <c r="AE46" s="76"/>
+      <c r="AF46" s="77"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="67" t="s">
+      <c r="AH46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="AI46" s="68"/>
-      <c r="AJ46" s="69"/>
+      <c r="AI46" s="76"/>
+      <c r="AJ46" s="77"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="67" t="s">
+      <c r="AL46" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="AM46" s="68"/>
-      <c r="AN46" s="69"/>
+      <c r="AM46" s="76"/>
+      <c r="AN46" s="77"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
       <c r="AR46" s="13"/>
     </row>
-    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
-      <c r="B47" s="82"/>
-      <c r="C47" s="83"/>
-      <c r="D47" s="84"/>
+      <c r="B47" s="83"/>
+      <c r="C47" s="84"/>
+      <c r="D47" s="85"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="82"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="84"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="84"/>
+      <c r="H47" s="85"/>
       <c r="I47" s="43"/>
-      <c r="J47" s="82"/>
-      <c r="K47" s="83"/>
-      <c r="L47" s="84"/>
+      <c r="J47" s="83"/>
+      <c r="K47" s="84"/>
+      <c r="L47" s="85"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="70"/>
-      <c r="O47" s="71"/>
-      <c r="P47" s="72"/>
+      <c r="N47" s="69"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="71"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="71"/>
-      <c r="T47" s="72"/>
+      <c r="R47" s="69"/>
+      <c r="S47" s="70"/>
+      <c r="T47" s="71"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="70"/>
-      <c r="W47" s="71"/>
-      <c r="X47" s="72"/>
+      <c r="V47" s="69"/>
+      <c r="W47" s="70"/>
+      <c r="X47" s="71"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="70"/>
-      <c r="AA47" s="71"/>
-      <c r="AB47" s="72"/>
+      <c r="Z47" s="69"/>
+      <c r="AA47" s="70"/>
+      <c r="AB47" s="71"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="70"/>
-      <c r="AE47" s="71"/>
-      <c r="AF47" s="72"/>
+      <c r="AD47" s="69"/>
+      <c r="AE47" s="70"/>
+      <c r="AF47" s="71"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="70"/>
-      <c r="AI47" s="71"/>
-      <c r="AJ47" s="72"/>
+      <c r="AH47" s="69"/>
+      <c r="AI47" s="70"/>
+      <c r="AJ47" s="71"/>
       <c r="AK47" s="43"/>
-      <c r="AL47" s="70"/>
-      <c r="AM47" s="71"/>
-      <c r="AN47" s="72"/>
+      <c r="AL47" s="69"/>
+      <c r="AM47" s="70"/>
+      <c r="AN47" s="71"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
       <c r="AR47" s="13"/>
     </row>
-    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="73" t="s">
+      <c r="B48" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="74"/>
-      <c r="D48" s="75"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="74"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="73" t="s">
+      <c r="F48" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="G48" s="74"/>
-      <c r="H48" s="75"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="74"/>
       <c r="I48" s="43"/>
-      <c r="J48" s="73" t="s">
+      <c r="J48" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="K48" s="74"/>
-      <c r="L48" s="75"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="74"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="76" t="s">
+      <c r="N48" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="O48" s="77"/>
-      <c r="P48" s="78"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="68"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="73" t="s">
+      <c r="R48" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="S48" s="74"/>
-      <c r="T48" s="75"/>
+      <c r="S48" s="73"/>
+      <c r="T48" s="74"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="73" t="s">
+      <c r="V48" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="W48" s="74"/>
-      <c r="X48" s="75"/>
+      <c r="W48" s="73"/>
+      <c r="X48" s="74"/>
       <c r="Y48" s="40"/>
-      <c r="Z48" s="73" t="s">
+      <c r="Z48" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="AA48" s="74"/>
-      <c r="AB48" s="75"/>
+      <c r="AA48" s="73"/>
+      <c r="AB48" s="74"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="73" t="s">
+      <c r="AD48" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="AE48" s="74"/>
-      <c r="AF48" s="75"/>
+      <c r="AE48" s="73"/>
+      <c r="AF48" s="74"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="73" t="s">
+      <c r="AH48" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="AI48" s="74"/>
-      <c r="AJ48" s="75"/>
+      <c r="AI48" s="73"/>
+      <c r="AJ48" s="74"/>
       <c r="AK48" s="43"/>
-      <c r="AL48" s="73" t="s">
+      <c r="AL48" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="AM48" s="74"/>
-      <c r="AN48" s="75"/>
+      <c r="AM48" s="73"/>
+      <c r="AN48" s="74"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
-    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="73" t="s">
+    <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="74"/>
-      <c r="D49" s="75"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="74"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="73" t="s">
+      <c r="F49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="74"/>
-      <c r="H49" s="75"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="74"/>
       <c r="I49" s="43"/>
-      <c r="J49" s="73" t="s">
+      <c r="J49" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="74"/>
-      <c r="L49" s="75"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="74"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="73" t="s">
+      <c r="N49" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="O49" s="74"/>
-      <c r="P49" s="75"/>
+      <c r="O49" s="73"/>
+      <c r="P49" s="74"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="73" t="s">
+      <c r="R49" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="S49" s="74"/>
-      <c r="T49" s="75"/>
+      <c r="S49" s="73"/>
+      <c r="T49" s="74"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="73" t="s">
+      <c r="V49" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="W49" s="74"/>
-      <c r="X49" s="75"/>
+      <c r="W49" s="73"/>
+      <c r="X49" s="74"/>
       <c r="Y49" s="44"/>
-      <c r="Z49" s="73" t="s">
+      <c r="Z49" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="AA49" s="74"/>
-      <c r="AB49" s="75"/>
+      <c r="AA49" s="73"/>
+      <c r="AB49" s="74"/>
       <c r="AC49" s="43"/>
-      <c r="AD49" s="73" t="s">
+      <c r="AD49" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="AE49" s="74"/>
-      <c r="AF49" s="75"/>
+      <c r="AE49" s="73"/>
+      <c r="AF49" s="74"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="73" t="s">
+      <c r="AH49" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="AI49" s="74"/>
-      <c r="AJ49" s="75"/>
+      <c r="AI49" s="73"/>
+      <c r="AJ49" s="74"/>
       <c r="AK49" s="43"/>
-      <c r="AL49" s="73" t="s">
+      <c r="AL49" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="AM49" s="74"/>
-      <c r="AN49" s="75"/>
+      <c r="AM49" s="73"/>
+      <c r="AN49" s="74"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
       <c r="AR49" s="13"/>
     </row>
-    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="60" t="s">
+    <row r="50" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="61"/>
-      <c r="D50" s="62"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="63"/>
       <c r="E50" s="35"/>
-      <c r="F50" s="60" t="s">
+      <c r="F50" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="G50" s="61"/>
-      <c r="H50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="63"/>
       <c r="I50" s="31"/>
-      <c r="J50" s="60" t="s">
+      <c r="J50" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="K50" s="61"/>
-      <c r="L50" s="62"/>
+      <c r="K50" s="62"/>
+      <c r="L50" s="63"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="60"/>
-      <c r="O50" s="61"/>
-      <c r="P50" s="62"/>
+      <c r="N50" s="61"/>
+      <c r="O50" s="62"/>
+      <c r="P50" s="63"/>
       <c r="Q50" s="31"/>
-      <c r="R50" s="60"/>
-      <c r="S50" s="61"/>
-      <c r="T50" s="62"/>
+      <c r="R50" s="61"/>
+      <c r="S50" s="62"/>
+      <c r="T50" s="63"/>
       <c r="U50" s="35"/>
-      <c r="V50" s="60"/>
-      <c r="W50" s="61"/>
-      <c r="X50" s="62"/>
+      <c r="V50" s="61"/>
+      <c r="W50" s="62"/>
+      <c r="X50" s="63"/>
       <c r="Y50" s="50"/>
-      <c r="Z50" s="60"/>
-      <c r="AA50" s="61"/>
-      <c r="AB50" s="62"/>
+      <c r="Z50" s="61"/>
+      <c r="AA50" s="62"/>
+      <c r="AB50" s="63"/>
       <c r="AC50" s="31"/>
-      <c r="AD50" s="60"/>
-      <c r="AE50" s="61"/>
-      <c r="AF50" s="62"/>
+      <c r="AD50" s="61"/>
+      <c r="AE50" s="62"/>
+      <c r="AF50" s="63"/>
       <c r="AG50" s="35"/>
-      <c r="AH50" s="60"/>
-      <c r="AI50" s="61"/>
-      <c r="AJ50" s="62"/>
+      <c r="AH50" s="61"/>
+      <c r="AI50" s="62"/>
+      <c r="AJ50" s="63"/>
       <c r="AK50" s="31"/>
-      <c r="AL50" s="60"/>
-      <c r="AM50" s="61"/>
-      <c r="AN50" s="62"/>
+      <c r="AL50" s="61"/>
+      <c r="AM50" s="62"/>
+      <c r="AN50" s="63"/>
       <c r="AO50" s="31"/>
       <c r="AP50" s="31"/>
       <c r="AQ50" s="31"/>
       <c r="AR50" s="13"/>
     </row>
-    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="35"/>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -4853,347 +4856,347 @@
       <c r="AQ51" s="31"/>
       <c r="AR51" s="13"/>
     </row>
-    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="63" t="s">
+    <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="64"/>
+      <c r="C52" s="79"/>
       <c r="D52" s="57"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="63" t="s">
+      <c r="F52" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="G52" s="64"/>
+      <c r="G52" s="79"/>
       <c r="H52" s="57"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="63" t="s">
+      <c r="J52" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="K52" s="64"/>
+      <c r="K52" s="79"/>
       <c r="L52" s="57"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="65" t="s">
+      <c r="N52" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="O52" s="66"/>
+      <c r="O52" s="65"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="65" t="s">
+      <c r="R52" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="S52" s="66"/>
+      <c r="S52" s="65"/>
       <c r="T52" s="34"/>
       <c r="U52" s="36"/>
-      <c r="V52" s="65" t="s">
+      <c r="V52" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="W52" s="66"/>
+      <c r="W52" s="65"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="37"/>
-      <c r="Z52" s="65" t="s">
+      <c r="Z52" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="AA52" s="66"/>
+      <c r="AA52" s="65"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="32"/>
-      <c r="AD52" s="65" t="s">
+      <c r="AD52" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="AE52" s="66"/>
+      <c r="AE52" s="65"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="65" t="s">
+      <c r="AH52" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="AI52" s="66"/>
+      <c r="AI52" s="65"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="65" t="s">
+      <c r="AL52" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="AM52" s="66"/>
+      <c r="AM52" s="65"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
-    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="79" t="s">
+    <row r="53" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="C53" s="80"/>
-      <c r="D53" s="81"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="82"/>
       <c r="E53" s="32"/>
-      <c r="F53" s="79" t="s">
+      <c r="F53" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="G53" s="80"/>
-      <c r="H53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="82"/>
       <c r="I53" s="54"/>
-      <c r="J53" s="79" t="s">
+      <c r="J53" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="K53" s="80"/>
-      <c r="L53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="82"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="67" t="s">
+      <c r="N53" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="O53" s="68"/>
-      <c r="P53" s="69"/>
+      <c r="O53" s="76"/>
+      <c r="P53" s="77"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="67" t="s">
+      <c r="R53" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="S53" s="68"/>
-      <c r="T53" s="69"/>
+      <c r="S53" s="76"/>
+      <c r="T53" s="77"/>
       <c r="U53" s="36"/>
-      <c r="V53" s="67" t="s">
+      <c r="V53" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="W53" s="68"/>
-      <c r="X53" s="69"/>
+      <c r="W53" s="76"/>
+      <c r="X53" s="77"/>
       <c r="Y53" s="50"/>
-      <c r="Z53" s="67" t="s">
+      <c r="Z53" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="AA53" s="68"/>
-      <c r="AB53" s="69"/>
+      <c r="AA53" s="76"/>
+      <c r="AB53" s="77"/>
       <c r="AC53" s="54"/>
-      <c r="AD53" s="67" t="s">
+      <c r="AD53" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="AE53" s="68"/>
-      <c r="AF53" s="69"/>
+      <c r="AE53" s="76"/>
+      <c r="AF53" s="77"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="67" t="s">
+      <c r="AH53" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="AI53" s="68"/>
-      <c r="AJ53" s="69"/>
+      <c r="AI53" s="76"/>
+      <c r="AJ53" s="77"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="67" t="s">
+      <c r="AL53" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="AM53" s="68"/>
-      <c r="AN53" s="69"/>
+      <c r="AM53" s="76"/>
+      <c r="AN53" s="77"/>
       <c r="AR53" s="13"/>
     </row>
-    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="82"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="84"/>
+    <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="83"/>
+      <c r="C54" s="84"/>
+      <c r="D54" s="85"/>
       <c r="E54" s="32"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="83"/>
-      <c r="H54" s="84"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="84"/>
+      <c r="H54" s="85"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="84"/>
+      <c r="J54" s="83"/>
+      <c r="K54" s="84"/>
+      <c r="L54" s="85"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="70"/>
-      <c r="O54" s="71"/>
-      <c r="P54" s="72"/>
+      <c r="N54" s="69"/>
+      <c r="O54" s="70"/>
+      <c r="P54" s="71"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="70" t="s">
+      <c r="R54" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="S54" s="71"/>
-      <c r="T54" s="72"/>
+      <c r="S54" s="70"/>
+      <c r="T54" s="71"/>
       <c r="U54" s="43"/>
-      <c r="V54" s="70"/>
-      <c r="W54" s="71"/>
-      <c r="X54" s="72"/>
+      <c r="V54" s="69"/>
+      <c r="W54" s="70"/>
+      <c r="X54" s="71"/>
       <c r="Y54" s="50"/>
-      <c r="Z54" s="70"/>
-      <c r="AA54" s="71"/>
-      <c r="AB54" s="72"/>
+      <c r="Z54" s="69"/>
+      <c r="AA54" s="70"/>
+      <c r="AB54" s="71"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="70"/>
-      <c r="AE54" s="71"/>
-      <c r="AF54" s="72"/>
+      <c r="AD54" s="69"/>
+      <c r="AE54" s="70"/>
+      <c r="AF54" s="71"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="70"/>
-      <c r="AI54" s="71"/>
-      <c r="AJ54" s="72"/>
+      <c r="AH54" s="69"/>
+      <c r="AI54" s="70"/>
+      <c r="AJ54" s="71"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="70"/>
-      <c r="AM54" s="71"/>
-      <c r="AN54" s="72"/>
+      <c r="AL54" s="69"/>
+      <c r="AM54" s="70"/>
+      <c r="AN54" s="71"/>
       <c r="AR54" s="13"/>
     </row>
-    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="76" t="s">
+    <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="77"/>
-      <c r="D55" s="78"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="68"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="76" t="s">
+      <c r="F55" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="G55" s="77"/>
-      <c r="H55" s="78"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="68"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="76" t="s">
+      <c r="J55" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="K55" s="77"/>
-      <c r="L55" s="78"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="68"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="76" t="s">
+      <c r="N55" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="O55" s="77"/>
-      <c r="P55" s="78"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="68"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="76" t="s">
+      <c r="R55" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="S55" s="77"/>
-      <c r="T55" s="78"/>
+      <c r="S55" s="67"/>
+      <c r="T55" s="68"/>
       <c r="U55" s="43"/>
-      <c r="V55" s="76" t="s">
+      <c r="V55" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="W55" s="77"/>
-      <c r="X55" s="78"/>
+      <c r="W55" s="67"/>
+      <c r="X55" s="68"/>
       <c r="Y55" s="32"/>
-      <c r="Z55" s="76" t="s">
+      <c r="Z55" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="AA55" s="77"/>
-      <c r="AB55" s="78"/>
+      <c r="AA55" s="67"/>
+      <c r="AB55" s="68"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="76" t="s">
+      <c r="AD55" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="AE55" s="77"/>
-      <c r="AF55" s="78"/>
+      <c r="AE55" s="67"/>
+      <c r="AF55" s="68"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="76" t="s">
+      <c r="AH55" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="AI55" s="77"/>
-      <c r="AJ55" s="78"/>
+      <c r="AI55" s="67"/>
+      <c r="AJ55" s="68"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="76" t="s">
+      <c r="AL55" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="AM55" s="77"/>
-      <c r="AN55" s="78"/>
+      <c r="AM55" s="67"/>
+      <c r="AN55" s="68"/>
       <c r="AR55" s="13"/>
     </row>
-    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="73" t="s">
+    <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="74"/>
-      <c r="D56" s="75"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="74"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="73" t="s">
+      <c r="F56" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="G56" s="74"/>
-      <c r="H56" s="75"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="74"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="73" t="s">
+      <c r="J56" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="K56" s="74"/>
-      <c r="L56" s="75"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="74"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="73" t="s">
+      <c r="N56" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="O56" s="74"/>
-      <c r="P56" s="75"/>
+      <c r="O56" s="73"/>
+      <c r="P56" s="74"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="73" t="s">
+      <c r="R56" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="S56" s="74"/>
-      <c r="T56" s="75"/>
+      <c r="S56" s="73"/>
+      <c r="T56" s="74"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="73" t="s">
+      <c r="V56" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="W56" s="74"/>
-      <c r="X56" s="75"/>
+      <c r="W56" s="73"/>
+      <c r="X56" s="74"/>
       <c r="Y56" s="32"/>
-      <c r="Z56" s="73" t="s">
+      <c r="Z56" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="AA56" s="74"/>
-      <c r="AB56" s="75"/>
+      <c r="AA56" s="73"/>
+      <c r="AB56" s="74"/>
       <c r="AC56" s="40"/>
-      <c r="AD56" s="73" t="s">
+      <c r="AD56" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="AE56" s="74"/>
-      <c r="AF56" s="75"/>
+      <c r="AE56" s="73"/>
+      <c r="AF56" s="74"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="73" t="s">
+      <c r="AH56" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="AI56" s="74"/>
-      <c r="AJ56" s="75"/>
+      <c r="AI56" s="73"/>
+      <c r="AJ56" s="74"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="73" t="s">
+      <c r="AL56" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="AM56" s="74"/>
-      <c r="AN56" s="75"/>
+      <c r="AM56" s="73"/>
+      <c r="AN56" s="74"/>
       <c r="AR56" s="13"/>
     </row>
-    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="60"/>
-      <c r="C57" s="61"/>
-      <c r="D57" s="62"/>
+    <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="61"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="63"/>
       <c r="E57" s="35"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="62"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="63"/>
       <c r="I57" s="50"/>
-      <c r="J57" s="60"/>
-      <c r="K57" s="61"/>
-      <c r="L57" s="62"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="62"/>
+      <c r="L57" s="63"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="60" t="s">
+      <c r="N57" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="O57" s="61"/>
-      <c r="P57" s="62"/>
+      <c r="O57" s="62"/>
+      <c r="P57" s="63"/>
       <c r="Q57" s="50"/>
-      <c r="R57" s="60" t="s">
+      <c r="R57" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="S57" s="61"/>
-      <c r="T57" s="62"/>
+      <c r="S57" s="62"/>
+      <c r="T57" s="63"/>
       <c r="U57" s="50"/>
-      <c r="V57" s="60" t="s">
+      <c r="V57" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="W57" s="61"/>
-      <c r="X57" s="62"/>
+      <c r="W57" s="62"/>
+      <c r="X57" s="63"/>
       <c r="Y57" s="37"/>
-      <c r="Z57" s="60"/>
-      <c r="AA57" s="61"/>
-      <c r="AB57" s="62"/>
+      <c r="Z57" s="61"/>
+      <c r="AA57" s="62"/>
+      <c r="AB57" s="63"/>
       <c r="AC57" s="50"/>
-      <c r="AD57" s="60"/>
-      <c r="AE57" s="61"/>
-      <c r="AF57" s="62"/>
+      <c r="AD57" s="61"/>
+      <c r="AE57" s="62"/>
+      <c r="AF57" s="63"/>
       <c r="AG57" s="35"/>
-      <c r="AH57" s="60"/>
-      <c r="AI57" s="61"/>
-      <c r="AJ57" s="62"/>
+      <c r="AH57" s="61"/>
+      <c r="AI57" s="62"/>
+      <c r="AJ57" s="63"/>
       <c r="AK57" s="50"/>
-      <c r="AL57" s="60"/>
-      <c r="AM57" s="61"/>
-      <c r="AN57" s="62"/>
+      <c r="AL57" s="61"/>
+      <c r="AM57" s="62"/>
+      <c r="AN57" s="63"/>
       <c r="AR57" s="13"/>
     </row>
-    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -5235,331 +5238,331 @@
       <c r="AN58" s="35"/>
       <c r="AR58" s="13"/>
     </row>
-    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="63" t="s">
+    <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="C59" s="64"/>
+      <c r="C59" s="79"/>
       <c r="D59" s="57" t="s">
         <v>66</v>
       </c>
       <c r="E59" s="36"/>
-      <c r="F59" s="63" t="s">
+      <c r="F59" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="G59" s="64"/>
+      <c r="G59" s="79"/>
       <c r="H59" s="57" t="s">
         <v>53</v>
       </c>
       <c r="I59" s="32"/>
-      <c r="J59" s="63" t="s">
+      <c r="J59" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="K59" s="64"/>
+      <c r="K59" s="79"/>
       <c r="L59" s="57"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="65"/>
-      <c r="O59" s="66"/>
+      <c r="N59" s="64"/>
+      <c r="O59" s="65"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="65"/>
-      <c r="S59" s="66"/>
+      <c r="R59" s="64"/>
+      <c r="S59" s="65"/>
       <c r="T59" s="34"/>
       <c r="U59" s="36"/>
-      <c r="V59" s="65"/>
-      <c r="W59" s="66"/>
+      <c r="V59" s="64"/>
+      <c r="W59" s="65"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="36"/>
-      <c r="Z59" s="65"/>
-      <c r="AA59" s="66"/>
+      <c r="Z59" s="64"/>
+      <c r="AA59" s="65"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="65" t="s">
+      <c r="AD59" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="AE59" s="66"/>
+      <c r="AE59" s="65"/>
       <c r="AF59" s="34" t="s">
         <v>53</v>
       </c>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="65" t="s">
+      <c r="AH59" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="AI59" s="66"/>
+      <c r="AI59" s="65"/>
       <c r="AJ59" s="34" t="s">
         <v>53</v>
       </c>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="65" t="s">
+      <c r="AL59" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="AM59" s="66"/>
+      <c r="AM59" s="65"/>
       <c r="AN59" s="34" t="s">
         <v>53</v>
       </c>
       <c r="AR59" s="13"/>
     </row>
-    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="79" t="s">
+    <row r="60" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="80"/>
-      <c r="D60" s="81"/>
+      <c r="C60" s="81"/>
+      <c r="D60" s="82"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="79" t="s">
+      <c r="F60" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="G60" s="80"/>
-      <c r="H60" s="81"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="82"/>
       <c r="I60" s="54"/>
-      <c r="J60" s="79" t="s">
+      <c r="J60" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="K60" s="80"/>
-      <c r="L60" s="81"/>
+      <c r="K60" s="81"/>
+      <c r="L60" s="82"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="67"/>
-      <c r="O60" s="68"/>
-      <c r="P60" s="69"/>
+      <c r="N60" s="75"/>
+      <c r="O60" s="76"/>
+      <c r="P60" s="77"/>
       <c r="Q60" s="37"/>
-      <c r="R60" s="67"/>
-      <c r="S60" s="68"/>
-      <c r="T60" s="69"/>
+      <c r="R60" s="75"/>
+      <c r="S60" s="76"/>
+      <c r="T60" s="77"/>
       <c r="U60" s="36"/>
-      <c r="V60" s="67"/>
-      <c r="W60" s="68"/>
-      <c r="X60" s="69"/>
+      <c r="V60" s="75"/>
+      <c r="W60" s="76"/>
+      <c r="X60" s="77"/>
       <c r="Y60" s="37"/>
-      <c r="Z60" s="67"/>
-      <c r="AA60" s="68"/>
-      <c r="AB60" s="69"/>
+      <c r="Z60" s="75"/>
+      <c r="AA60" s="76"/>
+      <c r="AB60" s="77"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="67" t="s">
+      <c r="AD60" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="AE60" s="68"/>
-      <c r="AF60" s="69"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="77"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="67" t="s">
+      <c r="AH60" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="AI60" s="68"/>
-      <c r="AJ60" s="69"/>
+      <c r="AI60" s="76"/>
+      <c r="AJ60" s="77"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="67" t="s">
+      <c r="AL60" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="AM60" s="68"/>
-      <c r="AN60" s="69"/>
+      <c r="AM60" s="76"/>
+      <c r="AN60" s="77"/>
       <c r="AR60" s="13"/>
     </row>
-    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="82"/>
-      <c r="C61" s="83"/>
-      <c r="D61" s="84"/>
+    <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="83"/>
+      <c r="C61" s="84"/>
+      <c r="D61" s="85"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="82"/>
-      <c r="G61" s="83"/>
-      <c r="H61" s="84"/>
+      <c r="F61" s="83"/>
+      <c r="G61" s="84"/>
+      <c r="H61" s="85"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="82" t="s">
+      <c r="J61" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="K61" s="83"/>
-      <c r="L61" s="84"/>
+      <c r="K61" s="84"/>
+      <c r="L61" s="85"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="70"/>
-      <c r="O61" s="71"/>
-      <c r="P61" s="72"/>
+      <c r="N61" s="69"/>
+      <c r="O61" s="70"/>
+      <c r="P61" s="71"/>
       <c r="Q61" s="36"/>
-      <c r="R61" s="70"/>
-      <c r="S61" s="71"/>
-      <c r="T61" s="72"/>
+      <c r="R61" s="69"/>
+      <c r="S61" s="70"/>
+      <c r="T61" s="71"/>
       <c r="U61" s="35"/>
-      <c r="V61" s="70"/>
-      <c r="W61" s="71"/>
-      <c r="X61" s="72"/>
+      <c r="V61" s="69"/>
+      <c r="W61" s="70"/>
+      <c r="X61" s="71"/>
       <c r="Y61" s="36"/>
-      <c r="Z61" s="70"/>
-      <c r="AA61" s="71"/>
-      <c r="AB61" s="72"/>
+      <c r="Z61" s="69"/>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="71"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="70"/>
-      <c r="AE61" s="71"/>
-      <c r="AF61" s="72"/>
+      <c r="AD61" s="69"/>
+      <c r="AE61" s="70"/>
+      <c r="AF61" s="71"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="70"/>
-      <c r="AI61" s="71"/>
-      <c r="AJ61" s="72"/>
+      <c r="AH61" s="69"/>
+      <c r="AI61" s="70"/>
+      <c r="AJ61" s="71"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="70"/>
-      <c r="AM61" s="71"/>
-      <c r="AN61" s="72"/>
+      <c r="AL61" s="69"/>
+      <c r="AM61" s="70"/>
+      <c r="AN61" s="71"/>
       <c r="AR61" s="13"/>
     </row>
-    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="91" t="s">
+    <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="92"/>
-      <c r="D62" s="93"/>
+      <c r="C62" s="123"/>
+      <c r="D62" s="124"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="91" t="s">
+      <c r="F62" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="G62" s="92"/>
-      <c r="H62" s="93"/>
+      <c r="G62" s="123"/>
+      <c r="H62" s="124"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="76" t="s">
+      <c r="J62" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="K62" s="77"/>
-      <c r="L62" s="78"/>
+      <c r="K62" s="67"/>
+      <c r="L62" s="68"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="73"/>
-      <c r="O62" s="74"/>
-      <c r="P62" s="75"/>
+      <c r="N62" s="72"/>
+      <c r="O62" s="73"/>
+      <c r="P62" s="74"/>
       <c r="Q62" s="43"/>
-      <c r="R62" s="73"/>
-      <c r="S62" s="74"/>
-      <c r="T62" s="75"/>
+      <c r="R62" s="72"/>
+      <c r="S62" s="73"/>
+      <c r="T62" s="74"/>
       <c r="U62" s="43"/>
-      <c r="V62" s="73"/>
-      <c r="W62" s="74"/>
-      <c r="X62" s="75"/>
+      <c r="V62" s="72"/>
+      <c r="W62" s="73"/>
+      <c r="X62" s="74"/>
       <c r="Y62" s="43"/>
-      <c r="Z62" s="73"/>
-      <c r="AA62" s="74"/>
-      <c r="AB62" s="75"/>
+      <c r="Z62" s="72"/>
+      <c r="AA62" s="73"/>
+      <c r="AB62" s="74"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="73" t="s">
+      <c r="AD62" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="AE62" s="74"/>
-      <c r="AF62" s="75"/>
+      <c r="AE62" s="73"/>
+      <c r="AF62" s="74"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="73" t="s">
+      <c r="AH62" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="AI62" s="74"/>
-      <c r="AJ62" s="75"/>
+      <c r="AI62" s="73"/>
+      <c r="AJ62" s="74"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="73" t="s">
+      <c r="AL62" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="AM62" s="74"/>
-      <c r="AN62" s="75"/>
+      <c r="AM62" s="73"/>
+      <c r="AN62" s="74"/>
       <c r="AR62" s="13"/>
     </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="73" t="s">
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="74"/>
-      <c r="D63" s="75"/>
+      <c r="C63" s="73"/>
+      <c r="D63" s="74"/>
       <c r="E63" s="44"/>
-      <c r="F63" s="73" t="s">
+      <c r="F63" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="G63" s="74"/>
-      <c r="H63" s="75"/>
+      <c r="G63" s="73"/>
+      <c r="H63" s="74"/>
       <c r="I63" s="44"/>
-      <c r="J63" s="88" t="s">
+      <c r="J63" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="K63" s="89"/>
-      <c r="L63" s="90"/>
+      <c r="K63" s="126"/>
+      <c r="L63" s="127"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="73"/>
-      <c r="O63" s="74"/>
-      <c r="P63" s="75"/>
+      <c r="N63" s="72"/>
+      <c r="O63" s="73"/>
+      <c r="P63" s="74"/>
       <c r="Q63" s="50"/>
-      <c r="R63" s="73"/>
-      <c r="S63" s="74"/>
-      <c r="T63" s="75"/>
+      <c r="R63" s="72"/>
+      <c r="S63" s="73"/>
+      <c r="T63" s="74"/>
       <c r="U63" s="44"/>
-      <c r="V63" s="73"/>
-      <c r="W63" s="74"/>
-      <c r="X63" s="75"/>
+      <c r="V63" s="72"/>
+      <c r="W63" s="73"/>
+      <c r="X63" s="74"/>
       <c r="Y63" s="50"/>
-      <c r="Z63" s="73"/>
-      <c r="AA63" s="74"/>
-      <c r="AB63" s="75"/>
+      <c r="Z63" s="72"/>
+      <c r="AA63" s="73"/>
+      <c r="AB63" s="74"/>
       <c r="AC63" s="44"/>
-      <c r="AD63" s="73" t="s">
+      <c r="AD63" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="AE63" s="74"/>
-      <c r="AF63" s="75"/>
+      <c r="AE63" s="73"/>
+      <c r="AF63" s="74"/>
       <c r="AG63" s="44"/>
-      <c r="AH63" s="73" t="s">
+      <c r="AH63" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="AI63" s="74"/>
-      <c r="AJ63" s="75"/>
+      <c r="AI63" s="73"/>
+      <c r="AJ63" s="74"/>
       <c r="AK63" s="44"/>
-      <c r="AL63" s="73" t="s">
+      <c r="AL63" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="AM63" s="74"/>
-      <c r="AN63" s="75"/>
+      <c r="AM63" s="73"/>
+      <c r="AN63" s="74"/>
       <c r="AR63" s="13"/>
     </row>
-    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="60" t="s">
+    <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="C64" s="61"/>
-      <c r="D64" s="62"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="63"/>
       <c r="E64" s="44"/>
-      <c r="F64" s="60" t="s">
+      <c r="F64" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="61"/>
-      <c r="H64" s="62"/>
+      <c r="G64" s="62"/>
+      <c r="H64" s="63"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="60" t="s">
+      <c r="J64" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="K64" s="61"/>
-      <c r="L64" s="62"/>
+      <c r="K64" s="62"/>
+      <c r="L64" s="63"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="60"/>
-      <c r="O64" s="61"/>
-      <c r="P64" s="62"/>
+      <c r="N64" s="61"/>
+      <c r="O64" s="62"/>
+      <c r="P64" s="63"/>
       <c r="Q64" s="50"/>
-      <c r="R64" s="60"/>
-      <c r="S64" s="61"/>
-      <c r="T64" s="62"/>
+      <c r="R64" s="61"/>
+      <c r="S64" s="62"/>
+      <c r="T64" s="63"/>
       <c r="U64" s="50"/>
-      <c r="V64" s="60"/>
-      <c r="W64" s="61"/>
-      <c r="X64" s="62"/>
+      <c r="V64" s="61"/>
+      <c r="W64" s="62"/>
+      <c r="X64" s="63"/>
       <c r="Y64" s="50"/>
-      <c r="Z64" s="60"/>
-      <c r="AA64" s="61"/>
-      <c r="AB64" s="62"/>
+      <c r="Z64" s="61"/>
+      <c r="AA64" s="62"/>
+      <c r="AB64" s="63"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="128" t="s">
+      <c r="AD64" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="AE64" s="129"/>
-      <c r="AF64" s="130"/>
+      <c r="AE64" s="99"/>
+      <c r="AF64" s="100"/>
       <c r="AG64" s="44"/>
-      <c r="AH64" s="60" t="s">
+      <c r="AH64" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="AI64" s="61"/>
-      <c r="AJ64" s="62"/>
+      <c r="AI64" s="62"/>
+      <c r="AJ64" s="63"/>
       <c r="AK64" s="44"/>
-      <c r="AL64" s="60" t="s">
+      <c r="AL64" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="AM64" s="61"/>
-      <c r="AN64" s="62"/>
+      <c r="AM64" s="62"/>
+      <c r="AN64" s="63"/>
       <c r="AR64" s="13"/>
     </row>
-    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="12"/>
       <c r="B65" s="33"/>
       <c r="C65" s="33"/>
@@ -5605,7 +5608,7 @@
       <c r="AQ65" s="12"/>
       <c r="AR65" s="13"/>
     </row>
-    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="12"/>
       <c r="B66" s="40"/>
       <c r="C66" s="33"/>
@@ -5619,23 +5622,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="94" t="s">
+      <c r="N66" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="94"/>
-      <c r="P66" s="94"/>
-      <c r="Q66" s="94"/>
-      <c r="R66" s="94"/>
-      <c r="S66" s="94"/>
-      <c r="T66" s="94"/>
-      <c r="U66" s="94"/>
-      <c r="V66" s="94"/>
-      <c r="W66" s="94"/>
-      <c r="X66" s="94"/>
-      <c r="Y66" s="94"/>
-      <c r="Z66" s="94"/>
-      <c r="AA66" s="94"/>
-      <c r="AB66" s="94"/>
+      <c r="O66" s="103"/>
+      <c r="P66" s="103"/>
+      <c r="Q66" s="103"/>
+      <c r="R66" s="103"/>
+      <c r="S66" s="103"/>
+      <c r="T66" s="103"/>
+      <c r="U66" s="103"/>
+      <c r="V66" s="103"/>
+      <c r="W66" s="103"/>
+      <c r="X66" s="103"/>
+      <c r="Y66" s="103"/>
+      <c r="Z66" s="103"/>
+      <c r="AA66" s="103"/>
+      <c r="AB66" s="103"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5652,7 +5655,7 @@
       <c r="AQ66" s="12"/>
       <c r="AR66" s="13"/>
     </row>
-    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="12"/>
       <c r="B67" s="33"/>
       <c r="C67" s="33"/>
@@ -5666,21 +5669,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="94"/>
-      <c r="O67" s="94"/>
-      <c r="P67" s="94"/>
-      <c r="Q67" s="94"/>
-      <c r="R67" s="94"/>
-      <c r="S67" s="94"/>
-      <c r="T67" s="94"/>
-      <c r="U67" s="94"/>
-      <c r="V67" s="94"/>
-      <c r="W67" s="94"/>
-      <c r="X67" s="94"/>
-      <c r="Y67" s="94"/>
-      <c r="Z67" s="94"/>
-      <c r="AA67" s="94"/>
-      <c r="AB67" s="94"/>
+      <c r="N67" s="103"/>
+      <c r="O67" s="103"/>
+      <c r="P67" s="103"/>
+      <c r="Q67" s="103"/>
+      <c r="R67" s="103"/>
+      <c r="S67" s="103"/>
+      <c r="T67" s="103"/>
+      <c r="U67" s="103"/>
+      <c r="V67" s="103"/>
+      <c r="W67" s="103"/>
+      <c r="X67" s="103"/>
+      <c r="Y67" s="103"/>
+      <c r="Z67" s="103"/>
+      <c r="AA67" s="103"/>
+      <c r="AB67" s="103"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5698,52 +5701,52 @@
       <c r="AQ67" s="12"/>
       <c r="AR67" s="13"/>
     </row>
-    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
-      <c r="B68" s="63"/>
-      <c r="C68" s="64"/>
+      <c r="B68" s="78"/>
+      <c r="C68" s="79"/>
       <c r="D68" s="57"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="63"/>
-      <c r="G68" s="64"/>
+      <c r="F68" s="78"/>
+      <c r="G68" s="79"/>
       <c r="H68" s="57"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="63"/>
-      <c r="K68" s="64"/>
+      <c r="J68" s="78"/>
+      <c r="K68" s="79"/>
       <c r="L68" s="57"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="65"/>
-      <c r="O68" s="66"/>
+      <c r="N68" s="64"/>
+      <c r="O68" s="65"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="44"/>
-      <c r="R68" s="65"/>
-      <c r="S68" s="66"/>
+      <c r="R68" s="64"/>
+      <c r="S68" s="65"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="65"/>
-      <c r="W68" s="66"/>
+      <c r="V68" s="64"/>
+      <c r="W68" s="65"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="65" t="s">
+      <c r="Z68" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="AA68" s="66"/>
+      <c r="AA68" s="65"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="65" t="s">
+      <c r="AD68" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="AE68" s="66"/>
+      <c r="AE68" s="65"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="65" t="s">
+      <c r="AH68" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="AI68" s="66"/>
+      <c r="AI68" s="65"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="65"/>
-      <c r="AM68" s="66"/>
+      <c r="AL68" s="64"/>
+      <c r="AM68" s="65"/>
       <c r="AN68" s="34"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
@@ -5752,53 +5755,53 @@
       <c r="AQ68" s="12"/>
       <c r="AR68" s="13"/>
     </row>
-    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
-      <c r="B69" s="79"/>
-      <c r="C69" s="80"/>
-      <c r="D69" s="81"/>
+      <c r="B69" s="80"/>
+      <c r="C69" s="81"/>
+      <c r="D69" s="82"/>
       <c r="E69" s="32"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="80"/>
-      <c r="H69" s="81"/>
+      <c r="F69" s="80"/>
+      <c r="G69" s="81"/>
+      <c r="H69" s="82"/>
       <c r="I69" s="32"/>
-      <c r="J69" s="79"/>
-      <c r="K69" s="80"/>
-      <c r="L69" s="81"/>
+      <c r="J69" s="80"/>
+      <c r="K69" s="81"/>
+      <c r="L69" s="82"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="67"/>
-      <c r="O69" s="68"/>
-      <c r="P69" s="69"/>
+      <c r="N69" s="75"/>
+      <c r="O69" s="76"/>
+      <c r="P69" s="77"/>
       <c r="Q69" s="44"/>
-      <c r="R69" s="67"/>
-      <c r="S69" s="68"/>
-      <c r="T69" s="69"/>
+      <c r="R69" s="75"/>
+      <c r="S69" s="76"/>
+      <c r="T69" s="77"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="67"/>
-      <c r="W69" s="68"/>
-      <c r="X69" s="69"/>
+      <c r="V69" s="75"/>
+      <c r="W69" s="76"/>
+      <c r="X69" s="77"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="67" t="s">
+      <c r="Z69" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="AA69" s="68"/>
-      <c r="AB69" s="69"/>
+      <c r="AA69" s="76"/>
+      <c r="AB69" s="77"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="67" t="s">
+      <c r="AD69" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="AE69" s="68"/>
-      <c r="AF69" s="69"/>
+      <c r="AE69" s="76"/>
+      <c r="AF69" s="77"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="67" t="s">
+      <c r="AH69" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="AI69" s="68"/>
-      <c r="AJ69" s="69"/>
+      <c r="AI69" s="76"/>
+      <c r="AJ69" s="77"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="67"/>
-      <c r="AM69" s="68"/>
-      <c r="AN69" s="69"/>
+      <c r="AL69" s="75"/>
+      <c r="AM69" s="76"/>
+      <c r="AN69" s="77"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5806,53 +5809,53 @@
       <c r="AQ69" s="12"/>
       <c r="AR69" s="13"/>
     </row>
-    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
-      <c r="B70" s="82"/>
-      <c r="C70" s="83"/>
-      <c r="D70" s="84"/>
+      <c r="B70" s="83"/>
+      <c r="C70" s="84"/>
+      <c r="D70" s="85"/>
       <c r="E70" s="32"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="83"/>
-      <c r="H70" s="84"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="84"/>
+      <c r="H70" s="85"/>
       <c r="I70" s="32"/>
-      <c r="J70" s="82"/>
-      <c r="K70" s="83"/>
-      <c r="L70" s="84"/>
+      <c r="J70" s="83"/>
+      <c r="K70" s="84"/>
+      <c r="L70" s="85"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="70"/>
-      <c r="O70" s="71"/>
-      <c r="P70" s="72"/>
+      <c r="N70" s="69"/>
+      <c r="O70" s="70"/>
+      <c r="P70" s="71"/>
       <c r="Q70" s="44"/>
-      <c r="R70" s="70"/>
-      <c r="S70" s="71"/>
-      <c r="T70" s="72"/>
+      <c r="R70" s="69"/>
+      <c r="S70" s="70"/>
+      <c r="T70" s="71"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="70"/>
-      <c r="W70" s="71"/>
-      <c r="X70" s="72"/>
+      <c r="V70" s="69"/>
+      <c r="W70" s="70"/>
+      <c r="X70" s="71"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="70" t="s">
+      <c r="Z70" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="AA70" s="71"/>
-      <c r="AB70" s="72"/>
+      <c r="AA70" s="70"/>
+      <c r="AB70" s="71"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="70" t="s">
+      <c r="AD70" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="AE70" s="71"/>
-      <c r="AF70" s="72"/>
+      <c r="AE70" s="70"/>
+      <c r="AF70" s="71"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="70" t="s">
+      <c r="AH70" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="AI70" s="71"/>
-      <c r="AJ70" s="72"/>
+      <c r="AI70" s="70"/>
+      <c r="AJ70" s="71"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="70"/>
-      <c r="AM70" s="71"/>
-      <c r="AN70" s="72"/>
+      <c r="AL70" s="69"/>
+      <c r="AM70" s="70"/>
+      <c r="AN70" s="71"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5860,53 +5863,53 @@
       <c r="AQ70" s="12"/>
       <c r="AR70" s="13"/>
     </row>
-    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="76"/>
-      <c r="C71" s="77"/>
-      <c r="D71" s="78"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="67"/>
+      <c r="D71" s="68"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="76"/>
-      <c r="G71" s="77"/>
-      <c r="H71" s="78"/>
+      <c r="F71" s="66"/>
+      <c r="G71" s="67"/>
+      <c r="H71" s="68"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="76"/>
-      <c r="K71" s="77"/>
-      <c r="L71" s="78"/>
+      <c r="J71" s="66"/>
+      <c r="K71" s="67"/>
+      <c r="L71" s="68"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="76"/>
-      <c r="O71" s="77"/>
-      <c r="P71" s="78"/>
+      <c r="N71" s="66"/>
+      <c r="O71" s="67"/>
+      <c r="P71" s="68"/>
       <c r="Q71" s="44"/>
-      <c r="R71" s="76"/>
-      <c r="S71" s="77"/>
-      <c r="T71" s="78"/>
+      <c r="R71" s="66"/>
+      <c r="S71" s="67"/>
+      <c r="T71" s="68"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="76"/>
-      <c r="W71" s="77"/>
-      <c r="X71" s="78"/>
+      <c r="V71" s="66"/>
+      <c r="W71" s="67"/>
+      <c r="X71" s="68"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="76" t="s">
+      <c r="Z71" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AA71" s="77"/>
-      <c r="AB71" s="78"/>
+      <c r="AA71" s="67"/>
+      <c r="AB71" s="68"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="76" t="s">
+      <c r="AD71" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AE71" s="77"/>
-      <c r="AF71" s="78"/>
+      <c r="AE71" s="67"/>
+      <c r="AF71" s="68"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="76" t="s">
+      <c r="AH71" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AI71" s="77"/>
-      <c r="AJ71" s="78"/>
+      <c r="AI71" s="67"/>
+      <c r="AJ71" s="68"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="76"/>
-      <c r="AM71" s="77"/>
-      <c r="AN71" s="78"/>
+      <c r="AL71" s="66"/>
+      <c r="AM71" s="67"/>
+      <c r="AN71" s="68"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -5914,57 +5917,57 @@
       <c r="AQ71" s="12"/>
       <c r="AR71" s="13"/>
     </row>
-    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12"/>
-      <c r="B72" s="60"/>
-      <c r="C72" s="61"/>
-      <c r="D72" s="62"/>
+      <c r="B72" s="61"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="63"/>
       <c r="E72" s="31"/>
-      <c r="F72" s="60"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="62"/>
+      <c r="F72" s="61"/>
+      <c r="G72" s="62"/>
+      <c r="H72" s="63"/>
       <c r="I72" s="32"/>
-      <c r="J72" s="60"/>
-      <c r="K72" s="61"/>
-      <c r="L72" s="62"/>
+      <c r="J72" s="61"/>
+      <c r="K72" s="62"/>
+      <c r="L72" s="63"/>
       <c r="M72" s="9"/>
-      <c r="N72" s="60"/>
-      <c r="O72" s="61"/>
-      <c r="P72" s="62"/>
+      <c r="N72" s="61"/>
+      <c r="O72" s="62"/>
+      <c r="P72" s="63"/>
       <c r="Q72" s="31"/>
-      <c r="R72" s="60"/>
-      <c r="S72" s="61"/>
-      <c r="T72" s="62"/>
+      <c r="R72" s="61"/>
+      <c r="S72" s="62"/>
+      <c r="T72" s="63"/>
       <c r="U72" s="32"/>
-      <c r="V72" s="60"/>
-      <c r="W72" s="61"/>
-      <c r="X72" s="62"/>
+      <c r="V72" s="61"/>
+      <c r="W72" s="62"/>
+      <c r="X72" s="63"/>
       <c r="Y72" s="32"/>
-      <c r="Z72" s="60"/>
-      <c r="AA72" s="61"/>
-      <c r="AB72" s="62"/>
+      <c r="Z72" s="61"/>
+      <c r="AA72" s="62"/>
+      <c r="AB72" s="63"/>
       <c r="AC72" s="32"/>
-      <c r="AD72" s="60" t="s">
+      <c r="AD72" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="AE72" s="61"/>
-      <c r="AF72" s="62"/>
+      <c r="AE72" s="62"/>
+      <c r="AF72" s="63"/>
       <c r="AG72" s="31"/>
-      <c r="AH72" s="60" t="s">
+      <c r="AH72" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="AI72" s="61"/>
-      <c r="AJ72" s="62"/>
+      <c r="AI72" s="62"/>
+      <c r="AJ72" s="63"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="60"/>
-      <c r="AM72" s="61"/>
-      <c r="AN72" s="62"/>
+      <c r="AL72" s="61"/>
+      <c r="AM72" s="62"/>
+      <c r="AN72" s="63"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -6010,245 +6013,247 @@
       <c r="AQ73" s="12"/>
       <c r="AR73" s="13"/>
     </row>
-    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
-      <c r="B74" s="63"/>
-      <c r="C74" s="64"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="79"/>
       <c r="D74" s="57"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="63"/>
-      <c r="G74" s="64"/>
+      <c r="F74" s="78"/>
+      <c r="G74" s="79"/>
       <c r="H74" s="57"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="63"/>
-      <c r="K74" s="64"/>
+      <c r="J74" s="78"/>
+      <c r="K74" s="79"/>
       <c r="L74" s="57"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="65"/>
-      <c r="O74" s="66"/>
+      <c r="N74" s="64"/>
+      <c r="O74" s="65"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="32"/>
-      <c r="R74" s="65"/>
-      <c r="S74" s="66"/>
+      <c r="R74" s="64"/>
+      <c r="S74" s="65"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="65"/>
-      <c r="W74" s="66"/>
+      <c r="V74" s="64"/>
+      <c r="W74" s="65"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="65"/>
-      <c r="AA74" s="66"/>
+      <c r="Z74" s="64"/>
+      <c r="AA74" s="65"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="125" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE74" s="126"/>
-      <c r="AF74" s="127"/>
+      <c r="AD74" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE74" s="97"/>
+      <c r="AF74" s="60"/>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="65"/>
-      <c r="AI74" s="66"/>
+      <c r="AH74" s="64"/>
+      <c r="AI74" s="65"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="65"/>
-      <c r="AM74" s="66"/>
+      <c r="AL74" s="64"/>
+      <c r="AM74" s="65"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
       <c r="AQ74" s="12"/>
       <c r="AR74" s="13"/>
     </row>
-    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
-      <c r="B75" s="79"/>
-      <c r="C75" s="80"/>
-      <c r="D75" s="81"/>
+      <c r="B75" s="80"/>
+      <c r="C75" s="81"/>
+      <c r="D75" s="82"/>
       <c r="E75" s="32"/>
-      <c r="F75" s="79"/>
-      <c r="G75" s="80"/>
-      <c r="H75" s="81"/>
+      <c r="F75" s="80"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="82"/>
       <c r="I75" s="35"/>
-      <c r="J75" s="79"/>
-      <c r="K75" s="80"/>
-      <c r="L75" s="81"/>
+      <c r="J75" s="80"/>
+      <c r="K75" s="81"/>
+      <c r="L75" s="82"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="67"/>
-      <c r="O75" s="68"/>
-      <c r="P75" s="69"/>
+      <c r="N75" s="75"/>
+      <c r="O75" s="76"/>
+      <c r="P75" s="77"/>
       <c r="Q75" s="35"/>
-      <c r="R75" s="67"/>
-      <c r="S75" s="68"/>
-      <c r="T75" s="69"/>
+      <c r="R75" s="75"/>
+      <c r="S75" s="76"/>
+      <c r="T75" s="77"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="67"/>
-      <c r="W75" s="68"/>
-      <c r="X75" s="69"/>
+      <c r="V75" s="75"/>
+      <c r="W75" s="76"/>
+      <c r="X75" s="77"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="67"/>
-      <c r="AA75" s="68"/>
-      <c r="AB75" s="69"/>
+      <c r="Z75" s="75"/>
+      <c r="AA75" s="76"/>
+      <c r="AB75" s="77"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="67" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE75" s="68"/>
-      <c r="AF75" s="69"/>
+      <c r="AD75" s="75" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE75" s="76"/>
+      <c r="AF75" s="77"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="67"/>
-      <c r="AI75" s="68"/>
-      <c r="AJ75" s="69"/>
+      <c r="AH75" s="75"/>
+      <c r="AI75" s="76"/>
+      <c r="AJ75" s="77"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="67"/>
-      <c r="AM75" s="68"/>
-      <c r="AN75" s="69"/>
+      <c r="AL75" s="75"/>
+      <c r="AM75" s="76"/>
+      <c r="AN75" s="77"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
       <c r="AR75" s="24"/>
     </row>
-    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
-      <c r="B76" s="82"/>
-      <c r="C76" s="83"/>
-      <c r="D76" s="84"/>
+      <c r="B76" s="83"/>
+      <c r="C76" s="84"/>
+      <c r="D76" s="85"/>
       <c r="E76" s="32"/>
-      <c r="F76" s="82"/>
-      <c r="G76" s="83"/>
-      <c r="H76" s="84"/>
+      <c r="F76" s="83"/>
+      <c r="G76" s="84"/>
+      <c r="H76" s="85"/>
       <c r="I76" s="31"/>
-      <c r="J76" s="82"/>
-      <c r="K76" s="83"/>
-      <c r="L76" s="84"/>
+      <c r="J76" s="83"/>
+      <c r="K76" s="84"/>
+      <c r="L76" s="85"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="70"/>
-      <c r="O76" s="71"/>
-      <c r="P76" s="72"/>
+      <c r="N76" s="69"/>
+      <c r="O76" s="70"/>
+      <c r="P76" s="71"/>
       <c r="Q76" s="31"/>
-      <c r="R76" s="70"/>
-      <c r="S76" s="71"/>
-      <c r="T76" s="72"/>
+      <c r="R76" s="69"/>
+      <c r="S76" s="70"/>
+      <c r="T76" s="71"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="70"/>
-      <c r="W76" s="71"/>
-      <c r="X76" s="72"/>
+      <c r="V76" s="69"/>
+      <c r="W76" s="70"/>
+      <c r="X76" s="71"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="70"/>
-      <c r="AA76" s="71"/>
-      <c r="AB76" s="72"/>
+      <c r="Z76" s="69"/>
+      <c r="AA76" s="70"/>
+      <c r="AB76" s="71"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="70"/>
-      <c r="AE76" s="71"/>
-      <c r="AF76" s="72"/>
+      <c r="AD76" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE76" s="70"/>
+      <c r="AF76" s="71"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="70"/>
-      <c r="AI76" s="71"/>
-      <c r="AJ76" s="72"/>
+      <c r="AH76" s="69"/>
+      <c r="AI76" s="70"/>
+      <c r="AJ76" s="71"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="70"/>
-      <c r="AM76" s="71"/>
-      <c r="AN76" s="72"/>
+      <c r="AL76" s="69"/>
+      <c r="AM76" s="70"/>
+      <c r="AN76" s="71"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
       <c r="AR76" s="24"/>
     </row>
-    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
-      <c r="B77" s="76"/>
-      <c r="C77" s="77"/>
-      <c r="D77" s="78"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="67"/>
+      <c r="D77" s="68"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="76"/>
-      <c r="G77" s="77"/>
-      <c r="H77" s="78"/>
+      <c r="F77" s="66"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="68"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="76"/>
-      <c r="K77" s="77"/>
-      <c r="L77" s="78"/>
+      <c r="J77" s="66"/>
+      <c r="K77" s="67"/>
+      <c r="L77" s="68"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="76"/>
-      <c r="O77" s="77"/>
-      <c r="P77" s="78"/>
+      <c r="N77" s="66"/>
+      <c r="O77" s="67"/>
+      <c r="P77" s="68"/>
       <c r="Q77" s="32"/>
-      <c r="R77" s="76"/>
-      <c r="S77" s="77"/>
-      <c r="T77" s="78"/>
+      <c r="R77" s="66"/>
+      <c r="S77" s="67"/>
+      <c r="T77" s="68"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="76"/>
-      <c r="W77" s="77"/>
-      <c r="X77" s="78"/>
+      <c r="V77" s="66"/>
+      <c r="W77" s="67"/>
+      <c r="X77" s="68"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="76"/>
-      <c r="AA77" s="77"/>
-      <c r="AB77" s="78"/>
+      <c r="Z77" s="66"/>
+      <c r="AA77" s="67"/>
+      <c r="AB77" s="68"/>
       <c r="AC77" s="43"/>
-      <c r="AD77" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE77" s="77"/>
-      <c r="AF77" s="78"/>
+      <c r="AD77" s="66" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE77" s="67"/>
+      <c r="AF77" s="68"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="76"/>
-      <c r="AI77" s="77"/>
-      <c r="AJ77" s="78"/>
+      <c r="AH77" s="66"/>
+      <c r="AI77" s="67"/>
+      <c r="AJ77" s="68"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="76"/>
-      <c r="AM77" s="77"/>
-      <c r="AN77" s="78"/>
+      <c r="AL77" s="66"/>
+      <c r="AM77" s="67"/>
+      <c r="AN77" s="68"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
       <c r="AR77" s="24"/>
     </row>
-    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
-      <c r="B78" s="60"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="62"/>
+      <c r="B78" s="61"/>
+      <c r="C78" s="62"/>
+      <c r="D78" s="63"/>
       <c r="E78" s="31"/>
-      <c r="F78" s="60"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="62"/>
+      <c r="F78" s="61"/>
+      <c r="G78" s="62"/>
+      <c r="H78" s="63"/>
       <c r="I78" s="32"/>
-      <c r="J78" s="60"/>
-      <c r="K78" s="61"/>
-      <c r="L78" s="62"/>
+      <c r="J78" s="61"/>
+      <c r="K78" s="62"/>
+      <c r="L78" s="63"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="60"/>
-      <c r="O78" s="61"/>
-      <c r="P78" s="62"/>
+      <c r="N78" s="61"/>
+      <c r="O78" s="62"/>
+      <c r="P78" s="63"/>
       <c r="Q78" s="31"/>
-      <c r="R78" s="60"/>
-      <c r="S78" s="61"/>
-      <c r="T78" s="62"/>
+      <c r="R78" s="61"/>
+      <c r="S78" s="62"/>
+      <c r="T78" s="63"/>
       <c r="U78" s="32"/>
-      <c r="V78" s="60"/>
-      <c r="W78" s="61"/>
-      <c r="X78" s="62"/>
+      <c r="V78" s="61"/>
+      <c r="W78" s="62"/>
+      <c r="X78" s="63"/>
       <c r="Y78" s="32"/>
-      <c r="Z78" s="60"/>
-      <c r="AA78" s="61"/>
-      <c r="AB78" s="62"/>
+      <c r="Z78" s="61"/>
+      <c r="AA78" s="62"/>
+      <c r="AB78" s="63"/>
       <c r="AC78" s="43"/>
-      <c r="AD78" s="60" t="s">
+      <c r="AD78" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="AE78" s="61"/>
-      <c r="AF78" s="62"/>
+      <c r="AE78" s="62"/>
+      <c r="AF78" s="63"/>
       <c r="AG78" s="31"/>
-      <c r="AH78" s="60"/>
-      <c r="AI78" s="61"/>
-      <c r="AJ78" s="62"/>
+      <c r="AH78" s="61"/>
+      <c r="AI78" s="62"/>
+      <c r="AJ78" s="63"/>
       <c r="AK78" s="32"/>
-      <c r="AL78" s="60"/>
-      <c r="AM78" s="61"/>
-      <c r="AN78" s="62"/>
+      <c r="AL78" s="61"/>
+      <c r="AM78" s="62"/>
+      <c r="AN78" s="63"/>
       <c r="AO78" s="12"/>
       <c r="AP78" s="29"/>
       <c r="AQ78" s="26"/>
       <c r="AR78" s="24"/>
     </row>
-    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -6294,237 +6299,237 @@
       <c r="AQ79" s="26"/>
       <c r="AR79" s="24"/>
     </row>
-    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
-      <c r="B80" s="63"/>
-      <c r="C80" s="64"/>
+      <c r="B80" s="78"/>
+      <c r="C80" s="79"/>
       <c r="D80" s="57"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="63"/>
-      <c r="G80" s="64"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="79"/>
       <c r="H80" s="57"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="63"/>
-      <c r="K80" s="64"/>
+      <c r="J80" s="78"/>
+      <c r="K80" s="79"/>
       <c r="L80" s="57"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="65"/>
-      <c r="O80" s="66"/>
+      <c r="N80" s="64"/>
+      <c r="O80" s="65"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="32"/>
-      <c r="R80" s="65"/>
-      <c r="S80" s="66"/>
+      <c r="R80" s="64"/>
+      <c r="S80" s="65"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="65"/>
-      <c r="W80" s="66"/>
+      <c r="V80" s="64"/>
+      <c r="W80" s="65"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="65"/>
-      <c r="AA80" s="66"/>
+      <c r="Z80" s="64"/>
+      <c r="AA80" s="65"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="65"/>
-      <c r="AE80" s="66"/>
+      <c r="AD80" s="64"/>
+      <c r="AE80" s="65"/>
       <c r="AF80" s="34"/>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="65"/>
-      <c r="AI80" s="66"/>
+      <c r="AH80" s="64"/>
+      <c r="AI80" s="65"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="65"/>
-      <c r="AM80" s="66"/>
+      <c r="AL80" s="64"/>
+      <c r="AM80" s="65"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
       <c r="AQ80" s="26"/>
       <c r="AR80" s="24"/>
     </row>
-    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
-      <c r="B81" s="79"/>
-      <c r="C81" s="80"/>
-      <c r="D81" s="81"/>
+      <c r="B81" s="80"/>
+      <c r="C81" s="81"/>
+      <c r="D81" s="82"/>
       <c r="E81" s="32"/>
-      <c r="F81" s="79"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="81"/>
+      <c r="F81" s="80"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="82"/>
       <c r="I81" s="32"/>
-      <c r="J81" s="79"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="81"/>
+      <c r="J81" s="80"/>
+      <c r="K81" s="81"/>
+      <c r="L81" s="82"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="67"/>
-      <c r="O81" s="68"/>
-      <c r="P81" s="69"/>
+      <c r="N81" s="75"/>
+      <c r="O81" s="76"/>
+      <c r="P81" s="77"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="67"/>
-      <c r="S81" s="68"/>
-      <c r="T81" s="69"/>
+      <c r="R81" s="75"/>
+      <c r="S81" s="76"/>
+      <c r="T81" s="77"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="67"/>
-      <c r="W81" s="68"/>
-      <c r="X81" s="69"/>
+      <c r="V81" s="75"/>
+      <c r="W81" s="76"/>
+      <c r="X81" s="77"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="67"/>
-      <c r="AA81" s="68"/>
-      <c r="AB81" s="69"/>
+      <c r="Z81" s="75"/>
+      <c r="AA81" s="76"/>
+      <c r="AB81" s="77"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="67"/>
-      <c r="AE81" s="68"/>
-      <c r="AF81" s="69"/>
+      <c r="AD81" s="75"/>
+      <c r="AE81" s="76"/>
+      <c r="AF81" s="77"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="67"/>
-      <c r="AI81" s="68"/>
-      <c r="AJ81" s="69"/>
+      <c r="AH81" s="75"/>
+      <c r="AI81" s="76"/>
+      <c r="AJ81" s="77"/>
       <c r="AK81" s="32"/>
-      <c r="AL81" s="67"/>
-      <c r="AM81" s="68"/>
-      <c r="AN81" s="69"/>
+      <c r="AL81" s="75"/>
+      <c r="AM81" s="76"/>
+      <c r="AN81" s="77"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
       <c r="AR81" s="24"/>
     </row>
-    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
-      <c r="B82" s="82"/>
-      <c r="C82" s="83"/>
-      <c r="D82" s="84"/>
+      <c r="B82" s="83"/>
+      <c r="C82" s="84"/>
+      <c r="D82" s="85"/>
       <c r="E82" s="32"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="83"/>
-      <c r="H82" s="84"/>
+      <c r="F82" s="83"/>
+      <c r="G82" s="84"/>
+      <c r="H82" s="85"/>
       <c r="I82" s="32"/>
-      <c r="J82" s="82"/>
-      <c r="K82" s="83"/>
-      <c r="L82" s="84"/>
+      <c r="J82" s="83"/>
+      <c r="K82" s="84"/>
+      <c r="L82" s="85"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="70"/>
-      <c r="O82" s="71"/>
-      <c r="P82" s="72"/>
+      <c r="N82" s="69"/>
+      <c r="O82" s="70"/>
+      <c r="P82" s="71"/>
       <c r="Q82" s="32"/>
-      <c r="R82" s="70"/>
-      <c r="S82" s="71"/>
-      <c r="T82" s="72"/>
+      <c r="R82" s="69"/>
+      <c r="S82" s="70"/>
+      <c r="T82" s="71"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="70"/>
-      <c r="W82" s="71"/>
-      <c r="X82" s="72"/>
+      <c r="V82" s="69"/>
+      <c r="W82" s="70"/>
+      <c r="X82" s="71"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="70"/>
-      <c r="AA82" s="71"/>
-      <c r="AB82" s="72"/>
+      <c r="Z82" s="69"/>
+      <c r="AA82" s="70"/>
+      <c r="AB82" s="71"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="70"/>
-      <c r="AE82" s="71"/>
-      <c r="AF82" s="72"/>
+      <c r="AD82" s="69"/>
+      <c r="AE82" s="70"/>
+      <c r="AF82" s="71"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="70"/>
-      <c r="AI82" s="71"/>
-      <c r="AJ82" s="72"/>
+      <c r="AH82" s="69"/>
+      <c r="AI82" s="70"/>
+      <c r="AJ82" s="71"/>
       <c r="AK82" s="32"/>
-      <c r="AL82" s="70"/>
-      <c r="AM82" s="71"/>
-      <c r="AN82" s="72"/>
+      <c r="AL82" s="69"/>
+      <c r="AM82" s="70"/>
+      <c r="AN82" s="71"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
       <c r="AR82" s="24"/>
     </row>
-    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
-      <c r="B83" s="76"/>
-      <c r="C83" s="77"/>
-      <c r="D83" s="78"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="68"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="76"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="78"/>
+      <c r="F83" s="66"/>
+      <c r="G83" s="67"/>
+      <c r="H83" s="68"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="76"/>
-      <c r="K83" s="77"/>
-      <c r="L83" s="78"/>
+      <c r="J83" s="66"/>
+      <c r="K83" s="67"/>
+      <c r="L83" s="68"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="76"/>
-      <c r="O83" s="77"/>
-      <c r="P83" s="78"/>
+      <c r="N83" s="66"/>
+      <c r="O83" s="67"/>
+      <c r="P83" s="68"/>
       <c r="Q83" s="32"/>
-      <c r="R83" s="76"/>
-      <c r="S83" s="77"/>
-      <c r="T83" s="78"/>
+      <c r="R83" s="66"/>
+      <c r="S83" s="67"/>
+      <c r="T83" s="68"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="76"/>
-      <c r="W83" s="77"/>
-      <c r="X83" s="78"/>
+      <c r="V83" s="66"/>
+      <c r="W83" s="67"/>
+      <c r="X83" s="68"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="76"/>
-      <c r="AA83" s="77"/>
-      <c r="AB83" s="78"/>
+      <c r="Z83" s="66"/>
+      <c r="AA83" s="67"/>
+      <c r="AB83" s="68"/>
       <c r="AC83" s="31"/>
-      <c r="AD83" s="76"/>
-      <c r="AE83" s="77"/>
-      <c r="AF83" s="78"/>
+      <c r="AD83" s="66"/>
+      <c r="AE83" s="67"/>
+      <c r="AF83" s="68"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="76"/>
-      <c r="AI83" s="77"/>
-      <c r="AJ83" s="78"/>
+      <c r="AH83" s="66"/>
+      <c r="AI83" s="67"/>
+      <c r="AJ83" s="68"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="76"/>
-      <c r="AM83" s="77"/>
-      <c r="AN83" s="78"/>
+      <c r="AL83" s="66"/>
+      <c r="AM83" s="67"/>
+      <c r="AN83" s="68"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
       <c r="AR83" s="24"/>
     </row>
-    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12"/>
-      <c r="B84" s="60"/>
-      <c r="C84" s="61"/>
-      <c r="D84" s="62"/>
+      <c r="B84" s="61"/>
+      <c r="C84" s="62"/>
+      <c r="D84" s="63"/>
       <c r="E84" s="31"/>
-      <c r="F84" s="60"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="62"/>
+      <c r="F84" s="61"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="63"/>
       <c r="I84" s="32"/>
-      <c r="J84" s="60"/>
-      <c r="K84" s="61"/>
-      <c r="L84" s="62"/>
+      <c r="J84" s="61"/>
+      <c r="K84" s="62"/>
+      <c r="L84" s="63"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="60"/>
-      <c r="O84" s="61"/>
-      <c r="P84" s="62"/>
+      <c r="N84" s="61"/>
+      <c r="O84" s="62"/>
+      <c r="P84" s="63"/>
       <c r="Q84" s="31"/>
-      <c r="R84" s="60"/>
-      <c r="S84" s="61"/>
-      <c r="T84" s="62"/>
+      <c r="R84" s="61"/>
+      <c r="S84" s="62"/>
+      <c r="T84" s="63"/>
       <c r="U84" s="32"/>
-      <c r="V84" s="60"/>
-      <c r="W84" s="61"/>
-      <c r="X84" s="62"/>
+      <c r="V84" s="61"/>
+      <c r="W84" s="62"/>
+      <c r="X84" s="63"/>
       <c r="Y84" s="31"/>
-      <c r="Z84" s="60"/>
-      <c r="AA84" s="61"/>
-      <c r="AB84" s="62"/>
+      <c r="Z84" s="61"/>
+      <c r="AA84" s="62"/>
+      <c r="AB84" s="63"/>
       <c r="AC84" s="31"/>
-      <c r="AD84" s="60"/>
-      <c r="AE84" s="61"/>
-      <c r="AF84" s="62"/>
+      <c r="AD84" s="61"/>
+      <c r="AE84" s="62"/>
+      <c r="AF84" s="63"/>
       <c r="AG84" s="31"/>
-      <c r="AH84" s="60"/>
-      <c r="AI84" s="61"/>
-      <c r="AJ84" s="62"/>
+      <c r="AH84" s="61"/>
+      <c r="AI84" s="62"/>
+      <c r="AJ84" s="63"/>
       <c r="AK84" s="32"/>
-      <c r="AL84" s="60"/>
-      <c r="AM84" s="61"/>
-      <c r="AN84" s="62"/>
+      <c r="AL84" s="61"/>
+      <c r="AM84" s="62"/>
+      <c r="AN84" s="63"/>
       <c r="AO84" s="12"/>
       <c r="AP84" s="29"/>
       <c r="AQ84" s="26"/>
       <c r="AR84" s="24"/>
     </row>
-    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -6570,237 +6575,237 @@
       <c r="AQ85" s="26"/>
       <c r="AR85" s="24"/>
     </row>
-    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="64"/>
+      <c r="B86" s="78"/>
+      <c r="C86" s="79"/>
       <c r="D86" s="57"/>
       <c r="E86" s="32"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="64"/>
+      <c r="F86" s="78"/>
+      <c r="G86" s="79"/>
       <c r="H86" s="57"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="64"/>
+      <c r="J86" s="78"/>
+      <c r="K86" s="79"/>
       <c r="L86" s="57"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="65"/>
-      <c r="O86" s="66"/>
+      <c r="N86" s="64"/>
+      <c r="O86" s="65"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="65"/>
-      <c r="S86" s="66"/>
+      <c r="R86" s="64"/>
+      <c r="S86" s="65"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="65"/>
-      <c r="W86" s="66"/>
+      <c r="V86" s="64"/>
+      <c r="W86" s="65"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="65"/>
-      <c r="AA86" s="66"/>
+      <c r="Z86" s="64"/>
+      <c r="AA86" s="65"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="65"/>
-      <c r="AE86" s="66"/>
+      <c r="AD86" s="64"/>
+      <c r="AE86" s="65"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="32"/>
-      <c r="AH86" s="65"/>
-      <c r="AI86" s="66"/>
+      <c r="AH86" s="64"/>
+      <c r="AI86" s="65"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="65"/>
-      <c r="AM86" s="66"/>
+      <c r="AL86" s="64"/>
+      <c r="AM86" s="65"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
       <c r="AQ86" s="26"/>
       <c r="AR86" s="24"/>
     </row>
-    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
-      <c r="B87" s="79"/>
-      <c r="C87" s="80"/>
-      <c r="D87" s="81"/>
+      <c r="B87" s="80"/>
+      <c r="C87" s="81"/>
+      <c r="D87" s="82"/>
       <c r="E87" s="32"/>
-      <c r="F87" s="79"/>
-      <c r="G87" s="80"/>
-      <c r="H87" s="81"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="81"/>
+      <c r="H87" s="82"/>
       <c r="I87" s="32"/>
-      <c r="J87" s="79"/>
-      <c r="K87" s="80"/>
-      <c r="L87" s="81"/>
+      <c r="J87" s="80"/>
+      <c r="K87" s="81"/>
+      <c r="L87" s="82"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="67"/>
-      <c r="O87" s="68"/>
-      <c r="P87" s="69"/>
+      <c r="N87" s="75"/>
+      <c r="O87" s="76"/>
+      <c r="P87" s="77"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="67"/>
-      <c r="S87" s="68"/>
-      <c r="T87" s="69"/>
+      <c r="R87" s="75"/>
+      <c r="S87" s="76"/>
+      <c r="T87" s="77"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="67"/>
-      <c r="W87" s="68"/>
-      <c r="X87" s="69"/>
+      <c r="V87" s="75"/>
+      <c r="W87" s="76"/>
+      <c r="X87" s="77"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="67"/>
-      <c r="AA87" s="68"/>
-      <c r="AB87" s="69"/>
+      <c r="Z87" s="75"/>
+      <c r="AA87" s="76"/>
+      <c r="AB87" s="77"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="67"/>
-      <c r="AE87" s="68"/>
-      <c r="AF87" s="69"/>
+      <c r="AD87" s="75"/>
+      <c r="AE87" s="76"/>
+      <c r="AF87" s="77"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="67"/>
-      <c r="AI87" s="68"/>
-      <c r="AJ87" s="69"/>
+      <c r="AH87" s="75"/>
+      <c r="AI87" s="76"/>
+      <c r="AJ87" s="77"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="67"/>
-      <c r="AM87" s="68"/>
-      <c r="AN87" s="69"/>
+      <c r="AL87" s="75"/>
+      <c r="AM87" s="76"/>
+      <c r="AN87" s="77"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
       <c r="AR87" s="24"/>
     </row>
-    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
-      <c r="B88" s="82"/>
-      <c r="C88" s="83"/>
-      <c r="D88" s="84"/>
+      <c r="B88" s="83"/>
+      <c r="C88" s="84"/>
+      <c r="D88" s="85"/>
       <c r="E88" s="32"/>
-      <c r="F88" s="82"/>
-      <c r="G88" s="83"/>
-      <c r="H88" s="84"/>
+      <c r="F88" s="83"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="85"/>
       <c r="I88" s="32"/>
-      <c r="J88" s="82"/>
-      <c r="K88" s="83"/>
-      <c r="L88" s="84"/>
+      <c r="J88" s="83"/>
+      <c r="K88" s="84"/>
+      <c r="L88" s="85"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="70"/>
-      <c r="O88" s="71"/>
-      <c r="P88" s="72"/>
+      <c r="N88" s="69"/>
+      <c r="O88" s="70"/>
+      <c r="P88" s="71"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="70"/>
-      <c r="S88" s="71"/>
-      <c r="T88" s="72"/>
+      <c r="R88" s="69"/>
+      <c r="S88" s="70"/>
+      <c r="T88" s="71"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="70"/>
-      <c r="W88" s="71"/>
-      <c r="X88" s="72"/>
+      <c r="V88" s="69"/>
+      <c r="W88" s="70"/>
+      <c r="X88" s="71"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="70"/>
-      <c r="AA88" s="71"/>
-      <c r="AB88" s="72"/>
+      <c r="Z88" s="69"/>
+      <c r="AA88" s="70"/>
+      <c r="AB88" s="71"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="70"/>
-      <c r="AE88" s="71"/>
-      <c r="AF88" s="72"/>
+      <c r="AD88" s="69"/>
+      <c r="AE88" s="70"/>
+      <c r="AF88" s="71"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="70"/>
-      <c r="AI88" s="71"/>
-      <c r="AJ88" s="72"/>
+      <c r="AH88" s="69"/>
+      <c r="AI88" s="70"/>
+      <c r="AJ88" s="71"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="70"/>
-      <c r="AM88" s="71"/>
-      <c r="AN88" s="72"/>
+      <c r="AL88" s="69"/>
+      <c r="AM88" s="70"/>
+      <c r="AN88" s="71"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
       <c r="AR88" s="24"/>
     </row>
-    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
-      <c r="B89" s="76"/>
-      <c r="C89" s="77"/>
-      <c r="D89" s="78"/>
+      <c r="B89" s="66"/>
+      <c r="C89" s="67"/>
+      <c r="D89" s="68"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="76"/>
-      <c r="G89" s="77"/>
-      <c r="H89" s="78"/>
+      <c r="F89" s="66"/>
+      <c r="G89" s="67"/>
+      <c r="H89" s="68"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="76"/>
-      <c r="K89" s="77"/>
-      <c r="L89" s="78"/>
+      <c r="J89" s="66"/>
+      <c r="K89" s="67"/>
+      <c r="L89" s="68"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="76"/>
-      <c r="O89" s="77"/>
-      <c r="P89" s="78"/>
+      <c r="N89" s="66"/>
+      <c r="O89" s="67"/>
+      <c r="P89" s="68"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="76"/>
-      <c r="S89" s="77"/>
-      <c r="T89" s="78"/>
+      <c r="R89" s="66"/>
+      <c r="S89" s="67"/>
+      <c r="T89" s="68"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="76"/>
-      <c r="W89" s="77"/>
-      <c r="X89" s="78"/>
+      <c r="V89" s="66"/>
+      <c r="W89" s="67"/>
+      <c r="X89" s="68"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="76"/>
-      <c r="AA89" s="77"/>
-      <c r="AB89" s="78"/>
+      <c r="Z89" s="66"/>
+      <c r="AA89" s="67"/>
+      <c r="AB89" s="68"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="76"/>
-      <c r="AE89" s="77"/>
-      <c r="AF89" s="78"/>
+      <c r="AD89" s="66"/>
+      <c r="AE89" s="67"/>
+      <c r="AF89" s="68"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="76"/>
-      <c r="AI89" s="77"/>
-      <c r="AJ89" s="78"/>
+      <c r="AH89" s="66"/>
+      <c r="AI89" s="67"/>
+      <c r="AJ89" s="68"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="76"/>
-      <c r="AM89" s="77"/>
-      <c r="AN89" s="78"/>
+      <c r="AL89" s="66"/>
+      <c r="AM89" s="67"/>
+      <c r="AN89" s="68"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
       <c r="AR89" s="24"/>
     </row>
-    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="12"/>
-      <c r="B90" s="60"/>
-      <c r="C90" s="61"/>
-      <c r="D90" s="62"/>
+      <c r="B90" s="61"/>
+      <c r="C90" s="62"/>
+      <c r="D90" s="63"/>
       <c r="E90" s="31"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="62"/>
+      <c r="F90" s="61"/>
+      <c r="G90" s="62"/>
+      <c r="H90" s="63"/>
       <c r="I90" s="32"/>
-      <c r="J90" s="60"/>
-      <c r="K90" s="61"/>
-      <c r="L90" s="62"/>
+      <c r="J90" s="61"/>
+      <c r="K90" s="62"/>
+      <c r="L90" s="63"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="60"/>
-      <c r="O90" s="61"/>
-      <c r="P90" s="62"/>
+      <c r="N90" s="61"/>
+      <c r="O90" s="62"/>
+      <c r="P90" s="63"/>
       <c r="Q90" s="31"/>
-      <c r="R90" s="60"/>
-      <c r="S90" s="61"/>
-      <c r="T90" s="62"/>
+      <c r="R90" s="61"/>
+      <c r="S90" s="62"/>
+      <c r="T90" s="63"/>
       <c r="U90" s="32"/>
-      <c r="V90" s="60"/>
-      <c r="W90" s="61"/>
-      <c r="X90" s="62"/>
+      <c r="V90" s="61"/>
+      <c r="W90" s="62"/>
+      <c r="X90" s="63"/>
       <c r="Y90" s="31"/>
-      <c r="Z90" s="60"/>
-      <c r="AA90" s="61"/>
-      <c r="AB90" s="62"/>
+      <c r="Z90" s="61"/>
+      <c r="AA90" s="62"/>
+      <c r="AB90" s="63"/>
       <c r="AC90" s="31"/>
-      <c r="AD90" s="60"/>
-      <c r="AE90" s="61"/>
-      <c r="AF90" s="62"/>
+      <c r="AD90" s="61"/>
+      <c r="AE90" s="62"/>
+      <c r="AF90" s="63"/>
       <c r="AG90" s="31"/>
-      <c r="AH90" s="60"/>
-      <c r="AI90" s="61"/>
-      <c r="AJ90" s="62"/>
+      <c r="AH90" s="61"/>
+      <c r="AI90" s="62"/>
+      <c r="AJ90" s="63"/>
       <c r="AK90" s="32"/>
-      <c r="AL90" s="60"/>
-      <c r="AM90" s="61"/>
-      <c r="AN90" s="62"/>
+      <c r="AL90" s="61"/>
+      <c r="AM90" s="62"/>
+      <c r="AN90" s="63"/>
       <c r="AO90" s="12"/>
       <c r="AP90" s="29"/>
       <c r="AQ90" s="26"/>
       <c r="AR90" s="24"/>
     </row>
-    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35"/>
@@ -6846,237 +6851,237 @@
       <c r="AQ91" s="26"/>
       <c r="AR91" s="24"/>
     </row>
-    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
-      <c r="B92" s="63"/>
-      <c r="C92" s="64"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="79"/>
       <c r="D92" s="57"/>
       <c r="E92" s="44"/>
-      <c r="F92" s="63"/>
-      <c r="G92" s="64"/>
+      <c r="F92" s="78"/>
+      <c r="G92" s="79"/>
       <c r="H92" s="57"/>
       <c r="I92" s="32"/>
-      <c r="J92" s="63"/>
-      <c r="K92" s="64"/>
+      <c r="J92" s="78"/>
+      <c r="K92" s="79"/>
       <c r="L92" s="57"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="65"/>
-      <c r="O92" s="66"/>
+      <c r="N92" s="64"/>
+      <c r="O92" s="65"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="32"/>
-      <c r="R92" s="65"/>
-      <c r="S92" s="66"/>
+      <c r="R92" s="64"/>
+      <c r="S92" s="65"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="65"/>
-      <c r="W92" s="66"/>
+      <c r="V92" s="64"/>
+      <c r="W92" s="65"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="65"/>
-      <c r="AA92" s="66"/>
+      <c r="Z92" s="64"/>
+      <c r="AA92" s="65"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="65"/>
-      <c r="AE92" s="66"/>
+      <c r="AD92" s="64"/>
+      <c r="AE92" s="65"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="65"/>
-      <c r="AI92" s="66"/>
+      <c r="AH92" s="64"/>
+      <c r="AI92" s="65"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="65"/>
-      <c r="AM92" s="66"/>
+      <c r="AL92" s="64"/>
+      <c r="AM92" s="65"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
       <c r="AQ92" s="26"/>
       <c r="AR92" s="24"/>
     </row>
-    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
-      <c r="B93" s="79"/>
-      <c r="C93" s="80"/>
-      <c r="D93" s="81"/>
+      <c r="B93" s="80"/>
+      <c r="C93" s="81"/>
+      <c r="D93" s="82"/>
       <c r="E93" s="43"/>
-      <c r="F93" s="79"/>
-      <c r="G93" s="80"/>
-      <c r="H93" s="81"/>
+      <c r="F93" s="80"/>
+      <c r="G93" s="81"/>
+      <c r="H93" s="82"/>
       <c r="I93" s="35"/>
-      <c r="J93" s="79"/>
-      <c r="K93" s="80"/>
-      <c r="L93" s="81"/>
+      <c r="J93" s="80"/>
+      <c r="K93" s="81"/>
+      <c r="L93" s="82"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="67"/>
-      <c r="O93" s="68"/>
-      <c r="P93" s="69"/>
+      <c r="N93" s="75"/>
+      <c r="O93" s="76"/>
+      <c r="P93" s="77"/>
       <c r="Q93" s="35"/>
-      <c r="R93" s="67"/>
-      <c r="S93" s="68"/>
-      <c r="T93" s="69"/>
+      <c r="R93" s="75"/>
+      <c r="S93" s="76"/>
+      <c r="T93" s="77"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="67"/>
-      <c r="W93" s="68"/>
-      <c r="X93" s="69"/>
+      <c r="V93" s="75"/>
+      <c r="W93" s="76"/>
+      <c r="X93" s="77"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="67"/>
-      <c r="AA93" s="68"/>
-      <c r="AB93" s="69"/>
+      <c r="Z93" s="75"/>
+      <c r="AA93" s="76"/>
+      <c r="AB93" s="77"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="67"/>
-      <c r="AE93" s="68"/>
-      <c r="AF93" s="69"/>
+      <c r="AD93" s="75"/>
+      <c r="AE93" s="76"/>
+      <c r="AF93" s="77"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="67"/>
-      <c r="AI93" s="68"/>
-      <c r="AJ93" s="69"/>
+      <c r="AH93" s="75"/>
+      <c r="AI93" s="76"/>
+      <c r="AJ93" s="77"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="67"/>
-      <c r="AM93" s="68"/>
-      <c r="AN93" s="69"/>
+      <c r="AL93" s="75"/>
+      <c r="AM93" s="76"/>
+      <c r="AN93" s="77"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
       <c r="AR93" s="24"/>
     </row>
-    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
-      <c r="B94" s="82"/>
-      <c r="C94" s="83"/>
-      <c r="D94" s="84"/>
+      <c r="B94" s="83"/>
+      <c r="C94" s="84"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="44"/>
-      <c r="F94" s="82"/>
-      <c r="G94" s="83"/>
-      <c r="H94" s="84"/>
+      <c r="F94" s="83"/>
+      <c r="G94" s="84"/>
+      <c r="H94" s="85"/>
       <c r="I94" s="31"/>
-      <c r="J94" s="82"/>
-      <c r="K94" s="83"/>
-      <c r="L94" s="84"/>
+      <c r="J94" s="83"/>
+      <c r="K94" s="84"/>
+      <c r="L94" s="85"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="70"/>
-      <c r="O94" s="71"/>
-      <c r="P94" s="72"/>
+      <c r="N94" s="69"/>
+      <c r="O94" s="70"/>
+      <c r="P94" s="71"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="70"/>
-      <c r="S94" s="71"/>
-      <c r="T94" s="72"/>
+      <c r="R94" s="69"/>
+      <c r="S94" s="70"/>
+      <c r="T94" s="71"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="70"/>
-      <c r="W94" s="71"/>
-      <c r="X94" s="72"/>
+      <c r="V94" s="69"/>
+      <c r="W94" s="70"/>
+      <c r="X94" s="71"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="70"/>
-      <c r="AA94" s="71"/>
-      <c r="AB94" s="72"/>
+      <c r="Z94" s="69"/>
+      <c r="AA94" s="70"/>
+      <c r="AB94" s="71"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="70"/>
-      <c r="AE94" s="71"/>
-      <c r="AF94" s="72"/>
+      <c r="AD94" s="69"/>
+      <c r="AE94" s="70"/>
+      <c r="AF94" s="71"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="70"/>
-      <c r="AI94" s="71"/>
-      <c r="AJ94" s="72"/>
+      <c r="AH94" s="69"/>
+      <c r="AI94" s="70"/>
+      <c r="AJ94" s="71"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="70"/>
-      <c r="AM94" s="71"/>
-      <c r="AN94" s="72"/>
+      <c r="AL94" s="69"/>
+      <c r="AM94" s="70"/>
+      <c r="AN94" s="71"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
       <c r="AR94" s="24"/>
     </row>
-    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
-      <c r="B95" s="76"/>
-      <c r="C95" s="77"/>
-      <c r="D95" s="78"/>
+      <c r="B95" s="66"/>
+      <c r="C95" s="67"/>
+      <c r="D95" s="68"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="76"/>
-      <c r="G95" s="77"/>
-      <c r="H95" s="78"/>
+      <c r="F95" s="66"/>
+      <c r="G95" s="67"/>
+      <c r="H95" s="68"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="76"/>
-      <c r="K95" s="77"/>
-      <c r="L95" s="78"/>
+      <c r="J95" s="66"/>
+      <c r="K95" s="67"/>
+      <c r="L95" s="68"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="76"/>
-      <c r="O95" s="77"/>
-      <c r="P95" s="78"/>
+      <c r="N95" s="66"/>
+      <c r="O95" s="67"/>
+      <c r="P95" s="68"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="76"/>
-      <c r="S95" s="77"/>
-      <c r="T95" s="78"/>
+      <c r="R95" s="66"/>
+      <c r="S95" s="67"/>
+      <c r="T95" s="68"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="76"/>
-      <c r="W95" s="77"/>
-      <c r="X95" s="78"/>
+      <c r="V95" s="66"/>
+      <c r="W95" s="67"/>
+      <c r="X95" s="68"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="76"/>
-      <c r="AA95" s="77"/>
-      <c r="AB95" s="78"/>
+      <c r="Z95" s="66"/>
+      <c r="AA95" s="67"/>
+      <c r="AB95" s="68"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="76"/>
-      <c r="AE95" s="77"/>
-      <c r="AF95" s="78"/>
+      <c r="AD95" s="66"/>
+      <c r="AE95" s="67"/>
+      <c r="AF95" s="68"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="76"/>
-      <c r="AI95" s="77"/>
-      <c r="AJ95" s="78"/>
+      <c r="AH95" s="66"/>
+      <c r="AI95" s="67"/>
+      <c r="AJ95" s="68"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="76"/>
-      <c r="AM95" s="77"/>
-      <c r="AN95" s="78"/>
+      <c r="AL95" s="66"/>
+      <c r="AM95" s="67"/>
+      <c r="AN95" s="68"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
       <c r="AR95" s="24"/>
     </row>
-    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="12"/>
-      <c r="B96" s="60"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="62"/>
+      <c r="B96" s="61"/>
+      <c r="C96" s="62"/>
+      <c r="D96" s="63"/>
       <c r="E96" s="44"/>
-      <c r="F96" s="60"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="62"/>
+      <c r="F96" s="61"/>
+      <c r="G96" s="62"/>
+      <c r="H96" s="63"/>
       <c r="I96" s="32"/>
-      <c r="J96" s="60"/>
-      <c r="K96" s="61"/>
-      <c r="L96" s="62"/>
+      <c r="J96" s="61"/>
+      <c r="K96" s="62"/>
+      <c r="L96" s="63"/>
       <c r="M96" s="26"/>
-      <c r="N96" s="60"/>
-      <c r="O96" s="61"/>
-      <c r="P96" s="62"/>
+      <c r="N96" s="61"/>
+      <c r="O96" s="62"/>
+      <c r="P96" s="63"/>
       <c r="Q96" s="44"/>
-      <c r="R96" s="60"/>
-      <c r="S96" s="61"/>
-      <c r="T96" s="62"/>
+      <c r="R96" s="61"/>
+      <c r="S96" s="62"/>
+      <c r="T96" s="63"/>
       <c r="U96" s="32"/>
-      <c r="V96" s="60"/>
-      <c r="W96" s="61"/>
-      <c r="X96" s="62"/>
+      <c r="V96" s="61"/>
+      <c r="W96" s="62"/>
+      <c r="X96" s="63"/>
       <c r="Y96" s="31"/>
-      <c r="Z96" s="60"/>
-      <c r="AA96" s="61"/>
-      <c r="AB96" s="62"/>
+      <c r="Z96" s="61"/>
+      <c r="AA96" s="62"/>
+      <c r="AB96" s="63"/>
       <c r="AC96" s="44"/>
-      <c r="AD96" s="60"/>
-      <c r="AE96" s="61"/>
-      <c r="AF96" s="62"/>
+      <c r="AD96" s="61"/>
+      <c r="AE96" s="62"/>
+      <c r="AF96" s="63"/>
       <c r="AG96" s="44"/>
-      <c r="AH96" s="60"/>
-      <c r="AI96" s="61"/>
-      <c r="AJ96" s="62"/>
+      <c r="AH96" s="61"/>
+      <c r="AI96" s="62"/>
+      <c r="AJ96" s="63"/>
       <c r="AK96" s="32"/>
-      <c r="AL96" s="60"/>
-      <c r="AM96" s="61"/>
-      <c r="AN96" s="62"/>
+      <c r="AL96" s="61"/>
+      <c r="AM96" s="62"/>
+      <c r="AN96" s="63"/>
       <c r="AO96" s="12"/>
       <c r="AP96" s="29"/>
       <c r="AQ96" s="26"/>
       <c r="AR96" s="24"/>
     </row>
-    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35"/>
@@ -7122,237 +7127,237 @@
       <c r="AQ97" s="26"/>
       <c r="AR97" s="24"/>
     </row>
-    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12"/>
-      <c r="B98" s="63"/>
-      <c r="C98" s="64"/>
+      <c r="B98" s="78"/>
+      <c r="C98" s="79"/>
       <c r="D98" s="57"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="63"/>
-      <c r="G98" s="64"/>
+      <c r="F98" s="78"/>
+      <c r="G98" s="79"/>
       <c r="H98" s="57"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="63"/>
-      <c r="K98" s="64"/>
+      <c r="J98" s="78"/>
+      <c r="K98" s="79"/>
       <c r="L98" s="57"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="65"/>
-      <c r="O98" s="66"/>
+      <c r="N98" s="64"/>
+      <c r="O98" s="65"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="65"/>
-      <c r="S98" s="66"/>
+      <c r="R98" s="64"/>
+      <c r="S98" s="65"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="65"/>
-      <c r="W98" s="66"/>
+      <c r="V98" s="64"/>
+      <c r="W98" s="65"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="65"/>
-      <c r="AA98" s="66"/>
+      <c r="Z98" s="64"/>
+      <c r="AA98" s="65"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="65"/>
-      <c r="AE98" s="66"/>
+      <c r="AD98" s="64"/>
+      <c r="AE98" s="65"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="65"/>
-      <c r="AI98" s="66"/>
+      <c r="AH98" s="64"/>
+      <c r="AI98" s="65"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="65"/>
-      <c r="AM98" s="66"/>
+      <c r="AL98" s="64"/>
+      <c r="AM98" s="65"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
       <c r="AQ98" s="26"/>
       <c r="AR98" s="24"/>
     </row>
-    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
-      <c r="B99" s="79"/>
-      <c r="C99" s="80"/>
-      <c r="D99" s="81"/>
+      <c r="B99" s="80"/>
+      <c r="C99" s="81"/>
+      <c r="D99" s="82"/>
       <c r="E99" s="32"/>
-      <c r="F99" s="79"/>
-      <c r="G99" s="80"/>
-      <c r="H99" s="81"/>
+      <c r="F99" s="80"/>
+      <c r="G99" s="81"/>
+      <c r="H99" s="82"/>
       <c r="I99" s="35"/>
-      <c r="J99" s="79"/>
-      <c r="K99" s="80"/>
-      <c r="L99" s="81"/>
+      <c r="J99" s="80"/>
+      <c r="K99" s="81"/>
+      <c r="L99" s="82"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="67"/>
-      <c r="O99" s="68"/>
-      <c r="P99" s="69"/>
+      <c r="N99" s="75"/>
+      <c r="O99" s="76"/>
+      <c r="P99" s="77"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="67"/>
-      <c r="S99" s="68"/>
-      <c r="T99" s="69"/>
+      <c r="R99" s="75"/>
+      <c r="S99" s="76"/>
+      <c r="T99" s="77"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="67"/>
-      <c r="W99" s="68"/>
-      <c r="X99" s="69"/>
+      <c r="V99" s="75"/>
+      <c r="W99" s="76"/>
+      <c r="X99" s="77"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="67"/>
-      <c r="AA99" s="68"/>
-      <c r="AB99" s="69"/>
+      <c r="Z99" s="75"/>
+      <c r="AA99" s="76"/>
+      <c r="AB99" s="77"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="67"/>
-      <c r="AE99" s="68"/>
-      <c r="AF99" s="69"/>
+      <c r="AD99" s="75"/>
+      <c r="AE99" s="76"/>
+      <c r="AF99" s="77"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="67"/>
-      <c r="AI99" s="68"/>
-      <c r="AJ99" s="69"/>
+      <c r="AH99" s="75"/>
+      <c r="AI99" s="76"/>
+      <c r="AJ99" s="77"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="67"/>
-      <c r="AM99" s="68"/>
-      <c r="AN99" s="69"/>
+      <c r="AL99" s="75"/>
+      <c r="AM99" s="76"/>
+      <c r="AN99" s="77"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
       <c r="AR99" s="24"/>
     </row>
-    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
-      <c r="B100" s="82"/>
-      <c r="C100" s="83"/>
-      <c r="D100" s="84"/>
+      <c r="B100" s="83"/>
+      <c r="C100" s="84"/>
+      <c r="D100" s="85"/>
       <c r="E100" s="32"/>
-      <c r="F100" s="82"/>
-      <c r="G100" s="83"/>
-      <c r="H100" s="84"/>
+      <c r="F100" s="83"/>
+      <c r="G100" s="84"/>
+      <c r="H100" s="85"/>
       <c r="I100" s="31"/>
-      <c r="J100" s="82"/>
-      <c r="K100" s="83"/>
-      <c r="L100" s="84"/>
+      <c r="J100" s="83"/>
+      <c r="K100" s="84"/>
+      <c r="L100" s="85"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="70"/>
-      <c r="O100" s="71"/>
-      <c r="P100" s="72"/>
+      <c r="N100" s="69"/>
+      <c r="O100" s="70"/>
+      <c r="P100" s="71"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="70"/>
-      <c r="S100" s="71"/>
-      <c r="T100" s="72"/>
+      <c r="R100" s="69"/>
+      <c r="S100" s="70"/>
+      <c r="T100" s="71"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="70"/>
-      <c r="W100" s="71"/>
-      <c r="X100" s="72"/>
+      <c r="V100" s="69"/>
+      <c r="W100" s="70"/>
+      <c r="X100" s="71"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="70"/>
-      <c r="AA100" s="71"/>
-      <c r="AB100" s="72"/>
+      <c r="Z100" s="69"/>
+      <c r="AA100" s="70"/>
+      <c r="AB100" s="71"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="70"/>
-      <c r="AE100" s="71"/>
-      <c r="AF100" s="72"/>
+      <c r="AD100" s="69"/>
+      <c r="AE100" s="70"/>
+      <c r="AF100" s="71"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="70"/>
-      <c r="AI100" s="71"/>
-      <c r="AJ100" s="72"/>
+      <c r="AH100" s="69"/>
+      <c r="AI100" s="70"/>
+      <c r="AJ100" s="71"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="70"/>
-      <c r="AM100" s="71"/>
-      <c r="AN100" s="72"/>
+      <c r="AL100" s="69"/>
+      <c r="AM100" s="70"/>
+      <c r="AN100" s="71"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
       <c r="AR100" s="24"/>
     </row>
-    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
-      <c r="B101" s="76"/>
-      <c r="C101" s="77"/>
-      <c r="D101" s="78"/>
+      <c r="B101" s="66"/>
+      <c r="C101" s="67"/>
+      <c r="D101" s="68"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="76"/>
-      <c r="G101" s="77"/>
-      <c r="H101" s="78"/>
+      <c r="F101" s="66"/>
+      <c r="G101" s="67"/>
+      <c r="H101" s="68"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="76"/>
-      <c r="K101" s="77"/>
-      <c r="L101" s="78"/>
+      <c r="J101" s="66"/>
+      <c r="K101" s="67"/>
+      <c r="L101" s="68"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="76"/>
-      <c r="O101" s="77"/>
-      <c r="P101" s="78"/>
+      <c r="N101" s="66"/>
+      <c r="O101" s="67"/>
+      <c r="P101" s="68"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="76"/>
-      <c r="S101" s="77"/>
-      <c r="T101" s="78"/>
+      <c r="R101" s="66"/>
+      <c r="S101" s="67"/>
+      <c r="T101" s="68"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="76"/>
-      <c r="W101" s="77"/>
-      <c r="X101" s="78"/>
+      <c r="V101" s="66"/>
+      <c r="W101" s="67"/>
+      <c r="X101" s="68"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="76"/>
-      <c r="AA101" s="77"/>
-      <c r="AB101" s="78"/>
+      <c r="Z101" s="66"/>
+      <c r="AA101" s="67"/>
+      <c r="AB101" s="68"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="76"/>
-      <c r="AE101" s="77"/>
-      <c r="AF101" s="78"/>
+      <c r="AD101" s="66"/>
+      <c r="AE101" s="67"/>
+      <c r="AF101" s="68"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="76"/>
-      <c r="AI101" s="77"/>
-      <c r="AJ101" s="78"/>
+      <c r="AH101" s="66"/>
+      <c r="AI101" s="67"/>
+      <c r="AJ101" s="68"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="76"/>
-      <c r="AM101" s="77"/>
-      <c r="AN101" s="78"/>
+      <c r="AL101" s="66"/>
+      <c r="AM101" s="67"/>
+      <c r="AN101" s="68"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
       <c r="AR101" s="24"/>
     </row>
-    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
-      <c r="B102" s="60"/>
-      <c r="C102" s="61"/>
-      <c r="D102" s="62"/>
+      <c r="B102" s="61"/>
+      <c r="C102" s="62"/>
+      <c r="D102" s="63"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="60"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="62"/>
+      <c r="F102" s="61"/>
+      <c r="G102" s="62"/>
+      <c r="H102" s="63"/>
       <c r="I102" s="32"/>
-      <c r="J102" s="60"/>
-      <c r="K102" s="61"/>
-      <c r="L102" s="62"/>
+      <c r="J102" s="61"/>
+      <c r="K102" s="62"/>
+      <c r="L102" s="63"/>
       <c r="M102" s="26"/>
-      <c r="N102" s="60"/>
-      <c r="O102" s="61"/>
-      <c r="P102" s="62"/>
+      <c r="N102" s="61"/>
+      <c r="O102" s="62"/>
+      <c r="P102" s="63"/>
       <c r="Q102" s="31"/>
-      <c r="R102" s="60"/>
-      <c r="S102" s="61"/>
-      <c r="T102" s="62"/>
+      <c r="R102" s="61"/>
+      <c r="S102" s="62"/>
+      <c r="T102" s="63"/>
       <c r="U102" s="32"/>
-      <c r="V102" s="60"/>
-      <c r="W102" s="61"/>
-      <c r="X102" s="62"/>
+      <c r="V102" s="61"/>
+      <c r="W102" s="62"/>
+      <c r="X102" s="63"/>
       <c r="Y102" s="32"/>
-      <c r="Z102" s="60"/>
-      <c r="AA102" s="61"/>
-      <c r="AB102" s="62"/>
+      <c r="Z102" s="61"/>
+      <c r="AA102" s="62"/>
+      <c r="AB102" s="63"/>
       <c r="AC102" s="32"/>
-      <c r="AD102" s="60"/>
-      <c r="AE102" s="61"/>
-      <c r="AF102" s="62"/>
+      <c r="AD102" s="61"/>
+      <c r="AE102" s="62"/>
+      <c r="AF102" s="63"/>
       <c r="AG102" s="31"/>
-      <c r="AH102" s="60"/>
-      <c r="AI102" s="61"/>
-      <c r="AJ102" s="62"/>
+      <c r="AH102" s="61"/>
+      <c r="AI102" s="62"/>
+      <c r="AJ102" s="63"/>
       <c r="AK102" s="32"/>
-      <c r="AL102" s="60"/>
-      <c r="AM102" s="61"/>
-      <c r="AN102" s="62"/>
+      <c r="AL102" s="61"/>
+      <c r="AM102" s="62"/>
+      <c r="AN102" s="63"/>
       <c r="AO102" s="12"/>
       <c r="AP102" s="29"/>
       <c r="AQ102" s="26"/>
       <c r="AR102" s="24"/>
     </row>
-    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="12"/>
       <c r="B103" s="40"/>
       <c r="C103" s="33"/>
@@ -7398,7 +7403,7 @@
       <c r="AQ103" s="26"/>
       <c r="AR103" s="26"/>
     </row>
-    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
       <c r="D104" s="33"/>
@@ -7415,73 +7420,73 @@
       <c r="AQ104" s="26"/>
       <c r="AR104" s="26"/>
     </row>
-    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="65"/>
-      <c r="C105" s="66"/>
+    <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="64"/>
+      <c r="C105" s="65"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="65"/>
-      <c r="G105" s="66"/>
+      <c r="F105" s="64"/>
+      <c r="G105" s="65"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="65"/>
-      <c r="K105" s="66"/>
+      <c r="J105" s="64"/>
+      <c r="K105" s="65"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
-    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="67"/>
-      <c r="C106" s="68"/>
-      <c r="D106" s="69"/>
+    <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="75"/>
+      <c r="C106" s="76"/>
+      <c r="D106" s="77"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="68"/>
-      <c r="H106" s="69"/>
+      <c r="F106" s="75"/>
+      <c r="G106" s="76"/>
+      <c r="H106" s="77"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="67"/>
-      <c r="K106" s="68"/>
-      <c r="L106" s="69"/>
-    </row>
-    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="70"/>
-      <c r="C107" s="71"/>
-      <c r="D107" s="72"/>
+      <c r="J106" s="75"/>
+      <c r="K106" s="76"/>
+      <c r="L106" s="77"/>
+    </row>
+    <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="69"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="71"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="70"/>
-      <c r="G107" s="71"/>
-      <c r="H107" s="72"/>
+      <c r="F107" s="69"/>
+      <c r="G107" s="70"/>
+      <c r="H107" s="71"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="70"/>
-      <c r="K107" s="71"/>
-      <c r="L107" s="72"/>
-    </row>
-    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="76"/>
-      <c r="C108" s="77"/>
-      <c r="D108" s="78"/>
+      <c r="J107" s="69"/>
+      <c r="K107" s="70"/>
+      <c r="L107" s="71"/>
+    </row>
+    <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="66"/>
+      <c r="C108" s="67"/>
+      <c r="D108" s="68"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="76"/>
-      <c r="G108" s="77"/>
-      <c r="H108" s="78"/>
+      <c r="F108" s="66"/>
+      <c r="G108" s="67"/>
+      <c r="H108" s="68"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="76"/>
-      <c r="K108" s="77"/>
-      <c r="L108" s="78"/>
-    </row>
-    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="60"/>
-      <c r="C109" s="61"/>
-      <c r="D109" s="62"/>
+      <c r="J108" s="66"/>
+      <c r="K108" s="67"/>
+      <c r="L108" s="68"/>
+    </row>
+    <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="61"/>
+      <c r="C109" s="62"/>
+      <c r="D109" s="63"/>
       <c r="E109" s="31"/>
-      <c r="F109" s="60"/>
-      <c r="G109" s="61"/>
-      <c r="H109" s="62"/>
+      <c r="F109" s="61"/>
+      <c r="G109" s="62"/>
+      <c r="H109" s="63"/>
       <c r="I109" s="31"/>
-      <c r="J109" s="60"/>
-      <c r="K109" s="61"/>
-      <c r="L109" s="62"/>
-    </row>
-    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J109" s="61"/>
+      <c r="K109" s="62"/>
+      <c r="L109" s="63"/>
+    </row>
+    <row r="110" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
@@ -7494,72 +7499,72 @@
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="65"/>
-      <c r="C111" s="66"/>
+    <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="64"/>
+      <c r="C111" s="65"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="65"/>
-      <c r="G111" s="66"/>
+      <c r="F111" s="64"/>
+      <c r="G111" s="65"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="65"/>
-      <c r="K111" s="66"/>
+      <c r="J111" s="64"/>
+      <c r="K111" s="65"/>
       <c r="L111" s="34"/>
     </row>
-    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="67"/>
-      <c r="C112" s="68"/>
-      <c r="D112" s="69"/>
+    <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="75"/>
+      <c r="C112" s="76"/>
+      <c r="D112" s="77"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="67"/>
-      <c r="G112" s="68"/>
-      <c r="H112" s="69"/>
+      <c r="F112" s="75"/>
+      <c r="G112" s="76"/>
+      <c r="H112" s="77"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="67"/>
-      <c r="K112" s="68"/>
-      <c r="L112" s="69"/>
-    </row>
-    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="70"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="72"/>
+      <c r="J112" s="75"/>
+      <c r="K112" s="76"/>
+      <c r="L112" s="77"/>
+    </row>
+    <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="69"/>
+      <c r="C113" s="70"/>
+      <c r="D113" s="71"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="70"/>
-      <c r="G113" s="71"/>
-      <c r="H113" s="72"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="70"/>
+      <c r="H113" s="71"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="70"/>
-      <c r="K113" s="71"/>
-      <c r="L113" s="72"/>
-    </row>
-    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="76"/>
-      <c r="C114" s="77"/>
-      <c r="D114" s="78"/>
+      <c r="J113" s="69"/>
+      <c r="K113" s="70"/>
+      <c r="L113" s="71"/>
+    </row>
+    <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="66"/>
+      <c r="C114" s="67"/>
+      <c r="D114" s="68"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="76"/>
-      <c r="G114" s="77"/>
-      <c r="H114" s="78"/>
+      <c r="F114" s="66"/>
+      <c r="G114" s="67"/>
+      <c r="H114" s="68"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="76"/>
-      <c r="K114" s="77"/>
-      <c r="L114" s="78"/>
-    </row>
-    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="60"/>
-      <c r="C115" s="61"/>
-      <c r="D115" s="62"/>
+      <c r="J114" s="66"/>
+      <c r="K114" s="67"/>
+      <c r="L114" s="68"/>
+    </row>
+    <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="61"/>
+      <c r="C115" s="62"/>
+      <c r="D115" s="63"/>
       <c r="E115" s="31"/>
-      <c r="F115" s="60"/>
-      <c r="G115" s="61"/>
-      <c r="H115" s="62"/>
+      <c r="F115" s="61"/>
+      <c r="G115" s="62"/>
+      <c r="H115" s="63"/>
       <c r="I115" s="31"/>
-      <c r="J115" s="60"/>
-      <c r="K115" s="61"/>
-      <c r="L115" s="62"/>
-    </row>
-    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J115" s="61"/>
+      <c r="K115" s="62"/>
+      <c r="L115" s="63"/>
+    </row>
+    <row r="116" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
@@ -7572,72 +7577,72 @@
       <c r="K116" s="35"/>
       <c r="L116" s="35"/>
     </row>
-    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="65"/>
-      <c r="C117" s="66"/>
+    <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="64"/>
+      <c r="C117" s="65"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="65"/>
-      <c r="G117" s="66"/>
+      <c r="F117" s="64"/>
+      <c r="G117" s="65"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="65"/>
-      <c r="K117" s="66"/>
+      <c r="J117" s="64"/>
+      <c r="K117" s="65"/>
       <c r="L117" s="34"/>
     </row>
-    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="67"/>
-      <c r="C118" s="68"/>
-      <c r="D118" s="69"/>
+    <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="75"/>
+      <c r="C118" s="76"/>
+      <c r="D118" s="77"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="67"/>
-      <c r="G118" s="68"/>
-      <c r="H118" s="69"/>
+      <c r="F118" s="75"/>
+      <c r="G118" s="76"/>
+      <c r="H118" s="77"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="67"/>
-      <c r="K118" s="68"/>
-      <c r="L118" s="69"/>
-    </row>
-    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="70"/>
-      <c r="C119" s="71"/>
-      <c r="D119" s="72"/>
+      <c r="J118" s="75"/>
+      <c r="K118" s="76"/>
+      <c r="L118" s="77"/>
+    </row>
+    <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="69"/>
+      <c r="C119" s="70"/>
+      <c r="D119" s="71"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="70"/>
-      <c r="G119" s="71"/>
-      <c r="H119" s="72"/>
+      <c r="F119" s="69"/>
+      <c r="G119" s="70"/>
+      <c r="H119" s="71"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="70"/>
-      <c r="K119" s="71"/>
-      <c r="L119" s="72"/>
-    </row>
-    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="76"/>
-      <c r="C120" s="77"/>
-      <c r="D120" s="78"/>
+      <c r="J119" s="69"/>
+      <c r="K119" s="70"/>
+      <c r="L119" s="71"/>
+    </row>
+    <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="66"/>
+      <c r="C120" s="67"/>
+      <c r="D120" s="68"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="76"/>
-      <c r="G120" s="77"/>
-      <c r="H120" s="78"/>
+      <c r="F120" s="66"/>
+      <c r="G120" s="67"/>
+      <c r="H120" s="68"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="76"/>
-      <c r="K120" s="77"/>
-      <c r="L120" s="78"/>
-    </row>
-    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="60"/>
-      <c r="C121" s="61"/>
-      <c r="D121" s="62"/>
+      <c r="J120" s="66"/>
+      <c r="K120" s="67"/>
+      <c r="L120" s="68"/>
+    </row>
+    <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="61"/>
+      <c r="C121" s="62"/>
+      <c r="D121" s="63"/>
       <c r="E121" s="31"/>
-      <c r="F121" s="60"/>
-      <c r="G121" s="61"/>
-      <c r="H121" s="62"/>
+      <c r="F121" s="61"/>
+      <c r="G121" s="62"/>
+      <c r="H121" s="63"/>
       <c r="I121" s="31"/>
-      <c r="J121" s="60"/>
-      <c r="K121" s="61"/>
-      <c r="L121" s="62"/>
-    </row>
-    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J121" s="61"/>
+      <c r="K121" s="62"/>
+      <c r="L121" s="63"/>
+    </row>
+    <row r="122" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
@@ -7650,72 +7655,72 @@
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
     </row>
-    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="65"/>
-      <c r="C123" s="66"/>
+    <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="64"/>
+      <c r="C123" s="65"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="65"/>
-      <c r="G123" s="66"/>
+      <c r="F123" s="64"/>
+      <c r="G123" s="65"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="65"/>
-      <c r="K123" s="66"/>
+      <c r="J123" s="64"/>
+      <c r="K123" s="65"/>
       <c r="L123" s="34"/>
     </row>
-    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="67"/>
-      <c r="C124" s="68"/>
-      <c r="D124" s="69"/>
+    <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="75"/>
+      <c r="C124" s="76"/>
+      <c r="D124" s="77"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="67"/>
-      <c r="G124" s="68"/>
-      <c r="H124" s="69"/>
+      <c r="F124" s="75"/>
+      <c r="G124" s="76"/>
+      <c r="H124" s="77"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="67"/>
-      <c r="K124" s="68"/>
-      <c r="L124" s="69"/>
-    </row>
-    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="70"/>
-      <c r="C125" s="71"/>
-      <c r="D125" s="72"/>
+      <c r="J124" s="75"/>
+      <c r="K124" s="76"/>
+      <c r="L124" s="77"/>
+    </row>
+    <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="69"/>
+      <c r="C125" s="70"/>
+      <c r="D125" s="71"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="70"/>
-      <c r="G125" s="71"/>
-      <c r="H125" s="72"/>
+      <c r="F125" s="69"/>
+      <c r="G125" s="70"/>
+      <c r="H125" s="71"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="70"/>
-      <c r="K125" s="71"/>
-      <c r="L125" s="72"/>
-    </row>
-    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="76"/>
-      <c r="C126" s="77"/>
-      <c r="D126" s="78"/>
+      <c r="J125" s="69"/>
+      <c r="K125" s="70"/>
+      <c r="L125" s="71"/>
+    </row>
+    <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="66"/>
+      <c r="C126" s="67"/>
+      <c r="D126" s="68"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="76"/>
-      <c r="G126" s="77"/>
-      <c r="H126" s="78"/>
+      <c r="F126" s="66"/>
+      <c r="G126" s="67"/>
+      <c r="H126" s="68"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="76"/>
-      <c r="K126" s="77"/>
-      <c r="L126" s="78"/>
-    </row>
-    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="60"/>
-      <c r="C127" s="61"/>
-      <c r="D127" s="62"/>
+      <c r="J126" s="66"/>
+      <c r="K126" s="67"/>
+      <c r="L126" s="68"/>
+    </row>
+    <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="61"/>
+      <c r="C127" s="62"/>
+      <c r="D127" s="63"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="60"/>
-      <c r="G127" s="61"/>
-      <c r="H127" s="62"/>
+      <c r="F127" s="61"/>
+      <c r="G127" s="62"/>
+      <c r="H127" s="63"/>
       <c r="I127" s="31"/>
-      <c r="J127" s="60"/>
-      <c r="K127" s="61"/>
-      <c r="L127" s="62"/>
-    </row>
-    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J127" s="61"/>
+      <c r="K127" s="62"/>
+      <c r="L127" s="63"/>
+    </row>
+    <row r="128" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
@@ -7728,121 +7733,886 @@
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
     </row>
-    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="65"/>
-      <c r="C129" s="66"/>
+    <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="64"/>
+      <c r="C129" s="65"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="65"/>
-      <c r="G129" s="66"/>
+      <c r="F129" s="64"/>
+      <c r="G129" s="65"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="65"/>
-      <c r="K129" s="66"/>
+      <c r="J129" s="64"/>
+      <c r="K129" s="65"/>
       <c r="L129" s="34"/>
     </row>
-    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="67"/>
-      <c r="C130" s="68"/>
-      <c r="D130" s="69"/>
+    <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="75"/>
+      <c r="C130" s="76"/>
+      <c r="D130" s="77"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="67"/>
-      <c r="G130" s="68"/>
-      <c r="H130" s="69"/>
+      <c r="F130" s="75"/>
+      <c r="G130" s="76"/>
+      <c r="H130" s="77"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="67"/>
-      <c r="K130" s="68"/>
-      <c r="L130" s="69"/>
-    </row>
-    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="70"/>
-      <c r="C131" s="71"/>
-      <c r="D131" s="72"/>
+      <c r="J130" s="75"/>
+      <c r="K130" s="76"/>
+      <c r="L130" s="77"/>
+    </row>
+    <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="69"/>
+      <c r="C131" s="70"/>
+      <c r="D131" s="71"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="70"/>
-      <c r="G131" s="71"/>
-      <c r="H131" s="72"/>
+      <c r="F131" s="69"/>
+      <c r="G131" s="70"/>
+      <c r="H131" s="71"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="70"/>
-      <c r="K131" s="71"/>
-      <c r="L131" s="72"/>
-    </row>
-    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="76"/>
-      <c r="C132" s="77"/>
-      <c r="D132" s="78"/>
+      <c r="J131" s="69"/>
+      <c r="K131" s="70"/>
+      <c r="L131" s="71"/>
+    </row>
+    <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="66"/>
+      <c r="C132" s="67"/>
+      <c r="D132" s="68"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="76"/>
-      <c r="G132" s="77"/>
-      <c r="H132" s="78"/>
+      <c r="F132" s="66"/>
+      <c r="G132" s="67"/>
+      <c r="H132" s="68"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="76"/>
-      <c r="K132" s="77"/>
-      <c r="L132" s="78"/>
-    </row>
-    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="60"/>
-      <c r="C133" s="61"/>
-      <c r="D133" s="62"/>
+      <c r="J132" s="66"/>
+      <c r="K132" s="67"/>
+      <c r="L132" s="68"/>
+    </row>
+    <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="61"/>
+      <c r="C133" s="62"/>
+      <c r="D133" s="63"/>
       <c r="E133" s="31"/>
-      <c r="F133" s="60"/>
-      <c r="G133" s="61"/>
-      <c r="H133" s="62"/>
+      <c r="F133" s="61"/>
+      <c r="G133" s="62"/>
+      <c r="H133" s="63"/>
       <c r="I133" s="31"/>
-      <c r="J133" s="60"/>
-      <c r="K133" s="61"/>
-      <c r="L133" s="62"/>
+      <c r="J133" s="61"/>
+      <c r="K133" s="62"/>
+      <c r="L133" s="63"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="881">
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="AD81:AF81"/>
+    <mergeCell ref="AH39:AI39"/>
+    <mergeCell ref="AD37:AF37"/>
+    <mergeCell ref="AD39:AE39"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="AH41:AJ41"/>
+    <mergeCell ref="AH60:AJ60"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AD60:AF60"/>
+    <mergeCell ref="AH49:AJ49"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AH45:AI45"/>
+    <mergeCell ref="AH50:AJ50"/>
+    <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="AH37:AJ37"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="V37:X37"/>
+    <mergeCell ref="V39:W39"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AL37:AN37"/>
+    <mergeCell ref="AL39:AM39"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="AH72:AJ72"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AL75:AN75"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="AD87:AF87"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AH87:AJ87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AH93:AJ93"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J24:K24"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="B23:C23"/>
@@ -7867,817 +8637,52 @@
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AH87:AJ87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AH93:AJ93"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="AD87:AF87"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="AH72:AJ72"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="V93:X93"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="Z93:AB93"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AL37:AN37"/>
-    <mergeCell ref="AL39:AM39"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="V37:X37"/>
-    <mergeCell ref="V39:W39"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="AD81:AF81"/>
-    <mergeCell ref="AH39:AI39"/>
-    <mergeCell ref="AD37:AF37"/>
-    <mergeCell ref="AD39:AE39"/>
-    <mergeCell ref="AD43:AF43"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AH41:AJ41"/>
-    <mergeCell ref="AH60:AJ60"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AD60:AF60"/>
-    <mergeCell ref="AH49:AJ49"/>
-    <mergeCell ref="AH48:AJ48"/>
-    <mergeCell ref="AH46:AJ46"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AH45:AI45"/>
-    <mergeCell ref="AH50:AJ50"/>
-    <mergeCell ref="AH52:AI52"/>
-    <mergeCell ref="AH37:AJ37"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="R49:T49"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="T22:T27 AB22:AB27 AF22:AF27 D22:D27 AJ22:AJ27 AN22:AN27 X22:X27 L22:L27 H22:H27 P22:P27">

--- a/Gorev-Listesi.xlsx
+++ b/Gorev-Listesi.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="82">
   <si>
     <t>CUMA</t>
   </si>
@@ -248,6 +248,9 @@
     <t>YENİ PROGRAM</t>
   </si>
   <si>
+    <t>HABER HİZMETİ</t>
+  </si>
+  <si>
     <t>Haliç Kongre Merkezi</t>
   </si>
   <si>
@@ -257,7 +260,16 @@
     <t>Sheraton Grand Ataşehir</t>
   </si>
   <si>
-    <t>HABER HİZMETİ x2</t>
+    <t>H.HEKİMHAN.</t>
+  </si>
+  <si>
+    <t>09.30</t>
+  </si>
+  <si>
+    <t>18.00</t>
+  </si>
+  <si>
+    <t>S.AKDAĞ (yedek)</t>
   </si>
 </sst>
 </file>
@@ -1464,12 +1476,45 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="7" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1479,39 +1524,6 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="16" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="11" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="12" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1530,140 +1542,140 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="16" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="17" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="18" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="19" xfId="57" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="17" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="18" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -2037,7 +2049,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="182" row="2" locked="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="175" row="3" locked="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2114,65 +2126,65 @@
   <sheetData>
     <row r="1" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
       <c r="I1" s="10"/>
-      <c r="J1" s="110" t="s">
+      <c r="J1" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="110"/>
-      <c r="L1" s="111"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="114"/>
       <c r="M1" s="12"/>
-      <c r="N1" s="114" t="s">
+      <c r="N1" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="108" t="s">
+      <c r="R1" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="108" t="s">
+      <c r="V1" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="108" t="s">
+      <c r="Z1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="108"/>
-      <c r="AB1" s="108"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="108" t="s">
+      <c r="AD1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="AE1" s="108"/>
-      <c r="AF1" s="108"/>
+      <c r="AE1" s="107"/>
+      <c r="AF1" s="107"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="108" t="s">
+      <c r="AH1" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="108"/>
-      <c r="AJ1" s="108"/>
+      <c r="AI1" s="107"/>
+      <c r="AJ1" s="107"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="108" t="s">
+      <c r="AL1" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="108"/>
-      <c r="AN1" s="118"/>
+      <c r="AM1" s="107"/>
+      <c r="AN1" s="108"/>
       <c r="AO1" s="12"/>
       <c r="AP1" s="12"/>
       <c r="AQ1" s="12"/>
@@ -2180,74 +2192,74 @@
     </row>
     <row r="2" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
-      <c r="B2" s="112">
+      <c r="B2" s="115">
         <f>N2-3</f>
         <v>46255</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="11"/>
-      <c r="F2" s="113">
+      <c r="F2" s="116">
         <f>N2-2</f>
         <v>46256</v>
       </c>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="113">
+      <c r="J2" s="116">
         <f>N2-1</f>
         <v>46257</v>
       </c>
-      <c r="K2" s="113"/>
-      <c r="L2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="119"/>
       <c r="M2" s="12"/>
-      <c r="N2" s="115">
+      <c r="N2" s="118">
         <v>46258</v>
       </c>
-      <c r="O2" s="104"/>
-      <c r="P2" s="104"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
       <c r="Q2" s="53"/>
-      <c r="R2" s="104">
+      <c r="R2" s="109">
         <f>N2+1</f>
         <v>46259</v>
       </c>
-      <c r="S2" s="104"/>
-      <c r="T2" s="104"/>
+      <c r="S2" s="109"/>
+      <c r="T2" s="109"/>
       <c r="U2" s="53"/>
-      <c r="V2" s="104">
+      <c r="V2" s="109">
         <f>N2+2</f>
         <v>46260</v>
       </c>
-      <c r="W2" s="104"/>
-      <c r="X2" s="104"/>
+      <c r="W2" s="109"/>
+      <c r="X2" s="109"/>
       <c r="Y2" s="53"/>
-      <c r="Z2" s="104">
+      <c r="Z2" s="109">
         <f>N2+3</f>
         <v>46261</v>
       </c>
-      <c r="AA2" s="104"/>
-      <c r="AB2" s="104"/>
+      <c r="AA2" s="109"/>
+      <c r="AB2" s="109"/>
       <c r="AC2" s="53"/>
-      <c r="AD2" s="104">
+      <c r="AD2" s="109">
         <f>N2+4</f>
         <v>46262</v>
       </c>
-      <c r="AE2" s="104"/>
-      <c r="AF2" s="104"/>
+      <c r="AE2" s="109"/>
+      <c r="AF2" s="109"/>
       <c r="AG2" s="53"/>
-      <c r="AH2" s="104">
+      <c r="AH2" s="109">
         <f>N2+5</f>
         <v>46263</v>
       </c>
-      <c r="AI2" s="104"/>
-      <c r="AJ2" s="104"/>
+      <c r="AI2" s="109"/>
+      <c r="AJ2" s="109"/>
       <c r="AK2" s="53"/>
-      <c r="AL2" s="104">
+      <c r="AL2" s="109">
         <f>N2+6</f>
         <v>46264</v>
       </c>
-      <c r="AM2" s="104"/>
-      <c r="AN2" s="119"/>
+      <c r="AM2" s="109"/>
+      <c r="AN2" s="110"/>
       <c r="AO2" s="12"/>
       <c r="AP2" s="12"/>
       <c r="AQ2" s="12"/>
@@ -2301,47 +2313,47 @@
     </row>
     <row r="4" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
       <c r="M4" s="14"/>
-      <c r="N4" s="103" t="s">
+      <c r="N4" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="103"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="103"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="103"/>
-      <c r="V4" s="103"/>
-      <c r="W4" s="103"/>
-      <c r="X4" s="103"/>
-      <c r="Y4" s="103"/>
-      <c r="Z4" s="103"/>
-      <c r="AA4" s="103"/>
-      <c r="AB4" s="103"/>
+      <c r="O4" s="95"/>
+      <c r="P4" s="95"/>
+      <c r="Q4" s="95"/>
+      <c r="R4" s="95"/>
+      <c r="S4" s="95"/>
+      <c r="T4" s="95"/>
+      <c r="U4" s="95"/>
+      <c r="V4" s="95"/>
+      <c r="W4" s="95"/>
+      <c r="X4" s="95"/>
+      <c r="Y4" s="95"/>
+      <c r="Z4" s="95"/>
+      <c r="AA4" s="95"/>
+      <c r="AB4" s="95"/>
       <c r="AC4" s="33"/>
-      <c r="AD4" s="117"/>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
+      <c r="AD4" s="111"/>
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
       <c r="AO4" s="12"/>
       <c r="AP4" s="12"/>
       <c r="AQ4" s="12"/>
@@ -2349,89 +2361,89 @@
     </row>
     <row r="5" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12"/>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
       <c r="M5" s="14"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="103"/>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
-      <c r="Z5" s="103"/>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="95"/>
+      <c r="S5" s="95"/>
+      <c r="T5" s="95"/>
+      <c r="U5" s="95"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="95"/>
+      <c r="X5" s="95"/>
+      <c r="Y5" s="95"/>
+      <c r="Z5" s="95"/>
+      <c r="AA5" s="95"/>
+      <c r="AB5" s="95"/>
       <c r="AC5" s="33"/>
-      <c r="AD5" s="117"/>
-      <c r="AE5" s="117"/>
-      <c r="AF5" s="117"/>
-      <c r="AG5" s="117"/>
-      <c r="AH5" s="117"/>
-      <c r="AI5" s="117"/>
-      <c r="AJ5" s="117"/>
-      <c r="AK5" s="117"/>
-      <c r="AL5" s="117"/>
-      <c r="AM5" s="117"/>
-      <c r="AN5" s="117"/>
+      <c r="AD5" s="111"/>
+      <c r="AE5" s="111"/>
+      <c r="AF5" s="111"/>
+      <c r="AG5" s="111"/>
+      <c r="AH5" s="111"/>
+      <c r="AI5" s="111"/>
+      <c r="AJ5" s="111"/>
+      <c r="AK5" s="111"/>
+      <c r="AL5" s="111"/>
+      <c r="AM5" s="111"/>
+      <c r="AN5" s="111"/>
       <c r="AO5" s="12"/>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="13"/>
     </row>
     <row r="6" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="78"/>
-      <c r="C6" s="79"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="65"/>
       <c r="D6" s="57"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="79"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
       <c r="H6" s="57"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="79"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
       <c r="L6" s="57"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="65"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="67"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="65"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="67"/>
       <c r="T6" s="34"/>
       <c r="U6" s="36"/>
-      <c r="V6" s="64"/>
-      <c r="W6" s="65"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="67"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="64"/>
-      <c r="AA6" s="65"/>
+      <c r="Z6" s="66"/>
+      <c r="AA6" s="67"/>
       <c r="AB6" s="34"/>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="64"/>
-      <c r="AE6" s="65"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="67"/>
       <c r="AF6" s="34"/>
       <c r="AG6" s="39"/>
-      <c r="AH6" s="64"/>
-      <c r="AI6" s="65"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="67"/>
       <c r="AJ6" s="34"/>
       <c r="AK6" s="36"/>
-      <c r="AL6" s="64"/>
-      <c r="AM6" s="65"/>
+      <c r="AL6" s="66"/>
+      <c r="AM6" s="67"/>
       <c r="AN6" s="34"/>
       <c r="AP6" s="46" t="s">
         <v>7</v>
@@ -2455,32 +2467,32 @@
       <c r="K7" s="84"/>
       <c r="L7" s="58"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="70"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="72"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="36"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="70"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="72"/>
       <c r="T7" s="18"/>
       <c r="U7" s="36"/>
-      <c r="V7" s="69"/>
-      <c r="W7" s="70"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="72"/>
       <c r="X7" s="18"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="69"/>
-      <c r="AA7" s="70"/>
+      <c r="Z7" s="71"/>
+      <c r="AA7" s="72"/>
       <c r="AB7" s="18"/>
       <c r="AC7" s="36"/>
-      <c r="AD7" s="69"/>
-      <c r="AE7" s="70"/>
+      <c r="AD7" s="71"/>
+      <c r="AE7" s="72"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="69"/>
-      <c r="AI7" s="70"/>
+      <c r="AH7" s="71"/>
+      <c r="AI7" s="72"/>
       <c r="AJ7" s="18"/>
       <c r="AK7" s="36"/>
-      <c r="AL7" s="69"/>
-      <c r="AM7" s="70"/>
+      <c r="AL7" s="71"/>
+      <c r="AM7" s="72"/>
       <c r="AN7" s="18"/>
       <c r="AP7" s="46" t="s">
         <v>9</v>
@@ -2492,45 +2504,45 @@
       <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="68"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="79"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="68"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
       <c r="I8" s="37"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="68"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="79"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="66"/>
-      <c r="O8" s="67"/>
-      <c r="P8" s="68"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="78"/>
+      <c r="P8" s="79"/>
       <c r="Q8" s="35"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="68"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="78"/>
+      <c r="T8" s="79"/>
       <c r="U8" s="37"/>
-      <c r="V8" s="66"/>
-      <c r="W8" s="67"/>
-      <c r="X8" s="68"/>
+      <c r="V8" s="77"/>
+      <c r="W8" s="78"/>
+      <c r="X8" s="79"/>
       <c r="Y8" s="35"/>
-      <c r="Z8" s="66"/>
-      <c r="AA8" s="67"/>
-      <c r="AB8" s="68"/>
+      <c r="Z8" s="77"/>
+      <c r="AA8" s="78"/>
+      <c r="AB8" s="79"/>
       <c r="AC8" s="35"/>
-      <c r="AD8" s="66"/>
-      <c r="AE8" s="67"/>
-      <c r="AF8" s="68"/>
+      <c r="AD8" s="77"/>
+      <c r="AE8" s="78"/>
+      <c r="AF8" s="79"/>
       <c r="AG8" s="35"/>
-      <c r="AH8" s="66"/>
-      <c r="AI8" s="67"/>
-      <c r="AJ8" s="68"/>
+      <c r="AH8" s="77"/>
+      <c r="AI8" s="78"/>
+      <c r="AJ8" s="79"/>
       <c r="AK8" s="37"/>
-      <c r="AL8" s="66"/>
-      <c r="AM8" s="67"/>
-      <c r="AN8" s="68"/>
+      <c r="AL8" s="77"/>
+      <c r="AM8" s="78"/>
+      <c r="AN8" s="79"/>
       <c r="AP8" s="59" t="s">
         <v>16</v>
       </c>
@@ -2543,45 +2555,45 @@
       </c>
     </row>
     <row r="9" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="72"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="74"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="76"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="76"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="74"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="76"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="74"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="76"/>
       <c r="Q9" s="43"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="74"/>
+      <c r="R9" s="74"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="76"/>
       <c r="U9" s="44"/>
-      <c r="V9" s="72"/>
-      <c r="W9" s="73"/>
-      <c r="X9" s="74"/>
+      <c r="V9" s="74"/>
+      <c r="W9" s="75"/>
+      <c r="X9" s="76"/>
       <c r="Y9" s="43"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="73"/>
-      <c r="AB9" s="74"/>
+      <c r="Z9" s="74"/>
+      <c r="AA9" s="75"/>
+      <c r="AB9" s="76"/>
       <c r="AC9" s="43"/>
-      <c r="AD9" s="72"/>
-      <c r="AE9" s="73"/>
-      <c r="AF9" s="74"/>
+      <c r="AD9" s="74"/>
+      <c r="AE9" s="75"/>
+      <c r="AF9" s="76"/>
       <c r="AG9" s="43"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="73"/>
-      <c r="AJ9" s="74"/>
+      <c r="AH9" s="74"/>
+      <c r="AI9" s="75"/>
+      <c r="AJ9" s="76"/>
       <c r="AK9" s="43"/>
-      <c r="AL9" s="72"/>
-      <c r="AM9" s="73"/>
-      <c r="AN9" s="74"/>
+      <c r="AL9" s="74"/>
+      <c r="AM9" s="75"/>
+      <c r="AN9" s="76"/>
       <c r="AP9" s="59" t="s">
         <v>11</v>
       </c>
@@ -2594,45 +2606,45 @@
       </c>
     </row>
     <row r="10" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="105"/>
-      <c r="C10" s="106"/>
-      <c r="D10" s="107"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="98"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="107"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="98"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="107"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="98"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="107"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="98"/>
       <c r="Q10" s="44"/>
-      <c r="R10" s="105"/>
-      <c r="S10" s="106"/>
-      <c r="T10" s="107"/>
+      <c r="R10" s="96"/>
+      <c r="S10" s="97"/>
+      <c r="T10" s="98"/>
       <c r="U10" s="44"/>
-      <c r="V10" s="105"/>
-      <c r="W10" s="106"/>
-      <c r="X10" s="107"/>
+      <c r="V10" s="96"/>
+      <c r="W10" s="97"/>
+      <c r="X10" s="98"/>
       <c r="Y10" s="44"/>
-      <c r="Z10" s="105"/>
-      <c r="AA10" s="106"/>
-      <c r="AB10" s="107"/>
+      <c r="Z10" s="96"/>
+      <c r="AA10" s="97"/>
+      <c r="AB10" s="98"/>
       <c r="AC10" s="44"/>
-      <c r="AD10" s="105"/>
-      <c r="AE10" s="106"/>
-      <c r="AF10" s="107"/>
+      <c r="AD10" s="96"/>
+      <c r="AE10" s="97"/>
+      <c r="AF10" s="98"/>
       <c r="AG10" s="44"/>
-      <c r="AH10" s="105"/>
-      <c r="AI10" s="106"/>
-      <c r="AJ10" s="107"/>
+      <c r="AH10" s="96"/>
+      <c r="AI10" s="97"/>
+      <c r="AJ10" s="98"/>
       <c r="AK10" s="44"/>
-      <c r="AL10" s="105"/>
-      <c r="AM10" s="106"/>
-      <c r="AN10" s="107"/>
+      <c r="AL10" s="96"/>
+      <c r="AM10" s="97"/>
+      <c r="AN10" s="98"/>
       <c r="AP10" s="59" t="s">
         <v>8</v>
       </c>
@@ -2694,59 +2706,59 @@
       <c r="AR11" s="30"/>
     </row>
     <row r="12" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="78"/>
-      <c r="C12" s="79"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="57"/>
       <c r="E12" s="39"/>
-      <c r="F12" s="78" t="s">
+      <c r="F12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="79"/>
+      <c r="G12" s="65"/>
       <c r="H12" s="57" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="36"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="79"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="65"/>
       <c r="L12" s="57"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="65"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="67"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="64"/>
-      <c r="S12" s="65"/>
+      <c r="R12" s="66"/>
+      <c r="S12" s="67"/>
       <c r="T12" s="34"/>
       <c r="U12" s="36"/>
-      <c r="V12" s="64"/>
-      <c r="W12" s="65"/>
+      <c r="V12" s="66"/>
+      <c r="W12" s="67"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="64"/>
-      <c r="AA12" s="65"/>
+      <c r="Z12" s="66"/>
+      <c r="AA12" s="67"/>
       <c r="AB12" s="34"/>
       <c r="AC12" s="36"/>
-      <c r="AD12" s="64"/>
-      <c r="AE12" s="65"/>
+      <c r="AD12" s="66"/>
+      <c r="AE12" s="67"/>
       <c r="AF12" s="34"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="64" t="s">
+      <c r="AH12" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="AI12" s="65"/>
+      <c r="AI12" s="67"/>
       <c r="AJ12" s="34" t="s">
         <v>46</v>
       </c>
       <c r="AK12" s="36"/>
-      <c r="AL12" s="64"/>
-      <c r="AM12" s="65"/>
+      <c r="AL12" s="66"/>
+      <c r="AM12" s="67"/>
       <c r="AN12" s="34"/>
       <c r="AP12" s="46" t="s">
         <v>19</v>
       </c>
       <c r="AQ12" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR12" s="30"/>
     </row>
@@ -2763,33 +2775,33 @@
       <c r="K13" s="81"/>
       <c r="L13" s="82"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="76"/>
-      <c r="P13" s="77"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="70"/>
       <c r="Q13" s="36"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="76"/>
-      <c r="T13" s="77"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="70"/>
       <c r="U13" s="36"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="76"/>
-      <c r="X13" s="77"/>
+      <c r="V13" s="68"/>
+      <c r="W13" s="69"/>
+      <c r="X13" s="70"/>
       <c r="Y13" s="36"/>
-      <c r="Z13" s="69"/>
-      <c r="AA13" s="70"/>
+      <c r="Z13" s="71"/>
+      <c r="AA13" s="72"/>
       <c r="AB13" s="18"/>
       <c r="AC13" s="36"/>
-      <c r="AD13" s="69"/>
-      <c r="AE13" s="70"/>
+      <c r="AD13" s="71"/>
+      <c r="AE13" s="72"/>
       <c r="AF13" s="18"/>
       <c r="AG13" s="38"/>
-      <c r="AH13" s="75"/>
-      <c r="AI13" s="76"/>
-      <c r="AJ13" s="77"/>
+      <c r="AH13" s="68"/>
+      <c r="AI13" s="69"/>
+      <c r="AJ13" s="70"/>
       <c r="AK13" s="36"/>
-      <c r="AL13" s="75"/>
-      <c r="AM13" s="76"/>
-      <c r="AN13" s="77"/>
+      <c r="AL13" s="68"/>
+      <c r="AM13" s="69"/>
+      <c r="AN13" s="70"/>
       <c r="AP13" s="46" t="s">
         <v>22</v>
       </c>
@@ -2800,49 +2812,49 @@
       <c r="AR13" s="30"/>
     </row>
     <row r="14" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="66"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="68"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
       <c r="E14" s="37"/>
-      <c r="F14" s="66" t="s">
+      <c r="F14" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="67"/>
-      <c r="H14" s="68"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="79"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="68"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="79"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="68"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="79"/>
       <c r="Q14" s="35"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="67"/>
-      <c r="T14" s="68"/>
+      <c r="R14" s="77"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="79"/>
       <c r="U14" s="37"/>
-      <c r="V14" s="66"/>
-      <c r="W14" s="67"/>
-      <c r="X14" s="68"/>
+      <c r="V14" s="77"/>
+      <c r="W14" s="78"/>
+      <c r="X14" s="79"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="66"/>
-      <c r="AA14" s="67"/>
-      <c r="AB14" s="68"/>
+      <c r="Z14" s="77"/>
+      <c r="AA14" s="78"/>
+      <c r="AB14" s="79"/>
       <c r="AC14" s="37"/>
-      <c r="AD14" s="66"/>
-      <c r="AE14" s="67"/>
-      <c r="AF14" s="68"/>
+      <c r="AD14" s="77"/>
+      <c r="AE14" s="78"/>
+      <c r="AF14" s="79"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="66" t="s">
+      <c r="AH14" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="AI14" s="67"/>
-      <c r="AJ14" s="68"/>
+      <c r="AI14" s="78"/>
+      <c r="AJ14" s="79"/>
       <c r="AK14" s="35"/>
-      <c r="AL14" s="66"/>
-      <c r="AM14" s="67"/>
-      <c r="AN14" s="68"/>
+      <c r="AL14" s="77"/>
+      <c r="AM14" s="78"/>
+      <c r="AN14" s="79"/>
       <c r="AP14" s="46" t="s">
         <v>23</v>
       </c>
@@ -2853,49 +2865,49 @@
       <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="72"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="74"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="76"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="76"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="73"/>
-      <c r="P15" s="74"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="76"/>
       <c r="Q15" s="43"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="73"/>
-      <c r="T15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="75"/>
+      <c r="T15" s="76"/>
       <c r="U15" s="44"/>
-      <c r="V15" s="72"/>
-      <c r="W15" s="73"/>
-      <c r="X15" s="74"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="75"/>
+      <c r="X15" s="76"/>
       <c r="Y15" s="43"/>
-      <c r="Z15" s="72"/>
-      <c r="AA15" s="73"/>
-      <c r="AB15" s="74"/>
+      <c r="Z15" s="74"/>
+      <c r="AA15" s="75"/>
+      <c r="AB15" s="76"/>
       <c r="AC15" s="43"/>
-      <c r="AD15" s="72"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="74"/>
+      <c r="AD15" s="74"/>
+      <c r="AE15" s="75"/>
+      <c r="AF15" s="76"/>
       <c r="AG15" s="44"/>
-      <c r="AH15" s="72" t="s">
+      <c r="AH15" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="AI15" s="73"/>
-      <c r="AJ15" s="74"/>
+      <c r="AI15" s="75"/>
+      <c r="AJ15" s="76"/>
       <c r="AK15" s="43"/>
-      <c r="AL15" s="72"/>
-      <c r="AM15" s="73"/>
-      <c r="AN15" s="74"/>
+      <c r="AL15" s="74"/>
+      <c r="AM15" s="75"/>
+      <c r="AN15" s="76"/>
       <c r="AP15" s="46" t="s">
         <v>18</v>
       </c>
@@ -2906,45 +2918,45 @@
       <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="1:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="105"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="107"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="98"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="107"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="98"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="107"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="98"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="105"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="107"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="97"/>
+      <c r="P16" s="98"/>
       <c r="Q16" s="44"/>
-      <c r="R16" s="105"/>
-      <c r="S16" s="106"/>
-      <c r="T16" s="107"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="97"/>
+      <c r="T16" s="98"/>
       <c r="U16" s="44"/>
-      <c r="V16" s="105"/>
-      <c r="W16" s="106"/>
-      <c r="X16" s="107"/>
+      <c r="V16" s="96"/>
+      <c r="W16" s="97"/>
+      <c r="X16" s="98"/>
       <c r="Y16" s="44"/>
-      <c r="Z16" s="105"/>
-      <c r="AA16" s="106"/>
-      <c r="AB16" s="107"/>
+      <c r="Z16" s="96"/>
+      <c r="AA16" s="97"/>
+      <c r="AB16" s="98"/>
       <c r="AC16" s="44"/>
-      <c r="AD16" s="105"/>
-      <c r="AE16" s="106"/>
-      <c r="AF16" s="107"/>
+      <c r="AD16" s="96"/>
+      <c r="AE16" s="97"/>
+      <c r="AF16" s="98"/>
       <c r="AG16" s="44"/>
-      <c r="AH16" s="105"/>
-      <c r="AI16" s="106"/>
-      <c r="AJ16" s="107"/>
+      <c r="AH16" s="96"/>
+      <c r="AI16" s="97"/>
+      <c r="AJ16" s="98"/>
       <c r="AK16" s="44"/>
-      <c r="AL16" s="105"/>
-      <c r="AM16" s="106"/>
-      <c r="AN16" s="107"/>
+      <c r="AL16" s="96"/>
+      <c r="AM16" s="97"/>
+      <c r="AN16" s="98"/>
       <c r="AP16" s="46" t="s">
         <v>24</v>
       </c>
@@ -3016,23 +3028,23 @@
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="103" t="s">
+      <c r="N18" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="103"/>
-      <c r="S18" s="103"/>
-      <c r="T18" s="103"/>
-      <c r="U18" s="103"/>
-      <c r="V18" s="103"/>
-      <c r="W18" s="103"/>
-      <c r="X18" s="103"/>
-      <c r="Y18" s="103"/>
-      <c r="Z18" s="103"/>
-      <c r="AA18" s="103"/>
-      <c r="AB18" s="103"/>
+      <c r="O18" s="95"/>
+      <c r="P18" s="95"/>
+      <c r="Q18" s="95"/>
+      <c r="R18" s="95"/>
+      <c r="S18" s="95"/>
+      <c r="T18" s="95"/>
+      <c r="U18" s="95"/>
+      <c r="V18" s="95"/>
+      <c r="W18" s="95"/>
+      <c r="X18" s="95"/>
+      <c r="Y18" s="95"/>
+      <c r="Z18" s="95"/>
+      <c r="AA18" s="95"/>
+      <c r="AB18" s="95"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
@@ -3067,21 +3079,21 @@
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="103"/>
-      <c r="O19" s="103"/>
-      <c r="P19" s="103"/>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="103"/>
-      <c r="S19" s="103"/>
-      <c r="T19" s="103"/>
-      <c r="U19" s="103"/>
-      <c r="V19" s="103"/>
-      <c r="W19" s="103"/>
-      <c r="X19" s="103"/>
-      <c r="Y19" s="103"/>
-      <c r="Z19" s="103"/>
-      <c r="AA19" s="103"/>
-      <c r="AB19" s="103"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="95"/>
+      <c r="P19" s="95"/>
+      <c r="Q19" s="95"/>
+      <c r="R19" s="95"/>
+      <c r="S19" s="95"/>
+      <c r="T19" s="95"/>
+      <c r="U19" s="95"/>
+      <c r="V19" s="95"/>
+      <c r="W19" s="95"/>
+      <c r="X19" s="95"/>
+      <c r="Y19" s="95"/>
+      <c r="Z19" s="95"/>
+      <c r="AA19" s="95"/>
+      <c r="AB19" s="95"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -3104,44 +3116,44 @@
       <c r="AR19" s="30"/>
     </row>
     <row r="20" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="78"/>
-      <c r="C20" s="79"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="57"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="79"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="65"/>
       <c r="H20" s="57"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="79"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="65"/>
       <c r="L20" s="57"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="65"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="67"/>
       <c r="P20" s="34"/>
       <c r="Q20" s="36"/>
-      <c r="R20" s="101"/>
-      <c r="S20" s="102"/>
+      <c r="R20" s="99"/>
+      <c r="S20" s="100"/>
       <c r="T20" s="55"/>
       <c r="U20" s="36"/>
-      <c r="V20" s="101"/>
-      <c r="W20" s="102"/>
+      <c r="V20" s="99"/>
+      <c r="W20" s="100"/>
       <c r="X20" s="55"/>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="101"/>
-      <c r="AA20" s="102"/>
+      <c r="Z20" s="99"/>
+      <c r="AA20" s="100"/>
       <c r="AB20" s="55"/>
       <c r="AC20" s="36"/>
-      <c r="AD20" s="64"/>
-      <c r="AE20" s="65"/>
+      <c r="AD20" s="66"/>
+      <c r="AE20" s="67"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="36"/>
-      <c r="AH20" s="64"/>
-      <c r="AI20" s="65"/>
+      <c r="AH20" s="66"/>
+      <c r="AI20" s="67"/>
       <c r="AJ20" s="34"/>
       <c r="AK20" s="36"/>
-      <c r="AL20" s="64"/>
-      <c r="AM20" s="65"/>
+      <c r="AL20" s="66"/>
+      <c r="AM20" s="67"/>
       <c r="AN20" s="34"/>
       <c r="AP20" s="46" t="s">
         <v>26</v>
@@ -3165,32 +3177,32 @@
       <c r="K21" s="84"/>
       <c r="L21" s="58"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="70"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="72"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="38"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="70"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="72"/>
       <c r="T21" s="18"/>
       <c r="U21" s="38"/>
-      <c r="V21" s="120"/>
-      <c r="W21" s="121"/>
+      <c r="V21" s="105"/>
+      <c r="W21" s="106"/>
       <c r="X21" s="56"/>
       <c r="Y21" s="36"/>
-      <c r="Z21" s="120"/>
-      <c r="AA21" s="121"/>
+      <c r="Z21" s="105"/>
+      <c r="AA21" s="106"/>
       <c r="AB21" s="56"/>
       <c r="AC21" s="36"/>
-      <c r="AD21" s="69"/>
-      <c r="AE21" s="70"/>
+      <c r="AD21" s="71"/>
+      <c r="AE21" s="72"/>
       <c r="AF21" s="18"/>
       <c r="AG21" s="38"/>
-      <c r="AH21" s="69"/>
-      <c r="AI21" s="70"/>
+      <c r="AH21" s="71"/>
+      <c r="AI21" s="72"/>
       <c r="AJ21" s="18"/>
       <c r="AK21" s="36"/>
-      <c r="AL21" s="69"/>
-      <c r="AM21" s="70"/>
+      <c r="AL21" s="71"/>
+      <c r="AM21" s="72"/>
       <c r="AN21" s="18"/>
       <c r="AP21" s="46" t="s">
         <v>12</v>
@@ -3202,44 +3214,44 @@
       <c r="AR21" s="30"/>
     </row>
     <row r="22" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="129"/>
+      <c r="C22" s="130"/>
       <c r="D22" s="41"/>
       <c r="E22" s="37"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="91"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="130"/>
       <c r="H22" s="41"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="90"/>
-      <c r="K22" s="91"/>
+      <c r="J22" s="129"/>
+      <c r="K22" s="130"/>
       <c r="L22" s="41"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="95"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="121"/>
       <c r="P22" s="41"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="95"/>
+      <c r="R22" s="120"/>
+      <c r="S22" s="121"/>
       <c r="T22" s="41"/>
       <c r="U22" s="37"/>
-      <c r="V22" s="94"/>
-      <c r="W22" s="95"/>
+      <c r="V22" s="120"/>
+      <c r="W22" s="121"/>
       <c r="X22" s="41"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="94"/>
-      <c r="AA22" s="95"/>
+      <c r="Z22" s="120"/>
+      <c r="AA22" s="121"/>
       <c r="AB22" s="41"/>
       <c r="AC22" s="35"/>
-      <c r="AD22" s="94"/>
-      <c r="AE22" s="95"/>
+      <c r="AD22" s="120"/>
+      <c r="AE22" s="121"/>
       <c r="AF22" s="41"/>
       <c r="AG22" s="37"/>
-      <c r="AH22" s="94"/>
-      <c r="AI22" s="95"/>
+      <c r="AH22" s="120"/>
+      <c r="AI22" s="121"/>
       <c r="AJ22" s="41"/>
       <c r="AK22" s="35"/>
-      <c r="AL22" s="94"/>
-      <c r="AM22" s="95"/>
+      <c r="AL22" s="120"/>
+      <c r="AM22" s="121"/>
       <c r="AN22" s="41"/>
       <c r="AP22" s="59" t="s">
         <v>15</v>
@@ -3253,44 +3265,44 @@
       </c>
     </row>
     <row r="23" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
       <c r="D23" s="45"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="93"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="123"/>
       <c r="H23" s="45"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="93"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="123"/>
       <c r="L23" s="45"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="93"/>
+      <c r="N23" s="122"/>
+      <c r="O23" s="123"/>
       <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="92"/>
-      <c r="S23" s="93"/>
+      <c r="R23" s="122"/>
+      <c r="S23" s="123"/>
       <c r="T23" s="45"/>
       <c r="U23" s="43"/>
-      <c r="V23" s="92"/>
-      <c r="W23" s="93"/>
+      <c r="V23" s="122"/>
+      <c r="W23" s="123"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="43"/>
-      <c r="Z23" s="92"/>
-      <c r="AA23" s="93"/>
+      <c r="Z23" s="122"/>
+      <c r="AA23" s="123"/>
       <c r="AB23" s="45"/>
       <c r="AC23" s="43"/>
-      <c r="AD23" s="92"/>
-      <c r="AE23" s="93"/>
+      <c r="AD23" s="122"/>
+      <c r="AE23" s="123"/>
       <c r="AF23" s="45"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="92"/>
-      <c r="AI23" s="93"/>
+      <c r="AH23" s="122"/>
+      <c r="AI23" s="123"/>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="43"/>
-      <c r="AL23" s="92"/>
-      <c r="AM23" s="93"/>
+      <c r="AL23" s="122"/>
+      <c r="AM23" s="123"/>
       <c r="AN23" s="45"/>
       <c r="AP23" s="46" t="s">
         <v>20</v>
@@ -3302,44 +3314,44 @@
       <c r="AR23" s="30"/>
     </row>
     <row r="24" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="86"/>
-      <c r="C24" s="87"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="45"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="87"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="45"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="87"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="104"/>
       <c r="L24" s="45"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="86"/>
-      <c r="O24" s="87"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="104"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="86"/>
-      <c r="S24" s="87"/>
+      <c r="R24" s="103"/>
+      <c r="S24" s="104"/>
       <c r="T24" s="45"/>
       <c r="U24" s="44"/>
-      <c r="V24" s="86"/>
-      <c r="W24" s="87"/>
+      <c r="V24" s="103"/>
+      <c r="W24" s="104"/>
       <c r="X24" s="45"/>
       <c r="Y24" s="43"/>
-      <c r="Z24" s="86"/>
-      <c r="AA24" s="87"/>
+      <c r="Z24" s="103"/>
+      <c r="AA24" s="104"/>
       <c r="AB24" s="45"/>
       <c r="AC24" s="43"/>
-      <c r="AD24" s="86"/>
-      <c r="AE24" s="87"/>
+      <c r="AD24" s="103"/>
+      <c r="AE24" s="104"/>
       <c r="AF24" s="45"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="86"/>
-      <c r="AI24" s="87"/>
+      <c r="AH24" s="103"/>
+      <c r="AI24" s="104"/>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="44"/>
-      <c r="AL24" s="86"/>
-      <c r="AM24" s="87"/>
+      <c r="AL24" s="103"/>
+      <c r="AM24" s="104"/>
       <c r="AN24" s="45"/>
       <c r="AP24" s="46" t="s">
         <v>14</v>
@@ -3351,44 +3363,44 @@
       <c r="AR24" s="30"/>
     </row>
     <row r="25" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="86"/>
-      <c r="C25" s="87"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
       <c r="D25" s="45"/>
       <c r="E25" s="44"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="104"/>
       <c r="H25" s="45"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="87"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="104"/>
       <c r="L25" s="45"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="86"/>
-      <c r="O25" s="87"/>
+      <c r="N25" s="103"/>
+      <c r="O25" s="104"/>
       <c r="P25" s="45"/>
       <c r="Q25" s="44"/>
-      <c r="R25" s="86"/>
-      <c r="S25" s="87"/>
+      <c r="R25" s="103"/>
+      <c r="S25" s="104"/>
       <c r="T25" s="45"/>
       <c r="U25" s="44"/>
-      <c r="V25" s="86"/>
-      <c r="W25" s="87"/>
+      <c r="V25" s="103"/>
+      <c r="W25" s="104"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="44"/>
-      <c r="Z25" s="86"/>
-      <c r="AA25" s="87"/>
+      <c r="Z25" s="103"/>
+      <c r="AA25" s="104"/>
       <c r="AB25" s="45"/>
       <c r="AC25" s="44"/>
-      <c r="AD25" s="86"/>
-      <c r="AE25" s="87"/>
+      <c r="AD25" s="103"/>
+      <c r="AE25" s="104"/>
       <c r="AF25" s="45"/>
       <c r="AG25" s="44"/>
-      <c r="AH25" s="86"/>
-      <c r="AI25" s="87"/>
+      <c r="AH25" s="103"/>
+      <c r="AI25" s="104"/>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="44"/>
-      <c r="AL25" s="86"/>
-      <c r="AM25" s="87"/>
+      <c r="AL25" s="103"/>
+      <c r="AM25" s="104"/>
       <c r="AN25" s="45"/>
       <c r="AP25" s="59" t="s">
         <v>21</v>
@@ -3402,93 +3414,93 @@
       </c>
     </row>
     <row r="26" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="86"/>
-      <c r="C26" s="87"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="104"/>
       <c r="D26" s="45"/>
       <c r="E26" s="44"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="87"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="87"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="104"/>
       <c r="L26" s="45"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="86"/>
-      <c r="O26" s="87"/>
+      <c r="N26" s="103"/>
+      <c r="O26" s="104"/>
       <c r="P26" s="45"/>
       <c r="Q26" s="44"/>
-      <c r="R26" s="86"/>
-      <c r="S26" s="87"/>
+      <c r="R26" s="103"/>
+      <c r="S26" s="104"/>
       <c r="T26" s="45"/>
       <c r="U26" s="44"/>
-      <c r="V26" s="86"/>
-      <c r="W26" s="87"/>
+      <c r="V26" s="103"/>
+      <c r="W26" s="104"/>
       <c r="X26" s="45"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="86"/>
-      <c r="AA26" s="87"/>
+      <c r="Z26" s="103"/>
+      <c r="AA26" s="104"/>
       <c r="AB26" s="45"/>
       <c r="AC26" s="44"/>
-      <c r="AD26" s="86"/>
-      <c r="AE26" s="87"/>
+      <c r="AD26" s="103"/>
+      <c r="AE26" s="104"/>
       <c r="AF26" s="45"/>
       <c r="AG26" s="44"/>
-      <c r="AH26" s="86"/>
-      <c r="AI26" s="87"/>
+      <c r="AH26" s="103"/>
+      <c r="AI26" s="104"/>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="44"/>
-      <c r="AL26" s="86"/>
-      <c r="AM26" s="87"/>
+      <c r="AL26" s="103"/>
+      <c r="AM26" s="104"/>
       <c r="AN26" s="45"/>
       <c r="AP26" s="46" t="s">
         <v>27</v>
       </c>
       <c r="AQ26" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR26" s="30"/>
     </row>
     <row r="27" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="88"/>
-      <c r="C27" s="89"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
       <c r="D27" s="42"/>
       <c r="E27" s="44"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="89"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="102"/>
       <c r="H27" s="42"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="89"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="102"/>
       <c r="L27" s="42"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="88"/>
-      <c r="O27" s="89"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="102"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="44"/>
-      <c r="R27" s="88"/>
-      <c r="S27" s="89"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="102"/>
       <c r="T27" s="42"/>
       <c r="U27" s="44"/>
-      <c r="V27" s="88"/>
-      <c r="W27" s="89"/>
+      <c r="V27" s="101"/>
+      <c r="W27" s="102"/>
       <c r="X27" s="42"/>
       <c r="Y27" s="44"/>
-      <c r="Z27" s="88"/>
-      <c r="AA27" s="89"/>
+      <c r="Z27" s="101"/>
+      <c r="AA27" s="102"/>
       <c r="AB27" s="42"/>
       <c r="AC27" s="44"/>
-      <c r="AD27" s="88"/>
-      <c r="AE27" s="89"/>
+      <c r="AD27" s="101"/>
+      <c r="AE27" s="102"/>
       <c r="AF27" s="42"/>
       <c r="AG27" s="44"/>
-      <c r="AH27" s="88"/>
-      <c r="AI27" s="89"/>
+      <c r="AH27" s="101"/>
+      <c r="AI27" s="102"/>
       <c r="AJ27" s="42"/>
       <c r="AK27" s="44"/>
-      <c r="AL27" s="88"/>
-      <c r="AM27" s="89"/>
+      <c r="AL27" s="101"/>
+      <c r="AM27" s="102"/>
       <c r="AN27" s="42"/>
       <c r="AP27" s="46" t="s">
         <v>13</v>
@@ -3561,23 +3573,23 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="103" t="s">
+      <c r="N29" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="O29" s="103"/>
-      <c r="P29" s="103"/>
-      <c r="Q29" s="103"/>
-      <c r="R29" s="103"/>
-      <c r="S29" s="103"/>
-      <c r="T29" s="103"/>
-      <c r="U29" s="103"/>
-      <c r="V29" s="103"/>
-      <c r="W29" s="103"/>
-      <c r="X29" s="103"/>
-      <c r="Y29" s="103"/>
-      <c r="Z29" s="103"/>
-      <c r="AA29" s="103"/>
-      <c r="AB29" s="103"/>
+      <c r="O29" s="95"/>
+      <c r="P29" s="95"/>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="95"/>
+      <c r="S29" s="95"/>
+      <c r="T29" s="95"/>
+      <c r="U29" s="95"/>
+      <c r="V29" s="95"/>
+      <c r="W29" s="95"/>
+      <c r="X29" s="95"/>
+      <c r="Y29" s="95"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="95"/>
+      <c r="AB29" s="95"/>
       <c r="AC29" s="33"/>
       <c r="AD29" s="33"/>
       <c r="AE29" s="33"/>
@@ -3612,21 +3624,21 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="103"/>
-      <c r="O30" s="103"/>
-      <c r="P30" s="103"/>
-      <c r="Q30" s="103"/>
-      <c r="R30" s="103"/>
-      <c r="S30" s="103"/>
-      <c r="T30" s="103"/>
-      <c r="U30" s="103"/>
-      <c r="V30" s="103"/>
-      <c r="W30" s="103"/>
-      <c r="X30" s="103"/>
-      <c r="Y30" s="103"/>
-      <c r="Z30" s="103"/>
-      <c r="AA30" s="103"/>
-      <c r="AB30" s="103"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="95"/>
+      <c r="T30" s="95"/>
+      <c r="U30" s="95"/>
+      <c r="V30" s="95"/>
+      <c r="W30" s="95"/>
+      <c r="X30" s="95"/>
+      <c r="Y30" s="95"/>
+      <c r="Z30" s="95"/>
+      <c r="AA30" s="95"/>
+      <c r="AB30" s="95"/>
       <c r="AC30" s="33"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="33"/>
@@ -3651,64 +3663,64 @@
       </c>
     </row>
     <row r="31" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="78" t="s">
+      <c r="B31" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="79"/>
+      <c r="C31" s="65"/>
       <c r="D31" s="57"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="78" t="s">
+      <c r="F31" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="79"/>
+      <c r="G31" s="65"/>
       <c r="H31" s="57"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="78" t="s">
+      <c r="J31" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="K31" s="79"/>
+      <c r="K31" s="65"/>
       <c r="L31" s="57"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="64" t="s">
+      <c r="N31" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="O31" s="65"/>
+      <c r="O31" s="67"/>
       <c r="P31" s="34"/>
       <c r="Q31" s="36"/>
-      <c r="R31" s="64" t="s">
+      <c r="R31" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="S31" s="65"/>
+      <c r="S31" s="67"/>
       <c r="T31" s="34"/>
       <c r="U31" s="36"/>
-      <c r="V31" s="64" t="s">
+      <c r="V31" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="W31" s="65"/>
+      <c r="W31" s="67"/>
       <c r="X31" s="34"/>
       <c r="Y31" s="36"/>
-      <c r="Z31" s="64" t="s">
+      <c r="Z31" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="AA31" s="65"/>
+      <c r="AA31" s="67"/>
       <c r="AB31" s="34"/>
       <c r="AC31" s="36"/>
-      <c r="AD31" s="64" t="s">
+      <c r="AD31" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="AE31" s="65"/>
+      <c r="AE31" s="67"/>
       <c r="AF31" s="34"/>
       <c r="AG31" s="36"/>
-      <c r="AH31" s="64" t="s">
+      <c r="AH31" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="AI31" s="65"/>
+      <c r="AI31" s="67"/>
       <c r="AJ31" s="34"/>
       <c r="AK31" s="36"/>
-      <c r="AL31" s="64" t="s">
+      <c r="AL31" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="AM31" s="65"/>
+      <c r="AM31" s="67"/>
       <c r="AN31" s="34"/>
       <c r="AP31" s="48"/>
       <c r="AQ31" s="49"/>
@@ -3733,47 +3745,47 @@
       <c r="K32" s="81"/>
       <c r="L32" s="82"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="75" t="s">
+      <c r="N32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="O32" s="76"/>
-      <c r="P32" s="77"/>
+      <c r="O32" s="69"/>
+      <c r="P32" s="70"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="75" t="s">
+      <c r="R32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="S32" s="76"/>
-      <c r="T32" s="77"/>
+      <c r="S32" s="69"/>
+      <c r="T32" s="70"/>
       <c r="U32" s="36"/>
-      <c r="V32" s="75" t="s">
+      <c r="V32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="W32" s="76"/>
-      <c r="X32" s="77"/>
+      <c r="W32" s="69"/>
+      <c r="X32" s="70"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="75" t="s">
+      <c r="Z32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="AA32" s="76"/>
-      <c r="AB32" s="77"/>
+      <c r="AA32" s="69"/>
+      <c r="AB32" s="70"/>
       <c r="AC32" s="36"/>
-      <c r="AD32" s="75" t="s">
+      <c r="AD32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="AE32" s="76"/>
-      <c r="AF32" s="77"/>
+      <c r="AE32" s="69"/>
+      <c r="AF32" s="70"/>
       <c r="AG32" s="36"/>
-      <c r="AH32" s="75" t="s">
+      <c r="AH32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="AI32" s="76"/>
-      <c r="AJ32" s="77"/>
+      <c r="AI32" s="69"/>
+      <c r="AJ32" s="70"/>
       <c r="AK32" s="36"/>
-      <c r="AL32" s="75" t="s">
+      <c r="AL32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="AM32" s="76"/>
-      <c r="AN32" s="77"/>
+      <c r="AM32" s="69"/>
+      <c r="AN32" s="70"/>
       <c r="AP32" s="51"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" s="30"/>
@@ -3797,110 +3809,110 @@
       <c r="K33" s="84"/>
       <c r="L33" s="85"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="69" t="s">
+      <c r="N33" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="O33" s="70"/>
-      <c r="P33" s="71"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="73"/>
       <c r="Q33" s="43"/>
-      <c r="R33" s="69" t="s">
+      <c r="R33" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="S33" s="70"/>
-      <c r="T33" s="71"/>
+      <c r="S33" s="72"/>
+      <c r="T33" s="73"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="69" t="s">
+      <c r="V33" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="W33" s="70"/>
-      <c r="X33" s="71"/>
+      <c r="W33" s="72"/>
+      <c r="X33" s="73"/>
       <c r="Y33" s="36"/>
-      <c r="Z33" s="69" t="s">
+      <c r="Z33" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="AA33" s="70"/>
-      <c r="AB33" s="71"/>
+      <c r="AA33" s="72"/>
+      <c r="AB33" s="73"/>
       <c r="AC33" s="36"/>
-      <c r="AD33" s="69" t="s">
+      <c r="AD33" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="AE33" s="70"/>
-      <c r="AF33" s="71"/>
+      <c r="AE33" s="72"/>
+      <c r="AF33" s="73"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="69" t="s">
+      <c r="AH33" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="AI33" s="70"/>
-      <c r="AJ33" s="71"/>
+      <c r="AI33" s="72"/>
+      <c r="AJ33" s="73"/>
       <c r="AK33" s="32"/>
-      <c r="AL33" s="69" t="s">
+      <c r="AL33" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="AM33" s="70"/>
-      <c r="AN33" s="71"/>
+      <c r="AM33" s="72"/>
+      <c r="AN33" s="73"/>
       <c r="AR33" s="13"/>
     </row>
     <row r="34" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="12"/>
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="73"/>
-      <c r="D34" s="74"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="76"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="72" t="s">
+      <c r="F34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="73"/>
-      <c r="H34" s="74"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="76"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="72" t="s">
+      <c r="J34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="73"/>
-      <c r="L34" s="74"/>
+      <c r="K34" s="75"/>
+      <c r="L34" s="76"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="72" t="s">
+      <c r="N34" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="O34" s="73"/>
-      <c r="P34" s="74"/>
+      <c r="O34" s="75"/>
+      <c r="P34" s="76"/>
       <c r="Q34" s="31"/>
-      <c r="R34" s="72" t="s">
+      <c r="R34" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="S34" s="73"/>
-      <c r="T34" s="74"/>
+      <c r="S34" s="75"/>
+      <c r="T34" s="76"/>
       <c r="U34" s="31"/>
-      <c r="V34" s="72" t="s">
+      <c r="V34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="W34" s="73"/>
-      <c r="X34" s="74"/>
+      <c r="W34" s="75"/>
+      <c r="X34" s="76"/>
       <c r="Y34" s="32"/>
-      <c r="Z34" s="72" t="s">
+      <c r="Z34" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="AA34" s="73"/>
-      <c r="AB34" s="74"/>
+      <c r="AA34" s="75"/>
+      <c r="AB34" s="76"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="72" t="s">
+      <c r="AD34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="AE34" s="73"/>
-      <c r="AF34" s="74"/>
+      <c r="AE34" s="75"/>
+      <c r="AF34" s="76"/>
       <c r="AG34" s="37"/>
-      <c r="AH34" s="72" t="s">
+      <c r="AH34" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="AI34" s="73"/>
-      <c r="AJ34" s="74"/>
+      <c r="AI34" s="75"/>
+      <c r="AJ34" s="76"/>
       <c r="AK34" s="32"/>
-      <c r="AL34" s="72" t="s">
+      <c r="AL34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="AM34" s="73"/>
-      <c r="AN34" s="74"/>
+      <c r="AM34" s="75"/>
+      <c r="AN34" s="76"/>
       <c r="AO34" s="12"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -3908,122 +3920,122 @@
     </row>
     <row r="35" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="73"/>
-      <c r="D35" s="74"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="76"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="72" t="s">
+      <c r="F35" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="73"/>
-      <c r="H35" s="74"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="76"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="72" t="s">
+      <c r="J35" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="K35" s="73"/>
-      <c r="L35" s="74"/>
+      <c r="K35" s="75"/>
+      <c r="L35" s="76"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="72" t="s">
+      <c r="N35" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="O35" s="73"/>
-      <c r="P35" s="74"/>
+      <c r="O35" s="75"/>
+      <c r="P35" s="76"/>
       <c r="Q35" s="31"/>
-      <c r="R35" s="72" t="s">
+      <c r="R35" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="S35" s="73"/>
-      <c r="T35" s="74"/>
+      <c r="S35" s="75"/>
+      <c r="T35" s="76"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="72" t="s">
+      <c r="V35" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="W35" s="73"/>
-      <c r="X35" s="74"/>
+      <c r="W35" s="75"/>
+      <c r="X35" s="76"/>
       <c r="Y35" s="32"/>
-      <c r="Z35" s="72" t="s">
+      <c r="Z35" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="73"/>
-      <c r="AB35" s="74"/>
+      <c r="AA35" s="75"/>
+      <c r="AB35" s="76"/>
       <c r="AC35" s="32"/>
-      <c r="AD35" s="72" t="s">
+      <c r="AD35" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="AE35" s="73"/>
-      <c r="AF35" s="74"/>
+      <c r="AE35" s="75"/>
+      <c r="AF35" s="76"/>
       <c r="AG35" s="44"/>
-      <c r="AH35" s="72" t="s">
+      <c r="AH35" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="AI35" s="73"/>
-      <c r="AJ35" s="74"/>
+      <c r="AI35" s="75"/>
+      <c r="AJ35" s="76"/>
       <c r="AK35" s="44"/>
-      <c r="AL35" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="AM35" s="73"/>
-      <c r="AN35" s="74"/>
+      <c r="AL35" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM35" s="90"/>
+      <c r="AN35" s="91"/>
       <c r="AO35" s="12"/>
       <c r="AQ35" s="12"/>
       <c r="AR35" s="13"/>
     </row>
     <row r="36" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="72" t="s">
+      <c r="B36" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="73"/>
-      <c r="D36" s="74"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="76"/>
       <c r="E36" s="35"/>
-      <c r="F36" s="72" t="s">
+      <c r="F36" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="73"/>
-      <c r="H36" s="74"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="76"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="72" t="s">
+      <c r="J36" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="K36" s="73"/>
-      <c r="L36" s="74"/>
+      <c r="K36" s="75"/>
+      <c r="L36" s="76"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="72" t="s">
+      <c r="N36" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="O36" s="73"/>
-      <c r="P36" s="74"/>
+      <c r="O36" s="75"/>
+      <c r="P36" s="76"/>
       <c r="Q36" s="40"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="73"/>
-      <c r="T36" s="74"/>
+      <c r="R36" s="74"/>
+      <c r="S36" s="75"/>
+      <c r="T36" s="76"/>
       <c r="U36" s="40"/>
-      <c r="V36" s="72" t="s">
+      <c r="V36" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="W36" s="73"/>
-      <c r="X36" s="74"/>
+      <c r="W36" s="75"/>
+      <c r="X36" s="76"/>
       <c r="Y36" s="40"/>
-      <c r="Z36" s="72"/>
-      <c r="AA36" s="73"/>
-      <c r="AB36" s="74"/>
+      <c r="Z36" s="74"/>
+      <c r="AA36" s="75"/>
+      <c r="AB36" s="76"/>
       <c r="AC36" s="40"/>
-      <c r="AD36" s="72" t="s">
+      <c r="AD36" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AE36" s="73"/>
-      <c r="AF36" s="74"/>
+      <c r="AE36" s="75"/>
+      <c r="AF36" s="76"/>
       <c r="AG36" s="35"/>
-      <c r="AH36" s="72"/>
-      <c r="AI36" s="73"/>
-      <c r="AJ36" s="74"/>
+      <c r="AH36" s="74"/>
+      <c r="AI36" s="75"/>
+      <c r="AJ36" s="76"/>
       <c r="AK36" s="35"/>
-      <c r="AL36" s="72"/>
-      <c r="AM36" s="73"/>
-      <c r="AN36" s="74"/>
+      <c r="AL36" s="74"/>
+      <c r="AM36" s="75"/>
+      <c r="AN36" s="76"/>
       <c r="AO36" s="12"/>
       <c r="AP36" s="22"/>
       <c r="AQ36" s="31"/>
@@ -4079,11 +4091,11 @@
       <c r="AI37" s="62"/>
       <c r="AJ37" s="63"/>
       <c r="AK37" s="32"/>
-      <c r="AL37" s="128" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM37" s="129"/>
-      <c r="AN37" s="130"/>
+      <c r="AL37" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM37" s="87"/>
+      <c r="AN37" s="88"/>
       <c r="AO37" s="31"/>
       <c r="AP37" s="22"/>
       <c r="AQ37" s="31"/>
@@ -4137,54 +4149,54 @@
     </row>
     <row r="39" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="78" t="s">
+      <c r="B39" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="79"/>
+      <c r="C39" s="65"/>
       <c r="D39" s="57"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="79"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="65"/>
       <c r="H39" s="57"/>
       <c r="I39" s="43"/>
-      <c r="J39" s="78" t="s">
+      <c r="J39" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="K39" s="79"/>
+      <c r="K39" s="65"/>
       <c r="L39" s="57"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="64" t="s">
+      <c r="N39" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="O39" s="65"/>
+      <c r="O39" s="67"/>
       <c r="P39" s="34"/>
       <c r="Q39" s="43"/>
-      <c r="R39" s="64"/>
-      <c r="S39" s="65"/>
+      <c r="R39" s="66"/>
+      <c r="S39" s="67"/>
       <c r="T39" s="34"/>
       <c r="U39" s="36"/>
-      <c r="V39" s="64" t="s">
+      <c r="V39" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="W39" s="65"/>
+      <c r="W39" s="67"/>
       <c r="X39" s="34"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="64"/>
-      <c r="AA39" s="65"/>
+      <c r="Z39" s="66"/>
+      <c r="AA39" s="67"/>
       <c r="AB39" s="34"/>
       <c r="AC39" s="36"/>
-      <c r="AD39" s="64" t="s">
+      <c r="AD39" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="AE39" s="65"/>
+      <c r="AE39" s="67"/>
       <c r="AF39" s="34"/>
       <c r="AG39" s="36"/>
-      <c r="AH39" s="64"/>
-      <c r="AI39" s="65"/>
+      <c r="AH39" s="66"/>
+      <c r="AI39" s="67"/>
       <c r="AJ39" s="34"/>
       <c r="AK39" s="43"/>
-      <c r="AL39" s="64"/>
-      <c r="AM39" s="65"/>
+      <c r="AL39" s="66"/>
+      <c r="AM39" s="67"/>
       <c r="AN39" s="34"/>
       <c r="AO39" s="31"/>
       <c r="AP39" s="31"/>
@@ -4209,39 +4221,39 @@
       <c r="K40" s="81"/>
       <c r="L40" s="82"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="75" t="s">
+      <c r="N40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="O40" s="76"/>
-      <c r="P40" s="77"/>
+      <c r="O40" s="69"/>
+      <c r="P40" s="70"/>
       <c r="Q40" s="37"/>
-      <c r="R40" s="75"/>
-      <c r="S40" s="76"/>
-      <c r="T40" s="77"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="69"/>
+      <c r="T40" s="70"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="75" t="s">
+      <c r="V40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="W40" s="76"/>
-      <c r="X40" s="77"/>
+      <c r="W40" s="69"/>
+      <c r="X40" s="70"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="75"/>
-      <c r="AA40" s="76"/>
-      <c r="AB40" s="77"/>
+      <c r="Z40" s="68"/>
+      <c r="AA40" s="69"/>
+      <c r="AB40" s="70"/>
       <c r="AC40" s="35"/>
-      <c r="AD40" s="75" t="s">
+      <c r="AD40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="AE40" s="76"/>
-      <c r="AF40" s="77"/>
+      <c r="AE40" s="69"/>
+      <c r="AF40" s="70"/>
       <c r="AG40" s="43"/>
-      <c r="AH40" s="75"/>
-      <c r="AI40" s="76"/>
-      <c r="AJ40" s="77"/>
+      <c r="AH40" s="68"/>
+      <c r="AI40" s="69"/>
+      <c r="AJ40" s="70"/>
       <c r="AK40" s="37"/>
-      <c r="AL40" s="75"/>
-      <c r="AM40" s="76"/>
-      <c r="AN40" s="77"/>
+      <c r="AL40" s="68"/>
+      <c r="AM40" s="69"/>
+      <c r="AN40" s="70"/>
       <c r="AO40" s="31"/>
       <c r="AP40" s="31"/>
       <c r="AQ40" s="31"/>
@@ -4261,33 +4273,33 @@
       <c r="K41" s="84"/>
       <c r="L41" s="85"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="71"/>
+      <c r="N41" s="71"/>
+      <c r="O41" s="72"/>
+      <c r="P41" s="73"/>
       <c r="Q41" s="44"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="70"/>
-      <c r="T41" s="71"/>
+      <c r="R41" s="71"/>
+      <c r="S41" s="72"/>
+      <c r="T41" s="73"/>
       <c r="U41" s="37"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="70"/>
-      <c r="X41" s="71"/>
+      <c r="V41" s="71"/>
+      <c r="W41" s="72"/>
+      <c r="X41" s="73"/>
       <c r="Y41" s="44"/>
-      <c r="Z41" s="69"/>
-      <c r="AA41" s="70"/>
-      <c r="AB41" s="71"/>
+      <c r="Z41" s="71"/>
+      <c r="AA41" s="72"/>
+      <c r="AB41" s="73"/>
       <c r="AC41" s="43"/>
-      <c r="AD41" s="69"/>
-      <c r="AE41" s="70"/>
-      <c r="AF41" s="71"/>
+      <c r="AD41" s="71"/>
+      <c r="AE41" s="72"/>
+      <c r="AF41" s="73"/>
       <c r="AG41" s="37"/>
-      <c r="AH41" s="69"/>
-      <c r="AI41" s="70"/>
-      <c r="AJ41" s="71"/>
+      <c r="AH41" s="71"/>
+      <c r="AI41" s="72"/>
+      <c r="AJ41" s="73"/>
       <c r="AK41" s="44"/>
-      <c r="AL41" s="69"/>
-      <c r="AM41" s="70"/>
-      <c r="AN41" s="71"/>
+      <c r="AL41" s="71"/>
+      <c r="AM41" s="72"/>
+      <c r="AN41" s="73"/>
       <c r="AO41" s="31"/>
       <c r="AP41" s="31"/>
       <c r="AQ41" s="31"/>
@@ -4295,55 +4307,55 @@
     </row>
     <row r="42" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
-      <c r="B42" s="66" t="s">
+      <c r="B42" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="67"/>
-      <c r="D42" s="68"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="79"/>
       <c r="E42" s="35"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="68"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="79"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="66" t="s">
+      <c r="J42" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="K42" s="67"/>
-      <c r="L42" s="68"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="79"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="66" t="s">
+      <c r="N42" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="O42" s="67"/>
-      <c r="P42" s="68"/>
+      <c r="O42" s="78"/>
+      <c r="P42" s="79"/>
       <c r="Q42" s="44"/>
-      <c r="R42" s="66"/>
-      <c r="S42" s="67"/>
-      <c r="T42" s="68"/>
+      <c r="R42" s="77"/>
+      <c r="S42" s="78"/>
+      <c r="T42" s="79"/>
       <c r="U42" s="35"/>
-      <c r="V42" s="66" t="s">
+      <c r="V42" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="W42" s="67"/>
-      <c r="X42" s="68"/>
+      <c r="W42" s="78"/>
+      <c r="X42" s="79"/>
       <c r="Y42" s="44"/>
-      <c r="Z42" s="66"/>
-      <c r="AA42" s="67"/>
-      <c r="AB42" s="68"/>
+      <c r="Z42" s="77"/>
+      <c r="AA42" s="78"/>
+      <c r="AB42" s="79"/>
       <c r="AC42" s="35"/>
-      <c r="AD42" s="66" t="s">
+      <c r="AD42" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="AE42" s="67"/>
-      <c r="AF42" s="68"/>
+      <c r="AE42" s="78"/>
+      <c r="AF42" s="79"/>
       <c r="AG42" s="35"/>
-      <c r="AH42" s="66"/>
-      <c r="AI42" s="67"/>
-      <c r="AJ42" s="68"/>
+      <c r="AH42" s="77"/>
+      <c r="AI42" s="78"/>
+      <c r="AJ42" s="79"/>
       <c r="AK42" s="44"/>
-      <c r="AL42" s="66"/>
-      <c r="AM42" s="67"/>
-      <c r="AN42" s="68"/>
+      <c r="AL42" s="77"/>
+      <c r="AM42" s="78"/>
+      <c r="AN42" s="79"/>
       <c r="AO42" s="31"/>
       <c r="AP42" s="31"/>
       <c r="AQ42" s="31"/>
@@ -4453,64 +4465,64 @@
     </row>
     <row r="45" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="78" t="s">
+      <c r="B45" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="79"/>
+      <c r="C45" s="65"/>
       <c r="D45" s="57"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="78" t="s">
+      <c r="F45" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="G45" s="79"/>
+      <c r="G45" s="65"/>
       <c r="H45" s="57"/>
       <c r="I45" s="31"/>
-      <c r="J45" s="78" t="s">
+      <c r="J45" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="K45" s="79"/>
+      <c r="K45" s="65"/>
       <c r="L45" s="57"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="64" t="s">
+      <c r="N45" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="O45" s="65"/>
+      <c r="O45" s="67"/>
       <c r="P45" s="34"/>
       <c r="Q45" s="31"/>
-      <c r="R45" s="64" t="s">
+      <c r="R45" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="S45" s="65"/>
+      <c r="S45" s="67"/>
       <c r="T45" s="34"/>
       <c r="U45" s="36"/>
-      <c r="V45" s="64" t="s">
+      <c r="V45" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="W45" s="65"/>
+      <c r="W45" s="67"/>
       <c r="X45" s="34"/>
       <c r="Y45" s="54"/>
-      <c r="Z45" s="64" t="s">
+      <c r="Z45" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="AA45" s="65"/>
+      <c r="AA45" s="67"/>
       <c r="AB45" s="34"/>
       <c r="AC45" s="36"/>
-      <c r="AD45" s="64" t="s">
+      <c r="AD45" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="AE45" s="65"/>
+      <c r="AE45" s="67"/>
       <c r="AF45" s="34"/>
       <c r="AG45" s="36"/>
-      <c r="AH45" s="64" t="s">
+      <c r="AH45" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="AI45" s="65"/>
+      <c r="AI45" s="67"/>
       <c r="AJ45" s="34"/>
       <c r="AK45" s="31"/>
-      <c r="AL45" s="64" t="s">
+      <c r="AL45" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="AM45" s="65"/>
+      <c r="AM45" s="67"/>
       <c r="AN45" s="34"/>
       <c r="AO45" s="31"/>
       <c r="AP45" s="31"/>
@@ -4537,47 +4549,47 @@
       <c r="K46" s="81"/>
       <c r="L46" s="82"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="75" t="s">
+      <c r="N46" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="O46" s="76"/>
-      <c r="P46" s="77"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="70"/>
       <c r="Q46" s="32"/>
-      <c r="R46" s="75" t="s">
+      <c r="R46" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="S46" s="76"/>
-      <c r="T46" s="77"/>
+      <c r="S46" s="69"/>
+      <c r="T46" s="70"/>
       <c r="U46" s="36"/>
-      <c r="V46" s="75" t="s">
+      <c r="V46" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="W46" s="76"/>
-      <c r="X46" s="77"/>
+      <c r="W46" s="69"/>
+      <c r="X46" s="70"/>
       <c r="Y46" s="35"/>
-      <c r="Z46" s="75" t="s">
+      <c r="Z46" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="AA46" s="76"/>
-      <c r="AB46" s="77"/>
+      <c r="AA46" s="69"/>
+      <c r="AB46" s="70"/>
       <c r="AC46" s="35"/>
-      <c r="AD46" s="75" t="s">
+      <c r="AD46" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="AE46" s="76"/>
-      <c r="AF46" s="77"/>
+      <c r="AE46" s="69"/>
+      <c r="AF46" s="70"/>
       <c r="AG46" s="36"/>
-      <c r="AH46" s="75" t="s">
+      <c r="AH46" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="AI46" s="76"/>
-      <c r="AJ46" s="77"/>
+      <c r="AI46" s="69"/>
+      <c r="AJ46" s="70"/>
       <c r="AK46" s="32"/>
-      <c r="AL46" s="75" t="s">
+      <c r="AL46" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="AM46" s="76"/>
-      <c r="AN46" s="77"/>
+      <c r="AM46" s="69"/>
+      <c r="AN46" s="70"/>
       <c r="AO46" s="31"/>
       <c r="AP46" s="31"/>
       <c r="AQ46" s="31"/>
@@ -4597,33 +4609,33 @@
       <c r="K47" s="84"/>
       <c r="L47" s="85"/>
       <c r="M47" s="4"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="71"/>
+      <c r="N47" s="71"/>
+      <c r="O47" s="72"/>
+      <c r="P47" s="73"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="69"/>
-      <c r="S47" s="70"/>
-      <c r="T47" s="71"/>
+      <c r="R47" s="71"/>
+      <c r="S47" s="72"/>
+      <c r="T47" s="73"/>
       <c r="U47" s="43"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="70"/>
-      <c r="X47" s="71"/>
+      <c r="V47" s="71"/>
+      <c r="W47" s="72"/>
+      <c r="X47" s="73"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="69"/>
-      <c r="AA47" s="70"/>
-      <c r="AB47" s="71"/>
+      <c r="Z47" s="71"/>
+      <c r="AA47" s="72"/>
+      <c r="AB47" s="73"/>
       <c r="AC47" s="31"/>
-      <c r="AD47" s="69"/>
-      <c r="AE47" s="70"/>
-      <c r="AF47" s="71"/>
+      <c r="AD47" s="71"/>
+      <c r="AE47" s="72"/>
+      <c r="AF47" s="73"/>
       <c r="AG47" s="43"/>
-      <c r="AH47" s="69"/>
-      <c r="AI47" s="70"/>
-      <c r="AJ47" s="71"/>
+      <c r="AH47" s="71"/>
+      <c r="AI47" s="72"/>
+      <c r="AJ47" s="73"/>
       <c r="AK47" s="43"/>
-      <c r="AL47" s="69"/>
-      <c r="AM47" s="70"/>
-      <c r="AN47" s="71"/>
+      <c r="AL47" s="71"/>
+      <c r="AM47" s="72"/>
+      <c r="AN47" s="73"/>
       <c r="AO47" s="31"/>
       <c r="AP47" s="31"/>
       <c r="AQ47" s="31"/>
@@ -4631,130 +4643,130 @@
     </row>
     <row r="48" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="73"/>
-      <c r="D48" s="74"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="76"/>
       <c r="E48" s="37"/>
-      <c r="F48" s="72" t="s">
+      <c r="F48" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="G48" s="73"/>
-      <c r="H48" s="74"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="76"/>
       <c r="I48" s="43"/>
-      <c r="J48" s="72" t="s">
+      <c r="J48" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="K48" s="73"/>
-      <c r="L48" s="74"/>
+      <c r="K48" s="75"/>
+      <c r="L48" s="76"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="66" t="s">
+      <c r="N48" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="O48" s="67"/>
-      <c r="P48" s="68"/>
+      <c r="O48" s="78"/>
+      <c r="P48" s="79"/>
       <c r="Q48" s="43"/>
-      <c r="R48" s="72" t="s">
+      <c r="R48" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="S48" s="73"/>
-      <c r="T48" s="74"/>
+      <c r="S48" s="75"/>
+      <c r="T48" s="76"/>
       <c r="U48" s="37"/>
-      <c r="V48" s="72" t="s">
+      <c r="V48" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="W48" s="73"/>
-      <c r="X48" s="74"/>
+      <c r="W48" s="75"/>
+      <c r="X48" s="76"/>
       <c r="Y48" s="40"/>
-      <c r="Z48" s="72" t="s">
+      <c r="Z48" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="AA48" s="73"/>
-      <c r="AB48" s="74"/>
+      <c r="AA48" s="75"/>
+      <c r="AB48" s="76"/>
       <c r="AC48" s="35"/>
-      <c r="AD48" s="72" t="s">
+      <c r="AD48" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="AE48" s="73"/>
-      <c r="AF48" s="74"/>
+      <c r="AE48" s="75"/>
+      <c r="AF48" s="76"/>
       <c r="AG48" s="37"/>
-      <c r="AH48" s="72" t="s">
+      <c r="AH48" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="AI48" s="73"/>
-      <c r="AJ48" s="74"/>
+      <c r="AI48" s="75"/>
+      <c r="AJ48" s="76"/>
       <c r="AK48" s="43"/>
-      <c r="AL48" s="72" t="s">
+      <c r="AL48" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="AM48" s="73"/>
-      <c r="AN48" s="74"/>
+      <c r="AM48" s="75"/>
+      <c r="AN48" s="76"/>
       <c r="AO48" s="31"/>
       <c r="AP48" s="31"/>
       <c r="AQ48" s="31"/>
       <c r="AR48" s="13"/>
     </row>
     <row r="49" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="72" t="s">
+      <c r="B49" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="73"/>
-      <c r="D49" s="74"/>
+      <c r="C49" s="75"/>
+      <c r="D49" s="76"/>
       <c r="E49" s="44"/>
-      <c r="F49" s="72" t="s">
+      <c r="F49" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="73"/>
-      <c r="H49" s="74"/>
+      <c r="G49" s="75"/>
+      <c r="H49" s="76"/>
       <c r="I49" s="43"/>
-      <c r="J49" s="72" t="s">
+      <c r="J49" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="73"/>
-      <c r="L49" s="74"/>
+      <c r="K49" s="75"/>
+      <c r="L49" s="76"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="72" t="s">
+      <c r="N49" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="O49" s="73"/>
-      <c r="P49" s="74"/>
+      <c r="O49" s="75"/>
+      <c r="P49" s="76"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="72" t="s">
+      <c r="R49" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="S49" s="73"/>
-      <c r="T49" s="74"/>
+      <c r="S49" s="75"/>
+      <c r="T49" s="76"/>
       <c r="U49" s="44"/>
-      <c r="V49" s="72" t="s">
+      <c r="V49" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="W49" s="73"/>
-      <c r="X49" s="74"/>
+      <c r="W49" s="75"/>
+      <c r="X49" s="76"/>
       <c r="Y49" s="44"/>
-      <c r="Z49" s="72" t="s">
+      <c r="Z49" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="AA49" s="73"/>
-      <c r="AB49" s="74"/>
+      <c r="AA49" s="75"/>
+      <c r="AB49" s="76"/>
       <c r="AC49" s="43"/>
-      <c r="AD49" s="72" t="s">
+      <c r="AD49" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="AE49" s="73"/>
-      <c r="AF49" s="74"/>
+      <c r="AE49" s="75"/>
+      <c r="AF49" s="76"/>
       <c r="AG49" s="44"/>
-      <c r="AH49" s="72" t="s">
+      <c r="AH49" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="AI49" s="73"/>
-      <c r="AJ49" s="74"/>
+      <c r="AI49" s="75"/>
+      <c r="AJ49" s="76"/>
       <c r="AK49" s="43"/>
-      <c r="AL49" s="72" t="s">
+      <c r="AL49" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="AM49" s="73"/>
-      <c r="AN49" s="74"/>
+      <c r="AM49" s="75"/>
+      <c r="AN49" s="76"/>
       <c r="AO49" s="31"/>
       <c r="AP49" s="31"/>
       <c r="AQ49" s="31"/>
@@ -4857,64 +4869,64 @@
       <c r="AR51" s="13"/>
     </row>
     <row r="52" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="78" t="s">
+      <c r="B52" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="79"/>
+      <c r="C52" s="65"/>
       <c r="D52" s="57"/>
       <c r="E52" s="50"/>
-      <c r="F52" s="78" t="s">
+      <c r="F52" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="G52" s="79"/>
+      <c r="G52" s="65"/>
       <c r="H52" s="57"/>
       <c r="I52" s="32"/>
-      <c r="J52" s="78" t="s">
+      <c r="J52" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="K52" s="79"/>
+      <c r="K52" s="65"/>
       <c r="L52" s="57"/>
       <c r="M52" s="14"/>
-      <c r="N52" s="64" t="s">
+      <c r="N52" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="O52" s="65"/>
+      <c r="O52" s="67"/>
       <c r="P52" s="34"/>
       <c r="Q52" s="36"/>
-      <c r="R52" s="64" t="s">
+      <c r="R52" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="S52" s="65"/>
+      <c r="S52" s="67"/>
       <c r="T52" s="34"/>
       <c r="U52" s="36"/>
-      <c r="V52" s="64" t="s">
+      <c r="V52" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="W52" s="65"/>
+      <c r="W52" s="67"/>
       <c r="X52" s="34"/>
       <c r="Y52" s="37"/>
-      <c r="Z52" s="64" t="s">
+      <c r="Z52" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="AA52" s="65"/>
+      <c r="AA52" s="67"/>
       <c r="AB52" s="34"/>
       <c r="AC52" s="32"/>
-      <c r="AD52" s="64" t="s">
+      <c r="AD52" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="AE52" s="65"/>
+      <c r="AE52" s="67"/>
       <c r="AF52" s="34"/>
       <c r="AG52" s="50"/>
-      <c r="AH52" s="64" t="s">
+      <c r="AH52" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="AI52" s="65"/>
+      <c r="AI52" s="67"/>
       <c r="AJ52" s="34"/>
       <c r="AK52" s="32"/>
-      <c r="AL52" s="64" t="s">
+      <c r="AL52" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="AM52" s="65"/>
+      <c r="AM52" s="67"/>
       <c r="AN52" s="34"/>
       <c r="AR52" s="13"/>
     </row>
@@ -4937,47 +4949,47 @@
       <c r="K53" s="81"/>
       <c r="L53" s="82"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="75" t="s">
+      <c r="N53" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="O53" s="76"/>
-      <c r="P53" s="77"/>
+      <c r="O53" s="69"/>
+      <c r="P53" s="70"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="75" t="s">
+      <c r="R53" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="S53" s="76"/>
-      <c r="T53" s="77"/>
+      <c r="S53" s="69"/>
+      <c r="T53" s="70"/>
       <c r="U53" s="36"/>
-      <c r="V53" s="75" t="s">
+      <c r="V53" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="W53" s="76"/>
-      <c r="X53" s="77"/>
+      <c r="W53" s="69"/>
+      <c r="X53" s="70"/>
       <c r="Y53" s="50"/>
-      <c r="Z53" s="75" t="s">
+      <c r="Z53" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="AA53" s="76"/>
-      <c r="AB53" s="77"/>
+      <c r="AA53" s="69"/>
+      <c r="AB53" s="70"/>
       <c r="AC53" s="54"/>
-      <c r="AD53" s="75" t="s">
+      <c r="AD53" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="AE53" s="76"/>
-      <c r="AF53" s="77"/>
+      <c r="AE53" s="69"/>
+      <c r="AF53" s="70"/>
       <c r="AG53" s="32"/>
-      <c r="AH53" s="75" t="s">
+      <c r="AH53" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="AI53" s="76"/>
-      <c r="AJ53" s="77"/>
+      <c r="AI53" s="69"/>
+      <c r="AJ53" s="70"/>
       <c r="AK53" s="54"/>
-      <c r="AL53" s="75" t="s">
+      <c r="AL53" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="AM53" s="76"/>
-      <c r="AN53" s="77"/>
+      <c r="AM53" s="69"/>
+      <c r="AN53" s="70"/>
       <c r="AR53" s="13"/>
     </row>
     <row r="54" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4993,159 +5005,159 @@
       <c r="K54" s="84"/>
       <c r="L54" s="85"/>
       <c r="M54" s="4"/>
-      <c r="N54" s="69"/>
-      <c r="O54" s="70"/>
-      <c r="P54" s="71"/>
+      <c r="N54" s="71"/>
+      <c r="O54" s="72"/>
+      <c r="P54" s="73"/>
       <c r="Q54" s="37"/>
-      <c r="R54" s="69" t="s">
+      <c r="R54" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="S54" s="70"/>
-      <c r="T54" s="71"/>
+      <c r="S54" s="72"/>
+      <c r="T54" s="73"/>
       <c r="U54" s="43"/>
-      <c r="V54" s="69"/>
-      <c r="W54" s="70"/>
-      <c r="X54" s="71"/>
+      <c r="V54" s="71"/>
+      <c r="W54" s="72"/>
+      <c r="X54" s="73"/>
       <c r="Y54" s="50"/>
-      <c r="Z54" s="69"/>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="71"/>
+      <c r="Z54" s="71"/>
+      <c r="AA54" s="72"/>
+      <c r="AB54" s="73"/>
       <c r="AC54" s="35"/>
-      <c r="AD54" s="69"/>
-      <c r="AE54" s="70"/>
-      <c r="AF54" s="71"/>
+      <c r="AD54" s="71"/>
+      <c r="AE54" s="72"/>
+      <c r="AF54" s="73"/>
       <c r="AG54" s="32"/>
-      <c r="AH54" s="69"/>
-      <c r="AI54" s="70"/>
-      <c r="AJ54" s="71"/>
+      <c r="AH54" s="71"/>
+      <c r="AI54" s="72"/>
+      <c r="AJ54" s="73"/>
       <c r="AK54" s="35"/>
-      <c r="AL54" s="69"/>
-      <c r="AM54" s="70"/>
-      <c r="AN54" s="71"/>
+      <c r="AL54" s="71"/>
+      <c r="AM54" s="72"/>
+      <c r="AN54" s="73"/>
       <c r="AR54" s="13"/>
     </row>
     <row r="55" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="66" t="s">
+      <c r="B55" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="67"/>
-      <c r="D55" s="68"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="79"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="G55" s="67"/>
-      <c r="H55" s="68"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="79"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="66" t="s">
+      <c r="J55" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K55" s="67"/>
-      <c r="L55" s="68"/>
+      <c r="K55" s="78"/>
+      <c r="L55" s="79"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="66" t="s">
+      <c r="N55" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="O55" s="67"/>
-      <c r="P55" s="68"/>
+      <c r="O55" s="78"/>
+      <c r="P55" s="79"/>
       <c r="Q55" s="44"/>
-      <c r="R55" s="66" t="s">
+      <c r="R55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="S55" s="67"/>
-      <c r="T55" s="68"/>
+      <c r="S55" s="78"/>
+      <c r="T55" s="79"/>
       <c r="U55" s="43"/>
-      <c r="V55" s="66" t="s">
+      <c r="V55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="W55" s="67"/>
-      <c r="X55" s="68"/>
+      <c r="W55" s="78"/>
+      <c r="X55" s="79"/>
       <c r="Y55" s="32"/>
-      <c r="Z55" s="66" t="s">
+      <c r="Z55" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="AA55" s="67"/>
-      <c r="AB55" s="68"/>
+      <c r="AA55" s="78"/>
+      <c r="AB55" s="79"/>
       <c r="AC55" s="35"/>
-      <c r="AD55" s="66" t="s">
+      <c r="AD55" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="AE55" s="67"/>
-      <c r="AF55" s="68"/>
+      <c r="AE55" s="78"/>
+      <c r="AF55" s="79"/>
       <c r="AG55" s="37"/>
-      <c r="AH55" s="66" t="s">
+      <c r="AH55" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AI55" s="67"/>
-      <c r="AJ55" s="68"/>
+      <c r="AI55" s="78"/>
+      <c r="AJ55" s="79"/>
       <c r="AK55" s="35"/>
-      <c r="AL55" s="66" t="s">
+      <c r="AL55" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="AM55" s="67"/>
-      <c r="AN55" s="68"/>
+      <c r="AM55" s="78"/>
+      <c r="AN55" s="79"/>
       <c r="AR55" s="13"/>
     </row>
     <row r="56" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="72" t="s">
+      <c r="B56" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="73"/>
-      <c r="D56" s="74"/>
+      <c r="C56" s="75"/>
+      <c r="D56" s="76"/>
       <c r="E56" s="44"/>
-      <c r="F56" s="72" t="s">
+      <c r="F56" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="G56" s="73"/>
-      <c r="H56" s="74"/>
+      <c r="G56" s="75"/>
+      <c r="H56" s="76"/>
       <c r="I56" s="40"/>
-      <c r="J56" s="72" t="s">
+      <c r="J56" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="K56" s="73"/>
-      <c r="L56" s="74"/>
+      <c r="K56" s="75"/>
+      <c r="L56" s="76"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="72" t="s">
+      <c r="N56" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="O56" s="73"/>
-      <c r="P56" s="74"/>
+      <c r="O56" s="75"/>
+      <c r="P56" s="76"/>
       <c r="Q56" s="44"/>
-      <c r="R56" s="72" t="s">
+      <c r="R56" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="S56" s="73"/>
-      <c r="T56" s="74"/>
+      <c r="S56" s="75"/>
+      <c r="T56" s="76"/>
       <c r="U56" s="44"/>
-      <c r="V56" s="72" t="s">
+      <c r="V56" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="W56" s="73"/>
-      <c r="X56" s="74"/>
+      <c r="W56" s="75"/>
+      <c r="X56" s="76"/>
       <c r="Y56" s="32"/>
-      <c r="Z56" s="72" t="s">
+      <c r="Z56" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AA56" s="73"/>
-      <c r="AB56" s="74"/>
+      <c r="AA56" s="75"/>
+      <c r="AB56" s="76"/>
       <c r="AC56" s="40"/>
-      <c r="AD56" s="72" t="s">
+      <c r="AD56" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="AE56" s="73"/>
-      <c r="AF56" s="74"/>
+      <c r="AE56" s="75"/>
+      <c r="AF56" s="76"/>
       <c r="AG56" s="44"/>
-      <c r="AH56" s="72" t="s">
+      <c r="AH56" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="AI56" s="73"/>
-      <c r="AJ56" s="74"/>
+      <c r="AI56" s="75"/>
+      <c r="AJ56" s="76"/>
       <c r="AK56" s="40"/>
-      <c r="AL56" s="72" t="s">
+      <c r="AL56" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="AM56" s="73"/>
-      <c r="AN56" s="74"/>
+      <c r="AM56" s="75"/>
+      <c r="AN56" s="76"/>
       <c r="AR56" s="13"/>
     </row>
     <row r="57" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5239,64 +5251,64 @@
       <c r="AR58" s="13"/>
     </row>
     <row r="59" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="78" t="s">
+      <c r="B59" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C59" s="79"/>
+      <c r="C59" s="65"/>
       <c r="D59" s="57" t="s">
         <v>66</v>
       </c>
       <c r="E59" s="36"/>
-      <c r="F59" s="78" t="s">
+      <c r="F59" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="G59" s="79"/>
+      <c r="G59" s="65"/>
       <c r="H59" s="57" t="s">
         <v>53</v>
       </c>
       <c r="I59" s="32"/>
-      <c r="J59" s="78" t="s">
+      <c r="J59" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="K59" s="79"/>
+      <c r="K59" s="65"/>
       <c r="L59" s="57"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="64"/>
-      <c r="O59" s="65"/>
+      <c r="N59" s="66"/>
+      <c r="O59" s="67"/>
       <c r="P59" s="34"/>
       <c r="Q59" s="36"/>
-      <c r="R59" s="64"/>
-      <c r="S59" s="65"/>
+      <c r="R59" s="66"/>
+      <c r="S59" s="67"/>
       <c r="T59" s="34"/>
       <c r="U59" s="36"/>
-      <c r="V59" s="64"/>
-      <c r="W59" s="65"/>
+      <c r="V59" s="66"/>
+      <c r="W59" s="67"/>
       <c r="X59" s="34"/>
       <c r="Y59" s="36"/>
-      <c r="Z59" s="64"/>
-      <c r="AA59" s="65"/>
+      <c r="Z59" s="66"/>
+      <c r="AA59" s="67"/>
       <c r="AB59" s="34"/>
       <c r="AC59" s="36"/>
-      <c r="AD59" s="64" t="s">
+      <c r="AD59" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="AE59" s="65"/>
+      <c r="AE59" s="67"/>
       <c r="AF59" s="34" t="s">
         <v>53</v>
       </c>
       <c r="AG59" s="36"/>
-      <c r="AH59" s="64" t="s">
+      <c r="AH59" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="AI59" s="65"/>
+      <c r="AI59" s="67"/>
       <c r="AJ59" s="34" t="s">
         <v>53</v>
       </c>
       <c r="AK59" s="32"/>
-      <c r="AL59" s="64" t="s">
+      <c r="AL59" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="AM59" s="65"/>
+      <c r="AM59" s="67"/>
       <c r="AN59" s="34" t="s">
         <v>53</v>
       </c>
@@ -5321,39 +5333,39 @@
       <c r="K60" s="81"/>
       <c r="L60" s="82"/>
       <c r="M60" s="4"/>
-      <c r="N60" s="75"/>
-      <c r="O60" s="76"/>
-      <c r="P60" s="77"/>
+      <c r="N60" s="68"/>
+      <c r="O60" s="69"/>
+      <c r="P60" s="70"/>
       <c r="Q60" s="37"/>
-      <c r="R60" s="75"/>
-      <c r="S60" s="76"/>
-      <c r="T60" s="77"/>
+      <c r="R60" s="68"/>
+      <c r="S60" s="69"/>
+      <c r="T60" s="70"/>
       <c r="U60" s="36"/>
-      <c r="V60" s="75"/>
-      <c r="W60" s="76"/>
-      <c r="X60" s="77"/>
+      <c r="V60" s="68"/>
+      <c r="W60" s="69"/>
+      <c r="X60" s="70"/>
       <c r="Y60" s="37"/>
-      <c r="Z60" s="75"/>
-      <c r="AA60" s="76"/>
-      <c r="AB60" s="77"/>
+      <c r="Z60" s="68"/>
+      <c r="AA60" s="69"/>
+      <c r="AB60" s="70"/>
       <c r="AC60" s="36"/>
-      <c r="AD60" s="75" t="s">
+      <c r="AD60" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="AE60" s="76"/>
-      <c r="AF60" s="77"/>
+      <c r="AE60" s="69"/>
+      <c r="AF60" s="70"/>
       <c r="AG60" s="36"/>
-      <c r="AH60" s="75" t="s">
+      <c r="AH60" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="AI60" s="76"/>
-      <c r="AJ60" s="77"/>
+      <c r="AI60" s="69"/>
+      <c r="AJ60" s="70"/>
       <c r="AK60" s="54"/>
-      <c r="AL60" s="75" t="s">
+      <c r="AL60" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="AM60" s="76"/>
-      <c r="AN60" s="77"/>
+      <c r="AM60" s="69"/>
+      <c r="AN60" s="70"/>
       <c r="AR60" s="13"/>
     </row>
     <row r="61" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5371,141 +5383,141 @@
       <c r="K61" s="84"/>
       <c r="L61" s="85"/>
       <c r="M61" s="4"/>
-      <c r="N61" s="69"/>
-      <c r="O61" s="70"/>
-      <c r="P61" s="71"/>
+      <c r="N61" s="71"/>
+      <c r="O61" s="72"/>
+      <c r="P61" s="73"/>
       <c r="Q61" s="36"/>
-      <c r="R61" s="69"/>
-      <c r="S61" s="70"/>
-      <c r="T61" s="71"/>
+      <c r="R61" s="71"/>
+      <c r="S61" s="72"/>
+      <c r="T61" s="73"/>
       <c r="U61" s="35"/>
-      <c r="V61" s="69"/>
-      <c r="W61" s="70"/>
-      <c r="X61" s="71"/>
+      <c r="V61" s="71"/>
+      <c r="W61" s="72"/>
+      <c r="X61" s="73"/>
       <c r="Y61" s="36"/>
-      <c r="Z61" s="69"/>
-      <c r="AA61" s="70"/>
-      <c r="AB61" s="71"/>
+      <c r="Z61" s="71"/>
+      <c r="AA61" s="72"/>
+      <c r="AB61" s="73"/>
       <c r="AC61" s="35"/>
-      <c r="AD61" s="69"/>
-      <c r="AE61" s="70"/>
-      <c r="AF61" s="71"/>
+      <c r="AD61" s="71"/>
+      <c r="AE61" s="72"/>
+      <c r="AF61" s="73"/>
       <c r="AG61" s="43"/>
-      <c r="AH61" s="69"/>
-      <c r="AI61" s="70"/>
-      <c r="AJ61" s="71"/>
+      <c r="AH61" s="71"/>
+      <c r="AI61" s="72"/>
+      <c r="AJ61" s="73"/>
       <c r="AK61" s="35"/>
-      <c r="AL61" s="69"/>
-      <c r="AM61" s="70"/>
-      <c r="AN61" s="71"/>
+      <c r="AL61" s="71"/>
+      <c r="AM61" s="72"/>
+      <c r="AN61" s="73"/>
       <c r="AR61" s="13"/>
     </row>
     <row r="62" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="122" t="s">
+      <c r="B62" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="123"/>
-      <c r="D62" s="124"/>
+      <c r="C62" s="93"/>
+      <c r="D62" s="94"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="122" t="s">
+      <c r="F62" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="G62" s="123"/>
-      <c r="H62" s="124"/>
+      <c r="G62" s="93"/>
+      <c r="H62" s="94"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="66" t="s">
+      <c r="J62" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="K62" s="67"/>
-      <c r="L62" s="68"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="79"/>
       <c r="M62" s="4"/>
-      <c r="N62" s="72"/>
-      <c r="O62" s="73"/>
-      <c r="P62" s="74"/>
+      <c r="N62" s="74"/>
+      <c r="O62" s="75"/>
+      <c r="P62" s="76"/>
       <c r="Q62" s="43"/>
-      <c r="R62" s="72"/>
-      <c r="S62" s="73"/>
-      <c r="T62" s="74"/>
+      <c r="R62" s="74"/>
+      <c r="S62" s="75"/>
+      <c r="T62" s="76"/>
       <c r="U62" s="43"/>
-      <c r="V62" s="72"/>
-      <c r="W62" s="73"/>
-      <c r="X62" s="74"/>
+      <c r="V62" s="74"/>
+      <c r="W62" s="75"/>
+      <c r="X62" s="76"/>
       <c r="Y62" s="43"/>
-      <c r="Z62" s="72"/>
-      <c r="AA62" s="73"/>
-      <c r="AB62" s="74"/>
+      <c r="Z62" s="74"/>
+      <c r="AA62" s="75"/>
+      <c r="AB62" s="76"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="72" t="s">
+      <c r="AD62" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="AE62" s="73"/>
-      <c r="AF62" s="74"/>
+      <c r="AE62" s="75"/>
+      <c r="AF62" s="76"/>
       <c r="AG62" s="37"/>
-      <c r="AH62" s="72" t="s">
+      <c r="AH62" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="AI62" s="73"/>
-      <c r="AJ62" s="74"/>
+      <c r="AI62" s="75"/>
+      <c r="AJ62" s="76"/>
       <c r="AK62" s="37"/>
-      <c r="AL62" s="72" t="s">
+      <c r="AL62" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM62" s="90"/>
+      <c r="AN62" s="91"/>
+      <c r="AR62" s="13"/>
+    </row>
+    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" s="75"/>
+      <c r="D63" s="76"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="75"/>
+      <c r="H63" s="76"/>
+      <c r="I63" s="44"/>
+      <c r="J63" s="89" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="90"/>
+      <c r="L63" s="91"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="74"/>
+      <c r="O63" s="75"/>
+      <c r="P63" s="76"/>
+      <c r="Q63" s="50"/>
+      <c r="R63" s="74"/>
+      <c r="S63" s="75"/>
+      <c r="T63" s="76"/>
+      <c r="U63" s="44"/>
+      <c r="V63" s="74"/>
+      <c r="W63" s="75"/>
+      <c r="X63" s="76"/>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="74"/>
+      <c r="AA63" s="75"/>
+      <c r="AB63" s="76"/>
+      <c r="AC63" s="44"/>
+      <c r="AD63" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE63" s="75"/>
+      <c r="AF63" s="76"/>
+      <c r="AG63" s="44"/>
+      <c r="AH63" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI63" s="75"/>
+      <c r="AJ63" s="76"/>
+      <c r="AK63" s="44"/>
+      <c r="AL63" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="AM62" s="73"/>
-      <c r="AN62" s="74"/>
-      <c r="AR62" s="13"/>
-    </row>
-    <row r="63" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="C63" s="73"/>
-      <c r="D63" s="74"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="73"/>
-      <c r="H63" s="74"/>
-      <c r="I63" s="44"/>
-      <c r="J63" s="125" t="s">
-        <v>17</v>
-      </c>
-      <c r="K63" s="126"/>
-      <c r="L63" s="127"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="72"/>
-      <c r="O63" s="73"/>
-      <c r="P63" s="74"/>
-      <c r="Q63" s="50"/>
-      <c r="R63" s="72"/>
-      <c r="S63" s="73"/>
-      <c r="T63" s="74"/>
-      <c r="U63" s="44"/>
-      <c r="V63" s="72"/>
-      <c r="W63" s="73"/>
-      <c r="X63" s="74"/>
-      <c r="Y63" s="50"/>
-      <c r="Z63" s="72"/>
-      <c r="AA63" s="73"/>
-      <c r="AB63" s="74"/>
-      <c r="AC63" s="44"/>
-      <c r="AD63" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE63" s="73"/>
-      <c r="AF63" s="74"/>
-      <c r="AG63" s="44"/>
-      <c r="AH63" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI63" s="73"/>
-      <c r="AJ63" s="74"/>
-      <c r="AK63" s="44"/>
-      <c r="AL63" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM63" s="73"/>
-      <c r="AN63" s="74"/>
+      <c r="AM63" s="75"/>
+      <c r="AN63" s="76"/>
       <c r="AR63" s="13"/>
     </row>
     <row r="64" spans="2:44" s="12" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5543,11 +5555,11 @@
       <c r="AA64" s="62"/>
       <c r="AB64" s="63"/>
       <c r="AC64" s="50"/>
-      <c r="AD64" s="98" t="s">
+      <c r="AD64" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="AE64" s="99"/>
-      <c r="AF64" s="100"/>
+      <c r="AE64" s="125"/>
+      <c r="AF64" s="126"/>
       <c r="AG64" s="44"/>
       <c r="AH64" s="61" t="s">
         <v>27</v>
@@ -5622,23 +5634,23 @@
       <c r="K66" s="33"/>
       <c r="L66" s="33"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="103" t="s">
+      <c r="N66" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="O66" s="103"/>
-      <c r="P66" s="103"/>
-      <c r="Q66" s="103"/>
-      <c r="R66" s="103"/>
-      <c r="S66" s="103"/>
-      <c r="T66" s="103"/>
-      <c r="U66" s="103"/>
-      <c r="V66" s="103"/>
-      <c r="W66" s="103"/>
-      <c r="X66" s="103"/>
-      <c r="Y66" s="103"/>
-      <c r="Z66" s="103"/>
-      <c r="AA66" s="103"/>
-      <c r="AB66" s="103"/>
+      <c r="O66" s="95"/>
+      <c r="P66" s="95"/>
+      <c r="Q66" s="95"/>
+      <c r="R66" s="95"/>
+      <c r="S66" s="95"/>
+      <c r="T66" s="95"/>
+      <c r="U66" s="95"/>
+      <c r="V66" s="95"/>
+      <c r="W66" s="95"/>
+      <c r="X66" s="95"/>
+      <c r="Y66" s="95"/>
+      <c r="Z66" s="95"/>
+      <c r="AA66" s="95"/>
+      <c r="AB66" s="95"/>
       <c r="AD66" s="40"/>
       <c r="AE66" s="33"/>
       <c r="AF66" s="33"/>
@@ -5669,21 +5681,21 @@
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="103"/>
-      <c r="O67" s="103"/>
-      <c r="P67" s="103"/>
-      <c r="Q67" s="103"/>
-      <c r="R67" s="103"/>
-      <c r="S67" s="103"/>
-      <c r="T67" s="103"/>
-      <c r="U67" s="103"/>
-      <c r="V67" s="103"/>
-      <c r="W67" s="103"/>
-      <c r="X67" s="103"/>
-      <c r="Y67" s="103"/>
-      <c r="Z67" s="103"/>
-      <c r="AA67" s="103"/>
-      <c r="AB67" s="103"/>
+      <c r="N67" s="95"/>
+      <c r="O67" s="95"/>
+      <c r="P67" s="95"/>
+      <c r="Q67" s="95"/>
+      <c r="R67" s="95"/>
+      <c r="S67" s="95"/>
+      <c r="T67" s="95"/>
+      <c r="U67" s="95"/>
+      <c r="V67" s="95"/>
+      <c r="W67" s="95"/>
+      <c r="X67" s="95"/>
+      <c r="Y67" s="95"/>
+      <c r="Z67" s="95"/>
+      <c r="AA67" s="95"/>
+      <c r="AB67" s="95"/>
       <c r="AC67" s="21"/>
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
@@ -5703,51 +5715,53 @@
     </row>
     <row r="68" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="12"/>
-      <c r="B68" s="78"/>
-      <c r="C68" s="79"/>
+      <c r="B68" s="64"/>
+      <c r="C68" s="65"/>
       <c r="D68" s="57"/>
       <c r="E68" s="32"/>
-      <c r="F68" s="78"/>
-      <c r="G68" s="79"/>
+      <c r="F68" s="64"/>
+      <c r="G68" s="65"/>
       <c r="H68" s="57"/>
       <c r="I68" s="32"/>
-      <c r="J68" s="78"/>
-      <c r="K68" s="79"/>
+      <c r="J68" s="64"/>
+      <c r="K68" s="65"/>
       <c r="L68" s="57"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="64"/>
-      <c r="O68" s="65"/>
+      <c r="N68" s="66"/>
+      <c r="O68" s="67"/>
       <c r="P68" s="34"/>
       <c r="Q68" s="44"/>
-      <c r="R68" s="64"/>
-      <c r="S68" s="65"/>
+      <c r="R68" s="66"/>
+      <c r="S68" s="67"/>
       <c r="T68" s="34"/>
       <c r="U68" s="36"/>
-      <c r="V68" s="64"/>
-      <c r="W68" s="65"/>
+      <c r="V68" s="66"/>
+      <c r="W68" s="67"/>
       <c r="X68" s="34"/>
       <c r="Y68" s="32"/>
-      <c r="Z68" s="64" t="s">
+      <c r="Z68" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="AA68" s="65"/>
+      <c r="AA68" s="67"/>
       <c r="AB68" s="34"/>
       <c r="AC68" s="32"/>
-      <c r="AD68" s="64" t="s">
+      <c r="AD68" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="AE68" s="65"/>
+      <c r="AE68" s="67"/>
       <c r="AF68" s="34"/>
       <c r="AG68" s="32"/>
-      <c r="AH68" s="64" t="s">
+      <c r="AH68" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="AI68" s="65"/>
+      <c r="AI68" s="67"/>
       <c r="AJ68" s="34"/>
       <c r="AK68" s="32"/>
-      <c r="AL68" s="64"/>
-      <c r="AM68" s="65"/>
-      <c r="AN68" s="34"/>
+      <c r="AL68" s="127" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM68" s="128"/>
+      <c r="AN68" s="60"/>
       <c r="AO68" s="17"/>
       <c r="AP68" s="27" t="s">
         <v>32</v>
@@ -5769,39 +5783,39 @@
       <c r="K69" s="81"/>
       <c r="L69" s="82"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="75"/>
-      <c r="O69" s="76"/>
-      <c r="P69" s="77"/>
+      <c r="N69" s="68"/>
+      <c r="O69" s="69"/>
+      <c r="P69" s="70"/>
       <c r="Q69" s="44"/>
-      <c r="R69" s="75"/>
-      <c r="S69" s="76"/>
-      <c r="T69" s="77"/>
+      <c r="R69" s="68"/>
+      <c r="S69" s="69"/>
+      <c r="T69" s="70"/>
       <c r="U69" s="32"/>
-      <c r="V69" s="75"/>
-      <c r="W69" s="76"/>
-      <c r="X69" s="77"/>
+      <c r="V69" s="68"/>
+      <c r="W69" s="69"/>
+      <c r="X69" s="70"/>
       <c r="Y69" s="32"/>
-      <c r="Z69" s="75" t="s">
+      <c r="Z69" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="AA69" s="76"/>
-      <c r="AB69" s="77"/>
+      <c r="AA69" s="69"/>
+      <c r="AB69" s="70"/>
       <c r="AC69" s="35"/>
-      <c r="AD69" s="75" t="s">
+      <c r="AD69" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="AE69" s="76"/>
-      <c r="AF69" s="77"/>
+      <c r="AE69" s="69"/>
+      <c r="AF69" s="70"/>
       <c r="AG69" s="32"/>
-      <c r="AH69" s="75" t="s">
+      <c r="AH69" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="AI69" s="76"/>
-      <c r="AJ69" s="77"/>
+      <c r="AI69" s="69"/>
+      <c r="AJ69" s="70"/>
       <c r="AK69" s="32"/>
-      <c r="AL69" s="75"/>
-      <c r="AM69" s="76"/>
-      <c r="AN69" s="77"/>
+      <c r="AL69" s="68"/>
+      <c r="AM69" s="69"/>
+      <c r="AN69" s="70"/>
       <c r="AO69" s="12"/>
       <c r="AP69" s="27" t="s">
         <v>33</v>
@@ -5823,39 +5837,39 @@
       <c r="K70" s="84"/>
       <c r="L70" s="85"/>
       <c r="M70" s="9"/>
-      <c r="N70" s="69"/>
-      <c r="O70" s="70"/>
-      <c r="P70" s="71"/>
+      <c r="N70" s="71"/>
+      <c r="O70" s="72"/>
+      <c r="P70" s="73"/>
       <c r="Q70" s="44"/>
-      <c r="R70" s="69"/>
-      <c r="S70" s="70"/>
-      <c r="T70" s="71"/>
+      <c r="R70" s="71"/>
+      <c r="S70" s="72"/>
+      <c r="T70" s="73"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="69"/>
-      <c r="W70" s="70"/>
-      <c r="X70" s="71"/>
+      <c r="V70" s="71"/>
+      <c r="W70" s="72"/>
+      <c r="X70" s="73"/>
       <c r="Y70" s="32"/>
-      <c r="Z70" s="69" t="s">
+      <c r="Z70" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="AA70" s="70"/>
-      <c r="AB70" s="71"/>
+      <c r="AA70" s="72"/>
+      <c r="AB70" s="73"/>
       <c r="AC70" s="31"/>
-      <c r="AD70" s="69" t="s">
+      <c r="AD70" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="AE70" s="70"/>
-      <c r="AF70" s="71"/>
+      <c r="AE70" s="72"/>
+      <c r="AF70" s="73"/>
       <c r="AG70" s="32"/>
-      <c r="AH70" s="69" t="s">
+      <c r="AH70" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="AI70" s="70"/>
-      <c r="AJ70" s="71"/>
+      <c r="AI70" s="72"/>
+      <c r="AJ70" s="73"/>
       <c r="AK70" s="32"/>
-      <c r="AL70" s="69"/>
-      <c r="AM70" s="70"/>
-      <c r="AN70" s="71"/>
+      <c r="AL70" s="71"/>
+      <c r="AM70" s="72"/>
+      <c r="AN70" s="73"/>
       <c r="AO70" s="12"/>
       <c r="AP70" s="27" t="s">
         <v>34</v>
@@ -5865,51 +5879,53 @@
     </row>
     <row r="71" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="66"/>
-      <c r="C71" s="67"/>
-      <c r="D71" s="68"/>
+      <c r="B71" s="77"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="79"/>
       <c r="E71" s="32"/>
-      <c r="F71" s="66"/>
-      <c r="G71" s="67"/>
-      <c r="H71" s="68"/>
+      <c r="F71" s="77"/>
+      <c r="G71" s="78"/>
+      <c r="H71" s="79"/>
       <c r="I71" s="32"/>
-      <c r="J71" s="66"/>
-      <c r="K71" s="67"/>
-      <c r="L71" s="68"/>
+      <c r="J71" s="77"/>
+      <c r="K71" s="78"/>
+      <c r="L71" s="79"/>
       <c r="M71" s="9"/>
-      <c r="N71" s="66"/>
-      <c r="O71" s="67"/>
-      <c r="P71" s="68"/>
+      <c r="N71" s="77"/>
+      <c r="O71" s="78"/>
+      <c r="P71" s="79"/>
       <c r="Q71" s="44"/>
-      <c r="R71" s="66"/>
-      <c r="S71" s="67"/>
-      <c r="T71" s="68"/>
+      <c r="R71" s="77"/>
+      <c r="S71" s="78"/>
+      <c r="T71" s="79"/>
       <c r="U71" s="32"/>
-      <c r="V71" s="66"/>
-      <c r="W71" s="67"/>
-      <c r="X71" s="68"/>
+      <c r="V71" s="77"/>
+      <c r="W71" s="78"/>
+      <c r="X71" s="79"/>
       <c r="Y71" s="32"/>
-      <c r="Z71" s="66" t="s">
+      <c r="Z71" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AA71" s="67"/>
-      <c r="AB71" s="68"/>
+      <c r="AA71" s="78"/>
+      <c r="AB71" s="79"/>
       <c r="AC71" s="32"/>
-      <c r="AD71" s="66" t="s">
+      <c r="AD71" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AE71" s="67"/>
-      <c r="AF71" s="68"/>
+      <c r="AE71" s="78"/>
+      <c r="AF71" s="79"/>
       <c r="AG71" s="32"/>
-      <c r="AH71" s="66" t="s">
+      <c r="AH71" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="AI71" s="67"/>
-      <c r="AJ71" s="68"/>
+      <c r="AI71" s="78"/>
+      <c r="AJ71" s="79"/>
       <c r="AK71" s="32"/>
-      <c r="AL71" s="66"/>
-      <c r="AM71" s="67"/>
-      <c r="AN71" s="68"/>
+      <c r="AL71" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM71" s="78"/>
+      <c r="AN71" s="79"/>
       <c r="AO71" s="12"/>
       <c r="AP71" s="27" t="s">
         <v>35</v>
@@ -5959,15 +5975,17 @@
       <c r="AI72" s="62"/>
       <c r="AJ72" s="63"/>
       <c r="AK72" s="32"/>
-      <c r="AL72" s="61"/>
-      <c r="AM72" s="62"/>
-      <c r="AN72" s="63"/>
+      <c r="AL72" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM72" s="75"/>
+      <c r="AN72" s="76"/>
       <c r="AO72" s="12"/>
       <c r="AP72" s="28"/>
       <c r="AQ72" s="12"/>
       <c r="AR72" s="13"/>
     </row>
-    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -6005,9 +6023,11 @@
       <c r="AI73" s="35"/>
       <c r="AJ73" s="35"/>
       <c r="AK73" s="35"/>
-      <c r="AL73" s="35"/>
-      <c r="AM73" s="35"/>
-      <c r="AN73" s="35"/>
+      <c r="AL73" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM73" s="62"/>
+      <c r="AN73" s="63"/>
       <c r="AO73" s="16"/>
       <c r="AP73" s="28"/>
       <c r="AQ73" s="12"/>
@@ -6015,47 +6035,49 @@
     </row>
     <row r="74" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
-      <c r="B74" s="78"/>
-      <c r="C74" s="79"/>
+      <c r="B74" s="64"/>
+      <c r="C74" s="65"/>
       <c r="D74" s="57"/>
       <c r="E74" s="32"/>
-      <c r="F74" s="78"/>
-      <c r="G74" s="79"/>
+      <c r="F74" s="64"/>
+      <c r="G74" s="65"/>
       <c r="H74" s="57"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="78"/>
-      <c r="K74" s="79"/>
+      <c r="J74" s="64"/>
+      <c r="K74" s="65"/>
       <c r="L74" s="57"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="64"/>
-      <c r="O74" s="65"/>
+      <c r="N74" s="66"/>
+      <c r="O74" s="67"/>
       <c r="P74" s="34"/>
       <c r="Q74" s="32"/>
-      <c r="R74" s="64"/>
-      <c r="S74" s="65"/>
+      <c r="R74" s="66"/>
+      <c r="S74" s="67"/>
       <c r="T74" s="34"/>
       <c r="U74" s="36"/>
-      <c r="V74" s="64"/>
-      <c r="W74" s="65"/>
+      <c r="V74" s="66"/>
+      <c r="W74" s="67"/>
       <c r="X74" s="34"/>
       <c r="Y74" s="32"/>
-      <c r="Z74" s="64"/>
-      <c r="AA74" s="65"/>
+      <c r="Z74" s="66"/>
+      <c r="AA74" s="67"/>
       <c r="AB74" s="34"/>
       <c r="AC74" s="36"/>
-      <c r="AD74" s="96" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE74" s="97"/>
-      <c r="AF74" s="60"/>
+      <c r="AD74" s="127" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE74" s="128"/>
+      <c r="AF74" s="60" t="s">
+        <v>79</v>
+      </c>
       <c r="AG74" s="32"/>
-      <c r="AH74" s="64"/>
-      <c r="AI74" s="65"/>
+      <c r="AH74" s="66"/>
+      <c r="AI74" s="67"/>
       <c r="AJ74" s="34"/>
       <c r="AK74" s="32"/>
-      <c r="AL74" s="64"/>
-      <c r="AM74" s="65"/>
-      <c r="AN74" s="34"/>
+      <c r="AL74" s="35"/>
+      <c r="AM74" s="35"/>
+      <c r="AN74" s="35"/>
       <c r="AO74" s="16"/>
       <c r="AP74" s="28"/>
       <c r="AQ74" s="12"/>
@@ -6075,35 +6097,35 @@
       <c r="K75" s="81"/>
       <c r="L75" s="82"/>
       <c r="M75" s="14"/>
-      <c r="N75" s="75"/>
-      <c r="O75" s="76"/>
-      <c r="P75" s="77"/>
+      <c r="N75" s="68"/>
+      <c r="O75" s="69"/>
+      <c r="P75" s="70"/>
       <c r="Q75" s="35"/>
-      <c r="R75" s="75"/>
-      <c r="S75" s="76"/>
-      <c r="T75" s="77"/>
+      <c r="R75" s="68"/>
+      <c r="S75" s="69"/>
+      <c r="T75" s="70"/>
       <c r="U75" s="32"/>
-      <c r="V75" s="75"/>
-      <c r="W75" s="76"/>
-      <c r="X75" s="77"/>
+      <c r="V75" s="68"/>
+      <c r="W75" s="69"/>
+      <c r="X75" s="70"/>
       <c r="Y75" s="32"/>
-      <c r="Z75" s="75"/>
-      <c r="AA75" s="76"/>
-      <c r="AB75" s="77"/>
+      <c r="Z75" s="68"/>
+      <c r="AA75" s="69"/>
+      <c r="AB75" s="70"/>
       <c r="AC75" s="36"/>
-      <c r="AD75" s="75" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE75" s="76"/>
-      <c r="AF75" s="77"/>
+      <c r="AD75" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE75" s="69"/>
+      <c r="AF75" s="70"/>
       <c r="AG75" s="32"/>
-      <c r="AH75" s="75"/>
-      <c r="AI75" s="76"/>
-      <c r="AJ75" s="77"/>
+      <c r="AH75" s="68"/>
+      <c r="AI75" s="69"/>
+      <c r="AJ75" s="70"/>
       <c r="AK75" s="32"/>
-      <c r="AL75" s="75"/>
-      <c r="AM75" s="76"/>
-      <c r="AN75" s="77"/>
+      <c r="AL75" s="66"/>
+      <c r="AM75" s="67"/>
+      <c r="AN75" s="34"/>
       <c r="AO75" s="16"/>
       <c r="AP75" s="29"/>
       <c r="AQ75" s="26"/>
@@ -6123,35 +6145,33 @@
       <c r="K76" s="84"/>
       <c r="L76" s="85"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="69"/>
-      <c r="O76" s="70"/>
-      <c r="P76" s="71"/>
+      <c r="N76" s="71"/>
+      <c r="O76" s="72"/>
+      <c r="P76" s="73"/>
       <c r="Q76" s="31"/>
-      <c r="R76" s="69"/>
-      <c r="S76" s="70"/>
-      <c r="T76" s="71"/>
+      <c r="R76" s="71"/>
+      <c r="S76" s="72"/>
+      <c r="T76" s="73"/>
       <c r="U76" s="31"/>
-      <c r="V76" s="69"/>
-      <c r="W76" s="70"/>
-      <c r="X76" s="71"/>
+      <c r="V76" s="71"/>
+      <c r="W76" s="72"/>
+      <c r="X76" s="73"/>
       <c r="Y76" s="32"/>
-      <c r="Z76" s="69"/>
-      <c r="AA76" s="70"/>
-      <c r="AB76" s="71"/>
+      <c r="Z76" s="71"/>
+      <c r="AA76" s="72"/>
+      <c r="AB76" s="73"/>
       <c r="AC76" s="35"/>
-      <c r="AD76" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE76" s="70"/>
-      <c r="AF76" s="71"/>
+      <c r="AD76" s="71"/>
+      <c r="AE76" s="72"/>
+      <c r="AF76" s="73"/>
       <c r="AG76" s="32"/>
-      <c r="AH76" s="69"/>
-      <c r="AI76" s="70"/>
-      <c r="AJ76" s="71"/>
+      <c r="AH76" s="71"/>
+      <c r="AI76" s="72"/>
+      <c r="AJ76" s="73"/>
       <c r="AK76" s="32"/>
-      <c r="AL76" s="69"/>
-      <c r="AM76" s="70"/>
-      <c r="AN76" s="71"/>
+      <c r="AL76" s="71"/>
+      <c r="AM76" s="72"/>
+      <c r="AN76" s="73"/>
       <c r="AO76" s="12"/>
       <c r="AP76" s="29"/>
       <c r="AQ76" s="26"/>
@@ -6159,47 +6179,47 @@
     </row>
     <row r="77" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
-      <c r="B77" s="66"/>
-      <c r="C77" s="67"/>
-      <c r="D77" s="68"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="79"/>
       <c r="E77" s="32"/>
-      <c r="F77" s="66"/>
-      <c r="G77" s="67"/>
-      <c r="H77" s="68"/>
+      <c r="F77" s="77"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="79"/>
       <c r="I77" s="32"/>
-      <c r="J77" s="66"/>
-      <c r="K77" s="67"/>
-      <c r="L77" s="68"/>
+      <c r="J77" s="77"/>
+      <c r="K77" s="78"/>
+      <c r="L77" s="79"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="66"/>
-      <c r="O77" s="67"/>
-      <c r="P77" s="68"/>
+      <c r="N77" s="77"/>
+      <c r="O77" s="78"/>
+      <c r="P77" s="79"/>
       <c r="Q77" s="32"/>
-      <c r="R77" s="66"/>
-      <c r="S77" s="67"/>
-      <c r="T77" s="68"/>
+      <c r="R77" s="77"/>
+      <c r="S77" s="78"/>
+      <c r="T77" s="79"/>
       <c r="U77" s="32"/>
-      <c r="V77" s="66"/>
-      <c r="W77" s="67"/>
-      <c r="X77" s="68"/>
+      <c r="V77" s="77"/>
+      <c r="W77" s="78"/>
+      <c r="X77" s="79"/>
       <c r="Y77" s="32"/>
-      <c r="Z77" s="66"/>
-      <c r="AA77" s="67"/>
-      <c r="AB77" s="68"/>
+      <c r="Z77" s="77"/>
+      <c r="AA77" s="78"/>
+      <c r="AB77" s="79"/>
       <c r="AC77" s="43"/>
-      <c r="AD77" s="66" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE77" s="67"/>
-      <c r="AF77" s="68"/>
+      <c r="AD77" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE77" s="78"/>
+      <c r="AF77" s="79"/>
       <c r="AG77" s="32"/>
-      <c r="AH77" s="66"/>
-      <c r="AI77" s="67"/>
-      <c r="AJ77" s="68"/>
+      <c r="AH77" s="77"/>
+      <c r="AI77" s="78"/>
+      <c r="AJ77" s="79"/>
       <c r="AK77" s="32"/>
-      <c r="AL77" s="66"/>
-      <c r="AM77" s="67"/>
-      <c r="AN77" s="68"/>
+      <c r="AL77" s="77"/>
+      <c r="AM77" s="78"/>
+      <c r="AN77" s="79"/>
       <c r="AO77" s="12"/>
       <c r="AP77" s="29"/>
       <c r="AQ77" s="26"/>
@@ -6301,44 +6321,48 @@
     </row>
     <row r="80" spans="1:44" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
-      <c r="B80" s="78"/>
-      <c r="C80" s="79"/>
+      <c r="B80" s="64"/>
+      <c r="C80" s="65"/>
       <c r="D80" s="57"/>
       <c r="E80" s="32"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="79"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="65"/>
       <c r="H80" s="57"/>
       <c r="I80" s="32"/>
-      <c r="J80" s="78"/>
-      <c r="K80" s="79"/>
+      <c r="J80" s="64"/>
+      <c r="K80" s="65"/>
       <c r="L80" s="57"/>
       <c r="M80" s="5"/>
-      <c r="N80" s="64"/>
-      <c r="O80" s="65"/>
+      <c r="N80" s="66"/>
+      <c r="O80" s="67"/>
       <c r="P80" s="34"/>
       <c r="Q80" s="32"/>
-      <c r="R80" s="64"/>
-      <c r="S80" s="65"/>
+      <c r="R80" s="66"/>
+      <c r="S80" s="67"/>
       <c r="T80" s="34"/>
       <c r="U80" s="36"/>
-      <c r="V80" s="64"/>
-      <c r="W80" s="65"/>
+      <c r="V80" s="66"/>
+      <c r="W80" s="67"/>
       <c r="X80" s="34"/>
       <c r="Y80" s="32"/>
-      <c r="Z80" s="64"/>
-      <c r="AA80" s="65"/>
+      <c r="Z80" s="66"/>
+      <c r="AA80" s="67"/>
       <c r="AB80" s="34"/>
       <c r="AC80" s="36"/>
-      <c r="AD80" s="64"/>
-      <c r="AE80" s="65"/>
-      <c r="AF80" s="34"/>
+      <c r="AD80" s="127" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE80" s="128"/>
+      <c r="AF80" s="60" t="s">
+        <v>80</v>
+      </c>
       <c r="AG80" s="32"/>
-      <c r="AH80" s="64"/>
-      <c r="AI80" s="65"/>
+      <c r="AH80" s="66"/>
+      <c r="AI80" s="67"/>
       <c r="AJ80" s="34"/>
       <c r="AK80" s="32"/>
-      <c r="AL80" s="64"/>
-      <c r="AM80" s="65"/>
+      <c r="AL80" s="66"/>
+      <c r="AM80" s="67"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="12"/>
       <c r="AP80" s="29"/>
@@ -6359,33 +6383,35 @@
       <c r="K81" s="81"/>
       <c r="L81" s="82"/>
       <c r="M81" s="5"/>
-      <c r="N81" s="75"/>
-      <c r="O81" s="76"/>
-      <c r="P81" s="77"/>
+      <c r="N81" s="68"/>
+      <c r="O81" s="69"/>
+      <c r="P81" s="70"/>
       <c r="Q81" s="32"/>
-      <c r="R81" s="75"/>
-      <c r="S81" s="76"/>
-      <c r="T81" s="77"/>
+      <c r="R81" s="68"/>
+      <c r="S81" s="69"/>
+      <c r="T81" s="70"/>
       <c r="U81" s="32"/>
-      <c r="V81" s="75"/>
-      <c r="W81" s="76"/>
-      <c r="X81" s="77"/>
+      <c r="V81" s="68"/>
+      <c r="W81" s="69"/>
+      <c r="X81" s="70"/>
       <c r="Y81" s="32"/>
-      <c r="Z81" s="75"/>
-      <c r="AA81" s="76"/>
-      <c r="AB81" s="77"/>
+      <c r="Z81" s="68"/>
+      <c r="AA81" s="69"/>
+      <c r="AB81" s="70"/>
       <c r="AC81" s="36"/>
-      <c r="AD81" s="75"/>
-      <c r="AE81" s="76"/>
-      <c r="AF81" s="77"/>
+      <c r="AD81" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE81" s="69"/>
+      <c r="AF81" s="70"/>
       <c r="AG81" s="32"/>
-      <c r="AH81" s="75"/>
-      <c r="AI81" s="76"/>
-      <c r="AJ81" s="77"/>
+      <c r="AH81" s="68"/>
+      <c r="AI81" s="69"/>
+      <c r="AJ81" s="70"/>
       <c r="AK81" s="32"/>
-      <c r="AL81" s="75"/>
-      <c r="AM81" s="76"/>
-      <c r="AN81" s="77"/>
+      <c r="AL81" s="68"/>
+      <c r="AM81" s="69"/>
+      <c r="AN81" s="70"/>
       <c r="AO81" s="12"/>
       <c r="AP81" s="29"/>
       <c r="AQ81" s="26"/>
@@ -6405,33 +6431,33 @@
       <c r="K82" s="84"/>
       <c r="L82" s="85"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="69"/>
-      <c r="O82" s="70"/>
-      <c r="P82" s="71"/>
+      <c r="N82" s="71"/>
+      <c r="O82" s="72"/>
+      <c r="P82" s="73"/>
       <c r="Q82" s="32"/>
-      <c r="R82" s="69"/>
-      <c r="S82" s="70"/>
-      <c r="T82" s="71"/>
+      <c r="R82" s="71"/>
+      <c r="S82" s="72"/>
+      <c r="T82" s="73"/>
       <c r="U82" s="31"/>
-      <c r="V82" s="69"/>
-      <c r="W82" s="70"/>
-      <c r="X82" s="71"/>
+      <c r="V82" s="71"/>
+      <c r="W82" s="72"/>
+      <c r="X82" s="73"/>
       <c r="Y82" s="32"/>
-      <c r="Z82" s="69"/>
-      <c r="AA82" s="70"/>
-      <c r="AB82" s="71"/>
+      <c r="Z82" s="71"/>
+      <c r="AA82" s="72"/>
+      <c r="AB82" s="73"/>
       <c r="AC82" s="35"/>
-      <c r="AD82" s="69"/>
-      <c r="AE82" s="70"/>
-      <c r="AF82" s="71"/>
+      <c r="AD82" s="71"/>
+      <c r="AE82" s="72"/>
+      <c r="AF82" s="73"/>
       <c r="AG82" s="32"/>
-      <c r="AH82" s="69"/>
-      <c r="AI82" s="70"/>
-      <c r="AJ82" s="71"/>
+      <c r="AH82" s="71"/>
+      <c r="AI82" s="72"/>
+      <c r="AJ82" s="73"/>
       <c r="AK82" s="32"/>
-      <c r="AL82" s="69"/>
-      <c r="AM82" s="70"/>
-      <c r="AN82" s="71"/>
+      <c r="AL82" s="71"/>
+      <c r="AM82" s="72"/>
+      <c r="AN82" s="73"/>
       <c r="AO82" s="12"/>
       <c r="AP82" s="29"/>
       <c r="AQ82" s="26"/>
@@ -6439,45 +6465,47 @@
     </row>
     <row r="83" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
-      <c r="B83" s="66"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="68"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="78"/>
+      <c r="D83" s="79"/>
       <c r="E83" s="32"/>
-      <c r="F83" s="66"/>
-      <c r="G83" s="67"/>
-      <c r="H83" s="68"/>
+      <c r="F83" s="77"/>
+      <c r="G83" s="78"/>
+      <c r="H83" s="79"/>
       <c r="I83" s="32"/>
-      <c r="J83" s="66"/>
-      <c r="K83" s="67"/>
-      <c r="L83" s="68"/>
+      <c r="J83" s="77"/>
+      <c r="K83" s="78"/>
+      <c r="L83" s="79"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="66"/>
-      <c r="O83" s="67"/>
-      <c r="P83" s="68"/>
+      <c r="N83" s="77"/>
+      <c r="O83" s="78"/>
+      <c r="P83" s="79"/>
       <c r="Q83" s="32"/>
-      <c r="R83" s="66"/>
-      <c r="S83" s="67"/>
-      <c r="T83" s="68"/>
+      <c r="R83" s="77"/>
+      <c r="S83" s="78"/>
+      <c r="T83" s="79"/>
       <c r="U83" s="32"/>
-      <c r="V83" s="66"/>
-      <c r="W83" s="67"/>
-      <c r="X83" s="68"/>
+      <c r="V83" s="77"/>
+      <c r="W83" s="78"/>
+      <c r="X83" s="79"/>
       <c r="Y83" s="32"/>
-      <c r="Z83" s="66"/>
-      <c r="AA83" s="67"/>
-      <c r="AB83" s="68"/>
+      <c r="Z83" s="77"/>
+      <c r="AA83" s="78"/>
+      <c r="AB83" s="79"/>
       <c r="AC83" s="31"/>
-      <c r="AD83" s="66"/>
-      <c r="AE83" s="67"/>
-      <c r="AF83" s="68"/>
+      <c r="AD83" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE83" s="78"/>
+      <c r="AF83" s="79"/>
       <c r="AG83" s="32"/>
-      <c r="AH83" s="66"/>
-      <c r="AI83" s="67"/>
-      <c r="AJ83" s="68"/>
+      <c r="AH83" s="77"/>
+      <c r="AI83" s="78"/>
+      <c r="AJ83" s="79"/>
       <c r="AK83" s="32"/>
-      <c r="AL83" s="66"/>
-      <c r="AM83" s="67"/>
-      <c r="AN83" s="68"/>
+      <c r="AL83" s="77"/>
+      <c r="AM83" s="78"/>
+      <c r="AN83" s="79"/>
       <c r="AO83" s="12"/>
       <c r="AP83" s="29"/>
       <c r="AQ83" s="26"/>
@@ -6513,7 +6541,9 @@
       <c r="AA84" s="62"/>
       <c r="AB84" s="63"/>
       <c r="AC84" s="31"/>
-      <c r="AD84" s="61"/>
+      <c r="AD84" s="61" t="s">
+        <v>27</v>
+      </c>
       <c r="AE84" s="62"/>
       <c r="AF84" s="63"/>
       <c r="AG84" s="31"/>
@@ -6577,44 +6607,44 @@
     </row>
     <row r="86" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
-      <c r="B86" s="78"/>
-      <c r="C86" s="79"/>
+      <c r="B86" s="64"/>
+      <c r="C86" s="65"/>
       <c r="D86" s="57"/>
       <c r="E86" s="32"/>
-      <c r="F86" s="78"/>
-      <c r="G86" s="79"/>
+      <c r="F86" s="64"/>
+      <c r="G86" s="65"/>
       <c r="H86" s="57"/>
       <c r="I86" s="32"/>
-      <c r="J86" s="78"/>
-      <c r="K86" s="79"/>
+      <c r="J86" s="64"/>
+      <c r="K86" s="65"/>
       <c r="L86" s="57"/>
       <c r="M86" s="6"/>
-      <c r="N86" s="64"/>
-      <c r="O86" s="65"/>
+      <c r="N86" s="66"/>
+      <c r="O86" s="67"/>
       <c r="P86" s="34"/>
       <c r="Q86" s="44"/>
-      <c r="R86" s="64"/>
-      <c r="S86" s="65"/>
+      <c r="R86" s="66"/>
+      <c r="S86" s="67"/>
       <c r="T86" s="34"/>
       <c r="U86" s="36"/>
-      <c r="V86" s="64"/>
-      <c r="W86" s="65"/>
+      <c r="V86" s="66"/>
+      <c r="W86" s="67"/>
       <c r="X86" s="34"/>
       <c r="Y86" s="32"/>
-      <c r="Z86" s="64"/>
-      <c r="AA86" s="65"/>
+      <c r="Z86" s="66"/>
+      <c r="AA86" s="67"/>
       <c r="AB86" s="34"/>
       <c r="AC86" s="36"/>
-      <c r="AD86" s="64"/>
-      <c r="AE86" s="65"/>
+      <c r="AD86" s="66"/>
+      <c r="AE86" s="67"/>
       <c r="AF86" s="34"/>
       <c r="AG86" s="32"/>
-      <c r="AH86" s="64"/>
-      <c r="AI86" s="65"/>
+      <c r="AH86" s="66"/>
+      <c r="AI86" s="67"/>
       <c r="AJ86" s="34"/>
       <c r="AK86" s="32"/>
-      <c r="AL86" s="64"/>
-      <c r="AM86" s="65"/>
+      <c r="AL86" s="66"/>
+      <c r="AM86" s="67"/>
       <c r="AN86" s="34"/>
       <c r="AO86" s="12"/>
       <c r="AP86" s="29"/>
@@ -6635,33 +6665,33 @@
       <c r="K87" s="81"/>
       <c r="L87" s="82"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="75"/>
-      <c r="O87" s="76"/>
-      <c r="P87" s="77"/>
+      <c r="N87" s="68"/>
+      <c r="O87" s="69"/>
+      <c r="P87" s="70"/>
       <c r="Q87" s="44"/>
-      <c r="R87" s="75"/>
-      <c r="S87" s="76"/>
-      <c r="T87" s="77"/>
+      <c r="R87" s="68"/>
+      <c r="S87" s="69"/>
+      <c r="T87" s="70"/>
       <c r="U87" s="32"/>
-      <c r="V87" s="75"/>
-      <c r="W87" s="76"/>
-      <c r="X87" s="77"/>
+      <c r="V87" s="68"/>
+      <c r="W87" s="69"/>
+      <c r="X87" s="70"/>
       <c r="Y87" s="32"/>
-      <c r="Z87" s="75"/>
-      <c r="AA87" s="76"/>
-      <c r="AB87" s="77"/>
+      <c r="Z87" s="68"/>
+      <c r="AA87" s="69"/>
+      <c r="AB87" s="70"/>
       <c r="AC87" s="36"/>
-      <c r="AD87" s="75"/>
-      <c r="AE87" s="76"/>
-      <c r="AF87" s="77"/>
+      <c r="AD87" s="68"/>
+      <c r="AE87" s="69"/>
+      <c r="AF87" s="70"/>
       <c r="AG87" s="32"/>
-      <c r="AH87" s="75"/>
-      <c r="AI87" s="76"/>
-      <c r="AJ87" s="77"/>
+      <c r="AH87" s="68"/>
+      <c r="AI87" s="69"/>
+      <c r="AJ87" s="70"/>
       <c r="AK87" s="32"/>
-      <c r="AL87" s="75"/>
-      <c r="AM87" s="76"/>
-      <c r="AN87" s="77"/>
+      <c r="AL87" s="68"/>
+      <c r="AM87" s="69"/>
+      <c r="AN87" s="70"/>
       <c r="AO87" s="12"/>
       <c r="AP87" s="29"/>
       <c r="AQ87" s="26"/>
@@ -6681,33 +6711,33 @@
       <c r="K88" s="84"/>
       <c r="L88" s="85"/>
       <c r="M88" s="6"/>
-      <c r="N88" s="69"/>
-      <c r="O88" s="70"/>
-      <c r="P88" s="71"/>
+      <c r="N88" s="71"/>
+      <c r="O88" s="72"/>
+      <c r="P88" s="73"/>
       <c r="Q88" s="44"/>
-      <c r="R88" s="69"/>
-      <c r="S88" s="70"/>
-      <c r="T88" s="71"/>
+      <c r="R88" s="71"/>
+      <c r="S88" s="72"/>
+      <c r="T88" s="73"/>
       <c r="U88" s="31"/>
-      <c r="V88" s="69"/>
-      <c r="W88" s="70"/>
-      <c r="X88" s="71"/>
+      <c r="V88" s="71"/>
+      <c r="W88" s="72"/>
+      <c r="X88" s="73"/>
       <c r="Y88" s="32"/>
-      <c r="Z88" s="69"/>
-      <c r="AA88" s="70"/>
-      <c r="AB88" s="71"/>
+      <c r="Z88" s="71"/>
+      <c r="AA88" s="72"/>
+      <c r="AB88" s="73"/>
       <c r="AC88" s="35"/>
-      <c r="AD88" s="69"/>
-      <c r="AE88" s="70"/>
-      <c r="AF88" s="71"/>
+      <c r="AD88" s="71"/>
+      <c r="AE88" s="72"/>
+      <c r="AF88" s="73"/>
       <c r="AG88" s="32"/>
-      <c r="AH88" s="69"/>
-      <c r="AI88" s="70"/>
-      <c r="AJ88" s="71"/>
+      <c r="AH88" s="71"/>
+      <c r="AI88" s="72"/>
+      <c r="AJ88" s="73"/>
       <c r="AK88" s="32"/>
-      <c r="AL88" s="69"/>
-      <c r="AM88" s="70"/>
-      <c r="AN88" s="71"/>
+      <c r="AL88" s="71"/>
+      <c r="AM88" s="72"/>
+      <c r="AN88" s="73"/>
       <c r="AO88" s="12"/>
       <c r="AP88" s="29"/>
       <c r="AQ88" s="26"/>
@@ -6715,45 +6745,45 @@
     </row>
     <row r="89" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
-      <c r="B89" s="66"/>
-      <c r="C89" s="67"/>
-      <c r="D89" s="68"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="79"/>
       <c r="E89" s="32"/>
-      <c r="F89" s="66"/>
-      <c r="G89" s="67"/>
-      <c r="H89" s="68"/>
+      <c r="F89" s="77"/>
+      <c r="G89" s="78"/>
+      <c r="H89" s="79"/>
       <c r="I89" s="32"/>
-      <c r="J89" s="66"/>
-      <c r="K89" s="67"/>
-      <c r="L89" s="68"/>
+      <c r="J89" s="77"/>
+      <c r="K89" s="78"/>
+      <c r="L89" s="79"/>
       <c r="M89" s="6"/>
-      <c r="N89" s="66"/>
-      <c r="O89" s="67"/>
-      <c r="P89" s="68"/>
+      <c r="N89" s="77"/>
+      <c r="O89" s="78"/>
+      <c r="P89" s="79"/>
       <c r="Q89" s="44"/>
-      <c r="R89" s="66"/>
-      <c r="S89" s="67"/>
-      <c r="T89" s="68"/>
+      <c r="R89" s="77"/>
+      <c r="S89" s="78"/>
+      <c r="T89" s="79"/>
       <c r="U89" s="32"/>
-      <c r="V89" s="66"/>
-      <c r="W89" s="67"/>
-      <c r="X89" s="68"/>
+      <c r="V89" s="77"/>
+      <c r="W89" s="78"/>
+      <c r="X89" s="79"/>
       <c r="Y89" s="32"/>
-      <c r="Z89" s="66"/>
-      <c r="AA89" s="67"/>
-      <c r="AB89" s="68"/>
+      <c r="Z89" s="77"/>
+      <c r="AA89" s="78"/>
+      <c r="AB89" s="79"/>
       <c r="AC89" s="31"/>
-      <c r="AD89" s="66"/>
-      <c r="AE89" s="67"/>
-      <c r="AF89" s="68"/>
+      <c r="AD89" s="77"/>
+      <c r="AE89" s="78"/>
+      <c r="AF89" s="79"/>
       <c r="AG89" s="32"/>
-      <c r="AH89" s="66"/>
-      <c r="AI89" s="67"/>
-      <c r="AJ89" s="68"/>
+      <c r="AH89" s="77"/>
+      <c r="AI89" s="78"/>
+      <c r="AJ89" s="79"/>
       <c r="AK89" s="32"/>
-      <c r="AL89" s="66"/>
-      <c r="AM89" s="67"/>
-      <c r="AN89" s="68"/>
+      <c r="AL89" s="77"/>
+      <c r="AM89" s="78"/>
+      <c r="AN89" s="79"/>
       <c r="AO89" s="12"/>
       <c r="AP89" s="29"/>
       <c r="AQ89" s="26"/>
@@ -6853,44 +6883,44 @@
     </row>
     <row r="92" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
-      <c r="B92" s="78"/>
-      <c r="C92" s="79"/>
+      <c r="B92" s="64"/>
+      <c r="C92" s="65"/>
       <c r="D92" s="57"/>
       <c r="E92" s="44"/>
-      <c r="F92" s="78"/>
-      <c r="G92" s="79"/>
+      <c r="F92" s="64"/>
+      <c r="G92" s="65"/>
       <c r="H92" s="57"/>
       <c r="I92" s="32"/>
-      <c r="J92" s="78"/>
-      <c r="K92" s="79"/>
+      <c r="J92" s="64"/>
+      <c r="K92" s="65"/>
       <c r="L92" s="57"/>
       <c r="M92" s="6"/>
-      <c r="N92" s="64"/>
-      <c r="O92" s="65"/>
+      <c r="N92" s="66"/>
+      <c r="O92" s="67"/>
       <c r="P92" s="34"/>
       <c r="Q92" s="32"/>
-      <c r="R92" s="64"/>
-      <c r="S92" s="65"/>
+      <c r="R92" s="66"/>
+      <c r="S92" s="67"/>
       <c r="T92" s="34"/>
       <c r="U92" s="36"/>
-      <c r="V92" s="64"/>
-      <c r="W92" s="65"/>
+      <c r="V92" s="66"/>
+      <c r="W92" s="67"/>
       <c r="X92" s="34"/>
       <c r="Y92" s="32"/>
-      <c r="Z92" s="64"/>
-      <c r="AA92" s="65"/>
+      <c r="Z92" s="66"/>
+      <c r="AA92" s="67"/>
       <c r="AB92" s="34"/>
       <c r="AC92" s="44"/>
-      <c r="AD92" s="64"/>
-      <c r="AE92" s="65"/>
+      <c r="AD92" s="66"/>
+      <c r="AE92" s="67"/>
       <c r="AF92" s="34"/>
       <c r="AG92" s="44"/>
-      <c r="AH92" s="64"/>
-      <c r="AI92" s="65"/>
+      <c r="AH92" s="66"/>
+      <c r="AI92" s="67"/>
       <c r="AJ92" s="34"/>
       <c r="AK92" s="32"/>
-      <c r="AL92" s="64"/>
-      <c r="AM92" s="65"/>
+      <c r="AL92" s="66"/>
+      <c r="AM92" s="67"/>
       <c r="AN92" s="34"/>
       <c r="AO92" s="12"/>
       <c r="AP92" s="29"/>
@@ -6911,33 +6941,33 @@
       <c r="K93" s="81"/>
       <c r="L93" s="82"/>
       <c r="M93" s="6"/>
-      <c r="N93" s="75"/>
-      <c r="O93" s="76"/>
-      <c r="P93" s="77"/>
+      <c r="N93" s="68"/>
+      <c r="O93" s="69"/>
+      <c r="P93" s="70"/>
       <c r="Q93" s="35"/>
-      <c r="R93" s="75"/>
-      <c r="S93" s="76"/>
-      <c r="T93" s="77"/>
+      <c r="R93" s="68"/>
+      <c r="S93" s="69"/>
+      <c r="T93" s="70"/>
       <c r="U93" s="36"/>
-      <c r="V93" s="75"/>
-      <c r="W93" s="76"/>
-      <c r="X93" s="77"/>
+      <c r="V93" s="68"/>
+      <c r="W93" s="69"/>
+      <c r="X93" s="70"/>
       <c r="Y93" s="32"/>
-      <c r="Z93" s="75"/>
-      <c r="AA93" s="76"/>
-      <c r="AB93" s="77"/>
+      <c r="Z93" s="68"/>
+      <c r="AA93" s="69"/>
+      <c r="AB93" s="70"/>
       <c r="AC93" s="43"/>
-      <c r="AD93" s="75"/>
-      <c r="AE93" s="76"/>
-      <c r="AF93" s="77"/>
+      <c r="AD93" s="68"/>
+      <c r="AE93" s="69"/>
+      <c r="AF93" s="70"/>
       <c r="AG93" s="43"/>
-      <c r="AH93" s="75"/>
-      <c r="AI93" s="76"/>
-      <c r="AJ93" s="77"/>
+      <c r="AH93" s="68"/>
+      <c r="AI93" s="69"/>
+      <c r="AJ93" s="70"/>
       <c r="AK93" s="35"/>
-      <c r="AL93" s="75"/>
-      <c r="AM93" s="76"/>
-      <c r="AN93" s="77"/>
+      <c r="AL93" s="68"/>
+      <c r="AM93" s="69"/>
+      <c r="AN93" s="70"/>
       <c r="AO93" s="12"/>
       <c r="AP93" s="29"/>
       <c r="AQ93" s="26"/>
@@ -6957,33 +6987,33 @@
       <c r="K94" s="84"/>
       <c r="L94" s="85"/>
       <c r="M94" s="26"/>
-      <c r="N94" s="69"/>
-      <c r="O94" s="70"/>
-      <c r="P94" s="71"/>
+      <c r="N94" s="71"/>
+      <c r="O94" s="72"/>
+      <c r="P94" s="73"/>
       <c r="Q94" s="31"/>
-      <c r="R94" s="69"/>
-      <c r="S94" s="70"/>
-      <c r="T94" s="71"/>
+      <c r="R94" s="71"/>
+      <c r="S94" s="72"/>
+      <c r="T94" s="73"/>
       <c r="U94" s="36"/>
-      <c r="V94" s="69"/>
-      <c r="W94" s="70"/>
-      <c r="X94" s="71"/>
+      <c r="V94" s="71"/>
+      <c r="W94" s="72"/>
+      <c r="X94" s="73"/>
       <c r="Y94" s="32"/>
-      <c r="Z94" s="69"/>
-      <c r="AA94" s="70"/>
-      <c r="AB94" s="71"/>
+      <c r="Z94" s="71"/>
+      <c r="AA94" s="72"/>
+      <c r="AB94" s="73"/>
       <c r="AC94" s="44"/>
-      <c r="AD94" s="69"/>
-      <c r="AE94" s="70"/>
-      <c r="AF94" s="71"/>
+      <c r="AD94" s="71"/>
+      <c r="AE94" s="72"/>
+      <c r="AF94" s="73"/>
       <c r="AG94" s="44"/>
-      <c r="AH94" s="69"/>
-      <c r="AI94" s="70"/>
-      <c r="AJ94" s="71"/>
+      <c r="AH94" s="71"/>
+      <c r="AI94" s="72"/>
+      <c r="AJ94" s="73"/>
       <c r="AK94" s="31"/>
-      <c r="AL94" s="69"/>
-      <c r="AM94" s="70"/>
-      <c r="AN94" s="71"/>
+      <c r="AL94" s="71"/>
+      <c r="AM94" s="72"/>
+      <c r="AN94" s="73"/>
       <c r="AO94" s="12"/>
       <c r="AP94" s="29"/>
       <c r="AQ94" s="26"/>
@@ -6991,45 +7021,45 @@
     </row>
     <row r="95" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
-      <c r="B95" s="66"/>
-      <c r="C95" s="67"/>
-      <c r="D95" s="68"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="78"/>
+      <c r="D95" s="79"/>
       <c r="E95" s="44"/>
-      <c r="F95" s="66"/>
-      <c r="G95" s="67"/>
-      <c r="H95" s="68"/>
+      <c r="F95" s="77"/>
+      <c r="G95" s="78"/>
+      <c r="H95" s="79"/>
       <c r="I95" s="31"/>
-      <c r="J95" s="66"/>
-      <c r="K95" s="67"/>
-      <c r="L95" s="68"/>
+      <c r="J95" s="77"/>
+      <c r="K95" s="78"/>
+      <c r="L95" s="79"/>
       <c r="M95" s="26"/>
-      <c r="N95" s="66"/>
-      <c r="O95" s="67"/>
-      <c r="P95" s="68"/>
+      <c r="N95" s="77"/>
+      <c r="O95" s="78"/>
+      <c r="P95" s="79"/>
       <c r="Q95" s="32"/>
-      <c r="R95" s="66"/>
-      <c r="S95" s="67"/>
-      <c r="T95" s="68"/>
+      <c r="R95" s="77"/>
+      <c r="S95" s="78"/>
+      <c r="T95" s="79"/>
       <c r="U95" s="32"/>
-      <c r="V95" s="66"/>
-      <c r="W95" s="67"/>
-      <c r="X95" s="68"/>
+      <c r="V95" s="77"/>
+      <c r="W95" s="78"/>
+      <c r="X95" s="79"/>
       <c r="Y95" s="32"/>
-      <c r="Z95" s="66"/>
-      <c r="AA95" s="67"/>
-      <c r="AB95" s="68"/>
+      <c r="Z95" s="77"/>
+      <c r="AA95" s="78"/>
+      <c r="AB95" s="79"/>
       <c r="AC95" s="44"/>
-      <c r="AD95" s="66"/>
-      <c r="AE95" s="67"/>
-      <c r="AF95" s="68"/>
+      <c r="AD95" s="77"/>
+      <c r="AE95" s="78"/>
+      <c r="AF95" s="79"/>
       <c r="AG95" s="44"/>
-      <c r="AH95" s="66"/>
-      <c r="AI95" s="67"/>
-      <c r="AJ95" s="68"/>
+      <c r="AH95" s="77"/>
+      <c r="AI95" s="78"/>
+      <c r="AJ95" s="79"/>
       <c r="AK95" s="31"/>
-      <c r="AL95" s="66"/>
-      <c r="AM95" s="67"/>
-      <c r="AN95" s="68"/>
+      <c r="AL95" s="77"/>
+      <c r="AM95" s="78"/>
+      <c r="AN95" s="79"/>
       <c r="AO95" s="12"/>
       <c r="AP95" s="29"/>
       <c r="AQ95" s="26"/>
@@ -7129,44 +7159,44 @@
     </row>
     <row r="98" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12"/>
-      <c r="B98" s="78"/>
-      <c r="C98" s="79"/>
+      <c r="B98" s="64"/>
+      <c r="C98" s="65"/>
       <c r="D98" s="57"/>
       <c r="E98" s="32"/>
-      <c r="F98" s="78"/>
-      <c r="G98" s="79"/>
+      <c r="F98" s="64"/>
+      <c r="G98" s="65"/>
       <c r="H98" s="57"/>
       <c r="I98" s="32"/>
-      <c r="J98" s="78"/>
-      <c r="K98" s="79"/>
+      <c r="J98" s="64"/>
+      <c r="K98" s="65"/>
       <c r="L98" s="57"/>
       <c r="M98" s="26"/>
-      <c r="N98" s="64"/>
-      <c r="O98" s="65"/>
+      <c r="N98" s="66"/>
+      <c r="O98" s="67"/>
       <c r="P98" s="34"/>
       <c r="Q98" s="32"/>
-      <c r="R98" s="64"/>
-      <c r="S98" s="65"/>
+      <c r="R98" s="66"/>
+      <c r="S98" s="67"/>
       <c r="T98" s="34"/>
       <c r="U98" s="36"/>
-      <c r="V98" s="64"/>
-      <c r="W98" s="65"/>
+      <c r="V98" s="66"/>
+      <c r="W98" s="67"/>
       <c r="X98" s="34"/>
       <c r="Y98" s="32"/>
-      <c r="Z98" s="64"/>
-      <c r="AA98" s="65"/>
+      <c r="Z98" s="66"/>
+      <c r="AA98" s="67"/>
       <c r="AB98" s="34"/>
       <c r="AC98" s="36"/>
-      <c r="AD98" s="64"/>
-      <c r="AE98" s="65"/>
+      <c r="AD98" s="66"/>
+      <c r="AE98" s="67"/>
       <c r="AF98" s="34"/>
       <c r="AG98" s="32"/>
-      <c r="AH98" s="64"/>
-      <c r="AI98" s="65"/>
+      <c r="AH98" s="66"/>
+      <c r="AI98" s="67"/>
       <c r="AJ98" s="34"/>
       <c r="AK98" s="32"/>
-      <c r="AL98" s="64"/>
-      <c r="AM98" s="65"/>
+      <c r="AL98" s="66"/>
+      <c r="AM98" s="67"/>
       <c r="AN98" s="34"/>
       <c r="AO98" s="12"/>
       <c r="AP98" s="29"/>
@@ -7187,33 +7217,33 @@
       <c r="K99" s="81"/>
       <c r="L99" s="82"/>
       <c r="M99" s="26"/>
-      <c r="N99" s="75"/>
-      <c r="O99" s="76"/>
-      <c r="P99" s="77"/>
+      <c r="N99" s="68"/>
+      <c r="O99" s="69"/>
+      <c r="P99" s="70"/>
       <c r="Q99" s="35"/>
-      <c r="R99" s="75"/>
-      <c r="S99" s="76"/>
-      <c r="T99" s="77"/>
+      <c r="R99" s="68"/>
+      <c r="S99" s="69"/>
+      <c r="T99" s="70"/>
       <c r="U99" s="32"/>
-      <c r="V99" s="75"/>
-      <c r="W99" s="76"/>
-      <c r="X99" s="77"/>
+      <c r="V99" s="68"/>
+      <c r="W99" s="69"/>
+      <c r="X99" s="70"/>
       <c r="Y99" s="32"/>
-      <c r="Z99" s="75"/>
-      <c r="AA99" s="76"/>
-      <c r="AB99" s="77"/>
+      <c r="Z99" s="68"/>
+      <c r="AA99" s="69"/>
+      <c r="AB99" s="70"/>
       <c r="AC99" s="36"/>
-      <c r="AD99" s="75"/>
-      <c r="AE99" s="76"/>
-      <c r="AF99" s="77"/>
+      <c r="AD99" s="68"/>
+      <c r="AE99" s="69"/>
+      <c r="AF99" s="70"/>
       <c r="AG99" s="32"/>
-      <c r="AH99" s="75"/>
-      <c r="AI99" s="76"/>
-      <c r="AJ99" s="77"/>
+      <c r="AH99" s="68"/>
+      <c r="AI99" s="69"/>
+      <c r="AJ99" s="70"/>
       <c r="AK99" s="35"/>
-      <c r="AL99" s="75"/>
-      <c r="AM99" s="76"/>
-      <c r="AN99" s="77"/>
+      <c r="AL99" s="68"/>
+      <c r="AM99" s="69"/>
+      <c r="AN99" s="70"/>
       <c r="AO99" s="12"/>
       <c r="AP99" s="29"/>
       <c r="AQ99" s="26"/>
@@ -7233,33 +7263,33 @@
       <c r="K100" s="84"/>
       <c r="L100" s="85"/>
       <c r="M100" s="26"/>
-      <c r="N100" s="69"/>
-      <c r="O100" s="70"/>
-      <c r="P100" s="71"/>
+      <c r="N100" s="71"/>
+      <c r="O100" s="72"/>
+      <c r="P100" s="73"/>
       <c r="Q100" s="31"/>
-      <c r="R100" s="69"/>
-      <c r="S100" s="70"/>
-      <c r="T100" s="71"/>
+      <c r="R100" s="71"/>
+      <c r="S100" s="72"/>
+      <c r="T100" s="73"/>
       <c r="U100" s="31"/>
-      <c r="V100" s="69"/>
-      <c r="W100" s="70"/>
-      <c r="X100" s="71"/>
+      <c r="V100" s="71"/>
+      <c r="W100" s="72"/>
+      <c r="X100" s="73"/>
       <c r="Y100" s="32"/>
-      <c r="Z100" s="69"/>
-      <c r="AA100" s="70"/>
-      <c r="AB100" s="71"/>
+      <c r="Z100" s="71"/>
+      <c r="AA100" s="72"/>
+      <c r="AB100" s="73"/>
       <c r="AC100" s="36"/>
-      <c r="AD100" s="69"/>
-      <c r="AE100" s="70"/>
-      <c r="AF100" s="71"/>
+      <c r="AD100" s="71"/>
+      <c r="AE100" s="72"/>
+      <c r="AF100" s="73"/>
       <c r="AG100" s="32"/>
-      <c r="AH100" s="69"/>
-      <c r="AI100" s="70"/>
-      <c r="AJ100" s="71"/>
+      <c r="AH100" s="71"/>
+      <c r="AI100" s="72"/>
+      <c r="AJ100" s="73"/>
       <c r="AK100" s="31"/>
-      <c r="AL100" s="69"/>
-      <c r="AM100" s="70"/>
-      <c r="AN100" s="71"/>
+      <c r="AL100" s="71"/>
+      <c r="AM100" s="72"/>
+      <c r="AN100" s="73"/>
       <c r="AO100" s="12"/>
       <c r="AP100" s="29"/>
       <c r="AQ100" s="26"/>
@@ -7267,45 +7297,45 @@
     </row>
     <row r="101" spans="1:44" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
-      <c r="B101" s="66"/>
-      <c r="C101" s="67"/>
-      <c r="D101" s="68"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="78"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="32"/>
-      <c r="F101" s="66"/>
-      <c r="G101" s="67"/>
-      <c r="H101" s="68"/>
+      <c r="F101" s="77"/>
+      <c r="G101" s="78"/>
+      <c r="H101" s="79"/>
       <c r="I101" s="31"/>
-      <c r="J101" s="66"/>
-      <c r="K101" s="67"/>
-      <c r="L101" s="68"/>
+      <c r="J101" s="77"/>
+      <c r="K101" s="78"/>
+      <c r="L101" s="79"/>
       <c r="M101" s="26"/>
-      <c r="N101" s="66"/>
-      <c r="O101" s="67"/>
-      <c r="P101" s="68"/>
+      <c r="N101" s="77"/>
+      <c r="O101" s="78"/>
+      <c r="P101" s="79"/>
       <c r="Q101" s="31"/>
-      <c r="R101" s="66"/>
-      <c r="S101" s="67"/>
-      <c r="T101" s="68"/>
+      <c r="R101" s="77"/>
+      <c r="S101" s="78"/>
+      <c r="T101" s="79"/>
       <c r="U101" s="32"/>
-      <c r="V101" s="66"/>
-      <c r="W101" s="67"/>
-      <c r="X101" s="68"/>
+      <c r="V101" s="77"/>
+      <c r="W101" s="78"/>
+      <c r="X101" s="79"/>
       <c r="Y101" s="32"/>
-      <c r="Z101" s="66"/>
-      <c r="AA101" s="67"/>
-      <c r="AB101" s="68"/>
+      <c r="Z101" s="77"/>
+      <c r="AA101" s="78"/>
+      <c r="AB101" s="79"/>
       <c r="AC101" s="31"/>
-      <c r="AD101" s="66"/>
-      <c r="AE101" s="67"/>
-      <c r="AF101" s="68"/>
+      <c r="AD101" s="77"/>
+      <c r="AE101" s="78"/>
+      <c r="AF101" s="79"/>
       <c r="AG101" s="32"/>
-      <c r="AH101" s="66"/>
-      <c r="AI101" s="67"/>
-      <c r="AJ101" s="68"/>
+      <c r="AH101" s="77"/>
+      <c r="AI101" s="78"/>
+      <c r="AJ101" s="79"/>
       <c r="AK101" s="31"/>
-      <c r="AL101" s="66"/>
-      <c r="AM101" s="67"/>
-      <c r="AN101" s="68"/>
+      <c r="AL101" s="77"/>
+      <c r="AM101" s="78"/>
+      <c r="AN101" s="79"/>
       <c r="AO101" s="12"/>
       <c r="AP101" s="29"/>
       <c r="AQ101" s="26"/>
@@ -7421,57 +7451,57 @@
       <c r="AR104" s="26"/>
     </row>
     <row r="105" spans="1:44" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="64"/>
-      <c r="C105" s="65"/>
+      <c r="B105" s="66"/>
+      <c r="C105" s="67"/>
       <c r="D105" s="34"/>
       <c r="E105" s="32"/>
-      <c r="F105" s="64"/>
-      <c r="G105" s="65"/>
+      <c r="F105" s="66"/>
+      <c r="G105" s="67"/>
       <c r="H105" s="34"/>
       <c r="I105" s="32"/>
-      <c r="J105" s="64"/>
-      <c r="K105" s="65"/>
+      <c r="J105" s="66"/>
+      <c r="K105" s="67"/>
       <c r="L105" s="34"/>
       <c r="AO105" s="26"/>
     </row>
     <row r="106" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="75"/>
-      <c r="C106" s="76"/>
-      <c r="D106" s="77"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="69"/>
+      <c r="D106" s="70"/>
       <c r="E106" s="32"/>
-      <c r="F106" s="75"/>
-      <c r="G106" s="76"/>
-      <c r="H106" s="77"/>
+      <c r="F106" s="68"/>
+      <c r="G106" s="69"/>
+      <c r="H106" s="70"/>
       <c r="I106" s="32"/>
-      <c r="J106" s="75"/>
-      <c r="K106" s="76"/>
-      <c r="L106" s="77"/>
+      <c r="J106" s="68"/>
+      <c r="K106" s="69"/>
+      <c r="L106" s="70"/>
     </row>
     <row r="107" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="69"/>
-      <c r="C107" s="70"/>
-      <c r="D107" s="71"/>
+      <c r="B107" s="71"/>
+      <c r="C107" s="72"/>
+      <c r="D107" s="73"/>
       <c r="E107" s="32"/>
-      <c r="F107" s="69"/>
-      <c r="G107" s="70"/>
-      <c r="H107" s="71"/>
+      <c r="F107" s="71"/>
+      <c r="G107" s="72"/>
+      <c r="H107" s="73"/>
       <c r="I107" s="32"/>
-      <c r="J107" s="69"/>
-      <c r="K107" s="70"/>
-      <c r="L107" s="71"/>
+      <c r="J107" s="71"/>
+      <c r="K107" s="72"/>
+      <c r="L107" s="73"/>
     </row>
     <row r="108" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="66"/>
-      <c r="C108" s="67"/>
-      <c r="D108" s="68"/>
+      <c r="B108" s="77"/>
+      <c r="C108" s="78"/>
+      <c r="D108" s="79"/>
       <c r="E108" s="32"/>
-      <c r="F108" s="66"/>
-      <c r="G108" s="67"/>
-      <c r="H108" s="68"/>
+      <c r="F108" s="77"/>
+      <c r="G108" s="78"/>
+      <c r="H108" s="79"/>
       <c r="I108" s="31"/>
-      <c r="J108" s="66"/>
-      <c r="K108" s="67"/>
-      <c r="L108" s="68"/>
+      <c r="J108" s="77"/>
+      <c r="K108" s="78"/>
+      <c r="L108" s="79"/>
     </row>
     <row r="109" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="61"/>
@@ -7500,56 +7530,56 @@
       <c r="L110" s="35"/>
     </row>
     <row r="111" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="64"/>
-      <c r="C111" s="65"/>
+      <c r="B111" s="66"/>
+      <c r="C111" s="67"/>
       <c r="D111" s="34"/>
       <c r="E111" s="31"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="65"/>
+      <c r="F111" s="66"/>
+      <c r="G111" s="67"/>
       <c r="H111" s="34"/>
       <c r="I111" s="31"/>
-      <c r="J111" s="64"/>
-      <c r="K111" s="65"/>
+      <c r="J111" s="66"/>
+      <c r="K111" s="67"/>
       <c r="L111" s="34"/>
     </row>
     <row r="112" spans="1:44" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="75"/>
-      <c r="C112" s="76"/>
-      <c r="D112" s="77"/>
+      <c r="B112" s="68"/>
+      <c r="C112" s="69"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="32"/>
-      <c r="F112" s="75"/>
-      <c r="G112" s="76"/>
-      <c r="H112" s="77"/>
+      <c r="F112" s="68"/>
+      <c r="G112" s="69"/>
+      <c r="H112" s="70"/>
       <c r="I112" s="32"/>
-      <c r="J112" s="75"/>
-      <c r="K112" s="76"/>
-      <c r="L112" s="77"/>
+      <c r="J112" s="68"/>
+      <c r="K112" s="69"/>
+      <c r="L112" s="70"/>
     </row>
     <row r="113" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="69"/>
-      <c r="C113" s="70"/>
-      <c r="D113" s="71"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="72"/>
+      <c r="D113" s="73"/>
       <c r="E113" s="35"/>
-      <c r="F113" s="69"/>
-      <c r="G113" s="70"/>
-      <c r="H113" s="71"/>
+      <c r="F113" s="71"/>
+      <c r="G113" s="72"/>
+      <c r="H113" s="73"/>
       <c r="I113" s="35"/>
-      <c r="J113" s="69"/>
-      <c r="K113" s="70"/>
-      <c r="L113" s="71"/>
+      <c r="J113" s="71"/>
+      <c r="K113" s="72"/>
+      <c r="L113" s="73"/>
     </row>
     <row r="114" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="66"/>
-      <c r="C114" s="67"/>
-      <c r="D114" s="68"/>
+      <c r="B114" s="77"/>
+      <c r="C114" s="78"/>
+      <c r="D114" s="79"/>
       <c r="E114" s="32"/>
-      <c r="F114" s="66"/>
-      <c r="G114" s="67"/>
-      <c r="H114" s="68"/>
+      <c r="F114" s="77"/>
+      <c r="G114" s="78"/>
+      <c r="H114" s="79"/>
       <c r="I114" s="32"/>
-      <c r="J114" s="66"/>
-      <c r="K114" s="67"/>
-      <c r="L114" s="68"/>
+      <c r="J114" s="77"/>
+      <c r="K114" s="78"/>
+      <c r="L114" s="79"/>
     </row>
     <row r="115" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="61"/>
@@ -7578,56 +7608,56 @@
       <c r="L116" s="35"/>
     </row>
     <row r="117" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="64"/>
-      <c r="C117" s="65"/>
+      <c r="B117" s="66"/>
+      <c r="C117" s="67"/>
       <c r="D117" s="34"/>
       <c r="E117" s="32"/>
-      <c r="F117" s="64"/>
-      <c r="G117" s="65"/>
+      <c r="F117" s="66"/>
+      <c r="G117" s="67"/>
       <c r="H117" s="34"/>
       <c r="I117" s="32"/>
-      <c r="J117" s="64"/>
-      <c r="K117" s="65"/>
+      <c r="J117" s="66"/>
+      <c r="K117" s="67"/>
       <c r="L117" s="34"/>
     </row>
     <row r="118" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="75"/>
-      <c r="C118" s="76"/>
-      <c r="D118" s="77"/>
+      <c r="B118" s="68"/>
+      <c r="C118" s="69"/>
+      <c r="D118" s="70"/>
       <c r="E118" s="32"/>
-      <c r="F118" s="75"/>
-      <c r="G118" s="76"/>
-      <c r="H118" s="77"/>
+      <c r="F118" s="68"/>
+      <c r="G118" s="69"/>
+      <c r="H118" s="70"/>
       <c r="I118" s="32"/>
-      <c r="J118" s="75"/>
-      <c r="K118" s="76"/>
-      <c r="L118" s="77"/>
+      <c r="J118" s="68"/>
+      <c r="K118" s="69"/>
+      <c r="L118" s="70"/>
     </row>
     <row r="119" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="69"/>
-      <c r="C119" s="70"/>
-      <c r="D119" s="71"/>
+      <c r="B119" s="71"/>
+      <c r="C119" s="72"/>
+      <c r="D119" s="73"/>
       <c r="E119" s="32"/>
-      <c r="F119" s="69"/>
-      <c r="G119" s="70"/>
-      <c r="H119" s="71"/>
+      <c r="F119" s="71"/>
+      <c r="G119" s="72"/>
+      <c r="H119" s="73"/>
       <c r="I119" s="32"/>
-      <c r="J119" s="69"/>
-      <c r="K119" s="70"/>
-      <c r="L119" s="71"/>
+      <c r="J119" s="71"/>
+      <c r="K119" s="72"/>
+      <c r="L119" s="73"/>
     </row>
     <row r="120" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="66"/>
-      <c r="C120" s="67"/>
-      <c r="D120" s="68"/>
+      <c r="B120" s="77"/>
+      <c r="C120" s="78"/>
+      <c r="D120" s="79"/>
       <c r="E120" s="32"/>
-      <c r="F120" s="66"/>
-      <c r="G120" s="67"/>
-      <c r="H120" s="68"/>
+      <c r="F120" s="77"/>
+      <c r="G120" s="78"/>
+      <c r="H120" s="79"/>
       <c r="I120" s="32"/>
-      <c r="J120" s="66"/>
-      <c r="K120" s="67"/>
-      <c r="L120" s="68"/>
+      <c r="J120" s="77"/>
+      <c r="K120" s="78"/>
+      <c r="L120" s="79"/>
     </row>
     <row r="121" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="61"/>
@@ -7656,56 +7686,56 @@
       <c r="L122" s="35"/>
     </row>
     <row r="123" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="64"/>
-      <c r="C123" s="65"/>
+      <c r="B123" s="66"/>
+      <c r="C123" s="67"/>
       <c r="D123" s="34"/>
       <c r="E123" s="32"/>
-      <c r="F123" s="64"/>
-      <c r="G123" s="65"/>
+      <c r="F123" s="66"/>
+      <c r="G123" s="67"/>
       <c r="H123" s="34"/>
       <c r="I123" s="32"/>
-      <c r="J123" s="64"/>
-      <c r="K123" s="65"/>
+      <c r="J123" s="66"/>
+      <c r="K123" s="67"/>
       <c r="L123" s="34"/>
     </row>
     <row r="124" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="75"/>
-      <c r="C124" s="76"/>
-      <c r="D124" s="77"/>
+      <c r="B124" s="68"/>
+      <c r="C124" s="69"/>
+      <c r="D124" s="70"/>
       <c r="E124" s="32"/>
-      <c r="F124" s="75"/>
-      <c r="G124" s="76"/>
-      <c r="H124" s="77"/>
+      <c r="F124" s="68"/>
+      <c r="G124" s="69"/>
+      <c r="H124" s="70"/>
       <c r="I124" s="32"/>
-      <c r="J124" s="75"/>
-      <c r="K124" s="76"/>
-      <c r="L124" s="77"/>
+      <c r="J124" s="68"/>
+      <c r="K124" s="69"/>
+      <c r="L124" s="70"/>
     </row>
     <row r="125" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="69"/>
-      <c r="C125" s="70"/>
-      <c r="D125" s="71"/>
+      <c r="B125" s="71"/>
+      <c r="C125" s="72"/>
+      <c r="D125" s="73"/>
       <c r="E125" s="32"/>
-      <c r="F125" s="69"/>
-      <c r="G125" s="70"/>
-      <c r="H125" s="71"/>
+      <c r="F125" s="71"/>
+      <c r="G125" s="72"/>
+      <c r="H125" s="73"/>
       <c r="I125" s="32"/>
-      <c r="J125" s="69"/>
-      <c r="K125" s="70"/>
-      <c r="L125" s="71"/>
+      <c r="J125" s="71"/>
+      <c r="K125" s="72"/>
+      <c r="L125" s="73"/>
     </row>
     <row r="126" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="66"/>
-      <c r="C126" s="67"/>
-      <c r="D126" s="68"/>
+      <c r="B126" s="77"/>
+      <c r="C126" s="78"/>
+      <c r="D126" s="79"/>
       <c r="E126" s="32"/>
-      <c r="F126" s="66"/>
-      <c r="G126" s="67"/>
-      <c r="H126" s="68"/>
+      <c r="F126" s="77"/>
+      <c r="G126" s="78"/>
+      <c r="H126" s="79"/>
       <c r="I126" s="31"/>
-      <c r="J126" s="66"/>
-      <c r="K126" s="67"/>
-      <c r="L126" s="68"/>
+      <c r="J126" s="77"/>
+      <c r="K126" s="78"/>
+      <c r="L126" s="79"/>
     </row>
     <row r="127" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="61"/>
@@ -7734,56 +7764,56 @@
       <c r="L128" s="35"/>
     </row>
     <row r="129" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="64"/>
-      <c r="C129" s="65"/>
+      <c r="B129" s="66"/>
+      <c r="C129" s="67"/>
       <c r="D129" s="34"/>
       <c r="E129" s="31"/>
-      <c r="F129" s="64"/>
-      <c r="G129" s="65"/>
+      <c r="F129" s="66"/>
+      <c r="G129" s="67"/>
       <c r="H129" s="34"/>
       <c r="I129" s="32"/>
-      <c r="J129" s="64"/>
-      <c r="K129" s="65"/>
+      <c r="J129" s="66"/>
+      <c r="K129" s="67"/>
       <c r="L129" s="34"/>
     </row>
     <row r="130" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="75"/>
-      <c r="C130" s="76"/>
-      <c r="D130" s="77"/>
+      <c r="B130" s="68"/>
+      <c r="C130" s="69"/>
+      <c r="D130" s="70"/>
       <c r="E130" s="32"/>
-      <c r="F130" s="75"/>
-      <c r="G130" s="76"/>
-      <c r="H130" s="77"/>
+      <c r="F130" s="68"/>
+      <c r="G130" s="69"/>
+      <c r="H130" s="70"/>
       <c r="I130" s="32"/>
-      <c r="J130" s="75"/>
-      <c r="K130" s="76"/>
-      <c r="L130" s="77"/>
+      <c r="J130" s="68"/>
+      <c r="K130" s="69"/>
+      <c r="L130" s="70"/>
     </row>
     <row r="131" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="69"/>
-      <c r="C131" s="70"/>
-      <c r="D131" s="71"/>
+      <c r="B131" s="71"/>
+      <c r="C131" s="72"/>
+      <c r="D131" s="73"/>
       <c r="E131" s="35"/>
-      <c r="F131" s="69"/>
-      <c r="G131" s="70"/>
-      <c r="H131" s="71"/>
+      <c r="F131" s="71"/>
+      <c r="G131" s="72"/>
+      <c r="H131" s="73"/>
       <c r="I131" s="32"/>
-      <c r="J131" s="69"/>
-      <c r="K131" s="70"/>
-      <c r="L131" s="71"/>
+      <c r="J131" s="71"/>
+      <c r="K131" s="72"/>
+      <c r="L131" s="73"/>
     </row>
     <row r="132" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="66"/>
-      <c r="C132" s="67"/>
-      <c r="D132" s="68"/>
+      <c r="B132" s="77"/>
+      <c r="C132" s="78"/>
+      <c r="D132" s="79"/>
       <c r="E132" s="35"/>
-      <c r="F132" s="66"/>
-      <c r="G132" s="67"/>
-      <c r="H132" s="68"/>
+      <c r="F132" s="77"/>
+      <c r="G132" s="78"/>
+      <c r="H132" s="79"/>
       <c r="I132" s="31"/>
-      <c r="J132" s="66"/>
-      <c r="K132" s="67"/>
-      <c r="L132" s="68"/>
+      <c r="J132" s="77"/>
+      <c r="K132" s="78"/>
+      <c r="L132" s="79"/>
     </row>
     <row r="133" spans="2:12" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="61"/>
@@ -7802,6 +7832,863 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="881">
+    <mergeCell ref="N57:P57"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="R53:T53"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AL35:AN35"/>
+    <mergeCell ref="AL32:AN32"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AL33:AN33"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AD33:AF33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AH20:AI20"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AL82:AN82"/>
+    <mergeCell ref="V62:X62"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="AH77:AJ77"/>
+    <mergeCell ref="AD78:AF78"/>
+    <mergeCell ref="AD82:AF82"/>
+    <mergeCell ref="AH63:AJ63"/>
+    <mergeCell ref="AH62:AJ62"/>
+    <mergeCell ref="AD62:AF62"/>
+    <mergeCell ref="AH80:AI80"/>
+    <mergeCell ref="AH82:AJ82"/>
+    <mergeCell ref="AH81:AJ81"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="AH76:AJ76"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="V71:X71"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="V64:X64"/>
+    <mergeCell ref="V69:X69"/>
+    <mergeCell ref="R69:T69"/>
+    <mergeCell ref="V70:X70"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="R70:T70"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="R77:T77"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R83:T83"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="R82:T82"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="R90:T90"/>
+    <mergeCell ref="R87:T87"/>
+    <mergeCell ref="V89:X89"/>
+    <mergeCell ref="AL100:AN100"/>
+    <mergeCell ref="AH87:AJ87"/>
+    <mergeCell ref="AH88:AJ88"/>
+    <mergeCell ref="AH89:AJ89"/>
+    <mergeCell ref="AH90:AJ90"/>
+    <mergeCell ref="AH83:AJ83"/>
+    <mergeCell ref="AD84:AF84"/>
+    <mergeCell ref="AH84:AJ84"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD83:AF83"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AN99"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL88:AN88"/>
+    <mergeCell ref="AL89:AN89"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL83:AN83"/>
+    <mergeCell ref="AL84:AN84"/>
+    <mergeCell ref="AH86:AI86"/>
+    <mergeCell ref="AH95:AJ95"/>
+    <mergeCell ref="AH92:AI92"/>
+    <mergeCell ref="AH93:AJ93"/>
+    <mergeCell ref="AH94:AJ94"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AL81:AN81"/>
+    <mergeCell ref="AL77:AN77"/>
+    <mergeCell ref="AL78:AN78"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL76:AN76"/>
+    <mergeCell ref="AD76:AF76"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="R78:T78"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="Z78:AB78"/>
+    <mergeCell ref="R81:T81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="Z81:AB81"/>
+    <mergeCell ref="AL102:AN102"/>
+    <mergeCell ref="AL101:AN101"/>
+    <mergeCell ref="AL96:AN96"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AH102:AJ102"/>
+    <mergeCell ref="AL90:AN90"/>
+    <mergeCell ref="AL95:AN95"/>
+    <mergeCell ref="AL87:AN87"/>
+    <mergeCell ref="AD101:AF101"/>
+    <mergeCell ref="AH101:AJ101"/>
+    <mergeCell ref="AH98:AI98"/>
+    <mergeCell ref="AD99:AF99"/>
+    <mergeCell ref="AH100:AJ100"/>
+    <mergeCell ref="AL93:AN93"/>
+    <mergeCell ref="AL94:AN94"/>
+    <mergeCell ref="AH99:AJ99"/>
+    <mergeCell ref="AD100:AF100"/>
+    <mergeCell ref="AD96:AF96"/>
+    <mergeCell ref="AD94:AF94"/>
+    <mergeCell ref="AD95:AF95"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AH96:AJ96"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="AD87:AF87"/>
+    <mergeCell ref="AL60:AN60"/>
+    <mergeCell ref="AL62:AN62"/>
+    <mergeCell ref="AL63:AN63"/>
+    <mergeCell ref="AL72:AN72"/>
+    <mergeCell ref="AL71:AN71"/>
+    <mergeCell ref="AL70:AN70"/>
+    <mergeCell ref="AL69:AN69"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AL73:AN73"/>
+    <mergeCell ref="AL75:AM75"/>
+    <mergeCell ref="AH75:AJ75"/>
+    <mergeCell ref="AD71:AF71"/>
+    <mergeCell ref="AH68:AI68"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AH70:AJ70"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AD75:AF75"/>
+    <mergeCell ref="AH72:AJ72"/>
+    <mergeCell ref="AD72:AF72"/>
+    <mergeCell ref="AH74:AI74"/>
+    <mergeCell ref="AH71:AJ71"/>
+    <mergeCell ref="AD69:AF69"/>
+    <mergeCell ref="AH69:AJ69"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AH61:AJ61"/>
+    <mergeCell ref="AL64:AN64"/>
+    <mergeCell ref="AL61:AN61"/>
+    <mergeCell ref="AD64:AF64"/>
+    <mergeCell ref="AD63:AF63"/>
+    <mergeCell ref="AH64:AJ64"/>
+    <mergeCell ref="AD61:AF61"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AH54:AJ54"/>
+    <mergeCell ref="AH55:AJ55"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AD55:AF55"/>
+    <mergeCell ref="AD56:AF56"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AH25:AI25"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AH57:AJ57"/>
+    <mergeCell ref="AH59:AI59"/>
+    <mergeCell ref="AH56:AJ56"/>
+    <mergeCell ref="AH53:AJ53"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="AH42:AJ42"/>
+    <mergeCell ref="AH43:AJ43"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AD57:AF57"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AH24:AI24"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AH23:AI23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AH22:AI22"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N29:AB30"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N4:AB5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="B4:L5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AD4:AN5"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="F78:H78"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="F106:H106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="AD40:AF40"/>
+    <mergeCell ref="AD41:AF41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="AD42:AF42"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AH40:AJ40"/>
+    <mergeCell ref="V41:X41"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AH21:AI21"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="AH31:AI31"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="AH15:AJ15"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="AH13:AJ13"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="F77:H77"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="J112:L112"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="N18:AB19"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="F127:H127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:H130"/>
+    <mergeCell ref="J130:L130"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="J132:L132"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="J131:L131"/>
+    <mergeCell ref="J99:L99"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="J126:L126"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="J121:L121"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="J101:L101"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="J114:L114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="J115:L115"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J124:L124"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="J119:L119"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="R89:T89"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="J87:L87"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="R93:T93"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="V93:X93"/>
+    <mergeCell ref="J94:L94"/>
+    <mergeCell ref="J95:L95"/>
+    <mergeCell ref="V94:X94"/>
+    <mergeCell ref="V96:X96"/>
+    <mergeCell ref="V95:X95"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="Z96:AB96"/>
+    <mergeCell ref="R95:T95"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="R96:T96"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="Z93:AB93"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="Z102:AB102"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="R99:T99"/>
+    <mergeCell ref="V102:X102"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="V101:X101"/>
+    <mergeCell ref="Z101:AB101"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB95"/>
+    <mergeCell ref="R102:T102"/>
+    <mergeCell ref="R100:T100"/>
+    <mergeCell ref="V99:X99"/>
+    <mergeCell ref="Z99:AB99"/>
+    <mergeCell ref="V100:X100"/>
+    <mergeCell ref="R101:T101"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="Z100:AB100"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:T94"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="R60:T60"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="V60:X60"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="V82:X82"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="R72:T72"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:T76"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="N66:AB67"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="J102:L102"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="J75:L75"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J81:L81"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="R84:T84"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="J100:L100"/>
+    <mergeCell ref="J88:L88"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="J72:L72"/>
+    <mergeCell ref="J76:L76"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="J70:L70"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="F76:H76"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="AD88:AF88"/>
+    <mergeCell ref="V75:X75"/>
+    <mergeCell ref="Z75:AB75"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="AD89:AF89"/>
+    <mergeCell ref="AD90:AF90"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="V90:X90"/>
+    <mergeCell ref="V87:X87"/>
+    <mergeCell ref="V88:X88"/>
+    <mergeCell ref="Z82:AB82"/>
+    <mergeCell ref="Z76:AB76"/>
+    <mergeCell ref="Z77:AB77"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="Z87:AB87"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="Z83:AB83"/>
+    <mergeCell ref="Z84:AB84"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="R88:T88"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AL50:AN50"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AL57:AN57"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AL40:AN40"/>
+    <mergeCell ref="AL41:AN41"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AL48:AN48"/>
+    <mergeCell ref="AL56:AN56"/>
+    <mergeCell ref="AL54:AN54"/>
+    <mergeCell ref="AL53:AN53"/>
+    <mergeCell ref="AL49:AN49"/>
+    <mergeCell ref="AL55:AN55"/>
+    <mergeCell ref="AL37:AN37"/>
+    <mergeCell ref="AL39:AM39"/>
+    <mergeCell ref="AL43:AN43"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="V37:X37"/>
+    <mergeCell ref="V39:W39"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="Z48:AB48"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="J37:L37"/>
     <mergeCell ref="B39:C39"/>
@@ -7826,869 +8713,12 @@
     <mergeCell ref="AH50:AJ50"/>
     <mergeCell ref="AH52:AI52"/>
     <mergeCell ref="AH37:AJ37"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="V37:X37"/>
-    <mergeCell ref="V39:W39"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="AL42:AN42"/>
-    <mergeCell ref="AL50:AN50"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AL57:AN57"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AL40:AN40"/>
-    <mergeCell ref="AL41:AN41"/>
-    <mergeCell ref="AL47:AN47"/>
-    <mergeCell ref="AL48:AN48"/>
-    <mergeCell ref="AL56:AN56"/>
-    <mergeCell ref="AL54:AN54"/>
-    <mergeCell ref="AL53:AN53"/>
-    <mergeCell ref="AL49:AN49"/>
-    <mergeCell ref="AL55:AN55"/>
-    <mergeCell ref="AL37:AN37"/>
-    <mergeCell ref="AL39:AM39"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="R42:T42"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="J47:L47"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="AD88:AF88"/>
-    <mergeCell ref="V75:X75"/>
-    <mergeCell ref="Z75:AB75"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="AD89:AF89"/>
-    <mergeCell ref="AD90:AF90"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="N88:P88"/>
-    <mergeCell ref="V90:X90"/>
-    <mergeCell ref="V87:X87"/>
-    <mergeCell ref="V88:X88"/>
-    <mergeCell ref="Z82:AB82"/>
-    <mergeCell ref="Z76:AB76"/>
-    <mergeCell ref="Z77:AB77"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="Z87:AB87"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="Z83:AB83"/>
-    <mergeCell ref="Z84:AB84"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="R88:T88"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="J70:L70"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="F76:H76"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="J69:L69"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="J102:L102"/>
-    <mergeCell ref="N54:P54"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="J75:L75"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="J84:L84"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J81:L81"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="R84:T84"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="J100:L100"/>
-    <mergeCell ref="J88:L88"/>
-    <mergeCell ref="J77:L77"/>
-    <mergeCell ref="J72:L72"/>
-    <mergeCell ref="J76:L76"/>
-    <mergeCell ref="N71:P71"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="R60:T60"/>
-    <mergeCell ref="N92:O92"/>
-    <mergeCell ref="J78:L78"/>
-    <mergeCell ref="V60:X60"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="N61:P61"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="V82:X82"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="V76:X76"/>
-    <mergeCell ref="R72:T72"/>
-    <mergeCell ref="R71:T71"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:T76"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="N66:AB67"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="N63:P63"/>
-    <mergeCell ref="N69:P69"/>
-    <mergeCell ref="Z102:AB102"/>
-    <mergeCell ref="N99:P99"/>
-    <mergeCell ref="R99:T99"/>
-    <mergeCell ref="V102:X102"/>
-    <mergeCell ref="N101:P101"/>
-    <mergeCell ref="N95:P95"/>
-    <mergeCell ref="V101:X101"/>
-    <mergeCell ref="Z101:AB101"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB95"/>
-    <mergeCell ref="R102:T102"/>
-    <mergeCell ref="R100:T100"/>
-    <mergeCell ref="V99:X99"/>
-    <mergeCell ref="Z99:AB99"/>
-    <mergeCell ref="V100:X100"/>
-    <mergeCell ref="R101:T101"/>
-    <mergeCell ref="N100:P100"/>
-    <mergeCell ref="Z100:AB100"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="R94:T94"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="B120:D120"/>
-    <mergeCell ref="R89:T89"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="J87:L87"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="R93:T93"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="V93:X93"/>
-    <mergeCell ref="J94:L94"/>
-    <mergeCell ref="J95:L95"/>
-    <mergeCell ref="V94:X94"/>
-    <mergeCell ref="V96:X96"/>
-    <mergeCell ref="V95:X95"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="Z96:AB96"/>
-    <mergeCell ref="R95:T95"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="N96:P96"/>
-    <mergeCell ref="R96:T96"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="Z93:AB93"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B124:D124"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="N102:P102"/>
-    <mergeCell ref="B119:D119"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="F115:H115"/>
-    <mergeCell ref="J115:L115"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J124:L124"/>
-    <mergeCell ref="F119:H119"/>
-    <mergeCell ref="J119:L119"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="J99:L99"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:H126"/>
-    <mergeCell ref="J126:L126"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="J123:K123"/>
-    <mergeCell ref="F112:H112"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="F125:H125"/>
-    <mergeCell ref="J121:L121"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="J101:L101"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:H127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:H130"/>
-    <mergeCell ref="J130:L130"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="J132:L132"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="J131:L131"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="J112:L112"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="F120:H120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="N18:AB19"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AL10:AN10"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH15:AJ15"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AL13:AN13"/>
-    <mergeCell ref="AH13:AJ13"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="AD34:AF34"/>
-    <mergeCell ref="AH40:AJ40"/>
-    <mergeCell ref="V41:X41"/>
-    <mergeCell ref="V40:X40"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AH26:AI26"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AH21:AI21"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="AH31:AI31"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="AD40:AF40"/>
-    <mergeCell ref="AD41:AF41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="AD42:AF42"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="F106:H106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="R43:T43"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="F78:H78"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AD4:AN5"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="B4:L5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="N4:AB5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="R57:T57"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AH23:AI23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AH22:AI22"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N29:AB30"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="Z60:AB60"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z54:AB54"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AH57:AJ57"/>
-    <mergeCell ref="AH59:AI59"/>
-    <mergeCell ref="AH56:AJ56"/>
-    <mergeCell ref="AH53:AJ53"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AH36:AJ36"/>
-    <mergeCell ref="AH42:AJ42"/>
-    <mergeCell ref="AH43:AJ43"/>
-    <mergeCell ref="AD35:AF35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="Z56:AB56"/>
-    <mergeCell ref="AD57:AF57"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="AH61:AJ61"/>
-    <mergeCell ref="AL64:AN64"/>
-    <mergeCell ref="AL61:AN61"/>
-    <mergeCell ref="AD64:AF64"/>
-    <mergeCell ref="AD63:AF63"/>
-    <mergeCell ref="AH64:AJ64"/>
-    <mergeCell ref="AD61:AF61"/>
-    <mergeCell ref="Z63:AB63"/>
-    <mergeCell ref="AH54:AJ54"/>
-    <mergeCell ref="AH55:AJ55"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AD55:AF55"/>
-    <mergeCell ref="AD56:AF56"/>
-    <mergeCell ref="AH75:AJ75"/>
-    <mergeCell ref="AD71:AF71"/>
-    <mergeCell ref="AH68:AI68"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AH70:AJ70"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AD75:AF75"/>
-    <mergeCell ref="AH72:AJ72"/>
-    <mergeCell ref="AD72:AF72"/>
-    <mergeCell ref="AH74:AI74"/>
-    <mergeCell ref="AH71:AJ71"/>
-    <mergeCell ref="AD69:AF69"/>
-    <mergeCell ref="AH69:AJ69"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AL75:AN75"/>
-    <mergeCell ref="AL60:AN60"/>
-    <mergeCell ref="AL62:AN62"/>
-    <mergeCell ref="AL63:AN63"/>
-    <mergeCell ref="AL72:AN72"/>
-    <mergeCell ref="AL71:AN71"/>
-    <mergeCell ref="AL70:AN70"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AL69:AN69"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AL102:AN102"/>
-    <mergeCell ref="AL101:AN101"/>
-    <mergeCell ref="AL96:AN96"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AH102:AJ102"/>
-    <mergeCell ref="AL90:AN90"/>
-    <mergeCell ref="AL95:AN95"/>
-    <mergeCell ref="AL87:AN87"/>
-    <mergeCell ref="AD101:AF101"/>
-    <mergeCell ref="AH101:AJ101"/>
-    <mergeCell ref="AH98:AI98"/>
-    <mergeCell ref="AD99:AF99"/>
-    <mergeCell ref="AH100:AJ100"/>
-    <mergeCell ref="AL93:AN93"/>
-    <mergeCell ref="AL94:AN94"/>
-    <mergeCell ref="AH99:AJ99"/>
-    <mergeCell ref="AD100:AF100"/>
-    <mergeCell ref="AD96:AF96"/>
-    <mergeCell ref="AD94:AF94"/>
-    <mergeCell ref="AD95:AF95"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AH96:AJ96"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="AD87:AF87"/>
-    <mergeCell ref="AL81:AN81"/>
-    <mergeCell ref="AL77:AN77"/>
-    <mergeCell ref="AL78:AN78"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL76:AN76"/>
-    <mergeCell ref="AD76:AF76"/>
-    <mergeCell ref="N78:P78"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="R78:T78"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="Z78:AB78"/>
-    <mergeCell ref="R81:T81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="Z81:AB81"/>
-    <mergeCell ref="AL100:AN100"/>
-    <mergeCell ref="AH87:AJ87"/>
-    <mergeCell ref="AH88:AJ88"/>
-    <mergeCell ref="AH89:AJ89"/>
-    <mergeCell ref="AH90:AJ90"/>
-    <mergeCell ref="AH83:AJ83"/>
-    <mergeCell ref="AD84:AF84"/>
-    <mergeCell ref="AH84:AJ84"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="AD83:AF83"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AN99"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL88:AN88"/>
-    <mergeCell ref="AL89:AN89"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL83:AN83"/>
-    <mergeCell ref="AL84:AN84"/>
-    <mergeCell ref="AH86:AI86"/>
-    <mergeCell ref="AH95:AJ95"/>
-    <mergeCell ref="AH92:AI92"/>
-    <mergeCell ref="AH93:AJ93"/>
-    <mergeCell ref="AH94:AJ94"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="N90:P90"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="R77:T77"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R83:T83"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="R82:T82"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="R90:T90"/>
-    <mergeCell ref="R87:T87"/>
-    <mergeCell ref="V89:X89"/>
-    <mergeCell ref="Z70:AB70"/>
-    <mergeCell ref="V71:X71"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Z72:AB72"/>
-    <mergeCell ref="Z71:AB71"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="R63:T63"/>
-    <mergeCell ref="V64:X64"/>
-    <mergeCell ref="V69:X69"/>
-    <mergeCell ref="R69:T69"/>
-    <mergeCell ref="V70:X70"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="Z62:AB62"/>
-    <mergeCell ref="Z61:AB61"/>
-    <mergeCell ref="R70:T70"/>
-    <mergeCell ref="R64:T64"/>
-    <mergeCell ref="R61:T61"/>
-    <mergeCell ref="V61:X61"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="AL82:AN82"/>
-    <mergeCell ref="V62:X62"/>
-    <mergeCell ref="V63:X63"/>
-    <mergeCell ref="AH77:AJ77"/>
-    <mergeCell ref="AD78:AF78"/>
-    <mergeCell ref="AD82:AF82"/>
-    <mergeCell ref="AH63:AJ63"/>
-    <mergeCell ref="AH62:AJ62"/>
-    <mergeCell ref="AD62:AF62"/>
-    <mergeCell ref="AH80:AI80"/>
-    <mergeCell ref="AH82:AJ82"/>
-    <mergeCell ref="AH81:AJ81"/>
-    <mergeCell ref="AH78:AJ78"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AH76:AJ76"/>
-    <mergeCell ref="Z64:AB64"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="R56:T56"/>
-    <mergeCell ref="Z69:AB69"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AL34:AN34"/>
-    <mergeCell ref="AL35:AN35"/>
-    <mergeCell ref="AL32:AN32"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AL33:AN33"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AH27:AI27"/>
-    <mergeCell ref="AD33:AF33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AH20:AI20"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="N57:P57"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="V55:X55"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V47:X47"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="R53:T53"/>
-    <mergeCell ref="V53:X53"/>
-    <mergeCell ref="R54:T54"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="R49:T49"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="T22:T27 AB22:AB27 AF22:AF27 D22:D27 AJ22:AJ27 AN22:AN27 X22:X27 L22:L27 H22:H27 P22:P27">
       <formula1>$AP$68:$AP$71</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R42:T43 AH14:AJ16 AH22:AI27 N42:P43 R48:T50 R22:S27 B101:D102 J132:L133 AD89:AF90 V62:X64 N77:P78 V42:X43 N95:P96 F14:H16 V22:W27 AH62:AJ64 AL101:AN102 J77:L78 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 V83:X84 AH95:AJ96 R8:T10 F89:H90 B108:D109 AL42:AN43 Z14:AB16 AH42:AJ43 R14:T16 F101:H102 AL14:AN16 J95:L96 AH48:AJ50 AD83:AF84 B71:D72 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 AL83:AN84 Z101:AB102 Z34:AB37 AL89:AN90 Z77:AB78 AD22:AE27 V14:X16 AL22:AM27 F108:H109 AL55:AN57 AL71:AN72 Z62:AB64 AH83:AJ84 J83:L84 AH34:AJ37 J8:L10 AH77:AJ78 R77:T78 J89:L90 AD62:AF64 N22:O27 F62:H64 Z42:AB43 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 V55:X57 N34:P37 Z83:AB84 N101:P102 AH71:AJ72 Z71:AB72 V95:X96 N55:P57 F83:H84 B83:D84 Z22:AA27 N48:P50 Z48:AB50 AD42:AF43 AH101:AJ102 AH89:AJ90 R83:T84 AD48:AF50 Z8:AB10 J62:L64 AL8:AN10 V89:X90 N8:P10 F71:H72 AL62:AN64 AL95:AN96 V101:X102 Z95:AB96 AD34:AF37 B89:D90 Z89:AB90 R62:T64 N71:P72 F77:H78 J22:K27 F22:G27 J101:L102 Z55:AB57 B95:D96 B77:D78 F95:H96 R34:T37 J71:L72 B8:D10 AD71:AF72 AL48:AN50 V77:X78 AD55:AF57 J14:L16 AH55:AJ57 B14:D16 B22:C27 R71:T72 V48:X50 N83:P84 AL34:AN37 V34:X37 AL77:AN78 R55:T57 V71:X72 F8:H10 B62:D64 F55:H57 F42:H43 B34:D37 B55:D57 B42:D43 J34:L37 J42:L43 B48:D50 F48:H50 F34:H37 J55:L57 J48:L50 N62:P64 AD77:AF78">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Yazım Hatası" error="İstanbul Ses Servisinde olmayan bir isim girdiniz." promptTitle="uuuuuuuuuu" prompt="yyyyyyyyyyyy" sqref="R42:T43 AH14:AJ16 AH22:AI27 N42:P43 R48:T50 R22:S27 B101:D102 J132:L133 AD89:AF90 V62:X64 N77:P78 V42:X43 N95:P96 F14:H16 V22:W27 AH62:AJ64 AL101:AN102 J77:L78 V8:X10 R101:T102 AD95:AF96 J114:L115 AD8:AF10 V83:X84 AH95:AJ96 R8:T10 F89:H90 B108:D109 AL42:AN43 Z14:AB16 AH42:AJ43 R14:T16 F101:H102 AL14:AN16 J95:L96 AH48:AJ50 AL71:AN73 B71:D72 N89:P90 J120:L121 F114:H115 F126:H127 F132:H133 B120:D121 J108:L109 F120:H121 B132:D133 B126:D127 AD14:AF16 B114:D115 J126:L127 AL83:AN84 Z101:AB102 Z34:AB37 AL89:AN90 Z77:AB78 AD22:AE27 V14:X16 AL22:AM27 F108:H109 AL34:AN37 AL55:AN57 Z62:AB64 AH83:AJ84 J83:L84 AH34:AJ37 J8:L10 AH77:AJ78 R77:T78 J89:L90 AD62:AF64 N22:O27 F62:H64 Z42:AB43 R89:T90 AD101:AF102 N14:P16 R95:T96 AH8:AJ10 V55:X57 N34:P37 Z83:AB84 N101:P102 AH71:AJ72 Z71:AB72 V95:X96 N55:P57 F83:H84 B83:D84 Z22:AA27 N48:P50 Z48:AB50 AD42:AF43 AH101:AJ102 AH89:AJ90 R83:T84 AD48:AF50 Z8:AB10 J62:L64 AL8:AN10 V89:X90 N8:P10 F71:H72 AL62:AN64 AL95:AN96 V101:X102 Z95:AB96 AD34:AF37 B89:D90 Z89:AB90 R62:T64 N71:P72 F77:H78 J22:K27 F22:G27 J101:L102 Z55:AB57 B95:D96 B77:D78 F95:H96 R34:T37 J71:L72 B8:D10 AD71:AF72 AL48:AN50 V77:X78 AD55:AF57 J14:L16 AH55:AJ57 B14:D16 B22:C27 R71:T72 V48:X50 N83:P84 AD77:AF78 V34:X37 AL77:AN78 R55:T57 V71:X72 F8:H10 B62:D64 F55:H57 F42:H43 B34:D37 B55:D57 B42:D43 J34:L37 J42:L43 B48:D50 F48:H50 F34:H37 J55:L57 J48:L50 N62:P64 AD83:AF84">
       <formula1>$AP$6:$AP$30</formula1>
     </dataValidation>
   </dataValidations>
